--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -47,12 +47,6 @@
     <t>Confirmado c/ Fornecedor</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Não Concluídos</t>
-  </si>
-  <si>
     <t>MARCO AURÉLIO SIMÃO FREIRE</t>
   </si>
   <si>
@@ -66,6 +60,12 @@
   </si>
   <si>
     <t>SUN MORITZ ADMINISTRADORA</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Não Concluídos</t>
   </si>
   <si>
     <t>MARIA BELTRÃO SALDANHA COELHO</t>
@@ -411,7 +411,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H482"/>
+  <dimension ref="A1:H483"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -1667,10 +1667,10 @@
         <v>46085</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="49">
@@ -1782,7 +1782,7 @@
         <v>2316</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C53" s="2">
         <v>84</v>
@@ -1808,7 +1808,7 @@
         <v>2316</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C54" s="2">
         <v>84</v>
@@ -1823,10 +1823,10 @@
         <v>46030</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="55">
@@ -1834,7 +1834,7 @@
         <v>2316</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C55" s="2">
         <v>85</v>
@@ -1860,7 +1860,7 @@
         <v>2316</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C56" s="2">
         <v>85</v>
@@ -1886,7 +1886,7 @@
         <v>2316</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C57" s="2">
         <v>85</v>
@@ -1912,7 +1912,7 @@
         <v>2316</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C58" s="2">
         <v>86</v>
@@ -1938,7 +1938,7 @@
         <v>2316</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C59" s="2">
         <v>87</v>
@@ -1964,7 +1964,7 @@
         <v>2316</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C60" s="2">
         <v>87</v>
@@ -1990,7 +1990,7 @@
         <v>2317</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C61" s="2">
         <v>64</v>
@@ -2016,7 +2016,7 @@
         <v>2317</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C62" s="2">
         <v>64</v>
@@ -2042,7 +2042,7 @@
         <v>2317</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C63" s="2">
         <v>64</v>
@@ -2068,7 +2068,7 @@
         <v>2317</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C64" s="2">
         <v>64</v>
@@ -2094,7 +2094,7 @@
         <v>2317</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C65" s="2">
         <v>64</v>
@@ -2120,7 +2120,7 @@
         <v>2317</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C66" s="2">
         <v>65</v>
@@ -2146,7 +2146,7 @@
         <v>2317</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C67" s="2">
         <v>66</v>
@@ -2172,7 +2172,7 @@
         <v>2317</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C68" s="2">
         <v>66</v>
@@ -2198,7 +2198,7 @@
         <v>2317</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C69" s="2">
         <v>66</v>
@@ -2224,7 +2224,7 @@
         <v>2317</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C70" s="2">
         <v>66</v>
@@ -2250,7 +2250,7 @@
         <v>2317</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C71" s="2">
         <v>67</v>
@@ -2276,7 +2276,7 @@
         <v>2317</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C72" s="2">
         <v>67</v>
@@ -2302,7 +2302,7 @@
         <v>2317</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C73" s="2">
         <v>67</v>
@@ -2328,7 +2328,7 @@
         <v>2317</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C74" s="2">
         <v>68</v>
@@ -2354,7 +2354,7 @@
         <v>2317</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C75" s="2">
         <v>69</v>
@@ -2380,7 +2380,7 @@
         <v>2317</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C76" s="2">
         <v>69</v>
@@ -2406,7 +2406,7 @@
         <v>2317</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C77" s="2">
         <v>69</v>
@@ -2432,7 +2432,7 @@
         <v>2317</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C78" s="2">
         <v>70</v>
@@ -2458,7 +2458,7 @@
         <v>2317</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C79" s="2">
         <v>70</v>
@@ -2484,7 +2484,7 @@
         <v>2317</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C80" s="2">
         <v>71</v>
@@ -2510,7 +2510,7 @@
         <v>2317</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C81" s="2">
         <v>72</v>
@@ -2536,7 +2536,7 @@
         <v>2317</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C82" s="2">
         <v>72</v>
@@ -2562,7 +2562,7 @@
         <v>2317</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C83" s="2">
         <v>73</v>
@@ -2588,7 +2588,7 @@
         <v>2317</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C84" s="2">
         <v>73</v>
@@ -2614,7 +2614,7 @@
         <v>2317</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C85" s="2">
         <v>74</v>
@@ -2640,7 +2640,7 @@
         <v>2317</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C86" s="2">
         <v>74</v>
@@ -2666,7 +2666,7 @@
         <v>2407</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C87" s="2">
         <v>79</v>
@@ -2692,7 +2692,7 @@
         <v>2407</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C88" s="2">
         <v>79</v>
@@ -2718,7 +2718,7 @@
         <v>2407</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C89" s="2">
         <v>80</v>
@@ -2744,7 +2744,7 @@
         <v>2407</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C90" s="2">
         <v>80</v>
@@ -2770,7 +2770,7 @@
         <v>2407</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C91" s="2">
         <v>80</v>
@@ -2796,7 +2796,7 @@
         <v>2407</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C92" s="2">
         <v>80</v>
@@ -2822,7 +2822,7 @@
         <v>2407</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C93" s="2">
         <v>81</v>
@@ -2848,7 +2848,7 @@
         <v>2407</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C94" s="2">
         <v>81</v>
@@ -2874,7 +2874,7 @@
         <v>2407</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C95" s="2">
         <v>82</v>
@@ -2900,7 +2900,7 @@
         <v>2407</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C96" s="2">
         <v>82</v>
@@ -2926,7 +2926,7 @@
         <v>2407</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C97" s="2">
         <v>82</v>
@@ -2952,7 +2952,7 @@
         <v>2407</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C98" s="2">
         <v>82</v>
@@ -2978,7 +2978,7 @@
         <v>2407</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C99" s="2">
         <v>82</v>
@@ -3004,7 +3004,7 @@
         <v>2407</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C100" s="2">
         <v>82</v>
@@ -3030,7 +3030,7 @@
         <v>2407</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C101" s="2">
         <v>83</v>
@@ -3056,7 +3056,7 @@
         <v>2407</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C102" s="2">
         <v>83</v>
@@ -3082,7 +3082,7 @@
         <v>2407</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C103" s="2">
         <v>84</v>
@@ -3108,7 +3108,7 @@
         <v>2407</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C104" s="2">
         <v>84</v>
@@ -3134,7 +3134,7 @@
         <v>2407</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C105" s="2">
         <v>84</v>
@@ -3157,28 +3157,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="106">
       <c r="A106" s="2">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C106" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D106" s="3">
-        <v>46014.6980340162</v>
+        <v>46087.643003044</v>
       </c>
       <c r="E106" s="2">
-        <v>81460</v>
+        <v>82489</v>
       </c>
       <c r="F106" s="3">
-        <v>46027</v>
+        <v>46087</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="107">
@@ -3195,7 +3195,7 @@
         <v>46014.6980340162</v>
       </c>
       <c r="E107" s="2">
-        <v>81461</v>
+        <v>81460</v>
       </c>
       <c r="F107" s="3">
         <v>46027</v>
@@ -3221,7 +3221,7 @@
         <v>46014.6980340162</v>
       </c>
       <c r="E108" s="2">
-        <v>81463</v>
+        <v>81461</v>
       </c>
       <c r="F108" s="3">
         <v>46027</v>
@@ -3241,16 +3241,16 @@
         <v>18</v>
       </c>
       <c r="C109" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D109" s="3">
-        <v>46030.4707423958</v>
+        <v>46014.6980340162</v>
       </c>
       <c r="E109" s="2">
-        <v>81542</v>
+        <v>81463</v>
       </c>
       <c r="F109" s="3">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>9</v>
@@ -3273,7 +3273,7 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E110" s="2">
-        <v>81548</v>
+        <v>81542</v>
       </c>
       <c r="F110" s="3">
         <v>46030</v>
@@ -3299,7 +3299,7 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E111" s="2">
-        <v>81549</v>
+        <v>81548</v>
       </c>
       <c r="F111" s="3">
         <v>46030</v>
@@ -3325,10 +3325,10 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E112" s="2">
-        <v>81569</v>
+        <v>81549</v>
       </c>
       <c r="F112" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>9</v>
@@ -3345,16 +3345,16 @@
         <v>18</v>
       </c>
       <c r="C113" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D113" s="3">
-        <v>46037.6468124884</v>
+        <v>46030.4707423958</v>
       </c>
       <c r="E113" s="2">
-        <v>81669</v>
+        <v>81569</v>
       </c>
       <c r="F113" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>9</v>
@@ -3377,7 +3377,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E114" s="2">
-        <v>81670</v>
+        <v>81669</v>
       </c>
       <c r="F114" s="3">
         <v>46037</v>
@@ -3403,10 +3403,10 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E115" s="2">
-        <v>81673</v>
+        <v>81670</v>
       </c>
       <c r="F115" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>9</v>
@@ -3429,7 +3429,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E116" s="2">
-        <v>81682</v>
+        <v>81673</v>
       </c>
       <c r="F116" s="3">
         <v>46038</v>
@@ -3455,7 +3455,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E117" s="2">
-        <v>81689</v>
+        <v>81682</v>
       </c>
       <c r="F117" s="3">
         <v>46038</v>
@@ -3475,16 +3475,16 @@
         <v>18</v>
       </c>
       <c r="C118" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D118" s="3">
-        <v>46038.5944713773</v>
+        <v>46037.6468124884</v>
       </c>
       <c r="E118" s="2">
-        <v>81707</v>
+        <v>81689</v>
       </c>
       <c r="F118" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>9</v>
@@ -3501,16 +3501,16 @@
         <v>18</v>
       </c>
       <c r="C119" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D119" s="3">
-        <v>46049.490160081</v>
+        <v>46038.5944713773</v>
       </c>
       <c r="E119" s="2">
-        <v>81866</v>
+        <v>81707</v>
       </c>
       <c r="F119" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>9</v>
@@ -3533,7 +3533,7 @@
         <v>46049.490160081</v>
       </c>
       <c r="E120" s="2">
-        <v>81867</v>
+        <v>81866</v>
       </c>
       <c r="F120" s="3">
         <v>46049</v>
@@ -3559,7 +3559,7 @@
         <v>46049.490160081</v>
       </c>
       <c r="E121" s="2">
-        <v>81871</v>
+        <v>81867</v>
       </c>
       <c r="F121" s="3">
         <v>46049</v>
@@ -3585,10 +3585,10 @@
         <v>46049.490160081</v>
       </c>
       <c r="E122" s="2">
-        <v>81882</v>
+        <v>81871</v>
       </c>
       <c r="F122" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>9</v>
@@ -3605,16 +3605,16 @@
         <v>18</v>
       </c>
       <c r="C123" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D123" s="3">
-        <v>46051.4127791667</v>
+        <v>46049.490160081</v>
       </c>
       <c r="E123" s="2">
-        <v>81922</v>
+        <v>81882</v>
       </c>
       <c r="F123" s="3">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>9</v>
@@ -3631,16 +3631,16 @@
         <v>18</v>
       </c>
       <c r="C124" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D124" s="3">
-        <v>46056.7141110995</v>
+        <v>46051.4127791667</v>
       </c>
       <c r="E124" s="2">
-        <v>81972</v>
+        <v>81922</v>
       </c>
       <c r="F124" s="3">
-        <v>46056</v>
+        <v>46051</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>9</v>
@@ -3663,7 +3663,7 @@
         <v>46056.7141110995</v>
       </c>
       <c r="E125" s="2">
-        <v>81973</v>
+        <v>81972</v>
       </c>
       <c r="F125" s="3">
         <v>46056</v>
@@ -3689,10 +3689,10 @@
         <v>46056.7141110995</v>
       </c>
       <c r="E126" s="2">
-        <v>81993</v>
+        <v>81973</v>
       </c>
       <c r="F126" s="3">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>9</v>
@@ -3709,16 +3709,16 @@
         <v>18</v>
       </c>
       <c r="C127" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D127" s="3">
-        <v>46063.7282468519</v>
+        <v>46056.7141110995</v>
       </c>
       <c r="E127" s="2">
-        <v>82090</v>
+        <v>81993</v>
       </c>
       <c r="F127" s="3">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>9</v>
@@ -3741,7 +3741,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E128" s="2">
-        <v>82093</v>
+        <v>82090</v>
       </c>
       <c r="F128" s="3">
         <v>46063</v>
@@ -3767,10 +3767,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E129" s="2">
-        <v>82094</v>
+        <v>82093</v>
       </c>
       <c r="F129" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>9</v>
@@ -3793,7 +3793,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E130" s="2">
-        <v>82098</v>
+        <v>82094</v>
       </c>
       <c r="F130" s="3">
         <v>46064</v>
@@ -3819,7 +3819,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E131" s="2">
-        <v>82119</v>
+        <v>82098</v>
       </c>
       <c r="F131" s="3">
         <v>46064</v>
@@ -3845,7 +3845,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E132" s="2">
-        <v>82120</v>
+        <v>82119</v>
       </c>
       <c r="F132" s="3">
         <v>46064</v>
@@ -3871,10 +3871,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E133" s="2">
-        <v>82131</v>
+        <v>82120</v>
       </c>
       <c r="F133" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>9</v>
@@ -3891,16 +3891,16 @@
         <v>18</v>
       </c>
       <c r="C134" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D134" s="3">
-        <v>46078.6817048032</v>
+        <v>46063.7282468519</v>
       </c>
       <c r="E134" s="2">
-        <v>82316</v>
+        <v>82131</v>
       </c>
       <c r="F134" s="3">
-        <v>46078</v>
+        <v>46065</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>9</v>
@@ -3923,10 +3923,10 @@
         <v>46078.6817048032</v>
       </c>
       <c r="E135" s="2">
-        <v>82325</v>
+        <v>82316</v>
       </c>
       <c r="F135" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>9</v>
@@ -3949,7 +3949,7 @@
         <v>46078.6817048032</v>
       </c>
       <c r="E136" s="2">
-        <v>82327</v>
+        <v>82325</v>
       </c>
       <c r="F136" s="3">
         <v>46079</v>
@@ -3969,16 +3969,16 @@
         <v>18</v>
       </c>
       <c r="C137" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D137" s="3">
-        <v>46086.632572419</v>
+        <v>46078.6817048032</v>
       </c>
       <c r="E137" s="2">
-        <v>82471</v>
+        <v>82327</v>
       </c>
       <c r="F137" s="3">
-        <v>46086</v>
+        <v>46079</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>9</v>
@@ -4001,10 +4001,10 @@
         <v>46086.632572419</v>
       </c>
       <c r="E138" s="2">
-        <v>82476</v>
+        <v>82471</v>
       </c>
       <c r="F138" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>9</v>
@@ -4015,22 +4015,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="139">
       <c r="A139" s="2">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C139" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D139" s="3">
-        <v>46030.4179771875</v>
+        <v>46086.632572419</v>
       </c>
       <c r="E139" s="2">
-        <v>81536</v>
+        <v>82476</v>
       </c>
       <c r="F139" s="3">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>9</v>
@@ -4053,7 +4053,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E140" s="2">
-        <v>81538</v>
+        <v>81536</v>
       </c>
       <c r="F140" s="3">
         <v>46030</v>
@@ -4079,7 +4079,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E141" s="2">
-        <v>81555</v>
+        <v>81538</v>
       </c>
       <c r="F141" s="3">
         <v>46030</v>
@@ -4105,7 +4105,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E142" s="2">
-        <v>81556</v>
+        <v>81555</v>
       </c>
       <c r="F142" s="3">
         <v>46030</v>
@@ -4131,7 +4131,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E143" s="2">
-        <v>81558</v>
+        <v>81556</v>
       </c>
       <c r="F143" s="3">
         <v>46030</v>
@@ -4151,16 +4151,16 @@
         <v>19</v>
       </c>
       <c r="C144" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D144" s="3">
-        <v>46036.4079311574</v>
+        <v>46030.4179771875</v>
       </c>
       <c r="E144" s="2">
-        <v>81615</v>
+        <v>81558</v>
       </c>
       <c r="F144" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>9</v>
@@ -4183,7 +4183,7 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E145" s="2">
-        <v>81621</v>
+        <v>81615</v>
       </c>
       <c r="F145" s="3">
         <v>46036</v>
@@ -4209,10 +4209,10 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E146" s="2">
-        <v>81647</v>
+        <v>81621</v>
       </c>
       <c r="F146" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>9</v>
@@ -4223,22 +4223,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="147">
       <c r="A147" s="2">
-        <v>2504</v>
+        <v>2411</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C147" s="2">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D147" s="3">
-        <v>46027.6983957986</v>
+        <v>46036.4079311574</v>
       </c>
       <c r="E147" s="2">
-        <v>81465</v>
+        <v>81647</v>
       </c>
       <c r="F147" s="3">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>9</v>
@@ -4261,16 +4261,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E148" s="2">
-        <v>81466</v>
+        <v>81465</v>
       </c>
       <c r="F148" s="3">
         <v>46027</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="149">
@@ -4287,16 +4287,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E149" s="2">
-        <v>81471</v>
+        <v>81466</v>
       </c>
       <c r="F149" s="3">
         <v>46027</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="150">
@@ -4313,10 +4313,10 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E150" s="2">
-        <v>81488</v>
+        <v>81471</v>
       </c>
       <c r="F150" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>9</v>
@@ -4339,7 +4339,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E151" s="2">
-        <v>81489</v>
+        <v>81488</v>
       </c>
       <c r="F151" s="3">
         <v>46029</v>
@@ -4365,7 +4365,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E152" s="2">
-        <v>81490</v>
+        <v>81489</v>
       </c>
       <c r="F152" s="3">
         <v>46029</v>
@@ -4391,7 +4391,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E153" s="2">
-        <v>81491</v>
+        <v>81490</v>
       </c>
       <c r="F153" s="3">
         <v>46029</v>
@@ -4411,16 +4411,16 @@
         <v>20</v>
       </c>
       <c r="C154" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D154" s="3">
-        <v>46038.4184531713</v>
+        <v>46027.6983957986</v>
       </c>
       <c r="E154" s="2">
-        <v>81688</v>
+        <v>81491</v>
       </c>
       <c r="F154" s="3">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>9</v>
@@ -4437,13 +4437,13 @@
         <v>20</v>
       </c>
       <c r="C155" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D155" s="3">
-        <v>46038.6993878241</v>
+        <v>46038.4184531713</v>
       </c>
       <c r="E155" s="2">
-        <v>81700</v>
+        <v>81688</v>
       </c>
       <c r="F155" s="3">
         <v>46038</v>
@@ -4469,7 +4469,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E156" s="2">
-        <v>81701</v>
+        <v>81700</v>
       </c>
       <c r="F156" s="3">
         <v>46038</v>
@@ -4495,7 +4495,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E157" s="2">
-        <v>81702</v>
+        <v>81701</v>
       </c>
       <c r="F157" s="3">
         <v>46038</v>
@@ -4521,7 +4521,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E158" s="2">
-        <v>81703</v>
+        <v>81702</v>
       </c>
       <c r="F158" s="3">
         <v>46038</v>
@@ -4547,10 +4547,10 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E159" s="2">
-        <v>81734</v>
+        <v>81703</v>
       </c>
       <c r="F159" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>9</v>
@@ -4567,16 +4567,16 @@
         <v>20</v>
       </c>
       <c r="C160" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D160" s="3">
-        <v>46050.7176682523</v>
+        <v>46038.6993878241</v>
       </c>
       <c r="E160" s="2">
-        <v>81914</v>
+        <v>81734</v>
       </c>
       <c r="F160" s="3">
-        <v>46051</v>
+        <v>46041</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>9</v>
@@ -4599,7 +4599,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E161" s="2">
-        <v>81915</v>
+        <v>81914</v>
       </c>
       <c r="F161" s="3">
         <v>46051</v>
@@ -4625,7 +4625,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E162" s="2">
-        <v>81921</v>
+        <v>81915</v>
       </c>
       <c r="F162" s="3">
         <v>46051</v>
@@ -4645,16 +4645,16 @@
         <v>20</v>
       </c>
       <c r="C163" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D163" s="3">
-        <v>46052.6247194676</v>
+        <v>46050.7176682523</v>
       </c>
       <c r="E163" s="2">
-        <v>81949</v>
+        <v>81921</v>
       </c>
       <c r="F163" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>9</v>
@@ -4677,7 +4677,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E164" s="2">
-        <v>81950</v>
+        <v>81949</v>
       </c>
       <c r="F164" s="3">
         <v>46052</v>
@@ -4703,7 +4703,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E165" s="2">
-        <v>81951</v>
+        <v>81950</v>
       </c>
       <c r="F165" s="3">
         <v>46052</v>
@@ -4729,7 +4729,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E166" s="2">
-        <v>81953</v>
+        <v>81951</v>
       </c>
       <c r="F166" s="3">
         <v>46052</v>
@@ -4749,16 +4749,16 @@
         <v>20</v>
       </c>
       <c r="C167" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D167" s="3">
-        <v>46058.6976675694</v>
+        <v>46052.6247194676</v>
       </c>
       <c r="E167" s="2">
-        <v>82028</v>
+        <v>81953</v>
       </c>
       <c r="F167" s="3">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>9</v>
@@ -4781,7 +4781,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E168" s="2">
-        <v>82029</v>
+        <v>82028</v>
       </c>
       <c r="F168" s="3">
         <v>46058</v>
@@ -4807,10 +4807,10 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E169" s="2">
-        <v>82040</v>
+        <v>82029</v>
       </c>
       <c r="F169" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>9</v>
@@ -4833,7 +4833,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E170" s="2">
-        <v>82041</v>
+        <v>82040</v>
       </c>
       <c r="F170" s="3">
         <v>46059</v>
@@ -4859,7 +4859,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E171" s="2">
-        <v>82051</v>
+        <v>82041</v>
       </c>
       <c r="F171" s="3">
         <v>46059</v>
@@ -4879,16 +4879,16 @@
         <v>20</v>
       </c>
       <c r="C172" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D172" s="3">
-        <v>46065.6309066782</v>
+        <v>46058.6976675694</v>
       </c>
       <c r="E172" s="2">
-        <v>82168</v>
+        <v>82051</v>
       </c>
       <c r="F172" s="3">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>9</v>
@@ -4911,16 +4911,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E173" s="2">
-        <v>82170</v>
+        <v>82168</v>
       </c>
       <c r="F173" s="3">
         <v>46066</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="174">
@@ -4937,16 +4937,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E174" s="2">
-        <v>82171</v>
+        <v>82170</v>
       </c>
       <c r="F174" s="3">
         <v>46066</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="175">
@@ -4963,7 +4963,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E175" s="2">
-        <v>82172</v>
+        <v>82171</v>
       </c>
       <c r="F175" s="3">
         <v>46066</v>
@@ -4989,7 +4989,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E176" s="2">
-        <v>82175</v>
+        <v>82172</v>
       </c>
       <c r="F176" s="3">
         <v>46066</v>
@@ -5015,7 +5015,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E177" s="2">
-        <v>82176</v>
+        <v>82175</v>
       </c>
       <c r="F177" s="3">
         <v>46066</v>
@@ -5035,16 +5035,16 @@
         <v>20</v>
       </c>
       <c r="C178" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D178" s="3">
-        <v>46072.5909779051</v>
+        <v>46065.6309066782</v>
       </c>
       <c r="E178" s="2">
-        <v>82206</v>
+        <v>82176</v>
       </c>
       <c r="F178" s="3">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>9</v>
@@ -5061,16 +5061,16 @@
         <v>20</v>
       </c>
       <c r="C179" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D179" s="3">
-        <v>46077.7262228935</v>
+        <v>46072.5909779051</v>
       </c>
       <c r="E179" s="2">
-        <v>82289</v>
+        <v>82206</v>
       </c>
       <c r="F179" s="3">
-        <v>46077</v>
+        <v>46072</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>9</v>
@@ -5093,7 +5093,7 @@
         <v>46077.7262228935</v>
       </c>
       <c r="E180" s="2">
-        <v>82290</v>
+        <v>82289</v>
       </c>
       <c r="F180" s="3">
         <v>46077</v>
@@ -5113,16 +5113,16 @@
         <v>20</v>
       </c>
       <c r="C181" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D181" s="3">
-        <v>46078.6799843634</v>
+        <v>46077.7262228935</v>
       </c>
       <c r="E181" s="2">
-        <v>82318</v>
+        <v>82290</v>
       </c>
       <c r="F181" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>9</v>
@@ -5139,16 +5139,16 @@
         <v>20</v>
       </c>
       <c r="C182" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D182" s="3">
-        <v>46080.6294471412</v>
+        <v>46078.6799843634</v>
       </c>
       <c r="E182" s="2">
-        <v>82368</v>
+        <v>82318</v>
       </c>
       <c r="F182" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>9</v>
@@ -5165,16 +5165,16 @@
         <v>20</v>
       </c>
       <c r="C183" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D183" s="3">
-        <v>46084.741264838</v>
+        <v>46080.6294471412</v>
       </c>
       <c r="E183" s="2">
-        <v>82425</v>
+        <v>82368</v>
       </c>
       <c r="F183" s="3">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>9</v>
@@ -5197,7 +5197,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="E184" s="2">
-        <v>82426</v>
+        <v>82425</v>
       </c>
       <c r="F184" s="3">
         <v>46084</v>
@@ -5223,10 +5223,10 @@
         <v>46084.741264838</v>
       </c>
       <c r="E185" s="2">
-        <v>82430</v>
+        <v>82426</v>
       </c>
       <c r="F185" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>9</v>
@@ -5249,7 +5249,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="E186" s="2">
-        <v>82431</v>
+        <v>82430</v>
       </c>
       <c r="F186" s="3">
         <v>46085</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="187">
       <c r="A187" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C187" s="2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D187" s="3">
-        <v>46041.6648751157</v>
+        <v>46084.741264838</v>
       </c>
       <c r="E187" s="2">
-        <v>81743</v>
+        <v>82431</v>
       </c>
       <c r="F187" s="3">
-        <v>46041</v>
+        <v>46085</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>9</v>
@@ -5301,7 +5301,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E188" s="2">
-        <v>81744</v>
+        <v>81743</v>
       </c>
       <c r="F188" s="3">
         <v>46041</v>
@@ -5327,7 +5327,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E189" s="2">
-        <v>81745</v>
+        <v>81744</v>
       </c>
       <c r="F189" s="3">
         <v>46041</v>
@@ -5353,10 +5353,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E190" s="2">
-        <v>81746</v>
+        <v>81745</v>
       </c>
       <c r="F190" s="3">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>9</v>
@@ -5379,10 +5379,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E191" s="2">
-        <v>81751</v>
+        <v>81746</v>
       </c>
       <c r="F191" s="3">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>9</v>
@@ -5405,7 +5405,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E192" s="2">
-        <v>81753</v>
+        <v>81751</v>
       </c>
       <c r="F192" s="3">
         <v>46043</v>
@@ -5431,7 +5431,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E193" s="2">
-        <v>81754</v>
+        <v>81753</v>
       </c>
       <c r="F193" s="3">
         <v>46043</v>
@@ -5457,7 +5457,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E194" s="2">
-        <v>81755</v>
+        <v>81754</v>
       </c>
       <c r="F194" s="3">
         <v>46043</v>
@@ -5483,7 +5483,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E195" s="2">
-        <v>81766</v>
+        <v>81755</v>
       </c>
       <c r="F195" s="3">
         <v>46043</v>
@@ -5503,16 +5503,16 @@
         <v>21</v>
       </c>
       <c r="C196" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D196" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E196" s="2">
-        <v>82088</v>
+        <v>81766</v>
       </c>
       <c r="F196" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>9</v>
@@ -5535,7 +5535,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E197" s="2">
-        <v>82089</v>
+        <v>82088</v>
       </c>
       <c r="F197" s="3">
         <v>46063</v>
@@ -5561,10 +5561,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E198" s="2">
-        <v>82163</v>
+        <v>82089</v>
       </c>
       <c r="F198" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>9</v>
@@ -5587,7 +5587,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E199" s="2">
-        <v>82179</v>
+        <v>82163</v>
       </c>
       <c r="F199" s="3">
         <v>46066</v>
@@ -5613,7 +5613,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E200" s="2">
-        <v>82193</v>
+        <v>82179</v>
       </c>
       <c r="F200" s="3">
         <v>46066</v>
@@ -5633,16 +5633,16 @@
         <v>21</v>
       </c>
       <c r="C201" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D201" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E201" s="2">
-        <v>82250</v>
+        <v>82193</v>
       </c>
       <c r="F201" s="3">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>9</v>
@@ -5665,10 +5665,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E202" s="2">
-        <v>82266</v>
+        <v>82250</v>
       </c>
       <c r="F202" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>9</v>
@@ -5691,10 +5691,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E203" s="2">
-        <v>82295</v>
+        <v>82266</v>
       </c>
       <c r="F203" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>9</v>
@@ -5717,7 +5717,7 @@
         <v>46073.714168287</v>
       </c>
       <c r="E204" s="2">
-        <v>82296</v>
+        <v>82295</v>
       </c>
       <c r="F204" s="3">
         <v>46078</v>
@@ -5743,16 +5743,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E205" s="2">
-        <v>82332</v>
+        <v>82296</v>
       </c>
       <c r="F205" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="206">
@@ -5769,16 +5769,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E206" s="2">
-        <v>82339</v>
+        <v>82332</v>
       </c>
       <c r="F206" s="3">
         <v>46079</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="207">
@@ -5789,16 +5789,16 @@
         <v>21</v>
       </c>
       <c r="C207" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D207" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E207" s="2">
-        <v>82266</v>
+        <v>82339</v>
       </c>
       <c r="F207" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>9</v>
@@ -5821,7 +5821,7 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E208" s="2">
-        <v>82273</v>
+        <v>82266</v>
       </c>
       <c r="F208" s="3">
         <v>46077</v>
@@ -5847,10 +5847,10 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E209" s="2">
-        <v>82294</v>
+        <v>82273</v>
       </c>
       <c r="F209" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>9</v>
@@ -5867,16 +5867,16 @@
         <v>21</v>
       </c>
       <c r="C210" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D210" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E210" s="2">
-        <v>82411</v>
+        <v>82294</v>
       </c>
       <c r="F210" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>9</v>
@@ -5899,10 +5899,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E211" s="2">
-        <v>82432</v>
+        <v>82411</v>
       </c>
       <c r="F211" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>9</v>
@@ -5925,10 +5925,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E212" s="2">
-        <v>82473</v>
+        <v>82432</v>
       </c>
       <c r="F212" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>9</v>
@@ -5951,10 +5951,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E213" s="2">
-        <v>82474</v>
+        <v>82473</v>
       </c>
       <c r="F213" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>9</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="214">
       <c r="A214" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C214" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D214" s="3">
-        <v>46044.6368950926</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E214" s="2">
-        <v>81802</v>
+        <v>82474</v>
       </c>
       <c r="F214" s="3">
-        <v>46044</v>
+        <v>46087</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>9</v>
@@ -6003,7 +6003,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E215" s="2">
-        <v>81803</v>
+        <v>81802</v>
       </c>
       <c r="F215" s="3">
         <v>46044</v>
@@ -6029,7 +6029,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E216" s="2">
-        <v>81804</v>
+        <v>81803</v>
       </c>
       <c r="F216" s="3">
         <v>46044</v>
@@ -6055,7 +6055,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E217" s="2">
-        <v>81806</v>
+        <v>81804</v>
       </c>
       <c r="F217" s="3">
         <v>46044</v>
@@ -6081,7 +6081,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E218" s="2">
-        <v>81807</v>
+        <v>81806</v>
       </c>
       <c r="F218" s="3">
         <v>46044</v>
@@ -6107,10 +6107,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E219" s="2">
-        <v>81812</v>
+        <v>81807</v>
       </c>
       <c r="F219" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>9</v>
@@ -6133,7 +6133,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E220" s="2">
-        <v>81813</v>
+        <v>81812</v>
       </c>
       <c r="F220" s="3">
         <v>46045</v>
@@ -6159,7 +6159,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E221" s="2">
-        <v>81814</v>
+        <v>81813</v>
       </c>
       <c r="F221" s="3">
         <v>46045</v>
@@ -6185,7 +6185,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E222" s="2">
-        <v>81818</v>
+        <v>81814</v>
       </c>
       <c r="F222" s="3">
         <v>46045</v>
@@ -6211,7 +6211,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E223" s="2">
-        <v>81822</v>
+        <v>81818</v>
       </c>
       <c r="F223" s="3">
         <v>46045</v>
@@ -6237,7 +6237,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E224" s="2">
-        <v>81833</v>
+        <v>81822</v>
       </c>
       <c r="F224" s="3">
         <v>46045</v>
@@ -6263,7 +6263,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E225" s="2">
-        <v>81841</v>
+        <v>81833</v>
       </c>
       <c r="F225" s="3">
         <v>46045</v>
@@ -6283,16 +6283,16 @@
         <v>24</v>
       </c>
       <c r="C226" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D226" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E226" s="2">
-        <v>81928</v>
+        <v>81841</v>
       </c>
       <c r="F226" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>9</v>
@@ -6315,7 +6315,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E227" s="2">
-        <v>81929</v>
+        <v>81928</v>
       </c>
       <c r="F227" s="3">
         <v>46052</v>
@@ -6341,7 +6341,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E228" s="2">
-        <v>81930</v>
+        <v>81929</v>
       </c>
       <c r="F228" s="3">
         <v>46052</v>
@@ -6367,7 +6367,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E229" s="2">
-        <v>81932</v>
+        <v>81930</v>
       </c>
       <c r="F229" s="3">
         <v>46052</v>
@@ -6393,7 +6393,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E230" s="2">
-        <v>81933</v>
+        <v>81932</v>
       </c>
       <c r="F230" s="3">
         <v>46052</v>
@@ -6419,7 +6419,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E231" s="2">
-        <v>81934</v>
+        <v>81933</v>
       </c>
       <c r="F231" s="3">
         <v>46052</v>
@@ -6445,7 +6445,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E232" s="2">
-        <v>81935</v>
+        <v>81934</v>
       </c>
       <c r="F232" s="3">
         <v>46052</v>
@@ -6471,7 +6471,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E233" s="2">
-        <v>81936</v>
+        <v>81935</v>
       </c>
       <c r="F233" s="3">
         <v>46052</v>
@@ -6491,16 +6491,16 @@
         <v>24</v>
       </c>
       <c r="C234" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D234" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E234" s="2">
-        <v>82222</v>
+        <v>81936</v>
       </c>
       <c r="F234" s="3">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>9</v>
@@ -6523,10 +6523,10 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E235" s="2">
-        <v>82226</v>
+        <v>82222</v>
       </c>
       <c r="F235" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>9</v>
@@ -6549,7 +6549,7 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E236" s="2">
-        <v>82229</v>
+        <v>82226</v>
       </c>
       <c r="F236" s="3">
         <v>46073</v>
@@ -6569,13 +6569,13 @@
         <v>24</v>
       </c>
       <c r="C237" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D237" s="3">
-        <v>46073.5838834375</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E237" s="2">
-        <v>82246</v>
+        <v>82229</v>
       </c>
       <c r="F237" s="3">
         <v>46073</v>
@@ -6595,16 +6595,16 @@
         <v>24</v>
       </c>
       <c r="C238" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D238" s="3">
-        <v>46080.6289065162</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E238" s="2">
-        <v>82387</v>
+        <v>82246</v>
       </c>
       <c r="F238" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>9</v>
@@ -6615,22 +6615,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="239">
       <c r="A239" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C239" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D239" s="3">
-        <v>46029.4161474769</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E239" s="2">
-        <v>81478</v>
+        <v>82387</v>
       </c>
       <c r="F239" s="3">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>9</v>
@@ -6653,7 +6653,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E240" s="2">
-        <v>81479</v>
+        <v>81478</v>
       </c>
       <c r="F240" s="3">
         <v>46029</v>
@@ -6679,7 +6679,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E241" s="2">
-        <v>81480</v>
+        <v>81479</v>
       </c>
       <c r="F241" s="3">
         <v>46029</v>
@@ -6705,7 +6705,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E242" s="2">
-        <v>81497</v>
+        <v>81480</v>
       </c>
       <c r="F242" s="3">
         <v>46029</v>
@@ -6731,7 +6731,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E243" s="2">
-        <v>81498</v>
+        <v>81497</v>
       </c>
       <c r="F243" s="3">
         <v>46029</v>
@@ -6757,7 +6757,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E244" s="2">
-        <v>81499</v>
+        <v>81498</v>
       </c>
       <c r="F244" s="3">
         <v>46029</v>
@@ -6783,7 +6783,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E245" s="2">
-        <v>81500</v>
+        <v>81499</v>
       </c>
       <c r="F245" s="3">
         <v>46029</v>
@@ -6803,16 +6803,16 @@
         <v>24</v>
       </c>
       <c r="C246" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D246" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E246" s="2">
-        <v>81878</v>
+        <v>81500</v>
       </c>
       <c r="F246" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>9</v>
@@ -6835,7 +6835,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E247" s="2">
-        <v>81879</v>
+        <v>81878</v>
       </c>
       <c r="F247" s="3">
         <v>46049</v>
@@ -6861,10 +6861,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E248" s="2">
-        <v>81885</v>
+        <v>81879</v>
       </c>
       <c r="F248" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>9</v>
@@ -6887,7 +6887,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E249" s="2">
-        <v>81886</v>
+        <v>81885</v>
       </c>
       <c r="F249" s="3">
         <v>46050</v>
@@ -6907,16 +6907,16 @@
         <v>24</v>
       </c>
       <c r="C250" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D250" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E250" s="2">
-        <v>82068</v>
+        <v>81886</v>
       </c>
       <c r="F250" s="3">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>9</v>
@@ -6939,10 +6939,10 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E251" s="2">
-        <v>82072</v>
+        <v>82068</v>
       </c>
       <c r="F251" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>9</v>
@@ -6965,7 +6965,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E252" s="2">
-        <v>82076</v>
+        <v>82072</v>
       </c>
       <c r="F252" s="3">
         <v>46063</v>
@@ -6991,7 +6991,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E253" s="2">
-        <v>82078</v>
+        <v>82076</v>
       </c>
       <c r="F253" s="3">
         <v>46063</v>
@@ -7011,16 +7011,16 @@
         <v>24</v>
       </c>
       <c r="C254" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D254" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E254" s="2">
-        <v>82287</v>
+        <v>82078</v>
       </c>
       <c r="F254" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>9</v>
@@ -7043,7 +7043,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E255" s="2">
-        <v>82288</v>
+        <v>82287</v>
       </c>
       <c r="F255" s="3">
         <v>46077</v>
@@ -7069,10 +7069,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E256" s="2">
-        <v>82298</v>
+        <v>82288</v>
       </c>
       <c r="F256" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>9</v>
@@ -7095,7 +7095,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E257" s="2">
-        <v>82301</v>
+        <v>82298</v>
       </c>
       <c r="F257" s="3">
         <v>46078</v>
@@ -7121,7 +7121,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E258" s="2">
-        <v>82304</v>
+        <v>82301</v>
       </c>
       <c r="F258" s="3">
         <v>46078</v>
@@ -7147,7 +7147,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E259" s="2">
-        <v>82308</v>
+        <v>82304</v>
       </c>
       <c r="F259" s="3">
         <v>46078</v>
@@ -7167,16 +7167,16 @@
         <v>24</v>
       </c>
       <c r="C260" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D260" s="3">
-        <v>46080.628344919</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E260" s="2">
-        <v>82373</v>
+        <v>82308</v>
       </c>
       <c r="F260" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>9</v>
@@ -7193,16 +7193,16 @@
         <v>24</v>
       </c>
       <c r="C261" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D261" s="3">
-        <v>46085.6581644213</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E261" s="2">
-        <v>82445</v>
+        <v>82373</v>
       </c>
       <c r="F261" s="3">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>9</v>
@@ -7225,7 +7225,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E262" s="2">
-        <v>82447</v>
+        <v>82445</v>
       </c>
       <c r="F262" s="3">
         <v>46085</v>
@@ -7251,10 +7251,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E263" s="2">
-        <v>82453</v>
+        <v>82447</v>
       </c>
       <c r="F263" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>9</v>
@@ -7277,7 +7277,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E264" s="2">
-        <v>82468</v>
+        <v>82453</v>
       </c>
       <c r="F264" s="3">
         <v>46086</v>
@@ -7291,22 +7291,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="265">
       <c r="A265" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C265" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D265" s="3">
-        <v>46029.6400966782</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E265" s="2">
-        <v>81506</v>
+        <v>82468</v>
       </c>
       <c r="F265" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>9</v>
@@ -7329,7 +7329,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E266" s="2">
-        <v>81507</v>
+        <v>81506</v>
       </c>
       <c r="F266" s="3">
         <v>46029</v>
@@ -7355,10 +7355,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E267" s="2">
-        <v>81524</v>
+        <v>81507</v>
       </c>
       <c r="F267" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>9</v>
@@ -7381,7 +7381,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E268" s="2">
-        <v>81525</v>
+        <v>81524</v>
       </c>
       <c r="F268" s="3">
         <v>46030</v>
@@ -7407,7 +7407,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E269" s="2">
-        <v>81526</v>
+        <v>81525</v>
       </c>
       <c r="F269" s="3">
         <v>46030</v>
@@ -7427,16 +7427,16 @@
         <v>25</v>
       </c>
       <c r="C270" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D270" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E270" s="2">
-        <v>81640</v>
+        <v>81526</v>
       </c>
       <c r="F270" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>9</v>
@@ -7459,7 +7459,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E271" s="2">
-        <v>81642</v>
+        <v>81640</v>
       </c>
       <c r="F271" s="3">
         <v>46036</v>
@@ -7485,7 +7485,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E272" s="2">
-        <v>81643</v>
+        <v>81642</v>
       </c>
       <c r="F272" s="3">
         <v>46036</v>
@@ -7505,16 +7505,16 @@
         <v>25</v>
       </c>
       <c r="C273" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D273" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E273" s="2">
-        <v>81835</v>
+        <v>81643</v>
       </c>
       <c r="F273" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>9</v>
@@ -7537,7 +7537,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E274" s="2">
-        <v>81836</v>
+        <v>81835</v>
       </c>
       <c r="F274" s="3">
         <v>46045</v>
@@ -7563,7 +7563,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E275" s="2">
-        <v>81837</v>
+        <v>81836</v>
       </c>
       <c r="F275" s="3">
         <v>46045</v>
@@ -7583,16 +7583,16 @@
         <v>25</v>
       </c>
       <c r="C276" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D276" s="3">
-        <v>46051.6376515278</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E276" s="2">
-        <v>81931</v>
+        <v>81837</v>
       </c>
       <c r="F276" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>9</v>
@@ -7609,16 +7609,16 @@
         <v>25</v>
       </c>
       <c r="C277" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D277" s="3">
-        <v>46056.7115158912</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E277" s="2">
-        <v>81978</v>
+        <v>81931</v>
       </c>
       <c r="F277" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>9</v>
@@ -7635,13 +7635,13 @@
         <v>25</v>
       </c>
       <c r="C278" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D278" s="3">
-        <v>46057.6911087731</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E278" s="2">
-        <v>81994</v>
+        <v>81978</v>
       </c>
       <c r="F278" s="3">
         <v>46057</v>
@@ -7667,7 +7667,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E279" s="2">
-        <v>81995</v>
+        <v>81994</v>
       </c>
       <c r="F279" s="3">
         <v>46057</v>
@@ -7693,7 +7693,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E280" s="2">
-        <v>81999</v>
+        <v>81995</v>
       </c>
       <c r="F280" s="3">
         <v>46057</v>
@@ -7719,10 +7719,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E281" s="2">
-        <v>82008</v>
+        <v>81999</v>
       </c>
       <c r="F281" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>9</v>
@@ -7745,7 +7745,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E282" s="2">
-        <v>82011</v>
+        <v>82008</v>
       </c>
       <c r="F282" s="3">
         <v>46058</v>
@@ -7771,7 +7771,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E283" s="2">
-        <v>82012</v>
+        <v>82011</v>
       </c>
       <c r="F283" s="3">
         <v>46058</v>
@@ -7797,7 +7797,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E284" s="2">
-        <v>82013</v>
+        <v>82012</v>
       </c>
       <c r="F284" s="3">
         <v>46058</v>
@@ -7823,7 +7823,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E285" s="2">
-        <v>82014</v>
+        <v>82013</v>
       </c>
       <c r="F285" s="3">
         <v>46058</v>
@@ -7843,22 +7843,22 @@
         <v>25</v>
       </c>
       <c r="C286" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D286" s="3">
-        <v>46058.6604985417</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E286" s="2">
-        <v>82046</v>
+        <v>82014</v>
       </c>
       <c r="F286" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="287">
@@ -7869,22 +7869,22 @@
         <v>25</v>
       </c>
       <c r="C287" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D287" s="3">
-        <v>46072.738871875</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E287" s="2">
-        <v>82217</v>
+        <v>82046</v>
       </c>
       <c r="F287" s="3">
-        <v>46072</v>
+        <v>46059</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="288">
@@ -7901,7 +7901,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E288" s="2">
-        <v>82218</v>
+        <v>82217</v>
       </c>
       <c r="F288" s="3">
         <v>46072</v>
@@ -7927,10 +7927,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E289" s="2">
-        <v>82234</v>
+        <v>82218</v>
       </c>
       <c r="F289" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>9</v>
@@ -7953,7 +7953,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E290" s="2">
-        <v>82238</v>
+        <v>82234</v>
       </c>
       <c r="F290" s="3">
         <v>46073</v>
@@ -7979,7 +7979,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E291" s="2">
-        <v>82245</v>
+        <v>82238</v>
       </c>
       <c r="F291" s="3">
         <v>46073</v>
@@ -7999,16 +7999,16 @@
         <v>25</v>
       </c>
       <c r="C292" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D292" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E292" s="2">
-        <v>82257</v>
+        <v>82245</v>
       </c>
       <c r="F292" s="3">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>9</v>
@@ -8031,10 +8031,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E293" s="2">
-        <v>82276</v>
+        <v>82257</v>
       </c>
       <c r="F293" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>9</v>
@@ -8057,7 +8057,7 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E294" s="2">
-        <v>82277</v>
+        <v>82276</v>
       </c>
       <c r="F294" s="3">
         <v>46077</v>
@@ -8083,10 +8083,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E295" s="2">
-        <v>82293</v>
+        <v>82277</v>
       </c>
       <c r="F295" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>9</v>
@@ -8103,16 +8103,16 @@
         <v>25</v>
       </c>
       <c r="C296" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D296" s="3">
-        <v>46077.4356327431</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E296" s="2">
-        <v>82269</v>
+        <v>82293</v>
       </c>
       <c r="F296" s="3">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>9</v>
@@ -8129,16 +8129,16 @@
         <v>25</v>
       </c>
       <c r="C297" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D297" s="3">
-        <v>46084.7378501505</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E297" s="2">
-        <v>82419</v>
+        <v>82269</v>
       </c>
       <c r="F297" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>9</v>
@@ -8161,7 +8161,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E298" s="2">
-        <v>82420</v>
+        <v>82419</v>
       </c>
       <c r="F298" s="3">
         <v>46084</v>
@@ -8187,7 +8187,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E299" s="2">
-        <v>82421</v>
+        <v>82420</v>
       </c>
       <c r="F299" s="3">
         <v>46084</v>
@@ -8213,7 +8213,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E300" s="2">
-        <v>82422</v>
+        <v>82421</v>
       </c>
       <c r="F300" s="3">
         <v>46084</v>
@@ -8239,7 +8239,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E301" s="2">
-        <v>82423</v>
+        <v>82422</v>
       </c>
       <c r="F301" s="3">
         <v>46084</v>
@@ -8265,10 +8265,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E302" s="2">
-        <v>82433</v>
+        <v>82423</v>
       </c>
       <c r="F302" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>9</v>
@@ -8291,7 +8291,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E303" s="2">
-        <v>82434</v>
+        <v>82433</v>
       </c>
       <c r="F303" s="3">
         <v>46085</v>
@@ -8317,10 +8317,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E304" s="2">
-        <v>82464</v>
+        <v>82434</v>
       </c>
       <c r="F304" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>9</v>
@@ -8343,7 +8343,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E305" s="2">
-        <v>82472</v>
+        <v>82464</v>
       </c>
       <c r="F305" s="3">
         <v>46086</v>
@@ -8357,22 +8357,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="306">
       <c r="A306" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C306" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D306" s="3">
-        <v>46027.6953206134</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E306" s="2">
-        <v>81464</v>
+        <v>82472</v>
       </c>
       <c r="F306" s="3">
-        <v>46027</v>
+        <v>46086</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>9</v>
@@ -8395,7 +8395,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E307" s="2">
-        <v>81472</v>
+        <v>81464</v>
       </c>
       <c r="F307" s="3">
         <v>46027</v>
@@ -8421,10 +8421,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E308" s="2">
-        <v>81492</v>
+        <v>81472</v>
       </c>
       <c r="F308" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>9</v>
@@ -8447,7 +8447,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E309" s="2">
-        <v>81493</v>
+        <v>81492</v>
       </c>
       <c r="F309" s="3">
         <v>46029</v>
@@ -8473,10 +8473,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E310" s="2">
-        <v>81568</v>
+        <v>81493</v>
       </c>
       <c r="F310" s="3">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>9</v>
@@ -8499,10 +8499,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E311" s="2">
-        <v>81601</v>
+        <v>81568</v>
       </c>
       <c r="F311" s="3">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>9</v>
@@ -8525,7 +8525,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E312" s="2">
-        <v>81602</v>
+        <v>81601</v>
       </c>
       <c r="F312" s="3">
         <v>46034</v>
@@ -8545,16 +8545,16 @@
         <v>26</v>
       </c>
       <c r="C313" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D313" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E313" s="2">
-        <v>81645</v>
+        <v>81602</v>
       </c>
       <c r="F313" s="3">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>9</v>
@@ -8577,7 +8577,7 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E314" s="2">
-        <v>81646</v>
+        <v>81645</v>
       </c>
       <c r="F314" s="3">
         <v>46036</v>
@@ -8603,10 +8603,10 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E315" s="2">
-        <v>81653</v>
+        <v>81646</v>
       </c>
       <c r="F315" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>9</v>
@@ -8623,13 +8623,13 @@
         <v>26</v>
       </c>
       <c r="C316" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D316" s="3">
-        <v>46037.4325152662</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E316" s="2">
-        <v>81662</v>
+        <v>81653</v>
       </c>
       <c r="F316" s="3">
         <v>46037</v>
@@ -8649,16 +8649,16 @@
         <v>26</v>
       </c>
       <c r="C317" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D317" s="3">
-        <v>46044.4079891435</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E317" s="2">
-        <v>81780</v>
+        <v>81662</v>
       </c>
       <c r="F317" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>9</v>
@@ -8681,7 +8681,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E318" s="2">
-        <v>81781</v>
+        <v>81780</v>
       </c>
       <c r="F318" s="3">
         <v>46044</v>
@@ -8707,7 +8707,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E319" s="2">
-        <v>81782</v>
+        <v>81781</v>
       </c>
       <c r="F319" s="3">
         <v>46044</v>
@@ -8733,7 +8733,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E320" s="2">
-        <v>81784</v>
+        <v>81782</v>
       </c>
       <c r="F320" s="3">
         <v>46044</v>
@@ -8759,7 +8759,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E321" s="2">
-        <v>81785</v>
+        <v>81784</v>
       </c>
       <c r="F321" s="3">
         <v>46044</v>
@@ -8785,7 +8785,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E322" s="2">
-        <v>81801</v>
+        <v>81785</v>
       </c>
       <c r="F322" s="3">
         <v>46044</v>
@@ -8805,16 +8805,16 @@
         <v>26</v>
       </c>
       <c r="C323" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D323" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E323" s="2">
-        <v>81860</v>
+        <v>81801</v>
       </c>
       <c r="F323" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>9</v>
@@ -8837,7 +8837,7 @@
         <v>46048.7319778588</v>
       </c>
       <c r="E324" s="2">
-        <v>81873</v>
+        <v>81860</v>
       </c>
       <c r="F324" s="3">
         <v>46049</v>
@@ -8857,13 +8857,13 @@
         <v>26</v>
       </c>
       <c r="C325" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D325" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E325" s="2">
-        <v>81865</v>
+        <v>81873</v>
       </c>
       <c r="F325" s="3">
         <v>46049</v>
@@ -8889,7 +8889,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E326" s="2">
-        <v>81870</v>
+        <v>81865</v>
       </c>
       <c r="F326" s="3">
         <v>46049</v>
@@ -8915,7 +8915,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E327" s="2">
-        <v>81872</v>
+        <v>81870</v>
       </c>
       <c r="F327" s="3">
         <v>46049</v>
@@ -8941,10 +8941,10 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E328" s="2">
-        <v>81896</v>
+        <v>81872</v>
       </c>
       <c r="F328" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>9</v>
@@ -8961,16 +8961,16 @@
         <v>26</v>
       </c>
       <c r="C329" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D329" s="3">
-        <v>46051.4046937153</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E329" s="2">
-        <v>81923</v>
+        <v>81896</v>
       </c>
       <c r="F329" s="3">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>9</v>
@@ -8987,16 +8987,16 @@
         <v>26</v>
       </c>
       <c r="C330" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D330" s="3">
-        <v>46057.6959672917</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E330" s="2">
-        <v>81998</v>
+        <v>81923</v>
       </c>
       <c r="F330" s="3">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>9</v>
@@ -9019,7 +9019,7 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E331" s="2">
-        <v>82002</v>
+        <v>81998</v>
       </c>
       <c r="F331" s="3">
         <v>46057</v>
@@ -9045,10 +9045,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E332" s="2">
-        <v>82005</v>
+        <v>82002</v>
       </c>
       <c r="F332" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>9</v>
@@ -9071,7 +9071,7 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E333" s="2">
-        <v>82007</v>
+        <v>82005</v>
       </c>
       <c r="F333" s="3">
         <v>46058</v>
@@ -9091,13 +9091,13 @@
         <v>26</v>
       </c>
       <c r="C334" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D334" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E334" s="2">
-        <v>82005</v>
+        <v>82007</v>
       </c>
       <c r="F334" s="3">
         <v>46058</v>
@@ -9123,10 +9123,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E335" s="2">
-        <v>82075</v>
+        <v>82005</v>
       </c>
       <c r="F335" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>9</v>
@@ -9149,7 +9149,7 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E336" s="2">
-        <v>82077</v>
+        <v>82075</v>
       </c>
       <c r="F336" s="3">
         <v>46063</v>
@@ -9175,10 +9175,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E337" s="2">
-        <v>82099</v>
+        <v>82077</v>
       </c>
       <c r="F337" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>9</v>
@@ -9195,16 +9195,16 @@
         <v>26</v>
       </c>
       <c r="C338" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D338" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E338" s="2">
-        <v>82219</v>
+        <v>82099</v>
       </c>
       <c r="F338" s="3">
-        <v>46072</v>
+        <v>46064</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>9</v>
@@ -9227,10 +9227,10 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E339" s="2">
-        <v>82230</v>
+        <v>82219</v>
       </c>
       <c r="F339" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>9</v>
@@ -9253,7 +9253,7 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E340" s="2">
-        <v>82231</v>
+        <v>82230</v>
       </c>
       <c r="F340" s="3">
         <v>46073</v>
@@ -9273,16 +9273,16 @@
         <v>26</v>
       </c>
       <c r="C341" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D341" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E341" s="2">
-        <v>82388</v>
+        <v>82231</v>
       </c>
       <c r="F341" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>9</v>
@@ -9305,7 +9305,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E342" s="2">
-        <v>82389</v>
+        <v>82388</v>
       </c>
       <c r="F342" s="3">
         <v>46083</v>
@@ -9331,7 +9331,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E343" s="2">
-        <v>82396</v>
+        <v>82389</v>
       </c>
       <c r="F343" s="3">
         <v>46083</v>
@@ -9357,7 +9357,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E344" s="2">
-        <v>82397</v>
+        <v>82396</v>
       </c>
       <c r="F344" s="3">
         <v>46083</v>
@@ -9377,16 +9377,16 @@
         <v>26</v>
       </c>
       <c r="C345" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D345" s="3">
-        <v>46085.6249659838</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E345" s="2">
-        <v>82435</v>
+        <v>82397</v>
       </c>
       <c r="F345" s="3">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>9</v>
@@ -9397,22 +9397,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="346">
       <c r="A346" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C346" s="2">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D346" s="3">
-        <v>46029.3821391551</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E346" s="2">
-        <v>81477</v>
+        <v>82435</v>
       </c>
       <c r="F346" s="3">
-        <v>46029</v>
+        <v>46085</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>9</v>
@@ -9429,16 +9429,16 @@
         <v>27</v>
       </c>
       <c r="C347" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D347" s="3">
-        <v>46030.4142968056</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E347" s="2">
-        <v>81532</v>
+        <v>81477</v>
       </c>
       <c r="F347" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>9</v>
@@ -9461,7 +9461,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E348" s="2">
-        <v>81534</v>
+        <v>81532</v>
       </c>
       <c r="F348" s="3">
         <v>46030</v>
@@ -9487,7 +9487,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E349" s="2">
-        <v>81535</v>
+        <v>81534</v>
       </c>
       <c r="F349" s="3">
         <v>46030</v>
@@ -9513,7 +9513,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E350" s="2">
-        <v>81550</v>
+        <v>81535</v>
       </c>
       <c r="F350" s="3">
         <v>46030</v>
@@ -9539,7 +9539,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E351" s="2">
-        <v>81553</v>
+        <v>81550</v>
       </c>
       <c r="F351" s="3">
         <v>46030</v>
@@ -9565,7 +9565,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E352" s="2">
-        <v>81554</v>
+        <v>81553</v>
       </c>
       <c r="F352" s="3">
         <v>46030</v>
@@ -9591,7 +9591,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E353" s="2">
-        <v>81557</v>
+        <v>81554</v>
       </c>
       <c r="F353" s="3">
         <v>46030</v>
@@ -9617,10 +9617,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E354" s="2">
-        <v>81588</v>
+        <v>81557</v>
       </c>
       <c r="F354" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>9</v>
@@ -9637,16 +9637,16 @@
         <v>27</v>
       </c>
       <c r="C355" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D355" s="3">
-        <v>46038.593985081</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E355" s="2">
-        <v>81692</v>
+        <v>81588</v>
       </c>
       <c r="F355" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>9</v>
@@ -9663,16 +9663,16 @@
         <v>27</v>
       </c>
       <c r="C356" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D356" s="3">
-        <v>46044.46462125</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E356" s="2">
-        <v>81786</v>
+        <v>81692</v>
       </c>
       <c r="F356" s="3">
-        <v>46044</v>
+        <v>46038</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>9</v>
@@ -9689,16 +9689,16 @@
         <v>27</v>
       </c>
       <c r="C357" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D357" s="3">
-        <v>46044.6362443171</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E357" s="2">
-        <v>81844</v>
+        <v>81786</v>
       </c>
       <c r="F357" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>9</v>
@@ -9715,16 +9715,16 @@
         <v>27</v>
       </c>
       <c r="C358" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D358" s="3">
-        <v>46062.717040544</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E358" s="2">
-        <v>82065</v>
+        <v>81844</v>
       </c>
       <c r="F358" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>9</v>
@@ -9747,7 +9747,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E359" s="2">
-        <v>82066</v>
+        <v>82065</v>
       </c>
       <c r="F359" s="3">
         <v>46062</v>
@@ -9773,7 +9773,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E360" s="2">
-        <v>82067</v>
+        <v>82066</v>
       </c>
       <c r="F360" s="3">
         <v>46062</v>
@@ -9793,16 +9793,16 @@
         <v>27</v>
       </c>
       <c r="C361" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D361" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E361" s="2">
-        <v>82190</v>
+        <v>82067</v>
       </c>
       <c r="F361" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>9</v>
@@ -9825,7 +9825,7 @@
         <v>46065.6300915625</v>
       </c>
       <c r="E362" s="2">
-        <v>82197</v>
+        <v>82190</v>
       </c>
       <c r="F362" s="3">
         <v>46066</v>
@@ -9845,16 +9845,16 @@
         <v>27</v>
       </c>
       <c r="C363" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D363" s="3">
-        <v>46077.5084780324</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E363" s="2">
-        <v>82270</v>
+        <v>82197</v>
       </c>
       <c r="F363" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>9</v>
@@ -9871,13 +9871,13 @@
         <v>27</v>
       </c>
       <c r="C364" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D364" s="3">
-        <v>46077.721037037</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E364" s="2">
-        <v>82285</v>
+        <v>82270</v>
       </c>
       <c r="F364" s="3">
         <v>46077</v>
@@ -9897,16 +9897,16 @@
         <v>27</v>
       </c>
       <c r="C365" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D365" s="3">
-        <v>46083.6694849421</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E365" s="2">
-        <v>82417</v>
+        <v>82285</v>
       </c>
       <c r="F365" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>9</v>
@@ -9923,16 +9923,16 @@
         <v>27</v>
       </c>
       <c r="C366" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D366" s="3">
-        <v>46085.7157723032</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E366" s="2">
-        <v>82457</v>
+        <v>82417</v>
       </c>
       <c r="F366" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>9</v>
@@ -9943,22 +9943,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="367">
       <c r="A367" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C367" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D367" s="3">
-        <v>46029.381258831</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E367" s="2">
-        <v>81484</v>
+        <v>82457</v>
       </c>
       <c r="F367" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>9</v>
@@ -9981,7 +9981,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E368" s="2">
-        <v>81486</v>
+        <v>81484</v>
       </c>
       <c r="F368" s="3">
         <v>46029</v>
@@ -10007,7 +10007,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E369" s="2">
-        <v>81487</v>
+        <v>81486</v>
       </c>
       <c r="F369" s="3">
         <v>46029</v>
@@ -10027,16 +10027,16 @@
         <v>28</v>
       </c>
       <c r="C370" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D370" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E370" s="2">
-        <v>81613</v>
+        <v>81487</v>
       </c>
       <c r="F370" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>9</v>
@@ -10059,7 +10059,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E371" s="2">
-        <v>81614</v>
+        <v>81613</v>
       </c>
       <c r="F371" s="3">
         <v>46036</v>
@@ -10085,7 +10085,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E372" s="2">
-        <v>81622</v>
+        <v>81614</v>
       </c>
       <c r="F372" s="3">
         <v>46036</v>
@@ -10111,7 +10111,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E373" s="2">
-        <v>81632</v>
+        <v>81622</v>
       </c>
       <c r="F373" s="3">
         <v>46036</v>
@@ -10137,10 +10137,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E374" s="2">
-        <v>81648</v>
+        <v>81632</v>
       </c>
       <c r="F374" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>9</v>
@@ -10163,7 +10163,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E375" s="2">
-        <v>81664</v>
+        <v>81648</v>
       </c>
       <c r="F375" s="3">
         <v>46037</v>
@@ -10183,16 +10183,16 @@
         <v>28</v>
       </c>
       <c r="C376" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D376" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E376" s="2">
-        <v>81815</v>
+        <v>81664</v>
       </c>
       <c r="F376" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>9</v>
@@ -10215,7 +10215,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E377" s="2">
-        <v>81816</v>
+        <v>81815</v>
       </c>
       <c r="F377" s="3">
         <v>46045</v>
@@ -10241,7 +10241,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E378" s="2">
-        <v>81838</v>
+        <v>81816</v>
       </c>
       <c r="F378" s="3">
         <v>46045</v>
@@ -10267,7 +10267,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E379" s="2">
-        <v>81840</v>
+        <v>81838</v>
       </c>
       <c r="F379" s="3">
         <v>46045</v>
@@ -10287,16 +10287,16 @@
         <v>28</v>
       </c>
       <c r="C380" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D380" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E380" s="2">
-        <v>81959</v>
+        <v>81840</v>
       </c>
       <c r="F380" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>9</v>
@@ -10319,7 +10319,7 @@
         <v>46055.5991080671</v>
       </c>
       <c r="E381" s="2">
-        <v>81960</v>
+        <v>81959</v>
       </c>
       <c r="F381" s="3">
         <v>46055</v>
@@ -10339,16 +10339,16 @@
         <v>28</v>
       </c>
       <c r="C382" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D382" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E382" s="2">
-        <v>82063</v>
+        <v>81960</v>
       </c>
       <c r="F382" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>9</v>
@@ -10371,7 +10371,7 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E383" s="2">
-        <v>82064</v>
+        <v>82063</v>
       </c>
       <c r="F383" s="3">
         <v>46062</v>
@@ -10397,10 +10397,10 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E384" s="2">
-        <v>82100</v>
+        <v>82064</v>
       </c>
       <c r="F384" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>9</v>
@@ -10417,16 +10417,16 @@
         <v>28</v>
       </c>
       <c r="C385" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D385" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E385" s="2">
-        <v>82333</v>
+        <v>82100</v>
       </c>
       <c r="F385" s="3">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>9</v>
@@ -10449,7 +10449,7 @@
         <v>46072.7410579977</v>
       </c>
       <c r="E386" s="2">
-        <v>82334</v>
+        <v>82333</v>
       </c>
       <c r="F386" s="3">
         <v>46079</v>
@@ -10469,16 +10469,16 @@
         <v>28</v>
       </c>
       <c r="C387" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D387" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E387" s="2">
-        <v>82258</v>
+        <v>82334</v>
       </c>
       <c r="F387" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>9</v>
@@ -10501,7 +10501,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E388" s="2">
-        <v>82259</v>
+        <v>82258</v>
       </c>
       <c r="F388" s="3">
         <v>46076</v>
@@ -10527,7 +10527,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E389" s="2">
-        <v>82260</v>
+        <v>82259</v>
       </c>
       <c r="F389" s="3">
         <v>46076</v>
@@ -10553,10 +10553,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E390" s="2">
-        <v>82274</v>
+        <v>82260</v>
       </c>
       <c r="F390" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>9</v>
@@ -10573,16 +10573,16 @@
         <v>28</v>
       </c>
       <c r="C391" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D391" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E391" s="2">
-        <v>82409</v>
+        <v>82274</v>
       </c>
       <c r="F391" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>9</v>
@@ -10593,22 +10593,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="392">
       <c r="A392" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C392" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D392" s="3">
-        <v>46035.4386099769</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E392" s="2">
-        <v>81608</v>
+        <v>82409</v>
       </c>
       <c r="F392" s="3">
-        <v>46035</v>
+        <v>46084</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>9</v>
@@ -10631,7 +10631,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E393" s="2">
-        <v>81609</v>
+        <v>81608</v>
       </c>
       <c r="F393" s="3">
         <v>46035</v>
@@ -10657,7 +10657,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E394" s="2">
-        <v>81610</v>
+        <v>81609</v>
       </c>
       <c r="F394" s="3">
         <v>46035</v>
@@ -10683,7 +10683,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E395" s="2">
-        <v>81611</v>
+        <v>81610</v>
       </c>
       <c r="F395" s="3">
         <v>46035</v>
@@ -10709,7 +10709,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E396" s="2">
-        <v>81612</v>
+        <v>81611</v>
       </c>
       <c r="F396" s="3">
         <v>46035</v>
@@ -10729,16 +10729,16 @@
         <v>29</v>
       </c>
       <c r="C397" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D397" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E397" s="2">
-        <v>81652</v>
+        <v>81612</v>
       </c>
       <c r="F397" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>9</v>
@@ -10761,7 +10761,7 @@
         <v>46036.6342081481</v>
       </c>
       <c r="E398" s="2">
-        <v>81659</v>
+        <v>81652</v>
       </c>
       <c r="F398" s="3">
         <v>46037</v>
@@ -10781,16 +10781,16 @@
         <v>29</v>
       </c>
       <c r="C399" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D399" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E399" s="2">
-        <v>81853</v>
+        <v>81659</v>
       </c>
       <c r="F399" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>9</v>
@@ -10813,10 +10813,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E400" s="2">
-        <v>81869</v>
+        <v>81853</v>
       </c>
       <c r="F400" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>9</v>
@@ -10839,10 +10839,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E401" s="2">
-        <v>81890</v>
+        <v>81869</v>
       </c>
       <c r="F401" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10859,16 +10859,16 @@
         <v>29</v>
       </c>
       <c r="C402" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D402" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E402" s="2">
-        <v>81875</v>
+        <v>81890</v>
       </c>
       <c r="F402" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10891,10 +10891,10 @@
         <v>46049.4871256134</v>
       </c>
       <c r="E403" s="2">
-        <v>81881</v>
+        <v>81875</v>
       </c>
       <c r="F403" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10911,16 +10911,16 @@
         <v>29</v>
       </c>
       <c r="C404" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D404" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E404" s="2">
-        <v>82015</v>
+        <v>81881</v>
       </c>
       <c r="F404" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>9</v>
@@ -10943,7 +10943,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E405" s="2">
-        <v>82017</v>
+        <v>82015</v>
       </c>
       <c r="F405" s="3">
         <v>46058</v>
@@ -10969,7 +10969,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E406" s="2">
-        <v>82020</v>
+        <v>82017</v>
       </c>
       <c r="F406" s="3">
         <v>46058</v>
@@ -10995,7 +10995,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E407" s="2">
-        <v>82023</v>
+        <v>82020</v>
       </c>
       <c r="F407" s="3">
         <v>46058</v>
@@ -11021,10 +11021,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E408" s="2">
-        <v>82061</v>
+        <v>82023</v>
       </c>
       <c r="F408" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>9</v>
@@ -11047,10 +11047,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E409" s="2">
-        <v>82081</v>
+        <v>82061</v>
       </c>
       <c r="F409" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>9</v>
@@ -11073,10 +11073,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E410" s="2">
-        <v>82095</v>
+        <v>82081</v>
       </c>
       <c r="F410" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11093,16 +11093,16 @@
         <v>29</v>
       </c>
       <c r="C411" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D411" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E411" s="2">
-        <v>82081</v>
+        <v>82095</v>
       </c>
       <c r="F411" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>9</v>
@@ -11125,10 +11125,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E412" s="2">
-        <v>82107</v>
+        <v>82081</v>
       </c>
       <c r="F412" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11151,7 +11151,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E413" s="2">
-        <v>82112</v>
+        <v>82107</v>
       </c>
       <c r="F413" s="3">
         <v>46064</v>
@@ -11177,7 +11177,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E414" s="2">
-        <v>82113</v>
+        <v>82112</v>
       </c>
       <c r="F414" s="3">
         <v>46064</v>
@@ -11203,10 +11203,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E415" s="2">
-        <v>82123</v>
+        <v>82113</v>
       </c>
       <c r="F415" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>9</v>
@@ -11223,16 +11223,16 @@
         <v>29</v>
       </c>
       <c r="C416" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D416" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E416" s="2">
-        <v>82095</v>
+        <v>82123</v>
       </c>
       <c r="F416" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>9</v>
@@ -11255,7 +11255,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E417" s="2">
-        <v>82106</v>
+        <v>82095</v>
       </c>
       <c r="F417" s="3">
         <v>46064</v>
@@ -11281,7 +11281,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E418" s="2">
-        <v>82107</v>
+        <v>82106</v>
       </c>
       <c r="F418" s="3">
         <v>46064</v>
@@ -11307,7 +11307,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E419" s="2">
-        <v>82109</v>
+        <v>82107</v>
       </c>
       <c r="F419" s="3">
         <v>46064</v>
@@ -11333,7 +11333,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E420" s="2">
-        <v>82110</v>
+        <v>82109</v>
       </c>
       <c r="F420" s="3">
         <v>46064</v>
@@ -11359,10 +11359,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E421" s="2">
-        <v>82139</v>
+        <v>82110</v>
       </c>
       <c r="F421" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>9</v>
@@ -11379,16 +11379,16 @@
         <v>29</v>
       </c>
       <c r="C422" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D422" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E422" s="2">
-        <v>82365</v>
+        <v>82139</v>
       </c>
       <c r="F422" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>9</v>
@@ -11411,7 +11411,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E423" s="2">
-        <v>82366</v>
+        <v>82365</v>
       </c>
       <c r="F423" s="3">
         <v>46080</v>
@@ -11437,7 +11437,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E424" s="2">
-        <v>82371</v>
+        <v>82366</v>
       </c>
       <c r="F424" s="3">
         <v>46080</v>
@@ -11463,10 +11463,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E425" s="2">
-        <v>82383</v>
+        <v>82371</v>
       </c>
       <c r="F425" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>9</v>
@@ -11489,7 +11489,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E426" s="2">
-        <v>82384</v>
+        <v>82383</v>
       </c>
       <c r="F426" s="3">
         <v>46083</v>
@@ -11503,28 +11503,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="427">
       <c r="A427" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C427" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D427" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E427" s="2">
-        <v>81592</v>
+        <v>82384</v>
       </c>
       <c r="F427" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="428">
@@ -11541,16 +11541,16 @@
         <v>46029.4149454282</v>
       </c>
       <c r="E428" s="2">
-        <v>81593</v>
+        <v>81592</v>
       </c>
       <c r="F428" s="3">
         <v>46031</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="429">
@@ -11561,16 +11561,16 @@
         <v>30</v>
       </c>
       <c r="C429" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D429" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E429" s="2">
-        <v>81697</v>
+        <v>81593</v>
       </c>
       <c r="F429" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>9</v>
@@ -11593,16 +11593,16 @@
         <v>46038.6827563889</v>
       </c>
       <c r="E430" s="2">
-        <v>81735</v>
+        <v>81697</v>
       </c>
       <c r="F430" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="431">
@@ -11613,42 +11613,42 @@
         <v>30</v>
       </c>
       <c r="C431" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D431" s="3">
-        <v>46045.4532476157</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E431" s="2">
-        <v>81823</v>
+        <v>81735</v>
       </c>
       <c r="F431" s="3">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="432">
       <c r="A432" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C432" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D432" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E432" s="2">
-        <v>81572</v>
+        <v>81823</v>
       </c>
       <c r="F432" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11671,7 +11671,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E433" s="2">
-        <v>81573</v>
+        <v>81572</v>
       </c>
       <c r="F433" s="3">
         <v>46031</v>
@@ -11697,7 +11697,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E434" s="2">
-        <v>81579</v>
+        <v>81573</v>
       </c>
       <c r="F434" s="3">
         <v>46031</v>
@@ -11723,7 +11723,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E435" s="2">
-        <v>81580</v>
+        <v>81579</v>
       </c>
       <c r="F435" s="3">
         <v>46031</v>
@@ -11749,7 +11749,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E436" s="2">
-        <v>81581</v>
+        <v>81580</v>
       </c>
       <c r="F436" s="3">
         <v>46031</v>
@@ -11775,7 +11775,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E437" s="2">
-        <v>81582</v>
+        <v>81581</v>
       </c>
       <c r="F437" s="3">
         <v>46031</v>
@@ -11801,7 +11801,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E438" s="2">
-        <v>81583</v>
+        <v>81582</v>
       </c>
       <c r="F438" s="3">
         <v>46031</v>
@@ -11821,16 +11821,16 @@
         <v>31</v>
       </c>
       <c r="C439" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D439" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E439" s="2">
-        <v>81667</v>
+        <v>81583</v>
       </c>
       <c r="F439" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11853,7 +11853,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E440" s="2">
-        <v>81668</v>
+        <v>81667</v>
       </c>
       <c r="F440" s="3">
         <v>46037</v>
@@ -11879,10 +11879,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E441" s="2">
-        <v>81674</v>
+        <v>81668</v>
       </c>
       <c r="F441" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11905,7 +11905,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E442" s="2">
-        <v>81675</v>
+        <v>81674</v>
       </c>
       <c r="F442" s="3">
         <v>46038</v>
@@ -11931,7 +11931,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E443" s="2">
-        <v>81677</v>
+        <v>81675</v>
       </c>
       <c r="F443" s="3">
         <v>46038</v>
@@ -11951,16 +11951,16 @@
         <v>31</v>
       </c>
       <c r="C444" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D444" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E444" s="2">
-        <v>81739</v>
+        <v>81677</v>
       </c>
       <c r="F444" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11983,7 +11983,7 @@
         <v>46041.6133887269</v>
       </c>
       <c r="E445" s="2">
-        <v>81741</v>
+        <v>81739</v>
       </c>
       <c r="F445" s="3">
         <v>46041</v>
@@ -12003,16 +12003,16 @@
         <v>31</v>
       </c>
       <c r="C446" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D446" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E446" s="2">
-        <v>81854</v>
+        <v>81741</v>
       </c>
       <c r="F446" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>9</v>
@@ -12035,7 +12035,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E447" s="2">
-        <v>81855</v>
+        <v>81854</v>
       </c>
       <c r="F447" s="3">
         <v>46048</v>
@@ -12061,10 +12061,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E448" s="2">
-        <v>81858</v>
+        <v>81855</v>
       </c>
       <c r="F448" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12087,7 +12087,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E449" s="2">
-        <v>81859</v>
+        <v>81858</v>
       </c>
       <c r="F449" s="3">
         <v>46049</v>
@@ -12113,7 +12113,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E450" s="2">
-        <v>81862</v>
+        <v>81859</v>
       </c>
       <c r="F450" s="3">
         <v>46049</v>
@@ -12139,7 +12139,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E451" s="2">
-        <v>81863</v>
+        <v>81862</v>
       </c>
       <c r="F451" s="3">
         <v>46049</v>
@@ -12159,16 +12159,16 @@
         <v>31</v>
       </c>
       <c r="C452" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D452" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E452" s="2">
-        <v>81958</v>
+        <v>81863</v>
       </c>
       <c r="F452" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12191,7 +12191,7 @@
         <v>46055.5924236111</v>
       </c>
       <c r="E453" s="2">
-        <v>81965</v>
+        <v>81958</v>
       </c>
       <c r="F453" s="3">
         <v>46055</v>
@@ -12211,16 +12211,16 @@
         <v>31</v>
       </c>
       <c r="C454" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D454" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E454" s="2">
-        <v>82085</v>
+        <v>81965</v>
       </c>
       <c r="F454" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>9</v>
@@ -12243,7 +12243,7 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E455" s="2">
-        <v>82086</v>
+        <v>82085</v>
       </c>
       <c r="F455" s="3">
         <v>46063</v>
@@ -12269,10 +12269,10 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E456" s="2">
-        <v>82126</v>
+        <v>82086</v>
       </c>
       <c r="F456" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12289,16 +12289,16 @@
         <v>31</v>
       </c>
       <c r="C457" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D457" s="3">
-        <v>46064.5127051505</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E457" s="2">
-        <v>82268</v>
+        <v>82126</v>
       </c>
       <c r="F457" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>9</v>
@@ -12315,16 +12315,16 @@
         <v>31</v>
       </c>
       <c r="C458" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D458" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E458" s="2">
-        <v>82142</v>
+        <v>82268</v>
       </c>
       <c r="F458" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12347,7 +12347,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E459" s="2">
-        <v>82143</v>
+        <v>82142</v>
       </c>
       <c r="F459" s="3">
         <v>46065</v>
@@ -12373,7 +12373,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E460" s="2">
-        <v>82144</v>
+        <v>82143</v>
       </c>
       <c r="F460" s="3">
         <v>46065</v>
@@ -12399,10 +12399,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E461" s="2">
-        <v>82166</v>
+        <v>82144</v>
       </c>
       <c r="F461" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12419,16 +12419,16 @@
         <v>31</v>
       </c>
       <c r="C462" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D462" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E462" s="2">
-        <v>82262</v>
+        <v>82166</v>
       </c>
       <c r="F462" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12451,7 +12451,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E463" s="2">
-        <v>82265</v>
+        <v>82262</v>
       </c>
       <c r="F463" s="3">
         <v>46077</v>
@@ -12477,7 +12477,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E464" s="2">
-        <v>82281</v>
+        <v>82265</v>
       </c>
       <c r="F464" s="3">
         <v>46077</v>
@@ -12503,7 +12503,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E465" s="2">
-        <v>82282</v>
+        <v>82281</v>
       </c>
       <c r="F465" s="3">
         <v>46077</v>
@@ -12523,16 +12523,16 @@
         <v>31</v>
       </c>
       <c r="C466" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D466" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E466" s="2">
-        <v>82340</v>
+        <v>82282</v>
       </c>
       <c r="F466" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12549,16 +12549,16 @@
         <v>31</v>
       </c>
       <c r="C467" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D467" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E467" s="2">
-        <v>82399</v>
+        <v>82340</v>
       </c>
       <c r="F467" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>9</v>
@@ -12581,7 +12581,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E468" s="2">
-        <v>82400</v>
+        <v>82399</v>
       </c>
       <c r="F468" s="3">
         <v>46083</v>
@@ -12607,7 +12607,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E469" s="2">
-        <v>82401</v>
+        <v>82400</v>
       </c>
       <c r="F469" s="3">
         <v>46083</v>
@@ -12633,10 +12633,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E470" s="2">
-        <v>82412</v>
+        <v>82401</v>
       </c>
       <c r="F470" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>9</v>
@@ -12659,7 +12659,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E471" s="2">
-        <v>82415</v>
+        <v>82412</v>
       </c>
       <c r="F471" s="3">
         <v>46084</v>
@@ -12673,22 +12673,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="472">
       <c r="A472" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C472" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D472" s="3">
-        <v>46078.6702738773</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E472" s="2">
-        <v>82311</v>
+        <v>82415</v>
       </c>
       <c r="F472" s="3">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12711,7 +12711,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E473" s="2">
-        <v>82312</v>
+        <v>82311</v>
       </c>
       <c r="F473" s="3">
         <v>46078</v>
@@ -12737,7 +12737,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E474" s="2">
-        <v>82313</v>
+        <v>82312</v>
       </c>
       <c r="F474" s="3">
         <v>46078</v>
@@ -12763,7 +12763,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E475" s="2">
-        <v>82314</v>
+        <v>82313</v>
       </c>
       <c r="F475" s="3">
         <v>46078</v>
@@ -12789,10 +12789,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E476" s="2">
-        <v>82346</v>
+        <v>82314</v>
       </c>
       <c r="F476" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>9</v>
@@ -12815,7 +12815,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E477" s="2">
-        <v>82361</v>
+        <v>82346</v>
       </c>
       <c r="F477" s="3">
         <v>46080</v>
@@ -12841,10 +12841,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E478" s="2">
-        <v>82385</v>
+        <v>82361</v>
       </c>
       <c r="F478" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12867,7 +12867,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E479" s="2">
-        <v>82391</v>
+        <v>82385</v>
       </c>
       <c r="F479" s="3">
         <v>46083</v>
@@ -12893,7 +12893,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E480" s="2">
-        <v>82392</v>
+        <v>82391</v>
       </c>
       <c r="F480" s="3">
         <v>46083</v>
@@ -12907,22 +12907,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="481">
       <c r="A481" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C481" s="2">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D481" s="3">
-        <v>46029.4632696412</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E481" s="2">
-        <v>81495</v>
+        <v>82392</v>
       </c>
       <c r="F481" s="3">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>9</v>
@@ -12933,27 +12933,53 @@
     </row>
     <row ht="12.75" customHeight="1" r="482">
       <c r="A482" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C482" s="2">
+        <v>62</v>
+      </c>
+      <c r="D482" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E482" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F482" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G482" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H482" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="483">
+      <c r="A483" s="2">
         <v>9992</v>
       </c>
-      <c r="B482" s="1" t="s">
+      <c r="B483" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C482" s="2">
+      <c r="C483" s="2">
         <v>390</v>
       </c>
-      <c r="D482" s="3">
+      <c r="D483" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E482" s="2">
+      <c r="E483" s="2">
         <v>81684</v>
       </c>
-      <c r="F482" s="3">
+      <c r="F483" s="3">
         <v>46038</v>
       </c>
-      <c r="G482" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H482" s="1" t="s">
+      <c r="G483" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H483" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>EMPRD_CDG</t>
   </si>
@@ -60,12 +60,6 @@
   </si>
   <si>
     <t>SUN MORITZ ADMINISTRADORA</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Não Concluídos</t>
   </si>
   <si>
     <t>MARIA BELTRÃO SALDANHA COELHO</t>
@@ -411,7 +405,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H483"/>
+  <dimension ref="A1:H484"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -3175,30 +3169,30 @@
         <v>46087</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="107">
       <c r="A107" s="2">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C107" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D107" s="3">
-        <v>46014.6980340162</v>
+        <v>46087.643003044</v>
       </c>
       <c r="E107" s="2">
-        <v>81460</v>
+        <v>82496</v>
       </c>
       <c r="F107" s="3">
-        <v>46027</v>
+        <v>46090</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>9</v>
@@ -3212,7 +3206,7 @@
         <v>2409</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C108" s="2">
         <v>82</v>
@@ -3221,7 +3215,7 @@
         <v>46014.6980340162</v>
       </c>
       <c r="E108" s="2">
-        <v>81461</v>
+        <v>81460</v>
       </c>
       <c r="F108" s="3">
         <v>46027</v>
@@ -3238,7 +3232,7 @@
         <v>2409</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C109" s="2">
         <v>82</v>
@@ -3247,7 +3241,7 @@
         <v>46014.6980340162</v>
       </c>
       <c r="E109" s="2">
-        <v>81463</v>
+        <v>81461</v>
       </c>
       <c r="F109" s="3">
         <v>46027</v>
@@ -3264,19 +3258,19 @@
         <v>2409</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C110" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D110" s="3">
-        <v>46030.4707423958</v>
+        <v>46014.6980340162</v>
       </c>
       <c r="E110" s="2">
-        <v>81542</v>
+        <v>81463</v>
       </c>
       <c r="F110" s="3">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>9</v>
@@ -3290,7 +3284,7 @@
         <v>2409</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C111" s="2">
         <v>83</v>
@@ -3299,7 +3293,7 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E111" s="2">
-        <v>81548</v>
+        <v>81542</v>
       </c>
       <c r="F111" s="3">
         <v>46030</v>
@@ -3316,7 +3310,7 @@
         <v>2409</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C112" s="2">
         <v>83</v>
@@ -3325,7 +3319,7 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E112" s="2">
-        <v>81549</v>
+        <v>81548</v>
       </c>
       <c r="F112" s="3">
         <v>46030</v>
@@ -3342,7 +3336,7 @@
         <v>2409</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C113" s="2">
         <v>83</v>
@@ -3351,10 +3345,10 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E113" s="2">
-        <v>81569</v>
+        <v>81549</v>
       </c>
       <c r="F113" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>9</v>
@@ -3368,19 +3362,19 @@
         <v>2409</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C114" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D114" s="3">
-        <v>46037.6468124884</v>
+        <v>46030.4707423958</v>
       </c>
       <c r="E114" s="2">
-        <v>81669</v>
+        <v>81569</v>
       </c>
       <c r="F114" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>9</v>
@@ -3394,7 +3388,7 @@
         <v>2409</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C115" s="2">
         <v>84</v>
@@ -3403,7 +3397,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E115" s="2">
-        <v>81670</v>
+        <v>81669</v>
       </c>
       <c r="F115" s="3">
         <v>46037</v>
@@ -3420,7 +3414,7 @@
         <v>2409</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C116" s="2">
         <v>84</v>
@@ -3429,10 +3423,10 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E116" s="2">
-        <v>81673</v>
+        <v>81670</v>
       </c>
       <c r="F116" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>9</v>
@@ -3446,7 +3440,7 @@
         <v>2409</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C117" s="2">
         <v>84</v>
@@ -3455,7 +3449,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E117" s="2">
-        <v>81682</v>
+        <v>81673</v>
       </c>
       <c r="F117" s="3">
         <v>46038</v>
@@ -3472,7 +3466,7 @@
         <v>2409</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C118" s="2">
         <v>84</v>
@@ -3481,7 +3475,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E118" s="2">
-        <v>81689</v>
+        <v>81682</v>
       </c>
       <c r="F118" s="3">
         <v>46038</v>
@@ -3498,19 +3492,19 @@
         <v>2409</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C119" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D119" s="3">
-        <v>46038.5944713773</v>
+        <v>46037.6468124884</v>
       </c>
       <c r="E119" s="2">
-        <v>81707</v>
+        <v>81689</v>
       </c>
       <c r="F119" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>9</v>
@@ -3524,19 +3518,19 @@
         <v>2409</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C120" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D120" s="3">
-        <v>46049.490160081</v>
+        <v>46038.5944713773</v>
       </c>
       <c r="E120" s="2">
-        <v>81866</v>
+        <v>81707</v>
       </c>
       <c r="F120" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>9</v>
@@ -3550,7 +3544,7 @@
         <v>2409</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C121" s="2">
         <v>86</v>
@@ -3559,7 +3553,7 @@
         <v>46049.490160081</v>
       </c>
       <c r="E121" s="2">
-        <v>81867</v>
+        <v>81866</v>
       </c>
       <c r="F121" s="3">
         <v>46049</v>
@@ -3576,7 +3570,7 @@
         <v>2409</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C122" s="2">
         <v>86</v>
@@ -3585,7 +3579,7 @@
         <v>46049.490160081</v>
       </c>
       <c r="E122" s="2">
-        <v>81871</v>
+        <v>81867</v>
       </c>
       <c r="F122" s="3">
         <v>46049</v>
@@ -3602,7 +3596,7 @@
         <v>2409</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C123" s="2">
         <v>86</v>
@@ -3611,10 +3605,10 @@
         <v>46049.490160081</v>
       </c>
       <c r="E123" s="2">
-        <v>81882</v>
+        <v>81871</v>
       </c>
       <c r="F123" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>9</v>
@@ -3628,19 +3622,19 @@
         <v>2409</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C124" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D124" s="3">
-        <v>46051.4127791667</v>
+        <v>46049.490160081</v>
       </c>
       <c r="E124" s="2">
-        <v>81922</v>
+        <v>81882</v>
       </c>
       <c r="F124" s="3">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>9</v>
@@ -3654,19 +3648,19 @@
         <v>2409</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C125" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D125" s="3">
-        <v>46056.7141110995</v>
+        <v>46051.4127791667</v>
       </c>
       <c r="E125" s="2">
-        <v>81972</v>
+        <v>81922</v>
       </c>
       <c r="F125" s="3">
-        <v>46056</v>
+        <v>46051</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>9</v>
@@ -3680,7 +3674,7 @@
         <v>2409</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C126" s="2">
         <v>88</v>
@@ -3689,7 +3683,7 @@
         <v>46056.7141110995</v>
       </c>
       <c r="E126" s="2">
-        <v>81973</v>
+        <v>81972</v>
       </c>
       <c r="F126" s="3">
         <v>46056</v>
@@ -3706,7 +3700,7 @@
         <v>2409</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C127" s="2">
         <v>88</v>
@@ -3715,10 +3709,10 @@
         <v>46056.7141110995</v>
       </c>
       <c r="E127" s="2">
-        <v>81993</v>
+        <v>81973</v>
       </c>
       <c r="F127" s="3">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>9</v>
@@ -3732,19 +3726,19 @@
         <v>2409</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C128" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D128" s="3">
-        <v>46063.7282468519</v>
+        <v>46056.7141110995</v>
       </c>
       <c r="E128" s="2">
-        <v>82090</v>
+        <v>81993</v>
       </c>
       <c r="F128" s="3">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>9</v>
@@ -3758,7 +3752,7 @@
         <v>2409</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C129" s="2">
         <v>89</v>
@@ -3767,7 +3761,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E129" s="2">
-        <v>82093</v>
+        <v>82090</v>
       </c>
       <c r="F129" s="3">
         <v>46063</v>
@@ -3784,7 +3778,7 @@
         <v>2409</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C130" s="2">
         <v>89</v>
@@ -3793,10 +3787,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E130" s="2">
-        <v>82094</v>
+        <v>82093</v>
       </c>
       <c r="F130" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>9</v>
@@ -3810,7 +3804,7 @@
         <v>2409</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C131" s="2">
         <v>89</v>
@@ -3819,7 +3813,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E131" s="2">
-        <v>82098</v>
+        <v>82094</v>
       </c>
       <c r="F131" s="3">
         <v>46064</v>
@@ -3836,7 +3830,7 @@
         <v>2409</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C132" s="2">
         <v>89</v>
@@ -3845,7 +3839,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E132" s="2">
-        <v>82119</v>
+        <v>82098</v>
       </c>
       <c r="F132" s="3">
         <v>46064</v>
@@ -3862,7 +3856,7 @@
         <v>2409</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C133" s="2">
         <v>89</v>
@@ -3871,7 +3865,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E133" s="2">
-        <v>82120</v>
+        <v>82119</v>
       </c>
       <c r="F133" s="3">
         <v>46064</v>
@@ -3888,7 +3882,7 @@
         <v>2409</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C134" s="2">
         <v>89</v>
@@ -3897,10 +3891,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E134" s="2">
-        <v>82131</v>
+        <v>82120</v>
       </c>
       <c r="F134" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>9</v>
@@ -3914,19 +3908,19 @@
         <v>2409</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C135" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D135" s="3">
-        <v>46078.6817048032</v>
+        <v>46063.7282468519</v>
       </c>
       <c r="E135" s="2">
-        <v>82316</v>
+        <v>82131</v>
       </c>
       <c r="F135" s="3">
-        <v>46078</v>
+        <v>46065</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>9</v>
@@ -3940,7 +3934,7 @@
         <v>2409</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C136" s="2">
         <v>90</v>
@@ -3949,10 +3943,10 @@
         <v>46078.6817048032</v>
       </c>
       <c r="E136" s="2">
-        <v>82325</v>
+        <v>82316</v>
       </c>
       <c r="F136" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>9</v>
@@ -3966,7 +3960,7 @@
         <v>2409</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C137" s="2">
         <v>90</v>
@@ -3975,7 +3969,7 @@
         <v>46078.6817048032</v>
       </c>
       <c r="E137" s="2">
-        <v>82327</v>
+        <v>82325</v>
       </c>
       <c r="F137" s="3">
         <v>46079</v>
@@ -3992,19 +3986,19 @@
         <v>2409</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C138" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D138" s="3">
-        <v>46086.632572419</v>
+        <v>46078.6817048032</v>
       </c>
       <c r="E138" s="2">
-        <v>82471</v>
+        <v>82327</v>
       </c>
       <c r="F138" s="3">
-        <v>46086</v>
+        <v>46079</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>9</v>
@@ -4018,7 +4012,7 @@
         <v>2409</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C139" s="2">
         <v>92</v>
@@ -4027,10 +4021,10 @@
         <v>46086.632572419</v>
       </c>
       <c r="E139" s="2">
-        <v>82476</v>
+        <v>82471</v>
       </c>
       <c r="F139" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>9</v>
@@ -4041,22 +4035,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="140">
       <c r="A140" s="2">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C140" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D140" s="3">
-        <v>46030.4179771875</v>
+        <v>46086.632572419</v>
       </c>
       <c r="E140" s="2">
-        <v>81536</v>
+        <v>82476</v>
       </c>
       <c r="F140" s="3">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>9</v>
@@ -4070,7 +4064,7 @@
         <v>2411</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C141" s="2">
         <v>77</v>
@@ -4079,7 +4073,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E141" s="2">
-        <v>81538</v>
+        <v>81536</v>
       </c>
       <c r="F141" s="3">
         <v>46030</v>
@@ -4096,7 +4090,7 @@
         <v>2411</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C142" s="2">
         <v>77</v>
@@ -4105,7 +4099,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E142" s="2">
-        <v>81555</v>
+        <v>81538</v>
       </c>
       <c r="F142" s="3">
         <v>46030</v>
@@ -4122,7 +4116,7 @@
         <v>2411</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C143" s="2">
         <v>77</v>
@@ -4131,7 +4125,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E143" s="2">
-        <v>81556</v>
+        <v>81555</v>
       </c>
       <c r="F143" s="3">
         <v>46030</v>
@@ -4148,7 +4142,7 @@
         <v>2411</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C144" s="2">
         <v>77</v>
@@ -4157,7 +4151,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E144" s="2">
-        <v>81558</v>
+        <v>81556</v>
       </c>
       <c r="F144" s="3">
         <v>46030</v>
@@ -4174,19 +4168,19 @@
         <v>2411</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C145" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D145" s="3">
-        <v>46036.4079311574</v>
+        <v>46030.4179771875</v>
       </c>
       <c r="E145" s="2">
-        <v>81615</v>
+        <v>81558</v>
       </c>
       <c r="F145" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>9</v>
@@ -4200,7 +4194,7 @@
         <v>2411</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C146" s="2">
         <v>78</v>
@@ -4209,7 +4203,7 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E146" s="2">
-        <v>81621</v>
+        <v>81615</v>
       </c>
       <c r="F146" s="3">
         <v>46036</v>
@@ -4226,7 +4220,7 @@
         <v>2411</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C147" s="2">
         <v>78</v>
@@ -4235,10 +4229,10 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E147" s="2">
-        <v>81647</v>
+        <v>81621</v>
       </c>
       <c r="F147" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>9</v>
@@ -4249,22 +4243,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="148">
       <c r="A148" s="2">
-        <v>2504</v>
+        <v>2411</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C148" s="2">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D148" s="3">
-        <v>46027.6983957986</v>
+        <v>46036.4079311574</v>
       </c>
       <c r="E148" s="2">
-        <v>81465</v>
+        <v>81647</v>
       </c>
       <c r="F148" s="3">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>9</v>
@@ -4278,7 +4272,7 @@
         <v>2504</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C149" s="2">
         <v>44</v>
@@ -4287,16 +4281,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E149" s="2">
-        <v>81466</v>
+        <v>81465</v>
       </c>
       <c r="F149" s="3">
         <v>46027</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="150">
@@ -4304,7 +4298,7 @@
         <v>2504</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C150" s="2">
         <v>44</v>
@@ -4313,16 +4307,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E150" s="2">
-        <v>81471</v>
+        <v>81466</v>
       </c>
       <c r="F150" s="3">
         <v>46027</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="151">
@@ -4330,7 +4324,7 @@
         <v>2504</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C151" s="2">
         <v>44</v>
@@ -4339,10 +4333,10 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E151" s="2">
-        <v>81488</v>
+        <v>81471</v>
       </c>
       <c r="F151" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>9</v>
@@ -4356,7 +4350,7 @@
         <v>2504</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C152" s="2">
         <v>44</v>
@@ -4365,7 +4359,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E152" s="2">
-        <v>81489</v>
+        <v>81488</v>
       </c>
       <c r="F152" s="3">
         <v>46029</v>
@@ -4382,7 +4376,7 @@
         <v>2504</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C153" s="2">
         <v>44</v>
@@ -4391,7 +4385,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E153" s="2">
-        <v>81490</v>
+        <v>81489</v>
       </c>
       <c r="F153" s="3">
         <v>46029</v>
@@ -4408,7 +4402,7 @@
         <v>2504</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C154" s="2">
         <v>44</v>
@@ -4417,7 +4411,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E154" s="2">
-        <v>81491</v>
+        <v>81490</v>
       </c>
       <c r="F154" s="3">
         <v>46029</v>
@@ -4434,19 +4428,19 @@
         <v>2504</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C155" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D155" s="3">
-        <v>46038.4184531713</v>
+        <v>46027.6983957986</v>
       </c>
       <c r="E155" s="2">
-        <v>81688</v>
+        <v>81491</v>
       </c>
       <c r="F155" s="3">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>9</v>
@@ -4460,16 +4454,16 @@
         <v>2504</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C156" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D156" s="3">
-        <v>46038.6993878241</v>
+        <v>46038.4184531713</v>
       </c>
       <c r="E156" s="2">
-        <v>81700</v>
+        <v>81688</v>
       </c>
       <c r="F156" s="3">
         <v>46038</v>
@@ -4486,7 +4480,7 @@
         <v>2504</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C157" s="2">
         <v>46</v>
@@ -4495,7 +4489,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E157" s="2">
-        <v>81701</v>
+        <v>81700</v>
       </c>
       <c r="F157" s="3">
         <v>46038</v>
@@ -4512,7 +4506,7 @@
         <v>2504</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C158" s="2">
         <v>46</v>
@@ -4521,7 +4515,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E158" s="2">
-        <v>81702</v>
+        <v>81701</v>
       </c>
       <c r="F158" s="3">
         <v>46038</v>
@@ -4538,7 +4532,7 @@
         <v>2504</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C159" s="2">
         <v>46</v>
@@ -4547,7 +4541,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E159" s="2">
-        <v>81703</v>
+        <v>81702</v>
       </c>
       <c r="F159" s="3">
         <v>46038</v>
@@ -4564,7 +4558,7 @@
         <v>2504</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C160" s="2">
         <v>46</v>
@@ -4573,10 +4567,10 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E160" s="2">
-        <v>81734</v>
+        <v>81703</v>
       </c>
       <c r="F160" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>9</v>
@@ -4590,19 +4584,19 @@
         <v>2504</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C161" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D161" s="3">
-        <v>46050.7176682523</v>
+        <v>46038.6993878241</v>
       </c>
       <c r="E161" s="2">
-        <v>81914</v>
+        <v>81734</v>
       </c>
       <c r="F161" s="3">
-        <v>46051</v>
+        <v>46041</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>9</v>
@@ -4616,7 +4610,7 @@
         <v>2504</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C162" s="2">
         <v>47</v>
@@ -4625,7 +4619,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E162" s="2">
-        <v>81915</v>
+        <v>81914</v>
       </c>
       <c r="F162" s="3">
         <v>46051</v>
@@ -4642,7 +4636,7 @@
         <v>2504</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C163" s="2">
         <v>47</v>
@@ -4651,7 +4645,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E163" s="2">
-        <v>81921</v>
+        <v>81915</v>
       </c>
       <c r="F163" s="3">
         <v>46051</v>
@@ -4668,19 +4662,19 @@
         <v>2504</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C164" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D164" s="3">
-        <v>46052.6247194676</v>
+        <v>46050.7176682523</v>
       </c>
       <c r="E164" s="2">
-        <v>81949</v>
+        <v>81921</v>
       </c>
       <c r="F164" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>9</v>
@@ -4694,7 +4688,7 @@
         <v>2504</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C165" s="2">
         <v>48</v>
@@ -4703,7 +4697,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E165" s="2">
-        <v>81950</v>
+        <v>81949</v>
       </c>
       <c r="F165" s="3">
         <v>46052</v>
@@ -4720,7 +4714,7 @@
         <v>2504</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C166" s="2">
         <v>48</v>
@@ -4729,7 +4723,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E166" s="2">
-        <v>81951</v>
+        <v>81950</v>
       </c>
       <c r="F166" s="3">
         <v>46052</v>
@@ -4746,7 +4740,7 @@
         <v>2504</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C167" s="2">
         <v>48</v>
@@ -4755,7 +4749,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E167" s="2">
-        <v>81953</v>
+        <v>81951</v>
       </c>
       <c r="F167" s="3">
         <v>46052</v>
@@ -4772,19 +4766,19 @@
         <v>2504</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C168" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D168" s="3">
-        <v>46058.6976675694</v>
+        <v>46052.6247194676</v>
       </c>
       <c r="E168" s="2">
-        <v>82028</v>
+        <v>81953</v>
       </c>
       <c r="F168" s="3">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>9</v>
@@ -4798,7 +4792,7 @@
         <v>2504</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C169" s="2">
         <v>49</v>
@@ -4807,7 +4801,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E169" s="2">
-        <v>82029</v>
+        <v>82028</v>
       </c>
       <c r="F169" s="3">
         <v>46058</v>
@@ -4824,7 +4818,7 @@
         <v>2504</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C170" s="2">
         <v>49</v>
@@ -4833,10 +4827,10 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E170" s="2">
-        <v>82040</v>
+        <v>82029</v>
       </c>
       <c r="F170" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>9</v>
@@ -4850,7 +4844,7 @@
         <v>2504</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C171" s="2">
         <v>49</v>
@@ -4859,7 +4853,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E171" s="2">
-        <v>82041</v>
+        <v>82040</v>
       </c>
       <c r="F171" s="3">
         <v>46059</v>
@@ -4876,7 +4870,7 @@
         <v>2504</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C172" s="2">
         <v>49</v>
@@ -4885,7 +4879,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E172" s="2">
-        <v>82051</v>
+        <v>82041</v>
       </c>
       <c r="F172" s="3">
         <v>46059</v>
@@ -4902,19 +4896,19 @@
         <v>2504</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C173" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D173" s="3">
-        <v>46065.6309066782</v>
+        <v>46058.6976675694</v>
       </c>
       <c r="E173" s="2">
-        <v>82168</v>
+        <v>82051</v>
       </c>
       <c r="F173" s="3">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>9</v>
@@ -4928,7 +4922,7 @@
         <v>2504</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C174" s="2">
         <v>50</v>
@@ -4937,16 +4931,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E174" s="2">
-        <v>82170</v>
+        <v>82168</v>
       </c>
       <c r="F174" s="3">
         <v>46066</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="175">
@@ -4954,7 +4948,7 @@
         <v>2504</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C175" s="2">
         <v>50</v>
@@ -4963,16 +4957,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E175" s="2">
-        <v>82171</v>
+        <v>82170</v>
       </c>
       <c r="F175" s="3">
         <v>46066</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="176">
@@ -4980,7 +4974,7 @@
         <v>2504</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C176" s="2">
         <v>50</v>
@@ -4989,7 +4983,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E176" s="2">
-        <v>82172</v>
+        <v>82171</v>
       </c>
       <c r="F176" s="3">
         <v>46066</v>
@@ -5006,7 +5000,7 @@
         <v>2504</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C177" s="2">
         <v>50</v>
@@ -5015,7 +5009,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E177" s="2">
-        <v>82175</v>
+        <v>82172</v>
       </c>
       <c r="F177" s="3">
         <v>46066</v>
@@ -5032,7 +5026,7 @@
         <v>2504</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C178" s="2">
         <v>50</v>
@@ -5041,7 +5035,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E178" s="2">
-        <v>82176</v>
+        <v>82175</v>
       </c>
       <c r="F178" s="3">
         <v>46066</v>
@@ -5058,19 +5052,19 @@
         <v>2504</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C179" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D179" s="3">
-        <v>46072.5909779051</v>
+        <v>46065.6309066782</v>
       </c>
       <c r="E179" s="2">
-        <v>82206</v>
+        <v>82176</v>
       </c>
       <c r="F179" s="3">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>9</v>
@@ -5084,19 +5078,19 @@
         <v>2504</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C180" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D180" s="3">
-        <v>46077.7262228935</v>
+        <v>46072.5909779051</v>
       </c>
       <c r="E180" s="2">
-        <v>82289</v>
+        <v>82206</v>
       </c>
       <c r="F180" s="3">
-        <v>46077</v>
+        <v>46072</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>9</v>
@@ -5110,7 +5104,7 @@
         <v>2504</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C181" s="2">
         <v>52</v>
@@ -5119,7 +5113,7 @@
         <v>46077.7262228935</v>
       </c>
       <c r="E181" s="2">
-        <v>82290</v>
+        <v>82289</v>
       </c>
       <c r="F181" s="3">
         <v>46077</v>
@@ -5136,19 +5130,19 @@
         <v>2504</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C182" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D182" s="3">
-        <v>46078.6799843634</v>
+        <v>46077.7262228935</v>
       </c>
       <c r="E182" s="2">
-        <v>82318</v>
+        <v>82290</v>
       </c>
       <c r="F182" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>9</v>
@@ -5162,19 +5156,19 @@
         <v>2504</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C183" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D183" s="3">
-        <v>46080.6294471412</v>
+        <v>46078.6799843634</v>
       </c>
       <c r="E183" s="2">
-        <v>82368</v>
+        <v>82318</v>
       </c>
       <c r="F183" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>9</v>
@@ -5188,19 +5182,19 @@
         <v>2504</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C184" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D184" s="3">
-        <v>46084.741264838</v>
+        <v>46080.6294471412</v>
       </c>
       <c r="E184" s="2">
-        <v>82425</v>
+        <v>82368</v>
       </c>
       <c r="F184" s="3">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>9</v>
@@ -5214,7 +5208,7 @@
         <v>2504</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C185" s="2">
         <v>55</v>
@@ -5223,7 +5217,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="E185" s="2">
-        <v>82426</v>
+        <v>82425</v>
       </c>
       <c r="F185" s="3">
         <v>46084</v>
@@ -5240,7 +5234,7 @@
         <v>2504</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C186" s="2">
         <v>55</v>
@@ -5249,10 +5243,10 @@
         <v>46084.741264838</v>
       </c>
       <c r="E186" s="2">
-        <v>82430</v>
+        <v>82426</v>
       </c>
       <c r="F186" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>9</v>
@@ -5266,7 +5260,7 @@
         <v>2504</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C187" s="2">
         <v>55</v>
@@ -5275,7 +5269,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="E187" s="2">
-        <v>82431</v>
+        <v>82430</v>
       </c>
       <c r="F187" s="3">
         <v>46085</v>
@@ -5289,22 +5283,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="188">
       <c r="A188" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C188" s="2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D188" s="3">
-        <v>46041.6648751157</v>
+        <v>46084.741264838</v>
       </c>
       <c r="E188" s="2">
-        <v>81743</v>
+        <v>82431</v>
       </c>
       <c r="F188" s="3">
-        <v>46041</v>
+        <v>46085</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>9</v>
@@ -5318,7 +5312,7 @@
         <v>2505</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C189" s="2">
         <v>42</v>
@@ -5327,7 +5321,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E189" s="2">
-        <v>81744</v>
+        <v>81743</v>
       </c>
       <c r="F189" s="3">
         <v>46041</v>
@@ -5344,7 +5338,7 @@
         <v>2505</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C190" s="2">
         <v>42</v>
@@ -5353,7 +5347,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E190" s="2">
-        <v>81745</v>
+        <v>81744</v>
       </c>
       <c r="F190" s="3">
         <v>46041</v>
@@ -5370,7 +5364,7 @@
         <v>2505</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C191" s="2">
         <v>42</v>
@@ -5379,10 +5373,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E191" s="2">
-        <v>81746</v>
+        <v>81745</v>
       </c>
       <c r="F191" s="3">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>9</v>
@@ -5396,7 +5390,7 @@
         <v>2505</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C192" s="2">
         <v>42</v>
@@ -5405,10 +5399,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E192" s="2">
-        <v>81751</v>
+        <v>81746</v>
       </c>
       <c r="F192" s="3">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>9</v>
@@ -5422,7 +5416,7 @@
         <v>2505</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C193" s="2">
         <v>42</v>
@@ -5431,7 +5425,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E193" s="2">
-        <v>81753</v>
+        <v>81751</v>
       </c>
       <c r="F193" s="3">
         <v>46043</v>
@@ -5448,7 +5442,7 @@
         <v>2505</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C194" s="2">
         <v>42</v>
@@ -5457,7 +5451,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E194" s="2">
-        <v>81754</v>
+        <v>81753</v>
       </c>
       <c r="F194" s="3">
         <v>46043</v>
@@ -5474,7 +5468,7 @@
         <v>2505</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C195" s="2">
         <v>42</v>
@@ -5483,7 +5477,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E195" s="2">
-        <v>81755</v>
+        <v>81754</v>
       </c>
       <c r="F195" s="3">
         <v>46043</v>
@@ -5500,7 +5494,7 @@
         <v>2505</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C196" s="2">
         <v>42</v>
@@ -5509,7 +5503,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E196" s="2">
-        <v>81766</v>
+        <v>81755</v>
       </c>
       <c r="F196" s="3">
         <v>46043</v>
@@ -5526,19 +5520,19 @@
         <v>2505</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C197" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D197" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E197" s="2">
-        <v>82088</v>
+        <v>81766</v>
       </c>
       <c r="F197" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>9</v>
@@ -5552,7 +5546,7 @@
         <v>2505</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C198" s="2">
         <v>43</v>
@@ -5561,7 +5555,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E198" s="2">
-        <v>82089</v>
+        <v>82088</v>
       </c>
       <c r="F198" s="3">
         <v>46063</v>
@@ -5578,7 +5572,7 @@
         <v>2505</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C199" s="2">
         <v>43</v>
@@ -5587,10 +5581,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E199" s="2">
-        <v>82163</v>
+        <v>82089</v>
       </c>
       <c r="F199" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>9</v>
@@ -5604,7 +5598,7 @@
         <v>2505</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C200" s="2">
         <v>43</v>
@@ -5613,7 +5607,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E200" s="2">
-        <v>82179</v>
+        <v>82163</v>
       </c>
       <c r="F200" s="3">
         <v>46066</v>
@@ -5630,7 +5624,7 @@
         <v>2505</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C201" s="2">
         <v>43</v>
@@ -5639,7 +5633,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E201" s="2">
-        <v>82193</v>
+        <v>82179</v>
       </c>
       <c r="F201" s="3">
         <v>46066</v>
@@ -5656,19 +5650,19 @@
         <v>2505</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C202" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D202" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E202" s="2">
-        <v>82250</v>
+        <v>82193</v>
       </c>
       <c r="F202" s="3">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>9</v>
@@ -5682,7 +5676,7 @@
         <v>2505</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C203" s="2">
         <v>44</v>
@@ -5691,10 +5685,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E203" s="2">
-        <v>82266</v>
+        <v>82250</v>
       </c>
       <c r="F203" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>9</v>
@@ -5708,7 +5702,7 @@
         <v>2505</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C204" s="2">
         <v>44</v>
@@ -5717,10 +5711,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E204" s="2">
-        <v>82295</v>
+        <v>82266</v>
       </c>
       <c r="F204" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>9</v>
@@ -5734,7 +5728,7 @@
         <v>2505</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C205" s="2">
         <v>44</v>
@@ -5743,7 +5737,7 @@
         <v>46073.714168287</v>
       </c>
       <c r="E205" s="2">
-        <v>82296</v>
+        <v>82295</v>
       </c>
       <c r="F205" s="3">
         <v>46078</v>
@@ -5760,7 +5754,7 @@
         <v>2505</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C206" s="2">
         <v>44</v>
@@ -5769,16 +5763,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E206" s="2">
-        <v>82332</v>
+        <v>82296</v>
       </c>
       <c r="F206" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="207">
@@ -5786,7 +5780,7 @@
         <v>2505</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C207" s="2">
         <v>44</v>
@@ -5795,16 +5789,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E207" s="2">
-        <v>82339</v>
+        <v>82332</v>
       </c>
       <c r="F207" s="3">
         <v>46079</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="208">
@@ -5812,19 +5806,19 @@
         <v>2505</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C208" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D208" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E208" s="2">
-        <v>82266</v>
+        <v>82339</v>
       </c>
       <c r="F208" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>9</v>
@@ -5838,7 +5832,7 @@
         <v>2505</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C209" s="2">
         <v>45</v>
@@ -5847,7 +5841,7 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E209" s="2">
-        <v>82273</v>
+        <v>82266</v>
       </c>
       <c r="F209" s="3">
         <v>46077</v>
@@ -5864,7 +5858,7 @@
         <v>2505</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C210" s="2">
         <v>45</v>
@@ -5873,10 +5867,10 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E210" s="2">
-        <v>82294</v>
+        <v>82273</v>
       </c>
       <c r="F210" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>9</v>
@@ -5890,19 +5884,19 @@
         <v>2505</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C211" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D211" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E211" s="2">
-        <v>82411</v>
+        <v>82294</v>
       </c>
       <c r="F211" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>9</v>
@@ -5916,7 +5910,7 @@
         <v>2505</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C212" s="2">
         <v>46</v>
@@ -5925,10 +5919,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E212" s="2">
-        <v>82432</v>
+        <v>82411</v>
       </c>
       <c r="F212" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>9</v>
@@ -5942,7 +5936,7 @@
         <v>2505</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C213" s="2">
         <v>46</v>
@@ -5951,10 +5945,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E213" s="2">
-        <v>82473</v>
+        <v>82432</v>
       </c>
       <c r="F213" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>9</v>
@@ -5968,7 +5962,7 @@
         <v>2505</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C214" s="2">
         <v>46</v>
@@ -5977,10 +5971,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E214" s="2">
-        <v>82474</v>
+        <v>82473</v>
       </c>
       <c r="F214" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>9</v>
@@ -5991,22 +5985,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="215">
       <c r="A215" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C215" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D215" s="3">
-        <v>46044.6368950926</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E215" s="2">
-        <v>81802</v>
+        <v>82474</v>
       </c>
       <c r="F215" s="3">
-        <v>46044</v>
+        <v>46087</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>9</v>
@@ -6020,7 +6014,7 @@
         <v>2506</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C216" s="2">
         <v>27</v>
@@ -6029,7 +6023,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E216" s="2">
-        <v>81803</v>
+        <v>81802</v>
       </c>
       <c r="F216" s="3">
         <v>46044</v>
@@ -6046,7 +6040,7 @@
         <v>2506</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C217" s="2">
         <v>27</v>
@@ -6055,7 +6049,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E217" s="2">
-        <v>81804</v>
+        <v>81803</v>
       </c>
       <c r="F217" s="3">
         <v>46044</v>
@@ -6072,7 +6066,7 @@
         <v>2506</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C218" s="2">
         <v>27</v>
@@ -6081,7 +6075,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E218" s="2">
-        <v>81806</v>
+        <v>81804</v>
       </c>
       <c r="F218" s="3">
         <v>46044</v>
@@ -6098,7 +6092,7 @@
         <v>2506</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C219" s="2">
         <v>27</v>
@@ -6107,7 +6101,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E219" s="2">
-        <v>81807</v>
+        <v>81806</v>
       </c>
       <c r="F219" s="3">
         <v>46044</v>
@@ -6124,7 +6118,7 @@
         <v>2506</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C220" s="2">
         <v>27</v>
@@ -6133,10 +6127,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E220" s="2">
-        <v>81812</v>
+        <v>81807</v>
       </c>
       <c r="F220" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>9</v>
@@ -6150,7 +6144,7 @@
         <v>2506</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C221" s="2">
         <v>27</v>
@@ -6159,7 +6153,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E221" s="2">
-        <v>81813</v>
+        <v>81812</v>
       </c>
       <c r="F221" s="3">
         <v>46045</v>
@@ -6176,7 +6170,7 @@
         <v>2506</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C222" s="2">
         <v>27</v>
@@ -6185,7 +6179,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E222" s="2">
-        <v>81814</v>
+        <v>81813</v>
       </c>
       <c r="F222" s="3">
         <v>46045</v>
@@ -6202,7 +6196,7 @@
         <v>2506</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C223" s="2">
         <v>27</v>
@@ -6211,7 +6205,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E223" s="2">
-        <v>81818</v>
+        <v>81814</v>
       </c>
       <c r="F223" s="3">
         <v>46045</v>
@@ -6228,7 +6222,7 @@
         <v>2506</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C224" s="2">
         <v>27</v>
@@ -6237,7 +6231,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E224" s="2">
-        <v>81822</v>
+        <v>81818</v>
       </c>
       <c r="F224" s="3">
         <v>46045</v>
@@ -6254,7 +6248,7 @@
         <v>2506</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C225" s="2">
         <v>27</v>
@@ -6263,7 +6257,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E225" s="2">
-        <v>81833</v>
+        <v>81822</v>
       </c>
       <c r="F225" s="3">
         <v>46045</v>
@@ -6280,7 +6274,7 @@
         <v>2506</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C226" s="2">
         <v>27</v>
@@ -6289,7 +6283,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E226" s="2">
-        <v>81841</v>
+        <v>81833</v>
       </c>
       <c r="F226" s="3">
         <v>46045</v>
@@ -6306,19 +6300,19 @@
         <v>2506</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C227" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D227" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E227" s="2">
-        <v>81928</v>
+        <v>81841</v>
       </c>
       <c r="F227" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>9</v>
@@ -6332,7 +6326,7 @@
         <v>2506</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C228" s="2">
         <v>28</v>
@@ -6341,7 +6335,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E228" s="2">
-        <v>81929</v>
+        <v>81928</v>
       </c>
       <c r="F228" s="3">
         <v>46052</v>
@@ -6358,7 +6352,7 @@
         <v>2506</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C229" s="2">
         <v>28</v>
@@ -6367,7 +6361,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E229" s="2">
-        <v>81930</v>
+        <v>81929</v>
       </c>
       <c r="F229" s="3">
         <v>46052</v>
@@ -6384,7 +6378,7 @@
         <v>2506</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C230" s="2">
         <v>28</v>
@@ -6393,7 +6387,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E230" s="2">
-        <v>81932</v>
+        <v>81930</v>
       </c>
       <c r="F230" s="3">
         <v>46052</v>
@@ -6410,7 +6404,7 @@
         <v>2506</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C231" s="2">
         <v>28</v>
@@ -6419,7 +6413,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E231" s="2">
-        <v>81933</v>
+        <v>81932</v>
       </c>
       <c r="F231" s="3">
         <v>46052</v>
@@ -6436,7 +6430,7 @@
         <v>2506</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C232" s="2">
         <v>28</v>
@@ -6445,7 +6439,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E232" s="2">
-        <v>81934</v>
+        <v>81933</v>
       </c>
       <c r="F232" s="3">
         <v>46052</v>
@@ -6462,7 +6456,7 @@
         <v>2506</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C233" s="2">
         <v>28</v>
@@ -6471,7 +6465,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E233" s="2">
-        <v>81935</v>
+        <v>81934</v>
       </c>
       <c r="F233" s="3">
         <v>46052</v>
@@ -6488,7 +6482,7 @@
         <v>2506</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C234" s="2">
         <v>28</v>
@@ -6497,7 +6491,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E234" s="2">
-        <v>81936</v>
+        <v>81935</v>
       </c>
       <c r="F234" s="3">
         <v>46052</v>
@@ -6514,19 +6508,19 @@
         <v>2506</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C235" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D235" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E235" s="2">
-        <v>82222</v>
+        <v>81936</v>
       </c>
       <c r="F235" s="3">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>9</v>
@@ -6540,7 +6534,7 @@
         <v>2506</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C236" s="2">
         <v>29</v>
@@ -6549,10 +6543,10 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E236" s="2">
-        <v>82226</v>
+        <v>82222</v>
       </c>
       <c r="F236" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>9</v>
@@ -6566,7 +6560,7 @@
         <v>2506</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C237" s="2">
         <v>29</v>
@@ -6575,7 +6569,7 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E237" s="2">
-        <v>82229</v>
+        <v>82226</v>
       </c>
       <c r="F237" s="3">
         <v>46073</v>
@@ -6592,16 +6586,16 @@
         <v>2506</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C238" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D238" s="3">
-        <v>46073.5838834375</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E238" s="2">
-        <v>82246</v>
+        <v>82229</v>
       </c>
       <c r="F238" s="3">
         <v>46073</v>
@@ -6618,19 +6612,19 @@
         <v>2506</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C239" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D239" s="3">
-        <v>46080.6289065162</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E239" s="2">
-        <v>82387</v>
+        <v>82246</v>
       </c>
       <c r="F239" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>9</v>
@@ -6641,22 +6635,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="240">
       <c r="A240" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C240" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D240" s="3">
-        <v>46029.4161474769</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E240" s="2">
-        <v>81478</v>
+        <v>82387</v>
       </c>
       <c r="F240" s="3">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>9</v>
@@ -6670,7 +6664,7 @@
         <v>2507</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C241" s="2">
         <v>26</v>
@@ -6679,7 +6673,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E241" s="2">
-        <v>81479</v>
+        <v>81478</v>
       </c>
       <c r="F241" s="3">
         <v>46029</v>
@@ -6696,7 +6690,7 @@
         <v>2507</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C242" s="2">
         <v>26</v>
@@ -6705,7 +6699,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E242" s="2">
-        <v>81480</v>
+        <v>81479</v>
       </c>
       <c r="F242" s="3">
         <v>46029</v>
@@ -6722,7 +6716,7 @@
         <v>2507</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C243" s="2">
         <v>26</v>
@@ -6731,7 +6725,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E243" s="2">
-        <v>81497</v>
+        <v>81480</v>
       </c>
       <c r="F243" s="3">
         <v>46029</v>
@@ -6748,7 +6742,7 @@
         <v>2507</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C244" s="2">
         <v>26</v>
@@ -6757,7 +6751,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E244" s="2">
-        <v>81498</v>
+        <v>81497</v>
       </c>
       <c r="F244" s="3">
         <v>46029</v>
@@ -6774,7 +6768,7 @@
         <v>2507</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C245" s="2">
         <v>26</v>
@@ -6783,7 +6777,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E245" s="2">
-        <v>81499</v>
+        <v>81498</v>
       </c>
       <c r="F245" s="3">
         <v>46029</v>
@@ -6800,7 +6794,7 @@
         <v>2507</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C246" s="2">
         <v>26</v>
@@ -6809,7 +6803,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E246" s="2">
-        <v>81500</v>
+        <v>81499</v>
       </c>
       <c r="F246" s="3">
         <v>46029</v>
@@ -6826,19 +6820,19 @@
         <v>2507</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C247" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D247" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E247" s="2">
-        <v>81878</v>
+        <v>81500</v>
       </c>
       <c r="F247" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>9</v>
@@ -6852,7 +6846,7 @@
         <v>2507</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C248" s="2">
         <v>27</v>
@@ -6861,7 +6855,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E248" s="2">
-        <v>81879</v>
+        <v>81878</v>
       </c>
       <c r="F248" s="3">
         <v>46049</v>
@@ -6878,7 +6872,7 @@
         <v>2507</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C249" s="2">
         <v>27</v>
@@ -6887,10 +6881,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E249" s="2">
-        <v>81885</v>
+        <v>81879</v>
       </c>
       <c r="F249" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>9</v>
@@ -6904,7 +6898,7 @@
         <v>2507</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C250" s="2">
         <v>27</v>
@@ -6913,7 +6907,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E250" s="2">
-        <v>81886</v>
+        <v>81885</v>
       </c>
       <c r="F250" s="3">
         <v>46050</v>
@@ -6930,19 +6924,19 @@
         <v>2507</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C251" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D251" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E251" s="2">
-        <v>82068</v>
+        <v>81886</v>
       </c>
       <c r="F251" s="3">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>9</v>
@@ -6956,7 +6950,7 @@
         <v>2507</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C252" s="2">
         <v>28</v>
@@ -6965,10 +6959,10 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E252" s="2">
-        <v>82072</v>
+        <v>82068</v>
       </c>
       <c r="F252" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>9</v>
@@ -6982,7 +6976,7 @@
         <v>2507</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C253" s="2">
         <v>28</v>
@@ -6991,7 +6985,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E253" s="2">
-        <v>82076</v>
+        <v>82072</v>
       </c>
       <c r="F253" s="3">
         <v>46063</v>
@@ -7008,7 +7002,7 @@
         <v>2507</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C254" s="2">
         <v>28</v>
@@ -7017,7 +7011,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E254" s="2">
-        <v>82078</v>
+        <v>82076</v>
       </c>
       <c r="F254" s="3">
         <v>46063</v>
@@ -7034,19 +7028,19 @@
         <v>2507</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C255" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D255" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E255" s="2">
-        <v>82287</v>
+        <v>82078</v>
       </c>
       <c r="F255" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>9</v>
@@ -7060,7 +7054,7 @@
         <v>2507</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C256" s="2">
         <v>29</v>
@@ -7069,7 +7063,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E256" s="2">
-        <v>82288</v>
+        <v>82287</v>
       </c>
       <c r="F256" s="3">
         <v>46077</v>
@@ -7086,7 +7080,7 @@
         <v>2507</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C257" s="2">
         <v>29</v>
@@ -7095,10 +7089,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E257" s="2">
-        <v>82298</v>
+        <v>82288</v>
       </c>
       <c r="F257" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>9</v>
@@ -7112,7 +7106,7 @@
         <v>2507</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C258" s="2">
         <v>29</v>
@@ -7121,7 +7115,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E258" s="2">
-        <v>82301</v>
+        <v>82298</v>
       </c>
       <c r="F258" s="3">
         <v>46078</v>
@@ -7138,7 +7132,7 @@
         <v>2507</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C259" s="2">
         <v>29</v>
@@ -7147,7 +7141,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E259" s="2">
-        <v>82304</v>
+        <v>82301</v>
       </c>
       <c r="F259" s="3">
         <v>46078</v>
@@ -7164,7 +7158,7 @@
         <v>2507</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C260" s="2">
         <v>29</v>
@@ -7173,7 +7167,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E260" s="2">
-        <v>82308</v>
+        <v>82304</v>
       </c>
       <c r="F260" s="3">
         <v>46078</v>
@@ -7190,19 +7184,19 @@
         <v>2507</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C261" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D261" s="3">
-        <v>46080.628344919</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E261" s="2">
-        <v>82373</v>
+        <v>82308</v>
       </c>
       <c r="F261" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>9</v>
@@ -7216,19 +7210,19 @@
         <v>2507</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C262" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D262" s="3">
-        <v>46085.6581644213</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E262" s="2">
-        <v>82445</v>
+        <v>82373</v>
       </c>
       <c r="F262" s="3">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>9</v>
@@ -7242,7 +7236,7 @@
         <v>2507</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C263" s="2">
         <v>31</v>
@@ -7251,7 +7245,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E263" s="2">
-        <v>82447</v>
+        <v>82445</v>
       </c>
       <c r="F263" s="3">
         <v>46085</v>
@@ -7268,7 +7262,7 @@
         <v>2507</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C264" s="2">
         <v>31</v>
@@ -7277,10 +7271,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E264" s="2">
-        <v>82453</v>
+        <v>82447</v>
       </c>
       <c r="F264" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>9</v>
@@ -7294,7 +7288,7 @@
         <v>2507</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C265" s="2">
         <v>31</v>
@@ -7303,7 +7297,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E265" s="2">
-        <v>82468</v>
+        <v>82453</v>
       </c>
       <c r="F265" s="3">
         <v>46086</v>
@@ -7317,22 +7311,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="266">
       <c r="A266" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C266" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D266" s="3">
-        <v>46029.6400966782</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E266" s="2">
-        <v>81506</v>
+        <v>82468</v>
       </c>
       <c r="F266" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>9</v>
@@ -7346,7 +7340,7 @@
         <v>2509</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C267" s="2">
         <v>22</v>
@@ -7355,7 +7349,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E267" s="2">
-        <v>81507</v>
+        <v>81506</v>
       </c>
       <c r="F267" s="3">
         <v>46029</v>
@@ -7372,7 +7366,7 @@
         <v>2509</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C268" s="2">
         <v>22</v>
@@ -7381,10 +7375,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E268" s="2">
-        <v>81524</v>
+        <v>81507</v>
       </c>
       <c r="F268" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>9</v>
@@ -7398,7 +7392,7 @@
         <v>2509</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C269" s="2">
         <v>22</v>
@@ -7407,7 +7401,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E269" s="2">
-        <v>81525</v>
+        <v>81524</v>
       </c>
       <c r="F269" s="3">
         <v>46030</v>
@@ -7424,7 +7418,7 @@
         <v>2509</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C270" s="2">
         <v>22</v>
@@ -7433,7 +7427,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E270" s="2">
-        <v>81526</v>
+        <v>81525</v>
       </c>
       <c r="F270" s="3">
         <v>46030</v>
@@ -7450,19 +7444,19 @@
         <v>2509</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C271" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D271" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E271" s="2">
-        <v>81640</v>
+        <v>81526</v>
       </c>
       <c r="F271" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>9</v>
@@ -7476,7 +7470,7 @@
         <v>2509</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C272" s="2">
         <v>23</v>
@@ -7485,7 +7479,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E272" s="2">
-        <v>81642</v>
+        <v>81640</v>
       </c>
       <c r="F272" s="3">
         <v>46036</v>
@@ -7502,7 +7496,7 @@
         <v>2509</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C273" s="2">
         <v>23</v>
@@ -7511,7 +7505,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E273" s="2">
-        <v>81643</v>
+        <v>81642</v>
       </c>
       <c r="F273" s="3">
         <v>46036</v>
@@ -7528,19 +7522,19 @@
         <v>2509</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C274" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D274" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E274" s="2">
-        <v>81835</v>
+        <v>81643</v>
       </c>
       <c r="F274" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>9</v>
@@ -7554,7 +7548,7 @@
         <v>2509</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C275" s="2">
         <v>24</v>
@@ -7563,7 +7557,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E275" s="2">
-        <v>81836</v>
+        <v>81835</v>
       </c>
       <c r="F275" s="3">
         <v>46045</v>
@@ -7580,7 +7574,7 @@
         <v>2509</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C276" s="2">
         <v>24</v>
@@ -7589,7 +7583,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E276" s="2">
-        <v>81837</v>
+        <v>81836</v>
       </c>
       <c r="F276" s="3">
         <v>46045</v>
@@ -7606,19 +7600,19 @@
         <v>2509</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C277" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D277" s="3">
-        <v>46051.6376515278</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E277" s="2">
-        <v>81931</v>
+        <v>81837</v>
       </c>
       <c r="F277" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>9</v>
@@ -7632,19 +7626,19 @@
         <v>2509</v>
       </c>
       <c r="B278" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C278" s="2">
         <v>25</v>
       </c>
-      <c r="C278" s="2">
-        <v>26</v>
-      </c>
       <c r="D278" s="3">
-        <v>46056.7115158912</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E278" s="2">
-        <v>81978</v>
+        <v>81931</v>
       </c>
       <c r="F278" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>9</v>
@@ -7658,16 +7652,16 @@
         <v>2509</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C279" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D279" s="3">
-        <v>46057.6911087731</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E279" s="2">
-        <v>81994</v>
+        <v>81978</v>
       </c>
       <c r="F279" s="3">
         <v>46057</v>
@@ -7684,7 +7678,7 @@
         <v>2509</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C280" s="2">
         <v>27</v>
@@ -7693,7 +7687,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E280" s="2">
-        <v>81995</v>
+        <v>81994</v>
       </c>
       <c r="F280" s="3">
         <v>46057</v>
@@ -7710,7 +7704,7 @@
         <v>2509</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C281" s="2">
         <v>27</v>
@@ -7719,7 +7713,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E281" s="2">
-        <v>81999</v>
+        <v>81995</v>
       </c>
       <c r="F281" s="3">
         <v>46057</v>
@@ -7736,7 +7730,7 @@
         <v>2509</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C282" s="2">
         <v>27</v>
@@ -7745,10 +7739,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E282" s="2">
-        <v>82008</v>
+        <v>81999</v>
       </c>
       <c r="F282" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>9</v>
@@ -7762,7 +7756,7 @@
         <v>2509</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C283" s="2">
         <v>27</v>
@@ -7771,7 +7765,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E283" s="2">
-        <v>82011</v>
+        <v>82008</v>
       </c>
       <c r="F283" s="3">
         <v>46058</v>
@@ -7788,7 +7782,7 @@
         <v>2509</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C284" s="2">
         <v>27</v>
@@ -7797,7 +7791,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E284" s="2">
-        <v>82012</v>
+        <v>82011</v>
       </c>
       <c r="F284" s="3">
         <v>46058</v>
@@ -7814,7 +7808,7 @@
         <v>2509</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C285" s="2">
         <v>27</v>
@@ -7823,7 +7817,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E285" s="2">
-        <v>82013</v>
+        <v>82012</v>
       </c>
       <c r="F285" s="3">
         <v>46058</v>
@@ -7840,7 +7834,7 @@
         <v>2509</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C286" s="2">
         <v>27</v>
@@ -7849,7 +7843,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E286" s="2">
-        <v>82014</v>
+        <v>82013</v>
       </c>
       <c r="F286" s="3">
         <v>46058</v>
@@ -7866,25 +7860,25 @@
         <v>2509</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C287" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D287" s="3">
-        <v>46058.6604985417</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E287" s="2">
-        <v>82046</v>
+        <v>82014</v>
       </c>
       <c r="F287" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="288">
@@ -7892,25 +7886,25 @@
         <v>2509</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C288" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D288" s="3">
-        <v>46072.738871875</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E288" s="2">
-        <v>82217</v>
+        <v>82046</v>
       </c>
       <c r="F288" s="3">
-        <v>46072</v>
+        <v>46059</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="289">
@@ -7918,7 +7912,7 @@
         <v>2509</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C289" s="2">
         <v>29</v>
@@ -7927,7 +7921,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E289" s="2">
-        <v>82218</v>
+        <v>82217</v>
       </c>
       <c r="F289" s="3">
         <v>46072</v>
@@ -7944,7 +7938,7 @@
         <v>2509</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C290" s="2">
         <v>29</v>
@@ -7953,10 +7947,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E290" s="2">
-        <v>82234</v>
+        <v>82218</v>
       </c>
       <c r="F290" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>9</v>
@@ -7970,7 +7964,7 @@
         <v>2509</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C291" s="2">
         <v>29</v>
@@ -7979,7 +7973,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E291" s="2">
-        <v>82238</v>
+        <v>82234</v>
       </c>
       <c r="F291" s="3">
         <v>46073</v>
@@ -7996,7 +7990,7 @@
         <v>2509</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C292" s="2">
         <v>29</v>
@@ -8005,7 +7999,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E292" s="2">
-        <v>82245</v>
+        <v>82238</v>
       </c>
       <c r="F292" s="3">
         <v>46073</v>
@@ -8022,19 +8016,19 @@
         <v>2509</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C293" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D293" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E293" s="2">
-        <v>82257</v>
+        <v>82245</v>
       </c>
       <c r="F293" s="3">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>9</v>
@@ -8048,7 +8042,7 @@
         <v>2509</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C294" s="2">
         <v>30</v>
@@ -8057,10 +8051,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E294" s="2">
-        <v>82276</v>
+        <v>82257</v>
       </c>
       <c r="F294" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>9</v>
@@ -8074,7 +8068,7 @@
         <v>2509</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C295" s="2">
         <v>30</v>
@@ -8083,7 +8077,7 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E295" s="2">
-        <v>82277</v>
+        <v>82276</v>
       </c>
       <c r="F295" s="3">
         <v>46077</v>
@@ -8100,7 +8094,7 @@
         <v>2509</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C296" s="2">
         <v>30</v>
@@ -8109,10 +8103,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E296" s="2">
-        <v>82293</v>
+        <v>82277</v>
       </c>
       <c r="F296" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>9</v>
@@ -8126,19 +8120,19 @@
         <v>2509</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C297" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D297" s="3">
-        <v>46077.4356327431</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E297" s="2">
-        <v>82269</v>
+        <v>82293</v>
       </c>
       <c r="F297" s="3">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>9</v>
@@ -8152,19 +8146,19 @@
         <v>2509</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C298" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D298" s="3">
-        <v>46084.7378501505</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E298" s="2">
-        <v>82419</v>
+        <v>82269</v>
       </c>
       <c r="F298" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>9</v>
@@ -8178,7 +8172,7 @@
         <v>2509</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C299" s="2">
         <v>32</v>
@@ -8187,7 +8181,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E299" s="2">
-        <v>82420</v>
+        <v>82419</v>
       </c>
       <c r="F299" s="3">
         <v>46084</v>
@@ -8204,7 +8198,7 @@
         <v>2509</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C300" s="2">
         <v>32</v>
@@ -8213,7 +8207,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E300" s="2">
-        <v>82421</v>
+        <v>82420</v>
       </c>
       <c r="F300" s="3">
         <v>46084</v>
@@ -8230,7 +8224,7 @@
         <v>2509</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C301" s="2">
         <v>32</v>
@@ -8239,7 +8233,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E301" s="2">
-        <v>82422</v>
+        <v>82421</v>
       </c>
       <c r="F301" s="3">
         <v>46084</v>
@@ -8256,7 +8250,7 @@
         <v>2509</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C302" s="2">
         <v>32</v>
@@ -8265,7 +8259,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E302" s="2">
-        <v>82423</v>
+        <v>82422</v>
       </c>
       <c r="F302" s="3">
         <v>46084</v>
@@ -8282,7 +8276,7 @@
         <v>2509</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C303" s="2">
         <v>32</v>
@@ -8291,10 +8285,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E303" s="2">
-        <v>82433</v>
+        <v>82423</v>
       </c>
       <c r="F303" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>9</v>
@@ -8308,7 +8302,7 @@
         <v>2509</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C304" s="2">
         <v>32</v>
@@ -8317,7 +8311,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E304" s="2">
-        <v>82434</v>
+        <v>82433</v>
       </c>
       <c r="F304" s="3">
         <v>46085</v>
@@ -8334,7 +8328,7 @@
         <v>2509</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C305" s="2">
         <v>32</v>
@@ -8343,10 +8337,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E305" s="2">
-        <v>82464</v>
+        <v>82434</v>
       </c>
       <c r="F305" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>9</v>
@@ -8360,7 +8354,7 @@
         <v>2509</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C306" s="2">
         <v>32</v>
@@ -8369,7 +8363,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E306" s="2">
-        <v>82472</v>
+        <v>82464</v>
       </c>
       <c r="F306" s="3">
         <v>46086</v>
@@ -8383,22 +8377,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="307">
       <c r="A307" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C307" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D307" s="3">
-        <v>46027.6953206134</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E307" s="2">
-        <v>81464</v>
+        <v>82472</v>
       </c>
       <c r="F307" s="3">
-        <v>46027</v>
+        <v>46086</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>9</v>
@@ -8412,7 +8406,7 @@
         <v>2510</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C308" s="2">
         <v>25</v>
@@ -8421,7 +8415,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E308" s="2">
-        <v>81472</v>
+        <v>81464</v>
       </c>
       <c r="F308" s="3">
         <v>46027</v>
@@ -8438,7 +8432,7 @@
         <v>2510</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C309" s="2">
         <v>25</v>
@@ -8447,10 +8441,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E309" s="2">
-        <v>81492</v>
+        <v>81472</v>
       </c>
       <c r="F309" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>9</v>
@@ -8464,7 +8458,7 @@
         <v>2510</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C310" s="2">
         <v>25</v>
@@ -8473,7 +8467,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E310" s="2">
-        <v>81493</v>
+        <v>81492</v>
       </c>
       <c r="F310" s="3">
         <v>46029</v>
@@ -8490,7 +8484,7 @@
         <v>2510</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C311" s="2">
         <v>25</v>
@@ -8499,10 +8493,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E311" s="2">
-        <v>81568</v>
+        <v>81493</v>
       </c>
       <c r="F311" s="3">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>9</v>
@@ -8516,7 +8510,7 @@
         <v>2510</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C312" s="2">
         <v>25</v>
@@ -8525,10 +8519,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E312" s="2">
-        <v>81601</v>
+        <v>81568</v>
       </c>
       <c r="F312" s="3">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>9</v>
@@ -8542,7 +8536,7 @@
         <v>2510</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C313" s="2">
         <v>25</v>
@@ -8551,7 +8545,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E313" s="2">
-        <v>81602</v>
+        <v>81601</v>
       </c>
       <c r="F313" s="3">
         <v>46034</v>
@@ -8568,19 +8562,19 @@
         <v>2510</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C314" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D314" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E314" s="2">
-        <v>81645</v>
+        <v>81602</v>
       </c>
       <c r="F314" s="3">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>9</v>
@@ -8594,7 +8588,7 @@
         <v>2510</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C315" s="2">
         <v>26</v>
@@ -8603,7 +8597,7 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E315" s="2">
-        <v>81646</v>
+        <v>81645</v>
       </c>
       <c r="F315" s="3">
         <v>46036</v>
@@ -8620,7 +8614,7 @@
         <v>2510</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C316" s="2">
         <v>26</v>
@@ -8629,10 +8623,10 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E316" s="2">
-        <v>81653</v>
+        <v>81646</v>
       </c>
       <c r="F316" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>9</v>
@@ -8646,16 +8640,16 @@
         <v>2510</v>
       </c>
       <c r="B317" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C317" s="2">
         <v>26</v>
       </c>
-      <c r="C317" s="2">
-        <v>27</v>
-      </c>
       <c r="D317" s="3">
-        <v>46037.4325152662</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E317" s="2">
-        <v>81662</v>
+        <v>81653</v>
       </c>
       <c r="F317" s="3">
         <v>46037</v>
@@ -8672,19 +8666,19 @@
         <v>2510</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C318" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D318" s="3">
-        <v>46044.4079891435</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E318" s="2">
-        <v>81780</v>
+        <v>81662</v>
       </c>
       <c r="F318" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>9</v>
@@ -8698,7 +8692,7 @@
         <v>2510</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C319" s="2">
         <v>28</v>
@@ -8707,7 +8701,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E319" s="2">
-        <v>81781</v>
+        <v>81780</v>
       </c>
       <c r="F319" s="3">
         <v>46044</v>
@@ -8724,7 +8718,7 @@
         <v>2510</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C320" s="2">
         <v>28</v>
@@ -8733,7 +8727,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E320" s="2">
-        <v>81782</v>
+        <v>81781</v>
       </c>
       <c r="F320" s="3">
         <v>46044</v>
@@ -8750,7 +8744,7 @@
         <v>2510</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C321" s="2">
         <v>28</v>
@@ -8759,7 +8753,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E321" s="2">
-        <v>81784</v>
+        <v>81782</v>
       </c>
       <c r="F321" s="3">
         <v>46044</v>
@@ -8776,7 +8770,7 @@
         <v>2510</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C322" s="2">
         <v>28</v>
@@ -8785,7 +8779,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E322" s="2">
-        <v>81785</v>
+        <v>81784</v>
       </c>
       <c r="F322" s="3">
         <v>46044</v>
@@ -8802,7 +8796,7 @@
         <v>2510</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C323" s="2">
         <v>28</v>
@@ -8811,7 +8805,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E323" s="2">
-        <v>81801</v>
+        <v>81785</v>
       </c>
       <c r="F323" s="3">
         <v>46044</v>
@@ -8828,19 +8822,19 @@
         <v>2510</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C324" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D324" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E324" s="2">
-        <v>81860</v>
+        <v>81801</v>
       </c>
       <c r="F324" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>9</v>
@@ -8854,7 +8848,7 @@
         <v>2510</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C325" s="2">
         <v>29</v>
@@ -8863,7 +8857,7 @@
         <v>46048.7319778588</v>
       </c>
       <c r="E325" s="2">
-        <v>81873</v>
+        <v>81860</v>
       </c>
       <c r="F325" s="3">
         <v>46049</v>
@@ -8880,16 +8874,16 @@
         <v>2510</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C326" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D326" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E326" s="2">
-        <v>81865</v>
+        <v>81873</v>
       </c>
       <c r="F326" s="3">
         <v>46049</v>
@@ -8906,7 +8900,7 @@
         <v>2510</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C327" s="2">
         <v>30</v>
@@ -8915,7 +8909,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E327" s="2">
-        <v>81870</v>
+        <v>81865</v>
       </c>
       <c r="F327" s="3">
         <v>46049</v>
@@ -8932,7 +8926,7 @@
         <v>2510</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C328" s="2">
         <v>30</v>
@@ -8941,7 +8935,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E328" s="2">
-        <v>81872</v>
+        <v>81870</v>
       </c>
       <c r="F328" s="3">
         <v>46049</v>
@@ -8958,7 +8952,7 @@
         <v>2510</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C329" s="2">
         <v>30</v>
@@ -8967,10 +8961,10 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E329" s="2">
-        <v>81896</v>
+        <v>81872</v>
       </c>
       <c r="F329" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>9</v>
@@ -8984,19 +8978,19 @@
         <v>2510</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C330" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D330" s="3">
-        <v>46051.4046937153</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E330" s="2">
-        <v>81923</v>
+        <v>81896</v>
       </c>
       <c r="F330" s="3">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>9</v>
@@ -9010,19 +9004,19 @@
         <v>2510</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C331" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D331" s="3">
-        <v>46057.6959672917</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E331" s="2">
-        <v>81998</v>
+        <v>81923</v>
       </c>
       <c r="F331" s="3">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>9</v>
@@ -9036,7 +9030,7 @@
         <v>2510</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C332" s="2">
         <v>32</v>
@@ -9045,7 +9039,7 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E332" s="2">
-        <v>82002</v>
+        <v>81998</v>
       </c>
       <c r="F332" s="3">
         <v>46057</v>
@@ -9062,7 +9056,7 @@
         <v>2510</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C333" s="2">
         <v>32</v>
@@ -9071,10 +9065,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E333" s="2">
-        <v>82005</v>
+        <v>82002</v>
       </c>
       <c r="F333" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>9</v>
@@ -9088,7 +9082,7 @@
         <v>2510</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C334" s="2">
         <v>32</v>
@@ -9097,7 +9091,7 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E334" s="2">
-        <v>82007</v>
+        <v>82005</v>
       </c>
       <c r="F334" s="3">
         <v>46058</v>
@@ -9114,16 +9108,16 @@
         <v>2510</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C335" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D335" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E335" s="2">
-        <v>82005</v>
+        <v>82007</v>
       </c>
       <c r="F335" s="3">
         <v>46058</v>
@@ -9140,7 +9134,7 @@
         <v>2510</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C336" s="2">
         <v>33</v>
@@ -9149,10 +9143,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E336" s="2">
-        <v>82075</v>
+        <v>82005</v>
       </c>
       <c r="F336" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>9</v>
@@ -9166,7 +9160,7 @@
         <v>2510</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C337" s="2">
         <v>33</v>
@@ -9175,7 +9169,7 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E337" s="2">
-        <v>82077</v>
+        <v>82075</v>
       </c>
       <c r="F337" s="3">
         <v>46063</v>
@@ -9192,7 +9186,7 @@
         <v>2510</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C338" s="2">
         <v>33</v>
@@ -9201,10 +9195,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E338" s="2">
-        <v>82099</v>
+        <v>82077</v>
       </c>
       <c r="F338" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>9</v>
@@ -9218,19 +9212,19 @@
         <v>2510</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C339" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D339" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E339" s="2">
-        <v>82219</v>
+        <v>82099</v>
       </c>
       <c r="F339" s="3">
-        <v>46072</v>
+        <v>46064</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>9</v>
@@ -9244,7 +9238,7 @@
         <v>2510</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C340" s="2">
         <v>34</v>
@@ -9253,10 +9247,10 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E340" s="2">
-        <v>82230</v>
+        <v>82219</v>
       </c>
       <c r="F340" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>9</v>
@@ -9270,7 +9264,7 @@
         <v>2510</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C341" s="2">
         <v>34</v>
@@ -9279,7 +9273,7 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E341" s="2">
-        <v>82231</v>
+        <v>82230</v>
       </c>
       <c r="F341" s="3">
         <v>46073</v>
@@ -9296,19 +9290,19 @@
         <v>2510</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C342" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D342" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E342" s="2">
-        <v>82388</v>
+        <v>82231</v>
       </c>
       <c r="F342" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>9</v>
@@ -9322,7 +9316,7 @@
         <v>2510</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C343" s="2">
         <v>35</v>
@@ -9331,7 +9325,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E343" s="2">
-        <v>82389</v>
+        <v>82388</v>
       </c>
       <c r="F343" s="3">
         <v>46083</v>
@@ -9348,7 +9342,7 @@
         <v>2510</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C344" s="2">
         <v>35</v>
@@ -9357,7 +9351,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E344" s="2">
-        <v>82396</v>
+        <v>82389</v>
       </c>
       <c r="F344" s="3">
         <v>46083</v>
@@ -9374,7 +9368,7 @@
         <v>2510</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C345" s="2">
         <v>35</v>
@@ -9383,7 +9377,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E345" s="2">
-        <v>82397</v>
+        <v>82396</v>
       </c>
       <c r="F345" s="3">
         <v>46083</v>
@@ -9400,19 +9394,19 @@
         <v>2510</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C346" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D346" s="3">
-        <v>46085.6249659838</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E346" s="2">
-        <v>82435</v>
+        <v>82397</v>
       </c>
       <c r="F346" s="3">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>9</v>
@@ -9423,22 +9417,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="347">
       <c r="A347" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C347" s="2">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D347" s="3">
-        <v>46029.3821391551</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E347" s="2">
-        <v>81477</v>
+        <v>82435</v>
       </c>
       <c r="F347" s="3">
-        <v>46029</v>
+        <v>46085</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>9</v>
@@ -9452,19 +9446,19 @@
         <v>2511</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C348" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D348" s="3">
-        <v>46030.4142968056</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E348" s="2">
-        <v>81532</v>
+        <v>81477</v>
       </c>
       <c r="F348" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>9</v>
@@ -9478,7 +9472,7 @@
         <v>2511</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C349" s="2">
         <v>18</v>
@@ -9487,7 +9481,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E349" s="2">
-        <v>81534</v>
+        <v>81532</v>
       </c>
       <c r="F349" s="3">
         <v>46030</v>
@@ -9504,7 +9498,7 @@
         <v>2511</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C350" s="2">
         <v>18</v>
@@ -9513,7 +9507,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E350" s="2">
-        <v>81535</v>
+        <v>81534</v>
       </c>
       <c r="F350" s="3">
         <v>46030</v>
@@ -9530,7 +9524,7 @@
         <v>2511</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C351" s="2">
         <v>18</v>
@@ -9539,7 +9533,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E351" s="2">
-        <v>81550</v>
+        <v>81535</v>
       </c>
       <c r="F351" s="3">
         <v>46030</v>
@@ -9556,7 +9550,7 @@
         <v>2511</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C352" s="2">
         <v>18</v>
@@ -9565,7 +9559,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E352" s="2">
-        <v>81553</v>
+        <v>81550</v>
       </c>
       <c r="F352" s="3">
         <v>46030</v>
@@ -9582,7 +9576,7 @@
         <v>2511</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C353" s="2">
         <v>18</v>
@@ -9591,7 +9585,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E353" s="2">
-        <v>81554</v>
+        <v>81553</v>
       </c>
       <c r="F353" s="3">
         <v>46030</v>
@@ -9608,7 +9602,7 @@
         <v>2511</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C354" s="2">
         <v>18</v>
@@ -9617,7 +9611,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E354" s="2">
-        <v>81557</v>
+        <v>81554</v>
       </c>
       <c r="F354" s="3">
         <v>46030</v>
@@ -9634,7 +9628,7 @@
         <v>2511</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C355" s="2">
         <v>18</v>
@@ -9643,10 +9637,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E355" s="2">
-        <v>81588</v>
+        <v>81557</v>
       </c>
       <c r="F355" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>9</v>
@@ -9660,19 +9654,19 @@
         <v>2511</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C356" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D356" s="3">
-        <v>46038.593985081</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E356" s="2">
-        <v>81692</v>
+        <v>81588</v>
       </c>
       <c r="F356" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>9</v>
@@ -9686,19 +9680,19 @@
         <v>2511</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C357" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D357" s="3">
-        <v>46044.46462125</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E357" s="2">
-        <v>81786</v>
+        <v>81692</v>
       </c>
       <c r="F357" s="3">
-        <v>46044</v>
+        <v>46038</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>9</v>
@@ -9712,19 +9706,19 @@
         <v>2511</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C358" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D358" s="3">
-        <v>46044.6362443171</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E358" s="2">
-        <v>81844</v>
+        <v>81786</v>
       </c>
       <c r="F358" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>9</v>
@@ -9738,19 +9732,19 @@
         <v>2511</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C359" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D359" s="3">
-        <v>46062.717040544</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E359" s="2">
-        <v>82065</v>
+        <v>81844</v>
       </c>
       <c r="F359" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>9</v>
@@ -9764,7 +9758,7 @@
         <v>2511</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C360" s="2">
         <v>22</v>
@@ -9773,7 +9767,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E360" s="2">
-        <v>82066</v>
+        <v>82065</v>
       </c>
       <c r="F360" s="3">
         <v>46062</v>
@@ -9790,7 +9784,7 @@
         <v>2511</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C361" s="2">
         <v>22</v>
@@ -9799,7 +9793,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E361" s="2">
-        <v>82067</v>
+        <v>82066</v>
       </c>
       <c r="F361" s="3">
         <v>46062</v>
@@ -9816,19 +9810,19 @@
         <v>2511</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C362" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D362" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E362" s="2">
-        <v>82190</v>
+        <v>82067</v>
       </c>
       <c r="F362" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G362" s="1" t="s">
         <v>9</v>
@@ -9842,7 +9836,7 @@
         <v>2511</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C363" s="2">
         <v>23</v>
@@ -9851,7 +9845,7 @@
         <v>46065.6300915625</v>
       </c>
       <c r="E363" s="2">
-        <v>82197</v>
+        <v>82190</v>
       </c>
       <c r="F363" s="3">
         <v>46066</v>
@@ -9868,19 +9862,19 @@
         <v>2511</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C364" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D364" s="3">
-        <v>46077.5084780324</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E364" s="2">
-        <v>82270</v>
+        <v>82197</v>
       </c>
       <c r="F364" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>9</v>
@@ -9894,16 +9888,16 @@
         <v>2511</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C365" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D365" s="3">
-        <v>46077.721037037</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E365" s="2">
-        <v>82285</v>
+        <v>82270</v>
       </c>
       <c r="F365" s="3">
         <v>46077</v>
@@ -9920,19 +9914,19 @@
         <v>2511</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C366" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D366" s="3">
-        <v>46083.6694849421</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E366" s="2">
-        <v>82417</v>
+        <v>82285</v>
       </c>
       <c r="F366" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>9</v>
@@ -9946,19 +9940,19 @@
         <v>2511</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C367" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D367" s="3">
-        <v>46085.7157723032</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E367" s="2">
-        <v>82457</v>
+        <v>82417</v>
       </c>
       <c r="F367" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>9</v>
@@ -9969,22 +9963,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="368">
       <c r="A368" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C368" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D368" s="3">
-        <v>46029.381258831</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E368" s="2">
-        <v>81484</v>
+        <v>82457</v>
       </c>
       <c r="F368" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>9</v>
@@ -9998,7 +9992,7 @@
         <v>2512</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C369" s="2">
         <v>13</v>
@@ -10007,7 +10001,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E369" s="2">
-        <v>81486</v>
+        <v>81484</v>
       </c>
       <c r="F369" s="3">
         <v>46029</v>
@@ -10024,7 +10018,7 @@
         <v>2512</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C370" s="2">
         <v>13</v>
@@ -10033,7 +10027,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E370" s="2">
-        <v>81487</v>
+        <v>81486</v>
       </c>
       <c r="F370" s="3">
         <v>46029</v>
@@ -10050,19 +10044,19 @@
         <v>2512</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C371" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D371" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E371" s="2">
-        <v>81613</v>
+        <v>81487</v>
       </c>
       <c r="F371" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>9</v>
@@ -10076,7 +10070,7 @@
         <v>2512</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C372" s="2">
         <v>14</v>
@@ -10085,7 +10079,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E372" s="2">
-        <v>81614</v>
+        <v>81613</v>
       </c>
       <c r="F372" s="3">
         <v>46036</v>
@@ -10102,7 +10096,7 @@
         <v>2512</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C373" s="2">
         <v>14</v>
@@ -10111,7 +10105,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E373" s="2">
-        <v>81622</v>
+        <v>81614</v>
       </c>
       <c r="F373" s="3">
         <v>46036</v>
@@ -10128,7 +10122,7 @@
         <v>2512</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C374" s="2">
         <v>14</v>
@@ -10137,7 +10131,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E374" s="2">
-        <v>81632</v>
+        <v>81622</v>
       </c>
       <c r="F374" s="3">
         <v>46036</v>
@@ -10154,7 +10148,7 @@
         <v>2512</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C375" s="2">
         <v>14</v>
@@ -10163,10 +10157,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E375" s="2">
-        <v>81648</v>
+        <v>81632</v>
       </c>
       <c r="F375" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>9</v>
@@ -10180,7 +10174,7 @@
         <v>2512</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C376" s="2">
         <v>14</v>
@@ -10189,7 +10183,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E376" s="2">
-        <v>81664</v>
+        <v>81648</v>
       </c>
       <c r="F376" s="3">
         <v>46037</v>
@@ -10206,19 +10200,19 @@
         <v>2512</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C377" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D377" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E377" s="2">
-        <v>81815</v>
+        <v>81664</v>
       </c>
       <c r="F377" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>9</v>
@@ -10232,7 +10226,7 @@
         <v>2512</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C378" s="2">
         <v>15</v>
@@ -10241,7 +10235,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E378" s="2">
-        <v>81816</v>
+        <v>81815</v>
       </c>
       <c r="F378" s="3">
         <v>46045</v>
@@ -10258,7 +10252,7 @@
         <v>2512</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C379" s="2">
         <v>15</v>
@@ -10267,7 +10261,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E379" s="2">
-        <v>81838</v>
+        <v>81816</v>
       </c>
       <c r="F379" s="3">
         <v>46045</v>
@@ -10284,7 +10278,7 @@
         <v>2512</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C380" s="2">
         <v>15</v>
@@ -10293,7 +10287,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E380" s="2">
-        <v>81840</v>
+        <v>81838</v>
       </c>
       <c r="F380" s="3">
         <v>46045</v>
@@ -10310,19 +10304,19 @@
         <v>2512</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C381" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D381" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E381" s="2">
-        <v>81959</v>
+        <v>81840</v>
       </c>
       <c r="F381" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>9</v>
@@ -10336,7 +10330,7 @@
         <v>2512</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C382" s="2">
         <v>16</v>
@@ -10345,7 +10339,7 @@
         <v>46055.5991080671</v>
       </c>
       <c r="E382" s="2">
-        <v>81960</v>
+        <v>81959</v>
       </c>
       <c r="F382" s="3">
         <v>46055</v>
@@ -10362,19 +10356,19 @@
         <v>2512</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C383" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D383" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E383" s="2">
-        <v>82063</v>
+        <v>81960</v>
       </c>
       <c r="F383" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>9</v>
@@ -10388,7 +10382,7 @@
         <v>2512</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C384" s="2">
         <v>17</v>
@@ -10397,7 +10391,7 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E384" s="2">
-        <v>82064</v>
+        <v>82063</v>
       </c>
       <c r="F384" s="3">
         <v>46062</v>
@@ -10414,7 +10408,7 @@
         <v>2512</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C385" s="2">
         <v>17</v>
@@ -10423,10 +10417,10 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E385" s="2">
-        <v>82100</v>
+        <v>82064</v>
       </c>
       <c r="F385" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>9</v>
@@ -10440,19 +10434,19 @@
         <v>2512</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C386" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D386" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E386" s="2">
-        <v>82333</v>
+        <v>82100</v>
       </c>
       <c r="F386" s="3">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>9</v>
@@ -10466,7 +10460,7 @@
         <v>2512</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C387" s="2">
         <v>18</v>
@@ -10475,7 +10469,7 @@
         <v>46072.7410579977</v>
       </c>
       <c r="E387" s="2">
-        <v>82334</v>
+        <v>82333</v>
       </c>
       <c r="F387" s="3">
         <v>46079</v>
@@ -10492,19 +10486,19 @@
         <v>2512</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C388" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D388" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E388" s="2">
-        <v>82258</v>
+        <v>82334</v>
       </c>
       <c r="F388" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>9</v>
@@ -10518,7 +10512,7 @@
         <v>2512</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C389" s="2">
         <v>19</v>
@@ -10527,7 +10521,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E389" s="2">
-        <v>82259</v>
+        <v>82258</v>
       </c>
       <c r="F389" s="3">
         <v>46076</v>
@@ -10544,7 +10538,7 @@
         <v>2512</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C390" s="2">
         <v>19</v>
@@ -10553,7 +10547,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E390" s="2">
-        <v>82260</v>
+        <v>82259</v>
       </c>
       <c r="F390" s="3">
         <v>46076</v>
@@ -10570,7 +10564,7 @@
         <v>2512</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C391" s="2">
         <v>19</v>
@@ -10579,10 +10573,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E391" s="2">
-        <v>82274</v>
+        <v>82260</v>
       </c>
       <c r="F391" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>9</v>
@@ -10596,19 +10590,19 @@
         <v>2512</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C392" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D392" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E392" s="2">
-        <v>82409</v>
+        <v>82274</v>
       </c>
       <c r="F392" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>9</v>
@@ -10619,22 +10613,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="393">
       <c r="A393" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C393" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D393" s="3">
-        <v>46035.4386099769</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E393" s="2">
-        <v>81608</v>
+        <v>82409</v>
       </c>
       <c r="F393" s="3">
-        <v>46035</v>
+        <v>46084</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>9</v>
@@ -10648,7 +10642,7 @@
         <v>2514</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C394" s="2">
         <v>6</v>
@@ -10657,7 +10651,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E394" s="2">
-        <v>81609</v>
+        <v>81608</v>
       </c>
       <c r="F394" s="3">
         <v>46035</v>
@@ -10674,7 +10668,7 @@
         <v>2514</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C395" s="2">
         <v>6</v>
@@ -10683,7 +10677,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E395" s="2">
-        <v>81610</v>
+        <v>81609</v>
       </c>
       <c r="F395" s="3">
         <v>46035</v>
@@ -10700,7 +10694,7 @@
         <v>2514</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C396" s="2">
         <v>6</v>
@@ -10709,7 +10703,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E396" s="2">
-        <v>81611</v>
+        <v>81610</v>
       </c>
       <c r="F396" s="3">
         <v>46035</v>
@@ -10726,7 +10720,7 @@
         <v>2514</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C397" s="2">
         <v>6</v>
@@ -10735,7 +10729,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E397" s="2">
-        <v>81612</v>
+        <v>81611</v>
       </c>
       <c r="F397" s="3">
         <v>46035</v>
@@ -10752,19 +10746,19 @@
         <v>2514</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C398" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D398" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E398" s="2">
-        <v>81652</v>
+        <v>81612</v>
       </c>
       <c r="F398" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>9</v>
@@ -10778,7 +10772,7 @@
         <v>2514</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C399" s="2">
         <v>7</v>
@@ -10787,7 +10781,7 @@
         <v>46036.6342081481</v>
       </c>
       <c r="E399" s="2">
-        <v>81659</v>
+        <v>81652</v>
       </c>
       <c r="F399" s="3">
         <v>46037</v>
@@ -10804,19 +10798,19 @@
         <v>2514</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C400" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D400" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E400" s="2">
-        <v>81853</v>
+        <v>81659</v>
       </c>
       <c r="F400" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>9</v>
@@ -10830,7 +10824,7 @@
         <v>2514</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C401" s="2">
         <v>8</v>
@@ -10839,10 +10833,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E401" s="2">
-        <v>81869</v>
+        <v>81853</v>
       </c>
       <c r="F401" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10856,7 +10850,7 @@
         <v>2514</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C402" s="2">
         <v>8</v>
@@ -10865,10 +10859,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E402" s="2">
-        <v>81890</v>
+        <v>81869</v>
       </c>
       <c r="F402" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10882,19 +10876,19 @@
         <v>2514</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C403" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D403" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E403" s="2">
-        <v>81875</v>
+        <v>81890</v>
       </c>
       <c r="F403" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10908,7 +10902,7 @@
         <v>2514</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C404" s="2">
         <v>9</v>
@@ -10917,10 +10911,10 @@
         <v>46049.4871256134</v>
       </c>
       <c r="E404" s="2">
-        <v>81881</v>
+        <v>81875</v>
       </c>
       <c r="F404" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>9</v>
@@ -10934,19 +10928,19 @@
         <v>2514</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C405" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D405" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E405" s="2">
-        <v>82015</v>
+        <v>81881</v>
       </c>
       <c r="F405" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>9</v>
@@ -10960,7 +10954,7 @@
         <v>2514</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C406" s="2">
         <v>10</v>
@@ -10969,7 +10963,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E406" s="2">
-        <v>82017</v>
+        <v>82015</v>
       </c>
       <c r="F406" s="3">
         <v>46058</v>
@@ -10986,7 +10980,7 @@
         <v>2514</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C407" s="2">
         <v>10</v>
@@ -10995,7 +10989,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E407" s="2">
-        <v>82020</v>
+        <v>82017</v>
       </c>
       <c r="F407" s="3">
         <v>46058</v>
@@ -11012,7 +11006,7 @@
         <v>2514</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C408" s="2">
         <v>10</v>
@@ -11021,7 +11015,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E408" s="2">
-        <v>82023</v>
+        <v>82020</v>
       </c>
       <c r="F408" s="3">
         <v>46058</v>
@@ -11038,7 +11032,7 @@
         <v>2514</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C409" s="2">
         <v>10</v>
@@ -11047,10 +11041,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E409" s="2">
-        <v>82061</v>
+        <v>82023</v>
       </c>
       <c r="F409" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>9</v>
@@ -11064,7 +11058,7 @@
         <v>2514</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C410" s="2">
         <v>10</v>
@@ -11073,10 +11067,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E410" s="2">
-        <v>82081</v>
+        <v>82061</v>
       </c>
       <c r="F410" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11090,7 +11084,7 @@
         <v>2514</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C411" s="2">
         <v>10</v>
@@ -11099,10 +11093,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E411" s="2">
-        <v>82095</v>
+        <v>82081</v>
       </c>
       <c r="F411" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>9</v>
@@ -11116,19 +11110,19 @@
         <v>2514</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C412" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D412" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E412" s="2">
-        <v>82081</v>
+        <v>82095</v>
       </c>
       <c r="F412" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11142,7 +11136,7 @@
         <v>2514</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C413" s="2">
         <v>11</v>
@@ -11151,10 +11145,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E413" s="2">
-        <v>82107</v>
+        <v>82081</v>
       </c>
       <c r="F413" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>9</v>
@@ -11168,7 +11162,7 @@
         <v>2514</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C414" s="2">
         <v>11</v>
@@ -11177,7 +11171,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E414" s="2">
-        <v>82112</v>
+        <v>82107</v>
       </c>
       <c r="F414" s="3">
         <v>46064</v>
@@ -11194,7 +11188,7 @@
         <v>2514</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C415" s="2">
         <v>11</v>
@@ -11203,7 +11197,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E415" s="2">
-        <v>82113</v>
+        <v>82112</v>
       </c>
       <c r="F415" s="3">
         <v>46064</v>
@@ -11220,7 +11214,7 @@
         <v>2514</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C416" s="2">
         <v>11</v>
@@ -11229,10 +11223,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E416" s="2">
-        <v>82123</v>
+        <v>82113</v>
       </c>
       <c r="F416" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>9</v>
@@ -11246,19 +11240,19 @@
         <v>2514</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C417" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D417" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E417" s="2">
-        <v>82095</v>
+        <v>82123</v>
       </c>
       <c r="F417" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>9</v>
@@ -11272,7 +11266,7 @@
         <v>2514</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C418" s="2">
         <v>12</v>
@@ -11281,7 +11275,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E418" s="2">
-        <v>82106</v>
+        <v>82095</v>
       </c>
       <c r="F418" s="3">
         <v>46064</v>
@@ -11298,7 +11292,7 @@
         <v>2514</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C419" s="2">
         <v>12</v>
@@ -11307,7 +11301,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E419" s="2">
-        <v>82107</v>
+        <v>82106</v>
       </c>
       <c r="F419" s="3">
         <v>46064</v>
@@ -11324,7 +11318,7 @@
         <v>2514</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C420" s="2">
         <v>12</v>
@@ -11333,7 +11327,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E420" s="2">
-        <v>82109</v>
+        <v>82107</v>
       </c>
       <c r="F420" s="3">
         <v>46064</v>
@@ -11350,7 +11344,7 @@
         <v>2514</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C421" s="2">
         <v>12</v>
@@ -11359,7 +11353,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E421" s="2">
-        <v>82110</v>
+        <v>82109</v>
       </c>
       <c r="F421" s="3">
         <v>46064</v>
@@ -11376,7 +11370,7 @@
         <v>2514</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C422" s="2">
         <v>12</v>
@@ -11385,10 +11379,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E422" s="2">
-        <v>82139</v>
+        <v>82110</v>
       </c>
       <c r="F422" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>9</v>
@@ -11402,19 +11396,19 @@
         <v>2514</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C423" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D423" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E423" s="2">
-        <v>82365</v>
+        <v>82139</v>
       </c>
       <c r="F423" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>9</v>
@@ -11428,7 +11422,7 @@
         <v>2514</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C424" s="2">
         <v>13</v>
@@ -11437,7 +11431,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E424" s="2">
-        <v>82366</v>
+        <v>82365</v>
       </c>
       <c r="F424" s="3">
         <v>46080</v>
@@ -11454,7 +11448,7 @@
         <v>2514</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C425" s="2">
         <v>13</v>
@@ -11463,7 +11457,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E425" s="2">
-        <v>82371</v>
+        <v>82366</v>
       </c>
       <c r="F425" s="3">
         <v>46080</v>
@@ -11480,7 +11474,7 @@
         <v>2514</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C426" s="2">
         <v>13</v>
@@ -11489,10 +11483,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E426" s="2">
-        <v>82383</v>
+        <v>82371</v>
       </c>
       <c r="F426" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>9</v>
@@ -11506,7 +11500,7 @@
         <v>2514</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C427" s="2">
         <v>13</v>
@@ -11515,7 +11509,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E427" s="2">
-        <v>82384</v>
+        <v>82383</v>
       </c>
       <c r="F427" s="3">
         <v>46083</v>
@@ -11529,28 +11523,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="428">
       <c r="A428" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C428" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D428" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E428" s="2">
-        <v>81592</v>
+        <v>82384</v>
       </c>
       <c r="F428" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="429">
@@ -11558,7 +11552,7 @@
         <v>2515</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C429" s="2">
         <v>15</v>
@@ -11567,16 +11561,16 @@
         <v>46029.4149454282</v>
       </c>
       <c r="E429" s="2">
-        <v>81593</v>
+        <v>81592</v>
       </c>
       <c r="F429" s="3">
         <v>46031</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="430">
@@ -11584,19 +11578,19 @@
         <v>2515</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C430" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D430" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E430" s="2">
-        <v>81697</v>
+        <v>81593</v>
       </c>
       <c r="F430" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>9</v>
@@ -11610,7 +11604,7 @@
         <v>2515</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C431" s="2">
         <v>16</v>
@@ -11619,16 +11613,16 @@
         <v>46038.6827563889</v>
       </c>
       <c r="E431" s="2">
-        <v>81735</v>
+        <v>81697</v>
       </c>
       <c r="F431" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="432">
@@ -11636,45 +11630,45 @@
         <v>2515</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C432" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D432" s="3">
-        <v>46045.4532476157</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E432" s="2">
-        <v>81823</v>
+        <v>81735</v>
       </c>
       <c r="F432" s="3">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="433">
       <c r="A433" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C433" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D433" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E433" s="2">
-        <v>81572</v>
+        <v>81823</v>
       </c>
       <c r="F433" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11688,7 +11682,7 @@
         <v>2516</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C434" s="2">
         <v>5</v>
@@ -11697,7 +11691,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E434" s="2">
-        <v>81573</v>
+        <v>81572</v>
       </c>
       <c r="F434" s="3">
         <v>46031</v>
@@ -11714,7 +11708,7 @@
         <v>2516</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C435" s="2">
         <v>5</v>
@@ -11723,7 +11717,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E435" s="2">
-        <v>81579</v>
+        <v>81573</v>
       </c>
       <c r="F435" s="3">
         <v>46031</v>
@@ -11740,7 +11734,7 @@
         <v>2516</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C436" s="2">
         <v>5</v>
@@ -11749,7 +11743,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E436" s="2">
-        <v>81580</v>
+        <v>81579</v>
       </c>
       <c r="F436" s="3">
         <v>46031</v>
@@ -11766,7 +11760,7 @@
         <v>2516</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C437" s="2">
         <v>5</v>
@@ -11775,7 +11769,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E437" s="2">
-        <v>81581</v>
+        <v>81580</v>
       </c>
       <c r="F437" s="3">
         <v>46031</v>
@@ -11792,7 +11786,7 @@
         <v>2516</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C438" s="2">
         <v>5</v>
@@ -11801,7 +11795,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E438" s="2">
-        <v>81582</v>
+        <v>81581</v>
       </c>
       <c r="F438" s="3">
         <v>46031</v>
@@ -11818,7 +11812,7 @@
         <v>2516</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C439" s="2">
         <v>5</v>
@@ -11827,7 +11821,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E439" s="2">
-        <v>81583</v>
+        <v>81582</v>
       </c>
       <c r="F439" s="3">
         <v>46031</v>
@@ -11844,19 +11838,19 @@
         <v>2516</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C440" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D440" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E440" s="2">
-        <v>81667</v>
+        <v>81583</v>
       </c>
       <c r="F440" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>9</v>
@@ -11870,7 +11864,7 @@
         <v>2516</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C441" s="2">
         <v>6</v>
@@ -11879,7 +11873,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E441" s="2">
-        <v>81668</v>
+        <v>81667</v>
       </c>
       <c r="F441" s="3">
         <v>46037</v>
@@ -11896,7 +11890,7 @@
         <v>2516</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C442" s="2">
         <v>6</v>
@@ -11905,10 +11899,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E442" s="2">
-        <v>81674</v>
+        <v>81668</v>
       </c>
       <c r="F442" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11922,7 +11916,7 @@
         <v>2516</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C443" s="2">
         <v>6</v>
@@ -11931,7 +11925,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E443" s="2">
-        <v>81675</v>
+        <v>81674</v>
       </c>
       <c r="F443" s="3">
         <v>46038</v>
@@ -11948,7 +11942,7 @@
         <v>2516</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C444" s="2">
         <v>6</v>
@@ -11957,7 +11951,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E444" s="2">
-        <v>81677</v>
+        <v>81675</v>
       </c>
       <c r="F444" s="3">
         <v>46038</v>
@@ -11974,19 +11968,19 @@
         <v>2516</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C445" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D445" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E445" s="2">
-        <v>81739</v>
+        <v>81677</v>
       </c>
       <c r="F445" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>9</v>
@@ -12000,7 +11994,7 @@
         <v>2516</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C446" s="2">
         <v>7</v>
@@ -12009,7 +12003,7 @@
         <v>46041.6133887269</v>
       </c>
       <c r="E446" s="2">
-        <v>81741</v>
+        <v>81739</v>
       </c>
       <c r="F446" s="3">
         <v>46041</v>
@@ -12026,19 +12020,19 @@
         <v>2516</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C447" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D447" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E447" s="2">
-        <v>81854</v>
+        <v>81741</v>
       </c>
       <c r="F447" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>9</v>
@@ -12052,7 +12046,7 @@
         <v>2516</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C448" s="2">
         <v>8</v>
@@ -12061,7 +12055,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E448" s="2">
-        <v>81855</v>
+        <v>81854</v>
       </c>
       <c r="F448" s="3">
         <v>46048</v>
@@ -12078,7 +12072,7 @@
         <v>2516</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C449" s="2">
         <v>8</v>
@@ -12087,10 +12081,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E449" s="2">
-        <v>81858</v>
+        <v>81855</v>
       </c>
       <c r="F449" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12104,7 +12098,7 @@
         <v>2516</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C450" s="2">
         <v>8</v>
@@ -12113,7 +12107,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E450" s="2">
-        <v>81859</v>
+        <v>81858</v>
       </c>
       <c r="F450" s="3">
         <v>46049</v>
@@ -12130,7 +12124,7 @@
         <v>2516</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C451" s="2">
         <v>8</v>
@@ -12139,7 +12133,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E451" s="2">
-        <v>81862</v>
+        <v>81859</v>
       </c>
       <c r="F451" s="3">
         <v>46049</v>
@@ -12156,7 +12150,7 @@
         <v>2516</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C452" s="2">
         <v>8</v>
@@ -12165,7 +12159,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E452" s="2">
-        <v>81863</v>
+        <v>81862</v>
       </c>
       <c r="F452" s="3">
         <v>46049</v>
@@ -12182,19 +12176,19 @@
         <v>2516</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C453" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D453" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E453" s="2">
-        <v>81958</v>
+        <v>81863</v>
       </c>
       <c r="F453" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>9</v>
@@ -12208,7 +12202,7 @@
         <v>2516</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C454" s="2">
         <v>9</v>
@@ -12217,7 +12211,7 @@
         <v>46055.5924236111</v>
       </c>
       <c r="E454" s="2">
-        <v>81965</v>
+        <v>81958</v>
       </c>
       <c r="F454" s="3">
         <v>46055</v>
@@ -12234,19 +12228,19 @@
         <v>2516</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C455" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D455" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E455" s="2">
-        <v>82085</v>
+        <v>81965</v>
       </c>
       <c r="F455" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>9</v>
@@ -12260,7 +12254,7 @@
         <v>2516</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C456" s="2">
         <v>10</v>
@@ -12269,7 +12263,7 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E456" s="2">
-        <v>82086</v>
+        <v>82085</v>
       </c>
       <c r="F456" s="3">
         <v>46063</v>
@@ -12286,7 +12280,7 @@
         <v>2516</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C457" s="2">
         <v>10</v>
@@ -12295,10 +12289,10 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E457" s="2">
-        <v>82126</v>
+        <v>82086</v>
       </c>
       <c r="F457" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>9</v>
@@ -12312,19 +12306,19 @@
         <v>2516</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C458" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D458" s="3">
-        <v>46064.5127051505</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E458" s="2">
-        <v>82268</v>
+        <v>82126</v>
       </c>
       <c r="F458" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12338,19 +12332,19 @@
         <v>2516</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C459" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D459" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E459" s="2">
-        <v>82142</v>
+        <v>82268</v>
       </c>
       <c r="F459" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12364,7 +12358,7 @@
         <v>2516</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C460" s="2">
         <v>12</v>
@@ -12373,7 +12367,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E460" s="2">
-        <v>82143</v>
+        <v>82142</v>
       </c>
       <c r="F460" s="3">
         <v>46065</v>
@@ -12390,7 +12384,7 @@
         <v>2516</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C461" s="2">
         <v>12</v>
@@ -12399,7 +12393,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E461" s="2">
-        <v>82144</v>
+        <v>82143</v>
       </c>
       <c r="F461" s="3">
         <v>46065</v>
@@ -12416,7 +12410,7 @@
         <v>2516</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C462" s="2">
         <v>12</v>
@@ -12425,10 +12419,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E462" s="2">
-        <v>82166</v>
+        <v>82144</v>
       </c>
       <c r="F462" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12442,19 +12436,19 @@
         <v>2516</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C463" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D463" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E463" s="2">
-        <v>82262</v>
+        <v>82166</v>
       </c>
       <c r="F463" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12468,7 +12462,7 @@
         <v>2516</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C464" s="2">
         <v>13</v>
@@ -12477,7 +12471,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E464" s="2">
-        <v>82265</v>
+        <v>82262</v>
       </c>
       <c r="F464" s="3">
         <v>46077</v>
@@ -12494,7 +12488,7 @@
         <v>2516</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C465" s="2">
         <v>13</v>
@@ -12503,7 +12497,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E465" s="2">
-        <v>82281</v>
+        <v>82265</v>
       </c>
       <c r="F465" s="3">
         <v>46077</v>
@@ -12520,7 +12514,7 @@
         <v>2516</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C466" s="2">
         <v>13</v>
@@ -12529,7 +12523,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E466" s="2">
-        <v>82282</v>
+        <v>82281</v>
       </c>
       <c r="F466" s="3">
         <v>46077</v>
@@ -12546,19 +12540,19 @@
         <v>2516</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C467" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D467" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E467" s="2">
-        <v>82340</v>
+        <v>82282</v>
       </c>
       <c r="F467" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>9</v>
@@ -12572,19 +12566,19 @@
         <v>2516</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C468" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D468" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E468" s="2">
-        <v>82399</v>
+        <v>82340</v>
       </c>
       <c r="F468" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>9</v>
@@ -12598,7 +12592,7 @@
         <v>2516</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C469" s="2">
         <v>15</v>
@@ -12607,7 +12601,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E469" s="2">
-        <v>82400</v>
+        <v>82399</v>
       </c>
       <c r="F469" s="3">
         <v>46083</v>
@@ -12624,7 +12618,7 @@
         <v>2516</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C470" s="2">
         <v>15</v>
@@ -12633,7 +12627,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E470" s="2">
-        <v>82401</v>
+        <v>82400</v>
       </c>
       <c r="F470" s="3">
         <v>46083</v>
@@ -12650,7 +12644,7 @@
         <v>2516</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C471" s="2">
         <v>15</v>
@@ -12659,10 +12653,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E471" s="2">
-        <v>82412</v>
+        <v>82401</v>
       </c>
       <c r="F471" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>9</v>
@@ -12676,7 +12670,7 @@
         <v>2516</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C472" s="2">
         <v>15</v>
@@ -12685,7 +12679,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E472" s="2">
-        <v>82415</v>
+        <v>82412</v>
       </c>
       <c r="F472" s="3">
         <v>46084</v>
@@ -12699,22 +12693,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="473">
       <c r="A473" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C473" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D473" s="3">
-        <v>46078.6702738773</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E473" s="2">
-        <v>82311</v>
+        <v>82415</v>
       </c>
       <c r="F473" s="3">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12728,7 +12722,7 @@
         <v>2601</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C474" s="2">
         <v>1</v>
@@ -12737,7 +12731,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E474" s="2">
-        <v>82312</v>
+        <v>82311</v>
       </c>
       <c r="F474" s="3">
         <v>46078</v>
@@ -12754,7 +12748,7 @@
         <v>2601</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C475" s="2">
         <v>1</v>
@@ -12763,7 +12757,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E475" s="2">
-        <v>82313</v>
+        <v>82312</v>
       </c>
       <c r="F475" s="3">
         <v>46078</v>
@@ -12780,7 +12774,7 @@
         <v>2601</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C476" s="2">
         <v>1</v>
@@ -12789,7 +12783,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E476" s="2">
-        <v>82314</v>
+        <v>82313</v>
       </c>
       <c r="F476" s="3">
         <v>46078</v>
@@ -12806,7 +12800,7 @@
         <v>2601</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C477" s="2">
         <v>1</v>
@@ -12815,10 +12809,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E477" s="2">
-        <v>82346</v>
+        <v>82314</v>
       </c>
       <c r="F477" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>9</v>
@@ -12832,7 +12826,7 @@
         <v>2601</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C478" s="2">
         <v>1</v>
@@ -12841,7 +12835,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E478" s="2">
-        <v>82361</v>
+        <v>82346</v>
       </c>
       <c r="F478" s="3">
         <v>46080</v>
@@ -12858,7 +12852,7 @@
         <v>2601</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C479" s="2">
         <v>1</v>
@@ -12867,10 +12861,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E479" s="2">
-        <v>82385</v>
+        <v>82361</v>
       </c>
       <c r="F479" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12884,7 +12878,7 @@
         <v>2601</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C480" s="2">
         <v>1</v>
@@ -12893,7 +12887,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E480" s="2">
-        <v>82391</v>
+        <v>82385</v>
       </c>
       <c r="F480" s="3">
         <v>46083</v>
@@ -12910,7 +12904,7 @@
         <v>2601</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C481" s="2">
         <v>1</v>
@@ -12919,7 +12913,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E481" s="2">
-        <v>82392</v>
+        <v>82391</v>
       </c>
       <c r="F481" s="3">
         <v>46083</v>
@@ -12933,22 +12927,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="482">
       <c r="A482" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C482" s="2">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D482" s="3">
-        <v>46029.4632696412</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E482" s="2">
-        <v>81495</v>
+        <v>82392</v>
       </c>
       <c r="F482" s="3">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12959,27 +12953,53 @@
     </row>
     <row ht="12.75" customHeight="1" r="483">
       <c r="A483" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C483" s="2">
+        <v>62</v>
+      </c>
+      <c r="D483" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E483" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F483" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G483" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H483" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="484">
+      <c r="A484" s="2">
         <v>9992</v>
       </c>
-      <c r="B483" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C483" s="2">
+      <c r="B484" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C484" s="2">
         <v>390</v>
       </c>
-      <c r="D483" s="3">
+      <c r="D484" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E483" s="2">
+      <c r="E484" s="2">
         <v>81684</v>
       </c>
-      <c r="F483" s="3">
+      <c r="F484" s="3">
         <v>46038</v>
       </c>
-      <c r="G483" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H483" s="1" t="s">
+      <c r="G484" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H484" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -405,7 +405,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H484"/>
+  <dimension ref="A1:H485"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -3203,22 +3203,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="108">
       <c r="A108" s="2">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C108" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D108" s="3">
-        <v>46014.6980340162</v>
+        <v>46087.643003044</v>
       </c>
       <c r="E108" s="2">
-        <v>81460</v>
+        <v>82497</v>
       </c>
       <c r="F108" s="3">
-        <v>46027</v>
+        <v>46090</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>9</v>
@@ -3241,7 +3241,7 @@
         <v>46014.6980340162</v>
       </c>
       <c r="E109" s="2">
-        <v>81461</v>
+        <v>81460</v>
       </c>
       <c r="F109" s="3">
         <v>46027</v>
@@ -3267,7 +3267,7 @@
         <v>46014.6980340162</v>
       </c>
       <c r="E110" s="2">
-        <v>81463</v>
+        <v>81461</v>
       </c>
       <c r="F110" s="3">
         <v>46027</v>
@@ -3287,16 +3287,16 @@
         <v>16</v>
       </c>
       <c r="C111" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D111" s="3">
-        <v>46030.4707423958</v>
+        <v>46014.6980340162</v>
       </c>
       <c r="E111" s="2">
-        <v>81542</v>
+        <v>81463</v>
       </c>
       <c r="F111" s="3">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>9</v>
@@ -3319,7 +3319,7 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E112" s="2">
-        <v>81548</v>
+        <v>81542</v>
       </c>
       <c r="F112" s="3">
         <v>46030</v>
@@ -3345,7 +3345,7 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E113" s="2">
-        <v>81549</v>
+        <v>81548</v>
       </c>
       <c r="F113" s="3">
         <v>46030</v>
@@ -3371,10 +3371,10 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E114" s="2">
-        <v>81569</v>
+        <v>81549</v>
       </c>
       <c r="F114" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>9</v>
@@ -3391,16 +3391,16 @@
         <v>16</v>
       </c>
       <c r="C115" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D115" s="3">
-        <v>46037.6468124884</v>
+        <v>46030.4707423958</v>
       </c>
       <c r="E115" s="2">
-        <v>81669</v>
+        <v>81569</v>
       </c>
       <c r="F115" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>9</v>
@@ -3423,7 +3423,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E116" s="2">
-        <v>81670</v>
+        <v>81669</v>
       </c>
       <c r="F116" s="3">
         <v>46037</v>
@@ -3449,10 +3449,10 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E117" s="2">
-        <v>81673</v>
+        <v>81670</v>
       </c>
       <c r="F117" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>9</v>
@@ -3475,7 +3475,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E118" s="2">
-        <v>81682</v>
+        <v>81673</v>
       </c>
       <c r="F118" s="3">
         <v>46038</v>
@@ -3501,7 +3501,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E119" s="2">
-        <v>81689</v>
+        <v>81682</v>
       </c>
       <c r="F119" s="3">
         <v>46038</v>
@@ -3521,16 +3521,16 @@
         <v>16</v>
       </c>
       <c r="C120" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D120" s="3">
-        <v>46038.5944713773</v>
+        <v>46037.6468124884</v>
       </c>
       <c r="E120" s="2">
-        <v>81707</v>
+        <v>81689</v>
       </c>
       <c r="F120" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>9</v>
@@ -3547,16 +3547,16 @@
         <v>16</v>
       </c>
       <c r="C121" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D121" s="3">
-        <v>46049.490160081</v>
+        <v>46038.5944713773</v>
       </c>
       <c r="E121" s="2">
-        <v>81866</v>
+        <v>81707</v>
       </c>
       <c r="F121" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>9</v>
@@ -3579,7 +3579,7 @@
         <v>46049.490160081</v>
       </c>
       <c r="E122" s="2">
-        <v>81867</v>
+        <v>81866</v>
       </c>
       <c r="F122" s="3">
         <v>46049</v>
@@ -3605,7 +3605,7 @@
         <v>46049.490160081</v>
       </c>
       <c r="E123" s="2">
-        <v>81871</v>
+        <v>81867</v>
       </c>
       <c r="F123" s="3">
         <v>46049</v>
@@ -3631,10 +3631,10 @@
         <v>46049.490160081</v>
       </c>
       <c r="E124" s="2">
-        <v>81882</v>
+        <v>81871</v>
       </c>
       <c r="F124" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>9</v>
@@ -3651,16 +3651,16 @@
         <v>16</v>
       </c>
       <c r="C125" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D125" s="3">
-        <v>46051.4127791667</v>
+        <v>46049.490160081</v>
       </c>
       <c r="E125" s="2">
-        <v>81922</v>
+        <v>81882</v>
       </c>
       <c r="F125" s="3">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>9</v>
@@ -3677,16 +3677,16 @@
         <v>16</v>
       </c>
       <c r="C126" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D126" s="3">
-        <v>46056.7141110995</v>
+        <v>46051.4127791667</v>
       </c>
       <c r="E126" s="2">
-        <v>81972</v>
+        <v>81922</v>
       </c>
       <c r="F126" s="3">
-        <v>46056</v>
+        <v>46051</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>9</v>
@@ -3709,7 +3709,7 @@
         <v>46056.7141110995</v>
       </c>
       <c r="E127" s="2">
-        <v>81973</v>
+        <v>81972</v>
       </c>
       <c r="F127" s="3">
         <v>46056</v>
@@ -3735,10 +3735,10 @@
         <v>46056.7141110995</v>
       </c>
       <c r="E128" s="2">
-        <v>81993</v>
+        <v>81973</v>
       </c>
       <c r="F128" s="3">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>9</v>
@@ -3755,16 +3755,16 @@
         <v>16</v>
       </c>
       <c r="C129" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D129" s="3">
-        <v>46063.7282468519</v>
+        <v>46056.7141110995</v>
       </c>
       <c r="E129" s="2">
-        <v>82090</v>
+        <v>81993</v>
       </c>
       <c r="F129" s="3">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>9</v>
@@ -3787,7 +3787,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E130" s="2">
-        <v>82093</v>
+        <v>82090</v>
       </c>
       <c r="F130" s="3">
         <v>46063</v>
@@ -3813,10 +3813,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E131" s="2">
-        <v>82094</v>
+        <v>82093</v>
       </c>
       <c r="F131" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>9</v>
@@ -3839,7 +3839,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E132" s="2">
-        <v>82098</v>
+        <v>82094</v>
       </c>
       <c r="F132" s="3">
         <v>46064</v>
@@ -3865,7 +3865,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E133" s="2">
-        <v>82119</v>
+        <v>82098</v>
       </c>
       <c r="F133" s="3">
         <v>46064</v>
@@ -3891,7 +3891,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E134" s="2">
-        <v>82120</v>
+        <v>82119</v>
       </c>
       <c r="F134" s="3">
         <v>46064</v>
@@ -3917,10 +3917,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E135" s="2">
-        <v>82131</v>
+        <v>82120</v>
       </c>
       <c r="F135" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>9</v>
@@ -3937,16 +3937,16 @@
         <v>16</v>
       </c>
       <c r="C136" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D136" s="3">
-        <v>46078.6817048032</v>
+        <v>46063.7282468519</v>
       </c>
       <c r="E136" s="2">
-        <v>82316</v>
+        <v>82131</v>
       </c>
       <c r="F136" s="3">
-        <v>46078</v>
+        <v>46065</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>9</v>
@@ -3969,10 +3969,10 @@
         <v>46078.6817048032</v>
       </c>
       <c r="E137" s="2">
-        <v>82325</v>
+        <v>82316</v>
       </c>
       <c r="F137" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>9</v>
@@ -3995,7 +3995,7 @@
         <v>46078.6817048032</v>
       </c>
       <c r="E138" s="2">
-        <v>82327</v>
+        <v>82325</v>
       </c>
       <c r="F138" s="3">
         <v>46079</v>
@@ -4015,16 +4015,16 @@
         <v>16</v>
       </c>
       <c r="C139" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D139" s="3">
-        <v>46086.632572419</v>
+        <v>46078.6817048032</v>
       </c>
       <c r="E139" s="2">
-        <v>82471</v>
+        <v>82327</v>
       </c>
       <c r="F139" s="3">
-        <v>46086</v>
+        <v>46079</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>9</v>
@@ -4047,10 +4047,10 @@
         <v>46086.632572419</v>
       </c>
       <c r="E140" s="2">
-        <v>82476</v>
+        <v>82471</v>
       </c>
       <c r="F140" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>9</v>
@@ -4061,22 +4061,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="141">
       <c r="A141" s="2">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C141" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D141" s="3">
-        <v>46030.4179771875</v>
+        <v>46086.632572419</v>
       </c>
       <c r="E141" s="2">
-        <v>81536</v>
+        <v>82476</v>
       </c>
       <c r="F141" s="3">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>9</v>
@@ -4099,7 +4099,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E142" s="2">
-        <v>81538</v>
+        <v>81536</v>
       </c>
       <c r="F142" s="3">
         <v>46030</v>
@@ -4125,7 +4125,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E143" s="2">
-        <v>81555</v>
+        <v>81538</v>
       </c>
       <c r="F143" s="3">
         <v>46030</v>
@@ -4151,7 +4151,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E144" s="2">
-        <v>81556</v>
+        <v>81555</v>
       </c>
       <c r="F144" s="3">
         <v>46030</v>
@@ -4177,7 +4177,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E145" s="2">
-        <v>81558</v>
+        <v>81556</v>
       </c>
       <c r="F145" s="3">
         <v>46030</v>
@@ -4197,16 +4197,16 @@
         <v>17</v>
       </c>
       <c r="C146" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D146" s="3">
-        <v>46036.4079311574</v>
+        <v>46030.4179771875</v>
       </c>
       <c r="E146" s="2">
-        <v>81615</v>
+        <v>81558</v>
       </c>
       <c r="F146" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>9</v>
@@ -4229,7 +4229,7 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E147" s="2">
-        <v>81621</v>
+        <v>81615</v>
       </c>
       <c r="F147" s="3">
         <v>46036</v>
@@ -4255,10 +4255,10 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E148" s="2">
-        <v>81647</v>
+        <v>81621</v>
       </c>
       <c r="F148" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>9</v>
@@ -4269,22 +4269,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="149">
       <c r="A149" s="2">
-        <v>2504</v>
+        <v>2411</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C149" s="2">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D149" s="3">
-        <v>46027.6983957986</v>
+        <v>46036.4079311574</v>
       </c>
       <c r="E149" s="2">
-        <v>81465</v>
+        <v>81647</v>
       </c>
       <c r="F149" s="3">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>9</v>
@@ -4307,16 +4307,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E150" s="2">
-        <v>81466</v>
+        <v>81465</v>
       </c>
       <c r="F150" s="3">
         <v>46027</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="151">
@@ -4333,16 +4333,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E151" s="2">
-        <v>81471</v>
+        <v>81466</v>
       </c>
       <c r="F151" s="3">
         <v>46027</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="152">
@@ -4359,10 +4359,10 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E152" s="2">
-        <v>81488</v>
+        <v>81471</v>
       </c>
       <c r="F152" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>9</v>
@@ -4385,7 +4385,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E153" s="2">
-        <v>81489</v>
+        <v>81488</v>
       </c>
       <c r="F153" s="3">
         <v>46029</v>
@@ -4411,7 +4411,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E154" s="2">
-        <v>81490</v>
+        <v>81489</v>
       </c>
       <c r="F154" s="3">
         <v>46029</v>
@@ -4437,7 +4437,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E155" s="2">
-        <v>81491</v>
+        <v>81490</v>
       </c>
       <c r="F155" s="3">
         <v>46029</v>
@@ -4457,16 +4457,16 @@
         <v>18</v>
       </c>
       <c r="C156" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D156" s="3">
-        <v>46038.4184531713</v>
+        <v>46027.6983957986</v>
       </c>
       <c r="E156" s="2">
-        <v>81688</v>
+        <v>81491</v>
       </c>
       <c r="F156" s="3">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>9</v>
@@ -4483,13 +4483,13 @@
         <v>18</v>
       </c>
       <c r="C157" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D157" s="3">
-        <v>46038.6993878241</v>
+        <v>46038.4184531713</v>
       </c>
       <c r="E157" s="2">
-        <v>81700</v>
+        <v>81688</v>
       </c>
       <c r="F157" s="3">
         <v>46038</v>
@@ -4515,7 +4515,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E158" s="2">
-        <v>81701</v>
+        <v>81700</v>
       </c>
       <c r="F158" s="3">
         <v>46038</v>
@@ -4541,7 +4541,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E159" s="2">
-        <v>81702</v>
+        <v>81701</v>
       </c>
       <c r="F159" s="3">
         <v>46038</v>
@@ -4567,7 +4567,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E160" s="2">
-        <v>81703</v>
+        <v>81702</v>
       </c>
       <c r="F160" s="3">
         <v>46038</v>
@@ -4593,10 +4593,10 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E161" s="2">
-        <v>81734</v>
+        <v>81703</v>
       </c>
       <c r="F161" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>9</v>
@@ -4613,16 +4613,16 @@
         <v>18</v>
       </c>
       <c r="C162" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D162" s="3">
-        <v>46050.7176682523</v>
+        <v>46038.6993878241</v>
       </c>
       <c r="E162" s="2">
-        <v>81914</v>
+        <v>81734</v>
       </c>
       <c r="F162" s="3">
-        <v>46051</v>
+        <v>46041</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>9</v>
@@ -4645,7 +4645,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E163" s="2">
-        <v>81915</v>
+        <v>81914</v>
       </c>
       <c r="F163" s="3">
         <v>46051</v>
@@ -4671,7 +4671,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E164" s="2">
-        <v>81921</v>
+        <v>81915</v>
       </c>
       <c r="F164" s="3">
         <v>46051</v>
@@ -4691,16 +4691,16 @@
         <v>18</v>
       </c>
       <c r="C165" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D165" s="3">
-        <v>46052.6247194676</v>
+        <v>46050.7176682523</v>
       </c>
       <c r="E165" s="2">
-        <v>81949</v>
+        <v>81921</v>
       </c>
       <c r="F165" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>9</v>
@@ -4723,7 +4723,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E166" s="2">
-        <v>81950</v>
+        <v>81949</v>
       </c>
       <c r="F166" s="3">
         <v>46052</v>
@@ -4749,7 +4749,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E167" s="2">
-        <v>81951</v>
+        <v>81950</v>
       </c>
       <c r="F167" s="3">
         <v>46052</v>
@@ -4775,7 +4775,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E168" s="2">
-        <v>81953</v>
+        <v>81951</v>
       </c>
       <c r="F168" s="3">
         <v>46052</v>
@@ -4795,16 +4795,16 @@
         <v>18</v>
       </c>
       <c r="C169" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D169" s="3">
-        <v>46058.6976675694</v>
+        <v>46052.6247194676</v>
       </c>
       <c r="E169" s="2">
-        <v>82028</v>
+        <v>81953</v>
       </c>
       <c r="F169" s="3">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>9</v>
@@ -4827,7 +4827,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E170" s="2">
-        <v>82029</v>
+        <v>82028</v>
       </c>
       <c r="F170" s="3">
         <v>46058</v>
@@ -4853,10 +4853,10 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E171" s="2">
-        <v>82040</v>
+        <v>82029</v>
       </c>
       <c r="F171" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>9</v>
@@ -4879,7 +4879,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E172" s="2">
-        <v>82041</v>
+        <v>82040</v>
       </c>
       <c r="F172" s="3">
         <v>46059</v>
@@ -4905,7 +4905,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E173" s="2">
-        <v>82051</v>
+        <v>82041</v>
       </c>
       <c r="F173" s="3">
         <v>46059</v>
@@ -4925,16 +4925,16 @@
         <v>18</v>
       </c>
       <c r="C174" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D174" s="3">
-        <v>46065.6309066782</v>
+        <v>46058.6976675694</v>
       </c>
       <c r="E174" s="2">
-        <v>82168</v>
+        <v>82051</v>
       </c>
       <c r="F174" s="3">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>9</v>
@@ -4957,16 +4957,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E175" s="2">
-        <v>82170</v>
+        <v>82168</v>
       </c>
       <c r="F175" s="3">
         <v>46066</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="176">
@@ -4983,16 +4983,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E176" s="2">
-        <v>82171</v>
+        <v>82170</v>
       </c>
       <c r="F176" s="3">
         <v>46066</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="177">
@@ -5009,7 +5009,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E177" s="2">
-        <v>82172</v>
+        <v>82171</v>
       </c>
       <c r="F177" s="3">
         <v>46066</v>
@@ -5035,7 +5035,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E178" s="2">
-        <v>82175</v>
+        <v>82172</v>
       </c>
       <c r="F178" s="3">
         <v>46066</v>
@@ -5061,7 +5061,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E179" s="2">
-        <v>82176</v>
+        <v>82175</v>
       </c>
       <c r="F179" s="3">
         <v>46066</v>
@@ -5081,16 +5081,16 @@
         <v>18</v>
       </c>
       <c r="C180" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D180" s="3">
-        <v>46072.5909779051</v>
+        <v>46065.6309066782</v>
       </c>
       <c r="E180" s="2">
-        <v>82206</v>
+        <v>82176</v>
       </c>
       <c r="F180" s="3">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>9</v>
@@ -5107,16 +5107,16 @@
         <v>18</v>
       </c>
       <c r="C181" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D181" s="3">
-        <v>46077.7262228935</v>
+        <v>46072.5909779051</v>
       </c>
       <c r="E181" s="2">
-        <v>82289</v>
+        <v>82206</v>
       </c>
       <c r="F181" s="3">
-        <v>46077</v>
+        <v>46072</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>9</v>
@@ -5139,7 +5139,7 @@
         <v>46077.7262228935</v>
       </c>
       <c r="E182" s="2">
-        <v>82290</v>
+        <v>82289</v>
       </c>
       <c r="F182" s="3">
         <v>46077</v>
@@ -5159,16 +5159,16 @@
         <v>18</v>
       </c>
       <c r="C183" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D183" s="3">
-        <v>46078.6799843634</v>
+        <v>46077.7262228935</v>
       </c>
       <c r="E183" s="2">
-        <v>82318</v>
+        <v>82290</v>
       </c>
       <c r="F183" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>9</v>
@@ -5185,16 +5185,16 @@
         <v>18</v>
       </c>
       <c r="C184" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D184" s="3">
-        <v>46080.6294471412</v>
+        <v>46078.6799843634</v>
       </c>
       <c r="E184" s="2">
-        <v>82368</v>
+        <v>82318</v>
       </c>
       <c r="F184" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>9</v>
@@ -5211,16 +5211,16 @@
         <v>18</v>
       </c>
       <c r="C185" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D185" s="3">
-        <v>46084.741264838</v>
+        <v>46080.6294471412</v>
       </c>
       <c r="E185" s="2">
-        <v>82425</v>
+        <v>82368</v>
       </c>
       <c r="F185" s="3">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>9</v>
@@ -5243,7 +5243,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="E186" s="2">
-        <v>82426</v>
+        <v>82425</v>
       </c>
       <c r="F186" s="3">
         <v>46084</v>
@@ -5269,10 +5269,10 @@
         <v>46084.741264838</v>
       </c>
       <c r="E187" s="2">
-        <v>82430</v>
+        <v>82426</v>
       </c>
       <c r="F187" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>9</v>
@@ -5295,7 +5295,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="E188" s="2">
-        <v>82431</v>
+        <v>82430</v>
       </c>
       <c r="F188" s="3">
         <v>46085</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="189">
       <c r="A189" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C189" s="2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D189" s="3">
-        <v>46041.6648751157</v>
+        <v>46084.741264838</v>
       </c>
       <c r="E189" s="2">
-        <v>81743</v>
+        <v>82431</v>
       </c>
       <c r="F189" s="3">
-        <v>46041</v>
+        <v>46085</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>9</v>
@@ -5347,7 +5347,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E190" s="2">
-        <v>81744</v>
+        <v>81743</v>
       </c>
       <c r="F190" s="3">
         <v>46041</v>
@@ -5373,7 +5373,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E191" s="2">
-        <v>81745</v>
+        <v>81744</v>
       </c>
       <c r="F191" s="3">
         <v>46041</v>
@@ -5399,10 +5399,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E192" s="2">
-        <v>81746</v>
+        <v>81745</v>
       </c>
       <c r="F192" s="3">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>9</v>
@@ -5425,10 +5425,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E193" s="2">
-        <v>81751</v>
+        <v>81746</v>
       </c>
       <c r="F193" s="3">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>9</v>
@@ -5451,7 +5451,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E194" s="2">
-        <v>81753</v>
+        <v>81751</v>
       </c>
       <c r="F194" s="3">
         <v>46043</v>
@@ -5477,7 +5477,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E195" s="2">
-        <v>81754</v>
+        <v>81753</v>
       </c>
       <c r="F195" s="3">
         <v>46043</v>
@@ -5503,7 +5503,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E196" s="2">
-        <v>81755</v>
+        <v>81754</v>
       </c>
       <c r="F196" s="3">
         <v>46043</v>
@@ -5529,7 +5529,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E197" s="2">
-        <v>81766</v>
+        <v>81755</v>
       </c>
       <c r="F197" s="3">
         <v>46043</v>
@@ -5549,16 +5549,16 @@
         <v>19</v>
       </c>
       <c r="C198" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D198" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E198" s="2">
-        <v>82088</v>
+        <v>81766</v>
       </c>
       <c r="F198" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>9</v>
@@ -5581,7 +5581,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E199" s="2">
-        <v>82089</v>
+        <v>82088</v>
       </c>
       <c r="F199" s="3">
         <v>46063</v>
@@ -5607,10 +5607,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E200" s="2">
-        <v>82163</v>
+        <v>82089</v>
       </c>
       <c r="F200" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>9</v>
@@ -5633,7 +5633,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E201" s="2">
-        <v>82179</v>
+        <v>82163</v>
       </c>
       <c r="F201" s="3">
         <v>46066</v>
@@ -5659,7 +5659,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E202" s="2">
-        <v>82193</v>
+        <v>82179</v>
       </c>
       <c r="F202" s="3">
         <v>46066</v>
@@ -5679,16 +5679,16 @@
         <v>19</v>
       </c>
       <c r="C203" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D203" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E203" s="2">
-        <v>82250</v>
+        <v>82193</v>
       </c>
       <c r="F203" s="3">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>9</v>
@@ -5711,10 +5711,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E204" s="2">
-        <v>82266</v>
+        <v>82250</v>
       </c>
       <c r="F204" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>9</v>
@@ -5737,10 +5737,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E205" s="2">
-        <v>82295</v>
+        <v>82266</v>
       </c>
       <c r="F205" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>9</v>
@@ -5763,7 +5763,7 @@
         <v>46073.714168287</v>
       </c>
       <c r="E206" s="2">
-        <v>82296</v>
+        <v>82295</v>
       </c>
       <c r="F206" s="3">
         <v>46078</v>
@@ -5789,16 +5789,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E207" s="2">
-        <v>82332</v>
+        <v>82296</v>
       </c>
       <c r="F207" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="208">
@@ -5815,16 +5815,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E208" s="2">
-        <v>82339</v>
+        <v>82332</v>
       </c>
       <c r="F208" s="3">
         <v>46079</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="209">
@@ -5835,16 +5835,16 @@
         <v>19</v>
       </c>
       <c r="C209" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D209" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E209" s="2">
-        <v>82266</v>
+        <v>82339</v>
       </c>
       <c r="F209" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>9</v>
@@ -5867,7 +5867,7 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E210" s="2">
-        <v>82273</v>
+        <v>82266</v>
       </c>
       <c r="F210" s="3">
         <v>46077</v>
@@ -5893,10 +5893,10 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E211" s="2">
-        <v>82294</v>
+        <v>82273</v>
       </c>
       <c r="F211" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>9</v>
@@ -5913,16 +5913,16 @@
         <v>19</v>
       </c>
       <c r="C212" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D212" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E212" s="2">
-        <v>82411</v>
+        <v>82294</v>
       </c>
       <c r="F212" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>9</v>
@@ -5945,10 +5945,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E213" s="2">
-        <v>82432</v>
+        <v>82411</v>
       </c>
       <c r="F213" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>9</v>
@@ -5971,10 +5971,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E214" s="2">
-        <v>82473</v>
+        <v>82432</v>
       </c>
       <c r="F214" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>9</v>
@@ -5997,10 +5997,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E215" s="2">
-        <v>82474</v>
+        <v>82473</v>
       </c>
       <c r="F215" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>9</v>
@@ -6011,22 +6011,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="216">
       <c r="A216" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C216" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D216" s="3">
-        <v>46044.6368950926</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E216" s="2">
-        <v>81802</v>
+        <v>82474</v>
       </c>
       <c r="F216" s="3">
-        <v>46044</v>
+        <v>46087</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>9</v>
@@ -6049,7 +6049,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E217" s="2">
-        <v>81803</v>
+        <v>81802</v>
       </c>
       <c r="F217" s="3">
         <v>46044</v>
@@ -6075,7 +6075,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E218" s="2">
-        <v>81804</v>
+        <v>81803</v>
       </c>
       <c r="F218" s="3">
         <v>46044</v>
@@ -6101,7 +6101,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E219" s="2">
-        <v>81806</v>
+        <v>81804</v>
       </c>
       <c r="F219" s="3">
         <v>46044</v>
@@ -6127,7 +6127,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E220" s="2">
-        <v>81807</v>
+        <v>81806</v>
       </c>
       <c r="F220" s="3">
         <v>46044</v>
@@ -6153,10 +6153,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E221" s="2">
-        <v>81812</v>
+        <v>81807</v>
       </c>
       <c r="F221" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>9</v>
@@ -6179,7 +6179,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E222" s="2">
-        <v>81813</v>
+        <v>81812</v>
       </c>
       <c r="F222" s="3">
         <v>46045</v>
@@ -6205,7 +6205,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E223" s="2">
-        <v>81814</v>
+        <v>81813</v>
       </c>
       <c r="F223" s="3">
         <v>46045</v>
@@ -6231,7 +6231,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E224" s="2">
-        <v>81818</v>
+        <v>81814</v>
       </c>
       <c r="F224" s="3">
         <v>46045</v>
@@ -6257,7 +6257,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E225" s="2">
-        <v>81822</v>
+        <v>81818</v>
       </c>
       <c r="F225" s="3">
         <v>46045</v>
@@ -6283,7 +6283,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E226" s="2">
-        <v>81833</v>
+        <v>81822</v>
       </c>
       <c r="F226" s="3">
         <v>46045</v>
@@ -6309,7 +6309,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E227" s="2">
-        <v>81841</v>
+        <v>81833</v>
       </c>
       <c r="F227" s="3">
         <v>46045</v>
@@ -6329,16 +6329,16 @@
         <v>22</v>
       </c>
       <c r="C228" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D228" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E228" s="2">
-        <v>81928</v>
+        <v>81841</v>
       </c>
       <c r="F228" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>9</v>
@@ -6361,7 +6361,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E229" s="2">
-        <v>81929</v>
+        <v>81928</v>
       </c>
       <c r="F229" s="3">
         <v>46052</v>
@@ -6387,7 +6387,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E230" s="2">
-        <v>81930</v>
+        <v>81929</v>
       </c>
       <c r="F230" s="3">
         <v>46052</v>
@@ -6413,7 +6413,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E231" s="2">
-        <v>81932</v>
+        <v>81930</v>
       </c>
       <c r="F231" s="3">
         <v>46052</v>
@@ -6439,7 +6439,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E232" s="2">
-        <v>81933</v>
+        <v>81932</v>
       </c>
       <c r="F232" s="3">
         <v>46052</v>
@@ -6465,7 +6465,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E233" s="2">
-        <v>81934</v>
+        <v>81933</v>
       </c>
       <c r="F233" s="3">
         <v>46052</v>
@@ -6491,7 +6491,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E234" s="2">
-        <v>81935</v>
+        <v>81934</v>
       </c>
       <c r="F234" s="3">
         <v>46052</v>
@@ -6517,7 +6517,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E235" s="2">
-        <v>81936</v>
+        <v>81935</v>
       </c>
       <c r="F235" s="3">
         <v>46052</v>
@@ -6537,16 +6537,16 @@
         <v>22</v>
       </c>
       <c r="C236" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D236" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E236" s="2">
-        <v>82222</v>
+        <v>81936</v>
       </c>
       <c r="F236" s="3">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>9</v>
@@ -6569,10 +6569,10 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E237" s="2">
-        <v>82226</v>
+        <v>82222</v>
       </c>
       <c r="F237" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>9</v>
@@ -6595,7 +6595,7 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E238" s="2">
-        <v>82229</v>
+        <v>82226</v>
       </c>
       <c r="F238" s="3">
         <v>46073</v>
@@ -6615,13 +6615,13 @@
         <v>22</v>
       </c>
       <c r="C239" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D239" s="3">
-        <v>46073.5838834375</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E239" s="2">
-        <v>82246</v>
+        <v>82229</v>
       </c>
       <c r="F239" s="3">
         <v>46073</v>
@@ -6641,16 +6641,16 @@
         <v>22</v>
       </c>
       <c r="C240" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D240" s="3">
-        <v>46080.6289065162</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E240" s="2">
-        <v>82387</v>
+        <v>82246</v>
       </c>
       <c r="F240" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>9</v>
@@ -6661,22 +6661,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="241">
       <c r="A241" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C241" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D241" s="3">
-        <v>46029.4161474769</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E241" s="2">
-        <v>81478</v>
+        <v>82387</v>
       </c>
       <c r="F241" s="3">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>9</v>
@@ -6699,7 +6699,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E242" s="2">
-        <v>81479</v>
+        <v>81478</v>
       </c>
       <c r="F242" s="3">
         <v>46029</v>
@@ -6725,7 +6725,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E243" s="2">
-        <v>81480</v>
+        <v>81479</v>
       </c>
       <c r="F243" s="3">
         <v>46029</v>
@@ -6751,7 +6751,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E244" s="2">
-        <v>81497</v>
+        <v>81480</v>
       </c>
       <c r="F244" s="3">
         <v>46029</v>
@@ -6777,7 +6777,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E245" s="2">
-        <v>81498</v>
+        <v>81497</v>
       </c>
       <c r="F245" s="3">
         <v>46029</v>
@@ -6803,7 +6803,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E246" s="2">
-        <v>81499</v>
+        <v>81498</v>
       </c>
       <c r="F246" s="3">
         <v>46029</v>
@@ -6829,7 +6829,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E247" s="2">
-        <v>81500</v>
+        <v>81499</v>
       </c>
       <c r="F247" s="3">
         <v>46029</v>
@@ -6849,16 +6849,16 @@
         <v>22</v>
       </c>
       <c r="C248" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D248" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E248" s="2">
-        <v>81878</v>
+        <v>81500</v>
       </c>
       <c r="F248" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>9</v>
@@ -6881,7 +6881,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E249" s="2">
-        <v>81879</v>
+        <v>81878</v>
       </c>
       <c r="F249" s="3">
         <v>46049</v>
@@ -6907,10 +6907,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E250" s="2">
-        <v>81885</v>
+        <v>81879</v>
       </c>
       <c r="F250" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>9</v>
@@ -6933,7 +6933,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E251" s="2">
-        <v>81886</v>
+        <v>81885</v>
       </c>
       <c r="F251" s="3">
         <v>46050</v>
@@ -6953,16 +6953,16 @@
         <v>22</v>
       </c>
       <c r="C252" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D252" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E252" s="2">
-        <v>82068</v>
+        <v>81886</v>
       </c>
       <c r="F252" s="3">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>9</v>
@@ -6985,10 +6985,10 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E253" s="2">
-        <v>82072</v>
+        <v>82068</v>
       </c>
       <c r="F253" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>9</v>
@@ -7011,7 +7011,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E254" s="2">
-        <v>82076</v>
+        <v>82072</v>
       </c>
       <c r="F254" s="3">
         <v>46063</v>
@@ -7037,7 +7037,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E255" s="2">
-        <v>82078</v>
+        <v>82076</v>
       </c>
       <c r="F255" s="3">
         <v>46063</v>
@@ -7057,16 +7057,16 @@
         <v>22</v>
       </c>
       <c r="C256" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D256" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E256" s="2">
-        <v>82287</v>
+        <v>82078</v>
       </c>
       <c r="F256" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>9</v>
@@ -7089,7 +7089,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E257" s="2">
-        <v>82288</v>
+        <v>82287</v>
       </c>
       <c r="F257" s="3">
         <v>46077</v>
@@ -7115,10 +7115,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E258" s="2">
-        <v>82298</v>
+        <v>82288</v>
       </c>
       <c r="F258" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>9</v>
@@ -7141,7 +7141,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E259" s="2">
-        <v>82301</v>
+        <v>82298</v>
       </c>
       <c r="F259" s="3">
         <v>46078</v>
@@ -7167,7 +7167,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E260" s="2">
-        <v>82304</v>
+        <v>82301</v>
       </c>
       <c r="F260" s="3">
         <v>46078</v>
@@ -7193,7 +7193,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E261" s="2">
-        <v>82308</v>
+        <v>82304</v>
       </c>
       <c r="F261" s="3">
         <v>46078</v>
@@ -7213,16 +7213,16 @@
         <v>22</v>
       </c>
       <c r="C262" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D262" s="3">
-        <v>46080.628344919</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E262" s="2">
-        <v>82373</v>
+        <v>82308</v>
       </c>
       <c r="F262" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>9</v>
@@ -7239,16 +7239,16 @@
         <v>22</v>
       </c>
       <c r="C263" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D263" s="3">
-        <v>46085.6581644213</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E263" s="2">
-        <v>82445</v>
+        <v>82373</v>
       </c>
       <c r="F263" s="3">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>9</v>
@@ -7271,7 +7271,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E264" s="2">
-        <v>82447</v>
+        <v>82445</v>
       </c>
       <c r="F264" s="3">
         <v>46085</v>
@@ -7297,10 +7297,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E265" s="2">
-        <v>82453</v>
+        <v>82447</v>
       </c>
       <c r="F265" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>9</v>
@@ -7323,7 +7323,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E266" s="2">
-        <v>82468</v>
+        <v>82453</v>
       </c>
       <c r="F266" s="3">
         <v>46086</v>
@@ -7337,22 +7337,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="267">
       <c r="A267" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C267" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D267" s="3">
-        <v>46029.6400966782</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E267" s="2">
-        <v>81506</v>
+        <v>82468</v>
       </c>
       <c r="F267" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>9</v>
@@ -7375,7 +7375,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E268" s="2">
-        <v>81507</v>
+        <v>81506</v>
       </c>
       <c r="F268" s="3">
         <v>46029</v>
@@ -7401,10 +7401,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E269" s="2">
-        <v>81524</v>
+        <v>81507</v>
       </c>
       <c r="F269" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>9</v>
@@ -7427,7 +7427,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E270" s="2">
-        <v>81525</v>
+        <v>81524</v>
       </c>
       <c r="F270" s="3">
         <v>46030</v>
@@ -7453,7 +7453,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E271" s="2">
-        <v>81526</v>
+        <v>81525</v>
       </c>
       <c r="F271" s="3">
         <v>46030</v>
@@ -7473,16 +7473,16 @@
         <v>23</v>
       </c>
       <c r="C272" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D272" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E272" s="2">
-        <v>81640</v>
+        <v>81526</v>
       </c>
       <c r="F272" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>9</v>
@@ -7505,7 +7505,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E273" s="2">
-        <v>81642</v>
+        <v>81640</v>
       </c>
       <c r="F273" s="3">
         <v>46036</v>
@@ -7531,7 +7531,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E274" s="2">
-        <v>81643</v>
+        <v>81642</v>
       </c>
       <c r="F274" s="3">
         <v>46036</v>
@@ -7551,16 +7551,16 @@
         <v>23</v>
       </c>
       <c r="C275" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D275" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E275" s="2">
-        <v>81835</v>
+        <v>81643</v>
       </c>
       <c r="F275" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>9</v>
@@ -7583,7 +7583,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E276" s="2">
-        <v>81836</v>
+        <v>81835</v>
       </c>
       <c r="F276" s="3">
         <v>46045</v>
@@ -7609,7 +7609,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E277" s="2">
-        <v>81837</v>
+        <v>81836</v>
       </c>
       <c r="F277" s="3">
         <v>46045</v>
@@ -7629,16 +7629,16 @@
         <v>23</v>
       </c>
       <c r="C278" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D278" s="3">
-        <v>46051.6376515278</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E278" s="2">
-        <v>81931</v>
+        <v>81837</v>
       </c>
       <c r="F278" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>9</v>
@@ -7655,16 +7655,16 @@
         <v>23</v>
       </c>
       <c r="C279" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D279" s="3">
-        <v>46056.7115158912</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E279" s="2">
-        <v>81978</v>
+        <v>81931</v>
       </c>
       <c r="F279" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>9</v>
@@ -7681,13 +7681,13 @@
         <v>23</v>
       </c>
       <c r="C280" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D280" s="3">
-        <v>46057.6911087731</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E280" s="2">
-        <v>81994</v>
+        <v>81978</v>
       </c>
       <c r="F280" s="3">
         <v>46057</v>
@@ -7713,7 +7713,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E281" s="2">
-        <v>81995</v>
+        <v>81994</v>
       </c>
       <c r="F281" s="3">
         <v>46057</v>
@@ -7739,7 +7739,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E282" s="2">
-        <v>81999</v>
+        <v>81995</v>
       </c>
       <c r="F282" s="3">
         <v>46057</v>
@@ -7765,10 +7765,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E283" s="2">
-        <v>82008</v>
+        <v>81999</v>
       </c>
       <c r="F283" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>9</v>
@@ -7791,7 +7791,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E284" s="2">
-        <v>82011</v>
+        <v>82008</v>
       </c>
       <c r="F284" s="3">
         <v>46058</v>
@@ -7817,7 +7817,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E285" s="2">
-        <v>82012</v>
+        <v>82011</v>
       </c>
       <c r="F285" s="3">
         <v>46058</v>
@@ -7843,7 +7843,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E286" s="2">
-        <v>82013</v>
+        <v>82012</v>
       </c>
       <c r="F286" s="3">
         <v>46058</v>
@@ -7869,7 +7869,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E287" s="2">
-        <v>82014</v>
+        <v>82013</v>
       </c>
       <c r="F287" s="3">
         <v>46058</v>
@@ -7889,22 +7889,22 @@
         <v>23</v>
       </c>
       <c r="C288" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D288" s="3">
-        <v>46058.6604985417</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E288" s="2">
-        <v>82046</v>
+        <v>82014</v>
       </c>
       <c r="F288" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="289">
@@ -7915,22 +7915,22 @@
         <v>23</v>
       </c>
       <c r="C289" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D289" s="3">
-        <v>46072.738871875</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E289" s="2">
-        <v>82217</v>
+        <v>82046</v>
       </c>
       <c r="F289" s="3">
-        <v>46072</v>
+        <v>46059</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="290">
@@ -7947,7 +7947,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E290" s="2">
-        <v>82218</v>
+        <v>82217</v>
       </c>
       <c r="F290" s="3">
         <v>46072</v>
@@ -7973,10 +7973,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E291" s="2">
-        <v>82234</v>
+        <v>82218</v>
       </c>
       <c r="F291" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>9</v>
@@ -7999,7 +7999,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E292" s="2">
-        <v>82238</v>
+        <v>82234</v>
       </c>
       <c r="F292" s="3">
         <v>46073</v>
@@ -8025,7 +8025,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E293" s="2">
-        <v>82245</v>
+        <v>82238</v>
       </c>
       <c r="F293" s="3">
         <v>46073</v>
@@ -8045,16 +8045,16 @@
         <v>23</v>
       </c>
       <c r="C294" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D294" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E294" s="2">
-        <v>82257</v>
+        <v>82245</v>
       </c>
       <c r="F294" s="3">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>9</v>
@@ -8077,10 +8077,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E295" s="2">
-        <v>82276</v>
+        <v>82257</v>
       </c>
       <c r="F295" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>9</v>
@@ -8103,7 +8103,7 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E296" s="2">
-        <v>82277</v>
+        <v>82276</v>
       </c>
       <c r="F296" s="3">
         <v>46077</v>
@@ -8129,10 +8129,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E297" s="2">
-        <v>82293</v>
+        <v>82277</v>
       </c>
       <c r="F297" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>9</v>
@@ -8149,16 +8149,16 @@
         <v>23</v>
       </c>
       <c r="C298" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D298" s="3">
-        <v>46077.4356327431</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E298" s="2">
-        <v>82269</v>
+        <v>82293</v>
       </c>
       <c r="F298" s="3">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>9</v>
@@ -8175,16 +8175,16 @@
         <v>23</v>
       </c>
       <c r="C299" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D299" s="3">
-        <v>46084.7378501505</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E299" s="2">
-        <v>82419</v>
+        <v>82269</v>
       </c>
       <c r="F299" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>9</v>
@@ -8207,7 +8207,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E300" s="2">
-        <v>82420</v>
+        <v>82419</v>
       </c>
       <c r="F300" s="3">
         <v>46084</v>
@@ -8233,7 +8233,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E301" s="2">
-        <v>82421</v>
+        <v>82420</v>
       </c>
       <c r="F301" s="3">
         <v>46084</v>
@@ -8259,7 +8259,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E302" s="2">
-        <v>82422</v>
+        <v>82421</v>
       </c>
       <c r="F302" s="3">
         <v>46084</v>
@@ -8285,7 +8285,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E303" s="2">
-        <v>82423</v>
+        <v>82422</v>
       </c>
       <c r="F303" s="3">
         <v>46084</v>
@@ -8311,10 +8311,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E304" s="2">
-        <v>82433</v>
+        <v>82423</v>
       </c>
       <c r="F304" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>9</v>
@@ -8337,7 +8337,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E305" s="2">
-        <v>82434</v>
+        <v>82433</v>
       </c>
       <c r="F305" s="3">
         <v>46085</v>
@@ -8363,10 +8363,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E306" s="2">
-        <v>82464</v>
+        <v>82434</v>
       </c>
       <c r="F306" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>9</v>
@@ -8389,7 +8389,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E307" s="2">
-        <v>82472</v>
+        <v>82464</v>
       </c>
       <c r="F307" s="3">
         <v>46086</v>
@@ -8403,22 +8403,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="308">
       <c r="A308" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C308" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D308" s="3">
-        <v>46027.6953206134</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E308" s="2">
-        <v>81464</v>
+        <v>82472</v>
       </c>
       <c r="F308" s="3">
-        <v>46027</v>
+        <v>46086</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>9</v>
@@ -8441,7 +8441,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E309" s="2">
-        <v>81472</v>
+        <v>81464</v>
       </c>
       <c r="F309" s="3">
         <v>46027</v>
@@ -8467,10 +8467,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E310" s="2">
-        <v>81492</v>
+        <v>81472</v>
       </c>
       <c r="F310" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>9</v>
@@ -8493,7 +8493,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E311" s="2">
-        <v>81493</v>
+        <v>81492</v>
       </c>
       <c r="F311" s="3">
         <v>46029</v>
@@ -8519,10 +8519,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E312" s="2">
-        <v>81568</v>
+        <v>81493</v>
       </c>
       <c r="F312" s="3">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>9</v>
@@ -8545,10 +8545,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E313" s="2">
-        <v>81601</v>
+        <v>81568</v>
       </c>
       <c r="F313" s="3">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>9</v>
@@ -8571,7 +8571,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E314" s="2">
-        <v>81602</v>
+        <v>81601</v>
       </c>
       <c r="F314" s="3">
         <v>46034</v>
@@ -8591,16 +8591,16 @@
         <v>24</v>
       </c>
       <c r="C315" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D315" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E315" s="2">
-        <v>81645</v>
+        <v>81602</v>
       </c>
       <c r="F315" s="3">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>9</v>
@@ -8623,7 +8623,7 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E316" s="2">
-        <v>81646</v>
+        <v>81645</v>
       </c>
       <c r="F316" s="3">
         <v>46036</v>
@@ -8649,10 +8649,10 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E317" s="2">
-        <v>81653</v>
+        <v>81646</v>
       </c>
       <c r="F317" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>9</v>
@@ -8669,13 +8669,13 @@
         <v>24</v>
       </c>
       <c r="C318" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D318" s="3">
-        <v>46037.4325152662</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E318" s="2">
-        <v>81662</v>
+        <v>81653</v>
       </c>
       <c r="F318" s="3">
         <v>46037</v>
@@ -8695,16 +8695,16 @@
         <v>24</v>
       </c>
       <c r="C319" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D319" s="3">
-        <v>46044.4079891435</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E319" s="2">
-        <v>81780</v>
+        <v>81662</v>
       </c>
       <c r="F319" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>9</v>
@@ -8727,7 +8727,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E320" s="2">
-        <v>81781</v>
+        <v>81780</v>
       </c>
       <c r="F320" s="3">
         <v>46044</v>
@@ -8753,7 +8753,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E321" s="2">
-        <v>81782</v>
+        <v>81781</v>
       </c>
       <c r="F321" s="3">
         <v>46044</v>
@@ -8779,7 +8779,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E322" s="2">
-        <v>81784</v>
+        <v>81782</v>
       </c>
       <c r="F322" s="3">
         <v>46044</v>
@@ -8805,7 +8805,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E323" s="2">
-        <v>81785</v>
+        <v>81784</v>
       </c>
       <c r="F323" s="3">
         <v>46044</v>
@@ -8831,7 +8831,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E324" s="2">
-        <v>81801</v>
+        <v>81785</v>
       </c>
       <c r="F324" s="3">
         <v>46044</v>
@@ -8851,16 +8851,16 @@
         <v>24</v>
       </c>
       <c r="C325" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D325" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E325" s="2">
-        <v>81860</v>
+        <v>81801</v>
       </c>
       <c r="F325" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>9</v>
@@ -8883,7 +8883,7 @@
         <v>46048.7319778588</v>
       </c>
       <c r="E326" s="2">
-        <v>81873</v>
+        <v>81860</v>
       </c>
       <c r="F326" s="3">
         <v>46049</v>
@@ -8903,13 +8903,13 @@
         <v>24</v>
       </c>
       <c r="C327" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D327" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E327" s="2">
-        <v>81865</v>
+        <v>81873</v>
       </c>
       <c r="F327" s="3">
         <v>46049</v>
@@ -8935,7 +8935,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E328" s="2">
-        <v>81870</v>
+        <v>81865</v>
       </c>
       <c r="F328" s="3">
         <v>46049</v>
@@ -8961,7 +8961,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E329" s="2">
-        <v>81872</v>
+        <v>81870</v>
       </c>
       <c r="F329" s="3">
         <v>46049</v>
@@ -8987,10 +8987,10 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E330" s="2">
-        <v>81896</v>
+        <v>81872</v>
       </c>
       <c r="F330" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>9</v>
@@ -9007,16 +9007,16 @@
         <v>24</v>
       </c>
       <c r="C331" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D331" s="3">
-        <v>46051.4046937153</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E331" s="2">
-        <v>81923</v>
+        <v>81896</v>
       </c>
       <c r="F331" s="3">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>9</v>
@@ -9033,16 +9033,16 @@
         <v>24</v>
       </c>
       <c r="C332" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D332" s="3">
-        <v>46057.6959672917</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E332" s="2">
-        <v>81998</v>
+        <v>81923</v>
       </c>
       <c r="F332" s="3">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>9</v>
@@ -9065,7 +9065,7 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E333" s="2">
-        <v>82002</v>
+        <v>81998</v>
       </c>
       <c r="F333" s="3">
         <v>46057</v>
@@ -9091,10 +9091,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E334" s="2">
-        <v>82005</v>
+        <v>82002</v>
       </c>
       <c r="F334" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>9</v>
@@ -9117,7 +9117,7 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E335" s="2">
-        <v>82007</v>
+        <v>82005</v>
       </c>
       <c r="F335" s="3">
         <v>46058</v>
@@ -9137,13 +9137,13 @@
         <v>24</v>
       </c>
       <c r="C336" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D336" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E336" s="2">
-        <v>82005</v>
+        <v>82007</v>
       </c>
       <c r="F336" s="3">
         <v>46058</v>
@@ -9169,10 +9169,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E337" s="2">
-        <v>82075</v>
+        <v>82005</v>
       </c>
       <c r="F337" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>9</v>
@@ -9195,7 +9195,7 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E338" s="2">
-        <v>82077</v>
+        <v>82075</v>
       </c>
       <c r="F338" s="3">
         <v>46063</v>
@@ -9221,10 +9221,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E339" s="2">
-        <v>82099</v>
+        <v>82077</v>
       </c>
       <c r="F339" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>9</v>
@@ -9241,16 +9241,16 @@
         <v>24</v>
       </c>
       <c r="C340" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D340" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E340" s="2">
-        <v>82219</v>
+        <v>82099</v>
       </c>
       <c r="F340" s="3">
-        <v>46072</v>
+        <v>46064</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>9</v>
@@ -9273,10 +9273,10 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E341" s="2">
-        <v>82230</v>
+        <v>82219</v>
       </c>
       <c r="F341" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>9</v>
@@ -9299,7 +9299,7 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E342" s="2">
-        <v>82231</v>
+        <v>82230</v>
       </c>
       <c r="F342" s="3">
         <v>46073</v>
@@ -9319,16 +9319,16 @@
         <v>24</v>
       </c>
       <c r="C343" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D343" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E343" s="2">
-        <v>82388</v>
+        <v>82231</v>
       </c>
       <c r="F343" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>9</v>
@@ -9351,7 +9351,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E344" s="2">
-        <v>82389</v>
+        <v>82388</v>
       </c>
       <c r="F344" s="3">
         <v>46083</v>
@@ -9377,7 +9377,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E345" s="2">
-        <v>82396</v>
+        <v>82389</v>
       </c>
       <c r="F345" s="3">
         <v>46083</v>
@@ -9403,7 +9403,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E346" s="2">
-        <v>82397</v>
+        <v>82396</v>
       </c>
       <c r="F346" s="3">
         <v>46083</v>
@@ -9423,16 +9423,16 @@
         <v>24</v>
       </c>
       <c r="C347" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D347" s="3">
-        <v>46085.6249659838</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E347" s="2">
-        <v>82435</v>
+        <v>82397</v>
       </c>
       <c r="F347" s="3">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>9</v>
@@ -9443,22 +9443,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="348">
       <c r="A348" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C348" s="2">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D348" s="3">
-        <v>46029.3821391551</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E348" s="2">
-        <v>81477</v>
+        <v>82435</v>
       </c>
       <c r="F348" s="3">
-        <v>46029</v>
+        <v>46085</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>9</v>
@@ -9475,16 +9475,16 @@
         <v>25</v>
       </c>
       <c r="C349" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D349" s="3">
-        <v>46030.4142968056</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E349" s="2">
-        <v>81532</v>
+        <v>81477</v>
       </c>
       <c r="F349" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>9</v>
@@ -9507,7 +9507,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E350" s="2">
-        <v>81534</v>
+        <v>81532</v>
       </c>
       <c r="F350" s="3">
         <v>46030</v>
@@ -9533,7 +9533,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E351" s="2">
-        <v>81535</v>
+        <v>81534</v>
       </c>
       <c r="F351" s="3">
         <v>46030</v>
@@ -9559,7 +9559,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E352" s="2">
-        <v>81550</v>
+        <v>81535</v>
       </c>
       <c r="F352" s="3">
         <v>46030</v>
@@ -9585,7 +9585,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E353" s="2">
-        <v>81553</v>
+        <v>81550</v>
       </c>
       <c r="F353" s="3">
         <v>46030</v>
@@ -9611,7 +9611,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E354" s="2">
-        <v>81554</v>
+        <v>81553</v>
       </c>
       <c r="F354" s="3">
         <v>46030</v>
@@ -9637,7 +9637,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E355" s="2">
-        <v>81557</v>
+        <v>81554</v>
       </c>
       <c r="F355" s="3">
         <v>46030</v>
@@ -9663,10 +9663,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E356" s="2">
-        <v>81588</v>
+        <v>81557</v>
       </c>
       <c r="F356" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>9</v>
@@ -9683,16 +9683,16 @@
         <v>25</v>
       </c>
       <c r="C357" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D357" s="3">
-        <v>46038.593985081</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E357" s="2">
-        <v>81692</v>
+        <v>81588</v>
       </c>
       <c r="F357" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>9</v>
@@ -9709,16 +9709,16 @@
         <v>25</v>
       </c>
       <c r="C358" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D358" s="3">
-        <v>46044.46462125</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E358" s="2">
-        <v>81786</v>
+        <v>81692</v>
       </c>
       <c r="F358" s="3">
-        <v>46044</v>
+        <v>46038</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>9</v>
@@ -9735,16 +9735,16 @@
         <v>25</v>
       </c>
       <c r="C359" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D359" s="3">
-        <v>46044.6362443171</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E359" s="2">
-        <v>81844</v>
+        <v>81786</v>
       </c>
       <c r="F359" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>9</v>
@@ -9761,16 +9761,16 @@
         <v>25</v>
       </c>
       <c r="C360" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D360" s="3">
-        <v>46062.717040544</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E360" s="2">
-        <v>82065</v>
+        <v>81844</v>
       </c>
       <c r="F360" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>9</v>
@@ -9793,7 +9793,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E361" s="2">
-        <v>82066</v>
+        <v>82065</v>
       </c>
       <c r="F361" s="3">
         <v>46062</v>
@@ -9819,7 +9819,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E362" s="2">
-        <v>82067</v>
+        <v>82066</v>
       </c>
       <c r="F362" s="3">
         <v>46062</v>
@@ -9839,16 +9839,16 @@
         <v>25</v>
       </c>
       <c r="C363" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D363" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E363" s="2">
-        <v>82190</v>
+        <v>82067</v>
       </c>
       <c r="F363" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>9</v>
@@ -9871,7 +9871,7 @@
         <v>46065.6300915625</v>
       </c>
       <c r="E364" s="2">
-        <v>82197</v>
+        <v>82190</v>
       </c>
       <c r="F364" s="3">
         <v>46066</v>
@@ -9891,16 +9891,16 @@
         <v>25</v>
       </c>
       <c r="C365" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D365" s="3">
-        <v>46077.5084780324</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E365" s="2">
-        <v>82270</v>
+        <v>82197</v>
       </c>
       <c r="F365" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>9</v>
@@ -9917,13 +9917,13 @@
         <v>25</v>
       </c>
       <c r="C366" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D366" s="3">
-        <v>46077.721037037</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E366" s="2">
-        <v>82285</v>
+        <v>82270</v>
       </c>
       <c r="F366" s="3">
         <v>46077</v>
@@ -9943,16 +9943,16 @@
         <v>25</v>
       </c>
       <c r="C367" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D367" s="3">
-        <v>46083.6694849421</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E367" s="2">
-        <v>82417</v>
+        <v>82285</v>
       </c>
       <c r="F367" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>9</v>
@@ -9969,16 +9969,16 @@
         <v>25</v>
       </c>
       <c r="C368" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D368" s="3">
-        <v>46085.7157723032</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E368" s="2">
-        <v>82457</v>
+        <v>82417</v>
       </c>
       <c r="F368" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>9</v>
@@ -9989,22 +9989,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="369">
       <c r="A369" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C369" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D369" s="3">
-        <v>46029.381258831</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E369" s="2">
-        <v>81484</v>
+        <v>82457</v>
       </c>
       <c r="F369" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>9</v>
@@ -10027,7 +10027,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E370" s="2">
-        <v>81486</v>
+        <v>81484</v>
       </c>
       <c r="F370" s="3">
         <v>46029</v>
@@ -10053,7 +10053,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E371" s="2">
-        <v>81487</v>
+        <v>81486</v>
       </c>
       <c r="F371" s="3">
         <v>46029</v>
@@ -10073,16 +10073,16 @@
         <v>26</v>
       </c>
       <c r="C372" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D372" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E372" s="2">
-        <v>81613</v>
+        <v>81487</v>
       </c>
       <c r="F372" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>9</v>
@@ -10105,7 +10105,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E373" s="2">
-        <v>81614</v>
+        <v>81613</v>
       </c>
       <c r="F373" s="3">
         <v>46036</v>
@@ -10131,7 +10131,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E374" s="2">
-        <v>81622</v>
+        <v>81614</v>
       </c>
       <c r="F374" s="3">
         <v>46036</v>
@@ -10157,7 +10157,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E375" s="2">
-        <v>81632</v>
+        <v>81622</v>
       </c>
       <c r="F375" s="3">
         <v>46036</v>
@@ -10183,10 +10183,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E376" s="2">
-        <v>81648</v>
+        <v>81632</v>
       </c>
       <c r="F376" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>9</v>
@@ -10209,7 +10209,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E377" s="2">
-        <v>81664</v>
+        <v>81648</v>
       </c>
       <c r="F377" s="3">
         <v>46037</v>
@@ -10229,16 +10229,16 @@
         <v>26</v>
       </c>
       <c r="C378" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D378" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E378" s="2">
-        <v>81815</v>
+        <v>81664</v>
       </c>
       <c r="F378" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>9</v>
@@ -10261,7 +10261,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E379" s="2">
-        <v>81816</v>
+        <v>81815</v>
       </c>
       <c r="F379" s="3">
         <v>46045</v>
@@ -10287,7 +10287,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E380" s="2">
-        <v>81838</v>
+        <v>81816</v>
       </c>
       <c r="F380" s="3">
         <v>46045</v>
@@ -10313,7 +10313,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E381" s="2">
-        <v>81840</v>
+        <v>81838</v>
       </c>
       <c r="F381" s="3">
         <v>46045</v>
@@ -10333,16 +10333,16 @@
         <v>26</v>
       </c>
       <c r="C382" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D382" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E382" s="2">
-        <v>81959</v>
+        <v>81840</v>
       </c>
       <c r="F382" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>9</v>
@@ -10365,7 +10365,7 @@
         <v>46055.5991080671</v>
       </c>
       <c r="E383" s="2">
-        <v>81960</v>
+        <v>81959</v>
       </c>
       <c r="F383" s="3">
         <v>46055</v>
@@ -10385,16 +10385,16 @@
         <v>26</v>
       </c>
       <c r="C384" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D384" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E384" s="2">
-        <v>82063</v>
+        <v>81960</v>
       </c>
       <c r="F384" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>9</v>
@@ -10417,7 +10417,7 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E385" s="2">
-        <v>82064</v>
+        <v>82063</v>
       </c>
       <c r="F385" s="3">
         <v>46062</v>
@@ -10443,10 +10443,10 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E386" s="2">
-        <v>82100</v>
+        <v>82064</v>
       </c>
       <c r="F386" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>9</v>
@@ -10463,16 +10463,16 @@
         <v>26</v>
       </c>
       <c r="C387" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D387" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E387" s="2">
-        <v>82333</v>
+        <v>82100</v>
       </c>
       <c r="F387" s="3">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>9</v>
@@ -10495,7 +10495,7 @@
         <v>46072.7410579977</v>
       </c>
       <c r="E388" s="2">
-        <v>82334</v>
+        <v>82333</v>
       </c>
       <c r="F388" s="3">
         <v>46079</v>
@@ -10515,16 +10515,16 @@
         <v>26</v>
       </c>
       <c r="C389" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D389" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E389" s="2">
-        <v>82258</v>
+        <v>82334</v>
       </c>
       <c r="F389" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>9</v>
@@ -10547,7 +10547,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E390" s="2">
-        <v>82259</v>
+        <v>82258</v>
       </c>
       <c r="F390" s="3">
         <v>46076</v>
@@ -10573,7 +10573,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E391" s="2">
-        <v>82260</v>
+        <v>82259</v>
       </c>
       <c r="F391" s="3">
         <v>46076</v>
@@ -10599,10 +10599,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E392" s="2">
-        <v>82274</v>
+        <v>82260</v>
       </c>
       <c r="F392" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>9</v>
@@ -10619,16 +10619,16 @@
         <v>26</v>
       </c>
       <c r="C393" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D393" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E393" s="2">
-        <v>82409</v>
+        <v>82274</v>
       </c>
       <c r="F393" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>9</v>
@@ -10639,22 +10639,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="394">
       <c r="A394" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C394" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D394" s="3">
-        <v>46035.4386099769</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E394" s="2">
-        <v>81608</v>
+        <v>82409</v>
       </c>
       <c r="F394" s="3">
-        <v>46035</v>
+        <v>46084</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>9</v>
@@ -10677,7 +10677,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E395" s="2">
-        <v>81609</v>
+        <v>81608</v>
       </c>
       <c r="F395" s="3">
         <v>46035</v>
@@ -10703,7 +10703,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E396" s="2">
-        <v>81610</v>
+        <v>81609</v>
       </c>
       <c r="F396" s="3">
         <v>46035</v>
@@ -10729,7 +10729,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E397" s="2">
-        <v>81611</v>
+        <v>81610</v>
       </c>
       <c r="F397" s="3">
         <v>46035</v>
@@ -10755,7 +10755,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E398" s="2">
-        <v>81612</v>
+        <v>81611</v>
       </c>
       <c r="F398" s="3">
         <v>46035</v>
@@ -10775,16 +10775,16 @@
         <v>27</v>
       </c>
       <c r="C399" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D399" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E399" s="2">
-        <v>81652</v>
+        <v>81612</v>
       </c>
       <c r="F399" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>9</v>
@@ -10807,7 +10807,7 @@
         <v>46036.6342081481</v>
       </c>
       <c r="E400" s="2">
-        <v>81659</v>
+        <v>81652</v>
       </c>
       <c r="F400" s="3">
         <v>46037</v>
@@ -10827,16 +10827,16 @@
         <v>27</v>
       </c>
       <c r="C401" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D401" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E401" s="2">
-        <v>81853</v>
+        <v>81659</v>
       </c>
       <c r="F401" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10859,10 +10859,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E402" s="2">
-        <v>81869</v>
+        <v>81853</v>
       </c>
       <c r="F402" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10885,10 +10885,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E403" s="2">
-        <v>81890</v>
+        <v>81869</v>
       </c>
       <c r="F403" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10905,16 +10905,16 @@
         <v>27</v>
       </c>
       <c r="C404" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D404" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E404" s="2">
-        <v>81875</v>
+        <v>81890</v>
       </c>
       <c r="F404" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>9</v>
@@ -10937,10 +10937,10 @@
         <v>46049.4871256134</v>
       </c>
       <c r="E405" s="2">
-        <v>81881</v>
+        <v>81875</v>
       </c>
       <c r="F405" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>9</v>
@@ -10957,16 +10957,16 @@
         <v>27</v>
       </c>
       <c r="C406" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D406" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E406" s="2">
-        <v>82015</v>
+        <v>81881</v>
       </c>
       <c r="F406" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>9</v>
@@ -10989,7 +10989,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E407" s="2">
-        <v>82017</v>
+        <v>82015</v>
       </c>
       <c r="F407" s="3">
         <v>46058</v>
@@ -11015,7 +11015,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E408" s="2">
-        <v>82020</v>
+        <v>82017</v>
       </c>
       <c r="F408" s="3">
         <v>46058</v>
@@ -11041,7 +11041,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E409" s="2">
-        <v>82023</v>
+        <v>82020</v>
       </c>
       <c r="F409" s="3">
         <v>46058</v>
@@ -11067,10 +11067,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E410" s="2">
-        <v>82061</v>
+        <v>82023</v>
       </c>
       <c r="F410" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11093,10 +11093,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E411" s="2">
-        <v>82081</v>
+        <v>82061</v>
       </c>
       <c r="F411" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>9</v>
@@ -11119,10 +11119,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E412" s="2">
-        <v>82095</v>
+        <v>82081</v>
       </c>
       <c r="F412" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11139,16 +11139,16 @@
         <v>27</v>
       </c>
       <c r="C413" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D413" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E413" s="2">
-        <v>82081</v>
+        <v>82095</v>
       </c>
       <c r="F413" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>9</v>
@@ -11171,10 +11171,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E414" s="2">
-        <v>82107</v>
+        <v>82081</v>
       </c>
       <c r="F414" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>9</v>
@@ -11197,7 +11197,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E415" s="2">
-        <v>82112</v>
+        <v>82107</v>
       </c>
       <c r="F415" s="3">
         <v>46064</v>
@@ -11223,7 +11223,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E416" s="2">
-        <v>82113</v>
+        <v>82112</v>
       </c>
       <c r="F416" s="3">
         <v>46064</v>
@@ -11249,10 +11249,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E417" s="2">
-        <v>82123</v>
+        <v>82113</v>
       </c>
       <c r="F417" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>9</v>
@@ -11269,16 +11269,16 @@
         <v>27</v>
       </c>
       <c r="C418" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D418" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E418" s="2">
-        <v>82095</v>
+        <v>82123</v>
       </c>
       <c r="F418" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G418" s="1" t="s">
         <v>9</v>
@@ -11301,7 +11301,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E419" s="2">
-        <v>82106</v>
+        <v>82095</v>
       </c>
       <c r="F419" s="3">
         <v>46064</v>
@@ -11327,7 +11327,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E420" s="2">
-        <v>82107</v>
+        <v>82106</v>
       </c>
       <c r="F420" s="3">
         <v>46064</v>
@@ -11353,7 +11353,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E421" s="2">
-        <v>82109</v>
+        <v>82107</v>
       </c>
       <c r="F421" s="3">
         <v>46064</v>
@@ -11379,7 +11379,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E422" s="2">
-        <v>82110</v>
+        <v>82109</v>
       </c>
       <c r="F422" s="3">
         <v>46064</v>
@@ -11405,10 +11405,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E423" s="2">
-        <v>82139</v>
+        <v>82110</v>
       </c>
       <c r="F423" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>9</v>
@@ -11425,16 +11425,16 @@
         <v>27</v>
       </c>
       <c r="C424" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D424" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E424" s="2">
-        <v>82365</v>
+        <v>82139</v>
       </c>
       <c r="F424" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>9</v>
@@ -11457,7 +11457,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E425" s="2">
-        <v>82366</v>
+        <v>82365</v>
       </c>
       <c r="F425" s="3">
         <v>46080</v>
@@ -11483,7 +11483,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E426" s="2">
-        <v>82371</v>
+        <v>82366</v>
       </c>
       <c r="F426" s="3">
         <v>46080</v>
@@ -11509,10 +11509,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E427" s="2">
-        <v>82383</v>
+        <v>82371</v>
       </c>
       <c r="F427" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11535,7 +11535,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E428" s="2">
-        <v>82384</v>
+        <v>82383</v>
       </c>
       <c r="F428" s="3">
         <v>46083</v>
@@ -11549,28 +11549,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="429">
       <c r="A429" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C429" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D429" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E429" s="2">
-        <v>81592</v>
+        <v>82384</v>
       </c>
       <c r="F429" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="430">
@@ -11587,16 +11587,16 @@
         <v>46029.4149454282</v>
       </c>
       <c r="E430" s="2">
-        <v>81593</v>
+        <v>81592</v>
       </c>
       <c r="F430" s="3">
         <v>46031</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="431">
@@ -11607,16 +11607,16 @@
         <v>28</v>
       </c>
       <c r="C431" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D431" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E431" s="2">
-        <v>81697</v>
+        <v>81593</v>
       </c>
       <c r="F431" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>9</v>
@@ -11639,16 +11639,16 @@
         <v>46038.6827563889</v>
       </c>
       <c r="E432" s="2">
-        <v>81735</v>
+        <v>81697</v>
       </c>
       <c r="F432" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="433">
@@ -11659,42 +11659,42 @@
         <v>28</v>
       </c>
       <c r="C433" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D433" s="3">
-        <v>46045.4532476157</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E433" s="2">
-        <v>81823</v>
+        <v>81735</v>
       </c>
       <c r="F433" s="3">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="434">
       <c r="A434" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C434" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D434" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E434" s="2">
-        <v>81572</v>
+        <v>81823</v>
       </c>
       <c r="F434" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>9</v>
@@ -11717,7 +11717,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E435" s="2">
-        <v>81573</v>
+        <v>81572</v>
       </c>
       <c r="F435" s="3">
         <v>46031</v>
@@ -11743,7 +11743,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E436" s="2">
-        <v>81579</v>
+        <v>81573</v>
       </c>
       <c r="F436" s="3">
         <v>46031</v>
@@ -11769,7 +11769,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E437" s="2">
-        <v>81580</v>
+        <v>81579</v>
       </c>
       <c r="F437" s="3">
         <v>46031</v>
@@ -11795,7 +11795,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E438" s="2">
-        <v>81581</v>
+        <v>81580</v>
       </c>
       <c r="F438" s="3">
         <v>46031</v>
@@ -11821,7 +11821,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E439" s="2">
-        <v>81582</v>
+        <v>81581</v>
       </c>
       <c r="F439" s="3">
         <v>46031</v>
@@ -11847,7 +11847,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E440" s="2">
-        <v>81583</v>
+        <v>81582</v>
       </c>
       <c r="F440" s="3">
         <v>46031</v>
@@ -11867,16 +11867,16 @@
         <v>29</v>
       </c>
       <c r="C441" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D441" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E441" s="2">
-        <v>81667</v>
+        <v>81583</v>
       </c>
       <c r="F441" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11899,7 +11899,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E442" s="2">
-        <v>81668</v>
+        <v>81667</v>
       </c>
       <c r="F442" s="3">
         <v>46037</v>
@@ -11925,10 +11925,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E443" s="2">
-        <v>81674</v>
+        <v>81668</v>
       </c>
       <c r="F443" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11951,7 +11951,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E444" s="2">
-        <v>81675</v>
+        <v>81674</v>
       </c>
       <c r="F444" s="3">
         <v>46038</v>
@@ -11977,7 +11977,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E445" s="2">
-        <v>81677</v>
+        <v>81675</v>
       </c>
       <c r="F445" s="3">
         <v>46038</v>
@@ -11997,16 +11997,16 @@
         <v>29</v>
       </c>
       <c r="C446" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D446" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E446" s="2">
-        <v>81739</v>
+        <v>81677</v>
       </c>
       <c r="F446" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>9</v>
@@ -12029,7 +12029,7 @@
         <v>46041.6133887269</v>
       </c>
       <c r="E447" s="2">
-        <v>81741</v>
+        <v>81739</v>
       </c>
       <c r="F447" s="3">
         <v>46041</v>
@@ -12049,16 +12049,16 @@
         <v>29</v>
       </c>
       <c r="C448" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D448" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E448" s="2">
-        <v>81854</v>
+        <v>81741</v>
       </c>
       <c r="F448" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12081,7 +12081,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E449" s="2">
-        <v>81855</v>
+        <v>81854</v>
       </c>
       <c r="F449" s="3">
         <v>46048</v>
@@ -12107,10 +12107,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E450" s="2">
-        <v>81858</v>
+        <v>81855</v>
       </c>
       <c r="F450" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12133,7 +12133,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E451" s="2">
-        <v>81859</v>
+        <v>81858</v>
       </c>
       <c r="F451" s="3">
         <v>46049</v>
@@ -12159,7 +12159,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E452" s="2">
-        <v>81862</v>
+        <v>81859</v>
       </c>
       <c r="F452" s="3">
         <v>46049</v>
@@ -12185,7 +12185,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E453" s="2">
-        <v>81863</v>
+        <v>81862</v>
       </c>
       <c r="F453" s="3">
         <v>46049</v>
@@ -12205,16 +12205,16 @@
         <v>29</v>
       </c>
       <c r="C454" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D454" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E454" s="2">
-        <v>81958</v>
+        <v>81863</v>
       </c>
       <c r="F454" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>9</v>
@@ -12237,7 +12237,7 @@
         <v>46055.5924236111</v>
       </c>
       <c r="E455" s="2">
-        <v>81965</v>
+        <v>81958</v>
       </c>
       <c r="F455" s="3">
         <v>46055</v>
@@ -12257,16 +12257,16 @@
         <v>29</v>
       </c>
       <c r="C456" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D456" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E456" s="2">
-        <v>82085</v>
+        <v>81965</v>
       </c>
       <c r="F456" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12289,7 +12289,7 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E457" s="2">
-        <v>82086</v>
+        <v>82085</v>
       </c>
       <c r="F457" s="3">
         <v>46063</v>
@@ -12315,10 +12315,10 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E458" s="2">
-        <v>82126</v>
+        <v>82086</v>
       </c>
       <c r="F458" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12335,16 +12335,16 @@
         <v>29</v>
       </c>
       <c r="C459" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D459" s="3">
-        <v>46064.5127051505</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E459" s="2">
-        <v>82268</v>
+        <v>82126</v>
       </c>
       <c r="F459" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12361,16 +12361,16 @@
         <v>29</v>
       </c>
       <c r="C460" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D460" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E460" s="2">
-        <v>82142</v>
+        <v>82268</v>
       </c>
       <c r="F460" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12393,7 +12393,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E461" s="2">
-        <v>82143</v>
+        <v>82142</v>
       </c>
       <c r="F461" s="3">
         <v>46065</v>
@@ -12419,7 +12419,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E462" s="2">
-        <v>82144</v>
+        <v>82143</v>
       </c>
       <c r="F462" s="3">
         <v>46065</v>
@@ -12445,10 +12445,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E463" s="2">
-        <v>82166</v>
+        <v>82144</v>
       </c>
       <c r="F463" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12465,16 +12465,16 @@
         <v>29</v>
       </c>
       <c r="C464" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D464" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E464" s="2">
-        <v>82262</v>
+        <v>82166</v>
       </c>
       <c r="F464" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12497,7 +12497,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E465" s="2">
-        <v>82265</v>
+        <v>82262</v>
       </c>
       <c r="F465" s="3">
         <v>46077</v>
@@ -12523,7 +12523,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E466" s="2">
-        <v>82281</v>
+        <v>82265</v>
       </c>
       <c r="F466" s="3">
         <v>46077</v>
@@ -12549,7 +12549,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E467" s="2">
-        <v>82282</v>
+        <v>82281</v>
       </c>
       <c r="F467" s="3">
         <v>46077</v>
@@ -12569,16 +12569,16 @@
         <v>29</v>
       </c>
       <c r="C468" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D468" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E468" s="2">
-        <v>82340</v>
+        <v>82282</v>
       </c>
       <c r="F468" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>9</v>
@@ -12595,16 +12595,16 @@
         <v>29</v>
       </c>
       <c r="C469" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D469" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E469" s="2">
-        <v>82399</v>
+        <v>82340</v>
       </c>
       <c r="F469" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>9</v>
@@ -12627,7 +12627,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E470" s="2">
-        <v>82400</v>
+        <v>82399</v>
       </c>
       <c r="F470" s="3">
         <v>46083</v>
@@ -12653,7 +12653,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E471" s="2">
-        <v>82401</v>
+        <v>82400</v>
       </c>
       <c r="F471" s="3">
         <v>46083</v>
@@ -12679,10 +12679,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E472" s="2">
-        <v>82412</v>
+        <v>82401</v>
       </c>
       <c r="F472" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12705,7 +12705,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E473" s="2">
-        <v>82415</v>
+        <v>82412</v>
       </c>
       <c r="F473" s="3">
         <v>46084</v>
@@ -12719,22 +12719,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="474">
       <c r="A474" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C474" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D474" s="3">
-        <v>46078.6702738773</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E474" s="2">
-        <v>82311</v>
+        <v>82415</v>
       </c>
       <c r="F474" s="3">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12757,7 +12757,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E475" s="2">
-        <v>82312</v>
+        <v>82311</v>
       </c>
       <c r="F475" s="3">
         <v>46078</v>
@@ -12783,7 +12783,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E476" s="2">
-        <v>82313</v>
+        <v>82312</v>
       </c>
       <c r="F476" s="3">
         <v>46078</v>
@@ -12809,7 +12809,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E477" s="2">
-        <v>82314</v>
+        <v>82313</v>
       </c>
       <c r="F477" s="3">
         <v>46078</v>
@@ -12835,10 +12835,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E478" s="2">
-        <v>82346</v>
+        <v>82314</v>
       </c>
       <c r="F478" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12861,7 +12861,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E479" s="2">
-        <v>82361</v>
+        <v>82346</v>
       </c>
       <c r="F479" s="3">
         <v>46080</v>
@@ -12887,10 +12887,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E480" s="2">
-        <v>82385</v>
+        <v>82361</v>
       </c>
       <c r="F480" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>9</v>
@@ -12913,7 +12913,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E481" s="2">
-        <v>82391</v>
+        <v>82385</v>
       </c>
       <c r="F481" s="3">
         <v>46083</v>
@@ -12939,7 +12939,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E482" s="2">
-        <v>82392</v>
+        <v>82391</v>
       </c>
       <c r="F482" s="3">
         <v>46083</v>
@@ -12953,22 +12953,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="483">
       <c r="A483" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C483" s="2">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D483" s="3">
-        <v>46029.4632696412</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E483" s="2">
-        <v>81495</v>
+        <v>82392</v>
       </c>
       <c r="F483" s="3">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>9</v>
@@ -12979,27 +12979,53 @@
     </row>
     <row ht="12.75" customHeight="1" r="484">
       <c r="A484" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C484" s="2">
+        <v>62</v>
+      </c>
+      <c r="D484" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E484" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F484" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G484" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H484" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="485">
+      <c r="A485" s="2">
         <v>9992</v>
       </c>
-      <c r="B484" s="1" t="s">
+      <c r="B485" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C484" s="2">
+      <c r="C485" s="2">
         <v>390</v>
       </c>
-      <c r="D484" s="3">
+      <c r="D485" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E484" s="2">
+      <c r="E485" s="2">
         <v>81684</v>
       </c>
-      <c r="F484" s="3">
+      <c r="F485" s="3">
         <v>46038</v>
       </c>
-      <c r="G484" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H484" s="1" t="s">
+      <c r="G485" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H485" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>EMPRD_CDG</t>
   </si>
@@ -83,10 +83,22 @@
     <t>Reprovados</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Não Concluídos</t>
+  </si>
+  <si>
     <t>KATIA FERREIRA DE BARROS</t>
   </si>
   <si>
     <t>RAFAEL CURSINO DE MOURA LEVY</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Em Aprovação</t>
   </si>
   <si>
     <t>SAMAUMA EVENTOS LTDA</t>
@@ -408,7 +420,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H489"/>
+  <dimension ref="A1:H508"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -6092,80 +6104,80 @@
     </row>
     <row ht="12.75" customHeight="1" r="219">
       <c r="A219" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B219" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C219" s="2">
+        <v>47</v>
+      </c>
+      <c r="D219" s="3">
+        <v>46093.5009358681</v>
+      </c>
+      <c r="E219" s="2">
+        <v>82594</v>
+      </c>
+      <c r="F219" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G219" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C219" s="2">
-        <v>27</v>
-      </c>
-      <c r="D219" s="3">
-        <v>46044.6368950926</v>
-      </c>
-      <c r="E219" s="2">
-        <v>81802</v>
-      </c>
-      <c r="F219" s="3">
-        <v>46044</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H219" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="220">
       <c r="A220" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B220" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C220" s="2">
+        <v>47</v>
+      </c>
+      <c r="D220" s="3">
+        <v>46093.5009358681</v>
+      </c>
+      <c r="E220" s="2">
+        <v>82595</v>
+      </c>
+      <c r="F220" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G220" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C220" s="2">
-        <v>27</v>
-      </c>
-      <c r="D220" s="3">
-        <v>46044.6368950926</v>
-      </c>
-      <c r="E220" s="2">
-        <v>81803</v>
-      </c>
-      <c r="F220" s="3">
-        <v>46044</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H220" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="221">
       <c r="A221" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B221" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C221" s="2">
+        <v>47</v>
+      </c>
+      <c r="D221" s="3">
+        <v>46093.5009358681</v>
+      </c>
+      <c r="E221" s="2">
+        <v>82596</v>
+      </c>
+      <c r="F221" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G221" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C221" s="2">
-        <v>27</v>
-      </c>
-      <c r="D221" s="3">
-        <v>46044.6368950926</v>
-      </c>
-      <c r="E221" s="2">
-        <v>81804</v>
-      </c>
-      <c r="F221" s="3">
-        <v>46044</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H221" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="222">
@@ -6173,7 +6185,7 @@
         <v>2506</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C222" s="2">
         <v>27</v>
@@ -6182,7 +6194,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E222" s="2">
-        <v>81806</v>
+        <v>81802</v>
       </c>
       <c r="F222" s="3">
         <v>46044</v>
@@ -6199,7 +6211,7 @@
         <v>2506</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C223" s="2">
         <v>27</v>
@@ -6208,7 +6220,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E223" s="2">
-        <v>81807</v>
+        <v>81803</v>
       </c>
       <c r="F223" s="3">
         <v>46044</v>
@@ -6225,7 +6237,7 @@
         <v>2506</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C224" s="2">
         <v>27</v>
@@ -6234,10 +6246,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E224" s="2">
-        <v>81812</v>
+        <v>81804</v>
       </c>
       <c r="F224" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>9</v>
@@ -6251,7 +6263,7 @@
         <v>2506</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C225" s="2">
         <v>27</v>
@@ -6260,10 +6272,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E225" s="2">
-        <v>81813</v>
+        <v>81806</v>
       </c>
       <c r="F225" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>9</v>
@@ -6277,7 +6289,7 @@
         <v>2506</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C226" s="2">
         <v>27</v>
@@ -6286,10 +6298,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E226" s="2">
-        <v>81814</v>
+        <v>81807</v>
       </c>
       <c r="F226" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>9</v>
@@ -6303,7 +6315,7 @@
         <v>2506</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C227" s="2">
         <v>27</v>
@@ -6312,7 +6324,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E227" s="2">
-        <v>81818</v>
+        <v>81812</v>
       </c>
       <c r="F227" s="3">
         <v>46045</v>
@@ -6329,7 +6341,7 @@
         <v>2506</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C228" s="2">
         <v>27</v>
@@ -6338,7 +6350,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E228" s="2">
-        <v>81822</v>
+        <v>81813</v>
       </c>
       <c r="F228" s="3">
         <v>46045</v>
@@ -6355,7 +6367,7 @@
         <v>2506</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C229" s="2">
         <v>27</v>
@@ -6364,7 +6376,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E229" s="2">
-        <v>81833</v>
+        <v>81814</v>
       </c>
       <c r="F229" s="3">
         <v>46045</v>
@@ -6381,7 +6393,7 @@
         <v>2506</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C230" s="2">
         <v>27</v>
@@ -6390,7 +6402,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E230" s="2">
-        <v>81841</v>
+        <v>81818</v>
       </c>
       <c r="F230" s="3">
         <v>46045</v>
@@ -6407,19 +6419,19 @@
         <v>2506</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C231" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D231" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E231" s="2">
-        <v>81928</v>
+        <v>81822</v>
       </c>
       <c r="F231" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>9</v>
@@ -6433,19 +6445,19 @@
         <v>2506</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C232" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D232" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E232" s="2">
-        <v>81929</v>
+        <v>81833</v>
       </c>
       <c r="F232" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>9</v>
@@ -6459,19 +6471,19 @@
         <v>2506</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C233" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D233" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E233" s="2">
-        <v>81930</v>
+        <v>81841</v>
       </c>
       <c r="F233" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>9</v>
@@ -6485,7 +6497,7 @@
         <v>2506</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C234" s="2">
         <v>28</v>
@@ -6494,7 +6506,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E234" s="2">
-        <v>81932</v>
+        <v>81928</v>
       </c>
       <c r="F234" s="3">
         <v>46052</v>
@@ -6511,7 +6523,7 @@
         <v>2506</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C235" s="2">
         <v>28</v>
@@ -6520,7 +6532,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E235" s="2">
-        <v>81933</v>
+        <v>81929</v>
       </c>
       <c r="F235" s="3">
         <v>46052</v>
@@ -6537,7 +6549,7 @@
         <v>2506</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C236" s="2">
         <v>28</v>
@@ -6546,7 +6558,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E236" s="2">
-        <v>81934</v>
+        <v>81930</v>
       </c>
       <c r="F236" s="3">
         <v>46052</v>
@@ -6563,7 +6575,7 @@
         <v>2506</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C237" s="2">
         <v>28</v>
@@ -6572,7 +6584,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E237" s="2">
-        <v>81935</v>
+        <v>81932</v>
       </c>
       <c r="F237" s="3">
         <v>46052</v>
@@ -6589,7 +6601,7 @@
         <v>2506</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C238" s="2">
         <v>28</v>
@@ -6598,7 +6610,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E238" s="2">
-        <v>81936</v>
+        <v>81933</v>
       </c>
       <c r="F238" s="3">
         <v>46052</v>
@@ -6615,19 +6627,19 @@
         <v>2506</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C239" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D239" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E239" s="2">
-        <v>82222</v>
+        <v>81934</v>
       </c>
       <c r="F239" s="3">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>9</v>
@@ -6641,19 +6653,19 @@
         <v>2506</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C240" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D240" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E240" s="2">
-        <v>82226</v>
+        <v>81935</v>
       </c>
       <c r="F240" s="3">
-        <v>46073</v>
+        <v>46052</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>9</v>
@@ -6667,19 +6679,19 @@
         <v>2506</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C241" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D241" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E241" s="2">
-        <v>82229</v>
+        <v>81936</v>
       </c>
       <c r="F241" s="3">
-        <v>46073</v>
+        <v>46052</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>9</v>
@@ -6693,19 +6705,19 @@
         <v>2506</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C242" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D242" s="3">
-        <v>46073.5838834375</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E242" s="2">
-        <v>82246</v>
+        <v>82222</v>
       </c>
       <c r="F242" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>9</v>
@@ -6719,19 +6731,19 @@
         <v>2506</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C243" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D243" s="3">
-        <v>46080.6289065162</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E243" s="2">
-        <v>82387</v>
+        <v>82226</v>
       </c>
       <c r="F243" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>9</v>
@@ -6742,22 +6754,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="244">
       <c r="A244" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C244" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D244" s="3">
-        <v>46029.4161474769</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E244" s="2">
-        <v>81478</v>
+        <v>82229</v>
       </c>
       <c r="F244" s="3">
-        <v>46029</v>
+        <v>46073</v>
       </c>
       <c r="G244" s="1" t="s">
         <v>9</v>
@@ -6768,22 +6780,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="245">
       <c r="A245" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C245" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D245" s="3">
-        <v>46029.4161474769</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E245" s="2">
-        <v>81479</v>
+        <v>82246</v>
       </c>
       <c r="F245" s="3">
-        <v>46029</v>
+        <v>46073</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>9</v>
@@ -6794,22 +6806,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="246">
       <c r="A246" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C246" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D246" s="3">
-        <v>46029.4161474769</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E246" s="2">
-        <v>81480</v>
+        <v>82387</v>
       </c>
       <c r="F246" s="3">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>9</v>
@@ -6820,22 +6832,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="247">
       <c r="A247" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C247" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D247" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E247" s="2">
-        <v>81497</v>
+        <v>82590</v>
       </c>
       <c r="F247" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>9</v>
@@ -6846,48 +6858,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="248">
       <c r="A248" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B248" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C248" s="2">
+        <v>32</v>
+      </c>
+      <c r="D248" s="3">
+        <v>46093.4978086806</v>
+      </c>
+      <c r="E248" s="2">
+        <v>82591</v>
+      </c>
+      <c r="F248" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G248" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C248" s="2">
-        <v>26</v>
-      </c>
-      <c r="D248" s="3">
-        <v>46029.4161474769</v>
-      </c>
-      <c r="E248" s="2">
-        <v>81498</v>
-      </c>
-      <c r="F248" s="3">
-        <v>46029</v>
-      </c>
-      <c r="G248" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H248" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="249">
       <c r="A249" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C249" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D249" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E249" s="2">
-        <v>81499</v>
+        <v>82592</v>
       </c>
       <c r="F249" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>9</v>
@@ -6898,22 +6910,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="250">
       <c r="A250" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C250" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D250" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E250" s="2">
-        <v>81500</v>
+        <v>82593</v>
       </c>
       <c r="F250" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>9</v>
@@ -6924,22 +6936,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="251">
       <c r="A251" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C251" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D251" s="3">
-        <v>46049.6888218403</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E251" s="2">
-        <v>81878</v>
+        <v>82600</v>
       </c>
       <c r="F251" s="3">
-        <v>46049</v>
+        <v>46093</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>9</v>
@@ -6953,19 +6965,19 @@
         <v>2507</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C252" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D252" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E252" s="2">
-        <v>81879</v>
+        <v>81478</v>
       </c>
       <c r="F252" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>9</v>
@@ -6979,19 +6991,19 @@
         <v>2507</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C253" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D253" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E253" s="2">
-        <v>81885</v>
+        <v>81479</v>
       </c>
       <c r="F253" s="3">
-        <v>46050</v>
+        <v>46029</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>9</v>
@@ -7005,19 +7017,19 @@
         <v>2507</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C254" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D254" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E254" s="2">
-        <v>81886</v>
+        <v>81480</v>
       </c>
       <c r="F254" s="3">
-        <v>46050</v>
+        <v>46029</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>9</v>
@@ -7031,19 +7043,19 @@
         <v>2507</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C255" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D255" s="3">
-        <v>46062.7199601505</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E255" s="2">
-        <v>82068</v>
+        <v>81497</v>
       </c>
       <c r="F255" s="3">
-        <v>46062</v>
+        <v>46029</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>9</v>
@@ -7057,19 +7069,19 @@
         <v>2507</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C256" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D256" s="3">
-        <v>46062.7199601505</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E256" s="2">
-        <v>82072</v>
+        <v>81498</v>
       </c>
       <c r="F256" s="3">
-        <v>46063</v>
+        <v>46029</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>9</v>
@@ -7083,19 +7095,19 @@
         <v>2507</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C257" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D257" s="3">
-        <v>46062.7199601505</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E257" s="2">
-        <v>82076</v>
+        <v>81499</v>
       </c>
       <c r="F257" s="3">
-        <v>46063</v>
+        <v>46029</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>9</v>
@@ -7109,19 +7121,19 @@
         <v>2507</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C258" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D258" s="3">
-        <v>46062.7199601505</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E258" s="2">
-        <v>82078</v>
+        <v>81500</v>
       </c>
       <c r="F258" s="3">
-        <v>46063</v>
+        <v>46029</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>9</v>
@@ -7135,19 +7147,19 @@
         <v>2507</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C259" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D259" s="3">
-        <v>46077.7216803356</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E259" s="2">
-        <v>82287</v>
+        <v>81878</v>
       </c>
       <c r="F259" s="3">
-        <v>46077</v>
+        <v>46049</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>9</v>
@@ -7161,19 +7173,19 @@
         <v>2507</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C260" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D260" s="3">
-        <v>46077.7216803356</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E260" s="2">
-        <v>82288</v>
+        <v>81879</v>
       </c>
       <c r="F260" s="3">
-        <v>46077</v>
+        <v>46049</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>9</v>
@@ -7187,19 +7199,19 @@
         <v>2507</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C261" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D261" s="3">
-        <v>46077.7216803356</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E261" s="2">
-        <v>82298</v>
+        <v>81885</v>
       </c>
       <c r="F261" s="3">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>9</v>
@@ -7213,19 +7225,19 @@
         <v>2507</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C262" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D262" s="3">
-        <v>46077.7216803356</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E262" s="2">
-        <v>82301</v>
+        <v>81886</v>
       </c>
       <c r="F262" s="3">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>9</v>
@@ -7239,19 +7251,19 @@
         <v>2507</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C263" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D263" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E263" s="2">
-        <v>82304</v>
+        <v>82068</v>
       </c>
       <c r="F263" s="3">
-        <v>46078</v>
+        <v>46062</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>9</v>
@@ -7265,19 +7277,19 @@
         <v>2507</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C264" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D264" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E264" s="2">
-        <v>82308</v>
+        <v>82072</v>
       </c>
       <c r="F264" s="3">
-        <v>46078</v>
+        <v>46063</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>9</v>
@@ -7291,19 +7303,19 @@
         <v>2507</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C265" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D265" s="3">
-        <v>46080.628344919</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E265" s="2">
-        <v>82373</v>
+        <v>82076</v>
       </c>
       <c r="F265" s="3">
-        <v>46080</v>
+        <v>46063</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>9</v>
@@ -7317,19 +7329,19 @@
         <v>2507</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C266" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D266" s="3">
-        <v>46085.6581644213</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E266" s="2">
-        <v>82445</v>
+        <v>82078</v>
       </c>
       <c r="F266" s="3">
-        <v>46085</v>
+        <v>46063</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>9</v>
@@ -7343,19 +7355,19 @@
         <v>2507</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C267" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D267" s="3">
-        <v>46085.6581644213</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E267" s="2">
-        <v>82447</v>
+        <v>82287</v>
       </c>
       <c r="F267" s="3">
-        <v>46085</v>
+        <v>46077</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>9</v>
@@ -7369,19 +7381,19 @@
         <v>2507</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C268" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D268" s="3">
-        <v>46085.6581644213</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E268" s="2">
-        <v>82453</v>
+        <v>82288</v>
       </c>
       <c r="F268" s="3">
-        <v>46086</v>
+        <v>46077</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>9</v>
@@ -7395,19 +7407,19 @@
         <v>2507</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C269" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D269" s="3">
-        <v>46085.6581644213</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E269" s="2">
-        <v>82468</v>
+        <v>82298</v>
       </c>
       <c r="F269" s="3">
-        <v>46086</v>
+        <v>46078</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>9</v>
@@ -7418,22 +7430,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="270">
       <c r="A270" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C270" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D270" s="3">
-        <v>46029.6400966782</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E270" s="2">
-        <v>81506</v>
+        <v>82301</v>
       </c>
       <c r="F270" s="3">
-        <v>46029</v>
+        <v>46078</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>9</v>
@@ -7444,22 +7456,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="271">
       <c r="A271" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C271" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D271" s="3">
-        <v>46029.6400966782</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E271" s="2">
-        <v>81507</v>
+        <v>82304</v>
       </c>
       <c r="F271" s="3">
-        <v>46029</v>
+        <v>46078</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>9</v>
@@ -7470,22 +7482,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="272">
       <c r="A272" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C272" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D272" s="3">
-        <v>46029.6400966782</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E272" s="2">
-        <v>81524</v>
+        <v>82308</v>
       </c>
       <c r="F272" s="3">
-        <v>46030</v>
+        <v>46078</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>9</v>
@@ -7496,22 +7508,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="273">
       <c r="A273" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C273" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D273" s="3">
-        <v>46029.6400966782</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E273" s="2">
-        <v>81525</v>
+        <v>82373</v>
       </c>
       <c r="F273" s="3">
-        <v>46030</v>
+        <v>46080</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>9</v>
@@ -7522,22 +7534,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="274">
       <c r="A274" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C274" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D274" s="3">
-        <v>46029.6400966782</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E274" s="2">
-        <v>81526</v>
+        <v>82445</v>
       </c>
       <c r="F274" s="3">
-        <v>46030</v>
+        <v>46085</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>9</v>
@@ -7548,22 +7560,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="275">
       <c r="A275" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C275" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D275" s="3">
-        <v>46036.6348522801</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E275" s="2">
-        <v>81640</v>
+        <v>82447</v>
       </c>
       <c r="F275" s="3">
-        <v>46036</v>
+        <v>46085</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>9</v>
@@ -7574,22 +7586,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="276">
       <c r="A276" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C276" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D276" s="3">
-        <v>46036.6348522801</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E276" s="2">
-        <v>81642</v>
+        <v>82453</v>
       </c>
       <c r="F276" s="3">
-        <v>46036</v>
+        <v>46086</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>9</v>
@@ -7600,22 +7612,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="277">
       <c r="A277" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C277" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D277" s="3">
-        <v>46036.6348522801</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E277" s="2">
-        <v>81643</v>
+        <v>82468</v>
       </c>
       <c r="F277" s="3">
-        <v>46036</v>
+        <v>46086</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>9</v>
@@ -7629,19 +7641,19 @@
         <v>2509</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C278" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D278" s="3">
-        <v>46045.4207558912</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E278" s="2">
-        <v>81835</v>
+        <v>81506</v>
       </c>
       <c r="F278" s="3">
-        <v>46045</v>
+        <v>46029</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>9</v>
@@ -7655,19 +7667,19 @@
         <v>2509</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C279" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D279" s="3">
-        <v>46045.4207558912</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E279" s="2">
-        <v>81836</v>
+        <v>81507</v>
       </c>
       <c r="F279" s="3">
-        <v>46045</v>
+        <v>46029</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>9</v>
@@ -7681,19 +7693,19 @@
         <v>2509</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C280" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D280" s="3">
-        <v>46045.4207558912</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E280" s="2">
-        <v>81837</v>
+        <v>81524</v>
       </c>
       <c r="F280" s="3">
-        <v>46045</v>
+        <v>46030</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>9</v>
@@ -7707,19 +7719,19 @@
         <v>2509</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C281" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D281" s="3">
-        <v>46051.6376515278</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E281" s="2">
-        <v>81931</v>
+        <v>81525</v>
       </c>
       <c r="F281" s="3">
-        <v>46052</v>
+        <v>46030</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>9</v>
@@ -7733,19 +7745,19 @@
         <v>2509</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C282" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D282" s="3">
-        <v>46056.7115158912</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E282" s="2">
-        <v>81978</v>
+        <v>81526</v>
       </c>
       <c r="F282" s="3">
-        <v>46057</v>
+        <v>46030</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>9</v>
@@ -7759,19 +7771,19 @@
         <v>2509</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C283" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D283" s="3">
-        <v>46057.6911087731</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E283" s="2">
-        <v>81994</v>
+        <v>81640</v>
       </c>
       <c r="F283" s="3">
-        <v>46057</v>
+        <v>46036</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>9</v>
@@ -7785,19 +7797,19 @@
         <v>2509</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C284" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D284" s="3">
-        <v>46057.6911087731</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E284" s="2">
-        <v>81995</v>
+        <v>81642</v>
       </c>
       <c r="F284" s="3">
-        <v>46057</v>
+        <v>46036</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>9</v>
@@ -7811,19 +7823,19 @@
         <v>2509</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C285" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D285" s="3">
-        <v>46057.6911087731</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E285" s="2">
-        <v>81999</v>
+        <v>81643</v>
       </c>
       <c r="F285" s="3">
-        <v>46057</v>
+        <v>46036</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>9</v>
@@ -7837,19 +7849,19 @@
         <v>2509</v>
       </c>
       <c r="B286" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C286" s="2">
         <v>24</v>
       </c>
-      <c r="C286" s="2">
-        <v>27</v>
-      </c>
       <c r="D286" s="3">
-        <v>46057.6911087731</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E286" s="2">
-        <v>82008</v>
+        <v>81835</v>
       </c>
       <c r="F286" s="3">
-        <v>46058</v>
+        <v>46045</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>9</v>
@@ -7863,19 +7875,19 @@
         <v>2509</v>
       </c>
       <c r="B287" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C287" s="2">
         <v>24</v>
       </c>
-      <c r="C287" s="2">
-        <v>27</v>
-      </c>
       <c r="D287" s="3">
-        <v>46057.6911087731</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E287" s="2">
-        <v>82011</v>
+        <v>81836</v>
       </c>
       <c r="F287" s="3">
-        <v>46058</v>
+        <v>46045</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>9</v>
@@ -7889,19 +7901,19 @@
         <v>2509</v>
       </c>
       <c r="B288" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C288" s="2">
         <v>24</v>
       </c>
-      <c r="C288" s="2">
-        <v>27</v>
-      </c>
       <c r="D288" s="3">
-        <v>46057.6911087731</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E288" s="2">
-        <v>82012</v>
+        <v>81837</v>
       </c>
       <c r="F288" s="3">
-        <v>46058</v>
+        <v>46045</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>9</v>
@@ -7915,19 +7927,19 @@
         <v>2509</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C289" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D289" s="3">
-        <v>46057.6911087731</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E289" s="2">
-        <v>82013</v>
+        <v>81931</v>
       </c>
       <c r="F289" s="3">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>9</v>
@@ -7941,19 +7953,19 @@
         <v>2509</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C290" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D290" s="3">
-        <v>46057.6911087731</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E290" s="2">
-        <v>82014</v>
+        <v>81978</v>
       </c>
       <c r="F290" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>9</v>
@@ -7967,25 +7979,25 @@
         <v>2509</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C291" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D291" s="3">
-        <v>46058.6604985417</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E291" s="2">
-        <v>82046</v>
+        <v>81994</v>
       </c>
       <c r="F291" s="3">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="292">
@@ -7993,19 +8005,19 @@
         <v>2509</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C292" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D292" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E292" s="2">
-        <v>82217</v>
+        <v>81995</v>
       </c>
       <c r="F292" s="3">
-        <v>46072</v>
+        <v>46057</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>9</v>
@@ -8019,19 +8031,19 @@
         <v>2509</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C293" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D293" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E293" s="2">
-        <v>82218</v>
+        <v>81999</v>
       </c>
       <c r="F293" s="3">
-        <v>46072</v>
+        <v>46057</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>9</v>
@@ -8045,19 +8057,19 @@
         <v>2509</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C294" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D294" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E294" s="2">
-        <v>82234</v>
+        <v>82008</v>
       </c>
       <c r="F294" s="3">
-        <v>46073</v>
+        <v>46058</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>9</v>
@@ -8071,19 +8083,19 @@
         <v>2509</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C295" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D295" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E295" s="2">
-        <v>82238</v>
+        <v>82011</v>
       </c>
       <c r="F295" s="3">
-        <v>46073</v>
+        <v>46058</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>9</v>
@@ -8097,19 +8109,19 @@
         <v>2509</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C296" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D296" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E296" s="2">
-        <v>82245</v>
+        <v>82012</v>
       </c>
       <c r="F296" s="3">
-        <v>46073</v>
+        <v>46058</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>9</v>
@@ -8123,19 +8135,19 @@
         <v>2509</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C297" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D297" s="3">
-        <v>46076.7244851042</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E297" s="2">
-        <v>82257</v>
+        <v>82013</v>
       </c>
       <c r="F297" s="3">
-        <v>46076</v>
+        <v>46058</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>9</v>
@@ -8149,19 +8161,19 @@
         <v>2509</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C298" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D298" s="3">
-        <v>46076.7244851042</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E298" s="2">
-        <v>82276</v>
+        <v>82014</v>
       </c>
       <c r="F298" s="3">
-        <v>46077</v>
+        <v>46058</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>9</v>
@@ -8175,25 +8187,25 @@
         <v>2509</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C299" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D299" s="3">
-        <v>46076.7244851042</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E299" s="2">
-        <v>82277</v>
+        <v>82046</v>
       </c>
       <c r="F299" s="3">
-        <v>46077</v>
+        <v>46059</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="300">
@@ -8201,19 +8213,19 @@
         <v>2509</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C300" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D300" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E300" s="2">
-        <v>82293</v>
+        <v>82217</v>
       </c>
       <c r="F300" s="3">
-        <v>46078</v>
+        <v>46072</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>9</v>
@@ -8227,19 +8239,19 @@
         <v>2509</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C301" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D301" s="3">
-        <v>46077.4356327431</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E301" s="2">
-        <v>82269</v>
+        <v>82218</v>
       </c>
       <c r="F301" s="3">
-        <v>46077</v>
+        <v>46072</v>
       </c>
       <c r="G301" s="1" t="s">
         <v>9</v>
@@ -8253,19 +8265,19 @@
         <v>2509</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C302" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D302" s="3">
-        <v>46084.7378501505</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E302" s="2">
-        <v>82419</v>
+        <v>82234</v>
       </c>
       <c r="F302" s="3">
-        <v>46084</v>
+        <v>46073</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>9</v>
@@ -8279,19 +8291,19 @@
         <v>2509</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C303" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D303" s="3">
-        <v>46084.7378501505</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E303" s="2">
-        <v>82420</v>
+        <v>82238</v>
       </c>
       <c r="F303" s="3">
-        <v>46084</v>
+        <v>46073</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>9</v>
@@ -8305,19 +8317,19 @@
         <v>2509</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C304" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D304" s="3">
-        <v>46084.7378501505</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E304" s="2">
-        <v>82421</v>
+        <v>82245</v>
       </c>
       <c r="F304" s="3">
-        <v>46084</v>
+        <v>46073</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>9</v>
@@ -8331,19 +8343,19 @@
         <v>2509</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C305" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D305" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E305" s="2">
-        <v>82422</v>
+        <v>82257</v>
       </c>
       <c r="F305" s="3">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>9</v>
@@ -8357,19 +8369,19 @@
         <v>2509</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C306" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D306" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E306" s="2">
-        <v>82423</v>
+        <v>82276</v>
       </c>
       <c r="F306" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>9</v>
@@ -8383,19 +8395,19 @@
         <v>2509</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C307" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D307" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E307" s="2">
-        <v>82433</v>
+        <v>82277</v>
       </c>
       <c r="F307" s="3">
-        <v>46085</v>
+        <v>46077</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>9</v>
@@ -8409,19 +8421,19 @@
         <v>2509</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C308" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D308" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E308" s="2">
-        <v>82434</v>
+        <v>82293</v>
       </c>
       <c r="F308" s="3">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>9</v>
@@ -8435,19 +8447,19 @@
         <v>2509</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C309" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D309" s="3">
-        <v>46084.7378501505</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E309" s="2">
-        <v>82464</v>
+        <v>82269</v>
       </c>
       <c r="F309" s="3">
-        <v>46086</v>
+        <v>46077</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>9</v>
@@ -8461,7 +8473,7 @@
         <v>2509</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C310" s="2">
         <v>32</v>
@@ -8470,10 +8482,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E310" s="2">
-        <v>82472</v>
+        <v>82419</v>
       </c>
       <c r="F310" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>9</v>
@@ -8484,22 +8496,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="311">
       <c r="A311" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C311" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D311" s="3">
-        <v>46027.6953206134</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E311" s="2">
-        <v>81464</v>
+        <v>82420</v>
       </c>
       <c r="F311" s="3">
-        <v>46027</v>
+        <v>46084</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>9</v>
@@ -8510,22 +8522,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="312">
       <c r="A312" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C312" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D312" s="3">
-        <v>46027.6953206134</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E312" s="2">
-        <v>81472</v>
+        <v>82421</v>
       </c>
       <c r="F312" s="3">
-        <v>46027</v>
+        <v>46084</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>9</v>
@@ -8536,22 +8548,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="313">
       <c r="A313" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C313" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D313" s="3">
-        <v>46027.6953206134</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E313" s="2">
-        <v>81492</v>
+        <v>82422</v>
       </c>
       <c r="F313" s="3">
-        <v>46029</v>
+        <v>46084</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>9</v>
@@ -8562,22 +8574,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="314">
       <c r="A314" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C314" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D314" s="3">
-        <v>46027.6953206134</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E314" s="2">
-        <v>81493</v>
+        <v>82423</v>
       </c>
       <c r="F314" s="3">
-        <v>46029</v>
+        <v>46084</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>9</v>
@@ -8588,22 +8600,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="315">
       <c r="A315" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C315" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D315" s="3">
-        <v>46027.6953206134</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E315" s="2">
-        <v>81568</v>
+        <v>82433</v>
       </c>
       <c r="F315" s="3">
-        <v>46031</v>
+        <v>46085</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>9</v>
@@ -8614,22 +8626,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="316">
       <c r="A316" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C316" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D316" s="3">
-        <v>46027.6953206134</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E316" s="2">
-        <v>81601</v>
+        <v>82434</v>
       </c>
       <c r="F316" s="3">
-        <v>46034</v>
+        <v>46085</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>9</v>
@@ -8640,22 +8652,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="317">
       <c r="A317" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C317" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D317" s="3">
-        <v>46027.6953206134</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E317" s="2">
-        <v>81602</v>
+        <v>82464</v>
       </c>
       <c r="F317" s="3">
-        <v>46034</v>
+        <v>46086</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>9</v>
@@ -8666,22 +8678,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="318">
       <c r="A318" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C318" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D318" s="3">
-        <v>46036.6368094444</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E318" s="2">
-        <v>81645</v>
+        <v>82472</v>
       </c>
       <c r="F318" s="3">
-        <v>46036</v>
+        <v>46086</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>9</v>
@@ -8692,22 +8704,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="319">
       <c r="A319" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C319" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D319" s="3">
-        <v>46036.6368094444</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E319" s="2">
-        <v>81646</v>
+        <v>82578</v>
       </c>
       <c r="F319" s="3">
-        <v>46036</v>
+        <v>46093</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>9</v>
@@ -8718,22 +8730,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="320">
       <c r="A320" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C320" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D320" s="3">
-        <v>46036.6368094444</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E320" s="2">
-        <v>81653</v>
+        <v>82579</v>
       </c>
       <c r="F320" s="3">
-        <v>46037</v>
+        <v>46093</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>9</v>
@@ -8744,74 +8756,74 @@
     </row>
     <row ht="12.75" customHeight="1" r="321">
       <c r="A321" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C321" s="2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D321" s="3">
-        <v>46037.4325152662</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E321" s="2">
-        <v>81662</v>
+        <v>82580</v>
       </c>
       <c r="F321" s="3">
-        <v>46037</v>
+        <v>46093</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="322">
       <c r="A322" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C322" s="2">
+        <v>33</v>
+      </c>
+      <c r="D322" s="3">
+        <v>46093.4897546412</v>
+      </c>
+      <c r="E322" s="2">
+        <v>82599</v>
+      </c>
+      <c r="F322" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G322" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H322" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D322" s="3">
-        <v>46044.4079891435</v>
-      </c>
-      <c r="E322" s="2">
-        <v>81780</v>
-      </c>
-      <c r="F322" s="3">
-        <v>46044</v>
-      </c>
-      <c r="G322" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H322" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="323">
       <c r="A323" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C323" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D323" s="3">
-        <v>46044.4079891435</v>
+        <v>46093.4957757986</v>
       </c>
       <c r="E323" s="2">
-        <v>81781</v>
+        <v>82584</v>
       </c>
       <c r="F323" s="3">
-        <v>46044</v>
+        <v>46093</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>9</v>
@@ -8825,19 +8837,19 @@
         <v>2510</v>
       </c>
       <c r="B324" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C324" s="2">
         <v>25</v>
       </c>
-      <c r="C324" s="2">
-        <v>28</v>
-      </c>
       <c r="D324" s="3">
-        <v>46044.4079891435</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E324" s="2">
-        <v>81782</v>
+        <v>81464</v>
       </c>
       <c r="F324" s="3">
-        <v>46044</v>
+        <v>46027</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>9</v>
@@ -8851,19 +8863,19 @@
         <v>2510</v>
       </c>
       <c r="B325" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C325" s="2">
         <v>25</v>
       </c>
-      <c r="C325" s="2">
-        <v>28</v>
-      </c>
       <c r="D325" s="3">
-        <v>46044.4079891435</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E325" s="2">
-        <v>81784</v>
+        <v>81472</v>
       </c>
       <c r="F325" s="3">
-        <v>46044</v>
+        <v>46027</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>9</v>
@@ -8877,19 +8889,19 @@
         <v>2510</v>
       </c>
       <c r="B326" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C326" s="2">
         <v>25</v>
       </c>
-      <c r="C326" s="2">
-        <v>28</v>
-      </c>
       <c r="D326" s="3">
-        <v>46044.4079891435</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E326" s="2">
-        <v>81785</v>
+        <v>81492</v>
       </c>
       <c r="F326" s="3">
-        <v>46044</v>
+        <v>46029</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>9</v>
@@ -8903,19 +8915,19 @@
         <v>2510</v>
       </c>
       <c r="B327" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C327" s="2">
         <v>25</v>
       </c>
-      <c r="C327" s="2">
-        <v>28</v>
-      </c>
       <c r="D327" s="3">
-        <v>46044.4079891435</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E327" s="2">
-        <v>81801</v>
+        <v>81493</v>
       </c>
       <c r="F327" s="3">
-        <v>46044</v>
+        <v>46029</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>9</v>
@@ -8929,19 +8941,19 @@
         <v>2510</v>
       </c>
       <c r="B328" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C328" s="2">
         <v>25</v>
       </c>
-      <c r="C328" s="2">
-        <v>29</v>
-      </c>
       <c r="D328" s="3">
-        <v>46048.7319778588</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E328" s="2">
-        <v>81860</v>
+        <v>81568</v>
       </c>
       <c r="F328" s="3">
-        <v>46049</v>
+        <v>46031</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>9</v>
@@ -8955,19 +8967,19 @@
         <v>2510</v>
       </c>
       <c r="B329" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C329" s="2">
         <v>25</v>
       </c>
-      <c r="C329" s="2">
-        <v>29</v>
-      </c>
       <c r="D329" s="3">
-        <v>46048.7319778588</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E329" s="2">
-        <v>81873</v>
+        <v>81601</v>
       </c>
       <c r="F329" s="3">
-        <v>46049</v>
+        <v>46034</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>9</v>
@@ -8981,19 +8993,19 @@
         <v>2510</v>
       </c>
       <c r="B330" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C330" s="2">
         <v>25</v>
       </c>
-      <c r="C330" s="2">
-        <v>30</v>
-      </c>
       <c r="D330" s="3">
-        <v>46049.4883916667</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E330" s="2">
-        <v>81865</v>
+        <v>81602</v>
       </c>
       <c r="F330" s="3">
-        <v>46049</v>
+        <v>46034</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>9</v>
@@ -9007,19 +9019,19 @@
         <v>2510</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C331" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D331" s="3">
-        <v>46049.4883916667</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E331" s="2">
-        <v>81870</v>
+        <v>81645</v>
       </c>
       <c r="F331" s="3">
-        <v>46049</v>
+        <v>46036</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>9</v>
@@ -9033,19 +9045,19 @@
         <v>2510</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C332" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D332" s="3">
-        <v>46049.4883916667</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E332" s="2">
-        <v>81872</v>
+        <v>81646</v>
       </c>
       <c r="F332" s="3">
-        <v>46049</v>
+        <v>46036</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>9</v>
@@ -9059,19 +9071,19 @@
         <v>2510</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C333" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D333" s="3">
-        <v>46049.4883916667</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E333" s="2">
-        <v>81896</v>
+        <v>81653</v>
       </c>
       <c r="F333" s="3">
-        <v>46050</v>
+        <v>46037</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>9</v>
@@ -9085,19 +9097,19 @@
         <v>2510</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C334" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D334" s="3">
-        <v>46051.4046937153</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E334" s="2">
-        <v>81923</v>
+        <v>81662</v>
       </c>
       <c r="F334" s="3">
-        <v>46051</v>
+        <v>46037</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>9</v>
@@ -9111,19 +9123,19 @@
         <v>2510</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C335" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D335" s="3">
-        <v>46057.6959672917</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E335" s="2">
-        <v>81998</v>
+        <v>81780</v>
       </c>
       <c r="F335" s="3">
-        <v>46057</v>
+        <v>46044</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>9</v>
@@ -9137,19 +9149,19 @@
         <v>2510</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C336" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D336" s="3">
-        <v>46057.6959672917</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E336" s="2">
-        <v>82002</v>
+        <v>81781</v>
       </c>
       <c r="F336" s="3">
-        <v>46057</v>
+        <v>46044</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>9</v>
@@ -9163,19 +9175,19 @@
         <v>2510</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C337" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D337" s="3">
-        <v>46057.6959672917</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E337" s="2">
-        <v>82005</v>
+        <v>81782</v>
       </c>
       <c r="F337" s="3">
-        <v>46058</v>
+        <v>46044</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>9</v>
@@ -9189,19 +9201,19 @@
         <v>2510</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C338" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D338" s="3">
-        <v>46057.6959672917</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E338" s="2">
-        <v>82007</v>
+        <v>81784</v>
       </c>
       <c r="F338" s="3">
-        <v>46058</v>
+        <v>46044</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>9</v>
@@ -9215,19 +9227,19 @@
         <v>2510</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C339" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D339" s="3">
-        <v>46063.5942651852</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E339" s="2">
-        <v>82005</v>
+        <v>81785</v>
       </c>
       <c r="F339" s="3">
-        <v>46058</v>
+        <v>46044</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>9</v>
@@ -9241,19 +9253,19 @@
         <v>2510</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C340" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D340" s="3">
-        <v>46063.5942651852</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E340" s="2">
-        <v>82075</v>
+        <v>81801</v>
       </c>
       <c r="F340" s="3">
-        <v>46063</v>
+        <v>46044</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>9</v>
@@ -9267,19 +9279,19 @@
         <v>2510</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C341" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D341" s="3">
-        <v>46063.5942651852</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E341" s="2">
-        <v>82077</v>
+        <v>81860</v>
       </c>
       <c r="F341" s="3">
-        <v>46063</v>
+        <v>46049</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>9</v>
@@ -9293,19 +9305,19 @@
         <v>2510</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C342" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D342" s="3">
-        <v>46063.5942651852</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E342" s="2">
-        <v>82099</v>
+        <v>81873</v>
       </c>
       <c r="F342" s="3">
-        <v>46064</v>
+        <v>46049</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>9</v>
@@ -9319,19 +9331,19 @@
         <v>2510</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C343" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D343" s="3">
-        <v>46072.7460071991</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E343" s="2">
-        <v>82219</v>
+        <v>81865</v>
       </c>
       <c r="F343" s="3">
-        <v>46072</v>
+        <v>46049</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>9</v>
@@ -9345,19 +9357,19 @@
         <v>2510</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C344" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D344" s="3">
-        <v>46072.7460071991</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E344" s="2">
-        <v>82230</v>
+        <v>81870</v>
       </c>
       <c r="F344" s="3">
-        <v>46073</v>
+        <v>46049</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>9</v>
@@ -9371,19 +9383,19 @@
         <v>2510</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C345" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D345" s="3">
-        <v>46072.7460071991</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E345" s="2">
-        <v>82231</v>
+        <v>81872</v>
       </c>
       <c r="F345" s="3">
-        <v>46073</v>
+        <v>46049</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>9</v>
@@ -9397,19 +9409,19 @@
         <v>2510</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C346" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D346" s="3">
-        <v>46079.5787315972</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E346" s="2">
-        <v>82388</v>
+        <v>81896</v>
       </c>
       <c r="F346" s="3">
-        <v>46083</v>
+        <v>46050</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>9</v>
@@ -9423,19 +9435,19 @@
         <v>2510</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C347" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D347" s="3">
-        <v>46079.5787315972</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E347" s="2">
-        <v>82389</v>
+        <v>81923</v>
       </c>
       <c r="F347" s="3">
-        <v>46083</v>
+        <v>46051</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>9</v>
@@ -9449,19 +9461,19 @@
         <v>2510</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C348" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D348" s="3">
-        <v>46079.5787315972</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E348" s="2">
-        <v>82396</v>
+        <v>81998</v>
       </c>
       <c r="F348" s="3">
-        <v>46083</v>
+        <v>46057</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>9</v>
@@ -9475,19 +9487,19 @@
         <v>2510</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C349" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D349" s="3">
-        <v>46079.5787315972</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E349" s="2">
-        <v>82397</v>
+        <v>82002</v>
       </c>
       <c r="F349" s="3">
-        <v>46083</v>
+        <v>46057</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>9</v>
@@ -9501,19 +9513,19 @@
         <v>2510</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C350" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D350" s="3">
-        <v>46085.6249659838</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E350" s="2">
-        <v>82435</v>
+        <v>82005</v>
       </c>
       <c r="F350" s="3">
-        <v>46085</v>
+        <v>46058</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>9</v>
@@ -9527,19 +9539,19 @@
         <v>2510</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C351" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D351" s="3">
-        <v>46091.449444456</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E351" s="2">
-        <v>82506</v>
+        <v>82007</v>
       </c>
       <c r="F351" s="3">
-        <v>46091</v>
+        <v>46058</v>
       </c>
       <c r="G351" s="1" t="s">
         <v>9</v>
@@ -9553,19 +9565,19 @@
         <v>2510</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C352" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D352" s="3">
-        <v>46091.4795702315</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E352" s="2">
-        <v>82509</v>
+        <v>82005</v>
       </c>
       <c r="F352" s="3">
-        <v>46091</v>
+        <v>46058</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>9</v>
@@ -9576,22 +9588,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="353">
       <c r="A353" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C353" s="2">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D353" s="3">
-        <v>46029.3821391551</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E353" s="2">
-        <v>81477</v>
+        <v>82075</v>
       </c>
       <c r="F353" s="3">
-        <v>46029</v>
+        <v>46063</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>9</v>
@@ -9602,22 +9614,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="354">
       <c r="A354" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C354" s="2">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D354" s="3">
-        <v>46030.4142968056</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E354" s="2">
-        <v>81532</v>
+        <v>82077</v>
       </c>
       <c r="F354" s="3">
-        <v>46030</v>
+        <v>46063</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>9</v>
@@ -9628,22 +9640,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="355">
       <c r="A355" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C355" s="2">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D355" s="3">
-        <v>46030.4142968056</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E355" s="2">
-        <v>81534</v>
+        <v>82099</v>
       </c>
       <c r="F355" s="3">
-        <v>46030</v>
+        <v>46064</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>9</v>
@@ -9654,22 +9666,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="356">
       <c r="A356" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C356" s="2">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D356" s="3">
-        <v>46030.4142968056</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E356" s="2">
-        <v>81535</v>
+        <v>82219</v>
       </c>
       <c r="F356" s="3">
-        <v>46030</v>
+        <v>46072</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>9</v>
@@ -9680,22 +9692,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="357">
       <c r="A357" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C357" s="2">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D357" s="3">
-        <v>46030.4142968056</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E357" s="2">
-        <v>81550</v>
+        <v>82230</v>
       </c>
       <c r="F357" s="3">
-        <v>46030</v>
+        <v>46073</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>9</v>
@@ -9706,22 +9718,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="358">
       <c r="A358" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C358" s="2">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D358" s="3">
-        <v>46030.4142968056</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E358" s="2">
-        <v>81553</v>
+        <v>82231</v>
       </c>
       <c r="F358" s="3">
-        <v>46030</v>
+        <v>46073</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>9</v>
@@ -9732,22 +9744,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="359">
       <c r="A359" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C359" s="2">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D359" s="3">
-        <v>46030.4142968056</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E359" s="2">
-        <v>81554</v>
+        <v>82388</v>
       </c>
       <c r="F359" s="3">
-        <v>46030</v>
+        <v>46083</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>9</v>
@@ -9758,22 +9770,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="360">
       <c r="A360" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C360" s="2">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D360" s="3">
-        <v>46030.4142968056</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E360" s="2">
-        <v>81557</v>
+        <v>82389</v>
       </c>
       <c r="F360" s="3">
-        <v>46030</v>
+        <v>46083</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>9</v>
@@ -9784,22 +9796,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="361">
       <c r="A361" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C361" s="2">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D361" s="3">
-        <v>46030.4142968056</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E361" s="2">
-        <v>81588</v>
+        <v>82396</v>
       </c>
       <c r="F361" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>9</v>
@@ -9810,22 +9822,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="362">
       <c r="A362" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C362" s="2">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D362" s="3">
-        <v>46038.593985081</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E362" s="2">
-        <v>81692</v>
+        <v>82397</v>
       </c>
       <c r="F362" s="3">
-        <v>46038</v>
+        <v>46083</v>
       </c>
       <c r="G362" s="1" t="s">
         <v>9</v>
@@ -9836,22 +9848,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="363">
       <c r="A363" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C363" s="2">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D363" s="3">
-        <v>46044.46462125</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E363" s="2">
-        <v>81786</v>
+        <v>82435</v>
       </c>
       <c r="F363" s="3">
-        <v>46044</v>
+        <v>46085</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>9</v>
@@ -9862,22 +9874,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="364">
       <c r="A364" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C364" s="2">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D364" s="3">
-        <v>46044.6362443171</v>
+        <v>46091.449444456</v>
       </c>
       <c r="E364" s="2">
-        <v>81844</v>
+        <v>82506</v>
       </c>
       <c r="F364" s="3">
-        <v>46045</v>
+        <v>46091</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>9</v>
@@ -9888,22 +9900,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="365">
       <c r="A365" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C365" s="2">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D365" s="3">
-        <v>46062.717040544</v>
+        <v>46091.4795702315</v>
       </c>
       <c r="E365" s="2">
-        <v>82065</v>
+        <v>82509</v>
       </c>
       <c r="F365" s="3">
-        <v>46062</v>
+        <v>46091</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>9</v>
@@ -9914,22 +9926,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="366">
       <c r="A366" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C366" s="2">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D366" s="3">
-        <v>46062.717040544</v>
+        <v>46093.4969972338</v>
       </c>
       <c r="E366" s="2">
-        <v>82066</v>
+        <v>82589</v>
       </c>
       <c r="F366" s="3">
-        <v>46062</v>
+        <v>46093</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>9</v>
@@ -9943,19 +9955,19 @@
         <v>2511</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C367" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D367" s="3">
-        <v>46062.717040544</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E367" s="2">
-        <v>82067</v>
+        <v>81477</v>
       </c>
       <c r="F367" s="3">
-        <v>46062</v>
+        <v>46029</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>9</v>
@@ -9969,19 +9981,19 @@
         <v>2511</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C368" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D368" s="3">
-        <v>46065.6300915625</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E368" s="2">
-        <v>82190</v>
+        <v>81532</v>
       </c>
       <c r="F368" s="3">
-        <v>46066</v>
+        <v>46030</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>9</v>
@@ -9995,19 +10007,19 @@
         <v>2511</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C369" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D369" s="3">
-        <v>46065.6300915625</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E369" s="2">
-        <v>82197</v>
+        <v>81534</v>
       </c>
       <c r="F369" s="3">
-        <v>46066</v>
+        <v>46030</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>9</v>
@@ -10021,19 +10033,19 @@
         <v>2511</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C370" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D370" s="3">
-        <v>46077.5084780324</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E370" s="2">
-        <v>82270</v>
+        <v>81535</v>
       </c>
       <c r="F370" s="3">
-        <v>46077</v>
+        <v>46030</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>9</v>
@@ -10047,19 +10059,19 @@
         <v>2511</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C371" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D371" s="3">
-        <v>46077.721037037</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E371" s="2">
-        <v>82285</v>
+        <v>81550</v>
       </c>
       <c r="F371" s="3">
-        <v>46077</v>
+        <v>46030</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>9</v>
@@ -10073,19 +10085,19 @@
         <v>2511</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C372" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D372" s="3">
-        <v>46083.6694849421</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E372" s="2">
-        <v>82417</v>
+        <v>81553</v>
       </c>
       <c r="F372" s="3">
-        <v>46084</v>
+        <v>46030</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>9</v>
@@ -10099,19 +10111,19 @@
         <v>2511</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C373" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D373" s="3">
-        <v>46085.7157723032</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E373" s="2">
-        <v>82457</v>
+        <v>81554</v>
       </c>
       <c r="F373" s="3">
-        <v>46086</v>
+        <v>46030</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>9</v>
@@ -10122,22 +10134,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="374">
       <c r="A374" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C374" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D374" s="3">
-        <v>46029.381258831</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E374" s="2">
-        <v>81484</v>
+        <v>81557</v>
       </c>
       <c r="F374" s="3">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>9</v>
@@ -10148,22 +10160,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="375">
       <c r="A375" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C375" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D375" s="3">
-        <v>46029.381258831</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E375" s="2">
-        <v>81486</v>
+        <v>81588</v>
       </c>
       <c r="F375" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>9</v>
@@ -10174,22 +10186,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="376">
       <c r="A376" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C376" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D376" s="3">
-        <v>46029.381258831</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E376" s="2">
-        <v>81487</v>
+        <v>81692</v>
       </c>
       <c r="F376" s="3">
-        <v>46029</v>
+        <v>46038</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>9</v>
@@ -10200,22 +10212,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="377">
       <c r="A377" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C377" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D377" s="3">
-        <v>46036.4048894097</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E377" s="2">
-        <v>81613</v>
+        <v>81786</v>
       </c>
       <c r="F377" s="3">
-        <v>46036</v>
+        <v>46044</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>9</v>
@@ -10226,22 +10238,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="378">
       <c r="A378" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C378" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D378" s="3">
-        <v>46036.4048894097</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E378" s="2">
-        <v>81614</v>
+        <v>81844</v>
       </c>
       <c r="F378" s="3">
-        <v>46036</v>
+        <v>46045</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>9</v>
@@ -10252,22 +10264,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="379">
       <c r="A379" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C379" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D379" s="3">
-        <v>46036.4048894097</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E379" s="2">
-        <v>81622</v>
+        <v>82065</v>
       </c>
       <c r="F379" s="3">
-        <v>46036</v>
+        <v>46062</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>9</v>
@@ -10278,22 +10290,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="380">
       <c r="A380" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C380" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D380" s="3">
-        <v>46036.4048894097</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E380" s="2">
-        <v>81632</v>
+        <v>82066</v>
       </c>
       <c r="F380" s="3">
-        <v>46036</v>
+        <v>46062</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>9</v>
@@ -10304,22 +10316,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="381">
       <c r="A381" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C381" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D381" s="3">
-        <v>46036.4048894097</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E381" s="2">
-        <v>81648</v>
+        <v>82067</v>
       </c>
       <c r="F381" s="3">
-        <v>46037</v>
+        <v>46062</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>9</v>
@@ -10330,22 +10342,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="382">
       <c r="A382" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C382" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D382" s="3">
-        <v>46036.4048894097</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E382" s="2">
-        <v>81664</v>
+        <v>82190</v>
       </c>
       <c r="F382" s="3">
-        <v>46037</v>
+        <v>46066</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>9</v>
@@ -10356,22 +10368,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="383">
       <c r="A383" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C383" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D383" s="3">
-        <v>46045.4188638426</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E383" s="2">
-        <v>81815</v>
+        <v>82197</v>
       </c>
       <c r="F383" s="3">
-        <v>46045</v>
+        <v>46066</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>9</v>
@@ -10382,22 +10394,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="384">
       <c r="A384" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C384" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D384" s="3">
-        <v>46045.4188638426</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E384" s="2">
-        <v>81816</v>
+        <v>82270</v>
       </c>
       <c r="F384" s="3">
-        <v>46045</v>
+        <v>46077</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>9</v>
@@ -10408,22 +10420,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="385">
       <c r="A385" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C385" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D385" s="3">
-        <v>46045.4188638426</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E385" s="2">
-        <v>81838</v>
+        <v>82285</v>
       </c>
       <c r="F385" s="3">
-        <v>46045</v>
+        <v>46077</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>9</v>
@@ -10434,22 +10446,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="386">
       <c r="A386" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C386" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D386" s="3">
-        <v>46045.4188638426</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E386" s="2">
-        <v>81840</v>
+        <v>82417</v>
       </c>
       <c r="F386" s="3">
-        <v>46045</v>
+        <v>46084</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>9</v>
@@ -10460,22 +10472,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="387">
       <c r="A387" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B387" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C387" s="2">
         <v>27</v>
       </c>
-      <c r="C387" s="2">
-        <v>16</v>
-      </c>
       <c r="D387" s="3">
-        <v>46055.5991080671</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E387" s="2">
-        <v>81959</v>
+        <v>82457</v>
       </c>
       <c r="F387" s="3">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>9</v>
@@ -10489,19 +10501,19 @@
         <v>2512</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C388" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D388" s="3">
-        <v>46055.5991080671</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E388" s="2">
-        <v>81960</v>
+        <v>81484</v>
       </c>
       <c r="F388" s="3">
-        <v>46055</v>
+        <v>46029</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>9</v>
@@ -10515,19 +10527,19 @@
         <v>2512</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C389" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D389" s="3">
-        <v>46062.7151302546</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E389" s="2">
-        <v>82063</v>
+        <v>81486</v>
       </c>
       <c r="F389" s="3">
-        <v>46062</v>
+        <v>46029</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>9</v>
@@ -10541,19 +10553,19 @@
         <v>2512</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C390" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D390" s="3">
-        <v>46062.7151302546</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E390" s="2">
-        <v>82064</v>
+        <v>81487</v>
       </c>
       <c r="F390" s="3">
-        <v>46062</v>
+        <v>46029</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>9</v>
@@ -10567,19 +10579,19 @@
         <v>2512</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C391" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D391" s="3">
-        <v>46062.7151302546</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E391" s="2">
-        <v>82100</v>
+        <v>81613</v>
       </c>
       <c r="F391" s="3">
-        <v>46064</v>
+        <v>46036</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>9</v>
@@ -10593,19 +10605,19 @@
         <v>2512</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C392" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D392" s="3">
-        <v>46072.7410579977</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E392" s="2">
-        <v>82333</v>
+        <v>81614</v>
       </c>
       <c r="F392" s="3">
-        <v>46079</v>
+        <v>46036</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>9</v>
@@ -10619,19 +10631,19 @@
         <v>2512</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C393" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D393" s="3">
-        <v>46072.7410579977</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E393" s="2">
-        <v>82334</v>
+        <v>81622</v>
       </c>
       <c r="F393" s="3">
-        <v>46079</v>
+        <v>46036</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>9</v>
@@ -10645,19 +10657,19 @@
         <v>2512</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C394" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D394" s="3">
-        <v>46076.7259125116</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E394" s="2">
-        <v>82258</v>
+        <v>81632</v>
       </c>
       <c r="F394" s="3">
-        <v>46076</v>
+        <v>46036</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>9</v>
@@ -10671,19 +10683,19 @@
         <v>2512</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C395" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D395" s="3">
-        <v>46076.7259125116</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E395" s="2">
-        <v>82259</v>
+        <v>81648</v>
       </c>
       <c r="F395" s="3">
-        <v>46076</v>
+        <v>46037</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>9</v>
@@ -10697,19 +10709,19 @@
         <v>2512</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C396" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D396" s="3">
-        <v>46076.7259125116</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E396" s="2">
-        <v>82260</v>
+        <v>81664</v>
       </c>
       <c r="F396" s="3">
-        <v>46076</v>
+        <v>46037</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>9</v>
@@ -10723,19 +10735,19 @@
         <v>2512</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C397" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D397" s="3">
-        <v>46076.7259125116</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E397" s="2">
-        <v>82274</v>
+        <v>81815</v>
       </c>
       <c r="F397" s="3">
-        <v>46077</v>
+        <v>46045</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>9</v>
@@ -10749,19 +10761,19 @@
         <v>2512</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C398" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D398" s="3">
-        <v>46084.5055666204</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E398" s="2">
-        <v>82409</v>
+        <v>81816</v>
       </c>
       <c r="F398" s="3">
-        <v>46084</v>
+        <v>46045</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>9</v>
@@ -10772,22 +10784,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="399">
       <c r="A399" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C399" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D399" s="3">
-        <v>46035.4386099769</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E399" s="2">
-        <v>81608</v>
+        <v>81838</v>
       </c>
       <c r="F399" s="3">
-        <v>46035</v>
+        <v>46045</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>9</v>
@@ -10798,22 +10810,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="400">
       <c r="A400" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C400" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D400" s="3">
-        <v>46035.4386099769</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E400" s="2">
-        <v>81609</v>
+        <v>81840</v>
       </c>
       <c r="F400" s="3">
-        <v>46035</v>
+        <v>46045</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>9</v>
@@ -10824,22 +10836,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="401">
       <c r="A401" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C401" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D401" s="3">
-        <v>46035.4386099769</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E401" s="2">
-        <v>81610</v>
+        <v>81959</v>
       </c>
       <c r="F401" s="3">
-        <v>46035</v>
+        <v>46055</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10850,22 +10862,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="402">
       <c r="A402" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C402" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D402" s="3">
-        <v>46035.4386099769</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E402" s="2">
-        <v>81611</v>
+        <v>81960</v>
       </c>
       <c r="F402" s="3">
-        <v>46035</v>
+        <v>46055</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10876,22 +10888,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="403">
       <c r="A403" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C403" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D403" s="3">
-        <v>46035.4386099769</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E403" s="2">
-        <v>81612</v>
+        <v>82063</v>
       </c>
       <c r="F403" s="3">
-        <v>46035</v>
+        <v>46062</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10902,22 +10914,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="404">
       <c r="A404" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C404" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D404" s="3">
-        <v>46036.6342081481</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E404" s="2">
-        <v>81652</v>
+        <v>82064</v>
       </c>
       <c r="F404" s="3">
-        <v>46037</v>
+        <v>46062</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>9</v>
@@ -10928,22 +10940,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="405">
       <c r="A405" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C405" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D405" s="3">
-        <v>46036.6342081481</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E405" s="2">
-        <v>81659</v>
+        <v>82100</v>
       </c>
       <c r="F405" s="3">
-        <v>46037</v>
+        <v>46064</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>9</v>
@@ -10954,22 +10966,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="406">
       <c r="A406" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C406" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D406" s="3">
-        <v>46048.6509980093</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E406" s="2">
-        <v>81853</v>
+        <v>82333</v>
       </c>
       <c r="F406" s="3">
-        <v>46048</v>
+        <v>46079</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>9</v>
@@ -10980,22 +10992,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="407">
       <c r="A407" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C407" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D407" s="3">
-        <v>46048.6509980093</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E407" s="2">
-        <v>81869</v>
+        <v>82334</v>
       </c>
       <c r="F407" s="3">
-        <v>46049</v>
+        <v>46079</v>
       </c>
       <c r="G407" s="1" t="s">
         <v>9</v>
@@ -11006,22 +11018,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="408">
       <c r="A408" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C408" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D408" s="3">
-        <v>46048.6509980093</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E408" s="2">
-        <v>81890</v>
+        <v>82258</v>
       </c>
       <c r="F408" s="3">
-        <v>46050</v>
+        <v>46076</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>9</v>
@@ -11032,22 +11044,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="409">
       <c r="A409" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C409" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D409" s="3">
-        <v>46049.4871256134</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E409" s="2">
-        <v>81875</v>
+        <v>82259</v>
       </c>
       <c r="F409" s="3">
-        <v>46049</v>
+        <v>46076</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>9</v>
@@ -11058,22 +11070,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="410">
       <c r="A410" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C410" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D410" s="3">
-        <v>46049.4871256134</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E410" s="2">
-        <v>81881</v>
+        <v>82260</v>
       </c>
       <c r="F410" s="3">
-        <v>46050</v>
+        <v>46076</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11084,22 +11096,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="411">
       <c r="A411" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C411" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D411" s="3">
-        <v>46056.7073643981</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E411" s="2">
-        <v>82015</v>
+        <v>82274</v>
       </c>
       <c r="F411" s="3">
-        <v>46058</v>
+        <v>46077</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>9</v>
@@ -11110,22 +11122,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="412">
       <c r="A412" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C412" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D412" s="3">
-        <v>46056.7073643981</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E412" s="2">
-        <v>82017</v>
+        <v>82409</v>
       </c>
       <c r="F412" s="3">
-        <v>46058</v>
+        <v>46084</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11136,80 +11148,80 @@
     </row>
     <row ht="12.75" customHeight="1" r="413">
       <c r="A413" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C413" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D413" s="3">
-        <v>46056.7073643981</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E413" s="2">
-        <v>82020</v>
+        <v>82581</v>
       </c>
       <c r="F413" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="G413" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H413" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="414">
       <c r="A414" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C414" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D414" s="3">
-        <v>46056.7073643981</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E414" s="2">
-        <v>82023</v>
+        <v>82582</v>
       </c>
       <c r="F414" s="3">
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H414" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="415">
       <c r="A415" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C415" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D415" s="3">
-        <v>46056.7073643981</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E415" s="2">
-        <v>82061</v>
+        <v>82583</v>
       </c>
       <c r="F415" s="3">
-        <v>46062</v>
+        <v>46093</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H415" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="416">
@@ -11217,19 +11229,19 @@
         <v>2514</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C416" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D416" s="3">
-        <v>46056.7073643981</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E416" s="2">
-        <v>82081</v>
+        <v>81608</v>
       </c>
       <c r="F416" s="3">
-        <v>46063</v>
+        <v>46035</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>9</v>
@@ -11243,19 +11255,19 @@
         <v>2514</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C417" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D417" s="3">
-        <v>46056.7073643981</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E417" s="2">
-        <v>82095</v>
+        <v>81609</v>
       </c>
       <c r="F417" s="3">
-        <v>46064</v>
+        <v>46035</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>9</v>
@@ -11269,19 +11281,19 @@
         <v>2514</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C418" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D418" s="3">
-        <v>46062.7129743866</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E418" s="2">
-        <v>82081</v>
+        <v>81610</v>
       </c>
       <c r="F418" s="3">
-        <v>46063</v>
+        <v>46035</v>
       </c>
       <c r="G418" s="1" t="s">
         <v>9</v>
@@ -11295,19 +11307,19 @@
         <v>2514</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C419" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D419" s="3">
-        <v>46062.7129743866</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E419" s="2">
-        <v>82107</v>
+        <v>81611</v>
       </c>
       <c r="F419" s="3">
-        <v>46064</v>
+        <v>46035</v>
       </c>
       <c r="G419" s="1" t="s">
         <v>9</v>
@@ -11321,19 +11333,19 @@
         <v>2514</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C420" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D420" s="3">
-        <v>46062.7129743866</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E420" s="2">
-        <v>82112</v>
+        <v>81612</v>
       </c>
       <c r="F420" s="3">
-        <v>46064</v>
+        <v>46035</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>9</v>
@@ -11347,19 +11359,19 @@
         <v>2514</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C421" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D421" s="3">
-        <v>46062.7129743866</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E421" s="2">
-        <v>82113</v>
+        <v>81652</v>
       </c>
       <c r="F421" s="3">
-        <v>46064</v>
+        <v>46037</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>9</v>
@@ -11373,19 +11385,19 @@
         <v>2514</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C422" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D422" s="3">
-        <v>46062.7129743866</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E422" s="2">
-        <v>82123</v>
+        <v>81659</v>
       </c>
       <c r="F422" s="3">
-        <v>46065</v>
+        <v>46037</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>9</v>
@@ -11399,19 +11411,19 @@
         <v>2514</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C423" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D423" s="3">
-        <v>46063.5787047801</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E423" s="2">
-        <v>82095</v>
+        <v>81853</v>
       </c>
       <c r="F423" s="3">
-        <v>46064</v>
+        <v>46048</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>9</v>
@@ -11425,19 +11437,19 @@
         <v>2514</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C424" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D424" s="3">
-        <v>46063.5787047801</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E424" s="2">
-        <v>82106</v>
+        <v>81869</v>
       </c>
       <c r="F424" s="3">
-        <v>46064</v>
+        <v>46049</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>9</v>
@@ -11451,19 +11463,19 @@
         <v>2514</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C425" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D425" s="3">
-        <v>46063.5787047801</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E425" s="2">
-        <v>82107</v>
+        <v>81890</v>
       </c>
       <c r="F425" s="3">
-        <v>46064</v>
+        <v>46050</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>9</v>
@@ -11477,19 +11489,19 @@
         <v>2514</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C426" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D426" s="3">
-        <v>46063.5787047801</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E426" s="2">
-        <v>82109</v>
+        <v>81875</v>
       </c>
       <c r="F426" s="3">
-        <v>46064</v>
+        <v>46049</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>9</v>
@@ -11503,19 +11515,19 @@
         <v>2514</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C427" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D427" s="3">
-        <v>46063.5787047801</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E427" s="2">
-        <v>82110</v>
+        <v>81881</v>
       </c>
       <c r="F427" s="3">
-        <v>46064</v>
+        <v>46050</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11529,19 +11541,19 @@
         <v>2514</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C428" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D428" s="3">
-        <v>46063.5787047801</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E428" s="2">
-        <v>82139</v>
+        <v>82015</v>
       </c>
       <c r="F428" s="3">
-        <v>46065</v>
+        <v>46058</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>9</v>
@@ -11555,19 +11567,19 @@
         <v>2514</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C429" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D429" s="3">
-        <v>46080.4604712616</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E429" s="2">
-        <v>82365</v>
+        <v>82017</v>
       </c>
       <c r="F429" s="3">
-        <v>46080</v>
+        <v>46058</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>9</v>
@@ -11581,19 +11593,19 @@
         <v>2514</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C430" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D430" s="3">
-        <v>46080.4604712616</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E430" s="2">
-        <v>82366</v>
+        <v>82020</v>
       </c>
       <c r="F430" s="3">
-        <v>46080</v>
+        <v>46058</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>9</v>
@@ -11607,19 +11619,19 @@
         <v>2514</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C431" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D431" s="3">
-        <v>46080.4604712616</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E431" s="2">
-        <v>82371</v>
+        <v>82023</v>
       </c>
       <c r="F431" s="3">
-        <v>46080</v>
+        <v>46058</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>9</v>
@@ -11633,19 +11645,19 @@
         <v>2514</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C432" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D432" s="3">
-        <v>46080.4604712616</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E432" s="2">
-        <v>82383</v>
+        <v>82061</v>
       </c>
       <c r="F432" s="3">
-        <v>46083</v>
+        <v>46062</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11659,19 +11671,19 @@
         <v>2514</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C433" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D433" s="3">
-        <v>46080.4604712616</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E433" s="2">
-        <v>82384</v>
+        <v>82081</v>
       </c>
       <c r="F433" s="3">
-        <v>46083</v>
+        <v>46063</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11682,48 +11694,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="434">
       <c r="A434" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C434" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D434" s="3">
-        <v>46029.4149454282</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E434" s="2">
-        <v>81592</v>
+        <v>82095</v>
       </c>
       <c r="F434" s="3">
-        <v>46031</v>
+        <v>46064</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="435">
       <c r="A435" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C435" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D435" s="3">
-        <v>46029.4149454282</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E435" s="2">
-        <v>81593</v>
+        <v>82081</v>
       </c>
       <c r="F435" s="3">
-        <v>46031</v>
+        <v>46063</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>9</v>
@@ -11734,22 +11746,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="436">
       <c r="A436" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C436" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D436" s="3">
-        <v>46038.6827563889</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E436" s="2">
-        <v>81697</v>
+        <v>82107</v>
       </c>
       <c r="F436" s="3">
-        <v>46038</v>
+        <v>46064</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>9</v>
@@ -11760,48 +11772,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="437">
       <c r="A437" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C437" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D437" s="3">
-        <v>46038.6827563889</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E437" s="2">
-        <v>81735</v>
+        <v>82112</v>
       </c>
       <c r="F437" s="3">
-        <v>46041</v>
+        <v>46064</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H437" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="438">
       <c r="A438" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C438" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D438" s="3">
-        <v>46045.4532476157</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E438" s="2">
-        <v>81823</v>
+        <v>82113</v>
       </c>
       <c r="F438" s="3">
-        <v>46045</v>
+        <v>46064</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11812,22 +11824,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="439">
       <c r="A439" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C439" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D439" s="3">
-        <v>46031.4724550926</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E439" s="2">
-        <v>81572</v>
+        <v>82123</v>
       </c>
       <c r="F439" s="3">
-        <v>46031</v>
+        <v>46065</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11838,22 +11850,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="440">
       <c r="A440" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C440" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D440" s="3">
-        <v>46031.4724550926</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E440" s="2">
-        <v>81573</v>
+        <v>82095</v>
       </c>
       <c r="F440" s="3">
-        <v>46031</v>
+        <v>46064</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>9</v>
@@ -11864,22 +11876,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="441">
       <c r="A441" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C441" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D441" s="3">
-        <v>46031.4724550926</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E441" s="2">
-        <v>81579</v>
+        <v>82106</v>
       </c>
       <c r="F441" s="3">
-        <v>46031</v>
+        <v>46064</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11890,22 +11902,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="442">
       <c r="A442" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C442" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D442" s="3">
-        <v>46031.4724550926</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E442" s="2">
-        <v>81580</v>
+        <v>82107</v>
       </c>
       <c r="F442" s="3">
-        <v>46031</v>
+        <v>46064</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11916,22 +11928,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="443">
       <c r="A443" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C443" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D443" s="3">
-        <v>46031.4724550926</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E443" s="2">
-        <v>81581</v>
+        <v>82109</v>
       </c>
       <c r="F443" s="3">
-        <v>46031</v>
+        <v>46064</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11942,22 +11954,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="444">
       <c r="A444" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C444" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D444" s="3">
-        <v>46031.4724550926</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E444" s="2">
-        <v>81582</v>
+        <v>82110</v>
       </c>
       <c r="F444" s="3">
-        <v>46031</v>
+        <v>46064</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11968,22 +11980,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="445">
       <c r="A445" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C445" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D445" s="3">
-        <v>46031.4724550926</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E445" s="2">
-        <v>81583</v>
+        <v>82139</v>
       </c>
       <c r="F445" s="3">
-        <v>46031</v>
+        <v>46065</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>9</v>
@@ -11994,22 +12006,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="446">
       <c r="A446" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C446" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D446" s="3">
-        <v>46037.6443999306</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E446" s="2">
-        <v>81667</v>
+        <v>82365</v>
       </c>
       <c r="F446" s="3">
-        <v>46037</v>
+        <v>46080</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>9</v>
@@ -12020,22 +12032,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="447">
       <c r="A447" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C447" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D447" s="3">
-        <v>46037.6443999306</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E447" s="2">
-        <v>81668</v>
+        <v>82366</v>
       </c>
       <c r="F447" s="3">
-        <v>46037</v>
+        <v>46080</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>9</v>
@@ -12046,22 +12058,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="448">
       <c r="A448" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C448" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D448" s="3">
-        <v>46037.6443999306</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E448" s="2">
-        <v>81674</v>
+        <v>82371</v>
       </c>
       <c r="F448" s="3">
-        <v>46038</v>
+        <v>46080</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12072,22 +12084,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="449">
       <c r="A449" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C449" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D449" s="3">
-        <v>46037.6443999306</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E449" s="2">
-        <v>81675</v>
+        <v>82383</v>
       </c>
       <c r="F449" s="3">
-        <v>46038</v>
+        <v>46083</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12098,22 +12110,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="450">
       <c r="A450" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C450" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D450" s="3">
-        <v>46037.6443999306</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E450" s="2">
-        <v>81677</v>
+        <v>82384</v>
       </c>
       <c r="F450" s="3">
-        <v>46038</v>
+        <v>46083</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12124,48 +12136,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="451">
       <c r="A451" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C451" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D451" s="3">
-        <v>46041.6133887269</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E451" s="2">
-        <v>81739</v>
+        <v>81592</v>
       </c>
       <c r="F451" s="3">
-        <v>46041</v>
+        <v>46031</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="452">
       <c r="A452" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C452" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D452" s="3">
-        <v>46041.6133887269</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E452" s="2">
-        <v>81741</v>
+        <v>81593</v>
       </c>
       <c r="F452" s="3">
-        <v>46041</v>
+        <v>46031</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12176,22 +12188,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="453">
       <c r="A453" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C453" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D453" s="3">
-        <v>46048.7298086806</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E453" s="2">
-        <v>81854</v>
+        <v>81697</v>
       </c>
       <c r="F453" s="3">
-        <v>46048</v>
+        <v>46038</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>9</v>
@@ -12202,48 +12214,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="454">
       <c r="A454" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C454" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D454" s="3">
-        <v>46048.7298086806</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E454" s="2">
-        <v>81855</v>
+        <v>81735</v>
       </c>
       <c r="F454" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="455">
       <c r="A455" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C455" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D455" s="3">
-        <v>46048.7298086806</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E455" s="2">
-        <v>81858</v>
+        <v>81823</v>
       </c>
       <c r="F455" s="3">
-        <v>46049</v>
+        <v>46045</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>9</v>
@@ -12257,19 +12269,19 @@
         <v>2516</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C456" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D456" s="3">
-        <v>46048.7298086806</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E456" s="2">
-        <v>81859</v>
+        <v>81572</v>
       </c>
       <c r="F456" s="3">
-        <v>46049</v>
+        <v>46031</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12283,19 +12295,19 @@
         <v>2516</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C457" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D457" s="3">
-        <v>46048.7298086806</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E457" s="2">
-        <v>81862</v>
+        <v>81573</v>
       </c>
       <c r="F457" s="3">
-        <v>46049</v>
+        <v>46031</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>9</v>
@@ -12309,19 +12321,19 @@
         <v>2516</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C458" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D458" s="3">
-        <v>46048.7298086806</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E458" s="2">
-        <v>81863</v>
+        <v>81579</v>
       </c>
       <c r="F458" s="3">
-        <v>46049</v>
+        <v>46031</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12335,19 +12347,19 @@
         <v>2516</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C459" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D459" s="3">
-        <v>46055.5924236111</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E459" s="2">
-        <v>81958</v>
+        <v>81580</v>
       </c>
       <c r="F459" s="3">
-        <v>46055</v>
+        <v>46031</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12361,19 +12373,19 @@
         <v>2516</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C460" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D460" s="3">
-        <v>46055.5924236111</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E460" s="2">
-        <v>81965</v>
+        <v>81581</v>
       </c>
       <c r="F460" s="3">
-        <v>46055</v>
+        <v>46031</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12387,19 +12399,19 @@
         <v>2516</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C461" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D461" s="3">
-        <v>46063.5923590625</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E461" s="2">
-        <v>82085</v>
+        <v>81582</v>
       </c>
       <c r="F461" s="3">
-        <v>46063</v>
+        <v>46031</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12413,19 +12425,19 @@
         <v>2516</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C462" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D462" s="3">
-        <v>46063.5923590625</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E462" s="2">
-        <v>82086</v>
+        <v>81583</v>
       </c>
       <c r="F462" s="3">
-        <v>46063</v>
+        <v>46031</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12439,19 +12451,19 @@
         <v>2516</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C463" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D463" s="3">
-        <v>46063.5923590625</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E463" s="2">
-        <v>82126</v>
+        <v>81667</v>
       </c>
       <c r="F463" s="3">
-        <v>46065</v>
+        <v>46037</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12465,19 +12477,19 @@
         <v>2516</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C464" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D464" s="3">
-        <v>46064.5127051505</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E464" s="2">
-        <v>82268</v>
+        <v>81668</v>
       </c>
       <c r="F464" s="3">
-        <v>46077</v>
+        <v>46037</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12491,19 +12503,19 @@
         <v>2516</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C465" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D465" s="3">
-        <v>46065.6275788773</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E465" s="2">
-        <v>82142</v>
+        <v>81674</v>
       </c>
       <c r="F465" s="3">
-        <v>46065</v>
+        <v>46038</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>9</v>
@@ -12517,19 +12529,19 @@
         <v>2516</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C466" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D466" s="3">
-        <v>46065.6275788773</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E466" s="2">
-        <v>82143</v>
+        <v>81675</v>
       </c>
       <c r="F466" s="3">
-        <v>46065</v>
+        <v>46038</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12543,19 +12555,19 @@
         <v>2516</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C467" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D467" s="3">
-        <v>46065.6275788773</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E467" s="2">
-        <v>82144</v>
+        <v>81677</v>
       </c>
       <c r="F467" s="3">
-        <v>46065</v>
+        <v>46038</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>9</v>
@@ -12569,19 +12581,19 @@
         <v>2516</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C468" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D468" s="3">
-        <v>46065.6275788773</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E468" s="2">
-        <v>82166</v>
+        <v>81739</v>
       </c>
       <c r="F468" s="3">
-        <v>46066</v>
+        <v>46041</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>9</v>
@@ -12595,19 +12607,19 @@
         <v>2516</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C469" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D469" s="3">
-        <v>46077.406463831</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E469" s="2">
-        <v>82262</v>
+        <v>81741</v>
       </c>
       <c r="F469" s="3">
-        <v>46077</v>
+        <v>46041</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>9</v>
@@ -12621,19 +12633,19 @@
         <v>2516</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C470" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D470" s="3">
-        <v>46077.406463831</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E470" s="2">
-        <v>82265</v>
+        <v>81854</v>
       </c>
       <c r="F470" s="3">
-        <v>46077</v>
+        <v>46048</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>9</v>
@@ -12647,19 +12659,19 @@
         <v>2516</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C471" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D471" s="3">
-        <v>46077.406463831</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E471" s="2">
-        <v>82281</v>
+        <v>81855</v>
       </c>
       <c r="F471" s="3">
-        <v>46077</v>
+        <v>46048</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>9</v>
@@ -12673,19 +12685,19 @@
         <v>2516</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C472" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D472" s="3">
-        <v>46077.406463831</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E472" s="2">
-        <v>82282</v>
+        <v>81858</v>
       </c>
       <c r="F472" s="3">
-        <v>46077</v>
+        <v>46049</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12699,19 +12711,19 @@
         <v>2516</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C473" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D473" s="3">
-        <v>46079.5782408912</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E473" s="2">
-        <v>82340</v>
+        <v>81859</v>
       </c>
       <c r="F473" s="3">
-        <v>46079</v>
+        <v>46049</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12725,19 +12737,19 @@
         <v>2516</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C474" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D474" s="3">
-        <v>46083.6671321991</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E474" s="2">
-        <v>82399</v>
+        <v>81862</v>
       </c>
       <c r="F474" s="3">
-        <v>46083</v>
+        <v>46049</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12751,19 +12763,19 @@
         <v>2516</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C475" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D475" s="3">
-        <v>46083.6671321991</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E475" s="2">
-        <v>82400</v>
+        <v>81863</v>
       </c>
       <c r="F475" s="3">
-        <v>46083</v>
+        <v>46049</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>9</v>
@@ -12777,19 +12789,19 @@
         <v>2516</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C476" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D476" s="3">
-        <v>46083.6671321991</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E476" s="2">
-        <v>82401</v>
+        <v>81958</v>
       </c>
       <c r="F476" s="3">
-        <v>46083</v>
+        <v>46055</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>9</v>
@@ -12803,19 +12815,19 @@
         <v>2516</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C477" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D477" s="3">
-        <v>46083.6671321991</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E477" s="2">
-        <v>82412</v>
+        <v>81965</v>
       </c>
       <c r="F477" s="3">
-        <v>46084</v>
+        <v>46055</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>9</v>
@@ -12829,19 +12841,19 @@
         <v>2516</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C478" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D478" s="3">
-        <v>46083.6671321991</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E478" s="2">
-        <v>82415</v>
+        <v>82085</v>
       </c>
       <c r="F478" s="3">
-        <v>46084</v>
+        <v>46063</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12852,22 +12864,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="479">
       <c r="A479" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C479" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D479" s="3">
-        <v>46078.6702738773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E479" s="2">
-        <v>82311</v>
+        <v>82086</v>
       </c>
       <c r="F479" s="3">
-        <v>46078</v>
+        <v>46063</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12878,22 +12890,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="480">
       <c r="A480" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C480" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D480" s="3">
-        <v>46078.6702738773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E480" s="2">
-        <v>82312</v>
+        <v>82126</v>
       </c>
       <c r="F480" s="3">
-        <v>46078</v>
+        <v>46065</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>9</v>
@@ -12904,22 +12916,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="481">
       <c r="A481" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C481" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D481" s="3">
-        <v>46078.6702738773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E481" s="2">
-        <v>82313</v>
+        <v>82268</v>
       </c>
       <c r="F481" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>9</v>
@@ -12930,22 +12942,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="482">
       <c r="A482" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C482" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D482" s="3">
-        <v>46078.6702738773</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E482" s="2">
-        <v>82314</v>
+        <v>82142</v>
       </c>
       <c r="F482" s="3">
-        <v>46078</v>
+        <v>46065</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12956,22 +12968,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="483">
       <c r="A483" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C483" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D483" s="3">
-        <v>46078.6702738773</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E483" s="2">
-        <v>82346</v>
+        <v>82143</v>
       </c>
       <c r="F483" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>9</v>
@@ -12982,22 +12994,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="484">
       <c r="A484" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C484" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D484" s="3">
-        <v>46078.6702738773</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E484" s="2">
-        <v>82361</v>
+        <v>82144</v>
       </c>
       <c r="F484" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G484" s="1" t="s">
         <v>9</v>
@@ -13008,22 +13020,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="485">
       <c r="A485" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C485" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D485" s="3">
-        <v>46078.6702738773</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E485" s="2">
-        <v>82385</v>
+        <v>82166</v>
       </c>
       <c r="F485" s="3">
-        <v>46083</v>
+        <v>46066</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>9</v>
@@ -13034,22 +13046,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="486">
       <c r="A486" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C486" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D486" s="3">
-        <v>46078.6702738773</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E486" s="2">
-        <v>82391</v>
+        <v>82262</v>
       </c>
       <c r="F486" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>9</v>
@@ -13060,22 +13072,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="487">
       <c r="A487" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C487" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D487" s="3">
-        <v>46078.6702738773</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E487" s="2">
-        <v>82392</v>
+        <v>82265</v>
       </c>
       <c r="F487" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>9</v>
@@ -13086,22 +13098,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="488">
       <c r="A488" s="2">
-        <v>9991</v>
+        <v>2516</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C488" s="2">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="D488" s="3">
-        <v>46029.4632696412</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E488" s="2">
-        <v>81495</v>
+        <v>82281</v>
       </c>
       <c r="F488" s="3">
-        <v>46029</v>
+        <v>46077</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>9</v>
@@ -13112,27 +13124,521 @@
     </row>
     <row ht="12.75" customHeight="1" r="489">
       <c r="A489" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C489" s="2">
+        <v>13</v>
+      </c>
+      <c r="D489" s="3">
+        <v>46077.406463831</v>
+      </c>
+      <c r="E489" s="2">
+        <v>82282</v>
+      </c>
+      <c r="F489" s="3">
+        <v>46077</v>
+      </c>
+      <c r="G489" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H489" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="490">
+      <c r="A490" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C490" s="2">
+        <v>14</v>
+      </c>
+      <c r="D490" s="3">
+        <v>46079.5782408912</v>
+      </c>
+      <c r="E490" s="2">
+        <v>82340</v>
+      </c>
+      <c r="F490" s="3">
+        <v>46079</v>
+      </c>
+      <c r="G490" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H490" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="491">
+      <c r="A491" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C491" s="2">
+        <v>15</v>
+      </c>
+      <c r="D491" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="E491" s="2">
+        <v>82399</v>
+      </c>
+      <c r="F491" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G491" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H491" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="492">
+      <c r="A492" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C492" s="2">
+        <v>15</v>
+      </c>
+      <c r="D492" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="E492" s="2">
+        <v>82400</v>
+      </c>
+      <c r="F492" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G492" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H492" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="493">
+      <c r="A493" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C493" s="2">
+        <v>15</v>
+      </c>
+      <c r="D493" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="E493" s="2">
+        <v>82401</v>
+      </c>
+      <c r="F493" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G493" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H493" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="494">
+      <c r="A494" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C494" s="2">
+        <v>15</v>
+      </c>
+      <c r="D494" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="E494" s="2">
+        <v>82412</v>
+      </c>
+      <c r="F494" s="3">
+        <v>46084</v>
+      </c>
+      <c r="G494" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H494" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="495">
+      <c r="A495" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C495" s="2">
+        <v>15</v>
+      </c>
+      <c r="D495" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="E495" s="2">
+        <v>82415</v>
+      </c>
+      <c r="F495" s="3">
+        <v>46084</v>
+      </c>
+      <c r="G495" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H495" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="496">
+      <c r="A496" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C496" s="2">
+        <v>16</v>
+      </c>
+      <c r="D496" s="3">
+        <v>46086.6312882639</v>
+      </c>
+      <c r="E496" s="2">
+        <v>82571</v>
+      </c>
+      <c r="F496" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G496" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H496" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="497">
+      <c r="A497" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C497" s="2">
+        <v>16</v>
+      </c>
+      <c r="D497" s="3">
+        <v>46086.6312882639</v>
+      </c>
+      <c r="E497" s="2">
+        <v>82572</v>
+      </c>
+      <c r="F497" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G497" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H497" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="498">
+      <c r="A498" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C498" s="2">
+        <v>1</v>
+      </c>
+      <c r="D498" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E498" s="2">
+        <v>82311</v>
+      </c>
+      <c r="F498" s="3">
+        <v>46078</v>
+      </c>
+      <c r="G498" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H498" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="499">
+      <c r="A499" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C499" s="2">
+        <v>1</v>
+      </c>
+      <c r="D499" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E499" s="2">
+        <v>82312</v>
+      </c>
+      <c r="F499" s="3">
+        <v>46078</v>
+      </c>
+      <c r="G499" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H499" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="500">
+      <c r="A500" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C500" s="2">
+        <v>1</v>
+      </c>
+      <c r="D500" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E500" s="2">
+        <v>82313</v>
+      </c>
+      <c r="F500" s="3">
+        <v>46078</v>
+      </c>
+      <c r="G500" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H500" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="501">
+      <c r="A501" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C501" s="2">
+        <v>1</v>
+      </c>
+      <c r="D501" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E501" s="2">
+        <v>82314</v>
+      </c>
+      <c r="F501" s="3">
+        <v>46078</v>
+      </c>
+      <c r="G501" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H501" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="502">
+      <c r="A502" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C502" s="2">
+        <v>1</v>
+      </c>
+      <c r="D502" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E502" s="2">
+        <v>82346</v>
+      </c>
+      <c r="F502" s="3">
+        <v>46080</v>
+      </c>
+      <c r="G502" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H502" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="503">
+      <c r="A503" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C503" s="2">
+        <v>1</v>
+      </c>
+      <c r="D503" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E503" s="2">
+        <v>82361</v>
+      </c>
+      <c r="F503" s="3">
+        <v>46080</v>
+      </c>
+      <c r="G503" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H503" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="504">
+      <c r="A504" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C504" s="2">
+        <v>1</v>
+      </c>
+      <c r="D504" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E504" s="2">
+        <v>82385</v>
+      </c>
+      <c r="F504" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G504" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H504" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="505">
+      <c r="A505" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C505" s="2">
+        <v>1</v>
+      </c>
+      <c r="D505" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E505" s="2">
+        <v>82391</v>
+      </c>
+      <c r="F505" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G505" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H505" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="506">
+      <c r="A506" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C506" s="2">
+        <v>1</v>
+      </c>
+      <c r="D506" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E506" s="2">
+        <v>82392</v>
+      </c>
+      <c r="F506" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G506" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H506" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="507">
+      <c r="A507" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C507" s="2">
+        <v>62</v>
+      </c>
+      <c r="D507" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E507" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F507" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G507" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H507" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="508">
+      <c r="A508" s="2">
         <v>9992</v>
       </c>
-      <c r="B489" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C489" s="2">
+      <c r="B508" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C508" s="2">
         <v>390</v>
       </c>
-      <c r="D489" s="3">
+      <c r="D508" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E489" s="2">
+      <c r="E508" s="2">
         <v>81684</v>
       </c>
-      <c r="F489" s="3">
+      <c r="F508" s="3">
         <v>46038</v>
       </c>
-      <c r="G489" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H489" s="1" t="s">
+      <c r="G508" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H508" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -4250,10 +4250,10 @@
         <v>46094</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="148">

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -1806,10 +1806,10 @@
         <v>46097</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="54">
@@ -1826,7 +1826,7 @@
         <v>46097.447005</v>
       </c>
       <c r="E54" s="2">
-        <v>82651</v>
+        <v>82652</v>
       </c>
       <c r="F54" s="3">
         <v>46097</v>
@@ -1852,16 +1852,16 @@
         <v>46097.447005</v>
       </c>
       <c r="E55" s="2">
-        <v>82652</v>
+        <v>82662</v>
       </c>
       <c r="F55" s="3">
         <v>46097</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="56">
@@ -5550,10 +5550,10 @@
         <v>46097</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="198">
@@ -5570,16 +5570,16 @@
         <v>46097.4509044907</v>
       </c>
       <c r="E198" s="2">
-        <v>82655</v>
+        <v>82660</v>
       </c>
       <c r="F198" s="3">
         <v>46097</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="199">
@@ -5596,16 +5596,16 @@
         <v>46097.4509044907</v>
       </c>
       <c r="E199" s="2">
-        <v>82656</v>
+        <v>82661</v>
       </c>
       <c r="F199" s="3">
         <v>46097</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="200">
@@ -13792,10 +13792,10 @@
         <v>46097</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="515">

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -47,12 +47,6 @@
     <t>Confirmado c/ Fornecedor</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Não Concluídos</t>
-  </si>
-  <si>
     <t>LUIZ ROGÉRIO BERTO</t>
   </si>
   <si>
@@ -72,6 +66,12 @@
   </si>
   <si>
     <t>MARIA BELTRÃO SALDANHA COELHO</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Não Concluídos</t>
   </si>
   <si>
     <t>JOÃO CARLOS BEHISNELIAN</t>
@@ -420,7 +420,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H525"/>
+  <dimension ref="A1:H531"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -1832,10 +1832,10 @@
         <v>46097</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="55">
@@ -1866,22 +1866,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="56">
       <c r="A56" s="2">
-        <v>2303</v>
+        <v>2212</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C56" s="2">
-        <v>75</v>
+        <v>285</v>
       </c>
       <c r="D56" s="3">
-        <v>46091.4108549653</v>
+        <v>46097.447005</v>
       </c>
       <c r="E56" s="2">
-        <v>82503</v>
+        <v>82663</v>
       </c>
       <c r="F56" s="3">
-        <v>46091</v>
+        <v>46097</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>9</v>
@@ -1892,22 +1892,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="57">
       <c r="A57" s="2">
-        <v>2303</v>
+        <v>2212</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C57" s="2">
-        <v>75</v>
+        <v>285</v>
       </c>
       <c r="D57" s="3">
-        <v>46091.4108549653</v>
+        <v>46097.447005</v>
       </c>
       <c r="E57" s="2">
-        <v>82504</v>
+        <v>82669</v>
       </c>
       <c r="F57" s="3">
-        <v>46091</v>
+        <v>46097</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>9</v>
@@ -1918,22 +1918,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="58">
       <c r="A58" s="2">
-        <v>2316</v>
+        <v>2303</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C58" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D58" s="3">
-        <v>46030.4693811574</v>
+        <v>46091.4108549653</v>
       </c>
       <c r="E58" s="2">
-        <v>81541</v>
+        <v>82503</v>
       </c>
       <c r="F58" s="3">
-        <v>46030</v>
+        <v>46091</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>9</v>
@@ -1944,28 +1944,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="59">
       <c r="A59" s="2">
-        <v>2316</v>
+        <v>2303</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C59" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D59" s="3">
-        <v>46030.4693811574</v>
+        <v>46091.4108549653</v>
       </c>
       <c r="E59" s="2">
-        <v>81552</v>
+        <v>82504</v>
       </c>
       <c r="F59" s="3">
-        <v>46030</v>
+        <v>46091</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="60">
@@ -1973,19 +1973,19 @@
         <v>2316</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C60" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D60" s="3">
-        <v>46031.4710430208</v>
+        <v>46030.4693811574</v>
       </c>
       <c r="E60" s="2">
-        <v>81570</v>
+        <v>81541</v>
       </c>
       <c r="F60" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>9</v>
@@ -1999,25 +1999,25 @@
         <v>2316</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="2">
+        <v>84</v>
+      </c>
+      <c r="D61" s="3">
+        <v>46030.4693811574</v>
+      </c>
+      <c r="E61" s="2">
+        <v>81552</v>
+      </c>
+      <c r="F61" s="3">
+        <v>46030</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C61" s="2">
-        <v>85</v>
-      </c>
-      <c r="D61" s="3">
-        <v>46031.4710430208</v>
-      </c>
-      <c r="E61" s="2">
-        <v>81571</v>
-      </c>
-      <c r="F61" s="3">
-        <v>46031</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="62">
@@ -2025,7 +2025,7 @@
         <v>2316</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C62" s="2">
         <v>85</v>
@@ -2034,7 +2034,7 @@
         <v>46031.4710430208</v>
       </c>
       <c r="E62" s="2">
-        <v>81576</v>
+        <v>81570</v>
       </c>
       <c r="F62" s="3">
         <v>46031</v>
@@ -2051,19 +2051,19 @@
         <v>2316</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C63" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D63" s="3">
-        <v>46037.4243290856</v>
+        <v>46031.4710430208</v>
       </c>
       <c r="E63" s="2">
-        <v>81660</v>
+        <v>81571</v>
       </c>
       <c r="F63" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>9</v>
@@ -2077,19 +2077,19 @@
         <v>2316</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C64" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D64" s="3">
-        <v>46065.748806412</v>
+        <v>46031.4710430208</v>
       </c>
       <c r="E64" s="2">
-        <v>82177</v>
+        <v>81576</v>
       </c>
       <c r="F64" s="3">
-        <v>46066</v>
+        <v>46031</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>9</v>
@@ -2103,19 +2103,19 @@
         <v>2316</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C65" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D65" s="3">
-        <v>46065.748806412</v>
+        <v>46037.4243290856</v>
       </c>
       <c r="E65" s="2">
-        <v>82187</v>
+        <v>81660</v>
       </c>
       <c r="F65" s="3">
-        <v>46066</v>
+        <v>46037</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>9</v>
@@ -2126,22 +2126,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="66">
       <c r="A66" s="2">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C66" s="2">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D66" s="3">
-        <v>46029.3826292245</v>
+        <v>46065.748806412</v>
       </c>
       <c r="E66" s="2">
-        <v>81476</v>
+        <v>82177</v>
       </c>
       <c r="F66" s="3">
-        <v>46029</v>
+        <v>46066</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>9</v>
@@ -2152,22 +2152,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="67">
       <c r="A67" s="2">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C67" s="2">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D67" s="3">
-        <v>46029.3826292245</v>
+        <v>46065.748806412</v>
       </c>
       <c r="E67" s="2">
-        <v>81483</v>
+        <v>82187</v>
       </c>
       <c r="F67" s="3">
-        <v>46029</v>
+        <v>46066</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>9</v>
@@ -2181,7 +2181,7 @@
         <v>2317</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C68" s="2">
         <v>64</v>
@@ -2190,7 +2190,7 @@
         <v>46029.3826292245</v>
       </c>
       <c r="E68" s="2">
-        <v>81505</v>
+        <v>81476</v>
       </c>
       <c r="F68" s="3">
         <v>46029</v>
@@ -2207,7 +2207,7 @@
         <v>2317</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C69" s="2">
         <v>64</v>
@@ -2216,10 +2216,10 @@
         <v>46029.3826292245</v>
       </c>
       <c r="E69" s="2">
-        <v>81517</v>
+        <v>81483</v>
       </c>
       <c r="F69" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>9</v>
@@ -2233,7 +2233,7 @@
         <v>2317</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C70" s="2">
         <v>64</v>
@@ -2242,10 +2242,10 @@
         <v>46029.3826292245</v>
       </c>
       <c r="E70" s="2">
-        <v>81547</v>
+        <v>81505</v>
       </c>
       <c r="F70" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>9</v>
@@ -2259,19 +2259,19 @@
         <v>2317</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C71" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D71" s="3">
-        <v>46037.4235473727</v>
+        <v>46029.3826292245</v>
       </c>
       <c r="E71" s="2">
-        <v>81661</v>
+        <v>81517</v>
       </c>
       <c r="F71" s="3">
-        <v>46037</v>
+        <v>46030</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>9</v>
@@ -2285,19 +2285,19 @@
         <v>2317</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C72" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>46043.6938147106</v>
+        <v>46029.3826292245</v>
       </c>
       <c r="E72" s="2">
-        <v>81771</v>
+        <v>81547</v>
       </c>
       <c r="F72" s="3">
-        <v>46043</v>
+        <v>46030</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>9</v>
@@ -2311,19 +2311,19 @@
         <v>2317</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C73" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D73" s="3">
-        <v>46043.6938147106</v>
+        <v>46037.4235473727</v>
       </c>
       <c r="E73" s="2">
-        <v>81773</v>
+        <v>81661</v>
       </c>
       <c r="F73" s="3">
-        <v>46043</v>
+        <v>46037</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>9</v>
@@ -2337,7 +2337,7 @@
         <v>2317</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C74" s="2">
         <v>66</v>
@@ -2346,10 +2346,10 @@
         <v>46043.6938147106</v>
       </c>
       <c r="E74" s="2">
-        <v>81776</v>
+        <v>81771</v>
       </c>
       <c r="F74" s="3">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>9</v>
@@ -2363,7 +2363,7 @@
         <v>2317</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C75" s="2">
         <v>66</v>
@@ -2372,10 +2372,10 @@
         <v>46043.6938147106</v>
       </c>
       <c r="E75" s="2">
-        <v>81777</v>
+        <v>81773</v>
       </c>
       <c r="F75" s="3">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>9</v>
@@ -2389,19 +2389,19 @@
         <v>2317</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C76" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D76" s="3">
-        <v>46050.7192297917</v>
+        <v>46043.6938147106</v>
       </c>
       <c r="E76" s="2">
-        <v>81910</v>
+        <v>81776</v>
       </c>
       <c r="F76" s="3">
-        <v>46050</v>
+        <v>46044</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>9</v>
@@ -2415,19 +2415,19 @@
         <v>2317</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C77" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D77" s="3">
-        <v>46050.7192297917</v>
+        <v>46043.6938147106</v>
       </c>
       <c r="E77" s="2">
-        <v>81916</v>
+        <v>81777</v>
       </c>
       <c r="F77" s="3">
-        <v>46051</v>
+        <v>46044</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>9</v>
@@ -2441,7 +2441,7 @@
         <v>2317</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C78" s="2">
         <v>67</v>
@@ -2450,10 +2450,10 @@
         <v>46050.7192297917</v>
       </c>
       <c r="E78" s="2">
-        <v>81917</v>
+        <v>81910</v>
       </c>
       <c r="F78" s="3">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>9</v>
@@ -2467,19 +2467,19 @@
         <v>2317</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C79" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D79" s="3">
-        <v>46056.7121682986</v>
+        <v>46050.7192297917</v>
       </c>
       <c r="E79" s="2">
-        <v>81990</v>
+        <v>81916</v>
       </c>
       <c r="F79" s="3">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>9</v>
@@ -2493,19 +2493,19 @@
         <v>2317</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C80" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D80" s="3">
-        <v>46058.6999666782</v>
+        <v>46050.7192297917</v>
       </c>
       <c r="E80" s="2">
-        <v>82030</v>
+        <v>81917</v>
       </c>
       <c r="F80" s="3">
-        <v>46058</v>
+        <v>46051</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>9</v>
@@ -2519,19 +2519,19 @@
         <v>2317</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C81" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D81" s="3">
-        <v>46058.6999666782</v>
+        <v>46056.7121682986</v>
       </c>
       <c r="E81" s="2">
-        <v>82031</v>
+        <v>81990</v>
       </c>
       <c r="F81" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>9</v>
@@ -2545,7 +2545,7 @@
         <v>2317</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C82" s="2">
         <v>69</v>
@@ -2554,10 +2554,10 @@
         <v>46058.6999666782</v>
       </c>
       <c r="E82" s="2">
-        <v>82045</v>
+        <v>82030</v>
       </c>
       <c r="F82" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>9</v>
@@ -2571,19 +2571,19 @@
         <v>2317</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C83" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D83" s="3">
-        <v>46063.596319213</v>
+        <v>46058.6999666782</v>
       </c>
       <c r="E83" s="2">
-        <v>82082</v>
+        <v>82031</v>
       </c>
       <c r="F83" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>9</v>
@@ -2597,19 +2597,19 @@
         <v>2317</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C84" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D84" s="3">
-        <v>46063.596319213</v>
+        <v>46058.6999666782</v>
       </c>
       <c r="E84" s="2">
-        <v>82083</v>
+        <v>82045</v>
       </c>
       <c r="F84" s="3">
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>9</v>
@@ -2623,19 +2623,19 @@
         <v>2317</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C85" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D85" s="3">
-        <v>46066.6139315162</v>
+        <v>46063.596319213</v>
       </c>
       <c r="E85" s="2">
-        <v>82191</v>
+        <v>82082</v>
       </c>
       <c r="F85" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>9</v>
@@ -2649,19 +2649,19 @@
         <v>2317</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C86" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D86" s="3">
-        <v>46076.7291292477</v>
+        <v>46063.596319213</v>
       </c>
       <c r="E86" s="2">
-        <v>82261</v>
+        <v>82083</v>
       </c>
       <c r="F86" s="3">
-        <v>46076</v>
+        <v>46063</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>9</v>
@@ -2675,19 +2675,19 @@
         <v>2317</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C87" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D87" s="3">
-        <v>46076.7291292477</v>
+        <v>46066.6139315162</v>
       </c>
       <c r="E87" s="2">
-        <v>82279</v>
+        <v>82191</v>
       </c>
       <c r="F87" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>9</v>
@@ -2701,19 +2701,19 @@
         <v>2317</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C88" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D88" s="3">
-        <v>46077.5089671528</v>
+        <v>46076.7291292477</v>
       </c>
       <c r="E88" s="2">
-        <v>82271</v>
+        <v>82261</v>
       </c>
       <c r="F88" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>9</v>
@@ -2727,16 +2727,16 @@
         <v>2317</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C89" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D89" s="3">
-        <v>46077.5089671528</v>
+        <v>46076.7291292477</v>
       </c>
       <c r="E89" s="2">
-        <v>82272</v>
+        <v>82279</v>
       </c>
       <c r="F89" s="3">
         <v>46077</v>
@@ -2753,19 +2753,19 @@
         <v>2317</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C90" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D90" s="3">
-        <v>46083.6704391782</v>
+        <v>46077.5089671528</v>
       </c>
       <c r="E90" s="2">
-        <v>82405</v>
+        <v>82271</v>
       </c>
       <c r="F90" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>9</v>
@@ -2779,19 +2779,19 @@
         <v>2317</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C91" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D91" s="3">
-        <v>46083.6704391782</v>
+        <v>46077.5089671528</v>
       </c>
       <c r="E91" s="2">
-        <v>82406</v>
+        <v>82272</v>
       </c>
       <c r="F91" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>9</v>
@@ -2802,22 +2802,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="92">
       <c r="A92" s="2">
-        <v>2407</v>
+        <v>2317</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C92" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D92" s="3">
-        <v>46035.4418341204</v>
+        <v>46083.6704391782</v>
       </c>
       <c r="E92" s="2">
-        <v>81606</v>
+        <v>82405</v>
       </c>
       <c r="F92" s="3">
-        <v>46035</v>
+        <v>46084</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>9</v>
@@ -2828,22 +2828,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="93">
       <c r="A93" s="2">
-        <v>2407</v>
+        <v>2317</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C93" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D93" s="3">
-        <v>46035.4418341204</v>
+        <v>46083.6704391782</v>
       </c>
       <c r="E93" s="2">
-        <v>81607</v>
+        <v>82406</v>
       </c>
       <c r="F93" s="3">
-        <v>46035</v>
+        <v>46084</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>9</v>
@@ -2854,22 +2854,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="94">
       <c r="A94" s="2">
-        <v>2407</v>
+        <v>2317</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C94" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D94" s="3">
-        <v>46048.4246969907</v>
+        <v>46097.6179829282</v>
       </c>
       <c r="E94" s="2">
-        <v>81847</v>
+        <v>82671</v>
       </c>
       <c r="F94" s="3">
-        <v>46048</v>
+        <v>46097</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>9</v>
@@ -2883,19 +2883,19 @@
         <v>2407</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C95" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D95" s="3">
-        <v>46048.4246969907</v>
+        <v>46035.4418341204</v>
       </c>
       <c r="E95" s="2">
-        <v>81848</v>
+        <v>81606</v>
       </c>
       <c r="F95" s="3">
-        <v>46048</v>
+        <v>46035</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>9</v>
@@ -2909,19 +2909,19 @@
         <v>2407</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C96" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D96" s="3">
-        <v>46048.4246969907</v>
+        <v>46035.4418341204</v>
       </c>
       <c r="E96" s="2">
-        <v>81849</v>
+        <v>81607</v>
       </c>
       <c r="F96" s="3">
-        <v>46048</v>
+        <v>46035</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>9</v>
@@ -2935,7 +2935,7 @@
         <v>2407</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C97" s="2">
         <v>80</v>
@@ -2944,7 +2944,7 @@
         <v>46048.4246969907</v>
       </c>
       <c r="E97" s="2">
-        <v>81850</v>
+        <v>81847</v>
       </c>
       <c r="F97" s="3">
         <v>46048</v>
@@ -2961,19 +2961,19 @@
         <v>2407</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C98" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D98" s="3">
-        <v>46055.6013222338</v>
+        <v>46048.4246969907</v>
       </c>
       <c r="E98" s="2">
-        <v>81962</v>
+        <v>81848</v>
       </c>
       <c r="F98" s="3">
-        <v>46055</v>
+        <v>46048</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>9</v>
@@ -2987,19 +2987,19 @@
         <v>2407</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C99" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D99" s="3">
-        <v>46055.6013222338</v>
+        <v>46048.4246969907</v>
       </c>
       <c r="E99" s="2">
-        <v>81963</v>
+        <v>81849</v>
       </c>
       <c r="F99" s="3">
-        <v>46055</v>
+        <v>46048</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>9</v>
@@ -3013,19 +3013,19 @@
         <v>2407</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C100" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D100" s="3">
-        <v>46072.5914714352</v>
+        <v>46048.4246969907</v>
       </c>
       <c r="E100" s="2">
-        <v>82207</v>
+        <v>81850</v>
       </c>
       <c r="F100" s="3">
-        <v>46072</v>
+        <v>46048</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>9</v>
@@ -3039,19 +3039,19 @@
         <v>2407</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C101" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D101" s="3">
-        <v>46072.5914714352</v>
+        <v>46055.6013222338</v>
       </c>
       <c r="E101" s="2">
-        <v>82209</v>
+        <v>81962</v>
       </c>
       <c r="F101" s="3">
-        <v>46072</v>
+        <v>46055</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>9</v>
@@ -3065,19 +3065,19 @@
         <v>2407</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C102" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D102" s="3">
-        <v>46072.5914714352</v>
+        <v>46055.6013222338</v>
       </c>
       <c r="E102" s="2">
-        <v>82210</v>
+        <v>81963</v>
       </c>
       <c r="F102" s="3">
-        <v>46072</v>
+        <v>46055</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>9</v>
@@ -3091,7 +3091,7 @@
         <v>2407</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C103" s="2">
         <v>82</v>
@@ -3100,7 +3100,7 @@
         <v>46072.5914714352</v>
       </c>
       <c r="E103" s="2">
-        <v>82213</v>
+        <v>82207</v>
       </c>
       <c r="F103" s="3">
         <v>46072</v>
@@ -3117,7 +3117,7 @@
         <v>2407</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C104" s="2">
         <v>82</v>
@@ -3126,10 +3126,10 @@
         <v>46072.5914714352</v>
       </c>
       <c r="E104" s="2">
-        <v>82227</v>
+        <v>82209</v>
       </c>
       <c r="F104" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>9</v>
@@ -3143,7 +3143,7 @@
         <v>2407</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C105" s="2">
         <v>82</v>
@@ -3152,10 +3152,10 @@
         <v>46072.5914714352</v>
       </c>
       <c r="E105" s="2">
-        <v>82228</v>
+        <v>82210</v>
       </c>
       <c r="F105" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>9</v>
@@ -3169,19 +3169,19 @@
         <v>2407</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C106" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D106" s="3">
-        <v>46073.7174898611</v>
+        <v>46072.5914714352</v>
       </c>
       <c r="E106" s="2">
-        <v>82252</v>
+        <v>82213</v>
       </c>
       <c r="F106" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>9</v>
@@ -3195,19 +3195,19 @@
         <v>2407</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C107" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D107" s="3">
-        <v>46073.7174898611</v>
+        <v>46072.5914714352</v>
       </c>
       <c r="E107" s="2">
-        <v>82256</v>
+        <v>82227</v>
       </c>
       <c r="F107" s="3">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>9</v>
@@ -3221,19 +3221,19 @@
         <v>2407</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C108" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D108" s="3">
-        <v>46080.46293125</v>
+        <v>46072.5914714352</v>
       </c>
       <c r="E108" s="2">
-        <v>82359</v>
+        <v>82228</v>
       </c>
       <c r="F108" s="3">
-        <v>46080</v>
+        <v>46073</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>9</v>
@@ -3247,19 +3247,19 @@
         <v>2407</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C109" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D109" s="3">
-        <v>46080.46293125</v>
+        <v>46073.7174898611</v>
       </c>
       <c r="E109" s="2">
-        <v>82360</v>
+        <v>82252</v>
       </c>
       <c r="F109" s="3">
-        <v>46080</v>
+        <v>46073</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>9</v>
@@ -3273,19 +3273,19 @@
         <v>2407</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C110" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D110" s="3">
-        <v>46080.46293125</v>
+        <v>46073.7174898611</v>
       </c>
       <c r="E110" s="2">
-        <v>82376</v>
+        <v>82256</v>
       </c>
       <c r="F110" s="3">
-        <v>46080</v>
+        <v>46076</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>9</v>
@@ -3299,19 +3299,19 @@
         <v>2407</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C111" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D111" s="3">
-        <v>46087.643003044</v>
+        <v>46080.46293125</v>
       </c>
       <c r="E111" s="2">
-        <v>82489</v>
+        <v>82359</v>
       </c>
       <c r="F111" s="3">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>9</v>
@@ -3325,19 +3325,19 @@
         <v>2407</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C112" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D112" s="3">
-        <v>46087.643003044</v>
+        <v>46080.46293125</v>
       </c>
       <c r="E112" s="2">
-        <v>82496</v>
+        <v>82360</v>
       </c>
       <c r="F112" s="3">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>9</v>
@@ -3351,19 +3351,19 @@
         <v>2407</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C113" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D113" s="3">
-        <v>46087.643003044</v>
+        <v>46080.46293125</v>
       </c>
       <c r="E113" s="2">
-        <v>82497</v>
+        <v>82376</v>
       </c>
       <c r="F113" s="3">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>9</v>
@@ -3374,22 +3374,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="114">
       <c r="A114" s="2">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C114" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D114" s="3">
-        <v>46014.6980340162</v>
+        <v>46087.643003044</v>
       </c>
       <c r="E114" s="2">
-        <v>81460</v>
+        <v>82489</v>
       </c>
       <c r="F114" s="3">
-        <v>46027</v>
+        <v>46087</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>9</v>
@@ -3400,22 +3400,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="115">
       <c r="A115" s="2">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C115" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D115" s="3">
-        <v>46014.6980340162</v>
+        <v>46087.643003044</v>
       </c>
       <c r="E115" s="2">
-        <v>81461</v>
+        <v>82496</v>
       </c>
       <c r="F115" s="3">
-        <v>46027</v>
+        <v>46090</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>9</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="116">
       <c r="A116" s="2">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C116" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D116" s="3">
-        <v>46014.6980340162</v>
+        <v>46087.643003044</v>
       </c>
       <c r="E116" s="2">
-        <v>81463</v>
+        <v>82497</v>
       </c>
       <c r="F116" s="3">
-        <v>46027</v>
+        <v>46090</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>9</v>
@@ -3455,19 +3455,19 @@
         <v>2409</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C117" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D117" s="3">
-        <v>46030.4707423958</v>
+        <v>46014.6980340162</v>
       </c>
       <c r="E117" s="2">
-        <v>81542</v>
+        <v>81460</v>
       </c>
       <c r="F117" s="3">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>9</v>
@@ -3481,19 +3481,19 @@
         <v>2409</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C118" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D118" s="3">
-        <v>46030.4707423958</v>
+        <v>46014.6980340162</v>
       </c>
       <c r="E118" s="2">
-        <v>81548</v>
+        <v>81461</v>
       </c>
       <c r="F118" s="3">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>9</v>
@@ -3507,19 +3507,19 @@
         <v>2409</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C119" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D119" s="3">
-        <v>46030.4707423958</v>
+        <v>46014.6980340162</v>
       </c>
       <c r="E119" s="2">
-        <v>81549</v>
+        <v>81463</v>
       </c>
       <c r="F119" s="3">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>9</v>
@@ -3533,7 +3533,7 @@
         <v>2409</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C120" s="2">
         <v>83</v>
@@ -3542,10 +3542,10 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E120" s="2">
-        <v>81569</v>
+        <v>81542</v>
       </c>
       <c r="F120" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>9</v>
@@ -3559,19 +3559,19 @@
         <v>2409</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C121" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D121" s="3">
-        <v>46037.6468124884</v>
+        <v>46030.4707423958</v>
       </c>
       <c r="E121" s="2">
-        <v>81669</v>
+        <v>81548</v>
       </c>
       <c r="F121" s="3">
-        <v>46037</v>
+        <v>46030</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>9</v>
@@ -3585,19 +3585,19 @@
         <v>2409</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C122" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D122" s="3">
-        <v>46037.6468124884</v>
+        <v>46030.4707423958</v>
       </c>
       <c r="E122" s="2">
-        <v>81670</v>
+        <v>81549</v>
       </c>
       <c r="F122" s="3">
-        <v>46037</v>
+        <v>46030</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>9</v>
@@ -3611,19 +3611,19 @@
         <v>2409</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C123" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D123" s="3">
-        <v>46037.6468124884</v>
+        <v>46030.4707423958</v>
       </c>
       <c r="E123" s="2">
-        <v>81673</v>
+        <v>81569</v>
       </c>
       <c r="F123" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>9</v>
@@ -3637,7 +3637,7 @@
         <v>2409</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C124" s="2">
         <v>84</v>
@@ -3646,10 +3646,10 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E124" s="2">
-        <v>81682</v>
+        <v>81669</v>
       </c>
       <c r="F124" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>9</v>
@@ -3663,7 +3663,7 @@
         <v>2409</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C125" s="2">
         <v>84</v>
@@ -3672,10 +3672,10 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E125" s="2">
-        <v>81689</v>
+        <v>81670</v>
       </c>
       <c r="F125" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>9</v>
@@ -3689,19 +3689,19 @@
         <v>2409</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C126" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D126" s="3">
-        <v>46038.5944713773</v>
+        <v>46037.6468124884</v>
       </c>
       <c r="E126" s="2">
-        <v>81707</v>
+        <v>81673</v>
       </c>
       <c r="F126" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>9</v>
@@ -3715,19 +3715,19 @@
         <v>2409</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C127" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D127" s="3">
-        <v>46049.490160081</v>
+        <v>46037.6468124884</v>
       </c>
       <c r="E127" s="2">
-        <v>81866</v>
+        <v>81682</v>
       </c>
       <c r="F127" s="3">
-        <v>46049</v>
+        <v>46038</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>9</v>
@@ -3741,19 +3741,19 @@
         <v>2409</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C128" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D128" s="3">
-        <v>46049.490160081</v>
+        <v>46037.6468124884</v>
       </c>
       <c r="E128" s="2">
-        <v>81867</v>
+        <v>81689</v>
       </c>
       <c r="F128" s="3">
-        <v>46049</v>
+        <v>46038</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>9</v>
@@ -3767,19 +3767,19 @@
         <v>2409</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C129" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D129" s="3">
-        <v>46049.490160081</v>
+        <v>46038.5944713773</v>
       </c>
       <c r="E129" s="2">
-        <v>81871</v>
+        <v>81707</v>
       </c>
       <c r="F129" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>9</v>
@@ -3793,7 +3793,7 @@
         <v>2409</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C130" s="2">
         <v>86</v>
@@ -3802,10 +3802,10 @@
         <v>46049.490160081</v>
       </c>
       <c r="E130" s="2">
-        <v>81882</v>
+        <v>81866</v>
       </c>
       <c r="F130" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>9</v>
@@ -3819,19 +3819,19 @@
         <v>2409</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C131" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D131" s="3">
-        <v>46051.4127791667</v>
+        <v>46049.490160081</v>
       </c>
       <c r="E131" s="2">
-        <v>81922</v>
+        <v>81867</v>
       </c>
       <c r="F131" s="3">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>9</v>
@@ -3845,19 +3845,19 @@
         <v>2409</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C132" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D132" s="3">
-        <v>46056.7141110995</v>
+        <v>46049.490160081</v>
       </c>
       <c r="E132" s="2">
-        <v>81972</v>
+        <v>81871</v>
       </c>
       <c r="F132" s="3">
-        <v>46056</v>
+        <v>46049</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>9</v>
@@ -3871,19 +3871,19 @@
         <v>2409</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C133" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D133" s="3">
-        <v>46056.7141110995</v>
+        <v>46049.490160081</v>
       </c>
       <c r="E133" s="2">
-        <v>81973</v>
+        <v>81882</v>
       </c>
       <c r="F133" s="3">
-        <v>46056</v>
+        <v>46050</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>9</v>
@@ -3897,19 +3897,19 @@
         <v>2409</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C134" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D134" s="3">
-        <v>46056.7141110995</v>
+        <v>46051.4127791667</v>
       </c>
       <c r="E134" s="2">
-        <v>81993</v>
+        <v>81922</v>
       </c>
       <c r="F134" s="3">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>9</v>
@@ -3923,19 +3923,19 @@
         <v>2409</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C135" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D135" s="3">
-        <v>46063.7282468519</v>
+        <v>46056.7141110995</v>
       </c>
       <c r="E135" s="2">
-        <v>82090</v>
+        <v>81972</v>
       </c>
       <c r="F135" s="3">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>9</v>
@@ -3949,19 +3949,19 @@
         <v>2409</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C136" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D136" s="3">
-        <v>46063.7282468519</v>
+        <v>46056.7141110995</v>
       </c>
       <c r="E136" s="2">
-        <v>82093</v>
+        <v>81973</v>
       </c>
       <c r="F136" s="3">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>9</v>
@@ -3975,19 +3975,19 @@
         <v>2409</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C137" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D137" s="3">
-        <v>46063.7282468519</v>
+        <v>46056.7141110995</v>
       </c>
       <c r="E137" s="2">
-        <v>82094</v>
+        <v>81993</v>
       </c>
       <c r="F137" s="3">
-        <v>46064</v>
+        <v>46057</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>9</v>
@@ -4001,7 +4001,7 @@
         <v>2409</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C138" s="2">
         <v>89</v>
@@ -4010,10 +4010,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E138" s="2">
-        <v>82098</v>
+        <v>82090</v>
       </c>
       <c r="F138" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>9</v>
@@ -4027,7 +4027,7 @@
         <v>2409</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C139" s="2">
         <v>89</v>
@@ -4036,10 +4036,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E139" s="2">
-        <v>82119</v>
+        <v>82093</v>
       </c>
       <c r="F139" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>9</v>
@@ -4053,7 +4053,7 @@
         <v>2409</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C140" s="2">
         <v>89</v>
@@ -4062,7 +4062,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E140" s="2">
-        <v>82120</v>
+        <v>82094</v>
       </c>
       <c r="F140" s="3">
         <v>46064</v>
@@ -4079,7 +4079,7 @@
         <v>2409</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C141" s="2">
         <v>89</v>
@@ -4088,10 +4088,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E141" s="2">
-        <v>82131</v>
+        <v>82098</v>
       </c>
       <c r="F141" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>9</v>
@@ -4105,19 +4105,19 @@
         <v>2409</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C142" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D142" s="3">
-        <v>46078.6817048032</v>
+        <v>46063.7282468519</v>
       </c>
       <c r="E142" s="2">
-        <v>82316</v>
+        <v>82119</v>
       </c>
       <c r="F142" s="3">
-        <v>46078</v>
+        <v>46064</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>9</v>
@@ -4131,19 +4131,19 @@
         <v>2409</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C143" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D143" s="3">
-        <v>46078.6817048032</v>
+        <v>46063.7282468519</v>
       </c>
       <c r="E143" s="2">
-        <v>82325</v>
+        <v>82120</v>
       </c>
       <c r="F143" s="3">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>9</v>
@@ -4157,19 +4157,19 @@
         <v>2409</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C144" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D144" s="3">
-        <v>46078.6817048032</v>
+        <v>46063.7282468519</v>
       </c>
       <c r="E144" s="2">
-        <v>82327</v>
+        <v>82131</v>
       </c>
       <c r="F144" s="3">
-        <v>46079</v>
+        <v>46065</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>9</v>
@@ -4183,19 +4183,19 @@
         <v>2409</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C145" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D145" s="3">
-        <v>46086.632572419</v>
+        <v>46078.6817048032</v>
       </c>
       <c r="E145" s="2">
-        <v>82471</v>
+        <v>82316</v>
       </c>
       <c r="F145" s="3">
-        <v>46086</v>
+        <v>46078</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>9</v>
@@ -4209,19 +4209,19 @@
         <v>2409</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C146" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D146" s="3">
-        <v>46086.632572419</v>
+        <v>46078.6817048032</v>
       </c>
       <c r="E146" s="2">
-        <v>82476</v>
+        <v>82325</v>
       </c>
       <c r="F146" s="3">
-        <v>46087</v>
+        <v>46079</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>9</v>
@@ -4235,19 +4235,19 @@
         <v>2409</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C147" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D147" s="3">
-        <v>46094.4767297338</v>
+        <v>46078.6817048032</v>
       </c>
       <c r="E147" s="2">
-        <v>82634</v>
+        <v>82327</v>
       </c>
       <c r="F147" s="3">
-        <v>46094</v>
+        <v>46079</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>9</v>
@@ -4261,45 +4261,45 @@
         <v>2409</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C148" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D148" s="3">
-        <v>46094.4767297338</v>
+        <v>46086.632572419</v>
       </c>
       <c r="E148" s="2">
-        <v>82635</v>
+        <v>82471</v>
       </c>
       <c r="F148" s="3">
-        <v>46094</v>
+        <v>46086</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="149">
       <c r="A149" s="2">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C149" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D149" s="3">
-        <v>46030.4179771875</v>
+        <v>46086.632572419</v>
       </c>
       <c r="E149" s="2">
-        <v>81536</v>
+        <v>82476</v>
       </c>
       <c r="F149" s="3">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>9</v>
@@ -4310,22 +4310,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="150">
       <c r="A150" s="2">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C150" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D150" s="3">
-        <v>46030.4179771875</v>
+        <v>46094.4767297338</v>
       </c>
       <c r="E150" s="2">
-        <v>81538</v>
+        <v>82634</v>
       </c>
       <c r="F150" s="3">
-        <v>46030</v>
+        <v>46094</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>9</v>
@@ -4336,28 +4336,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="151">
       <c r="A151" s="2">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C151" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D151" s="3">
-        <v>46030.4179771875</v>
+        <v>46094.4767297338</v>
       </c>
       <c r="E151" s="2">
-        <v>81555</v>
+        <v>82635</v>
       </c>
       <c r="F151" s="3">
-        <v>46030</v>
+        <v>46094</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="152">
@@ -4374,7 +4374,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E152" s="2">
-        <v>81556</v>
+        <v>81536</v>
       </c>
       <c r="F152" s="3">
         <v>46030</v>
@@ -4400,7 +4400,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E153" s="2">
-        <v>81558</v>
+        <v>81538</v>
       </c>
       <c r="F153" s="3">
         <v>46030</v>
@@ -4420,16 +4420,16 @@
         <v>20</v>
       </c>
       <c r="C154" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D154" s="3">
-        <v>46036.4079311574</v>
+        <v>46030.4179771875</v>
       </c>
       <c r="E154" s="2">
-        <v>81615</v>
+        <v>81555</v>
       </c>
       <c r="F154" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>9</v>
@@ -4446,16 +4446,16 @@
         <v>20</v>
       </c>
       <c r="C155" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D155" s="3">
-        <v>46036.4079311574</v>
+        <v>46030.4179771875</v>
       </c>
       <c r="E155" s="2">
-        <v>81621</v>
+        <v>81556</v>
       </c>
       <c r="F155" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>9</v>
@@ -4472,16 +4472,16 @@
         <v>20</v>
       </c>
       <c r="C156" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D156" s="3">
-        <v>46036.4079311574</v>
+        <v>46030.4179771875</v>
       </c>
       <c r="E156" s="2">
-        <v>81647</v>
+        <v>81558</v>
       </c>
       <c r="F156" s="3">
-        <v>46037</v>
+        <v>46030</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>9</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="157">
       <c r="A157" s="2">
-        <v>2504</v>
+        <v>2411</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C157" s="2">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D157" s="3">
-        <v>46027.6983957986</v>
+        <v>46036.4079311574</v>
       </c>
       <c r="E157" s="2">
-        <v>81465</v>
+        <v>81615</v>
       </c>
       <c r="F157" s="3">
-        <v>46027</v>
+        <v>46036</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>9</v>
@@ -4518,48 +4518,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="158">
       <c r="A158" s="2">
-        <v>2504</v>
+        <v>2411</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C158" s="2">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D158" s="3">
-        <v>46027.6983957986</v>
+        <v>46036.4079311574</v>
       </c>
       <c r="E158" s="2">
-        <v>81466</v>
+        <v>81621</v>
       </c>
       <c r="F158" s="3">
-        <v>46027</v>
+        <v>46036</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="159">
       <c r="A159" s="2">
-        <v>2504</v>
+        <v>2411</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C159" s="2">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D159" s="3">
-        <v>46027.6983957986</v>
+        <v>46036.4079311574</v>
       </c>
       <c r="E159" s="2">
-        <v>81471</v>
+        <v>81647</v>
       </c>
       <c r="F159" s="3">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>9</v>
@@ -4582,10 +4582,10 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E160" s="2">
-        <v>81488</v>
+        <v>81465</v>
       </c>
       <c r="F160" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>9</v>
@@ -4608,16 +4608,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E161" s="2">
-        <v>81489</v>
+        <v>81466</v>
       </c>
       <c r="F161" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="162">
@@ -4634,10 +4634,10 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E162" s="2">
-        <v>81490</v>
+        <v>81471</v>
       </c>
       <c r="F162" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>9</v>
@@ -4660,7 +4660,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E163" s="2">
-        <v>81491</v>
+        <v>81488</v>
       </c>
       <c r="F163" s="3">
         <v>46029</v>
@@ -4680,16 +4680,16 @@
         <v>21</v>
       </c>
       <c r="C164" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D164" s="3">
-        <v>46038.4184531713</v>
+        <v>46027.6983957986</v>
       </c>
       <c r="E164" s="2">
-        <v>81688</v>
+        <v>81489</v>
       </c>
       <c r="F164" s="3">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>9</v>
@@ -4706,16 +4706,16 @@
         <v>21</v>
       </c>
       <c r="C165" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D165" s="3">
-        <v>46038.6993878241</v>
+        <v>46027.6983957986</v>
       </c>
       <c r="E165" s="2">
-        <v>81700</v>
+        <v>81490</v>
       </c>
       <c r="F165" s="3">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>9</v>
@@ -4732,16 +4732,16 @@
         <v>21</v>
       </c>
       <c r="C166" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D166" s="3">
-        <v>46038.6993878241</v>
+        <v>46027.6983957986</v>
       </c>
       <c r="E166" s="2">
-        <v>81701</v>
+        <v>81491</v>
       </c>
       <c r="F166" s="3">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>9</v>
@@ -4758,13 +4758,13 @@
         <v>21</v>
       </c>
       <c r="C167" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D167" s="3">
-        <v>46038.6993878241</v>
+        <v>46038.4184531713</v>
       </c>
       <c r="E167" s="2">
-        <v>81702</v>
+        <v>81688</v>
       </c>
       <c r="F167" s="3">
         <v>46038</v>
@@ -4790,7 +4790,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E168" s="2">
-        <v>81703</v>
+        <v>81700</v>
       </c>
       <c r="F168" s="3">
         <v>46038</v>
@@ -4816,10 +4816,10 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E169" s="2">
-        <v>81734</v>
+        <v>81701</v>
       </c>
       <c r="F169" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>9</v>
@@ -4836,16 +4836,16 @@
         <v>21</v>
       </c>
       <c r="C170" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D170" s="3">
-        <v>46050.7176682523</v>
+        <v>46038.6993878241</v>
       </c>
       <c r="E170" s="2">
-        <v>81914</v>
+        <v>81702</v>
       </c>
       <c r="F170" s="3">
-        <v>46051</v>
+        <v>46038</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>9</v>
@@ -4862,16 +4862,16 @@
         <v>21</v>
       </c>
       <c r="C171" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D171" s="3">
-        <v>46050.7176682523</v>
+        <v>46038.6993878241</v>
       </c>
       <c r="E171" s="2">
-        <v>81915</v>
+        <v>81703</v>
       </c>
       <c r="F171" s="3">
-        <v>46051</v>
+        <v>46038</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>9</v>
@@ -4888,16 +4888,16 @@
         <v>21</v>
       </c>
       <c r="C172" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D172" s="3">
-        <v>46050.7176682523</v>
+        <v>46038.6993878241</v>
       </c>
       <c r="E172" s="2">
-        <v>81921</v>
+        <v>81734</v>
       </c>
       <c r="F172" s="3">
-        <v>46051</v>
+        <v>46041</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>9</v>
@@ -4914,16 +4914,16 @@
         <v>21</v>
       </c>
       <c r="C173" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D173" s="3">
-        <v>46052.6247194676</v>
+        <v>46050.7176682523</v>
       </c>
       <c r="E173" s="2">
-        <v>81949</v>
+        <v>81914</v>
       </c>
       <c r="F173" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>9</v>
@@ -4940,16 +4940,16 @@
         <v>21</v>
       </c>
       <c r="C174" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D174" s="3">
-        <v>46052.6247194676</v>
+        <v>46050.7176682523</v>
       </c>
       <c r="E174" s="2">
-        <v>81950</v>
+        <v>81915</v>
       </c>
       <c r="F174" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>9</v>
@@ -4966,16 +4966,16 @@
         <v>21</v>
       </c>
       <c r="C175" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D175" s="3">
-        <v>46052.6247194676</v>
+        <v>46050.7176682523</v>
       </c>
       <c r="E175" s="2">
-        <v>81951</v>
+        <v>81921</v>
       </c>
       <c r="F175" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>9</v>
@@ -4998,7 +4998,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E176" s="2">
-        <v>81953</v>
+        <v>81949</v>
       </c>
       <c r="F176" s="3">
         <v>46052</v>
@@ -5018,16 +5018,16 @@
         <v>21</v>
       </c>
       <c r="C177" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D177" s="3">
-        <v>46058.6976675694</v>
+        <v>46052.6247194676</v>
       </c>
       <c r="E177" s="2">
-        <v>82028</v>
+        <v>81950</v>
       </c>
       <c r="F177" s="3">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>9</v>
@@ -5044,16 +5044,16 @@
         <v>21</v>
       </c>
       <c r="C178" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D178" s="3">
-        <v>46058.6976675694</v>
+        <v>46052.6247194676</v>
       </c>
       <c r="E178" s="2">
-        <v>82029</v>
+        <v>81951</v>
       </c>
       <c r="F178" s="3">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>9</v>
@@ -5070,16 +5070,16 @@
         <v>21</v>
       </c>
       <c r="C179" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D179" s="3">
-        <v>46058.6976675694</v>
+        <v>46052.6247194676</v>
       </c>
       <c r="E179" s="2">
-        <v>82040</v>
+        <v>81953</v>
       </c>
       <c r="F179" s="3">
-        <v>46059</v>
+        <v>46052</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>9</v>
@@ -5102,10 +5102,10 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E180" s="2">
-        <v>82041</v>
+        <v>82028</v>
       </c>
       <c r="F180" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>9</v>
@@ -5128,10 +5128,10 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E181" s="2">
-        <v>82051</v>
+        <v>82029</v>
       </c>
       <c r="F181" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>9</v>
@@ -5148,16 +5148,16 @@
         <v>21</v>
       </c>
       <c r="C182" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D182" s="3">
-        <v>46065.6309066782</v>
+        <v>46058.6976675694</v>
       </c>
       <c r="E182" s="2">
-        <v>82168</v>
+        <v>82040</v>
       </c>
       <c r="F182" s="3">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>9</v>
@@ -5174,22 +5174,22 @@
         <v>21</v>
       </c>
       <c r="C183" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D183" s="3">
-        <v>46065.6309066782</v>
+        <v>46058.6976675694</v>
       </c>
       <c r="E183" s="2">
-        <v>82170</v>
+        <v>82041</v>
       </c>
       <c r="F183" s="3">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="184">
@@ -5200,16 +5200,16 @@
         <v>21</v>
       </c>
       <c r="C184" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D184" s="3">
-        <v>46065.6309066782</v>
+        <v>46058.6976675694</v>
       </c>
       <c r="E184" s="2">
-        <v>82171</v>
+        <v>82051</v>
       </c>
       <c r="F184" s="3">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>9</v>
@@ -5232,7 +5232,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E185" s="2">
-        <v>82172</v>
+        <v>82168</v>
       </c>
       <c r="F185" s="3">
         <v>46066</v>
@@ -5258,16 +5258,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E186" s="2">
-        <v>82175</v>
+        <v>82170</v>
       </c>
       <c r="F186" s="3">
         <v>46066</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="187">
@@ -5284,7 +5284,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E187" s="2">
-        <v>82176</v>
+        <v>82171</v>
       </c>
       <c r="F187" s="3">
         <v>46066</v>
@@ -5304,16 +5304,16 @@
         <v>21</v>
       </c>
       <c r="C188" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D188" s="3">
-        <v>46072.5909779051</v>
+        <v>46065.6309066782</v>
       </c>
       <c r="E188" s="2">
-        <v>82206</v>
+        <v>82172</v>
       </c>
       <c r="F188" s="3">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>9</v>
@@ -5330,16 +5330,16 @@
         <v>21</v>
       </c>
       <c r="C189" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D189" s="3">
-        <v>46077.7262228935</v>
+        <v>46065.6309066782</v>
       </c>
       <c r="E189" s="2">
-        <v>82289</v>
+        <v>82175</v>
       </c>
       <c r="F189" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>9</v>
@@ -5356,16 +5356,16 @@
         <v>21</v>
       </c>
       <c r="C190" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D190" s="3">
-        <v>46077.7262228935</v>
+        <v>46065.6309066782</v>
       </c>
       <c r="E190" s="2">
-        <v>82290</v>
+        <v>82176</v>
       </c>
       <c r="F190" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>9</v>
@@ -5382,16 +5382,16 @@
         <v>21</v>
       </c>
       <c r="C191" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D191" s="3">
-        <v>46078.6799843634</v>
+        <v>46072.5909779051</v>
       </c>
       <c r="E191" s="2">
-        <v>82318</v>
+        <v>82206</v>
       </c>
       <c r="F191" s="3">
-        <v>46078</v>
+        <v>46072</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>9</v>
@@ -5408,16 +5408,16 @@
         <v>21</v>
       </c>
       <c r="C192" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D192" s="3">
-        <v>46080.6294471412</v>
+        <v>46077.7262228935</v>
       </c>
       <c r="E192" s="2">
-        <v>82368</v>
+        <v>82289</v>
       </c>
       <c r="F192" s="3">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>9</v>
@@ -5434,16 +5434,16 @@
         <v>21</v>
       </c>
       <c r="C193" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D193" s="3">
-        <v>46084.741264838</v>
+        <v>46077.7262228935</v>
       </c>
       <c r="E193" s="2">
-        <v>82425</v>
+        <v>82290</v>
       </c>
       <c r="F193" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>9</v>
@@ -5460,16 +5460,16 @@
         <v>21</v>
       </c>
       <c r="C194" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D194" s="3">
-        <v>46084.741264838</v>
+        <v>46078.6799843634</v>
       </c>
       <c r="E194" s="2">
-        <v>82426</v>
+        <v>82318</v>
       </c>
       <c r="F194" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>9</v>
@@ -5486,16 +5486,16 @@
         <v>21</v>
       </c>
       <c r="C195" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D195" s="3">
-        <v>46084.741264838</v>
+        <v>46080.6294471412</v>
       </c>
       <c r="E195" s="2">
-        <v>82430</v>
+        <v>82368</v>
       </c>
       <c r="F195" s="3">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>9</v>
@@ -5518,10 +5518,10 @@
         <v>46084.741264838</v>
       </c>
       <c r="E196" s="2">
-        <v>82431</v>
+        <v>82425</v>
       </c>
       <c r="F196" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>9</v>
@@ -5538,16 +5538,16 @@
         <v>21</v>
       </c>
       <c r="C197" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D197" s="3">
-        <v>46097.4509044907</v>
+        <v>46084.741264838</v>
       </c>
       <c r="E197" s="2">
-        <v>82654</v>
+        <v>82426</v>
       </c>
       <c r="F197" s="3">
-        <v>46097</v>
+        <v>46084</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>9</v>
@@ -5564,16 +5564,16 @@
         <v>21</v>
       </c>
       <c r="C198" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D198" s="3">
-        <v>46097.4509044907</v>
+        <v>46084.741264838</v>
       </c>
       <c r="E198" s="2">
-        <v>82660</v>
+        <v>82430</v>
       </c>
       <c r="F198" s="3">
-        <v>46097</v>
+        <v>46085</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>9</v>
@@ -5590,16 +5590,16 @@
         <v>21</v>
       </c>
       <c r="C199" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D199" s="3">
-        <v>46097.4509044907</v>
+        <v>46084.741264838</v>
       </c>
       <c r="E199" s="2">
-        <v>82661</v>
+        <v>82431</v>
       </c>
       <c r="F199" s="3">
-        <v>46097</v>
+        <v>46085</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>9</v>
@@ -5610,22 +5610,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="200">
       <c r="A200" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C200" s="2">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D200" s="3">
-        <v>46041.6648751157</v>
+        <v>46097.4509044907</v>
       </c>
       <c r="E200" s="2">
-        <v>81743</v>
+        <v>82654</v>
       </c>
       <c r="F200" s="3">
-        <v>46041</v>
+        <v>46097</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>9</v>
@@ -5636,22 +5636,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="201">
       <c r="A201" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C201" s="2">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D201" s="3">
-        <v>46041.6648751157</v>
+        <v>46097.4509044907</v>
       </c>
       <c r="E201" s="2">
-        <v>81744</v>
+        <v>82660</v>
       </c>
       <c r="F201" s="3">
-        <v>46041</v>
+        <v>46097</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>9</v>
@@ -5662,22 +5662,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="202">
       <c r="A202" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C202" s="2">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D202" s="3">
-        <v>46041.6648751157</v>
+        <v>46097.4509044907</v>
       </c>
       <c r="E202" s="2">
-        <v>81745</v>
+        <v>82661</v>
       </c>
       <c r="F202" s="3">
-        <v>46041</v>
+        <v>46097</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>9</v>
@@ -5700,10 +5700,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E203" s="2">
-        <v>81746</v>
+        <v>81743</v>
       </c>
       <c r="F203" s="3">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>9</v>
@@ -5726,10 +5726,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E204" s="2">
-        <v>81751</v>
+        <v>81744</v>
       </c>
       <c r="F204" s="3">
-        <v>46043</v>
+        <v>46041</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>9</v>
@@ -5752,10 +5752,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E205" s="2">
-        <v>81753</v>
+        <v>81745</v>
       </c>
       <c r="F205" s="3">
-        <v>46043</v>
+        <v>46041</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>9</v>
@@ -5778,10 +5778,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E206" s="2">
-        <v>81754</v>
+        <v>81746</v>
       </c>
       <c r="F206" s="3">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>9</v>
@@ -5804,7 +5804,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E207" s="2">
-        <v>81755</v>
+        <v>81751</v>
       </c>
       <c r="F207" s="3">
         <v>46043</v>
@@ -5830,7 +5830,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E208" s="2">
-        <v>81766</v>
+        <v>81753</v>
       </c>
       <c r="F208" s="3">
         <v>46043</v>
@@ -5850,16 +5850,16 @@
         <v>22</v>
       </c>
       <c r="C209" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D209" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E209" s="2">
-        <v>82088</v>
+        <v>81754</v>
       </c>
       <c r="F209" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>9</v>
@@ -5876,16 +5876,16 @@
         <v>22</v>
       </c>
       <c r="C210" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D210" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E210" s="2">
-        <v>82089</v>
+        <v>81755</v>
       </c>
       <c r="F210" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>9</v>
@@ -5902,16 +5902,16 @@
         <v>22</v>
       </c>
       <c r="C211" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D211" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E211" s="2">
-        <v>82163</v>
+        <v>81766</v>
       </c>
       <c r="F211" s="3">
-        <v>46066</v>
+        <v>46043</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>9</v>
@@ -5934,10 +5934,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E212" s="2">
-        <v>82179</v>
+        <v>82088</v>
       </c>
       <c r="F212" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>9</v>
@@ -5960,10 +5960,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E213" s="2">
-        <v>82193</v>
+        <v>82089</v>
       </c>
       <c r="F213" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>9</v>
@@ -5980,16 +5980,16 @@
         <v>22</v>
       </c>
       <c r="C214" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D214" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E214" s="2">
-        <v>82250</v>
+        <v>82163</v>
       </c>
       <c r="F214" s="3">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>9</v>
@@ -6006,16 +6006,16 @@
         <v>22</v>
       </c>
       <c r="C215" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D215" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E215" s="2">
-        <v>82266</v>
+        <v>82179</v>
       </c>
       <c r="F215" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>9</v>
@@ -6032,16 +6032,16 @@
         <v>22</v>
       </c>
       <c r="C216" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D216" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E216" s="2">
-        <v>82295</v>
+        <v>82193</v>
       </c>
       <c r="F216" s="3">
-        <v>46078</v>
+        <v>46066</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>9</v>
@@ -6064,10 +6064,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E217" s="2">
-        <v>82296</v>
+        <v>82250</v>
       </c>
       <c r="F217" s="3">
-        <v>46078</v>
+        <v>46073</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>9</v>
@@ -6090,16 +6090,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E218" s="2">
-        <v>82332</v>
+        <v>82266</v>
       </c>
       <c r="F218" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="219">
@@ -6116,10 +6116,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E219" s="2">
-        <v>82339</v>
+        <v>82295</v>
       </c>
       <c r="F219" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>9</v>
@@ -6136,16 +6136,16 @@
         <v>22</v>
       </c>
       <c r="C220" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D220" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E220" s="2">
-        <v>82266</v>
+        <v>82296</v>
       </c>
       <c r="F220" s="3">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>9</v>
@@ -6162,22 +6162,22 @@
         <v>22</v>
       </c>
       <c r="C221" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D221" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E221" s="2">
-        <v>82273</v>
+        <v>82332</v>
       </c>
       <c r="F221" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="222">
@@ -6188,16 +6188,16 @@
         <v>22</v>
       </c>
       <c r="C222" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D222" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E222" s="2">
-        <v>82294</v>
+        <v>82339</v>
       </c>
       <c r="F222" s="3">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>9</v>
@@ -6214,16 +6214,16 @@
         <v>22</v>
       </c>
       <c r="C223" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D223" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E223" s="2">
-        <v>82411</v>
+        <v>82266</v>
       </c>
       <c r="F223" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>9</v>
@@ -6240,16 +6240,16 @@
         <v>22</v>
       </c>
       <c r="C224" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D224" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E224" s="2">
-        <v>82432</v>
+        <v>82273</v>
       </c>
       <c r="F224" s="3">
-        <v>46085</v>
+        <v>46077</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>9</v>
@@ -6266,16 +6266,16 @@
         <v>22</v>
       </c>
       <c r="C225" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D225" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E225" s="2">
-        <v>82473</v>
+        <v>82294</v>
       </c>
       <c r="F225" s="3">
-        <v>46086</v>
+        <v>46078</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>9</v>
@@ -6298,10 +6298,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E226" s="2">
-        <v>82474</v>
+        <v>82411</v>
       </c>
       <c r="F226" s="3">
-        <v>46087</v>
+        <v>46084</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>9</v>
@@ -6318,22 +6318,22 @@
         <v>22</v>
       </c>
       <c r="C227" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D227" s="3">
-        <v>46093.5009358681</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E227" s="2">
-        <v>82594</v>
+        <v>82432</v>
       </c>
       <c r="F227" s="3">
-        <v>46093</v>
+        <v>46085</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="228">
@@ -6344,22 +6344,22 @@
         <v>22</v>
       </c>
       <c r="C228" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D228" s="3">
-        <v>46093.5009358681</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E228" s="2">
-        <v>82595</v>
+        <v>82473</v>
       </c>
       <c r="F228" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="229">
@@ -6370,22 +6370,22 @@
         <v>22</v>
       </c>
       <c r="C229" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D229" s="3">
-        <v>46093.5009358681</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E229" s="2">
-        <v>82596</v>
+        <v>82474</v>
       </c>
       <c r="F229" s="3">
-        <v>46093</v>
+        <v>46087</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="230">
@@ -6402,94 +6402,94 @@
         <v>46093.5009358681</v>
       </c>
       <c r="E230" s="2">
-        <v>82657</v>
+        <v>82594</v>
       </c>
       <c r="F230" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="231">
       <c r="A231" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C231" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D231" s="3">
-        <v>46044.6368950926</v>
+        <v>46093.5009358681</v>
       </c>
       <c r="E231" s="2">
-        <v>81802</v>
+        <v>82595</v>
       </c>
       <c r="F231" s="3">
-        <v>46044</v>
+        <v>46093</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="232">
       <c r="A232" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C232" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D232" s="3">
-        <v>46044.6368950926</v>
+        <v>46093.5009358681</v>
       </c>
       <c r="E232" s="2">
-        <v>81803</v>
+        <v>82596</v>
       </c>
       <c r="F232" s="3">
-        <v>46044</v>
+        <v>46093</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="233">
       <c r="A233" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C233" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D233" s="3">
-        <v>46044.6368950926</v>
+        <v>46093.5009358681</v>
       </c>
       <c r="E233" s="2">
-        <v>81804</v>
+        <v>82657</v>
       </c>
       <c r="F233" s="3">
-        <v>46044</v>
+        <v>46097</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="234">
@@ -6506,7 +6506,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E234" s="2">
-        <v>81806</v>
+        <v>81802</v>
       </c>
       <c r="F234" s="3">
         <v>46044</v>
@@ -6532,7 +6532,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E235" s="2">
-        <v>81807</v>
+        <v>81803</v>
       </c>
       <c r="F235" s="3">
         <v>46044</v>
@@ -6558,10 +6558,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E236" s="2">
-        <v>81812</v>
+        <v>81804</v>
       </c>
       <c r="F236" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>9</v>
@@ -6584,10 +6584,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E237" s="2">
-        <v>81813</v>
+        <v>81806</v>
       </c>
       <c r="F237" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>9</v>
@@ -6610,10 +6610,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E238" s="2">
-        <v>81814</v>
+        <v>81807</v>
       </c>
       <c r="F238" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>9</v>
@@ -6636,7 +6636,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E239" s="2">
-        <v>81818</v>
+        <v>81812</v>
       </c>
       <c r="F239" s="3">
         <v>46045</v>
@@ -6662,7 +6662,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E240" s="2">
-        <v>81822</v>
+        <v>81813</v>
       </c>
       <c r="F240" s="3">
         <v>46045</v>
@@ -6688,7 +6688,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E241" s="2">
-        <v>81833</v>
+        <v>81814</v>
       </c>
       <c r="F241" s="3">
         <v>46045</v>
@@ -6714,7 +6714,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E242" s="2">
-        <v>81841</v>
+        <v>81818</v>
       </c>
       <c r="F242" s="3">
         <v>46045</v>
@@ -6734,16 +6734,16 @@
         <v>27</v>
       </c>
       <c r="C243" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D243" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E243" s="2">
-        <v>81928</v>
+        <v>81822</v>
       </c>
       <c r="F243" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>9</v>
@@ -6760,16 +6760,16 @@
         <v>27</v>
       </c>
       <c r="C244" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D244" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E244" s="2">
-        <v>81929</v>
+        <v>81833</v>
       </c>
       <c r="F244" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G244" s="1" t="s">
         <v>9</v>
@@ -6786,16 +6786,16 @@
         <v>27</v>
       </c>
       <c r="C245" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D245" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E245" s="2">
-        <v>81930</v>
+        <v>81841</v>
       </c>
       <c r="F245" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>9</v>
@@ -6818,7 +6818,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E246" s="2">
-        <v>81932</v>
+        <v>81928</v>
       </c>
       <c r="F246" s="3">
         <v>46052</v>
@@ -6844,7 +6844,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E247" s="2">
-        <v>81933</v>
+        <v>81929</v>
       </c>
       <c r="F247" s="3">
         <v>46052</v>
@@ -6870,7 +6870,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E248" s="2">
-        <v>81934</v>
+        <v>81930</v>
       </c>
       <c r="F248" s="3">
         <v>46052</v>
@@ -6896,7 +6896,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E249" s="2">
-        <v>81935</v>
+        <v>81932</v>
       </c>
       <c r="F249" s="3">
         <v>46052</v>
@@ -6922,7 +6922,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E250" s="2">
-        <v>81936</v>
+        <v>81933</v>
       </c>
       <c r="F250" s="3">
         <v>46052</v>
@@ -6942,16 +6942,16 @@
         <v>27</v>
       </c>
       <c r="C251" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D251" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E251" s="2">
-        <v>82222</v>
+        <v>81934</v>
       </c>
       <c r="F251" s="3">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>9</v>
@@ -6968,16 +6968,16 @@
         <v>27</v>
       </c>
       <c r="C252" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D252" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E252" s="2">
-        <v>82226</v>
+        <v>81935</v>
       </c>
       <c r="F252" s="3">
-        <v>46073</v>
+        <v>46052</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>9</v>
@@ -6994,16 +6994,16 @@
         <v>27</v>
       </c>
       <c r="C253" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D253" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E253" s="2">
-        <v>82229</v>
+        <v>81936</v>
       </c>
       <c r="F253" s="3">
-        <v>46073</v>
+        <v>46052</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>9</v>
@@ -7020,16 +7020,16 @@
         <v>27</v>
       </c>
       <c r="C254" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D254" s="3">
-        <v>46073.5838834375</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E254" s="2">
-        <v>82246</v>
+        <v>82222</v>
       </c>
       <c r="F254" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>9</v>
@@ -7046,16 +7046,16 @@
         <v>27</v>
       </c>
       <c r="C255" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D255" s="3">
-        <v>46080.6289065162</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E255" s="2">
-        <v>82387</v>
+        <v>82226</v>
       </c>
       <c r="F255" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>9</v>
@@ -7072,16 +7072,16 @@
         <v>27</v>
       </c>
       <c r="C256" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D256" s="3">
-        <v>46093.4978086806</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E256" s="2">
-        <v>82590</v>
+        <v>82229</v>
       </c>
       <c r="F256" s="3">
-        <v>46093</v>
+        <v>46073</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>9</v>
@@ -7098,22 +7098,22 @@
         <v>27</v>
       </c>
       <c r="C257" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D257" s="3">
-        <v>46093.4978086806</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E257" s="2">
-        <v>82591</v>
+        <v>82246</v>
       </c>
       <c r="F257" s="3">
-        <v>46093</v>
+        <v>46073</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="258">
@@ -7124,16 +7124,16 @@
         <v>27</v>
       </c>
       <c r="C258" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D258" s="3">
-        <v>46093.4978086806</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E258" s="2">
-        <v>82592</v>
+        <v>82387</v>
       </c>
       <c r="F258" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>9</v>
@@ -7156,7 +7156,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E259" s="2">
-        <v>82593</v>
+        <v>82590</v>
       </c>
       <c r="F259" s="3">
         <v>46093</v>
@@ -7182,16 +7182,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E260" s="2">
-        <v>82600</v>
+        <v>82591</v>
       </c>
       <c r="F260" s="3">
         <v>46093</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="261">
@@ -7208,7 +7208,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E261" s="2">
-        <v>82603</v>
+        <v>82592</v>
       </c>
       <c r="F261" s="3">
         <v>46093</v>
@@ -7234,7 +7234,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E262" s="2">
-        <v>82604</v>
+        <v>82593</v>
       </c>
       <c r="F262" s="3">
         <v>46093</v>
@@ -7260,7 +7260,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E263" s="2">
-        <v>82605</v>
+        <v>82600</v>
       </c>
       <c r="F263" s="3">
         <v>46093</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="264">
       <c r="A264" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C264" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D264" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E264" s="2">
-        <v>81478</v>
+        <v>82603</v>
       </c>
       <c r="F264" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>9</v>
@@ -7300,22 +7300,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="265">
       <c r="A265" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C265" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D265" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E265" s="2">
-        <v>81479</v>
+        <v>82604</v>
       </c>
       <c r="F265" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>9</v>
@@ -7326,22 +7326,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="266">
       <c r="A266" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C266" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D266" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E266" s="2">
-        <v>81480</v>
+        <v>82605</v>
       </c>
       <c r="F266" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>9</v>
@@ -7364,7 +7364,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E267" s="2">
-        <v>81497</v>
+        <v>81478</v>
       </c>
       <c r="F267" s="3">
         <v>46029</v>
@@ -7390,7 +7390,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E268" s="2">
-        <v>81498</v>
+        <v>81479</v>
       </c>
       <c r="F268" s="3">
         <v>46029</v>
@@ -7416,7 +7416,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E269" s="2">
-        <v>81499</v>
+        <v>81480</v>
       </c>
       <c r="F269" s="3">
         <v>46029</v>
@@ -7442,7 +7442,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E270" s="2">
-        <v>81500</v>
+        <v>81497</v>
       </c>
       <c r="F270" s="3">
         <v>46029</v>
@@ -7462,16 +7462,16 @@
         <v>27</v>
       </c>
       <c r="C271" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D271" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E271" s="2">
-        <v>81878</v>
+        <v>81498</v>
       </c>
       <c r="F271" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>9</v>
@@ -7488,16 +7488,16 @@
         <v>27</v>
       </c>
       <c r="C272" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D272" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E272" s="2">
-        <v>81879</v>
+        <v>81499</v>
       </c>
       <c r="F272" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>9</v>
@@ -7514,16 +7514,16 @@
         <v>27</v>
       </c>
       <c r="C273" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D273" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E273" s="2">
-        <v>81885</v>
+        <v>81500</v>
       </c>
       <c r="F273" s="3">
-        <v>46050</v>
+        <v>46029</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>9</v>
@@ -7546,10 +7546,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E274" s="2">
-        <v>81886</v>
+        <v>81878</v>
       </c>
       <c r="F274" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>9</v>
@@ -7566,16 +7566,16 @@
         <v>27</v>
       </c>
       <c r="C275" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D275" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E275" s="2">
-        <v>82068</v>
+        <v>81879</v>
       </c>
       <c r="F275" s="3">
-        <v>46062</v>
+        <v>46049</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>9</v>
@@ -7592,16 +7592,16 @@
         <v>27</v>
       </c>
       <c r="C276" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D276" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E276" s="2">
-        <v>82072</v>
+        <v>81885</v>
       </c>
       <c r="F276" s="3">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>9</v>
@@ -7618,16 +7618,16 @@
         <v>27</v>
       </c>
       <c r="C277" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D277" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E277" s="2">
-        <v>82076</v>
+        <v>81886</v>
       </c>
       <c r="F277" s="3">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>9</v>
@@ -7650,10 +7650,10 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E278" s="2">
-        <v>82078</v>
+        <v>82068</v>
       </c>
       <c r="F278" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>9</v>
@@ -7670,16 +7670,16 @@
         <v>27</v>
       </c>
       <c r="C279" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D279" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E279" s="2">
-        <v>82287</v>
+        <v>82072</v>
       </c>
       <c r="F279" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>9</v>
@@ -7696,16 +7696,16 @@
         <v>27</v>
       </c>
       <c r="C280" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D280" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E280" s="2">
-        <v>82288</v>
+        <v>82076</v>
       </c>
       <c r="F280" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>9</v>
@@ -7722,16 +7722,16 @@
         <v>27</v>
       </c>
       <c r="C281" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D281" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E281" s="2">
-        <v>82298</v>
+        <v>82078</v>
       </c>
       <c r="F281" s="3">
-        <v>46078</v>
+        <v>46063</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>9</v>
@@ -7754,10 +7754,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E282" s="2">
-        <v>82301</v>
+        <v>82287</v>
       </c>
       <c r="F282" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>9</v>
@@ -7780,10 +7780,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E283" s="2">
-        <v>82304</v>
+        <v>82288</v>
       </c>
       <c r="F283" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>9</v>
@@ -7806,7 +7806,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E284" s="2">
-        <v>82308</v>
+        <v>82298</v>
       </c>
       <c r="F284" s="3">
         <v>46078</v>
@@ -7826,16 +7826,16 @@
         <v>27</v>
       </c>
       <c r="C285" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D285" s="3">
-        <v>46080.628344919</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E285" s="2">
-        <v>82373</v>
+        <v>82301</v>
       </c>
       <c r="F285" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>9</v>
@@ -7852,16 +7852,16 @@
         <v>27</v>
       </c>
       <c r="C286" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D286" s="3">
-        <v>46085.6581644213</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E286" s="2">
-        <v>82445</v>
+        <v>82304</v>
       </c>
       <c r="F286" s="3">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>9</v>
@@ -7878,16 +7878,16 @@
         <v>27</v>
       </c>
       <c r="C287" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D287" s="3">
-        <v>46085.6581644213</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E287" s="2">
-        <v>82447</v>
+        <v>82308</v>
       </c>
       <c r="F287" s="3">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>9</v>
@@ -7904,16 +7904,16 @@
         <v>27</v>
       </c>
       <c r="C288" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D288" s="3">
-        <v>46085.6581644213</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E288" s="2">
-        <v>82453</v>
+        <v>82373</v>
       </c>
       <c r="F288" s="3">
-        <v>46086</v>
+        <v>46080</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>9</v>
@@ -7936,10 +7936,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E289" s="2">
-        <v>82468</v>
+        <v>82445</v>
       </c>
       <c r="F289" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>9</v>
@@ -7950,22 +7950,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="290">
       <c r="A290" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C290" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D290" s="3">
-        <v>46029.6400966782</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E290" s="2">
-        <v>81506</v>
+        <v>82447</v>
       </c>
       <c r="F290" s="3">
-        <v>46029</v>
+        <v>46085</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>9</v>
@@ -7976,22 +7976,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="291">
       <c r="A291" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C291" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D291" s="3">
-        <v>46029.6400966782</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E291" s="2">
-        <v>81507</v>
+        <v>82453</v>
       </c>
       <c r="F291" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>9</v>
@@ -8002,22 +8002,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="292">
       <c r="A292" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C292" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D292" s="3">
-        <v>46029.6400966782</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E292" s="2">
-        <v>81524</v>
+        <v>82468</v>
       </c>
       <c r="F292" s="3">
-        <v>46030</v>
+        <v>46086</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>9</v>
@@ -8040,10 +8040,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E293" s="2">
-        <v>81525</v>
+        <v>81506</v>
       </c>
       <c r="F293" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>9</v>
@@ -8066,10 +8066,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E294" s="2">
-        <v>81526</v>
+        <v>81507</v>
       </c>
       <c r="F294" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>9</v>
@@ -8086,16 +8086,16 @@
         <v>28</v>
       </c>
       <c r="C295" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D295" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E295" s="2">
-        <v>81640</v>
+        <v>81524</v>
       </c>
       <c r="F295" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>9</v>
@@ -8112,16 +8112,16 @@
         <v>28</v>
       </c>
       <c r="C296" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D296" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E296" s="2">
-        <v>81642</v>
+        <v>81525</v>
       </c>
       <c r="F296" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>9</v>
@@ -8138,16 +8138,16 @@
         <v>28</v>
       </c>
       <c r="C297" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D297" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E297" s="2">
-        <v>81643</v>
+        <v>81526</v>
       </c>
       <c r="F297" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>9</v>
@@ -8164,16 +8164,16 @@
         <v>28</v>
       </c>
       <c r="C298" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D298" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E298" s="2">
-        <v>81835</v>
+        <v>81640</v>
       </c>
       <c r="F298" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>9</v>
@@ -8190,16 +8190,16 @@
         <v>28</v>
       </c>
       <c r="C299" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D299" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E299" s="2">
-        <v>81836</v>
+        <v>81642</v>
       </c>
       <c r="F299" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>9</v>
@@ -8216,16 +8216,16 @@
         <v>28</v>
       </c>
       <c r="C300" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D300" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E300" s="2">
-        <v>81837</v>
+        <v>81643</v>
       </c>
       <c r="F300" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>9</v>
@@ -8242,16 +8242,16 @@
         <v>28</v>
       </c>
       <c r="C301" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D301" s="3">
-        <v>46051.6376515278</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E301" s="2">
-        <v>81931</v>
+        <v>81835</v>
       </c>
       <c r="F301" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G301" s="1" t="s">
         <v>9</v>
@@ -8268,16 +8268,16 @@
         <v>28</v>
       </c>
       <c r="C302" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D302" s="3">
-        <v>46056.7115158912</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E302" s="2">
-        <v>81978</v>
+        <v>81836</v>
       </c>
       <c r="F302" s="3">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>9</v>
@@ -8294,16 +8294,16 @@
         <v>28</v>
       </c>
       <c r="C303" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D303" s="3">
-        <v>46057.6911087731</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E303" s="2">
-        <v>81994</v>
+        <v>81837</v>
       </c>
       <c r="F303" s="3">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>9</v>
@@ -8320,16 +8320,16 @@
         <v>28</v>
       </c>
       <c r="C304" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D304" s="3">
-        <v>46057.6911087731</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E304" s="2">
-        <v>81995</v>
+        <v>81931</v>
       </c>
       <c r="F304" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>9</v>
@@ -8346,13 +8346,13 @@
         <v>28</v>
       </c>
       <c r="C305" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D305" s="3">
-        <v>46057.6911087731</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E305" s="2">
-        <v>81999</v>
+        <v>81978</v>
       </c>
       <c r="F305" s="3">
         <v>46057</v>
@@ -8378,10 +8378,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E306" s="2">
-        <v>82008</v>
+        <v>81994</v>
       </c>
       <c r="F306" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>9</v>
@@ -8404,10 +8404,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E307" s="2">
-        <v>82011</v>
+        <v>81995</v>
       </c>
       <c r="F307" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>9</v>
@@ -8430,10 +8430,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E308" s="2">
-        <v>82012</v>
+        <v>81999</v>
       </c>
       <c r="F308" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>9</v>
@@ -8456,7 +8456,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E309" s="2">
-        <v>82013</v>
+        <v>82008</v>
       </c>
       <c r="F309" s="3">
         <v>46058</v>
@@ -8482,7 +8482,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E310" s="2">
-        <v>82014</v>
+        <v>82011</v>
       </c>
       <c r="F310" s="3">
         <v>46058</v>
@@ -8502,22 +8502,22 @@
         <v>28</v>
       </c>
       <c r="C311" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D311" s="3">
-        <v>46058.6604985417</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E311" s="2">
-        <v>82046</v>
+        <v>82012</v>
       </c>
       <c r="F311" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="312">
@@ -8528,16 +8528,16 @@
         <v>28</v>
       </c>
       <c r="C312" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D312" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E312" s="2">
-        <v>82217</v>
+        <v>82013</v>
       </c>
       <c r="F312" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>9</v>
@@ -8554,16 +8554,16 @@
         <v>28</v>
       </c>
       <c r="C313" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D313" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E313" s="2">
-        <v>82218</v>
+        <v>82014</v>
       </c>
       <c r="F313" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>9</v>
@@ -8580,22 +8580,22 @@
         <v>28</v>
       </c>
       <c r="C314" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D314" s="3">
-        <v>46072.738871875</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E314" s="2">
-        <v>82234</v>
+        <v>82046</v>
       </c>
       <c r="F314" s="3">
-        <v>46073</v>
+        <v>46059</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="315">
@@ -8612,10 +8612,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E315" s="2">
-        <v>82238</v>
+        <v>82217</v>
       </c>
       <c r="F315" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>9</v>
@@ -8638,10 +8638,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E316" s="2">
-        <v>82245</v>
+        <v>82218</v>
       </c>
       <c r="F316" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>9</v>
@@ -8658,16 +8658,16 @@
         <v>28</v>
       </c>
       <c r="C317" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D317" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E317" s="2">
-        <v>82257</v>
+        <v>82234</v>
       </c>
       <c r="F317" s="3">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>9</v>
@@ -8684,16 +8684,16 @@
         <v>28</v>
       </c>
       <c r="C318" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D318" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E318" s="2">
-        <v>82276</v>
+        <v>82238</v>
       </c>
       <c r="F318" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>9</v>
@@ -8710,16 +8710,16 @@
         <v>28</v>
       </c>
       <c r="C319" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D319" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E319" s="2">
-        <v>82277</v>
+        <v>82245</v>
       </c>
       <c r="F319" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>9</v>
@@ -8742,10 +8742,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E320" s="2">
-        <v>82293</v>
+        <v>82257</v>
       </c>
       <c r="F320" s="3">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>9</v>
@@ -8762,13 +8762,13 @@
         <v>28</v>
       </c>
       <c r="C321" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D321" s="3">
-        <v>46077.4356327431</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E321" s="2">
-        <v>82269</v>
+        <v>82276</v>
       </c>
       <c r="F321" s="3">
         <v>46077</v>
@@ -8788,16 +8788,16 @@
         <v>28</v>
       </c>
       <c r="C322" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D322" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E322" s="2">
-        <v>82419</v>
+        <v>82277</v>
       </c>
       <c r="F322" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>9</v>
@@ -8814,16 +8814,16 @@
         <v>28</v>
       </c>
       <c r="C323" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D323" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E323" s="2">
-        <v>82420</v>
+        <v>82293</v>
       </c>
       <c r="F323" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>9</v>
@@ -8840,16 +8840,16 @@
         <v>28</v>
       </c>
       <c r="C324" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D324" s="3">
-        <v>46084.7378501505</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E324" s="2">
-        <v>82421</v>
+        <v>82269</v>
       </c>
       <c r="F324" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>9</v>
@@ -8872,7 +8872,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E325" s="2">
-        <v>82422</v>
+        <v>82419</v>
       </c>
       <c r="F325" s="3">
         <v>46084</v>
@@ -8898,7 +8898,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E326" s="2">
-        <v>82423</v>
+        <v>82420</v>
       </c>
       <c r="F326" s="3">
         <v>46084</v>
@@ -8924,10 +8924,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E327" s="2">
-        <v>82433</v>
+        <v>82421</v>
       </c>
       <c r="F327" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>9</v>
@@ -8950,10 +8950,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E328" s="2">
-        <v>82434</v>
+        <v>82422</v>
       </c>
       <c r="F328" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>9</v>
@@ -8976,10 +8976,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E329" s="2">
-        <v>82464</v>
+        <v>82423</v>
       </c>
       <c r="F329" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>9</v>
@@ -9002,10 +9002,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E330" s="2">
-        <v>82472</v>
+        <v>82433</v>
       </c>
       <c r="F330" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>9</v>
@@ -9022,16 +9022,16 @@
         <v>28</v>
       </c>
       <c r="C331" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D331" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E331" s="2">
-        <v>82578</v>
+        <v>82434</v>
       </c>
       <c r="F331" s="3">
-        <v>46093</v>
+        <v>46085</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>9</v>
@@ -9048,16 +9048,16 @@
         <v>28</v>
       </c>
       <c r="C332" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D332" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E332" s="2">
-        <v>82579</v>
+        <v>82464</v>
       </c>
       <c r="F332" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>9</v>
@@ -9074,16 +9074,16 @@
         <v>28</v>
       </c>
       <c r="C333" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D333" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E333" s="2">
-        <v>82580</v>
+        <v>82472</v>
       </c>
       <c r="F333" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>9</v>
@@ -9106,16 +9106,16 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E334" s="2">
-        <v>82599</v>
+        <v>82578</v>
       </c>
       <c r="F334" s="3">
         <v>46093</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="335">
@@ -9132,7 +9132,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E335" s="2">
-        <v>82602</v>
+        <v>82579</v>
       </c>
       <c r="F335" s="3">
         <v>46093</v>
@@ -9152,13 +9152,13 @@
         <v>28</v>
       </c>
       <c r="C336" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D336" s="3">
-        <v>46093.4957757986</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E336" s="2">
-        <v>82584</v>
+        <v>82580</v>
       </c>
       <c r="F336" s="3">
         <v>46093</v>
@@ -9172,48 +9172,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="337">
       <c r="A337" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C337" s="2">
+        <v>33</v>
+      </c>
+      <c r="D337" s="3">
+        <v>46093.4897546412</v>
+      </c>
+      <c r="E337" s="2">
+        <v>82599</v>
+      </c>
+      <c r="F337" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G337" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D337" s="3">
-        <v>46027.6953206134</v>
-      </c>
-      <c r="E337" s="2">
-        <v>81464</v>
-      </c>
-      <c r="F337" s="3">
-        <v>46027</v>
-      </c>
-      <c r="G337" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H337" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="338">
       <c r="A338" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C338" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D338" s="3">
-        <v>46027.6953206134</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E338" s="2">
-        <v>81472</v>
+        <v>82602</v>
       </c>
       <c r="F338" s="3">
-        <v>46027</v>
+        <v>46093</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>9</v>
@@ -9224,22 +9224,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="339">
       <c r="A339" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C339" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D339" s="3">
-        <v>46027.6953206134</v>
+        <v>46093.4957757986</v>
       </c>
       <c r="E339" s="2">
-        <v>81492</v>
+        <v>82584</v>
       </c>
       <c r="F339" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>9</v>
@@ -9262,10 +9262,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E340" s="2">
-        <v>81493</v>
+        <v>81464</v>
       </c>
       <c r="F340" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>9</v>
@@ -9288,10 +9288,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E341" s="2">
-        <v>81568</v>
+        <v>81472</v>
       </c>
       <c r="F341" s="3">
-        <v>46031</v>
+        <v>46027</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>9</v>
@@ -9314,10 +9314,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E342" s="2">
-        <v>81601</v>
+        <v>81492</v>
       </c>
       <c r="F342" s="3">
-        <v>46034</v>
+        <v>46029</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>9</v>
@@ -9340,10 +9340,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E343" s="2">
-        <v>81602</v>
+        <v>81493</v>
       </c>
       <c r="F343" s="3">
-        <v>46034</v>
+        <v>46029</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>9</v>
@@ -9360,16 +9360,16 @@
         <v>29</v>
       </c>
       <c r="C344" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D344" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E344" s="2">
-        <v>81645</v>
+        <v>81568</v>
       </c>
       <c r="F344" s="3">
-        <v>46036</v>
+        <v>46031</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>9</v>
@@ -9386,16 +9386,16 @@
         <v>29</v>
       </c>
       <c r="C345" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D345" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E345" s="2">
-        <v>81646</v>
+        <v>81601</v>
       </c>
       <c r="F345" s="3">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>9</v>
@@ -9412,16 +9412,16 @@
         <v>29</v>
       </c>
       <c r="C346" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D346" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E346" s="2">
-        <v>81653</v>
+        <v>81602</v>
       </c>
       <c r="F346" s="3">
-        <v>46037</v>
+        <v>46034</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>9</v>
@@ -9438,16 +9438,16 @@
         <v>29</v>
       </c>
       <c r="C347" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D347" s="3">
-        <v>46037.4325152662</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E347" s="2">
-        <v>81662</v>
+        <v>81645</v>
       </c>
       <c r="F347" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>9</v>
@@ -9464,16 +9464,16 @@
         <v>29</v>
       </c>
       <c r="C348" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D348" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E348" s="2">
-        <v>81780</v>
+        <v>81646</v>
       </c>
       <c r="F348" s="3">
-        <v>46044</v>
+        <v>46036</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>9</v>
@@ -9490,16 +9490,16 @@
         <v>29</v>
       </c>
       <c r="C349" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D349" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E349" s="2">
-        <v>81781</v>
+        <v>81653</v>
       </c>
       <c r="F349" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>9</v>
@@ -9516,16 +9516,16 @@
         <v>29</v>
       </c>
       <c r="C350" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D350" s="3">
-        <v>46044.4079891435</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E350" s="2">
-        <v>81782</v>
+        <v>81662</v>
       </c>
       <c r="F350" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>9</v>
@@ -9548,7 +9548,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E351" s="2">
-        <v>81784</v>
+        <v>81780</v>
       </c>
       <c r="F351" s="3">
         <v>46044</v>
@@ -9574,7 +9574,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E352" s="2">
-        <v>81785</v>
+        <v>81781</v>
       </c>
       <c r="F352" s="3">
         <v>46044</v>
@@ -9600,7 +9600,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E353" s="2">
-        <v>81801</v>
+        <v>81782</v>
       </c>
       <c r="F353" s="3">
         <v>46044</v>
@@ -9620,16 +9620,16 @@
         <v>29</v>
       </c>
       <c r="C354" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D354" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E354" s="2">
-        <v>81860</v>
+        <v>81784</v>
       </c>
       <c r="F354" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>9</v>
@@ -9646,16 +9646,16 @@
         <v>29</v>
       </c>
       <c r="C355" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D355" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E355" s="2">
-        <v>81873</v>
+        <v>81785</v>
       </c>
       <c r="F355" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>9</v>
@@ -9672,16 +9672,16 @@
         <v>29</v>
       </c>
       <c r="C356" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D356" s="3">
-        <v>46049.4883916667</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E356" s="2">
-        <v>81865</v>
+        <v>81801</v>
       </c>
       <c r="F356" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>9</v>
@@ -9698,13 +9698,13 @@
         <v>29</v>
       </c>
       <c r="C357" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D357" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E357" s="2">
-        <v>81870</v>
+        <v>81860</v>
       </c>
       <c r="F357" s="3">
         <v>46049</v>
@@ -9724,13 +9724,13 @@
         <v>29</v>
       </c>
       <c r="C358" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D358" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E358" s="2">
-        <v>81872</v>
+        <v>81873</v>
       </c>
       <c r="F358" s="3">
         <v>46049</v>
@@ -9756,10 +9756,10 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E359" s="2">
-        <v>81896</v>
+        <v>81865</v>
       </c>
       <c r="F359" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>9</v>
@@ -9776,16 +9776,16 @@
         <v>29</v>
       </c>
       <c r="C360" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D360" s="3">
-        <v>46051.4046937153</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E360" s="2">
-        <v>81923</v>
+        <v>81870</v>
       </c>
       <c r="F360" s="3">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>9</v>
@@ -9802,16 +9802,16 @@
         <v>29</v>
       </c>
       <c r="C361" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D361" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E361" s="2">
-        <v>81998</v>
+        <v>81872</v>
       </c>
       <c r="F361" s="3">
-        <v>46057</v>
+        <v>46049</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>9</v>
@@ -9828,16 +9828,16 @@
         <v>29</v>
       </c>
       <c r="C362" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D362" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E362" s="2">
-        <v>82002</v>
+        <v>81896</v>
       </c>
       <c r="F362" s="3">
-        <v>46057</v>
+        <v>46050</v>
       </c>
       <c r="G362" s="1" t="s">
         <v>9</v>
@@ -9854,16 +9854,16 @@
         <v>29</v>
       </c>
       <c r="C363" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D363" s="3">
-        <v>46057.6959672917</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E363" s="2">
-        <v>82005</v>
+        <v>81923</v>
       </c>
       <c r="F363" s="3">
-        <v>46058</v>
+        <v>46051</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>9</v>
@@ -9886,10 +9886,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E364" s="2">
-        <v>82007</v>
+        <v>81998</v>
       </c>
       <c r="F364" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>9</v>
@@ -9906,16 +9906,16 @@
         <v>29</v>
       </c>
       <c r="C365" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D365" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E365" s="2">
-        <v>82005</v>
+        <v>82002</v>
       </c>
       <c r="F365" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>9</v>
@@ -9932,16 +9932,16 @@
         <v>29</v>
       </c>
       <c r="C366" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D366" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E366" s="2">
-        <v>82075</v>
+        <v>82005</v>
       </c>
       <c r="F366" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>9</v>
@@ -9958,16 +9958,16 @@
         <v>29</v>
       </c>
       <c r="C367" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D367" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E367" s="2">
-        <v>82077</v>
+        <v>82007</v>
       </c>
       <c r="F367" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>9</v>
@@ -9990,10 +9990,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E368" s="2">
-        <v>82099</v>
+        <v>82005</v>
       </c>
       <c r="F368" s="3">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>9</v>
@@ -10010,16 +10010,16 @@
         <v>29</v>
       </c>
       <c r="C369" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D369" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E369" s="2">
-        <v>82219</v>
+        <v>82075</v>
       </c>
       <c r="F369" s="3">
-        <v>46072</v>
+        <v>46063</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>9</v>
@@ -10036,16 +10036,16 @@
         <v>29</v>
       </c>
       <c r="C370" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D370" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E370" s="2">
-        <v>82230</v>
+        <v>82077</v>
       </c>
       <c r="F370" s="3">
-        <v>46073</v>
+        <v>46063</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>9</v>
@@ -10062,16 +10062,16 @@
         <v>29</v>
       </c>
       <c r="C371" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D371" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E371" s="2">
-        <v>82231</v>
+        <v>82099</v>
       </c>
       <c r="F371" s="3">
-        <v>46073</v>
+        <v>46064</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>9</v>
@@ -10088,16 +10088,16 @@
         <v>29</v>
       </c>
       <c r="C372" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D372" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E372" s="2">
-        <v>82388</v>
+        <v>82219</v>
       </c>
       <c r="F372" s="3">
-        <v>46083</v>
+        <v>46072</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>9</v>
@@ -10114,16 +10114,16 @@
         <v>29</v>
       </c>
       <c r="C373" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D373" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E373" s="2">
-        <v>82389</v>
+        <v>82230</v>
       </c>
       <c r="F373" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>9</v>
@@ -10140,16 +10140,16 @@
         <v>29</v>
       </c>
       <c r="C374" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D374" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E374" s="2">
-        <v>82396</v>
+        <v>82231</v>
       </c>
       <c r="F374" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>9</v>
@@ -10172,7 +10172,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E375" s="2">
-        <v>82397</v>
+        <v>82388</v>
       </c>
       <c r="F375" s="3">
         <v>46083</v>
@@ -10192,16 +10192,16 @@
         <v>29</v>
       </c>
       <c r="C376" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D376" s="3">
-        <v>46085.6249659838</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E376" s="2">
-        <v>82435</v>
+        <v>82389</v>
       </c>
       <c r="F376" s="3">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>9</v>
@@ -10218,16 +10218,16 @@
         <v>29</v>
       </c>
       <c r="C377" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D377" s="3">
-        <v>46091.449444456</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E377" s="2">
-        <v>82506</v>
+        <v>82396</v>
       </c>
       <c r="F377" s="3">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>9</v>
@@ -10244,16 +10244,16 @@
         <v>29</v>
       </c>
       <c r="C378" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D378" s="3">
-        <v>46091.4795702315</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E378" s="2">
-        <v>82509</v>
+        <v>82397</v>
       </c>
       <c r="F378" s="3">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>9</v>
@@ -10270,16 +10270,16 @@
         <v>29</v>
       </c>
       <c r="C379" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D379" s="3">
-        <v>46093.4969972338</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E379" s="2">
-        <v>82589</v>
+        <v>82435</v>
       </c>
       <c r="F379" s="3">
-        <v>46093</v>
+        <v>46085</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>9</v>
@@ -10290,22 +10290,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="380">
       <c r="A380" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C380" s="2">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D380" s="3">
-        <v>46029.3821391551</v>
+        <v>46091.449444456</v>
       </c>
       <c r="E380" s="2">
-        <v>81477</v>
+        <v>82506</v>
       </c>
       <c r="F380" s="3">
-        <v>46029</v>
+        <v>46091</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>9</v>
@@ -10316,22 +10316,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="381">
       <c r="A381" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C381" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D381" s="3">
-        <v>46030.4142968056</v>
+        <v>46091.4795702315</v>
       </c>
       <c r="E381" s="2">
-        <v>81532</v>
+        <v>82509</v>
       </c>
       <c r="F381" s="3">
-        <v>46030</v>
+        <v>46091</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>9</v>
@@ -10342,22 +10342,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="382">
       <c r="A382" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C382" s="2">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D382" s="3">
-        <v>46030.4142968056</v>
+        <v>46093.4969972338</v>
       </c>
       <c r="E382" s="2">
-        <v>81534</v>
+        <v>82589</v>
       </c>
       <c r="F382" s="3">
-        <v>46030</v>
+        <v>46093</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>9</v>
@@ -10374,16 +10374,16 @@
         <v>30</v>
       </c>
       <c r="C383" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D383" s="3">
-        <v>46030.4142968056</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E383" s="2">
-        <v>81535</v>
+        <v>81477</v>
       </c>
       <c r="F383" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>9</v>
@@ -10406,7 +10406,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E384" s="2">
-        <v>81550</v>
+        <v>81532</v>
       </c>
       <c r="F384" s="3">
         <v>46030</v>
@@ -10432,7 +10432,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E385" s="2">
-        <v>81553</v>
+        <v>81534</v>
       </c>
       <c r="F385" s="3">
         <v>46030</v>
@@ -10458,7 +10458,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E386" s="2">
-        <v>81554</v>
+        <v>81535</v>
       </c>
       <c r="F386" s="3">
         <v>46030</v>
@@ -10484,7 +10484,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E387" s="2">
-        <v>81557</v>
+        <v>81550</v>
       </c>
       <c r="F387" s="3">
         <v>46030</v>
@@ -10510,10 +10510,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E388" s="2">
-        <v>81588</v>
+        <v>81553</v>
       </c>
       <c r="F388" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>9</v>
@@ -10530,16 +10530,16 @@
         <v>30</v>
       </c>
       <c r="C389" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D389" s="3">
-        <v>46038.593985081</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E389" s="2">
-        <v>81692</v>
+        <v>81554</v>
       </c>
       <c r="F389" s="3">
-        <v>46038</v>
+        <v>46030</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>9</v>
@@ -10556,16 +10556,16 @@
         <v>30</v>
       </c>
       <c r="C390" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D390" s="3">
-        <v>46044.46462125</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E390" s="2">
-        <v>81786</v>
+        <v>81557</v>
       </c>
       <c r="F390" s="3">
-        <v>46044</v>
+        <v>46030</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>9</v>
@@ -10582,16 +10582,16 @@
         <v>30</v>
       </c>
       <c r="C391" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D391" s="3">
-        <v>46044.6362443171</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E391" s="2">
-        <v>81844</v>
+        <v>81588</v>
       </c>
       <c r="F391" s="3">
-        <v>46045</v>
+        <v>46031</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>9</v>
@@ -10608,16 +10608,16 @@
         <v>30</v>
       </c>
       <c r="C392" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D392" s="3">
-        <v>46062.717040544</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E392" s="2">
-        <v>82065</v>
+        <v>81692</v>
       </c>
       <c r="F392" s="3">
-        <v>46062</v>
+        <v>46038</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>9</v>
@@ -10634,16 +10634,16 @@
         <v>30</v>
       </c>
       <c r="C393" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D393" s="3">
-        <v>46062.717040544</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E393" s="2">
-        <v>82066</v>
+        <v>81786</v>
       </c>
       <c r="F393" s="3">
-        <v>46062</v>
+        <v>46044</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>9</v>
@@ -10660,16 +10660,16 @@
         <v>30</v>
       </c>
       <c r="C394" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D394" s="3">
-        <v>46062.717040544</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E394" s="2">
-        <v>82067</v>
+        <v>81844</v>
       </c>
       <c r="F394" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>9</v>
@@ -10686,16 +10686,16 @@
         <v>30</v>
       </c>
       <c r="C395" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D395" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E395" s="2">
-        <v>82190</v>
+        <v>82065</v>
       </c>
       <c r="F395" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>9</v>
@@ -10712,16 +10712,16 @@
         <v>30</v>
       </c>
       <c r="C396" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D396" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E396" s="2">
-        <v>82197</v>
+        <v>82066</v>
       </c>
       <c r="F396" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>9</v>
@@ -10738,16 +10738,16 @@
         <v>30</v>
       </c>
       <c r="C397" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D397" s="3">
-        <v>46077.5084780324</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E397" s="2">
-        <v>82270</v>
+        <v>82067</v>
       </c>
       <c r="F397" s="3">
-        <v>46077</v>
+        <v>46062</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>9</v>
@@ -10764,16 +10764,16 @@
         <v>30</v>
       </c>
       <c r="C398" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D398" s="3">
-        <v>46077.721037037</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E398" s="2">
-        <v>82285</v>
+        <v>82190</v>
       </c>
       <c r="F398" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>9</v>
@@ -10790,16 +10790,16 @@
         <v>30</v>
       </c>
       <c r="C399" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D399" s="3">
-        <v>46083.6694849421</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E399" s="2">
-        <v>82417</v>
+        <v>82197</v>
       </c>
       <c r="F399" s="3">
-        <v>46084</v>
+        <v>46066</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>9</v>
@@ -10816,16 +10816,16 @@
         <v>30</v>
       </c>
       <c r="C400" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D400" s="3">
-        <v>46085.7157723032</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E400" s="2">
-        <v>82457</v>
+        <v>82270</v>
       </c>
       <c r="F400" s="3">
-        <v>46086</v>
+        <v>46077</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>9</v>
@@ -10836,22 +10836,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="401">
       <c r="A401" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C401" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D401" s="3">
-        <v>46029.381258831</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E401" s="2">
-        <v>81484</v>
+        <v>82285</v>
       </c>
       <c r="F401" s="3">
-        <v>46029</v>
+        <v>46077</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10862,22 +10862,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="402">
       <c r="A402" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C402" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D402" s="3">
-        <v>46029.381258831</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E402" s="2">
-        <v>81486</v>
+        <v>82417</v>
       </c>
       <c r="F402" s="3">
-        <v>46029</v>
+        <v>46084</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10888,22 +10888,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="403">
       <c r="A403" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C403" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D403" s="3">
-        <v>46029.381258831</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E403" s="2">
-        <v>81487</v>
+        <v>82457</v>
       </c>
       <c r="F403" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10920,16 +10920,16 @@
         <v>31</v>
       </c>
       <c r="C404" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D404" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E404" s="2">
-        <v>81613</v>
+        <v>81484</v>
       </c>
       <c r="F404" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>9</v>
@@ -10946,16 +10946,16 @@
         <v>31</v>
       </c>
       <c r="C405" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D405" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E405" s="2">
-        <v>81614</v>
+        <v>81486</v>
       </c>
       <c r="F405" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>9</v>
@@ -10972,16 +10972,16 @@
         <v>31</v>
       </c>
       <c r="C406" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D406" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E406" s="2">
-        <v>81622</v>
+        <v>81487</v>
       </c>
       <c r="F406" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>9</v>
@@ -11004,7 +11004,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E407" s="2">
-        <v>81632</v>
+        <v>81613</v>
       </c>
       <c r="F407" s="3">
         <v>46036</v>
@@ -11030,10 +11030,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E408" s="2">
-        <v>81648</v>
+        <v>81614</v>
       </c>
       <c r="F408" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>9</v>
@@ -11056,10 +11056,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E409" s="2">
-        <v>81664</v>
+        <v>81622</v>
       </c>
       <c r="F409" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>9</v>
@@ -11076,16 +11076,16 @@
         <v>31</v>
       </c>
       <c r="C410" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D410" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E410" s="2">
-        <v>81815</v>
+        <v>81632</v>
       </c>
       <c r="F410" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11102,16 +11102,16 @@
         <v>31</v>
       </c>
       <c r="C411" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D411" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E411" s="2">
-        <v>81816</v>
+        <v>81648</v>
       </c>
       <c r="F411" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>9</v>
@@ -11128,16 +11128,16 @@
         <v>31</v>
       </c>
       <c r="C412" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D412" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E412" s="2">
-        <v>81838</v>
+        <v>81664</v>
       </c>
       <c r="F412" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11160,7 +11160,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E413" s="2">
-        <v>81840</v>
+        <v>81815</v>
       </c>
       <c r="F413" s="3">
         <v>46045</v>
@@ -11180,16 +11180,16 @@
         <v>31</v>
       </c>
       <c r="C414" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D414" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E414" s="2">
-        <v>81959</v>
+        <v>81816</v>
       </c>
       <c r="F414" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>9</v>
@@ -11206,16 +11206,16 @@
         <v>31</v>
       </c>
       <c r="C415" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D415" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E415" s="2">
-        <v>81960</v>
+        <v>81838</v>
       </c>
       <c r="F415" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>9</v>
@@ -11232,16 +11232,16 @@
         <v>31</v>
       </c>
       <c r="C416" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D416" s="3">
-        <v>46062.7151302546</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E416" s="2">
-        <v>82063</v>
+        <v>81840</v>
       </c>
       <c r="F416" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>9</v>
@@ -11258,16 +11258,16 @@
         <v>31</v>
       </c>
       <c r="C417" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D417" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E417" s="2">
-        <v>82064</v>
+        <v>81959</v>
       </c>
       <c r="F417" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>9</v>
@@ -11284,16 +11284,16 @@
         <v>31</v>
       </c>
       <c r="C418" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D418" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E418" s="2">
-        <v>82100</v>
+        <v>81960</v>
       </c>
       <c r="F418" s="3">
-        <v>46064</v>
+        <v>46055</v>
       </c>
       <c r="G418" s="1" t="s">
         <v>9</v>
@@ -11310,16 +11310,16 @@
         <v>31</v>
       </c>
       <c r="C419" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D419" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E419" s="2">
-        <v>82333</v>
+        <v>82063</v>
       </c>
       <c r="F419" s="3">
-        <v>46079</v>
+        <v>46062</v>
       </c>
       <c r="G419" s="1" t="s">
         <v>9</v>
@@ -11336,16 +11336,16 @@
         <v>31</v>
       </c>
       <c r="C420" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D420" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E420" s="2">
-        <v>82334</v>
+        <v>82064</v>
       </c>
       <c r="F420" s="3">
-        <v>46079</v>
+        <v>46062</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>9</v>
@@ -11362,16 +11362,16 @@
         <v>31</v>
       </c>
       <c r="C421" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D421" s="3">
-        <v>46076.7259125116</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E421" s="2">
-        <v>82258</v>
+        <v>82100</v>
       </c>
       <c r="F421" s="3">
-        <v>46076</v>
+        <v>46064</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>9</v>
@@ -11388,16 +11388,16 @@
         <v>31</v>
       </c>
       <c r="C422" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D422" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E422" s="2">
-        <v>82259</v>
+        <v>82333</v>
       </c>
       <c r="F422" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>9</v>
@@ -11414,16 +11414,16 @@
         <v>31</v>
       </c>
       <c r="C423" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D423" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E423" s="2">
-        <v>82260</v>
+        <v>82334</v>
       </c>
       <c r="F423" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>9</v>
@@ -11446,10 +11446,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E424" s="2">
-        <v>82274</v>
+        <v>82258</v>
       </c>
       <c r="F424" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>9</v>
@@ -11466,16 +11466,16 @@
         <v>31</v>
       </c>
       <c r="C425" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D425" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E425" s="2">
-        <v>82409</v>
+        <v>82259</v>
       </c>
       <c r="F425" s="3">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>9</v>
@@ -11492,22 +11492,22 @@
         <v>31</v>
       </c>
       <c r="C426" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D426" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E426" s="2">
-        <v>82581</v>
+        <v>82260</v>
       </c>
       <c r="F426" s="3">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H426" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="427">
@@ -11518,16 +11518,16 @@
         <v>31</v>
       </c>
       <c r="C427" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D427" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E427" s="2">
-        <v>82582</v>
+        <v>82274</v>
       </c>
       <c r="F427" s="3">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11544,68 +11544,68 @@
         <v>31</v>
       </c>
       <c r="C428" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D428" s="3">
-        <v>46093.4920058565</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E428" s="2">
-        <v>82583</v>
+        <v>82409</v>
       </c>
       <c r="F428" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="429">
       <c r="A429" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C429" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D429" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E429" s="2">
-        <v>81608</v>
+        <v>82581</v>
       </c>
       <c r="F429" s="3">
-        <v>46035</v>
+        <v>46093</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="430">
       <c r="A430" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C430" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D430" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E430" s="2">
-        <v>81609</v>
+        <v>82582</v>
       </c>
       <c r="F430" s="3">
-        <v>46035</v>
+        <v>46093</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>9</v>
@@ -11616,48 +11616,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="431">
       <c r="A431" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C431" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D431" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E431" s="2">
-        <v>81610</v>
+        <v>82583</v>
       </c>
       <c r="F431" s="3">
-        <v>46035</v>
+        <v>46093</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="432">
       <c r="A432" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C432" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D432" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E432" s="2">
-        <v>81611</v>
+        <v>82672</v>
       </c>
       <c r="F432" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11680,7 +11680,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E433" s="2">
-        <v>81612</v>
+        <v>81608</v>
       </c>
       <c r="F433" s="3">
         <v>46035</v>
@@ -11700,16 +11700,16 @@
         <v>32</v>
       </c>
       <c r="C434" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D434" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E434" s="2">
-        <v>81652</v>
+        <v>81609</v>
       </c>
       <c r="F434" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>9</v>
@@ -11726,16 +11726,16 @@
         <v>32</v>
       </c>
       <c r="C435" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D435" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E435" s="2">
-        <v>81659</v>
+        <v>81610</v>
       </c>
       <c r="F435" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>9</v>
@@ -11752,16 +11752,16 @@
         <v>32</v>
       </c>
       <c r="C436" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D436" s="3">
-        <v>46048.6509980093</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E436" s="2">
-        <v>81853</v>
+        <v>81611</v>
       </c>
       <c r="F436" s="3">
-        <v>46048</v>
+        <v>46035</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>9</v>
@@ -11778,16 +11778,16 @@
         <v>32</v>
       </c>
       <c r="C437" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D437" s="3">
-        <v>46048.6509980093</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E437" s="2">
-        <v>81869</v>
+        <v>81612</v>
       </c>
       <c r="F437" s="3">
-        <v>46049</v>
+        <v>46035</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>9</v>
@@ -11804,16 +11804,16 @@
         <v>32</v>
       </c>
       <c r="C438" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D438" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E438" s="2">
-        <v>81890</v>
+        <v>81652</v>
       </c>
       <c r="F438" s="3">
-        <v>46050</v>
+        <v>46037</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11830,16 +11830,16 @@
         <v>32</v>
       </c>
       <c r="C439" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D439" s="3">
-        <v>46049.4871256134</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E439" s="2">
-        <v>81875</v>
+        <v>81659</v>
       </c>
       <c r="F439" s="3">
-        <v>46049</v>
+        <v>46037</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11856,16 +11856,16 @@
         <v>32</v>
       </c>
       <c r="C440" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D440" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E440" s="2">
-        <v>81881</v>
+        <v>81853</v>
       </c>
       <c r="F440" s="3">
-        <v>46050</v>
+        <v>46048</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>9</v>
@@ -11882,16 +11882,16 @@
         <v>32</v>
       </c>
       <c r="C441" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D441" s="3">
-        <v>46056.7073643981</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E441" s="2">
-        <v>82015</v>
+        <v>81869</v>
       </c>
       <c r="F441" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11908,16 +11908,16 @@
         <v>32</v>
       </c>
       <c r="C442" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D442" s="3">
-        <v>46056.7073643981</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E442" s="2">
-        <v>82017</v>
+        <v>81890</v>
       </c>
       <c r="F442" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11934,16 +11934,16 @@
         <v>32</v>
       </c>
       <c r="C443" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D443" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E443" s="2">
-        <v>82020</v>
+        <v>81875</v>
       </c>
       <c r="F443" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11960,16 +11960,16 @@
         <v>32</v>
       </c>
       <c r="C444" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D444" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E444" s="2">
-        <v>82023</v>
+        <v>81881</v>
       </c>
       <c r="F444" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11992,10 +11992,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E445" s="2">
-        <v>82061</v>
+        <v>82015</v>
       </c>
       <c r="F445" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>9</v>
@@ -12018,10 +12018,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E446" s="2">
-        <v>82081</v>
+        <v>82017</v>
       </c>
       <c r="F446" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>9</v>
@@ -12044,10 +12044,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E447" s="2">
-        <v>82095</v>
+        <v>82020</v>
       </c>
       <c r="F447" s="3">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>9</v>
@@ -12064,16 +12064,16 @@
         <v>32</v>
       </c>
       <c r="C448" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D448" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E448" s="2">
-        <v>82081</v>
+        <v>82023</v>
       </c>
       <c r="F448" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12090,16 +12090,16 @@
         <v>32</v>
       </c>
       <c r="C449" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D449" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E449" s="2">
-        <v>82107</v>
+        <v>82061</v>
       </c>
       <c r="F449" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12116,16 +12116,16 @@
         <v>32</v>
       </c>
       <c r="C450" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D450" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E450" s="2">
-        <v>82112</v>
+        <v>82081</v>
       </c>
       <c r="F450" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12142,13 +12142,13 @@
         <v>32</v>
       </c>
       <c r="C451" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D451" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E451" s="2">
-        <v>82113</v>
+        <v>82095</v>
       </c>
       <c r="F451" s="3">
         <v>46064</v>
@@ -12174,10 +12174,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E452" s="2">
-        <v>82123</v>
+        <v>82081</v>
       </c>
       <c r="F452" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12194,13 +12194,13 @@
         <v>32</v>
       </c>
       <c r="C453" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D453" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E453" s="2">
-        <v>82095</v>
+        <v>82107</v>
       </c>
       <c r="F453" s="3">
         <v>46064</v>
@@ -12220,13 +12220,13 @@
         <v>32</v>
       </c>
       <c r="C454" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D454" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E454" s="2">
-        <v>82106</v>
+        <v>82112</v>
       </c>
       <c r="F454" s="3">
         <v>46064</v>
@@ -12246,13 +12246,13 @@
         <v>32</v>
       </c>
       <c r="C455" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D455" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E455" s="2">
-        <v>82107</v>
+        <v>82113</v>
       </c>
       <c r="F455" s="3">
         <v>46064</v>
@@ -12272,16 +12272,16 @@
         <v>32</v>
       </c>
       <c r="C456" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D456" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E456" s="2">
-        <v>82109</v>
+        <v>82123</v>
       </c>
       <c r="F456" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12304,7 +12304,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E457" s="2">
-        <v>82110</v>
+        <v>82095</v>
       </c>
       <c r="F457" s="3">
         <v>46064</v>
@@ -12330,10 +12330,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E458" s="2">
-        <v>82139</v>
+        <v>82106</v>
       </c>
       <c r="F458" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12350,16 +12350,16 @@
         <v>32</v>
       </c>
       <c r="C459" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D459" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E459" s="2">
-        <v>82365</v>
+        <v>82107</v>
       </c>
       <c r="F459" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12376,16 +12376,16 @@
         <v>32</v>
       </c>
       <c r="C460" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D460" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E460" s="2">
-        <v>82366</v>
+        <v>82109</v>
       </c>
       <c r="F460" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12402,16 +12402,16 @@
         <v>32</v>
       </c>
       <c r="C461" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D461" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E461" s="2">
-        <v>82371</v>
+        <v>82110</v>
       </c>
       <c r="F461" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12428,16 +12428,16 @@
         <v>32</v>
       </c>
       <c r="C462" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D462" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E462" s="2">
-        <v>82383</v>
+        <v>82139</v>
       </c>
       <c r="F462" s="3">
-        <v>46083</v>
+        <v>46065</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12460,10 +12460,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E463" s="2">
-        <v>82384</v>
+        <v>82365</v>
       </c>
       <c r="F463" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12474,48 +12474,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="464">
       <c r="A464" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C464" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D464" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E464" s="2">
-        <v>81592</v>
+        <v>82366</v>
       </c>
       <c r="F464" s="3">
-        <v>46031</v>
+        <v>46080</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H464" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="465">
       <c r="A465" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C465" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D465" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E465" s="2">
-        <v>81593</v>
+        <v>82371</v>
       </c>
       <c r="F465" s="3">
-        <v>46031</v>
+        <v>46080</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>9</v>
@@ -12526,22 +12526,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="466">
       <c r="A466" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C466" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D466" s="3">
-        <v>46038.6827563889</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E466" s="2">
-        <v>81697</v>
+        <v>82383</v>
       </c>
       <c r="F466" s="3">
-        <v>46038</v>
+        <v>46083</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12552,28 +12552,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="467">
       <c r="A467" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C467" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D467" s="3">
-        <v>46038.6827563889</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E467" s="2">
-        <v>81735</v>
+        <v>82384</v>
       </c>
       <c r="F467" s="3">
-        <v>46041</v>
+        <v>46083</v>
       </c>
       <c r="G467" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H467" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="468">
@@ -12584,39 +12584,39 @@
         <v>33</v>
       </c>
       <c r="C468" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D468" s="3">
-        <v>46045.4532476157</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E468" s="2">
-        <v>81823</v>
+        <v>81592</v>
       </c>
       <c r="F468" s="3">
-        <v>46045</v>
+        <v>46031</v>
       </c>
       <c r="G468" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H468" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="469">
       <c r="A469" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C469" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D469" s="3">
-        <v>46031.4724550926</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E469" s="2">
-        <v>81572</v>
+        <v>81593</v>
       </c>
       <c r="F469" s="3">
         <v>46031</v>
@@ -12630,22 +12630,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="470">
       <c r="A470" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C470" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D470" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E470" s="2">
-        <v>81573</v>
+        <v>81697</v>
       </c>
       <c r="F470" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>9</v>
@@ -12656,48 +12656,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="471">
       <c r="A471" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C471" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D471" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E471" s="2">
-        <v>81579</v>
+        <v>81735</v>
       </c>
       <c r="F471" s="3">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="G471" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H471" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="472">
       <c r="A472" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C472" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D472" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E472" s="2">
-        <v>81580</v>
+        <v>81823</v>
       </c>
       <c r="F472" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12720,7 +12720,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E473" s="2">
-        <v>81581</v>
+        <v>81572</v>
       </c>
       <c r="F473" s="3">
         <v>46031</v>
@@ -12746,7 +12746,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E474" s="2">
-        <v>81582</v>
+        <v>81573</v>
       </c>
       <c r="F474" s="3">
         <v>46031</v>
@@ -12772,7 +12772,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E475" s="2">
-        <v>81583</v>
+        <v>81579</v>
       </c>
       <c r="F475" s="3">
         <v>46031</v>
@@ -12792,16 +12792,16 @@
         <v>34</v>
       </c>
       <c r="C476" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D476" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E476" s="2">
-        <v>81667</v>
+        <v>81580</v>
       </c>
       <c r="F476" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>9</v>
@@ -12818,16 +12818,16 @@
         <v>34</v>
       </c>
       <c r="C477" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D477" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E477" s="2">
-        <v>81668</v>
+        <v>81581</v>
       </c>
       <c r="F477" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>9</v>
@@ -12844,16 +12844,16 @@
         <v>34</v>
       </c>
       <c r="C478" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D478" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E478" s="2">
-        <v>81674</v>
+        <v>81582</v>
       </c>
       <c r="F478" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12870,16 +12870,16 @@
         <v>34</v>
       </c>
       <c r="C479" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D479" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E479" s="2">
-        <v>81675</v>
+        <v>81583</v>
       </c>
       <c r="F479" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12902,10 +12902,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E480" s="2">
-        <v>81677</v>
+        <v>81667</v>
       </c>
       <c r="F480" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>9</v>
@@ -12922,16 +12922,16 @@
         <v>34</v>
       </c>
       <c r="C481" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D481" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E481" s="2">
-        <v>81739</v>
+        <v>81668</v>
       </c>
       <c r="F481" s="3">
-        <v>46041</v>
+        <v>46037</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>9</v>
@@ -12948,16 +12948,16 @@
         <v>34</v>
       </c>
       <c r="C482" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D482" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E482" s="2">
-        <v>81741</v>
+        <v>81674</v>
       </c>
       <c r="F482" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12974,16 +12974,16 @@
         <v>34</v>
       </c>
       <c r="C483" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D483" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E483" s="2">
-        <v>81854</v>
+        <v>81675</v>
       </c>
       <c r="F483" s="3">
-        <v>46048</v>
+        <v>46038</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>9</v>
@@ -13000,16 +13000,16 @@
         <v>34</v>
       </c>
       <c r="C484" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D484" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E484" s="2">
-        <v>81855</v>
+        <v>81677</v>
       </c>
       <c r="F484" s="3">
-        <v>46048</v>
+        <v>46038</v>
       </c>
       <c r="G484" s="1" t="s">
         <v>9</v>
@@ -13026,16 +13026,16 @@
         <v>34</v>
       </c>
       <c r="C485" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D485" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E485" s="2">
-        <v>81858</v>
+        <v>81739</v>
       </c>
       <c r="F485" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>9</v>
@@ -13052,16 +13052,16 @@
         <v>34</v>
       </c>
       <c r="C486" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D486" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E486" s="2">
-        <v>81859</v>
+        <v>81741</v>
       </c>
       <c r="F486" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>9</v>
@@ -13084,10 +13084,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E487" s="2">
-        <v>81862</v>
+        <v>81854</v>
       </c>
       <c r="F487" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>9</v>
@@ -13110,10 +13110,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E488" s="2">
-        <v>81863</v>
+        <v>81855</v>
       </c>
       <c r="F488" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>9</v>
@@ -13130,16 +13130,16 @@
         <v>34</v>
       </c>
       <c r="C489" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D489" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E489" s="2">
-        <v>81958</v>
+        <v>81858</v>
       </c>
       <c r="F489" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>9</v>
@@ -13156,16 +13156,16 @@
         <v>34</v>
       </c>
       <c r="C490" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D490" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E490" s="2">
-        <v>81965</v>
+        <v>81859</v>
       </c>
       <c r="F490" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>9</v>
@@ -13182,16 +13182,16 @@
         <v>34</v>
       </c>
       <c r="C491" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D491" s="3">
-        <v>46063.5923590625</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E491" s="2">
-        <v>82085</v>
+        <v>81862</v>
       </c>
       <c r="F491" s="3">
-        <v>46063</v>
+        <v>46049</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>9</v>
@@ -13208,16 +13208,16 @@
         <v>34</v>
       </c>
       <c r="C492" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D492" s="3">
-        <v>46063.5923590625</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E492" s="2">
-        <v>82086</v>
+        <v>81863</v>
       </c>
       <c r="F492" s="3">
-        <v>46063</v>
+        <v>46049</v>
       </c>
       <c r="G492" s="1" t="s">
         <v>9</v>
@@ -13234,16 +13234,16 @@
         <v>34</v>
       </c>
       <c r="C493" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D493" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E493" s="2">
-        <v>82126</v>
+        <v>81958</v>
       </c>
       <c r="F493" s="3">
-        <v>46065</v>
+        <v>46055</v>
       </c>
       <c r="G493" s="1" t="s">
         <v>9</v>
@@ -13260,16 +13260,16 @@
         <v>34</v>
       </c>
       <c r="C494" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D494" s="3">
-        <v>46064.5127051505</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E494" s="2">
-        <v>82268</v>
+        <v>81965</v>
       </c>
       <c r="F494" s="3">
-        <v>46077</v>
+        <v>46055</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>9</v>
@@ -13286,16 +13286,16 @@
         <v>34</v>
       </c>
       <c r="C495" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D495" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E495" s="2">
-        <v>82142</v>
+        <v>82085</v>
       </c>
       <c r="F495" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>9</v>
@@ -13312,16 +13312,16 @@
         <v>34</v>
       </c>
       <c r="C496" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D496" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E496" s="2">
-        <v>82143</v>
+        <v>82086</v>
       </c>
       <c r="F496" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G496" s="1" t="s">
         <v>9</v>
@@ -13338,13 +13338,13 @@
         <v>34</v>
       </c>
       <c r="C497" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D497" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E497" s="2">
-        <v>82144</v>
+        <v>82126</v>
       </c>
       <c r="F497" s="3">
         <v>46065</v>
@@ -13364,16 +13364,16 @@
         <v>34</v>
       </c>
       <c r="C498" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D498" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E498" s="2">
-        <v>82166</v>
+        <v>82268</v>
       </c>
       <c r="F498" s="3">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="G498" s="1" t="s">
         <v>9</v>
@@ -13390,16 +13390,16 @@
         <v>34</v>
       </c>
       <c r="C499" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D499" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E499" s="2">
-        <v>82262</v>
+        <v>82142</v>
       </c>
       <c r="F499" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>9</v>
@@ -13416,16 +13416,16 @@
         <v>34</v>
       </c>
       <c r="C500" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D500" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E500" s="2">
-        <v>82265</v>
+        <v>82143</v>
       </c>
       <c r="F500" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G500" s="1" t="s">
         <v>9</v>
@@ -13442,16 +13442,16 @@
         <v>34</v>
       </c>
       <c r="C501" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D501" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E501" s="2">
-        <v>82281</v>
+        <v>82144</v>
       </c>
       <c r="F501" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G501" s="1" t="s">
         <v>9</v>
@@ -13468,16 +13468,16 @@
         <v>34</v>
       </c>
       <c r="C502" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D502" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E502" s="2">
-        <v>82282</v>
+        <v>82166</v>
       </c>
       <c r="F502" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G502" s="1" t="s">
         <v>9</v>
@@ -13494,16 +13494,16 @@
         <v>34</v>
       </c>
       <c r="C503" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D503" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E503" s="2">
-        <v>82340</v>
+        <v>82262</v>
       </c>
       <c r="F503" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G503" s="1" t="s">
         <v>9</v>
@@ -13520,16 +13520,16 @@
         <v>34</v>
       </c>
       <c r="C504" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D504" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E504" s="2">
-        <v>82399</v>
+        <v>82265</v>
       </c>
       <c r="F504" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>9</v>
@@ -13546,16 +13546,16 @@
         <v>34</v>
       </c>
       <c r="C505" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D505" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E505" s="2">
-        <v>82400</v>
+        <v>82281</v>
       </c>
       <c r="F505" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G505" s="1" t="s">
         <v>9</v>
@@ -13572,16 +13572,16 @@
         <v>34</v>
       </c>
       <c r="C506" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D506" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E506" s="2">
-        <v>82401</v>
+        <v>82282</v>
       </c>
       <c r="F506" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>9</v>
@@ -13598,16 +13598,16 @@
         <v>34</v>
       </c>
       <c r="C507" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D507" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E507" s="2">
-        <v>82412</v>
+        <v>82340</v>
       </c>
       <c r="F507" s="3">
-        <v>46084</v>
+        <v>46079</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>9</v>
@@ -13630,10 +13630,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E508" s="2">
-        <v>82415</v>
+        <v>82399</v>
       </c>
       <c r="F508" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G508" s="1" t="s">
         <v>9</v>
@@ -13650,16 +13650,16 @@
         <v>34</v>
       </c>
       <c r="C509" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D509" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E509" s="2">
-        <v>82571</v>
+        <v>82400</v>
       </c>
       <c r="F509" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G509" s="1" t="s">
         <v>9</v>
@@ -13676,16 +13676,16 @@
         <v>34</v>
       </c>
       <c r="C510" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D510" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E510" s="2">
-        <v>82572</v>
+        <v>82401</v>
       </c>
       <c r="F510" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G510" s="1" t="s">
         <v>9</v>
@@ -13702,16 +13702,16 @@
         <v>34</v>
       </c>
       <c r="C511" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D511" s="3">
-        <v>46094.4745190394</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E511" s="2">
-        <v>82630</v>
+        <v>82412</v>
       </c>
       <c r="F511" s="3">
-        <v>46094</v>
+        <v>46084</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>9</v>
@@ -13728,22 +13728,22 @@
         <v>34</v>
       </c>
       <c r="C512" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D512" s="3">
-        <v>46094.4745190394</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E512" s="2">
-        <v>82631</v>
+        <v>82415</v>
       </c>
       <c r="F512" s="3">
-        <v>46094</v>
+        <v>46084</v>
       </c>
       <c r="G512" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="513">
@@ -13754,16 +13754,16 @@
         <v>34</v>
       </c>
       <c r="C513" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D513" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E513" s="2">
-        <v>82632</v>
+        <v>82571</v>
       </c>
       <c r="F513" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G513" s="1" t="s">
         <v>9</v>
@@ -13780,16 +13780,16 @@
         <v>34</v>
       </c>
       <c r="C514" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D514" s="3">
-        <v>46097.4499278356</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E514" s="2">
-        <v>82653</v>
+        <v>82572</v>
       </c>
       <c r="F514" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G514" s="1" t="s">
         <v>9</v>
@@ -13800,22 +13800,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="515">
       <c r="A515" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C515" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D515" s="3">
-        <v>46078.6702738773</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E515" s="2">
-        <v>82311</v>
+        <v>82630</v>
       </c>
       <c r="F515" s="3">
-        <v>46078</v>
+        <v>46094</v>
       </c>
       <c r="G515" s="1" t="s">
         <v>9</v>
@@ -13826,48 +13826,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="516">
       <c r="A516" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C516" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D516" s="3">
-        <v>46078.6702738773</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E516" s="2">
-        <v>82312</v>
+        <v>82631</v>
       </c>
       <c r="F516" s="3">
-        <v>46078</v>
+        <v>46094</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="517">
       <c r="A517" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C517" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D517" s="3">
-        <v>46078.6702738773</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E517" s="2">
-        <v>82313</v>
+        <v>82632</v>
       </c>
       <c r="F517" s="3">
-        <v>46078</v>
+        <v>46094</v>
       </c>
       <c r="G517" s="1" t="s">
         <v>9</v>
@@ -13878,22 +13878,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="518">
       <c r="A518" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C518" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D518" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E518" s="2">
-        <v>82314</v>
+        <v>82653</v>
       </c>
       <c r="F518" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>9</v>
@@ -13904,22 +13904,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="519">
       <c r="A519" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C519" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D519" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E519" s="2">
-        <v>82346</v>
+        <v>82665</v>
       </c>
       <c r="F519" s="3">
-        <v>46080</v>
+        <v>46097</v>
       </c>
       <c r="G519" s="1" t="s">
         <v>9</v>
@@ -13930,28 +13930,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="520">
       <c r="A520" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C520" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D520" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E520" s="2">
-        <v>82361</v>
+        <v>82668</v>
       </c>
       <c r="F520" s="3">
-        <v>46080</v>
+        <v>46097</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="521">
@@ -13968,10 +13968,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E521" s="2">
-        <v>82385</v>
+        <v>82311</v>
       </c>
       <c r="F521" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G521" s="1" t="s">
         <v>9</v>
@@ -13994,10 +13994,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E522" s="2">
-        <v>82391</v>
+        <v>82312</v>
       </c>
       <c r="F522" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G522" s="1" t="s">
         <v>9</v>
@@ -14020,10 +14020,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E523" s="2">
-        <v>82392</v>
+        <v>82313</v>
       </c>
       <c r="F523" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>9</v>
@@ -14034,22 +14034,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="524">
       <c r="A524" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C524" s="2">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D524" s="3">
-        <v>46029.4632696412</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E524" s="2">
-        <v>81495</v>
+        <v>82314</v>
       </c>
       <c r="F524" s="3">
-        <v>46029</v>
+        <v>46078</v>
       </c>
       <c r="G524" s="1" t="s">
         <v>9</v>
@@ -14060,27 +14060,183 @@
     </row>
     <row ht="12.75" customHeight="1" r="525">
       <c r="A525" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C525" s="2">
+        <v>1</v>
+      </c>
+      <c r="D525" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E525" s="2">
+        <v>82346</v>
+      </c>
+      <c r="F525" s="3">
+        <v>46080</v>
+      </c>
+      <c r="G525" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H525" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="526">
+      <c r="A526" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C526" s="2">
+        <v>1</v>
+      </c>
+      <c r="D526" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E526" s="2">
+        <v>82361</v>
+      </c>
+      <c r="F526" s="3">
+        <v>46080</v>
+      </c>
+      <c r="G526" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H526" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="527">
+      <c r="A527" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C527" s="2">
+        <v>1</v>
+      </c>
+      <c r="D527" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E527" s="2">
+        <v>82385</v>
+      </c>
+      <c r="F527" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G527" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H527" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="528">
+      <c r="A528" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C528" s="2">
+        <v>1</v>
+      </c>
+      <c r="D528" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E528" s="2">
+        <v>82391</v>
+      </c>
+      <c r="F528" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G528" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H528" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="529">
+      <c r="A529" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C529" s="2">
+        <v>1</v>
+      </c>
+      <c r="D529" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E529" s="2">
+        <v>82392</v>
+      </c>
+      <c r="F529" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G529" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H529" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="530">
+      <c r="A530" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C530" s="2">
+        <v>62</v>
+      </c>
+      <c r="D530" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E530" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F530" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G530" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H530" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="531">
+      <c r="A531" s="2">
         <v>9992</v>
       </c>
-      <c r="B525" s="1" t="s">
+      <c r="B531" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C525" s="2">
+      <c r="C531" s="2">
         <v>390</v>
       </c>
-      <c r="D525" s="3">
+      <c r="D531" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E525" s="2">
+      <c r="E531" s="2">
         <v>81684</v>
       </c>
-      <c r="F525" s="3">
+      <c r="F531" s="3">
         <v>46038</v>
       </c>
-      <c r="G525" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H525" s="1" t="s">
+      <c r="G531" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H531" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -420,7 +420,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H531"/>
+  <dimension ref="A1:H532"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -11668,22 +11668,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="433">
       <c r="A433" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C433" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D433" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E433" s="2">
-        <v>81608</v>
+        <v>82674</v>
       </c>
       <c r="F433" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11706,7 +11706,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E434" s="2">
-        <v>81609</v>
+        <v>81608</v>
       </c>
       <c r="F434" s="3">
         <v>46035</v>
@@ -11732,7 +11732,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E435" s="2">
-        <v>81610</v>
+        <v>81609</v>
       </c>
       <c r="F435" s="3">
         <v>46035</v>
@@ -11758,7 +11758,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E436" s="2">
-        <v>81611</v>
+        <v>81610</v>
       </c>
       <c r="F436" s="3">
         <v>46035</v>
@@ -11784,7 +11784,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E437" s="2">
-        <v>81612</v>
+        <v>81611</v>
       </c>
       <c r="F437" s="3">
         <v>46035</v>
@@ -11804,16 +11804,16 @@
         <v>32</v>
       </c>
       <c r="C438" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D438" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E438" s="2">
-        <v>81652</v>
+        <v>81612</v>
       </c>
       <c r="F438" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11836,7 +11836,7 @@
         <v>46036.6342081481</v>
       </c>
       <c r="E439" s="2">
-        <v>81659</v>
+        <v>81652</v>
       </c>
       <c r="F439" s="3">
         <v>46037</v>
@@ -11856,16 +11856,16 @@
         <v>32</v>
       </c>
       <c r="C440" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D440" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E440" s="2">
-        <v>81853</v>
+        <v>81659</v>
       </c>
       <c r="F440" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>9</v>
@@ -11888,10 +11888,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E441" s="2">
-        <v>81869</v>
+        <v>81853</v>
       </c>
       <c r="F441" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11914,10 +11914,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E442" s="2">
-        <v>81890</v>
+        <v>81869</v>
       </c>
       <c r="F442" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11934,16 +11934,16 @@
         <v>32</v>
       </c>
       <c r="C443" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D443" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E443" s="2">
-        <v>81875</v>
+        <v>81890</v>
       </c>
       <c r="F443" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11966,10 +11966,10 @@
         <v>46049.4871256134</v>
       </c>
       <c r="E444" s="2">
-        <v>81881</v>
+        <v>81875</v>
       </c>
       <c r="F444" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11986,16 +11986,16 @@
         <v>32</v>
       </c>
       <c r="C445" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D445" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E445" s="2">
-        <v>82015</v>
+        <v>81881</v>
       </c>
       <c r="F445" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>9</v>
@@ -12018,7 +12018,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E446" s="2">
-        <v>82017</v>
+        <v>82015</v>
       </c>
       <c r="F446" s="3">
         <v>46058</v>
@@ -12044,7 +12044,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E447" s="2">
-        <v>82020</v>
+        <v>82017</v>
       </c>
       <c r="F447" s="3">
         <v>46058</v>
@@ -12070,7 +12070,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E448" s="2">
-        <v>82023</v>
+        <v>82020</v>
       </c>
       <c r="F448" s="3">
         <v>46058</v>
@@ -12096,10 +12096,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E449" s="2">
-        <v>82061</v>
+        <v>82023</v>
       </c>
       <c r="F449" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12122,10 +12122,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E450" s="2">
-        <v>82081</v>
+        <v>82061</v>
       </c>
       <c r="F450" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12148,10 +12148,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E451" s="2">
-        <v>82095</v>
+        <v>82081</v>
       </c>
       <c r="F451" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>9</v>
@@ -12168,16 +12168,16 @@
         <v>32</v>
       </c>
       <c r="C452" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D452" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E452" s="2">
-        <v>82081</v>
+        <v>82095</v>
       </c>
       <c r="F452" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12200,10 +12200,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E453" s="2">
-        <v>82107</v>
+        <v>82081</v>
       </c>
       <c r="F453" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>9</v>
@@ -12226,7 +12226,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E454" s="2">
-        <v>82112</v>
+        <v>82107</v>
       </c>
       <c r="F454" s="3">
         <v>46064</v>
@@ -12252,7 +12252,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E455" s="2">
-        <v>82113</v>
+        <v>82112</v>
       </c>
       <c r="F455" s="3">
         <v>46064</v>
@@ -12278,10 +12278,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E456" s="2">
-        <v>82123</v>
+        <v>82113</v>
       </c>
       <c r="F456" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12298,16 +12298,16 @@
         <v>32</v>
       </c>
       <c r="C457" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D457" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E457" s="2">
-        <v>82095</v>
+        <v>82123</v>
       </c>
       <c r="F457" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>9</v>
@@ -12330,7 +12330,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E458" s="2">
-        <v>82106</v>
+        <v>82095</v>
       </c>
       <c r="F458" s="3">
         <v>46064</v>
@@ -12356,7 +12356,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E459" s="2">
-        <v>82107</v>
+        <v>82106</v>
       </c>
       <c r="F459" s="3">
         <v>46064</v>
@@ -12382,7 +12382,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E460" s="2">
-        <v>82109</v>
+        <v>82107</v>
       </c>
       <c r="F460" s="3">
         <v>46064</v>
@@ -12408,7 +12408,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E461" s="2">
-        <v>82110</v>
+        <v>82109</v>
       </c>
       <c r="F461" s="3">
         <v>46064</v>
@@ -12434,10 +12434,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E462" s="2">
-        <v>82139</v>
+        <v>82110</v>
       </c>
       <c r="F462" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12454,16 +12454,16 @@
         <v>32</v>
       </c>
       <c r="C463" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D463" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E463" s="2">
-        <v>82365</v>
+        <v>82139</v>
       </c>
       <c r="F463" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12486,7 +12486,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E464" s="2">
-        <v>82366</v>
+        <v>82365</v>
       </c>
       <c r="F464" s="3">
         <v>46080</v>
@@ -12512,7 +12512,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E465" s="2">
-        <v>82371</v>
+        <v>82366</v>
       </c>
       <c r="F465" s="3">
         <v>46080</v>
@@ -12538,10 +12538,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E466" s="2">
-        <v>82383</v>
+        <v>82371</v>
       </c>
       <c r="F466" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12564,7 +12564,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E467" s="2">
-        <v>82384</v>
+        <v>82383</v>
       </c>
       <c r="F467" s="3">
         <v>46083</v>
@@ -12578,28 +12578,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="468">
       <c r="A468" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C468" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D468" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E468" s="2">
-        <v>81592</v>
+        <v>82384</v>
       </c>
       <c r="F468" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="G468" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H468" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="469">
@@ -12616,16 +12616,16 @@
         <v>46029.4149454282</v>
       </c>
       <c r="E469" s="2">
-        <v>81593</v>
+        <v>81592</v>
       </c>
       <c r="F469" s="3">
         <v>46031</v>
       </c>
       <c r="G469" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H469" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="470">
@@ -12636,16 +12636,16 @@
         <v>33</v>
       </c>
       <c r="C470" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D470" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E470" s="2">
-        <v>81697</v>
+        <v>81593</v>
       </c>
       <c r="F470" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>9</v>
@@ -12668,16 +12668,16 @@
         <v>46038.6827563889</v>
       </c>
       <c r="E471" s="2">
-        <v>81735</v>
+        <v>81697</v>
       </c>
       <c r="F471" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G471" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H471" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="472">
@@ -12688,42 +12688,42 @@
         <v>33</v>
       </c>
       <c r="C472" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D472" s="3">
-        <v>46045.4532476157</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E472" s="2">
-        <v>81823</v>
+        <v>81735</v>
       </c>
       <c r="F472" s="3">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="G472" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H472" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="473">
       <c r="A473" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C473" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D473" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E473" s="2">
-        <v>81572</v>
+        <v>81823</v>
       </c>
       <c r="F473" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12746,7 +12746,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E474" s="2">
-        <v>81573</v>
+        <v>81572</v>
       </c>
       <c r="F474" s="3">
         <v>46031</v>
@@ -12772,7 +12772,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E475" s="2">
-        <v>81579</v>
+        <v>81573</v>
       </c>
       <c r="F475" s="3">
         <v>46031</v>
@@ -12798,7 +12798,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E476" s="2">
-        <v>81580</v>
+        <v>81579</v>
       </c>
       <c r="F476" s="3">
         <v>46031</v>
@@ -12824,7 +12824,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E477" s="2">
-        <v>81581</v>
+        <v>81580</v>
       </c>
       <c r="F477" s="3">
         <v>46031</v>
@@ -12850,7 +12850,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E478" s="2">
-        <v>81582</v>
+        <v>81581</v>
       </c>
       <c r="F478" s="3">
         <v>46031</v>
@@ -12876,7 +12876,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E479" s="2">
-        <v>81583</v>
+        <v>81582</v>
       </c>
       <c r="F479" s="3">
         <v>46031</v>
@@ -12896,16 +12896,16 @@
         <v>34</v>
       </c>
       <c r="C480" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D480" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E480" s="2">
-        <v>81667</v>
+        <v>81583</v>
       </c>
       <c r="F480" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>9</v>
@@ -12928,7 +12928,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E481" s="2">
-        <v>81668</v>
+        <v>81667</v>
       </c>
       <c r="F481" s="3">
         <v>46037</v>
@@ -12954,10 +12954,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E482" s="2">
-        <v>81674</v>
+        <v>81668</v>
       </c>
       <c r="F482" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12980,7 +12980,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E483" s="2">
-        <v>81675</v>
+        <v>81674</v>
       </c>
       <c r="F483" s="3">
         <v>46038</v>
@@ -13006,7 +13006,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E484" s="2">
-        <v>81677</v>
+        <v>81675</v>
       </c>
       <c r="F484" s="3">
         <v>46038</v>
@@ -13026,16 +13026,16 @@
         <v>34</v>
       </c>
       <c r="C485" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D485" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E485" s="2">
-        <v>81739</v>
+        <v>81677</v>
       </c>
       <c r="F485" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>9</v>
@@ -13058,7 +13058,7 @@
         <v>46041.6133887269</v>
       </c>
       <c r="E486" s="2">
-        <v>81741</v>
+        <v>81739</v>
       </c>
       <c r="F486" s="3">
         <v>46041</v>
@@ -13078,16 +13078,16 @@
         <v>34</v>
       </c>
       <c r="C487" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D487" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E487" s="2">
-        <v>81854</v>
+        <v>81741</v>
       </c>
       <c r="F487" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>9</v>
@@ -13110,7 +13110,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E488" s="2">
-        <v>81855</v>
+        <v>81854</v>
       </c>
       <c r="F488" s="3">
         <v>46048</v>
@@ -13136,10 +13136,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E489" s="2">
-        <v>81858</v>
+        <v>81855</v>
       </c>
       <c r="F489" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>9</v>
@@ -13162,7 +13162,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E490" s="2">
-        <v>81859</v>
+        <v>81858</v>
       </c>
       <c r="F490" s="3">
         <v>46049</v>
@@ -13188,7 +13188,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E491" s="2">
-        <v>81862</v>
+        <v>81859</v>
       </c>
       <c r="F491" s="3">
         <v>46049</v>
@@ -13214,7 +13214,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E492" s="2">
-        <v>81863</v>
+        <v>81862</v>
       </c>
       <c r="F492" s="3">
         <v>46049</v>
@@ -13234,16 +13234,16 @@
         <v>34</v>
       </c>
       <c r="C493" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D493" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E493" s="2">
-        <v>81958</v>
+        <v>81863</v>
       </c>
       <c r="F493" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G493" s="1" t="s">
         <v>9</v>
@@ -13266,7 +13266,7 @@
         <v>46055.5924236111</v>
       </c>
       <c r="E494" s="2">
-        <v>81965</v>
+        <v>81958</v>
       </c>
       <c r="F494" s="3">
         <v>46055</v>
@@ -13286,16 +13286,16 @@
         <v>34</v>
       </c>
       <c r="C495" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D495" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E495" s="2">
-        <v>82085</v>
+        <v>81965</v>
       </c>
       <c r="F495" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>9</v>
@@ -13318,7 +13318,7 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E496" s="2">
-        <v>82086</v>
+        <v>82085</v>
       </c>
       <c r="F496" s="3">
         <v>46063</v>
@@ -13344,10 +13344,10 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E497" s="2">
-        <v>82126</v>
+        <v>82086</v>
       </c>
       <c r="F497" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G497" s="1" t="s">
         <v>9</v>
@@ -13364,16 +13364,16 @@
         <v>34</v>
       </c>
       <c r="C498" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D498" s="3">
-        <v>46064.5127051505</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E498" s="2">
-        <v>82268</v>
+        <v>82126</v>
       </c>
       <c r="F498" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G498" s="1" t="s">
         <v>9</v>
@@ -13390,16 +13390,16 @@
         <v>34</v>
       </c>
       <c r="C499" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D499" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E499" s="2">
-        <v>82142</v>
+        <v>82268</v>
       </c>
       <c r="F499" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>9</v>
@@ -13422,7 +13422,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E500" s="2">
-        <v>82143</v>
+        <v>82142</v>
       </c>
       <c r="F500" s="3">
         <v>46065</v>
@@ -13448,7 +13448,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E501" s="2">
-        <v>82144</v>
+        <v>82143</v>
       </c>
       <c r="F501" s="3">
         <v>46065</v>
@@ -13474,10 +13474,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E502" s="2">
-        <v>82166</v>
+        <v>82144</v>
       </c>
       <c r="F502" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="G502" s="1" t="s">
         <v>9</v>
@@ -13494,16 +13494,16 @@
         <v>34</v>
       </c>
       <c r="C503" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D503" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E503" s="2">
-        <v>82262</v>
+        <v>82166</v>
       </c>
       <c r="F503" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G503" s="1" t="s">
         <v>9</v>
@@ -13526,7 +13526,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E504" s="2">
-        <v>82265</v>
+        <v>82262</v>
       </c>
       <c r="F504" s="3">
         <v>46077</v>
@@ -13552,7 +13552,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E505" s="2">
-        <v>82281</v>
+        <v>82265</v>
       </c>
       <c r="F505" s="3">
         <v>46077</v>
@@ -13578,7 +13578,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E506" s="2">
-        <v>82282</v>
+        <v>82281</v>
       </c>
       <c r="F506" s="3">
         <v>46077</v>
@@ -13598,16 +13598,16 @@
         <v>34</v>
       </c>
       <c r="C507" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D507" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E507" s="2">
-        <v>82340</v>
+        <v>82282</v>
       </c>
       <c r="F507" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>9</v>
@@ -13624,16 +13624,16 @@
         <v>34</v>
       </c>
       <c r="C508" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D508" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E508" s="2">
-        <v>82399</v>
+        <v>82340</v>
       </c>
       <c r="F508" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="G508" s="1" t="s">
         <v>9</v>
@@ -13656,7 +13656,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E509" s="2">
-        <v>82400</v>
+        <v>82399</v>
       </c>
       <c r="F509" s="3">
         <v>46083</v>
@@ -13682,7 +13682,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E510" s="2">
-        <v>82401</v>
+        <v>82400</v>
       </c>
       <c r="F510" s="3">
         <v>46083</v>
@@ -13708,10 +13708,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E511" s="2">
-        <v>82412</v>
+        <v>82401</v>
       </c>
       <c r="F511" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>9</v>
@@ -13734,7 +13734,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E512" s="2">
-        <v>82415</v>
+        <v>82412</v>
       </c>
       <c r="F512" s="3">
         <v>46084</v>
@@ -13754,16 +13754,16 @@
         <v>34</v>
       </c>
       <c r="C513" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D513" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E513" s="2">
-        <v>82571</v>
+        <v>82415</v>
       </c>
       <c r="F513" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G513" s="1" t="s">
         <v>9</v>
@@ -13786,7 +13786,7 @@
         <v>46086.6312882639</v>
       </c>
       <c r="E514" s="2">
-        <v>82572</v>
+        <v>82571</v>
       </c>
       <c r="F514" s="3">
         <v>46093</v>
@@ -13806,16 +13806,16 @@
         <v>34</v>
       </c>
       <c r="C515" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D515" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E515" s="2">
-        <v>82630</v>
+        <v>82572</v>
       </c>
       <c r="F515" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G515" s="1" t="s">
         <v>9</v>
@@ -13838,16 +13838,16 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E516" s="2">
-        <v>82631</v>
+        <v>82630</v>
       </c>
       <c r="F516" s="3">
         <v>46094</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="517">
@@ -13864,16 +13864,16 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E517" s="2">
-        <v>82632</v>
+        <v>82631</v>
       </c>
       <c r="F517" s="3">
         <v>46094</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="518">
@@ -13884,16 +13884,16 @@
         <v>34</v>
       </c>
       <c r="C518" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D518" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E518" s="2">
-        <v>82653</v>
+        <v>82632</v>
       </c>
       <c r="F518" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>9</v>
@@ -13916,7 +13916,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E519" s="2">
-        <v>82665</v>
+        <v>82653</v>
       </c>
       <c r="F519" s="3">
         <v>46097</v>
@@ -13942,42 +13942,42 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E520" s="2">
-        <v>82668</v>
+        <v>82665</v>
       </c>
       <c r="F520" s="3">
         <v>46097</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="521">
       <c r="A521" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C521" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D521" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E521" s="2">
-        <v>82311</v>
+        <v>82668</v>
       </c>
       <c r="F521" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="522">
@@ -13994,7 +13994,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E522" s="2">
-        <v>82312</v>
+        <v>82311</v>
       </c>
       <c r="F522" s="3">
         <v>46078</v>
@@ -14020,7 +14020,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E523" s="2">
-        <v>82313</v>
+        <v>82312</v>
       </c>
       <c r="F523" s="3">
         <v>46078</v>
@@ -14046,7 +14046,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E524" s="2">
-        <v>82314</v>
+        <v>82313</v>
       </c>
       <c r="F524" s="3">
         <v>46078</v>
@@ -14072,10 +14072,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E525" s="2">
-        <v>82346</v>
+        <v>82314</v>
       </c>
       <c r="F525" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>9</v>
@@ -14098,7 +14098,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E526" s="2">
-        <v>82361</v>
+        <v>82346</v>
       </c>
       <c r="F526" s="3">
         <v>46080</v>
@@ -14124,10 +14124,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E527" s="2">
-        <v>82385</v>
+        <v>82361</v>
       </c>
       <c r="F527" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G527" s="1" t="s">
         <v>9</v>
@@ -14150,7 +14150,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E528" s="2">
-        <v>82391</v>
+        <v>82385</v>
       </c>
       <c r="F528" s="3">
         <v>46083</v>
@@ -14176,7 +14176,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E529" s="2">
-        <v>82392</v>
+        <v>82391</v>
       </c>
       <c r="F529" s="3">
         <v>46083</v>
@@ -14190,22 +14190,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="530">
       <c r="A530" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C530" s="2">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D530" s="3">
-        <v>46029.4632696412</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E530" s="2">
-        <v>81495</v>
+        <v>82392</v>
       </c>
       <c r="F530" s="3">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>9</v>
@@ -14216,27 +14216,53 @@
     </row>
     <row ht="12.75" customHeight="1" r="531">
       <c r="A531" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C531" s="2">
+        <v>62</v>
+      </c>
+      <c r="D531" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E531" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F531" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G531" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H531" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="532">
+      <c r="A532" s="2">
         <v>9992</v>
       </c>
-      <c r="B531" s="1" t="s">
+      <c r="B532" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C531" s="2">
+      <c r="C532" s="2">
         <v>390</v>
       </c>
-      <c r="D531" s="3">
+      <c r="D532" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E531" s="2">
+      <c r="E532" s="2">
         <v>81684</v>
       </c>
-      <c r="F531" s="3">
+      <c r="F532" s="3">
         <v>46038</v>
       </c>
-      <c r="G531" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H531" s="1" t="s">
+      <c r="G532" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H532" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H541"/>
+  <dimension ref="A1:H547"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -4495,22 +4495,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="157">
       <c r="A157" s="2">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C157" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D157" s="3">
-        <v>46030.4179771875</v>
+        <v>46094.4767297338</v>
       </c>
       <c r="E157" s="2">
-        <v>81536</v>
+        <v>82698</v>
       </c>
       <c r="F157" s="3">
-        <v>46030</v>
+        <v>46098</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>9</v>
@@ -4533,7 +4533,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E158" s="2">
-        <v>81538</v>
+        <v>81536</v>
       </c>
       <c r="F158" s="3">
         <v>46030</v>
@@ -4559,7 +4559,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E159" s="2">
-        <v>81555</v>
+        <v>81538</v>
       </c>
       <c r="F159" s="3">
         <v>46030</v>
@@ -4585,7 +4585,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E160" s="2">
-        <v>81556</v>
+        <v>81555</v>
       </c>
       <c r="F160" s="3">
         <v>46030</v>
@@ -4611,7 +4611,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E161" s="2">
-        <v>81558</v>
+        <v>81556</v>
       </c>
       <c r="F161" s="3">
         <v>46030</v>
@@ -4631,16 +4631,16 @@
         <v>21</v>
       </c>
       <c r="C162" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D162" s="3">
-        <v>46036.4079311574</v>
+        <v>46030.4179771875</v>
       </c>
       <c r="E162" s="2">
-        <v>81615</v>
+        <v>81558</v>
       </c>
       <c r="F162" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>9</v>
@@ -4663,7 +4663,7 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E163" s="2">
-        <v>81621</v>
+        <v>81615</v>
       </c>
       <c r="F163" s="3">
         <v>46036</v>
@@ -4689,10 +4689,10 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E164" s="2">
-        <v>81647</v>
+        <v>81621</v>
       </c>
       <c r="F164" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>9</v>
@@ -4703,22 +4703,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="165">
       <c r="A165" s="2">
-        <v>2504</v>
+        <v>2411</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C165" s="2">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D165" s="3">
-        <v>46027.6983957986</v>
+        <v>46036.4079311574</v>
       </c>
       <c r="E165" s="2">
-        <v>81465</v>
+        <v>81647</v>
       </c>
       <c r="F165" s="3">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>9</v>
@@ -4741,16 +4741,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E166" s="2">
-        <v>81466</v>
+        <v>81465</v>
       </c>
       <c r="F166" s="3">
         <v>46027</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="167">
@@ -4767,16 +4767,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E167" s="2">
-        <v>81471</v>
+        <v>81466</v>
       </c>
       <c r="F167" s="3">
         <v>46027</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="168">
@@ -4793,10 +4793,10 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E168" s="2">
-        <v>81488</v>
+        <v>81471</v>
       </c>
       <c r="F168" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>9</v>
@@ -4819,7 +4819,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E169" s="2">
-        <v>81489</v>
+        <v>81488</v>
       </c>
       <c r="F169" s="3">
         <v>46029</v>
@@ -4845,7 +4845,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E170" s="2">
-        <v>81490</v>
+        <v>81489</v>
       </c>
       <c r="F170" s="3">
         <v>46029</v>
@@ -4871,7 +4871,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E171" s="2">
-        <v>81491</v>
+        <v>81490</v>
       </c>
       <c r="F171" s="3">
         <v>46029</v>
@@ -4891,16 +4891,16 @@
         <v>22</v>
       </c>
       <c r="C172" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D172" s="3">
-        <v>46038.4184531713</v>
+        <v>46027.6983957986</v>
       </c>
       <c r="E172" s="2">
-        <v>81688</v>
+        <v>81491</v>
       </c>
       <c r="F172" s="3">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>9</v>
@@ -4917,13 +4917,13 @@
         <v>22</v>
       </c>
       <c r="C173" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D173" s="3">
-        <v>46038.6993878241</v>
+        <v>46038.4184531713</v>
       </c>
       <c r="E173" s="2">
-        <v>81700</v>
+        <v>81688</v>
       </c>
       <c r="F173" s="3">
         <v>46038</v>
@@ -4949,7 +4949,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E174" s="2">
-        <v>81701</v>
+        <v>81700</v>
       </c>
       <c r="F174" s="3">
         <v>46038</v>
@@ -4975,7 +4975,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E175" s="2">
-        <v>81702</v>
+        <v>81701</v>
       </c>
       <c r="F175" s="3">
         <v>46038</v>
@@ -5001,7 +5001,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E176" s="2">
-        <v>81703</v>
+        <v>81702</v>
       </c>
       <c r="F176" s="3">
         <v>46038</v>
@@ -5027,10 +5027,10 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E177" s="2">
-        <v>81734</v>
+        <v>81703</v>
       </c>
       <c r="F177" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>9</v>
@@ -5047,16 +5047,16 @@
         <v>22</v>
       </c>
       <c r="C178" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D178" s="3">
-        <v>46050.7176682523</v>
+        <v>46038.6993878241</v>
       </c>
       <c r="E178" s="2">
-        <v>81914</v>
+        <v>81734</v>
       </c>
       <c r="F178" s="3">
-        <v>46051</v>
+        <v>46041</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>9</v>
@@ -5079,7 +5079,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E179" s="2">
-        <v>81915</v>
+        <v>81914</v>
       </c>
       <c r="F179" s="3">
         <v>46051</v>
@@ -5105,7 +5105,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E180" s="2">
-        <v>81921</v>
+        <v>81915</v>
       </c>
       <c r="F180" s="3">
         <v>46051</v>
@@ -5125,16 +5125,16 @@
         <v>22</v>
       </c>
       <c r="C181" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D181" s="3">
-        <v>46052.6247194676</v>
+        <v>46050.7176682523</v>
       </c>
       <c r="E181" s="2">
-        <v>81949</v>
+        <v>81921</v>
       </c>
       <c r="F181" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>9</v>
@@ -5157,7 +5157,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E182" s="2">
-        <v>81950</v>
+        <v>81949</v>
       </c>
       <c r="F182" s="3">
         <v>46052</v>
@@ -5183,7 +5183,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E183" s="2">
-        <v>81951</v>
+        <v>81950</v>
       </c>
       <c r="F183" s="3">
         <v>46052</v>
@@ -5209,7 +5209,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E184" s="2">
-        <v>81953</v>
+        <v>81951</v>
       </c>
       <c r="F184" s="3">
         <v>46052</v>
@@ -5229,16 +5229,16 @@
         <v>22</v>
       </c>
       <c r="C185" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D185" s="3">
-        <v>46058.6976675694</v>
+        <v>46052.6247194676</v>
       </c>
       <c r="E185" s="2">
-        <v>82028</v>
+        <v>81953</v>
       </c>
       <c r="F185" s="3">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>9</v>
@@ -5261,7 +5261,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E186" s="2">
-        <v>82029</v>
+        <v>82028</v>
       </c>
       <c r="F186" s="3">
         <v>46058</v>
@@ -5287,10 +5287,10 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E187" s="2">
-        <v>82040</v>
+        <v>82029</v>
       </c>
       <c r="F187" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>9</v>
@@ -5313,7 +5313,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E188" s="2">
-        <v>82041</v>
+        <v>82040</v>
       </c>
       <c r="F188" s="3">
         <v>46059</v>
@@ -5339,7 +5339,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E189" s="2">
-        <v>82051</v>
+        <v>82041</v>
       </c>
       <c r="F189" s="3">
         <v>46059</v>
@@ -5359,16 +5359,16 @@
         <v>22</v>
       </c>
       <c r="C190" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D190" s="3">
-        <v>46065.6309066782</v>
+        <v>46058.6976675694</v>
       </c>
       <c r="E190" s="2">
-        <v>82168</v>
+        <v>82051</v>
       </c>
       <c r="F190" s="3">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>9</v>
@@ -5391,16 +5391,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E191" s="2">
-        <v>82170</v>
+        <v>82168</v>
       </c>
       <c r="F191" s="3">
         <v>46066</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="192">
@@ -5417,16 +5417,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E192" s="2">
-        <v>82171</v>
+        <v>82170</v>
       </c>
       <c r="F192" s="3">
         <v>46066</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="193">
@@ -5443,7 +5443,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E193" s="2">
-        <v>82172</v>
+        <v>82171</v>
       </c>
       <c r="F193" s="3">
         <v>46066</v>
@@ -5469,7 +5469,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E194" s="2">
-        <v>82175</v>
+        <v>82172</v>
       </c>
       <c r="F194" s="3">
         <v>46066</v>
@@ -5495,7 +5495,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E195" s="2">
-        <v>82176</v>
+        <v>82175</v>
       </c>
       <c r="F195" s="3">
         <v>46066</v>
@@ -5515,16 +5515,16 @@
         <v>22</v>
       </c>
       <c r="C196" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D196" s="3">
-        <v>46072.5909779051</v>
+        <v>46065.6309066782</v>
       </c>
       <c r="E196" s="2">
-        <v>82206</v>
+        <v>82176</v>
       </c>
       <c r="F196" s="3">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>9</v>
@@ -5541,16 +5541,16 @@
         <v>22</v>
       </c>
       <c r="C197" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D197" s="3">
-        <v>46077.7262228935</v>
+        <v>46072.5909779051</v>
       </c>
       <c r="E197" s="2">
-        <v>82289</v>
+        <v>82206</v>
       </c>
       <c r="F197" s="3">
-        <v>46077</v>
+        <v>46072</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>9</v>
@@ -5573,7 +5573,7 @@
         <v>46077.7262228935</v>
       </c>
       <c r="E198" s="2">
-        <v>82290</v>
+        <v>82289</v>
       </c>
       <c r="F198" s="3">
         <v>46077</v>
@@ -5593,16 +5593,16 @@
         <v>22</v>
       </c>
       <c r="C199" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D199" s="3">
-        <v>46078.6799843634</v>
+        <v>46077.7262228935</v>
       </c>
       <c r="E199" s="2">
-        <v>82318</v>
+        <v>82290</v>
       </c>
       <c r="F199" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>9</v>
@@ -5619,16 +5619,16 @@
         <v>22</v>
       </c>
       <c r="C200" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D200" s="3">
-        <v>46080.6294471412</v>
+        <v>46078.6799843634</v>
       </c>
       <c r="E200" s="2">
-        <v>82368</v>
+        <v>82318</v>
       </c>
       <c r="F200" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>9</v>
@@ -5645,16 +5645,16 @@
         <v>22</v>
       </c>
       <c r="C201" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D201" s="3">
-        <v>46084.741264838</v>
+        <v>46080.6294471412</v>
       </c>
       <c r="E201" s="2">
-        <v>82425</v>
+        <v>82368</v>
       </c>
       <c r="F201" s="3">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>9</v>
@@ -5677,7 +5677,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="E202" s="2">
-        <v>82426</v>
+        <v>82425</v>
       </c>
       <c r="F202" s="3">
         <v>46084</v>
@@ -5703,10 +5703,10 @@
         <v>46084.741264838</v>
       </c>
       <c r="E203" s="2">
-        <v>82430</v>
+        <v>82426</v>
       </c>
       <c r="F203" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>9</v>
@@ -5729,7 +5729,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="E204" s="2">
-        <v>82431</v>
+        <v>82430</v>
       </c>
       <c r="F204" s="3">
         <v>46085</v>
@@ -5749,16 +5749,16 @@
         <v>22</v>
       </c>
       <c r="C205" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D205" s="3">
-        <v>46097.4509044907</v>
+        <v>46084.741264838</v>
       </c>
       <c r="E205" s="2">
-        <v>82654</v>
+        <v>82431</v>
       </c>
       <c r="F205" s="3">
-        <v>46097</v>
+        <v>46085</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>9</v>
@@ -5781,7 +5781,7 @@
         <v>46097.4509044907</v>
       </c>
       <c r="E206" s="2">
-        <v>82660</v>
+        <v>82654</v>
       </c>
       <c r="F206" s="3">
         <v>46097</v>
@@ -5807,7 +5807,7 @@
         <v>46097.4509044907</v>
       </c>
       <c r="E207" s="2">
-        <v>82661</v>
+        <v>82660</v>
       </c>
       <c r="F207" s="3">
         <v>46097</v>
@@ -5827,22 +5827,22 @@
         <v>22</v>
       </c>
       <c r="C208" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D208" s="3">
-        <v>46098.5062577778</v>
+        <v>46097.4509044907</v>
       </c>
       <c r="E208" s="2">
-        <v>82689</v>
+        <v>82661</v>
       </c>
       <c r="F208" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="209">
@@ -5859,7 +5859,7 @@
         <v>46098.5062577778</v>
       </c>
       <c r="E209" s="2">
-        <v>82690</v>
+        <v>82689</v>
       </c>
       <c r="F209" s="3">
         <v>46098</v>
@@ -5873,22 +5873,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="210">
       <c r="A210" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C210" s="2">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D210" s="3">
-        <v>46041.6648751157</v>
+        <v>46098.5062577778</v>
       </c>
       <c r="E210" s="2">
-        <v>81743</v>
+        <v>82690</v>
       </c>
       <c r="F210" s="3">
-        <v>46041</v>
+        <v>46098</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>9</v>
@@ -5911,7 +5911,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E211" s="2">
-        <v>81744</v>
+        <v>81743</v>
       </c>
       <c r="F211" s="3">
         <v>46041</v>
@@ -5937,7 +5937,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E212" s="2">
-        <v>81745</v>
+        <v>81744</v>
       </c>
       <c r="F212" s="3">
         <v>46041</v>
@@ -5963,10 +5963,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E213" s="2">
-        <v>81746</v>
+        <v>81745</v>
       </c>
       <c r="F213" s="3">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>9</v>
@@ -5989,10 +5989,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E214" s="2">
-        <v>81751</v>
+        <v>81746</v>
       </c>
       <c r="F214" s="3">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>9</v>
@@ -6015,7 +6015,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E215" s="2">
-        <v>81753</v>
+        <v>81751</v>
       </c>
       <c r="F215" s="3">
         <v>46043</v>
@@ -6041,7 +6041,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E216" s="2">
-        <v>81754</v>
+        <v>81753</v>
       </c>
       <c r="F216" s="3">
         <v>46043</v>
@@ -6067,7 +6067,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E217" s="2">
-        <v>81755</v>
+        <v>81754</v>
       </c>
       <c r="F217" s="3">
         <v>46043</v>
@@ -6093,7 +6093,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E218" s="2">
-        <v>81766</v>
+        <v>81755</v>
       </c>
       <c r="F218" s="3">
         <v>46043</v>
@@ -6113,16 +6113,16 @@
         <v>23</v>
       </c>
       <c r="C219" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D219" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E219" s="2">
-        <v>82088</v>
+        <v>81766</v>
       </c>
       <c r="F219" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>9</v>
@@ -6145,7 +6145,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E220" s="2">
-        <v>82089</v>
+        <v>82088</v>
       </c>
       <c r="F220" s="3">
         <v>46063</v>
@@ -6171,10 +6171,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E221" s="2">
-        <v>82163</v>
+        <v>82089</v>
       </c>
       <c r="F221" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>9</v>
@@ -6197,7 +6197,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E222" s="2">
-        <v>82179</v>
+        <v>82163</v>
       </c>
       <c r="F222" s="3">
         <v>46066</v>
@@ -6223,7 +6223,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E223" s="2">
-        <v>82193</v>
+        <v>82179</v>
       </c>
       <c r="F223" s="3">
         <v>46066</v>
@@ -6243,16 +6243,16 @@
         <v>23</v>
       </c>
       <c r="C224" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D224" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E224" s="2">
-        <v>82250</v>
+        <v>82193</v>
       </c>
       <c r="F224" s="3">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>9</v>
@@ -6275,10 +6275,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E225" s="2">
-        <v>82266</v>
+        <v>82250</v>
       </c>
       <c r="F225" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>9</v>
@@ -6301,10 +6301,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E226" s="2">
-        <v>82295</v>
+        <v>82266</v>
       </c>
       <c r="F226" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>9</v>
@@ -6327,7 +6327,7 @@
         <v>46073.714168287</v>
       </c>
       <c r="E227" s="2">
-        <v>82296</v>
+        <v>82295</v>
       </c>
       <c r="F227" s="3">
         <v>46078</v>
@@ -6353,16 +6353,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E228" s="2">
-        <v>82332</v>
+        <v>82296</v>
       </c>
       <c r="F228" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="229">
@@ -6379,16 +6379,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E229" s="2">
-        <v>82339</v>
+        <v>82332</v>
       </c>
       <c r="F229" s="3">
         <v>46079</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="230">
@@ -6399,16 +6399,16 @@
         <v>23</v>
       </c>
       <c r="C230" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D230" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E230" s="2">
-        <v>82266</v>
+        <v>82339</v>
       </c>
       <c r="F230" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>9</v>
@@ -6431,7 +6431,7 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E231" s="2">
-        <v>82273</v>
+        <v>82266</v>
       </c>
       <c r="F231" s="3">
         <v>46077</v>
@@ -6457,10 +6457,10 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E232" s="2">
-        <v>82294</v>
+        <v>82273</v>
       </c>
       <c r="F232" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>9</v>
@@ -6477,16 +6477,16 @@
         <v>23</v>
       </c>
       <c r="C233" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D233" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E233" s="2">
-        <v>82411</v>
+        <v>82294</v>
       </c>
       <c r="F233" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>9</v>
@@ -6509,10 +6509,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E234" s="2">
-        <v>82432</v>
+        <v>82411</v>
       </c>
       <c r="F234" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>9</v>
@@ -6535,10 +6535,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E235" s="2">
-        <v>82473</v>
+        <v>82432</v>
       </c>
       <c r="F235" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>9</v>
@@ -6561,10 +6561,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E236" s="2">
-        <v>82474</v>
+        <v>82473</v>
       </c>
       <c r="F236" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>9</v>
@@ -6581,16 +6581,16 @@
         <v>23</v>
       </c>
       <c r="C237" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D237" s="3">
-        <v>46093.5009358681</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E237" s="2">
-        <v>82594</v>
+        <v>82474</v>
       </c>
       <c r="F237" s="3">
-        <v>46093</v>
+        <v>46087</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>9</v>
@@ -6613,7 +6613,7 @@
         <v>46093.5009358681</v>
       </c>
       <c r="E238" s="2">
-        <v>82595</v>
+        <v>82594</v>
       </c>
       <c r="F238" s="3">
         <v>46093</v>
@@ -6639,10 +6639,10 @@
         <v>46093.5009358681</v>
       </c>
       <c r="E239" s="2">
-        <v>82657</v>
+        <v>82595</v>
       </c>
       <c r="F239" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>9</v>
@@ -6659,22 +6659,22 @@
         <v>23</v>
       </c>
       <c r="C240" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D240" s="3">
-        <v>46098.5034667708</v>
+        <v>46093.5009358681</v>
       </c>
       <c r="E240" s="2">
-        <v>82686</v>
+        <v>82657</v>
       </c>
       <c r="F240" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="241">
@@ -6691,7 +6691,7 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E241" s="2">
-        <v>82687</v>
+        <v>82686</v>
       </c>
       <c r="F241" s="3">
         <v>46098</v>
@@ -6717,7 +6717,7 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E242" s="2">
-        <v>82688</v>
+        <v>82687</v>
       </c>
       <c r="F242" s="3">
         <v>46098</v>
@@ -6731,28 +6731,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="243">
       <c r="A243" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C243" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D243" s="3">
-        <v>46044.6368950926</v>
+        <v>46098.5034667708</v>
       </c>
       <c r="E243" s="2">
-        <v>81802</v>
+        <v>82688</v>
       </c>
       <c r="F243" s="3">
-        <v>46044</v>
+        <v>46098</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="244">
@@ -6769,7 +6769,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E244" s="2">
-        <v>81803</v>
+        <v>81802</v>
       </c>
       <c r="F244" s="3">
         <v>46044</v>
@@ -6795,7 +6795,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E245" s="2">
-        <v>81804</v>
+        <v>81803</v>
       </c>
       <c r="F245" s="3">
         <v>46044</v>
@@ -6821,7 +6821,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E246" s="2">
-        <v>81806</v>
+        <v>81804</v>
       </c>
       <c r="F246" s="3">
         <v>46044</v>
@@ -6847,7 +6847,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E247" s="2">
-        <v>81807</v>
+        <v>81806</v>
       </c>
       <c r="F247" s="3">
         <v>46044</v>
@@ -6873,10 +6873,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E248" s="2">
-        <v>81812</v>
+        <v>81807</v>
       </c>
       <c r="F248" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>9</v>
@@ -6899,7 +6899,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E249" s="2">
-        <v>81813</v>
+        <v>81812</v>
       </c>
       <c r="F249" s="3">
         <v>46045</v>
@@ -6925,7 +6925,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E250" s="2">
-        <v>81814</v>
+        <v>81813</v>
       </c>
       <c r="F250" s="3">
         <v>46045</v>
@@ -6951,7 +6951,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E251" s="2">
-        <v>81818</v>
+        <v>81814</v>
       </c>
       <c r="F251" s="3">
         <v>46045</v>
@@ -6977,7 +6977,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E252" s="2">
-        <v>81822</v>
+        <v>81818</v>
       </c>
       <c r="F252" s="3">
         <v>46045</v>
@@ -7003,7 +7003,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E253" s="2">
-        <v>81833</v>
+        <v>81822</v>
       </c>
       <c r="F253" s="3">
         <v>46045</v>
@@ -7029,7 +7029,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E254" s="2">
-        <v>81841</v>
+        <v>81833</v>
       </c>
       <c r="F254" s="3">
         <v>46045</v>
@@ -7049,16 +7049,16 @@
         <v>26</v>
       </c>
       <c r="C255" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D255" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E255" s="2">
-        <v>81928</v>
+        <v>81841</v>
       </c>
       <c r="F255" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>9</v>
@@ -7081,7 +7081,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E256" s="2">
-        <v>81929</v>
+        <v>81928</v>
       </c>
       <c r="F256" s="3">
         <v>46052</v>
@@ -7107,7 +7107,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E257" s="2">
-        <v>81930</v>
+        <v>81929</v>
       </c>
       <c r="F257" s="3">
         <v>46052</v>
@@ -7133,7 +7133,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E258" s="2">
-        <v>81932</v>
+        <v>81930</v>
       </c>
       <c r="F258" s="3">
         <v>46052</v>
@@ -7159,7 +7159,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E259" s="2">
-        <v>81933</v>
+        <v>81932</v>
       </c>
       <c r="F259" s="3">
         <v>46052</v>
@@ -7185,7 +7185,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E260" s="2">
-        <v>81934</v>
+        <v>81933</v>
       </c>
       <c r="F260" s="3">
         <v>46052</v>
@@ -7211,7 +7211,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E261" s="2">
-        <v>81935</v>
+        <v>81934</v>
       </c>
       <c r="F261" s="3">
         <v>46052</v>
@@ -7237,7 +7237,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E262" s="2">
-        <v>81936</v>
+        <v>81935</v>
       </c>
       <c r="F262" s="3">
         <v>46052</v>
@@ -7257,16 +7257,16 @@
         <v>26</v>
       </c>
       <c r="C263" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D263" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E263" s="2">
-        <v>82222</v>
+        <v>81936</v>
       </c>
       <c r="F263" s="3">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>9</v>
@@ -7289,10 +7289,10 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E264" s="2">
-        <v>82226</v>
+        <v>82222</v>
       </c>
       <c r="F264" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>9</v>
@@ -7315,7 +7315,7 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E265" s="2">
-        <v>82229</v>
+        <v>82226</v>
       </c>
       <c r="F265" s="3">
         <v>46073</v>
@@ -7335,13 +7335,13 @@
         <v>26</v>
       </c>
       <c r="C266" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D266" s="3">
-        <v>46073.5838834375</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E266" s="2">
-        <v>82246</v>
+        <v>82229</v>
       </c>
       <c r="F266" s="3">
         <v>46073</v>
@@ -7361,16 +7361,16 @@
         <v>26</v>
       </c>
       <c r="C267" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D267" s="3">
-        <v>46080.6289065162</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E267" s="2">
-        <v>82387</v>
+        <v>82246</v>
       </c>
       <c r="F267" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>9</v>
@@ -7387,16 +7387,16 @@
         <v>26</v>
       </c>
       <c r="C268" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D268" s="3">
-        <v>46093.4978086806</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E268" s="2">
-        <v>82590</v>
+        <v>82387</v>
       </c>
       <c r="F268" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>9</v>
@@ -7419,16 +7419,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E269" s="2">
-        <v>82591</v>
+        <v>82590</v>
       </c>
       <c r="F269" s="3">
         <v>46093</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="270">
@@ -7445,16 +7445,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E270" s="2">
-        <v>82592</v>
+        <v>82591</v>
       </c>
       <c r="F270" s="3">
         <v>46093</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="271">
@@ -7471,7 +7471,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E271" s="2">
-        <v>82593</v>
+        <v>82592</v>
       </c>
       <c r="F271" s="3">
         <v>46093</v>
@@ -7497,7 +7497,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E272" s="2">
-        <v>82600</v>
+        <v>82593</v>
       </c>
       <c r="F272" s="3">
         <v>46093</v>
@@ -7523,7 +7523,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E273" s="2">
-        <v>82603</v>
+        <v>82600</v>
       </c>
       <c r="F273" s="3">
         <v>46093</v>
@@ -7549,7 +7549,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E274" s="2">
-        <v>82604</v>
+        <v>82603</v>
       </c>
       <c r="F274" s="3">
         <v>46093</v>
@@ -7575,7 +7575,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E275" s="2">
-        <v>82605</v>
+        <v>82604</v>
       </c>
       <c r="F275" s="3">
         <v>46093</v>
@@ -7589,22 +7589,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="276">
       <c r="A276" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C276" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D276" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E276" s="2">
-        <v>81478</v>
+        <v>82605</v>
       </c>
       <c r="F276" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>9</v>
@@ -7627,7 +7627,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E277" s="2">
-        <v>81479</v>
+        <v>81478</v>
       </c>
       <c r="F277" s="3">
         <v>46029</v>
@@ -7653,7 +7653,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E278" s="2">
-        <v>81480</v>
+        <v>81479</v>
       </c>
       <c r="F278" s="3">
         <v>46029</v>
@@ -7679,7 +7679,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E279" s="2">
-        <v>81497</v>
+        <v>81480</v>
       </c>
       <c r="F279" s="3">
         <v>46029</v>
@@ -7705,7 +7705,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E280" s="2">
-        <v>81498</v>
+        <v>81497</v>
       </c>
       <c r="F280" s="3">
         <v>46029</v>
@@ -7731,7 +7731,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E281" s="2">
-        <v>81499</v>
+        <v>81498</v>
       </c>
       <c r="F281" s="3">
         <v>46029</v>
@@ -7757,7 +7757,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E282" s="2">
-        <v>81500</v>
+        <v>81499</v>
       </c>
       <c r="F282" s="3">
         <v>46029</v>
@@ -7777,16 +7777,16 @@
         <v>26</v>
       </c>
       <c r="C283" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D283" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E283" s="2">
-        <v>81878</v>
+        <v>81500</v>
       </c>
       <c r="F283" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>9</v>
@@ -7809,7 +7809,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E284" s="2">
-        <v>81879</v>
+        <v>81878</v>
       </c>
       <c r="F284" s="3">
         <v>46049</v>
@@ -7835,10 +7835,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E285" s="2">
-        <v>81885</v>
+        <v>81879</v>
       </c>
       <c r="F285" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>9</v>
@@ -7861,7 +7861,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E286" s="2">
-        <v>81886</v>
+        <v>81885</v>
       </c>
       <c r="F286" s="3">
         <v>46050</v>
@@ -7881,16 +7881,16 @@
         <v>26</v>
       </c>
       <c r="C287" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D287" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E287" s="2">
-        <v>82068</v>
+        <v>81886</v>
       </c>
       <c r="F287" s="3">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>9</v>
@@ -7913,10 +7913,10 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E288" s="2">
-        <v>82072</v>
+        <v>82068</v>
       </c>
       <c r="F288" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>9</v>
@@ -7939,7 +7939,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E289" s="2">
-        <v>82076</v>
+        <v>82072</v>
       </c>
       <c r="F289" s="3">
         <v>46063</v>
@@ -7965,7 +7965,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E290" s="2">
-        <v>82078</v>
+        <v>82076</v>
       </c>
       <c r="F290" s="3">
         <v>46063</v>
@@ -7985,16 +7985,16 @@
         <v>26</v>
       </c>
       <c r="C291" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D291" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E291" s="2">
-        <v>82287</v>
+        <v>82078</v>
       </c>
       <c r="F291" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>9</v>
@@ -8017,7 +8017,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E292" s="2">
-        <v>82288</v>
+        <v>82287</v>
       </c>
       <c r="F292" s="3">
         <v>46077</v>
@@ -8043,10 +8043,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E293" s="2">
-        <v>82298</v>
+        <v>82288</v>
       </c>
       <c r="F293" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>9</v>
@@ -8069,7 +8069,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E294" s="2">
-        <v>82301</v>
+        <v>82298</v>
       </c>
       <c r="F294" s="3">
         <v>46078</v>
@@ -8095,7 +8095,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E295" s="2">
-        <v>82304</v>
+        <v>82301</v>
       </c>
       <c r="F295" s="3">
         <v>46078</v>
@@ -8121,7 +8121,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E296" s="2">
-        <v>82308</v>
+        <v>82304</v>
       </c>
       <c r="F296" s="3">
         <v>46078</v>
@@ -8141,16 +8141,16 @@
         <v>26</v>
       </c>
       <c r="C297" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D297" s="3">
-        <v>46080.628344919</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E297" s="2">
-        <v>82373</v>
+        <v>82308</v>
       </c>
       <c r="F297" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>9</v>
@@ -8167,16 +8167,16 @@
         <v>26</v>
       </c>
       <c r="C298" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D298" s="3">
-        <v>46085.6581644213</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E298" s="2">
-        <v>82445</v>
+        <v>82373</v>
       </c>
       <c r="F298" s="3">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>9</v>
@@ -8199,7 +8199,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E299" s="2">
-        <v>82447</v>
+        <v>82445</v>
       </c>
       <c r="F299" s="3">
         <v>46085</v>
@@ -8225,10 +8225,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E300" s="2">
-        <v>82453</v>
+        <v>82447</v>
       </c>
       <c r="F300" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>9</v>
@@ -8251,7 +8251,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E301" s="2">
-        <v>82468</v>
+        <v>82453</v>
       </c>
       <c r="F301" s="3">
         <v>46086</v>
@@ -8265,22 +8265,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="302">
       <c r="A302" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C302" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D302" s="3">
-        <v>46029.6400966782</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E302" s="2">
-        <v>81506</v>
+        <v>82468</v>
       </c>
       <c r="F302" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>9</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="303">
       <c r="A303" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C303" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D303" s="3">
-        <v>46029.6400966782</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E303" s="2">
-        <v>81507</v>
+        <v>82697</v>
       </c>
       <c r="F303" s="3">
-        <v>46029</v>
+        <v>46098</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>9</v>
@@ -8329,10 +8329,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E304" s="2">
-        <v>81524</v>
+        <v>81506</v>
       </c>
       <c r="F304" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>9</v>
@@ -8355,10 +8355,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E305" s="2">
-        <v>81525</v>
+        <v>81507</v>
       </c>
       <c r="F305" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>9</v>
@@ -8381,7 +8381,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E306" s="2">
-        <v>81526</v>
+        <v>81524</v>
       </c>
       <c r="F306" s="3">
         <v>46030</v>
@@ -8401,16 +8401,16 @@
         <v>27</v>
       </c>
       <c r="C307" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D307" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E307" s="2">
-        <v>81640</v>
+        <v>81525</v>
       </c>
       <c r="F307" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>9</v>
@@ -8427,16 +8427,16 @@
         <v>27</v>
       </c>
       <c r="C308" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D308" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E308" s="2">
-        <v>81642</v>
+        <v>81526</v>
       </c>
       <c r="F308" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>9</v>
@@ -8459,7 +8459,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E309" s="2">
-        <v>81643</v>
+        <v>81640</v>
       </c>
       <c r="F309" s="3">
         <v>46036</v>
@@ -8479,16 +8479,16 @@
         <v>27</v>
       </c>
       <c r="C310" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D310" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E310" s="2">
-        <v>81835</v>
+        <v>81642</v>
       </c>
       <c r="F310" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>9</v>
@@ -8505,16 +8505,16 @@
         <v>27</v>
       </c>
       <c r="C311" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D311" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E311" s="2">
-        <v>81836</v>
+        <v>81643</v>
       </c>
       <c r="F311" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>9</v>
@@ -8537,7 +8537,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E312" s="2">
-        <v>81837</v>
+        <v>81835</v>
       </c>
       <c r="F312" s="3">
         <v>46045</v>
@@ -8557,16 +8557,16 @@
         <v>27</v>
       </c>
       <c r="C313" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D313" s="3">
-        <v>46051.6376515278</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E313" s="2">
-        <v>81931</v>
+        <v>81836</v>
       </c>
       <c r="F313" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>9</v>
@@ -8583,16 +8583,16 @@
         <v>27</v>
       </c>
       <c r="C314" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D314" s="3">
-        <v>46056.7115158912</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E314" s="2">
-        <v>81978</v>
+        <v>81837</v>
       </c>
       <c r="F314" s="3">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>9</v>
@@ -8609,16 +8609,16 @@
         <v>27</v>
       </c>
       <c r="C315" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D315" s="3">
-        <v>46057.6911087731</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E315" s="2">
-        <v>81994</v>
+        <v>81931</v>
       </c>
       <c r="F315" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>9</v>
@@ -8635,13 +8635,13 @@
         <v>27</v>
       </c>
       <c r="C316" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D316" s="3">
-        <v>46057.6911087731</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E316" s="2">
-        <v>81995</v>
+        <v>81978</v>
       </c>
       <c r="F316" s="3">
         <v>46057</v>
@@ -8667,7 +8667,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E317" s="2">
-        <v>81999</v>
+        <v>81994</v>
       </c>
       <c r="F317" s="3">
         <v>46057</v>
@@ -8693,10 +8693,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E318" s="2">
-        <v>82008</v>
+        <v>81995</v>
       </c>
       <c r="F318" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>9</v>
@@ -8719,10 +8719,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E319" s="2">
-        <v>82011</v>
+        <v>81999</v>
       </c>
       <c r="F319" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>9</v>
@@ -8745,7 +8745,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E320" s="2">
-        <v>82012</v>
+        <v>82008</v>
       </c>
       <c r="F320" s="3">
         <v>46058</v>
@@ -8771,7 +8771,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E321" s="2">
-        <v>82013</v>
+        <v>82011</v>
       </c>
       <c r="F321" s="3">
         <v>46058</v>
@@ -8797,7 +8797,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E322" s="2">
-        <v>82014</v>
+        <v>82012</v>
       </c>
       <c r="F322" s="3">
         <v>46058</v>
@@ -8817,22 +8817,22 @@
         <v>27</v>
       </c>
       <c r="C323" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D323" s="3">
-        <v>46058.6604985417</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E323" s="2">
-        <v>82046</v>
+        <v>82013</v>
       </c>
       <c r="F323" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="324">
@@ -8843,16 +8843,16 @@
         <v>27</v>
       </c>
       <c r="C324" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D324" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E324" s="2">
-        <v>82217</v>
+        <v>82014</v>
       </c>
       <c r="F324" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>9</v>
@@ -8869,22 +8869,22 @@
         <v>27</v>
       </c>
       <c r="C325" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D325" s="3">
-        <v>46072.738871875</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E325" s="2">
-        <v>82218</v>
+        <v>82046</v>
       </c>
       <c r="F325" s="3">
-        <v>46072</v>
+        <v>46059</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="326">
@@ -8901,10 +8901,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E326" s="2">
-        <v>82234</v>
+        <v>82217</v>
       </c>
       <c r="F326" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>9</v>
@@ -8927,10 +8927,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E327" s="2">
-        <v>82238</v>
+        <v>82218</v>
       </c>
       <c r="F327" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>9</v>
@@ -8953,7 +8953,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E328" s="2">
-        <v>82245</v>
+        <v>82234</v>
       </c>
       <c r="F328" s="3">
         <v>46073</v>
@@ -8973,16 +8973,16 @@
         <v>27</v>
       </c>
       <c r="C329" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D329" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E329" s="2">
-        <v>82257</v>
+        <v>82238</v>
       </c>
       <c r="F329" s="3">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>9</v>
@@ -8999,16 +8999,16 @@
         <v>27</v>
       </c>
       <c r="C330" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D330" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E330" s="2">
-        <v>82276</v>
+        <v>82245</v>
       </c>
       <c r="F330" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>9</v>
@@ -9031,10 +9031,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E331" s="2">
-        <v>82277</v>
+        <v>82257</v>
       </c>
       <c r="F331" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>9</v>
@@ -9057,10 +9057,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E332" s="2">
-        <v>82293</v>
+        <v>82276</v>
       </c>
       <c r="F332" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>9</v>
@@ -9077,13 +9077,13 @@
         <v>27</v>
       </c>
       <c r="C333" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D333" s="3">
-        <v>46077.4356327431</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E333" s="2">
-        <v>82269</v>
+        <v>82277</v>
       </c>
       <c r="F333" s="3">
         <v>46077</v>
@@ -9103,16 +9103,16 @@
         <v>27</v>
       </c>
       <c r="C334" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D334" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E334" s="2">
-        <v>82419</v>
+        <v>82293</v>
       </c>
       <c r="F334" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>9</v>
@@ -9129,16 +9129,16 @@
         <v>27</v>
       </c>
       <c r="C335" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D335" s="3">
-        <v>46084.7378501505</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E335" s="2">
-        <v>82420</v>
+        <v>82269</v>
       </c>
       <c r="F335" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>9</v>
@@ -9161,7 +9161,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E336" s="2">
-        <v>82421</v>
+        <v>82419</v>
       </c>
       <c r="F336" s="3">
         <v>46084</v>
@@ -9187,7 +9187,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E337" s="2">
-        <v>82422</v>
+        <v>82420</v>
       </c>
       <c r="F337" s="3">
         <v>46084</v>
@@ -9213,7 +9213,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E338" s="2">
-        <v>82423</v>
+        <v>82421</v>
       </c>
       <c r="F338" s="3">
         <v>46084</v>
@@ -9239,10 +9239,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E339" s="2">
-        <v>82433</v>
+        <v>82422</v>
       </c>
       <c r="F339" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>9</v>
@@ -9265,10 +9265,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E340" s="2">
-        <v>82434</v>
+        <v>82423</v>
       </c>
       <c r="F340" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>9</v>
@@ -9291,10 +9291,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E341" s="2">
-        <v>82464</v>
+        <v>82433</v>
       </c>
       <c r="F341" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>9</v>
@@ -9317,10 +9317,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E342" s="2">
-        <v>82472</v>
+        <v>82434</v>
       </c>
       <c r="F342" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>9</v>
@@ -9337,16 +9337,16 @@
         <v>27</v>
       </c>
       <c r="C343" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D343" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E343" s="2">
-        <v>82578</v>
+        <v>82464</v>
       </c>
       <c r="F343" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>9</v>
@@ -9363,16 +9363,16 @@
         <v>27</v>
       </c>
       <c r="C344" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D344" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E344" s="2">
-        <v>82579</v>
+        <v>82472</v>
       </c>
       <c r="F344" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>9</v>
@@ -9395,7 +9395,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E345" s="2">
-        <v>82580</v>
+        <v>82578</v>
       </c>
       <c r="F345" s="3">
         <v>46093</v>
@@ -9421,16 +9421,16 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E346" s="2">
-        <v>82599</v>
+        <v>82579</v>
       </c>
       <c r="F346" s="3">
         <v>46093</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="347">
@@ -9447,7 +9447,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E347" s="2">
-        <v>82602</v>
+        <v>82580</v>
       </c>
       <c r="F347" s="3">
         <v>46093</v>
@@ -9467,42 +9467,42 @@
         <v>27</v>
       </c>
       <c r="C348" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D348" s="3">
-        <v>46093.4957757986</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E348" s="2">
-        <v>82584</v>
+        <v>82599</v>
       </c>
       <c r="F348" s="3">
         <v>46093</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="349">
       <c r="A349" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C349" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D349" s="3">
-        <v>46027.6953206134</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E349" s="2">
-        <v>81464</v>
+        <v>82602</v>
       </c>
       <c r="F349" s="3">
-        <v>46027</v>
+        <v>46093</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>9</v>
@@ -9513,22 +9513,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="350">
       <c r="A350" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C350" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D350" s="3">
-        <v>46027.6953206134</v>
+        <v>46093.4957757986</v>
       </c>
       <c r="E350" s="2">
-        <v>81472</v>
+        <v>82584</v>
       </c>
       <c r="F350" s="3">
-        <v>46027</v>
+        <v>46093</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>9</v>
@@ -9551,10 +9551,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E351" s="2">
-        <v>81492</v>
+        <v>81464</v>
       </c>
       <c r="F351" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G351" s="1" t="s">
         <v>9</v>
@@ -9577,10 +9577,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E352" s="2">
-        <v>81493</v>
+        <v>81472</v>
       </c>
       <c r="F352" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>9</v>
@@ -9603,10 +9603,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E353" s="2">
-        <v>81568</v>
+        <v>81492</v>
       </c>
       <c r="F353" s="3">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>9</v>
@@ -9629,10 +9629,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E354" s="2">
-        <v>81601</v>
+        <v>81493</v>
       </c>
       <c r="F354" s="3">
-        <v>46034</v>
+        <v>46029</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>9</v>
@@ -9655,10 +9655,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E355" s="2">
-        <v>81602</v>
+        <v>81568</v>
       </c>
       <c r="F355" s="3">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>9</v>
@@ -9675,16 +9675,16 @@
         <v>30</v>
       </c>
       <c r="C356" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D356" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E356" s="2">
-        <v>81645</v>
+        <v>81601</v>
       </c>
       <c r="F356" s="3">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>9</v>
@@ -9701,16 +9701,16 @@
         <v>30</v>
       </c>
       <c r="C357" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D357" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E357" s="2">
-        <v>81646</v>
+        <v>81602</v>
       </c>
       <c r="F357" s="3">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>9</v>
@@ -9733,10 +9733,10 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E358" s="2">
-        <v>81653</v>
+        <v>81645</v>
       </c>
       <c r="F358" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>9</v>
@@ -9753,16 +9753,16 @@
         <v>30</v>
       </c>
       <c r="C359" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D359" s="3">
-        <v>46037.4325152662</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E359" s="2">
-        <v>81662</v>
+        <v>81646</v>
       </c>
       <c r="F359" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>9</v>
@@ -9779,16 +9779,16 @@
         <v>30</v>
       </c>
       <c r="C360" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D360" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E360" s="2">
-        <v>81780</v>
+        <v>81653</v>
       </c>
       <c r="F360" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>9</v>
@@ -9805,16 +9805,16 @@
         <v>30</v>
       </c>
       <c r="C361" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D361" s="3">
-        <v>46044.4079891435</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E361" s="2">
-        <v>81781</v>
+        <v>81662</v>
       </c>
       <c r="F361" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>9</v>
@@ -9837,7 +9837,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E362" s="2">
-        <v>81782</v>
+        <v>81780</v>
       </c>
       <c r="F362" s="3">
         <v>46044</v>
@@ -9863,7 +9863,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E363" s="2">
-        <v>81784</v>
+        <v>81781</v>
       </c>
       <c r="F363" s="3">
         <v>46044</v>
@@ -9889,7 +9889,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E364" s="2">
-        <v>81785</v>
+        <v>81782</v>
       </c>
       <c r="F364" s="3">
         <v>46044</v>
@@ -9915,7 +9915,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E365" s="2">
-        <v>81801</v>
+        <v>81784</v>
       </c>
       <c r="F365" s="3">
         <v>46044</v>
@@ -9935,16 +9935,16 @@
         <v>30</v>
       </c>
       <c r="C366" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D366" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E366" s="2">
-        <v>81860</v>
+        <v>81785</v>
       </c>
       <c r="F366" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>9</v>
@@ -9961,16 +9961,16 @@
         <v>30</v>
       </c>
       <c r="C367" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D367" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E367" s="2">
-        <v>81873</v>
+        <v>81801</v>
       </c>
       <c r="F367" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>9</v>
@@ -9987,13 +9987,13 @@
         <v>30</v>
       </c>
       <c r="C368" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D368" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E368" s="2">
-        <v>81865</v>
+        <v>81860</v>
       </c>
       <c r="F368" s="3">
         <v>46049</v>
@@ -10013,13 +10013,13 @@
         <v>30</v>
       </c>
       <c r="C369" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D369" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E369" s="2">
-        <v>81870</v>
+        <v>81873</v>
       </c>
       <c r="F369" s="3">
         <v>46049</v>
@@ -10045,7 +10045,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E370" s="2">
-        <v>81872</v>
+        <v>81865</v>
       </c>
       <c r="F370" s="3">
         <v>46049</v>
@@ -10071,10 +10071,10 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E371" s="2">
-        <v>81896</v>
+        <v>81870</v>
       </c>
       <c r="F371" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>9</v>
@@ -10091,16 +10091,16 @@
         <v>30</v>
       </c>
       <c r="C372" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D372" s="3">
-        <v>46051.4046937153</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E372" s="2">
-        <v>81923</v>
+        <v>81872</v>
       </c>
       <c r="F372" s="3">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>9</v>
@@ -10117,16 +10117,16 @@
         <v>30</v>
       </c>
       <c r="C373" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D373" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E373" s="2">
-        <v>81998</v>
+        <v>81896</v>
       </c>
       <c r="F373" s="3">
-        <v>46057</v>
+        <v>46050</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>9</v>
@@ -10143,16 +10143,16 @@
         <v>30</v>
       </c>
       <c r="C374" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D374" s="3">
-        <v>46057.6959672917</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E374" s="2">
-        <v>82002</v>
+        <v>81923</v>
       </c>
       <c r="F374" s="3">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>9</v>
@@ -10175,10 +10175,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E375" s="2">
-        <v>82005</v>
+        <v>81998</v>
       </c>
       <c r="F375" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>9</v>
@@ -10201,10 +10201,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E376" s="2">
-        <v>82007</v>
+        <v>82002</v>
       </c>
       <c r="F376" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>9</v>
@@ -10221,10 +10221,10 @@
         <v>30</v>
       </c>
       <c r="C377" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D377" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E377" s="2">
         <v>82005</v>
@@ -10247,16 +10247,16 @@
         <v>30</v>
       </c>
       <c r="C378" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D378" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E378" s="2">
-        <v>82075</v>
+        <v>82007</v>
       </c>
       <c r="F378" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>9</v>
@@ -10279,10 +10279,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E379" s="2">
-        <v>82077</v>
+        <v>82005</v>
       </c>
       <c r="F379" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>9</v>
@@ -10305,10 +10305,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E380" s="2">
-        <v>82099</v>
+        <v>82075</v>
       </c>
       <c r="F380" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>9</v>
@@ -10325,16 +10325,16 @@
         <v>30</v>
       </c>
       <c r="C381" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D381" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E381" s="2">
-        <v>82219</v>
+        <v>82077</v>
       </c>
       <c r="F381" s="3">
-        <v>46072</v>
+        <v>46063</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>9</v>
@@ -10351,16 +10351,16 @@
         <v>30</v>
       </c>
       <c r="C382" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D382" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E382" s="2">
-        <v>82230</v>
+        <v>82099</v>
       </c>
       <c r="F382" s="3">
-        <v>46073</v>
+        <v>46064</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>9</v>
@@ -10383,10 +10383,10 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E383" s="2">
-        <v>82231</v>
+        <v>82219</v>
       </c>
       <c r="F383" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>9</v>
@@ -10403,16 +10403,16 @@
         <v>30</v>
       </c>
       <c r="C384" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D384" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E384" s="2">
-        <v>82388</v>
+        <v>82230</v>
       </c>
       <c r="F384" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>9</v>
@@ -10429,16 +10429,16 @@
         <v>30</v>
       </c>
       <c r="C385" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D385" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E385" s="2">
-        <v>82389</v>
+        <v>82231</v>
       </c>
       <c r="F385" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>9</v>
@@ -10461,7 +10461,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E386" s="2">
-        <v>82396</v>
+        <v>82388</v>
       </c>
       <c r="F386" s="3">
         <v>46083</v>
@@ -10487,7 +10487,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E387" s="2">
-        <v>82397</v>
+        <v>82389</v>
       </c>
       <c r="F387" s="3">
         <v>46083</v>
@@ -10507,16 +10507,16 @@
         <v>30</v>
       </c>
       <c r="C388" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D388" s="3">
-        <v>46085.6249659838</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E388" s="2">
-        <v>82435</v>
+        <v>82396</v>
       </c>
       <c r="F388" s="3">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>9</v>
@@ -10533,16 +10533,16 @@
         <v>30</v>
       </c>
       <c r="C389" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D389" s="3">
-        <v>46091.449444456</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E389" s="2">
-        <v>82506</v>
+        <v>82397</v>
       </c>
       <c r="F389" s="3">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>9</v>
@@ -10559,16 +10559,16 @@
         <v>30</v>
       </c>
       <c r="C390" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D390" s="3">
-        <v>46091.4795702315</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E390" s="2">
-        <v>82509</v>
+        <v>82435</v>
       </c>
       <c r="F390" s="3">
-        <v>46091</v>
+        <v>46085</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>9</v>
@@ -10585,16 +10585,16 @@
         <v>30</v>
       </c>
       <c r="C391" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D391" s="3">
-        <v>46093.4969972338</v>
+        <v>46091.449444456</v>
       </c>
       <c r="E391" s="2">
-        <v>82589</v>
+        <v>82506</v>
       </c>
       <c r="F391" s="3">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>9</v>
@@ -10605,22 +10605,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="392">
       <c r="A392" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C392" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D392" s="3">
-        <v>46029.3821391551</v>
+        <v>46091.4795702315</v>
       </c>
       <c r="E392" s="2">
-        <v>81477</v>
+        <v>82509</v>
       </c>
       <c r="F392" s="3">
-        <v>46029</v>
+        <v>46091</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>9</v>
@@ -10631,22 +10631,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="393">
       <c r="A393" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C393" s="2">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D393" s="3">
-        <v>46030.4142968056</v>
+        <v>46093.4969972338</v>
       </c>
       <c r="E393" s="2">
-        <v>81532</v>
+        <v>82589</v>
       </c>
       <c r="F393" s="3">
-        <v>46030</v>
+        <v>46093</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>9</v>
@@ -10663,16 +10663,16 @@
         <v>31</v>
       </c>
       <c r="C394" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D394" s="3">
-        <v>46030.4142968056</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E394" s="2">
-        <v>81534</v>
+        <v>81477</v>
       </c>
       <c r="F394" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>9</v>
@@ -10695,7 +10695,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E395" s="2">
-        <v>81535</v>
+        <v>81532</v>
       </c>
       <c r="F395" s="3">
         <v>46030</v>
@@ -10721,7 +10721,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E396" s="2">
-        <v>81550</v>
+        <v>81534</v>
       </c>
       <c r="F396" s="3">
         <v>46030</v>
@@ -10747,7 +10747,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E397" s="2">
-        <v>81553</v>
+        <v>81535</v>
       </c>
       <c r="F397" s="3">
         <v>46030</v>
@@ -10773,7 +10773,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E398" s="2">
-        <v>81554</v>
+        <v>81550</v>
       </c>
       <c r="F398" s="3">
         <v>46030</v>
@@ -10799,7 +10799,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E399" s="2">
-        <v>81557</v>
+        <v>81553</v>
       </c>
       <c r="F399" s="3">
         <v>46030</v>
@@ -10825,10 +10825,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E400" s="2">
-        <v>81588</v>
+        <v>81554</v>
       </c>
       <c r="F400" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>9</v>
@@ -10845,16 +10845,16 @@
         <v>31</v>
       </c>
       <c r="C401" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D401" s="3">
-        <v>46038.593985081</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E401" s="2">
-        <v>81692</v>
+        <v>81557</v>
       </c>
       <c r="F401" s="3">
-        <v>46038</v>
+        <v>46030</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10871,16 +10871,16 @@
         <v>31</v>
       </c>
       <c r="C402" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D402" s="3">
-        <v>46044.46462125</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E402" s="2">
-        <v>81786</v>
+        <v>81588</v>
       </c>
       <c r="F402" s="3">
-        <v>46044</v>
+        <v>46031</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10897,16 +10897,16 @@
         <v>31</v>
       </c>
       <c r="C403" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D403" s="3">
-        <v>46044.6362443171</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E403" s="2">
-        <v>81844</v>
+        <v>81692</v>
       </c>
       <c r="F403" s="3">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10923,16 +10923,16 @@
         <v>31</v>
       </c>
       <c r="C404" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D404" s="3">
-        <v>46062.717040544</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E404" s="2">
-        <v>82065</v>
+        <v>81786</v>
       </c>
       <c r="F404" s="3">
-        <v>46062</v>
+        <v>46044</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>9</v>
@@ -10949,16 +10949,16 @@
         <v>31</v>
       </c>
       <c r="C405" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D405" s="3">
-        <v>46062.717040544</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E405" s="2">
-        <v>82066</v>
+        <v>81844</v>
       </c>
       <c r="F405" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>9</v>
@@ -10981,7 +10981,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E406" s="2">
-        <v>82067</v>
+        <v>82065</v>
       </c>
       <c r="F406" s="3">
         <v>46062</v>
@@ -11001,16 +11001,16 @@
         <v>31</v>
       </c>
       <c r="C407" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D407" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E407" s="2">
-        <v>82190</v>
+        <v>82066</v>
       </c>
       <c r="F407" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G407" s="1" t="s">
         <v>9</v>
@@ -11027,16 +11027,16 @@
         <v>31</v>
       </c>
       <c r="C408" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D408" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E408" s="2">
-        <v>82197</v>
+        <v>82067</v>
       </c>
       <c r="F408" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>9</v>
@@ -11053,16 +11053,16 @@
         <v>31</v>
       </c>
       <c r="C409" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D409" s="3">
-        <v>46077.5084780324</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E409" s="2">
-        <v>82270</v>
+        <v>82190</v>
       </c>
       <c r="F409" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>9</v>
@@ -11079,16 +11079,16 @@
         <v>31</v>
       </c>
       <c r="C410" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D410" s="3">
-        <v>46077.721037037</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E410" s="2">
-        <v>82285</v>
+        <v>82197</v>
       </c>
       <c r="F410" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11105,16 +11105,16 @@
         <v>31</v>
       </c>
       <c r="C411" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D411" s="3">
-        <v>46083.6694849421</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E411" s="2">
-        <v>82417</v>
+        <v>82270</v>
       </c>
       <c r="F411" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>9</v>
@@ -11131,16 +11131,16 @@
         <v>31</v>
       </c>
       <c r="C412" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D412" s="3">
-        <v>46085.7157723032</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E412" s="2">
-        <v>82457</v>
+        <v>82285</v>
       </c>
       <c r="F412" s="3">
-        <v>46086</v>
+        <v>46077</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11151,22 +11151,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="413">
       <c r="A413" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C413" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D413" s="3">
-        <v>46029.381258831</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E413" s="2">
-        <v>81484</v>
+        <v>82417</v>
       </c>
       <c r="F413" s="3">
-        <v>46029</v>
+        <v>46084</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>9</v>
@@ -11177,22 +11177,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="414">
       <c r="A414" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C414" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D414" s="3">
-        <v>46029.381258831</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E414" s="2">
-        <v>81486</v>
+        <v>82457</v>
       </c>
       <c r="F414" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>9</v>
@@ -11215,7 +11215,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E415" s="2">
-        <v>81487</v>
+        <v>81484</v>
       </c>
       <c r="F415" s="3">
         <v>46029</v>
@@ -11235,16 +11235,16 @@
         <v>32</v>
       </c>
       <c r="C416" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D416" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E416" s="2">
-        <v>81613</v>
+        <v>81486</v>
       </c>
       <c r="F416" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>9</v>
@@ -11261,16 +11261,16 @@
         <v>32</v>
       </c>
       <c r="C417" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D417" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E417" s="2">
-        <v>81614</v>
+        <v>81487</v>
       </c>
       <c r="F417" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>9</v>
@@ -11293,7 +11293,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E418" s="2">
-        <v>81622</v>
+        <v>81613</v>
       </c>
       <c r="F418" s="3">
         <v>46036</v>
@@ -11319,7 +11319,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E419" s="2">
-        <v>81632</v>
+        <v>81614</v>
       </c>
       <c r="F419" s="3">
         <v>46036</v>
@@ -11345,10 +11345,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E420" s="2">
-        <v>81648</v>
+        <v>81622</v>
       </c>
       <c r="F420" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>9</v>
@@ -11371,10 +11371,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E421" s="2">
-        <v>81664</v>
+        <v>81632</v>
       </c>
       <c r="F421" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>9</v>
@@ -11391,16 +11391,16 @@
         <v>32</v>
       </c>
       <c r="C422" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D422" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E422" s="2">
-        <v>81815</v>
+        <v>81648</v>
       </c>
       <c r="F422" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>9</v>
@@ -11417,16 +11417,16 @@
         <v>32</v>
       </c>
       <c r="C423" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D423" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E423" s="2">
-        <v>81816</v>
+        <v>81664</v>
       </c>
       <c r="F423" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>9</v>
@@ -11449,7 +11449,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E424" s="2">
-        <v>81838</v>
+        <v>81815</v>
       </c>
       <c r="F424" s="3">
         <v>46045</v>
@@ -11475,7 +11475,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E425" s="2">
-        <v>81840</v>
+        <v>81816</v>
       </c>
       <c r="F425" s="3">
         <v>46045</v>
@@ -11495,16 +11495,16 @@
         <v>32</v>
       </c>
       <c r="C426" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D426" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E426" s="2">
-        <v>81959</v>
+        <v>81838</v>
       </c>
       <c r="F426" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>9</v>
@@ -11521,16 +11521,16 @@
         <v>32</v>
       </c>
       <c r="C427" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D427" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E427" s="2">
-        <v>81960</v>
+        <v>81840</v>
       </c>
       <c r="F427" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11547,16 +11547,16 @@
         <v>32</v>
       </c>
       <c r="C428" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D428" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E428" s="2">
-        <v>82063</v>
+        <v>81959</v>
       </c>
       <c r="F428" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>9</v>
@@ -11573,16 +11573,16 @@
         <v>32</v>
       </c>
       <c r="C429" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D429" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E429" s="2">
-        <v>82064</v>
+        <v>81960</v>
       </c>
       <c r="F429" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>9</v>
@@ -11605,10 +11605,10 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E430" s="2">
-        <v>82100</v>
+        <v>82063</v>
       </c>
       <c r="F430" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>9</v>
@@ -11625,16 +11625,16 @@
         <v>32</v>
       </c>
       <c r="C431" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D431" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E431" s="2">
-        <v>82333</v>
+        <v>82064</v>
       </c>
       <c r="F431" s="3">
-        <v>46079</v>
+        <v>46062</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>9</v>
@@ -11651,16 +11651,16 @@
         <v>32</v>
       </c>
       <c r="C432" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D432" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E432" s="2">
-        <v>82334</v>
+        <v>82100</v>
       </c>
       <c r="F432" s="3">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11677,16 +11677,16 @@
         <v>32</v>
       </c>
       <c r="C433" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D433" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E433" s="2">
-        <v>82258</v>
+        <v>82333</v>
       </c>
       <c r="F433" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11703,16 +11703,16 @@
         <v>32</v>
       </c>
       <c r="C434" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D434" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E434" s="2">
-        <v>82259</v>
+        <v>82334</v>
       </c>
       <c r="F434" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>9</v>
@@ -11735,7 +11735,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E435" s="2">
-        <v>82260</v>
+        <v>82258</v>
       </c>
       <c r="F435" s="3">
         <v>46076</v>
@@ -11761,10 +11761,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E436" s="2">
-        <v>82274</v>
+        <v>82259</v>
       </c>
       <c r="F436" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>9</v>
@@ -11781,16 +11781,16 @@
         <v>32</v>
       </c>
       <c r="C437" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D437" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E437" s="2">
-        <v>82409</v>
+        <v>82260</v>
       </c>
       <c r="F437" s="3">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>9</v>
@@ -11807,16 +11807,16 @@
         <v>32</v>
       </c>
       <c r="C438" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D438" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E438" s="2">
-        <v>82581</v>
+        <v>82274</v>
       </c>
       <c r="F438" s="3">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11833,16 +11833,16 @@
         <v>32</v>
       </c>
       <c r="C439" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D439" s="3">
-        <v>46093.4920058565</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E439" s="2">
-        <v>82582</v>
+        <v>82409</v>
       </c>
       <c r="F439" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11865,7 +11865,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E440" s="2">
-        <v>82583</v>
+        <v>82581</v>
       </c>
       <c r="F440" s="3">
         <v>46093</v>
@@ -11891,10 +11891,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E441" s="2">
-        <v>82672</v>
+        <v>82582</v>
       </c>
       <c r="F441" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11917,10 +11917,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E442" s="2">
-        <v>82674</v>
+        <v>82583</v>
       </c>
       <c r="F442" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11931,22 +11931,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="443">
       <c r="A443" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C443" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D443" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E443" s="2">
-        <v>81608</v>
+        <v>82672</v>
       </c>
       <c r="F443" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11957,22 +11957,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="444">
       <c r="A444" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C444" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D444" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E444" s="2">
-        <v>81609</v>
+        <v>82674</v>
       </c>
       <c r="F444" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11995,7 +11995,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E445" s="2">
-        <v>81610</v>
+        <v>81608</v>
       </c>
       <c r="F445" s="3">
         <v>46035</v>
@@ -12021,7 +12021,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E446" s="2">
-        <v>81611</v>
+        <v>81609</v>
       </c>
       <c r="F446" s="3">
         <v>46035</v>
@@ -12047,7 +12047,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E447" s="2">
-        <v>81612</v>
+        <v>81610</v>
       </c>
       <c r="F447" s="3">
         <v>46035</v>
@@ -12067,16 +12067,16 @@
         <v>33</v>
       </c>
       <c r="C448" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D448" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E448" s="2">
-        <v>81652</v>
+        <v>81611</v>
       </c>
       <c r="F448" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12093,16 +12093,16 @@
         <v>33</v>
       </c>
       <c r="C449" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D449" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E449" s="2">
-        <v>81659</v>
+        <v>81612</v>
       </c>
       <c r="F449" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12119,16 +12119,16 @@
         <v>33</v>
       </c>
       <c r="C450" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D450" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E450" s="2">
-        <v>81853</v>
+        <v>81652</v>
       </c>
       <c r="F450" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12145,16 +12145,16 @@
         <v>33</v>
       </c>
       <c r="C451" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D451" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E451" s="2">
-        <v>81869</v>
+        <v>81659</v>
       </c>
       <c r="F451" s="3">
-        <v>46049</v>
+        <v>46037</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>9</v>
@@ -12177,10 +12177,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E452" s="2">
-        <v>81890</v>
+        <v>81853</v>
       </c>
       <c r="F452" s="3">
-        <v>46050</v>
+        <v>46048</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12197,13 +12197,13 @@
         <v>33</v>
       </c>
       <c r="C453" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D453" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E453" s="2">
-        <v>81875</v>
+        <v>81869</v>
       </c>
       <c r="F453" s="3">
         <v>46049</v>
@@ -12223,13 +12223,13 @@
         <v>33</v>
       </c>
       <c r="C454" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D454" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E454" s="2">
-        <v>81881</v>
+        <v>81890</v>
       </c>
       <c r="F454" s="3">
         <v>46050</v>
@@ -12249,16 +12249,16 @@
         <v>33</v>
       </c>
       <c r="C455" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D455" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E455" s="2">
-        <v>82015</v>
+        <v>81875</v>
       </c>
       <c r="F455" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>9</v>
@@ -12275,16 +12275,16 @@
         <v>33</v>
       </c>
       <c r="C456" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D456" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E456" s="2">
-        <v>82017</v>
+        <v>81881</v>
       </c>
       <c r="F456" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12307,7 +12307,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E457" s="2">
-        <v>82020</v>
+        <v>82015</v>
       </c>
       <c r="F457" s="3">
         <v>46058</v>
@@ -12333,7 +12333,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E458" s="2">
-        <v>82023</v>
+        <v>82017</v>
       </c>
       <c r="F458" s="3">
         <v>46058</v>
@@ -12359,10 +12359,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E459" s="2">
-        <v>82061</v>
+        <v>82020</v>
       </c>
       <c r="F459" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12385,10 +12385,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E460" s="2">
-        <v>82081</v>
+        <v>82023</v>
       </c>
       <c r="F460" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12411,10 +12411,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E461" s="2">
-        <v>82095</v>
+        <v>82061</v>
       </c>
       <c r="F461" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12431,10 +12431,10 @@
         <v>33</v>
       </c>
       <c r="C462" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D462" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E462" s="2">
         <v>82081</v>
@@ -12457,13 +12457,13 @@
         <v>33</v>
       </c>
       <c r="C463" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D463" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E463" s="2">
-        <v>82107</v>
+        <v>82095</v>
       </c>
       <c r="F463" s="3">
         <v>46064</v>
@@ -12489,10 +12489,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E464" s="2">
-        <v>82112</v>
+        <v>82081</v>
       </c>
       <c r="F464" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12515,7 +12515,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E465" s="2">
-        <v>82113</v>
+        <v>82107</v>
       </c>
       <c r="F465" s="3">
         <v>46064</v>
@@ -12541,10 +12541,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E466" s="2">
-        <v>82123</v>
+        <v>82112</v>
       </c>
       <c r="F466" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12561,13 +12561,13 @@
         <v>33</v>
       </c>
       <c r="C467" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D467" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E467" s="2">
-        <v>82095</v>
+        <v>82113</v>
       </c>
       <c r="F467" s="3">
         <v>46064</v>
@@ -12587,16 +12587,16 @@
         <v>33</v>
       </c>
       <c r="C468" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D468" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E468" s="2">
-        <v>82106</v>
+        <v>82123</v>
       </c>
       <c r="F468" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>9</v>
@@ -12619,7 +12619,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E469" s="2">
-        <v>82107</v>
+        <v>82095</v>
       </c>
       <c r="F469" s="3">
         <v>46064</v>
@@ -12645,7 +12645,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E470" s="2">
-        <v>82109</v>
+        <v>82106</v>
       </c>
       <c r="F470" s="3">
         <v>46064</v>
@@ -12671,7 +12671,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E471" s="2">
-        <v>82110</v>
+        <v>82107</v>
       </c>
       <c r="F471" s="3">
         <v>46064</v>
@@ -12697,10 +12697,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E472" s="2">
-        <v>82139</v>
+        <v>82109</v>
       </c>
       <c r="F472" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12717,16 +12717,16 @@
         <v>33</v>
       </c>
       <c r="C473" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D473" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E473" s="2">
-        <v>82365</v>
+        <v>82110</v>
       </c>
       <c r="F473" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12743,16 +12743,16 @@
         <v>33</v>
       </c>
       <c r="C474" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D474" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E474" s="2">
-        <v>82366</v>
+        <v>82139</v>
       </c>
       <c r="F474" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12775,7 +12775,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E475" s="2">
-        <v>82371</v>
+        <v>82365</v>
       </c>
       <c r="F475" s="3">
         <v>46080</v>
@@ -12801,10 +12801,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E476" s="2">
-        <v>82383</v>
+        <v>82366</v>
       </c>
       <c r="F476" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>9</v>
@@ -12827,10 +12827,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E477" s="2">
-        <v>82384</v>
+        <v>82371</v>
       </c>
       <c r="F477" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>9</v>
@@ -12841,48 +12841,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="478">
       <c r="A478" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C478" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D478" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E478" s="2">
-        <v>81592</v>
+        <v>82383</v>
       </c>
       <c r="F478" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="G478" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H478" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="479">
       <c r="A479" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C479" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D479" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E479" s="2">
-        <v>81593</v>
+        <v>82384</v>
       </c>
       <c r="F479" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12893,22 +12893,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="480">
       <c r="A480" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C480" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D480" s="3">
-        <v>46038.6827563889</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E480" s="2">
-        <v>81697</v>
+        <v>82693</v>
       </c>
       <c r="F480" s="3">
-        <v>46038</v>
+        <v>46098</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>9</v>
@@ -12925,16 +12925,16 @@
         <v>34</v>
       </c>
       <c r="C481" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D481" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E481" s="2">
-        <v>81735</v>
+        <v>81592</v>
       </c>
       <c r="F481" s="3">
-        <v>46041</v>
+        <v>46031</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>24</v>
@@ -12951,16 +12951,16 @@
         <v>34</v>
       </c>
       <c r="C482" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D482" s="3">
-        <v>46045.4532476157</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E482" s="2">
-        <v>81823</v>
+        <v>81593</v>
       </c>
       <c r="F482" s="3">
-        <v>46045</v>
+        <v>46031</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12971,22 +12971,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="483">
       <c r="A483" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C483" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D483" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E483" s="2">
-        <v>81572</v>
+        <v>81697</v>
       </c>
       <c r="F483" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>9</v>
@@ -12997,48 +12997,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="484">
       <c r="A484" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C484" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D484" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E484" s="2">
-        <v>81573</v>
+        <v>81735</v>
       </c>
       <c r="F484" s="3">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H484" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="485">
       <c r="A485" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C485" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D485" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E485" s="2">
-        <v>81579</v>
+        <v>81823</v>
       </c>
       <c r="F485" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>9</v>
@@ -13061,7 +13061,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E486" s="2">
-        <v>81580</v>
+        <v>81572</v>
       </c>
       <c r="F486" s="3">
         <v>46031</v>
@@ -13087,7 +13087,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E487" s="2">
-        <v>81581</v>
+        <v>81573</v>
       </c>
       <c r="F487" s="3">
         <v>46031</v>
@@ -13113,7 +13113,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E488" s="2">
-        <v>81582</v>
+        <v>81579</v>
       </c>
       <c r="F488" s="3">
         <v>46031</v>
@@ -13139,7 +13139,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E489" s="2">
-        <v>81583</v>
+        <v>81580</v>
       </c>
       <c r="F489" s="3">
         <v>46031</v>
@@ -13159,16 +13159,16 @@
         <v>35</v>
       </c>
       <c r="C490" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D490" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E490" s="2">
-        <v>81667</v>
+        <v>81581</v>
       </c>
       <c r="F490" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>9</v>
@@ -13185,16 +13185,16 @@
         <v>35</v>
       </c>
       <c r="C491" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D491" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E491" s="2">
-        <v>81668</v>
+        <v>81582</v>
       </c>
       <c r="F491" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>9</v>
@@ -13211,16 +13211,16 @@
         <v>35</v>
       </c>
       <c r="C492" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D492" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E492" s="2">
-        <v>81674</v>
+        <v>81583</v>
       </c>
       <c r="F492" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G492" s="1" t="s">
         <v>9</v>
@@ -13243,10 +13243,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E493" s="2">
-        <v>81675</v>
+        <v>81667</v>
       </c>
       <c r="F493" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G493" s="1" t="s">
         <v>9</v>
@@ -13269,10 +13269,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E494" s="2">
-        <v>81677</v>
+        <v>81668</v>
       </c>
       <c r="F494" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>9</v>
@@ -13289,16 +13289,16 @@
         <v>35</v>
       </c>
       <c r="C495" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D495" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E495" s="2">
-        <v>81739</v>
+        <v>81674</v>
       </c>
       <c r="F495" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>9</v>
@@ -13315,16 +13315,16 @@
         <v>35</v>
       </c>
       <c r="C496" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D496" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E496" s="2">
-        <v>81741</v>
+        <v>81675</v>
       </c>
       <c r="F496" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G496" s="1" t="s">
         <v>9</v>
@@ -13341,16 +13341,16 @@
         <v>35</v>
       </c>
       <c r="C497" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D497" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E497" s="2">
-        <v>81854</v>
+        <v>81677</v>
       </c>
       <c r="F497" s="3">
-        <v>46048</v>
+        <v>46038</v>
       </c>
       <c r="G497" s="1" t="s">
         <v>9</v>
@@ -13367,16 +13367,16 @@
         <v>35</v>
       </c>
       <c r="C498" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D498" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E498" s="2">
-        <v>81855</v>
+        <v>81739</v>
       </c>
       <c r="F498" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G498" s="1" t="s">
         <v>9</v>
@@ -13393,16 +13393,16 @@
         <v>35</v>
       </c>
       <c r="C499" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D499" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E499" s="2">
-        <v>81858</v>
+        <v>81741</v>
       </c>
       <c r="F499" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>9</v>
@@ -13425,10 +13425,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E500" s="2">
-        <v>81859</v>
+        <v>81854</v>
       </c>
       <c r="F500" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G500" s="1" t="s">
         <v>9</v>
@@ -13451,10 +13451,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E501" s="2">
-        <v>81862</v>
+        <v>81855</v>
       </c>
       <c r="F501" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G501" s="1" t="s">
         <v>9</v>
@@ -13477,7 +13477,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E502" s="2">
-        <v>81863</v>
+        <v>81858</v>
       </c>
       <c r="F502" s="3">
         <v>46049</v>
@@ -13497,16 +13497,16 @@
         <v>35</v>
       </c>
       <c r="C503" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D503" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E503" s="2">
-        <v>81958</v>
+        <v>81859</v>
       </c>
       <c r="F503" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G503" s="1" t="s">
         <v>9</v>
@@ -13523,16 +13523,16 @@
         <v>35</v>
       </c>
       <c r="C504" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D504" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E504" s="2">
-        <v>81965</v>
+        <v>81862</v>
       </c>
       <c r="F504" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>9</v>
@@ -13549,16 +13549,16 @@
         <v>35</v>
       </c>
       <c r="C505" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D505" s="3">
-        <v>46063.5923590625</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E505" s="2">
-        <v>82085</v>
+        <v>81863</v>
       </c>
       <c r="F505" s="3">
-        <v>46063</v>
+        <v>46049</v>
       </c>
       <c r="G505" s="1" t="s">
         <v>9</v>
@@ -13575,16 +13575,16 @@
         <v>35</v>
       </c>
       <c r="C506" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D506" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E506" s="2">
-        <v>82086</v>
+        <v>81958</v>
       </c>
       <c r="F506" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>9</v>
@@ -13601,16 +13601,16 @@
         <v>35</v>
       </c>
       <c r="C507" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D507" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E507" s="2">
-        <v>82126</v>
+        <v>81965</v>
       </c>
       <c r="F507" s="3">
-        <v>46065</v>
+        <v>46055</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>9</v>
@@ -13627,16 +13627,16 @@
         <v>35</v>
       </c>
       <c r="C508" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D508" s="3">
-        <v>46064.5127051505</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E508" s="2">
-        <v>82268</v>
+        <v>82085</v>
       </c>
       <c r="F508" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G508" s="1" t="s">
         <v>9</v>
@@ -13653,16 +13653,16 @@
         <v>35</v>
       </c>
       <c r="C509" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D509" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E509" s="2">
-        <v>82142</v>
+        <v>82086</v>
       </c>
       <c r="F509" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G509" s="1" t="s">
         <v>9</v>
@@ -13679,13 +13679,13 @@
         <v>35</v>
       </c>
       <c r="C510" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D510" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E510" s="2">
-        <v>82143</v>
+        <v>82126</v>
       </c>
       <c r="F510" s="3">
         <v>46065</v>
@@ -13705,16 +13705,16 @@
         <v>35</v>
       </c>
       <c r="C511" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D511" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E511" s="2">
-        <v>82144</v>
+        <v>82268</v>
       </c>
       <c r="F511" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>9</v>
@@ -13737,10 +13737,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E512" s="2">
-        <v>82166</v>
+        <v>82142</v>
       </c>
       <c r="F512" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="G512" s="1" t="s">
         <v>9</v>
@@ -13757,16 +13757,16 @@
         <v>35</v>
       </c>
       <c r="C513" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D513" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E513" s="2">
-        <v>82262</v>
+        <v>82143</v>
       </c>
       <c r="F513" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G513" s="1" t="s">
         <v>9</v>
@@ -13783,16 +13783,16 @@
         <v>35</v>
       </c>
       <c r="C514" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D514" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E514" s="2">
-        <v>82265</v>
+        <v>82144</v>
       </c>
       <c r="F514" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G514" s="1" t="s">
         <v>9</v>
@@ -13809,16 +13809,16 @@
         <v>35</v>
       </c>
       <c r="C515" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D515" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E515" s="2">
-        <v>82281</v>
+        <v>82166</v>
       </c>
       <c r="F515" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G515" s="1" t="s">
         <v>9</v>
@@ -13841,7 +13841,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E516" s="2">
-        <v>82282</v>
+        <v>82262</v>
       </c>
       <c r="F516" s="3">
         <v>46077</v>
@@ -13861,16 +13861,16 @@
         <v>35</v>
       </c>
       <c r="C517" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D517" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E517" s="2">
-        <v>82340</v>
+        <v>82265</v>
       </c>
       <c r="F517" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G517" s="1" t="s">
         <v>9</v>
@@ -13887,16 +13887,16 @@
         <v>35</v>
       </c>
       <c r="C518" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D518" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E518" s="2">
-        <v>82399</v>
+        <v>82281</v>
       </c>
       <c r="F518" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>9</v>
@@ -13913,16 +13913,16 @@
         <v>35</v>
       </c>
       <c r="C519" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D519" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E519" s="2">
-        <v>82400</v>
+        <v>82282</v>
       </c>
       <c r="F519" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G519" s="1" t="s">
         <v>9</v>
@@ -13939,16 +13939,16 @@
         <v>35</v>
       </c>
       <c r="C520" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D520" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E520" s="2">
-        <v>82401</v>
+        <v>82340</v>
       </c>
       <c r="F520" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="G520" s="1" t="s">
         <v>9</v>
@@ -13971,10 +13971,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E521" s="2">
-        <v>82412</v>
+        <v>82399</v>
       </c>
       <c r="F521" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G521" s="1" t="s">
         <v>9</v>
@@ -13997,10 +13997,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E522" s="2">
-        <v>82415</v>
+        <v>82400</v>
       </c>
       <c r="F522" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G522" s="1" t="s">
         <v>9</v>
@@ -14017,16 +14017,16 @@
         <v>35</v>
       </c>
       <c r="C523" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D523" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E523" s="2">
-        <v>82571</v>
+        <v>82401</v>
       </c>
       <c r="F523" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>9</v>
@@ -14043,16 +14043,16 @@
         <v>35</v>
       </c>
       <c r="C524" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D524" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E524" s="2">
-        <v>82572</v>
+        <v>82412</v>
       </c>
       <c r="F524" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G524" s="1" t="s">
         <v>9</v>
@@ -14069,16 +14069,16 @@
         <v>35</v>
       </c>
       <c r="C525" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D525" s="3">
-        <v>46094.4745190394</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E525" s="2">
-        <v>82630</v>
+        <v>82415</v>
       </c>
       <c r="F525" s="3">
-        <v>46094</v>
+        <v>46084</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>9</v>
@@ -14095,16 +14095,16 @@
         <v>35</v>
       </c>
       <c r="C526" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D526" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E526" s="2">
-        <v>82631</v>
+        <v>82571</v>
       </c>
       <c r="F526" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G526" s="1" t="s">
         <v>9</v>
@@ -14121,16 +14121,16 @@
         <v>35</v>
       </c>
       <c r="C527" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D527" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E527" s="2">
-        <v>82632</v>
+        <v>82572</v>
       </c>
       <c r="F527" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G527" s="1" t="s">
         <v>9</v>
@@ -14147,16 +14147,16 @@
         <v>35</v>
       </c>
       <c r="C528" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D528" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E528" s="2">
-        <v>82653</v>
+        <v>82630</v>
       </c>
       <c r="F528" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G528" s="1" t="s">
         <v>9</v>
@@ -14173,16 +14173,16 @@
         <v>35</v>
       </c>
       <c r="C529" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D529" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E529" s="2">
-        <v>82665</v>
+        <v>82631</v>
       </c>
       <c r="F529" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G529" s="1" t="s">
         <v>9</v>
@@ -14199,16 +14199,16 @@
         <v>35</v>
       </c>
       <c r="C530" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D530" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E530" s="2">
-        <v>82668</v>
+        <v>82632</v>
       </c>
       <c r="F530" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>9</v>
@@ -14219,22 +14219,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="531">
       <c r="A531" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C531" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D531" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E531" s="2">
-        <v>82311</v>
+        <v>82653</v>
       </c>
       <c r="F531" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G531" s="1" t="s">
         <v>9</v>
@@ -14245,22 +14245,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="532">
       <c r="A532" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C532" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D532" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E532" s="2">
-        <v>82312</v>
+        <v>82665</v>
       </c>
       <c r="F532" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G532" s="1" t="s">
         <v>9</v>
@@ -14271,22 +14271,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="533">
       <c r="A533" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C533" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D533" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E533" s="2">
-        <v>82313</v>
+        <v>82668</v>
       </c>
       <c r="F533" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G533" s="1" t="s">
         <v>9</v>
@@ -14297,28 +14297,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="534">
       <c r="A534" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C534" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D534" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E534" s="2">
-        <v>82314</v>
+        <v>82696</v>
       </c>
       <c r="F534" s="3">
-        <v>46078</v>
+        <v>46098</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H534" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="535">
@@ -14335,10 +14335,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E535" s="2">
-        <v>82346</v>
+        <v>82311</v>
       </c>
       <c r="F535" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G535" s="1" t="s">
         <v>9</v>
@@ -14361,10 +14361,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E536" s="2">
-        <v>82361</v>
+        <v>82312</v>
       </c>
       <c r="F536" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G536" s="1" t="s">
         <v>9</v>
@@ -14387,10 +14387,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E537" s="2">
-        <v>82385</v>
+        <v>82313</v>
       </c>
       <c r="F537" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G537" s="1" t="s">
         <v>9</v>
@@ -14413,10 +14413,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E538" s="2">
-        <v>82391</v>
+        <v>82314</v>
       </c>
       <c r="F538" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G538" s="1" t="s">
         <v>9</v>
@@ -14439,10 +14439,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E539" s="2">
-        <v>82392</v>
+        <v>82346</v>
       </c>
       <c r="F539" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G539" s="1" t="s">
         <v>9</v>
@@ -14453,22 +14453,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="540">
       <c r="A540" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C540" s="2">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D540" s="3">
-        <v>46029.4632696412</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E540" s="2">
-        <v>81495</v>
+        <v>82361</v>
       </c>
       <c r="F540" s="3">
-        <v>46029</v>
+        <v>46080</v>
       </c>
       <c r="G540" s="1" t="s">
         <v>9</v>
@@ -14479,27 +14479,183 @@
     </row>
     <row ht="12.75" customHeight="1" r="541">
       <c r="A541" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C541" s="2">
+        <v>1</v>
+      </c>
+      <c r="D541" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E541" s="2">
+        <v>82385</v>
+      </c>
+      <c r="F541" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G541" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H541" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="542">
+      <c r="A542" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C542" s="2">
+        <v>1</v>
+      </c>
+      <c r="D542" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E542" s="2">
+        <v>82391</v>
+      </c>
+      <c r="F542" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G542" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H542" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="543">
+      <c r="A543" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C543" s="2">
+        <v>1</v>
+      </c>
+      <c r="D543" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E543" s="2">
+        <v>82392</v>
+      </c>
+      <c r="F543" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G543" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H543" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="544">
+      <c r="A544" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C544" s="2">
+        <v>2</v>
+      </c>
+      <c r="D544" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="E544" s="2">
+        <v>82691</v>
+      </c>
+      <c r="F544" s="3">
+        <v>46098</v>
+      </c>
+      <c r="G544" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H544" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="545">
+      <c r="A545" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C545" s="2">
+        <v>2</v>
+      </c>
+      <c r="D545" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="E545" s="2">
+        <v>82692</v>
+      </c>
+      <c r="F545" s="3">
+        <v>46098</v>
+      </c>
+      <c r="G545" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H545" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="546">
+      <c r="A546" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C546" s="2">
+        <v>62</v>
+      </c>
+      <c r="D546" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E546" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F546" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G546" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H546" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="547">
+      <c r="A547" s="2">
         <v>9992</v>
       </c>
-      <c r="B541" s="1" t="s">
+      <c r="B547" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C541" s="2">
+      <c r="C547" s="2">
         <v>390</v>
       </c>
-      <c r="D541" s="3">
+      <c r="D547" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E541" s="2">
+      <c r="E547" s="2">
         <v>81684</v>
       </c>
-      <c r="F541" s="3">
+      <c r="F547" s="3">
         <v>46038</v>
       </c>
-      <c r="G541" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H541" s="1" t="s">
+      <c r="G547" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H547" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -92,16 +92,16 @@
     <t>Reprovados</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Em Aprovação</t>
+  </si>
+  <si>
     <t>KATIA FERREIRA DE BARROS</t>
   </si>
   <si>
     <t>RAFAEL CURSINO DE MOURA LEVY</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Em Aprovação</t>
   </si>
   <si>
     <t>SAMAUMA EVENTOS LTDA</t>
@@ -5891,10 +5891,10 @@
         <v>46098</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="211">
@@ -6723,36 +6723,36 @@
         <v>46098</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="243">
       <c r="A243" s="2">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C243" s="2">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D243" s="3">
-        <v>46098.5034667708</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E243" s="2">
-        <v>82688</v>
+        <v>81802</v>
       </c>
       <c r="F243" s="3">
-        <v>46098</v>
+        <v>46044</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="244">
@@ -6760,7 +6760,7 @@
         <v>2506</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C244" s="2">
         <v>27</v>
@@ -6769,7 +6769,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E244" s="2">
-        <v>81802</v>
+        <v>81803</v>
       </c>
       <c r="F244" s="3">
         <v>46044</v>
@@ -6786,7 +6786,7 @@
         <v>2506</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C245" s="2">
         <v>27</v>
@@ -6795,7 +6795,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E245" s="2">
-        <v>81803</v>
+        <v>81804</v>
       </c>
       <c r="F245" s="3">
         <v>46044</v>
@@ -6812,7 +6812,7 @@
         <v>2506</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C246" s="2">
         <v>27</v>
@@ -6821,7 +6821,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E246" s="2">
-        <v>81804</v>
+        <v>81806</v>
       </c>
       <c r="F246" s="3">
         <v>46044</v>
@@ -6838,7 +6838,7 @@
         <v>2506</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C247" s="2">
         <v>27</v>
@@ -6847,7 +6847,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E247" s="2">
-        <v>81806</v>
+        <v>81807</v>
       </c>
       <c r="F247" s="3">
         <v>46044</v>
@@ -6864,7 +6864,7 @@
         <v>2506</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C248" s="2">
         <v>27</v>
@@ -6873,10 +6873,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E248" s="2">
-        <v>81807</v>
+        <v>81812</v>
       </c>
       <c r="F248" s="3">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>9</v>
@@ -6890,7 +6890,7 @@
         <v>2506</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C249" s="2">
         <v>27</v>
@@ -6899,7 +6899,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E249" s="2">
-        <v>81812</v>
+        <v>81813</v>
       </c>
       <c r="F249" s="3">
         <v>46045</v>
@@ -6916,7 +6916,7 @@
         <v>2506</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C250" s="2">
         <v>27</v>
@@ -6925,7 +6925,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E250" s="2">
-        <v>81813</v>
+        <v>81814</v>
       </c>
       <c r="F250" s="3">
         <v>46045</v>
@@ -6942,7 +6942,7 @@
         <v>2506</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C251" s="2">
         <v>27</v>
@@ -6951,7 +6951,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E251" s="2">
-        <v>81814</v>
+        <v>81818</v>
       </c>
       <c r="F251" s="3">
         <v>46045</v>
@@ -6968,7 +6968,7 @@
         <v>2506</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C252" s="2">
         <v>27</v>
@@ -6977,7 +6977,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E252" s="2">
-        <v>81818</v>
+        <v>81822</v>
       </c>
       <c r="F252" s="3">
         <v>46045</v>
@@ -6994,7 +6994,7 @@
         <v>2506</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C253" s="2">
         <v>27</v>
@@ -7003,7 +7003,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E253" s="2">
-        <v>81822</v>
+        <v>81833</v>
       </c>
       <c r="F253" s="3">
         <v>46045</v>
@@ -7020,7 +7020,7 @@
         <v>2506</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C254" s="2">
         <v>27</v>
@@ -7029,7 +7029,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E254" s="2">
-        <v>81833</v>
+        <v>81841</v>
       </c>
       <c r="F254" s="3">
         <v>46045</v>
@@ -7046,19 +7046,19 @@
         <v>2506</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C255" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D255" s="3">
-        <v>46044.6368950926</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E255" s="2">
-        <v>81841</v>
+        <v>81928</v>
       </c>
       <c r="F255" s="3">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>9</v>
@@ -7072,7 +7072,7 @@
         <v>2506</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C256" s="2">
         <v>28</v>
@@ -7081,7 +7081,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E256" s="2">
-        <v>81928</v>
+        <v>81929</v>
       </c>
       <c r="F256" s="3">
         <v>46052</v>
@@ -7098,7 +7098,7 @@
         <v>2506</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C257" s="2">
         <v>28</v>
@@ -7107,7 +7107,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E257" s="2">
-        <v>81929</v>
+        <v>81930</v>
       </c>
       <c r="F257" s="3">
         <v>46052</v>
@@ -7124,7 +7124,7 @@
         <v>2506</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C258" s="2">
         <v>28</v>
@@ -7133,7 +7133,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E258" s="2">
-        <v>81930</v>
+        <v>81932</v>
       </c>
       <c r="F258" s="3">
         <v>46052</v>
@@ -7150,7 +7150,7 @@
         <v>2506</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C259" s="2">
         <v>28</v>
@@ -7159,7 +7159,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E259" s="2">
-        <v>81932</v>
+        <v>81933</v>
       </c>
       <c r="F259" s="3">
         <v>46052</v>
@@ -7176,7 +7176,7 @@
         <v>2506</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C260" s="2">
         <v>28</v>
@@ -7185,7 +7185,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E260" s="2">
-        <v>81933</v>
+        <v>81934</v>
       </c>
       <c r="F260" s="3">
         <v>46052</v>
@@ -7202,7 +7202,7 @@
         <v>2506</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C261" s="2">
         <v>28</v>
@@ -7211,7 +7211,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E261" s="2">
-        <v>81934</v>
+        <v>81935</v>
       </c>
       <c r="F261" s="3">
         <v>46052</v>
@@ -7228,7 +7228,7 @@
         <v>2506</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C262" s="2">
         <v>28</v>
@@ -7237,7 +7237,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E262" s="2">
-        <v>81935</v>
+        <v>81936</v>
       </c>
       <c r="F262" s="3">
         <v>46052</v>
@@ -7254,19 +7254,19 @@
         <v>2506</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C263" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D263" s="3">
-        <v>46052.4025905208</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E263" s="2">
-        <v>81936</v>
+        <v>82222</v>
       </c>
       <c r="F263" s="3">
-        <v>46052</v>
+        <v>46072</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>9</v>
@@ -7280,7 +7280,7 @@
         <v>2506</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C264" s="2">
         <v>29</v>
@@ -7289,10 +7289,10 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E264" s="2">
-        <v>82222</v>
+        <v>82226</v>
       </c>
       <c r="F264" s="3">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>9</v>
@@ -7306,7 +7306,7 @@
         <v>2506</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C265" s="2">
         <v>29</v>
@@ -7315,7 +7315,7 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E265" s="2">
-        <v>82226</v>
+        <v>82229</v>
       </c>
       <c r="F265" s="3">
         <v>46073</v>
@@ -7332,16 +7332,16 @@
         <v>2506</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C266" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D266" s="3">
-        <v>46072.7468210069</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E266" s="2">
-        <v>82229</v>
+        <v>82246</v>
       </c>
       <c r="F266" s="3">
         <v>46073</v>
@@ -7358,19 +7358,19 @@
         <v>2506</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C267" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D267" s="3">
-        <v>46073.5838834375</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E267" s="2">
-        <v>82246</v>
+        <v>82387</v>
       </c>
       <c r="F267" s="3">
-        <v>46073</v>
+        <v>46083</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>9</v>
@@ -7384,19 +7384,19 @@
         <v>2506</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C268" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D268" s="3">
-        <v>46080.6289065162</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E268" s="2">
-        <v>82387</v>
+        <v>82590</v>
       </c>
       <c r="F268" s="3">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>9</v>
@@ -7410,7 +7410,7 @@
         <v>2506</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C269" s="2">
         <v>32</v>
@@ -7419,16 +7419,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E269" s="2">
-        <v>82590</v>
+        <v>82591</v>
       </c>
       <c r="F269" s="3">
         <v>46093</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="270">
@@ -7436,7 +7436,7 @@
         <v>2506</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C270" s="2">
         <v>32</v>
@@ -7445,16 +7445,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E270" s="2">
-        <v>82591</v>
+        <v>82592</v>
       </c>
       <c r="F270" s="3">
         <v>46093</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="271">
@@ -7462,7 +7462,7 @@
         <v>2506</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C271" s="2">
         <v>32</v>
@@ -7471,7 +7471,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E271" s="2">
-        <v>82592</v>
+        <v>82593</v>
       </c>
       <c r="F271" s="3">
         <v>46093</v>
@@ -7488,7 +7488,7 @@
         <v>2506</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C272" s="2">
         <v>32</v>
@@ -7497,7 +7497,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E272" s="2">
-        <v>82593</v>
+        <v>82600</v>
       </c>
       <c r="F272" s="3">
         <v>46093</v>
@@ -7514,7 +7514,7 @@
         <v>2506</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C273" s="2">
         <v>32</v>
@@ -7523,7 +7523,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E273" s="2">
-        <v>82600</v>
+        <v>82603</v>
       </c>
       <c r="F273" s="3">
         <v>46093</v>
@@ -7540,7 +7540,7 @@
         <v>2506</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C274" s="2">
         <v>32</v>
@@ -7549,7 +7549,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E274" s="2">
-        <v>82603</v>
+        <v>82604</v>
       </c>
       <c r="F274" s="3">
         <v>46093</v>
@@ -7566,7 +7566,7 @@
         <v>2506</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C275" s="2">
         <v>32</v>
@@ -7575,7 +7575,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E275" s="2">
-        <v>82604</v>
+        <v>82605</v>
       </c>
       <c r="F275" s="3">
         <v>46093</v>
@@ -7589,22 +7589,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="276">
       <c r="A276" s="2">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="B276" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C276" s="2">
         <v>26</v>
       </c>
-      <c r="C276" s="2">
-        <v>32</v>
-      </c>
       <c r="D276" s="3">
-        <v>46093.4978086806</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E276" s="2">
-        <v>82605</v>
+        <v>81478</v>
       </c>
       <c r="F276" s="3">
-        <v>46093</v>
+        <v>46029</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>9</v>
@@ -7618,7 +7618,7 @@
         <v>2507</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C277" s="2">
         <v>26</v>
@@ -7627,7 +7627,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E277" s="2">
-        <v>81478</v>
+        <v>81479</v>
       </c>
       <c r="F277" s="3">
         <v>46029</v>
@@ -7644,7 +7644,7 @@
         <v>2507</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C278" s="2">
         <v>26</v>
@@ -7653,7 +7653,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E278" s="2">
-        <v>81479</v>
+        <v>81480</v>
       </c>
       <c r="F278" s="3">
         <v>46029</v>
@@ -7670,7 +7670,7 @@
         <v>2507</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C279" s="2">
         <v>26</v>
@@ -7679,7 +7679,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E279" s="2">
-        <v>81480</v>
+        <v>81497</v>
       </c>
       <c r="F279" s="3">
         <v>46029</v>
@@ -7696,7 +7696,7 @@
         <v>2507</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C280" s="2">
         <v>26</v>
@@ -7705,7 +7705,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E280" s="2">
-        <v>81497</v>
+        <v>81498</v>
       </c>
       <c r="F280" s="3">
         <v>46029</v>
@@ -7722,7 +7722,7 @@
         <v>2507</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C281" s="2">
         <v>26</v>
@@ -7731,7 +7731,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E281" s="2">
-        <v>81498</v>
+        <v>81499</v>
       </c>
       <c r="F281" s="3">
         <v>46029</v>
@@ -7748,7 +7748,7 @@
         <v>2507</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C282" s="2">
         <v>26</v>
@@ -7757,7 +7757,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E282" s="2">
-        <v>81499</v>
+        <v>81500</v>
       </c>
       <c r="F282" s="3">
         <v>46029</v>
@@ -7774,19 +7774,19 @@
         <v>2507</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C283" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D283" s="3">
-        <v>46029.4161474769</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E283" s="2">
-        <v>81500</v>
+        <v>81878</v>
       </c>
       <c r="F283" s="3">
-        <v>46029</v>
+        <v>46049</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>9</v>
@@ -7800,7 +7800,7 @@
         <v>2507</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C284" s="2">
         <v>27</v>
@@ -7809,7 +7809,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E284" s="2">
-        <v>81878</v>
+        <v>81879</v>
       </c>
       <c r="F284" s="3">
         <v>46049</v>
@@ -7826,7 +7826,7 @@
         <v>2507</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C285" s="2">
         <v>27</v>
@@ -7835,10 +7835,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E285" s="2">
-        <v>81879</v>
+        <v>81885</v>
       </c>
       <c r="F285" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>9</v>
@@ -7852,7 +7852,7 @@
         <v>2507</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C286" s="2">
         <v>27</v>
@@ -7861,7 +7861,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E286" s="2">
-        <v>81885</v>
+        <v>81886</v>
       </c>
       <c r="F286" s="3">
         <v>46050</v>
@@ -7878,19 +7878,19 @@
         <v>2507</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C287" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D287" s="3">
-        <v>46049.6888218403</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E287" s="2">
-        <v>81886</v>
+        <v>82068</v>
       </c>
       <c r="F287" s="3">
-        <v>46050</v>
+        <v>46062</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>9</v>
@@ -7904,7 +7904,7 @@
         <v>2507</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C288" s="2">
         <v>28</v>
@@ -7913,10 +7913,10 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E288" s="2">
-        <v>82068</v>
+        <v>82072</v>
       </c>
       <c r="F288" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>9</v>
@@ -7930,7 +7930,7 @@
         <v>2507</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C289" s="2">
         <v>28</v>
@@ -7939,7 +7939,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E289" s="2">
-        <v>82072</v>
+        <v>82076</v>
       </c>
       <c r="F289" s="3">
         <v>46063</v>
@@ -7956,7 +7956,7 @@
         <v>2507</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C290" s="2">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E290" s="2">
-        <v>82076</v>
+        <v>82078</v>
       </c>
       <c r="F290" s="3">
         <v>46063</v>
@@ -7982,19 +7982,19 @@
         <v>2507</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C291" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D291" s="3">
-        <v>46062.7199601505</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E291" s="2">
-        <v>82078</v>
+        <v>82287</v>
       </c>
       <c r="F291" s="3">
-        <v>46063</v>
+        <v>46077</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>9</v>
@@ -8008,7 +8008,7 @@
         <v>2507</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C292" s="2">
         <v>29</v>
@@ -8017,7 +8017,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E292" s="2">
-        <v>82287</v>
+        <v>82288</v>
       </c>
       <c r="F292" s="3">
         <v>46077</v>
@@ -8034,7 +8034,7 @@
         <v>2507</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C293" s="2">
         <v>29</v>
@@ -8043,10 +8043,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E293" s="2">
-        <v>82288</v>
+        <v>82298</v>
       </c>
       <c r="F293" s="3">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>9</v>
@@ -8060,7 +8060,7 @@
         <v>2507</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C294" s="2">
         <v>29</v>
@@ -8069,7 +8069,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E294" s="2">
-        <v>82298</v>
+        <v>82301</v>
       </c>
       <c r="F294" s="3">
         <v>46078</v>
@@ -8086,7 +8086,7 @@
         <v>2507</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C295" s="2">
         <v>29</v>
@@ -8095,7 +8095,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E295" s="2">
-        <v>82301</v>
+        <v>82304</v>
       </c>
       <c r="F295" s="3">
         <v>46078</v>
@@ -8112,7 +8112,7 @@
         <v>2507</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C296" s="2">
         <v>29</v>
@@ -8121,7 +8121,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E296" s="2">
-        <v>82304</v>
+        <v>82308</v>
       </c>
       <c r="F296" s="3">
         <v>46078</v>
@@ -8138,19 +8138,19 @@
         <v>2507</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C297" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D297" s="3">
-        <v>46077.7216803356</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E297" s="2">
-        <v>82308</v>
+        <v>82373</v>
       </c>
       <c r="F297" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>9</v>
@@ -8164,19 +8164,19 @@
         <v>2507</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C298" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D298" s="3">
-        <v>46080.628344919</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E298" s="2">
-        <v>82373</v>
+        <v>82445</v>
       </c>
       <c r="F298" s="3">
-        <v>46080</v>
+        <v>46085</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>9</v>
@@ -8190,7 +8190,7 @@
         <v>2507</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C299" s="2">
         <v>31</v>
@@ -8199,7 +8199,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E299" s="2">
-        <v>82445</v>
+        <v>82447</v>
       </c>
       <c r="F299" s="3">
         <v>46085</v>
@@ -8216,7 +8216,7 @@
         <v>2507</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C300" s="2">
         <v>31</v>
@@ -8225,10 +8225,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E300" s="2">
-        <v>82447</v>
+        <v>82453</v>
       </c>
       <c r="F300" s="3">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>9</v>
@@ -8242,7 +8242,7 @@
         <v>2507</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C301" s="2">
         <v>31</v>
@@ -8251,7 +8251,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E301" s="2">
-        <v>82453</v>
+        <v>82468</v>
       </c>
       <c r="F301" s="3">
         <v>46086</v>
@@ -8268,19 +8268,19 @@
         <v>2507</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C302" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D302" s="3">
-        <v>46085.6581644213</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E302" s="2">
-        <v>82468</v>
+        <v>82697</v>
       </c>
       <c r="F302" s="3">
-        <v>46086</v>
+        <v>46098</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>9</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="303">
       <c r="A303" s="2">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C303" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D303" s="3">
-        <v>46098.6669450579</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E303" s="2">
-        <v>82697</v>
+        <v>81506</v>
       </c>
       <c r="F303" s="3">
-        <v>46098</v>
+        <v>46029</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>9</v>
@@ -8320,7 +8320,7 @@
         <v>2509</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C304" s="2">
         <v>22</v>
@@ -8329,7 +8329,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E304" s="2">
-        <v>81506</v>
+        <v>81507</v>
       </c>
       <c r="F304" s="3">
         <v>46029</v>
@@ -8346,7 +8346,7 @@
         <v>2509</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C305" s="2">
         <v>22</v>
@@ -8355,10 +8355,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E305" s="2">
-        <v>81507</v>
+        <v>81524</v>
       </c>
       <c r="F305" s="3">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>9</v>
@@ -8372,7 +8372,7 @@
         <v>2509</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C306" s="2">
         <v>22</v>
@@ -8381,7 +8381,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E306" s="2">
-        <v>81524</v>
+        <v>81525</v>
       </c>
       <c r="F306" s="3">
         <v>46030</v>
@@ -8398,7 +8398,7 @@
         <v>2509</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C307" s="2">
         <v>22</v>
@@ -8407,7 +8407,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E307" s="2">
-        <v>81525</v>
+        <v>81526</v>
       </c>
       <c r="F307" s="3">
         <v>46030</v>
@@ -8424,19 +8424,19 @@
         <v>2509</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C308" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D308" s="3">
-        <v>46029.6400966782</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E308" s="2">
-        <v>81526</v>
+        <v>81640</v>
       </c>
       <c r="F308" s="3">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>9</v>
@@ -8450,7 +8450,7 @@
         <v>2509</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C309" s="2">
         <v>23</v>
@@ -8459,7 +8459,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E309" s="2">
-        <v>81640</v>
+        <v>81642</v>
       </c>
       <c r="F309" s="3">
         <v>46036</v>
@@ -8476,7 +8476,7 @@
         <v>2509</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C310" s="2">
         <v>23</v>
@@ -8485,7 +8485,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E310" s="2">
-        <v>81642</v>
+        <v>81643</v>
       </c>
       <c r="F310" s="3">
         <v>46036</v>
@@ -8502,19 +8502,19 @@
         <v>2509</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C311" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D311" s="3">
-        <v>46036.6348522801</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E311" s="2">
-        <v>81643</v>
+        <v>81835</v>
       </c>
       <c r="F311" s="3">
-        <v>46036</v>
+        <v>46045</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>9</v>
@@ -8528,7 +8528,7 @@
         <v>2509</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C312" s="2">
         <v>24</v>
@@ -8537,7 +8537,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E312" s="2">
-        <v>81835</v>
+        <v>81836</v>
       </c>
       <c r="F312" s="3">
         <v>46045</v>
@@ -8554,7 +8554,7 @@
         <v>2509</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C313" s="2">
         <v>24</v>
@@ -8563,7 +8563,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E313" s="2">
-        <v>81836</v>
+        <v>81837</v>
       </c>
       <c r="F313" s="3">
         <v>46045</v>
@@ -8580,19 +8580,19 @@
         <v>2509</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C314" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D314" s="3">
-        <v>46045.4207558912</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E314" s="2">
-        <v>81837</v>
+        <v>81931</v>
       </c>
       <c r="F314" s="3">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>9</v>
@@ -8606,19 +8606,19 @@
         <v>2509</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C315" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D315" s="3">
-        <v>46051.6376515278</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E315" s="2">
-        <v>81931</v>
+        <v>81978</v>
       </c>
       <c r="F315" s="3">
-        <v>46052</v>
+        <v>46057</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>9</v>
@@ -8632,16 +8632,16 @@
         <v>2509</v>
       </c>
       <c r="B316" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C316" s="2">
         <v>27</v>
       </c>
-      <c r="C316" s="2">
-        <v>26</v>
-      </c>
       <c r="D316" s="3">
-        <v>46056.7115158912</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E316" s="2">
-        <v>81978</v>
+        <v>81994</v>
       </c>
       <c r="F316" s="3">
         <v>46057</v>
@@ -8658,7 +8658,7 @@
         <v>2509</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C317" s="2">
         <v>27</v>
@@ -8667,7 +8667,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E317" s="2">
-        <v>81994</v>
+        <v>81995</v>
       </c>
       <c r="F317" s="3">
         <v>46057</v>
@@ -8684,7 +8684,7 @@
         <v>2509</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C318" s="2">
         <v>27</v>
@@ -8693,7 +8693,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E318" s="2">
-        <v>81995</v>
+        <v>81999</v>
       </c>
       <c r="F318" s="3">
         <v>46057</v>
@@ -8710,7 +8710,7 @@
         <v>2509</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C319" s="2">
         <v>27</v>
@@ -8719,10 +8719,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E319" s="2">
-        <v>81999</v>
+        <v>82008</v>
       </c>
       <c r="F319" s="3">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>9</v>
@@ -8736,7 +8736,7 @@
         <v>2509</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C320" s="2">
         <v>27</v>
@@ -8745,7 +8745,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E320" s="2">
-        <v>82008</v>
+        <v>82011</v>
       </c>
       <c r="F320" s="3">
         <v>46058</v>
@@ -8762,7 +8762,7 @@
         <v>2509</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C321" s="2">
         <v>27</v>
@@ -8771,7 +8771,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E321" s="2">
-        <v>82011</v>
+        <v>82012</v>
       </c>
       <c r="F321" s="3">
         <v>46058</v>
@@ -8788,7 +8788,7 @@
         <v>2509</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C322" s="2">
         <v>27</v>
@@ -8797,7 +8797,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E322" s="2">
-        <v>82012</v>
+        <v>82013</v>
       </c>
       <c r="F322" s="3">
         <v>46058</v>
@@ -8814,7 +8814,7 @@
         <v>2509</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C323" s="2">
         <v>27</v>
@@ -8823,7 +8823,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E323" s="2">
-        <v>82013</v>
+        <v>82014</v>
       </c>
       <c r="F323" s="3">
         <v>46058</v>
@@ -8840,25 +8840,25 @@
         <v>2509</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C324" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D324" s="3">
-        <v>46057.6911087731</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E324" s="2">
-        <v>82014</v>
+        <v>82046</v>
       </c>
       <c r="F324" s="3">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H324" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="325">
@@ -8866,25 +8866,25 @@
         <v>2509</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C325" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D325" s="3">
-        <v>46058.6604985417</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E325" s="2">
-        <v>82046</v>
+        <v>82217</v>
       </c>
       <c r="F325" s="3">
-        <v>46059</v>
+        <v>46072</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="326">
@@ -8892,7 +8892,7 @@
         <v>2509</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C326" s="2">
         <v>29</v>
@@ -8901,7 +8901,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E326" s="2">
-        <v>82217</v>
+        <v>82218</v>
       </c>
       <c r="F326" s="3">
         <v>46072</v>
@@ -8918,7 +8918,7 @@
         <v>2509</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C327" s="2">
         <v>29</v>
@@ -8927,10 +8927,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E327" s="2">
-        <v>82218</v>
+        <v>82234</v>
       </c>
       <c r="F327" s="3">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>9</v>
@@ -8944,7 +8944,7 @@
         <v>2509</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C328" s="2">
         <v>29</v>
@@ -8953,7 +8953,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E328" s="2">
-        <v>82234</v>
+        <v>82238</v>
       </c>
       <c r="F328" s="3">
         <v>46073</v>
@@ -8970,7 +8970,7 @@
         <v>2509</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C329" s="2">
         <v>29</v>
@@ -8979,7 +8979,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E329" s="2">
-        <v>82238</v>
+        <v>82245</v>
       </c>
       <c r="F329" s="3">
         <v>46073</v>
@@ -8996,19 +8996,19 @@
         <v>2509</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C330" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D330" s="3">
-        <v>46072.738871875</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E330" s="2">
-        <v>82245</v>
+        <v>82257</v>
       </c>
       <c r="F330" s="3">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>9</v>
@@ -9022,7 +9022,7 @@
         <v>2509</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C331" s="2">
         <v>30</v>
@@ -9031,10 +9031,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E331" s="2">
-        <v>82257</v>
+        <v>82276</v>
       </c>
       <c r="F331" s="3">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>9</v>
@@ -9048,7 +9048,7 @@
         <v>2509</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C332" s="2">
         <v>30</v>
@@ -9057,7 +9057,7 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E332" s="2">
-        <v>82276</v>
+        <v>82277</v>
       </c>
       <c r="F332" s="3">
         <v>46077</v>
@@ -9074,7 +9074,7 @@
         <v>2509</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C333" s="2">
         <v>30</v>
@@ -9083,10 +9083,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E333" s="2">
-        <v>82277</v>
+        <v>82293</v>
       </c>
       <c r="F333" s="3">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>9</v>
@@ -9100,19 +9100,19 @@
         <v>2509</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C334" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D334" s="3">
-        <v>46076.7244851042</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E334" s="2">
-        <v>82293</v>
+        <v>82269</v>
       </c>
       <c r="F334" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>9</v>
@@ -9126,19 +9126,19 @@
         <v>2509</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C335" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D335" s="3">
-        <v>46077.4356327431</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E335" s="2">
-        <v>82269</v>
+        <v>82419</v>
       </c>
       <c r="F335" s="3">
-        <v>46077</v>
+        <v>46084</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>9</v>
@@ -9152,7 +9152,7 @@
         <v>2509</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C336" s="2">
         <v>32</v>
@@ -9161,7 +9161,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E336" s="2">
-        <v>82419</v>
+        <v>82420</v>
       </c>
       <c r="F336" s="3">
         <v>46084</v>
@@ -9178,7 +9178,7 @@
         <v>2509</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C337" s="2">
         <v>32</v>
@@ -9187,7 +9187,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E337" s="2">
-        <v>82420</v>
+        <v>82421</v>
       </c>
       <c r="F337" s="3">
         <v>46084</v>
@@ -9204,7 +9204,7 @@
         <v>2509</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C338" s="2">
         <v>32</v>
@@ -9213,7 +9213,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E338" s="2">
-        <v>82421</v>
+        <v>82422</v>
       </c>
       <c r="F338" s="3">
         <v>46084</v>
@@ -9230,7 +9230,7 @@
         <v>2509</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C339" s="2">
         <v>32</v>
@@ -9239,7 +9239,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E339" s="2">
-        <v>82422</v>
+        <v>82423</v>
       </c>
       <c r="F339" s="3">
         <v>46084</v>
@@ -9256,7 +9256,7 @@
         <v>2509</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C340" s="2">
         <v>32</v>
@@ -9265,10 +9265,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E340" s="2">
-        <v>82423</v>
+        <v>82433</v>
       </c>
       <c r="F340" s="3">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>9</v>
@@ -9282,7 +9282,7 @@
         <v>2509</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C341" s="2">
         <v>32</v>
@@ -9291,7 +9291,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E341" s="2">
-        <v>82433</v>
+        <v>82434</v>
       </c>
       <c r="F341" s="3">
         <v>46085</v>
@@ -9308,7 +9308,7 @@
         <v>2509</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C342" s="2">
         <v>32</v>
@@ -9317,10 +9317,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E342" s="2">
-        <v>82434</v>
+        <v>82464</v>
       </c>
       <c r="F342" s="3">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>9</v>
@@ -9334,7 +9334,7 @@
         <v>2509</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C343" s="2">
         <v>32</v>
@@ -9343,7 +9343,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E343" s="2">
-        <v>82464</v>
+        <v>82472</v>
       </c>
       <c r="F343" s="3">
         <v>46086</v>
@@ -9360,19 +9360,19 @@
         <v>2509</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C344" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D344" s="3">
-        <v>46084.7378501505</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E344" s="2">
-        <v>82472</v>
+        <v>82578</v>
       </c>
       <c r="F344" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>9</v>
@@ -9386,7 +9386,7 @@
         <v>2509</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C345" s="2">
         <v>33</v>
@@ -9395,7 +9395,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E345" s="2">
-        <v>82578</v>
+        <v>82579</v>
       </c>
       <c r="F345" s="3">
         <v>46093</v>
@@ -9412,7 +9412,7 @@
         <v>2509</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C346" s="2">
         <v>33</v>
@@ -9421,7 +9421,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E346" s="2">
-        <v>82579</v>
+        <v>82580</v>
       </c>
       <c r="F346" s="3">
         <v>46093</v>
@@ -9438,7 +9438,7 @@
         <v>2509</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C347" s="2">
         <v>33</v>
@@ -9447,16 +9447,16 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E347" s="2">
-        <v>82580</v>
+        <v>82599</v>
       </c>
       <c r="F347" s="3">
         <v>46093</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="348">
@@ -9464,7 +9464,7 @@
         <v>2509</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C348" s="2">
         <v>33</v>
@@ -9473,16 +9473,16 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E348" s="2">
-        <v>82599</v>
+        <v>82602</v>
       </c>
       <c r="F348" s="3">
         <v>46093</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="349">
@@ -9490,16 +9490,16 @@
         <v>2509</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C349" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D349" s="3">
-        <v>46093.4897546412</v>
+        <v>46093.4957757986</v>
       </c>
       <c r="E349" s="2">
-        <v>82602</v>
+        <v>82584</v>
       </c>
       <c r="F349" s="3">
         <v>46093</v>
@@ -9513,22 +9513,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="350">
       <c r="A350" s="2">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C350" s="2">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D350" s="3">
-        <v>46093.4957757986</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E350" s="2">
-        <v>82584</v>
+        <v>81464</v>
       </c>
       <c r="F350" s="3">
-        <v>46093</v>
+        <v>46027</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>9</v>
@@ -9551,7 +9551,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E351" s="2">
-        <v>81464</v>
+        <v>81472</v>
       </c>
       <c r="F351" s="3">
         <v>46027</v>
@@ -9577,10 +9577,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E352" s="2">
-        <v>81472</v>
+        <v>81492</v>
       </c>
       <c r="F352" s="3">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>9</v>
@@ -9603,7 +9603,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E353" s="2">
-        <v>81492</v>
+        <v>81493</v>
       </c>
       <c r="F353" s="3">
         <v>46029</v>
@@ -9629,10 +9629,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E354" s="2">
-        <v>81493</v>
+        <v>81568</v>
       </c>
       <c r="F354" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>9</v>
@@ -9655,10 +9655,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E355" s="2">
-        <v>81568</v>
+        <v>81601</v>
       </c>
       <c r="F355" s="3">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>9</v>
@@ -9681,7 +9681,7 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E356" s="2">
-        <v>81601</v>
+        <v>81602</v>
       </c>
       <c r="F356" s="3">
         <v>46034</v>
@@ -9701,16 +9701,16 @@
         <v>30</v>
       </c>
       <c r="C357" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D357" s="3">
-        <v>46027.6953206134</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E357" s="2">
-        <v>81602</v>
+        <v>81645</v>
       </c>
       <c r="F357" s="3">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>9</v>
@@ -9733,7 +9733,7 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E358" s="2">
-        <v>81645</v>
+        <v>81646</v>
       </c>
       <c r="F358" s="3">
         <v>46036</v>
@@ -9759,10 +9759,10 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E359" s="2">
-        <v>81646</v>
+        <v>81653</v>
       </c>
       <c r="F359" s="3">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>9</v>
@@ -9779,13 +9779,13 @@
         <v>30</v>
       </c>
       <c r="C360" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D360" s="3">
-        <v>46036.6368094444</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E360" s="2">
-        <v>81653</v>
+        <v>81662</v>
       </c>
       <c r="F360" s="3">
         <v>46037</v>
@@ -9805,16 +9805,16 @@
         <v>30</v>
       </c>
       <c r="C361" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D361" s="3">
-        <v>46037.4325152662</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E361" s="2">
-        <v>81662</v>
+        <v>81780</v>
       </c>
       <c r="F361" s="3">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>9</v>
@@ -9837,7 +9837,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E362" s="2">
-        <v>81780</v>
+        <v>81781</v>
       </c>
       <c r="F362" s="3">
         <v>46044</v>
@@ -9863,7 +9863,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E363" s="2">
-        <v>81781</v>
+        <v>81782</v>
       </c>
       <c r="F363" s="3">
         <v>46044</v>
@@ -9889,7 +9889,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E364" s="2">
-        <v>81782</v>
+        <v>81784</v>
       </c>
       <c r="F364" s="3">
         <v>46044</v>
@@ -9915,7 +9915,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E365" s="2">
-        <v>81784</v>
+        <v>81785</v>
       </c>
       <c r="F365" s="3">
         <v>46044</v>
@@ -9941,7 +9941,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E366" s="2">
-        <v>81785</v>
+        <v>81801</v>
       </c>
       <c r="F366" s="3">
         <v>46044</v>
@@ -9961,16 +9961,16 @@
         <v>30</v>
       </c>
       <c r="C367" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D367" s="3">
-        <v>46044.4079891435</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E367" s="2">
-        <v>81801</v>
+        <v>81860</v>
       </c>
       <c r="F367" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>9</v>
@@ -9993,7 +9993,7 @@
         <v>46048.7319778588</v>
       </c>
       <c r="E368" s="2">
-        <v>81860</v>
+        <v>81873</v>
       </c>
       <c r="F368" s="3">
         <v>46049</v>
@@ -10013,13 +10013,13 @@
         <v>30</v>
       </c>
       <c r="C369" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D369" s="3">
-        <v>46048.7319778588</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E369" s="2">
-        <v>81873</v>
+        <v>81865</v>
       </c>
       <c r="F369" s="3">
         <v>46049</v>
@@ -10045,7 +10045,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E370" s="2">
-        <v>81865</v>
+        <v>81870</v>
       </c>
       <c r="F370" s="3">
         <v>46049</v>
@@ -10071,7 +10071,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E371" s="2">
-        <v>81870</v>
+        <v>81872</v>
       </c>
       <c r="F371" s="3">
         <v>46049</v>
@@ -10097,10 +10097,10 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E372" s="2">
-        <v>81872</v>
+        <v>81896</v>
       </c>
       <c r="F372" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>9</v>
@@ -10117,16 +10117,16 @@
         <v>30</v>
       </c>
       <c r="C373" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D373" s="3">
-        <v>46049.4883916667</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E373" s="2">
-        <v>81896</v>
+        <v>81923</v>
       </c>
       <c r="F373" s="3">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>9</v>
@@ -10143,16 +10143,16 @@
         <v>30</v>
       </c>
       <c r="C374" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D374" s="3">
-        <v>46051.4046937153</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E374" s="2">
-        <v>81923</v>
+        <v>81998</v>
       </c>
       <c r="F374" s="3">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>9</v>
@@ -10175,7 +10175,7 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E375" s="2">
-        <v>81998</v>
+        <v>82002</v>
       </c>
       <c r="F375" s="3">
         <v>46057</v>
@@ -10201,10 +10201,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E376" s="2">
-        <v>82002</v>
+        <v>82005</v>
       </c>
       <c r="F376" s="3">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>9</v>
@@ -10227,7 +10227,7 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E377" s="2">
-        <v>82005</v>
+        <v>82007</v>
       </c>
       <c r="F377" s="3">
         <v>46058</v>
@@ -10247,13 +10247,13 @@
         <v>30</v>
       </c>
       <c r="C378" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D378" s="3">
-        <v>46057.6959672917</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E378" s="2">
-        <v>82007</v>
+        <v>82005</v>
       </c>
       <c r="F378" s="3">
         <v>46058</v>
@@ -10279,10 +10279,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E379" s="2">
-        <v>82005</v>
+        <v>82075</v>
       </c>
       <c r="F379" s="3">
-        <v>46058</v>
+        <v>46063</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>9</v>
@@ -10305,7 +10305,7 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E380" s="2">
-        <v>82075</v>
+        <v>82077</v>
       </c>
       <c r="F380" s="3">
         <v>46063</v>
@@ -10331,10 +10331,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E381" s="2">
-        <v>82077</v>
+        <v>82099</v>
       </c>
       <c r="F381" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>9</v>
@@ -10351,16 +10351,16 @@
         <v>30</v>
       </c>
       <c r="C382" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D382" s="3">
-        <v>46063.5942651852</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E382" s="2">
-        <v>82099</v>
+        <v>82219</v>
       </c>
       <c r="F382" s="3">
-        <v>46064</v>
+        <v>46072</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>9</v>
@@ -10383,10 +10383,10 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E383" s="2">
-        <v>82219</v>
+        <v>82230</v>
       </c>
       <c r="F383" s="3">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>9</v>
@@ -10409,7 +10409,7 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E384" s="2">
-        <v>82230</v>
+        <v>82231</v>
       </c>
       <c r="F384" s="3">
         <v>46073</v>
@@ -10429,16 +10429,16 @@
         <v>30</v>
       </c>
       <c r="C385" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D385" s="3">
-        <v>46072.7460071991</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E385" s="2">
-        <v>82231</v>
+        <v>82388</v>
       </c>
       <c r="F385" s="3">
-        <v>46073</v>
+        <v>46083</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>9</v>
@@ -10461,7 +10461,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E386" s="2">
-        <v>82388</v>
+        <v>82389</v>
       </c>
       <c r="F386" s="3">
         <v>46083</v>
@@ -10487,7 +10487,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E387" s="2">
-        <v>82389</v>
+        <v>82396</v>
       </c>
       <c r="F387" s="3">
         <v>46083</v>
@@ -10513,7 +10513,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E388" s="2">
-        <v>82396</v>
+        <v>82397</v>
       </c>
       <c r="F388" s="3">
         <v>46083</v>
@@ -10533,16 +10533,16 @@
         <v>30</v>
       </c>
       <c r="C389" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D389" s="3">
-        <v>46079.5787315972</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E389" s="2">
-        <v>82397</v>
+        <v>82435</v>
       </c>
       <c r="F389" s="3">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>9</v>
@@ -10559,16 +10559,16 @@
         <v>30</v>
       </c>
       <c r="C390" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D390" s="3">
-        <v>46085.6249659838</v>
+        <v>46091.449444456</v>
       </c>
       <c r="E390" s="2">
-        <v>82435</v>
+        <v>82506</v>
       </c>
       <c r="F390" s="3">
-        <v>46085</v>
+        <v>46091</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>9</v>
@@ -10585,13 +10585,13 @@
         <v>30</v>
       </c>
       <c r="C391" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D391" s="3">
-        <v>46091.449444456</v>
+        <v>46091.4795702315</v>
       </c>
       <c r="E391" s="2">
-        <v>82506</v>
+        <v>82509</v>
       </c>
       <c r="F391" s="3">
         <v>46091</v>
@@ -10611,16 +10611,16 @@
         <v>30</v>
       </c>
       <c r="C392" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D392" s="3">
-        <v>46091.4795702315</v>
+        <v>46093.4969972338</v>
       </c>
       <c r="E392" s="2">
-        <v>82509</v>
+        <v>82589</v>
       </c>
       <c r="F392" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>9</v>
@@ -10631,22 +10631,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="393">
       <c r="A393" s="2">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C393" s="2">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D393" s="3">
-        <v>46093.4969972338</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E393" s="2">
-        <v>82589</v>
+        <v>81477</v>
       </c>
       <c r="F393" s="3">
-        <v>46093</v>
+        <v>46029</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>9</v>
@@ -10663,16 +10663,16 @@
         <v>31</v>
       </c>
       <c r="C394" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D394" s="3">
-        <v>46029.3821391551</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E394" s="2">
-        <v>81477</v>
+        <v>81532</v>
       </c>
       <c r="F394" s="3">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>9</v>
@@ -10695,7 +10695,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E395" s="2">
-        <v>81532</v>
+        <v>81534</v>
       </c>
       <c r="F395" s="3">
         <v>46030</v>
@@ -10721,7 +10721,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E396" s="2">
-        <v>81534</v>
+        <v>81535</v>
       </c>
       <c r="F396" s="3">
         <v>46030</v>
@@ -10747,7 +10747,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E397" s="2">
-        <v>81535</v>
+        <v>81550</v>
       </c>
       <c r="F397" s="3">
         <v>46030</v>
@@ -10773,7 +10773,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E398" s="2">
-        <v>81550</v>
+        <v>81553</v>
       </c>
       <c r="F398" s="3">
         <v>46030</v>
@@ -10799,7 +10799,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E399" s="2">
-        <v>81553</v>
+        <v>81554</v>
       </c>
       <c r="F399" s="3">
         <v>46030</v>
@@ -10825,7 +10825,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E400" s="2">
-        <v>81554</v>
+        <v>81557</v>
       </c>
       <c r="F400" s="3">
         <v>46030</v>
@@ -10851,10 +10851,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E401" s="2">
-        <v>81557</v>
+        <v>81588</v>
       </c>
       <c r="F401" s="3">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10871,16 +10871,16 @@
         <v>31</v>
       </c>
       <c r="C402" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D402" s="3">
-        <v>46030.4142968056</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E402" s="2">
-        <v>81588</v>
+        <v>81692</v>
       </c>
       <c r="F402" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10897,16 +10897,16 @@
         <v>31</v>
       </c>
       <c r="C403" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D403" s="3">
-        <v>46038.593985081</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E403" s="2">
-        <v>81692</v>
+        <v>81786</v>
       </c>
       <c r="F403" s="3">
-        <v>46038</v>
+        <v>46044</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10923,16 +10923,16 @@
         <v>31</v>
       </c>
       <c r="C404" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D404" s="3">
-        <v>46044.46462125</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E404" s="2">
-        <v>81786</v>
+        <v>81844</v>
       </c>
       <c r="F404" s="3">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>9</v>
@@ -10949,16 +10949,16 @@
         <v>31</v>
       </c>
       <c r="C405" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D405" s="3">
-        <v>46044.6362443171</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E405" s="2">
-        <v>81844</v>
+        <v>82065</v>
       </c>
       <c r="F405" s="3">
-        <v>46045</v>
+        <v>46062</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>9</v>
@@ -10981,7 +10981,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E406" s="2">
-        <v>82065</v>
+        <v>82066</v>
       </c>
       <c r="F406" s="3">
         <v>46062</v>
@@ -11007,7 +11007,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E407" s="2">
-        <v>82066</v>
+        <v>82067</v>
       </c>
       <c r="F407" s="3">
         <v>46062</v>
@@ -11027,16 +11027,16 @@
         <v>31</v>
       </c>
       <c r="C408" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D408" s="3">
-        <v>46062.717040544</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E408" s="2">
-        <v>82067</v>
+        <v>82190</v>
       </c>
       <c r="F408" s="3">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>9</v>
@@ -11059,7 +11059,7 @@
         <v>46065.6300915625</v>
       </c>
       <c r="E409" s="2">
-        <v>82190</v>
+        <v>82197</v>
       </c>
       <c r="F409" s="3">
         <v>46066</v>
@@ -11079,16 +11079,16 @@
         <v>31</v>
       </c>
       <c r="C410" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D410" s="3">
-        <v>46065.6300915625</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E410" s="2">
-        <v>82197</v>
+        <v>82270</v>
       </c>
       <c r="F410" s="3">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11105,13 +11105,13 @@
         <v>31</v>
       </c>
       <c r="C411" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D411" s="3">
-        <v>46077.5084780324</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E411" s="2">
-        <v>82270</v>
+        <v>82285</v>
       </c>
       <c r="F411" s="3">
         <v>46077</v>
@@ -11131,16 +11131,16 @@
         <v>31</v>
       </c>
       <c r="C412" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D412" s="3">
-        <v>46077.721037037</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E412" s="2">
-        <v>82285</v>
+        <v>82417</v>
       </c>
       <c r="F412" s="3">
-        <v>46077</v>
+        <v>46084</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11157,16 +11157,16 @@
         <v>31</v>
       </c>
       <c r="C413" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D413" s="3">
-        <v>46083.6694849421</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E413" s="2">
-        <v>82417</v>
+        <v>82457</v>
       </c>
       <c r="F413" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>9</v>
@@ -11177,22 +11177,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="414">
       <c r="A414" s="2">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C414" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D414" s="3">
-        <v>46085.7157723032</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E414" s="2">
-        <v>82457</v>
+        <v>81484</v>
       </c>
       <c r="F414" s="3">
-        <v>46086</v>
+        <v>46029</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>9</v>
@@ -11215,7 +11215,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E415" s="2">
-        <v>81484</v>
+        <v>81486</v>
       </c>
       <c r="F415" s="3">
         <v>46029</v>
@@ -11241,7 +11241,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E416" s="2">
-        <v>81486</v>
+        <v>81487</v>
       </c>
       <c r="F416" s="3">
         <v>46029</v>
@@ -11261,16 +11261,16 @@
         <v>32</v>
       </c>
       <c r="C417" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D417" s="3">
-        <v>46029.381258831</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E417" s="2">
-        <v>81487</v>
+        <v>81613</v>
       </c>
       <c r="F417" s="3">
-        <v>46029</v>
+        <v>46036</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>9</v>
@@ -11293,7 +11293,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E418" s="2">
-        <v>81613</v>
+        <v>81614</v>
       </c>
       <c r="F418" s="3">
         <v>46036</v>
@@ -11319,7 +11319,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E419" s="2">
-        <v>81614</v>
+        <v>81622</v>
       </c>
       <c r="F419" s="3">
         <v>46036</v>
@@ -11345,7 +11345,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E420" s="2">
-        <v>81622</v>
+        <v>81632</v>
       </c>
       <c r="F420" s="3">
         <v>46036</v>
@@ -11371,10 +11371,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E421" s="2">
-        <v>81632</v>
+        <v>81648</v>
       </c>
       <c r="F421" s="3">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>9</v>
@@ -11397,7 +11397,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E422" s="2">
-        <v>81648</v>
+        <v>81664</v>
       </c>
       <c r="F422" s="3">
         <v>46037</v>
@@ -11417,16 +11417,16 @@
         <v>32</v>
       </c>
       <c r="C423" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D423" s="3">
-        <v>46036.4048894097</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E423" s="2">
-        <v>81664</v>
+        <v>81815</v>
       </c>
       <c r="F423" s="3">
-        <v>46037</v>
+        <v>46045</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>9</v>
@@ -11449,7 +11449,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E424" s="2">
-        <v>81815</v>
+        <v>81816</v>
       </c>
       <c r="F424" s="3">
         <v>46045</v>
@@ -11475,7 +11475,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E425" s="2">
-        <v>81816</v>
+        <v>81838</v>
       </c>
       <c r="F425" s="3">
         <v>46045</v>
@@ -11501,7 +11501,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E426" s="2">
-        <v>81838</v>
+        <v>81840</v>
       </c>
       <c r="F426" s="3">
         <v>46045</v>
@@ -11521,16 +11521,16 @@
         <v>32</v>
       </c>
       <c r="C427" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D427" s="3">
-        <v>46045.4188638426</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E427" s="2">
-        <v>81840</v>
+        <v>81959</v>
       </c>
       <c r="F427" s="3">
-        <v>46045</v>
+        <v>46055</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11553,7 +11553,7 @@
         <v>46055.5991080671</v>
       </c>
       <c r="E428" s="2">
-        <v>81959</v>
+        <v>81960</v>
       </c>
       <c r="F428" s="3">
         <v>46055</v>
@@ -11573,16 +11573,16 @@
         <v>32</v>
       </c>
       <c r="C429" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D429" s="3">
-        <v>46055.5991080671</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E429" s="2">
-        <v>81960</v>
+        <v>82063</v>
       </c>
       <c r="F429" s="3">
-        <v>46055</v>
+        <v>46062</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>9</v>
@@ -11605,7 +11605,7 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E430" s="2">
-        <v>82063</v>
+        <v>82064</v>
       </c>
       <c r="F430" s="3">
         <v>46062</v>
@@ -11631,10 +11631,10 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E431" s="2">
-        <v>82064</v>
+        <v>82100</v>
       </c>
       <c r="F431" s="3">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>9</v>
@@ -11651,16 +11651,16 @@
         <v>32</v>
       </c>
       <c r="C432" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D432" s="3">
-        <v>46062.7151302546</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E432" s="2">
-        <v>82100</v>
+        <v>82333</v>
       </c>
       <c r="F432" s="3">
-        <v>46064</v>
+        <v>46079</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11683,7 +11683,7 @@
         <v>46072.7410579977</v>
       </c>
       <c r="E433" s="2">
-        <v>82333</v>
+        <v>82334</v>
       </c>
       <c r="F433" s="3">
         <v>46079</v>
@@ -11703,16 +11703,16 @@
         <v>32</v>
       </c>
       <c r="C434" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D434" s="3">
-        <v>46072.7410579977</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E434" s="2">
-        <v>82334</v>
+        <v>82258</v>
       </c>
       <c r="F434" s="3">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>9</v>
@@ -11735,7 +11735,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E435" s="2">
-        <v>82258</v>
+        <v>82259</v>
       </c>
       <c r="F435" s="3">
         <v>46076</v>
@@ -11761,7 +11761,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E436" s="2">
-        <v>82259</v>
+        <v>82260</v>
       </c>
       <c r="F436" s="3">
         <v>46076</v>
@@ -11787,10 +11787,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E437" s="2">
-        <v>82260</v>
+        <v>82274</v>
       </c>
       <c r="F437" s="3">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>9</v>
@@ -11807,16 +11807,16 @@
         <v>32</v>
       </c>
       <c r="C438" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D438" s="3">
-        <v>46076.7259125116</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E438" s="2">
-        <v>82274</v>
+        <v>82409</v>
       </c>
       <c r="F438" s="3">
-        <v>46077</v>
+        <v>46084</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11833,16 +11833,16 @@
         <v>32</v>
       </c>
       <c r="C439" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D439" s="3">
-        <v>46084.5055666204</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E439" s="2">
-        <v>82409</v>
+        <v>82581</v>
       </c>
       <c r="F439" s="3">
-        <v>46084</v>
+        <v>46093</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11865,7 +11865,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E440" s="2">
-        <v>82581</v>
+        <v>82582</v>
       </c>
       <c r="F440" s="3">
         <v>46093</v>
@@ -11891,7 +11891,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E441" s="2">
-        <v>82582</v>
+        <v>82583</v>
       </c>
       <c r="F441" s="3">
         <v>46093</v>
@@ -11917,10 +11917,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E442" s="2">
-        <v>82583</v>
+        <v>82672</v>
       </c>
       <c r="F442" s="3">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11943,7 +11943,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E443" s="2">
-        <v>82672</v>
+        <v>82674</v>
       </c>
       <c r="F443" s="3">
         <v>46097</v>
@@ -11957,22 +11957,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="444">
       <c r="A444" s="2">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C444" s="2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D444" s="3">
-        <v>46093.4920058565</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E444" s="2">
-        <v>82674</v>
+        <v>81608</v>
       </c>
       <c r="F444" s="3">
-        <v>46097</v>
+        <v>46035</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11995,7 +11995,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E445" s="2">
-        <v>81608</v>
+        <v>81609</v>
       </c>
       <c r="F445" s="3">
         <v>46035</v>
@@ -12021,7 +12021,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E446" s="2">
-        <v>81609</v>
+        <v>81610</v>
       </c>
       <c r="F446" s="3">
         <v>46035</v>
@@ -12047,7 +12047,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E447" s="2">
-        <v>81610</v>
+        <v>81611</v>
       </c>
       <c r="F447" s="3">
         <v>46035</v>
@@ -12073,7 +12073,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E448" s="2">
-        <v>81611</v>
+        <v>81612</v>
       </c>
       <c r="F448" s="3">
         <v>46035</v>
@@ -12093,16 +12093,16 @@
         <v>33</v>
       </c>
       <c r="C449" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D449" s="3">
-        <v>46035.4386099769</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E449" s="2">
-        <v>81612</v>
+        <v>81652</v>
       </c>
       <c r="F449" s="3">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12125,7 +12125,7 @@
         <v>46036.6342081481</v>
       </c>
       <c r="E450" s="2">
-        <v>81652</v>
+        <v>81659</v>
       </c>
       <c r="F450" s="3">
         <v>46037</v>
@@ -12145,16 +12145,16 @@
         <v>33</v>
       </c>
       <c r="C451" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D451" s="3">
-        <v>46036.6342081481</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E451" s="2">
-        <v>81659</v>
+        <v>81853</v>
       </c>
       <c r="F451" s="3">
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>9</v>
@@ -12177,10 +12177,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E452" s="2">
-        <v>81853</v>
+        <v>81869</v>
       </c>
       <c r="F452" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12203,10 +12203,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E453" s="2">
-        <v>81869</v>
+        <v>81890</v>
       </c>
       <c r="F453" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>9</v>
@@ -12223,16 +12223,16 @@
         <v>33</v>
       </c>
       <c r="C454" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D454" s="3">
-        <v>46048.6509980093</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E454" s="2">
-        <v>81890</v>
+        <v>81875</v>
       </c>
       <c r="F454" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>9</v>
@@ -12255,10 +12255,10 @@
         <v>46049.4871256134</v>
       </c>
       <c r="E455" s="2">
-        <v>81875</v>
+        <v>81881</v>
       </c>
       <c r="F455" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>9</v>
@@ -12275,16 +12275,16 @@
         <v>33</v>
       </c>
       <c r="C456" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D456" s="3">
-        <v>46049.4871256134</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E456" s="2">
-        <v>81881</v>
+        <v>82015</v>
       </c>
       <c r="F456" s="3">
-        <v>46050</v>
+        <v>46058</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12307,7 +12307,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E457" s="2">
-        <v>82015</v>
+        <v>82017</v>
       </c>
       <c r="F457" s="3">
         <v>46058</v>
@@ -12333,7 +12333,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E458" s="2">
-        <v>82017</v>
+        <v>82020</v>
       </c>
       <c r="F458" s="3">
         <v>46058</v>
@@ -12359,7 +12359,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E459" s="2">
-        <v>82020</v>
+        <v>82023</v>
       </c>
       <c r="F459" s="3">
         <v>46058</v>
@@ -12385,10 +12385,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E460" s="2">
-        <v>82023</v>
+        <v>82061</v>
       </c>
       <c r="F460" s="3">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12411,10 +12411,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E461" s="2">
-        <v>82061</v>
+        <v>82081</v>
       </c>
       <c r="F461" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12437,10 +12437,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E462" s="2">
-        <v>82081</v>
+        <v>82095</v>
       </c>
       <c r="F462" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12457,16 +12457,16 @@
         <v>33</v>
       </c>
       <c r="C463" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D463" s="3">
-        <v>46056.7073643981</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E463" s="2">
-        <v>82095</v>
+        <v>82081</v>
       </c>
       <c r="F463" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12489,10 +12489,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E464" s="2">
-        <v>82081</v>
+        <v>82107</v>
       </c>
       <c r="F464" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12515,7 +12515,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E465" s="2">
-        <v>82107</v>
+        <v>82112</v>
       </c>
       <c r="F465" s="3">
         <v>46064</v>
@@ -12541,7 +12541,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E466" s="2">
-        <v>82112</v>
+        <v>82113</v>
       </c>
       <c r="F466" s="3">
         <v>46064</v>
@@ -12567,10 +12567,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E467" s="2">
-        <v>82113</v>
+        <v>82123</v>
       </c>
       <c r="F467" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>9</v>
@@ -12587,16 +12587,16 @@
         <v>33</v>
       </c>
       <c r="C468" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D468" s="3">
-        <v>46062.7129743866</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E468" s="2">
-        <v>82123</v>
+        <v>82095</v>
       </c>
       <c r="F468" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>9</v>
@@ -12619,7 +12619,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E469" s="2">
-        <v>82095</v>
+        <v>82106</v>
       </c>
       <c r="F469" s="3">
         <v>46064</v>
@@ -12645,7 +12645,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E470" s="2">
-        <v>82106</v>
+        <v>82107</v>
       </c>
       <c r="F470" s="3">
         <v>46064</v>
@@ -12671,7 +12671,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E471" s="2">
-        <v>82107</v>
+        <v>82109</v>
       </c>
       <c r="F471" s="3">
         <v>46064</v>
@@ -12697,7 +12697,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E472" s="2">
-        <v>82109</v>
+        <v>82110</v>
       </c>
       <c r="F472" s="3">
         <v>46064</v>
@@ -12723,10 +12723,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E473" s="2">
-        <v>82110</v>
+        <v>82139</v>
       </c>
       <c r="F473" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12743,16 +12743,16 @@
         <v>33</v>
       </c>
       <c r="C474" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D474" s="3">
-        <v>46063.5787047801</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E474" s="2">
-        <v>82139</v>
+        <v>82365</v>
       </c>
       <c r="F474" s="3">
-        <v>46065</v>
+        <v>46080</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12775,7 +12775,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E475" s="2">
-        <v>82365</v>
+        <v>82366</v>
       </c>
       <c r="F475" s="3">
         <v>46080</v>
@@ -12801,7 +12801,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E476" s="2">
-        <v>82366</v>
+        <v>82371</v>
       </c>
       <c r="F476" s="3">
         <v>46080</v>
@@ -12827,10 +12827,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E477" s="2">
-        <v>82371</v>
+        <v>82383</v>
       </c>
       <c r="F477" s="3">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>9</v>
@@ -12853,7 +12853,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E478" s="2">
-        <v>82383</v>
+        <v>82384</v>
       </c>
       <c r="F478" s="3">
         <v>46083</v>
@@ -12873,16 +12873,16 @@
         <v>33</v>
       </c>
       <c r="C479" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D479" s="3">
-        <v>46080.4604712616</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E479" s="2">
-        <v>82384</v>
+        <v>82693</v>
       </c>
       <c r="F479" s="3">
-        <v>46083</v>
+        <v>46098</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12893,28 +12893,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="480">
       <c r="A480" s="2">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C480" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D480" s="3">
-        <v>46098.4979333449</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E480" s="2">
-        <v>82693</v>
+        <v>81592</v>
       </c>
       <c r="F480" s="3">
-        <v>46098</v>
+        <v>46031</v>
       </c>
       <c r="G480" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H480" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="481">
@@ -12931,16 +12931,16 @@
         <v>46029.4149454282</v>
       </c>
       <c r="E481" s="2">
-        <v>81592</v>
+        <v>81593</v>
       </c>
       <c r="F481" s="3">
         <v>46031</v>
       </c>
       <c r="G481" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H481" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="482">
@@ -12951,16 +12951,16 @@
         <v>34</v>
       </c>
       <c r="C482" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D482" s="3">
-        <v>46029.4149454282</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E482" s="2">
-        <v>81593</v>
+        <v>81697</v>
       </c>
       <c r="F482" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12983,16 +12983,16 @@
         <v>46038.6827563889</v>
       </c>
       <c r="E483" s="2">
-        <v>81697</v>
+        <v>81735</v>
       </c>
       <c r="F483" s="3">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="G483" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H483" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="484">
@@ -13003,42 +13003,42 @@
         <v>34</v>
       </c>
       <c r="C484" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D484" s="3">
-        <v>46038.6827563889</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E484" s="2">
-        <v>81735</v>
+        <v>81823</v>
       </c>
       <c r="F484" s="3">
-        <v>46041</v>
+        <v>46045</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H484" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="485">
       <c r="A485" s="2">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C485" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D485" s="3">
-        <v>46045.4532476157</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E485" s="2">
-        <v>81823</v>
+        <v>81572</v>
       </c>
       <c r="F485" s="3">
-        <v>46045</v>
+        <v>46031</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>9</v>
@@ -13061,7 +13061,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E486" s="2">
-        <v>81572</v>
+        <v>81573</v>
       </c>
       <c r="F486" s="3">
         <v>46031</v>
@@ -13087,7 +13087,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E487" s="2">
-        <v>81573</v>
+        <v>81579</v>
       </c>
       <c r="F487" s="3">
         <v>46031</v>
@@ -13113,7 +13113,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E488" s="2">
-        <v>81579</v>
+        <v>81580</v>
       </c>
       <c r="F488" s="3">
         <v>46031</v>
@@ -13139,7 +13139,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E489" s="2">
-        <v>81580</v>
+        <v>81581</v>
       </c>
       <c r="F489" s="3">
         <v>46031</v>
@@ -13165,7 +13165,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E490" s="2">
-        <v>81581</v>
+        <v>81582</v>
       </c>
       <c r="F490" s="3">
         <v>46031</v>
@@ -13191,7 +13191,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E491" s="2">
-        <v>81582</v>
+        <v>81583</v>
       </c>
       <c r="F491" s="3">
         <v>46031</v>
@@ -13211,16 +13211,16 @@
         <v>35</v>
       </c>
       <c r="C492" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D492" s="3">
-        <v>46031.4724550926</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E492" s="2">
-        <v>81583</v>
+        <v>81667</v>
       </c>
       <c r="F492" s="3">
-        <v>46031</v>
+        <v>46037</v>
       </c>
       <c r="G492" s="1" t="s">
         <v>9</v>
@@ -13243,7 +13243,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E493" s="2">
-        <v>81667</v>
+        <v>81668</v>
       </c>
       <c r="F493" s="3">
         <v>46037</v>
@@ -13269,10 +13269,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E494" s="2">
-        <v>81668</v>
+        <v>81674</v>
       </c>
       <c r="F494" s="3">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>9</v>
@@ -13295,7 +13295,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E495" s="2">
-        <v>81674</v>
+        <v>81675</v>
       </c>
       <c r="F495" s="3">
         <v>46038</v>
@@ -13321,7 +13321,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E496" s="2">
-        <v>81675</v>
+        <v>81677</v>
       </c>
       <c r="F496" s="3">
         <v>46038</v>
@@ -13341,16 +13341,16 @@
         <v>35</v>
       </c>
       <c r="C497" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D497" s="3">
-        <v>46037.6443999306</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E497" s="2">
-        <v>81677</v>
+        <v>81739</v>
       </c>
       <c r="F497" s="3">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="G497" s="1" t="s">
         <v>9</v>
@@ -13373,7 +13373,7 @@
         <v>46041.6133887269</v>
       </c>
       <c r="E498" s="2">
-        <v>81739</v>
+        <v>81741</v>
       </c>
       <c r="F498" s="3">
         <v>46041</v>
@@ -13393,16 +13393,16 @@
         <v>35</v>
       </c>
       <c r="C499" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D499" s="3">
-        <v>46041.6133887269</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E499" s="2">
-        <v>81741</v>
+        <v>81854</v>
       </c>
       <c r="F499" s="3">
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>9</v>
@@ -13425,7 +13425,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E500" s="2">
-        <v>81854</v>
+        <v>81855</v>
       </c>
       <c r="F500" s="3">
         <v>46048</v>
@@ -13451,10 +13451,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E501" s="2">
-        <v>81855</v>
+        <v>81858</v>
       </c>
       <c r="F501" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="G501" s="1" t="s">
         <v>9</v>
@@ -13477,7 +13477,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E502" s="2">
-        <v>81858</v>
+        <v>81859</v>
       </c>
       <c r="F502" s="3">
         <v>46049</v>
@@ -13503,7 +13503,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E503" s="2">
-        <v>81859</v>
+        <v>81862</v>
       </c>
       <c r="F503" s="3">
         <v>46049</v>
@@ -13529,7 +13529,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E504" s="2">
-        <v>81862</v>
+        <v>81863</v>
       </c>
       <c r="F504" s="3">
         <v>46049</v>
@@ -13549,16 +13549,16 @@
         <v>35</v>
       </c>
       <c r="C505" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D505" s="3">
-        <v>46048.7298086806</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E505" s="2">
-        <v>81863</v>
+        <v>81958</v>
       </c>
       <c r="F505" s="3">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="G505" s="1" t="s">
         <v>9</v>
@@ -13581,7 +13581,7 @@
         <v>46055.5924236111</v>
       </c>
       <c r="E506" s="2">
-        <v>81958</v>
+        <v>81965</v>
       </c>
       <c r="F506" s="3">
         <v>46055</v>
@@ -13601,16 +13601,16 @@
         <v>35</v>
       </c>
       <c r="C507" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D507" s="3">
-        <v>46055.5924236111</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E507" s="2">
-        <v>81965</v>
+        <v>82085</v>
       </c>
       <c r="F507" s="3">
-        <v>46055</v>
+        <v>46063</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>9</v>
@@ -13633,7 +13633,7 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E508" s="2">
-        <v>82085</v>
+        <v>82086</v>
       </c>
       <c r="F508" s="3">
         <v>46063</v>
@@ -13659,10 +13659,10 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E509" s="2">
-        <v>82086</v>
+        <v>82126</v>
       </c>
       <c r="F509" s="3">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="G509" s="1" t="s">
         <v>9</v>
@@ -13679,16 +13679,16 @@
         <v>35</v>
       </c>
       <c r="C510" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D510" s="3">
-        <v>46063.5923590625</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E510" s="2">
-        <v>82126</v>
+        <v>82268</v>
       </c>
       <c r="F510" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G510" s="1" t="s">
         <v>9</v>
@@ -13705,16 +13705,16 @@
         <v>35</v>
       </c>
       <c r="C511" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D511" s="3">
-        <v>46064.5127051505</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E511" s="2">
-        <v>82268</v>
+        <v>82142</v>
       </c>
       <c r="F511" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>9</v>
@@ -13737,7 +13737,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E512" s="2">
-        <v>82142</v>
+        <v>82143</v>
       </c>
       <c r="F512" s="3">
         <v>46065</v>
@@ -13763,7 +13763,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E513" s="2">
-        <v>82143</v>
+        <v>82144</v>
       </c>
       <c r="F513" s="3">
         <v>46065</v>
@@ -13789,10 +13789,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E514" s="2">
-        <v>82144</v>
+        <v>82166</v>
       </c>
       <c r="F514" s="3">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="G514" s="1" t="s">
         <v>9</v>
@@ -13809,16 +13809,16 @@
         <v>35</v>
       </c>
       <c r="C515" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D515" s="3">
-        <v>46065.6275788773</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E515" s="2">
-        <v>82166</v>
+        <v>82262</v>
       </c>
       <c r="F515" s="3">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="G515" s="1" t="s">
         <v>9</v>
@@ -13841,7 +13841,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E516" s="2">
-        <v>82262</v>
+        <v>82265</v>
       </c>
       <c r="F516" s="3">
         <v>46077</v>
@@ -13867,7 +13867,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E517" s="2">
-        <v>82265</v>
+        <v>82281</v>
       </c>
       <c r="F517" s="3">
         <v>46077</v>
@@ -13893,7 +13893,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E518" s="2">
-        <v>82281</v>
+        <v>82282</v>
       </c>
       <c r="F518" s="3">
         <v>46077</v>
@@ -13913,16 +13913,16 @@
         <v>35</v>
       </c>
       <c r="C519" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D519" s="3">
-        <v>46077.406463831</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E519" s="2">
-        <v>82282</v>
+        <v>82340</v>
       </c>
       <c r="F519" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G519" s="1" t="s">
         <v>9</v>
@@ -13939,16 +13939,16 @@
         <v>35</v>
       </c>
       <c r="C520" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D520" s="3">
-        <v>46079.5782408912</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E520" s="2">
-        <v>82340</v>
+        <v>82399</v>
       </c>
       <c r="F520" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="G520" s="1" t="s">
         <v>9</v>
@@ -13971,7 +13971,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E521" s="2">
-        <v>82399</v>
+        <v>82400</v>
       </c>
       <c r="F521" s="3">
         <v>46083</v>
@@ -13997,7 +13997,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E522" s="2">
-        <v>82400</v>
+        <v>82401</v>
       </c>
       <c r="F522" s="3">
         <v>46083</v>
@@ -14023,10 +14023,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E523" s="2">
-        <v>82401</v>
+        <v>82412</v>
       </c>
       <c r="F523" s="3">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>9</v>
@@ -14049,7 +14049,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E524" s="2">
-        <v>82412</v>
+        <v>82415</v>
       </c>
       <c r="F524" s="3">
         <v>46084</v>
@@ -14069,16 +14069,16 @@
         <v>35</v>
       </c>
       <c r="C525" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D525" s="3">
-        <v>46083.6671321991</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E525" s="2">
-        <v>82415</v>
+        <v>82571</v>
       </c>
       <c r="F525" s="3">
-        <v>46084</v>
+        <v>46093</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>9</v>
@@ -14101,7 +14101,7 @@
         <v>46086.6312882639</v>
       </c>
       <c r="E526" s="2">
-        <v>82571</v>
+        <v>82572</v>
       </c>
       <c r="F526" s="3">
         <v>46093</v>
@@ -14121,16 +14121,16 @@
         <v>35</v>
       </c>
       <c r="C527" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D527" s="3">
-        <v>46086.6312882639</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E527" s="2">
-        <v>82572</v>
+        <v>82630</v>
       </c>
       <c r="F527" s="3">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="G527" s="1" t="s">
         <v>9</v>
@@ -14153,7 +14153,7 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E528" s="2">
-        <v>82630</v>
+        <v>82631</v>
       </c>
       <c r="F528" s="3">
         <v>46094</v>
@@ -14179,7 +14179,7 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E529" s="2">
-        <v>82631</v>
+        <v>82632</v>
       </c>
       <c r="F529" s="3">
         <v>46094</v>
@@ -14199,16 +14199,16 @@
         <v>35</v>
       </c>
       <c r="C530" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D530" s="3">
-        <v>46094.4745190394</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E530" s="2">
-        <v>82632</v>
+        <v>82653</v>
       </c>
       <c r="F530" s="3">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>9</v>
@@ -14231,7 +14231,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E531" s="2">
-        <v>82653</v>
+        <v>82665</v>
       </c>
       <c r="F531" s="3">
         <v>46097</v>
@@ -14257,7 +14257,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E532" s="2">
-        <v>82665</v>
+        <v>82668</v>
       </c>
       <c r="F532" s="3">
         <v>46097</v>
@@ -14277,48 +14277,48 @@
         <v>35</v>
       </c>
       <c r="C533" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D533" s="3">
-        <v>46097.4499278356</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E533" s="2">
-        <v>82668</v>
+        <v>82696</v>
       </c>
       <c r="F533" s="3">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H533" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="534">
       <c r="A534" s="2">
-        <v>2516</v>
+        <v>2601</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C534" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D534" s="3">
-        <v>46098.6661386574</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E534" s="2">
-        <v>82696</v>
+        <v>82311</v>
       </c>
       <c r="F534" s="3">
-        <v>46098</v>
+        <v>46078</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H534" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="535">
@@ -14335,7 +14335,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E535" s="2">
-        <v>82311</v>
+        <v>82312</v>
       </c>
       <c r="F535" s="3">
         <v>46078</v>
@@ -14361,7 +14361,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E536" s="2">
-        <v>82312</v>
+        <v>82313</v>
       </c>
       <c r="F536" s="3">
         <v>46078</v>
@@ -14387,7 +14387,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E537" s="2">
-        <v>82313</v>
+        <v>82314</v>
       </c>
       <c r="F537" s="3">
         <v>46078</v>
@@ -14413,10 +14413,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E538" s="2">
-        <v>82314</v>
+        <v>82346</v>
       </c>
       <c r="F538" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="G538" s="1" t="s">
         <v>9</v>
@@ -14439,7 +14439,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E539" s="2">
-        <v>82346</v>
+        <v>82361</v>
       </c>
       <c r="F539" s="3">
         <v>46080</v>
@@ -14465,10 +14465,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E540" s="2">
-        <v>82361</v>
+        <v>82385</v>
       </c>
       <c r="F540" s="3">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="G540" s="1" t="s">
         <v>9</v>
@@ -14491,7 +14491,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E541" s="2">
-        <v>82385</v>
+        <v>82391</v>
       </c>
       <c r="F541" s="3">
         <v>46083</v>
@@ -14517,7 +14517,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E542" s="2">
-        <v>82391</v>
+        <v>82392</v>
       </c>
       <c r="F542" s="3">
         <v>46083</v>
@@ -14537,16 +14537,16 @@
         <v>36</v>
       </c>
       <c r="C543" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D543" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E543" s="2">
-        <v>82392</v>
+        <v>82691</v>
       </c>
       <c r="F543" s="3">
-        <v>46083</v>
+        <v>46098</v>
       </c>
       <c r="G543" s="1" t="s">
         <v>9</v>
@@ -14569,7 +14569,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E544" s="2">
-        <v>82691</v>
+        <v>82692</v>
       </c>
       <c r="F544" s="3">
         <v>46098</v>
@@ -14595,7 +14595,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E545" s="2">
-        <v>82692</v>
+        <v>82699</v>
       </c>
       <c r="F545" s="3">
         <v>46098</v>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -86,22 +86,22 @@
     <t>Reprovados</t>
   </si>
   <si>
+    <t>KATIA FERREIRA DE BARROS</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>Não Concluídos</t>
   </si>
   <si>
+    <t>RAFAEL CURSINO DE MOURA LEVY</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>Em Aprovação</t>
-  </si>
-  <si>
-    <t>KATIA FERREIRA DE BARROS</t>
-  </si>
-  <si>
-    <t>RAFAEL CURSINO DE MOURA LEVY</t>
   </si>
   <si>
     <t>SAMAUMA EVENTOS LTDA</t>
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H559"/>
+  <dimension ref="A1:H561"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -6723,10 +6723,10 @@
         <v>46098</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="243">
@@ -6749,10 +6749,10 @@
         <v>46098</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="244">
@@ -6775,10 +6775,10 @@
         <v>46099</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="245">
@@ -6801,10 +6801,10 @@
         <v>46099</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="246">
@@ -6812,7 +6812,7 @@
         <v>2506</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C246" s="2">
         <v>27</v>
@@ -6838,7 +6838,7 @@
         <v>2506</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C247" s="2">
         <v>27</v>
@@ -6864,7 +6864,7 @@
         <v>2506</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C248" s="2">
         <v>27</v>
@@ -6890,7 +6890,7 @@
         <v>2506</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C249" s="2">
         <v>27</v>
@@ -6916,7 +6916,7 @@
         <v>2506</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C250" s="2">
         <v>27</v>
@@ -6942,7 +6942,7 @@
         <v>2506</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C251" s="2">
         <v>27</v>
@@ -6968,7 +6968,7 @@
         <v>2506</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C252" s="2">
         <v>27</v>
@@ -6994,7 +6994,7 @@
         <v>2506</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C253" s="2">
         <v>27</v>
@@ -7020,7 +7020,7 @@
         <v>2506</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C254" s="2">
         <v>27</v>
@@ -7046,7 +7046,7 @@
         <v>2506</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C255" s="2">
         <v>27</v>
@@ -7072,7 +7072,7 @@
         <v>2506</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C256" s="2">
         <v>27</v>
@@ -7098,7 +7098,7 @@
         <v>2506</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C257" s="2">
         <v>27</v>
@@ -7124,7 +7124,7 @@
         <v>2506</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C258" s="2">
         <v>28</v>
@@ -7150,7 +7150,7 @@
         <v>2506</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C259" s="2">
         <v>28</v>
@@ -7176,7 +7176,7 @@
         <v>2506</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C260" s="2">
         <v>28</v>
@@ -7202,7 +7202,7 @@
         <v>2506</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C261" s="2">
         <v>28</v>
@@ -7228,7 +7228,7 @@
         <v>2506</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C262" s="2">
         <v>28</v>
@@ -7254,7 +7254,7 @@
         <v>2506</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C263" s="2">
         <v>28</v>
@@ -7280,7 +7280,7 @@
         <v>2506</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C264" s="2">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>2506</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C265" s="2">
         <v>28</v>
@@ -7332,7 +7332,7 @@
         <v>2506</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C266" s="2">
         <v>29</v>
@@ -7358,7 +7358,7 @@
         <v>2506</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C267" s="2">
         <v>29</v>
@@ -7384,7 +7384,7 @@
         <v>2506</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C268" s="2">
         <v>29</v>
@@ -7410,7 +7410,7 @@
         <v>2506</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C269" s="2">
         <v>30</v>
@@ -7436,7 +7436,7 @@
         <v>2506</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C270" s="2">
         <v>31</v>
@@ -7462,7 +7462,7 @@
         <v>2506</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C271" s="2">
         <v>32</v>
@@ -7488,7 +7488,7 @@
         <v>2506</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C272" s="2">
         <v>32</v>
@@ -7503,10 +7503,10 @@
         <v>46093</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="273">
@@ -7514,7 +7514,7 @@
         <v>2506</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C273" s="2">
         <v>32</v>
@@ -7540,7 +7540,7 @@
         <v>2506</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C274" s="2">
         <v>32</v>
@@ -7566,7 +7566,7 @@
         <v>2506</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C275" s="2">
         <v>32</v>
@@ -7592,7 +7592,7 @@
         <v>2506</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C276" s="2">
         <v>32</v>
@@ -7618,7 +7618,7 @@
         <v>2506</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C277" s="2">
         <v>32</v>
@@ -7644,7 +7644,7 @@
         <v>2506</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C278" s="2">
         <v>32</v>
@@ -7670,7 +7670,7 @@
         <v>2507</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C279" s="2">
         <v>26</v>
@@ -7696,7 +7696,7 @@
         <v>2507</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C280" s="2">
         <v>26</v>
@@ -7722,7 +7722,7 @@
         <v>2507</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C281" s="2">
         <v>26</v>
@@ -7748,7 +7748,7 @@
         <v>2507</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C282" s="2">
         <v>26</v>
@@ -7774,7 +7774,7 @@
         <v>2507</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C283" s="2">
         <v>26</v>
@@ -7800,7 +7800,7 @@
         <v>2507</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C284" s="2">
         <v>26</v>
@@ -7826,7 +7826,7 @@
         <v>2507</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C285" s="2">
         <v>26</v>
@@ -7852,7 +7852,7 @@
         <v>2507</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C286" s="2">
         <v>27</v>
@@ -7878,7 +7878,7 @@
         <v>2507</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C287" s="2">
         <v>27</v>
@@ -7904,7 +7904,7 @@
         <v>2507</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C288" s="2">
         <v>27</v>
@@ -7930,7 +7930,7 @@
         <v>2507</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C289" s="2">
         <v>27</v>
@@ -7956,7 +7956,7 @@
         <v>2507</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C290" s="2">
         <v>28</v>
@@ -7982,7 +7982,7 @@
         <v>2507</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C291" s="2">
         <v>28</v>
@@ -8008,7 +8008,7 @@
         <v>2507</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C292" s="2">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>2507</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C293" s="2">
         <v>28</v>
@@ -8060,7 +8060,7 @@
         <v>2507</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C294" s="2">
         <v>29</v>
@@ -8086,7 +8086,7 @@
         <v>2507</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C295" s="2">
         <v>29</v>
@@ -8112,7 +8112,7 @@
         <v>2507</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C296" s="2">
         <v>29</v>
@@ -8138,7 +8138,7 @@
         <v>2507</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C297" s="2">
         <v>29</v>
@@ -8164,7 +8164,7 @@
         <v>2507</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C298" s="2">
         <v>29</v>
@@ -8190,7 +8190,7 @@
         <v>2507</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C299" s="2">
         <v>29</v>
@@ -8216,7 +8216,7 @@
         <v>2507</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C300" s="2">
         <v>30</v>
@@ -8242,7 +8242,7 @@
         <v>2507</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C301" s="2">
         <v>31</v>
@@ -8268,7 +8268,7 @@
         <v>2507</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C302" s="2">
         <v>31</v>
@@ -8294,7 +8294,7 @@
         <v>2507</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C303" s="2">
         <v>31</v>
@@ -8320,7 +8320,7 @@
         <v>2507</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C304" s="2">
         <v>31</v>
@@ -8346,7 +8346,7 @@
         <v>2507</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C305" s="2">
         <v>32</v>
@@ -8372,7 +8372,7 @@
         <v>2507</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C306" s="2">
         <v>32</v>
@@ -8398,7 +8398,7 @@
         <v>2507</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C307" s="2">
         <v>32</v>
@@ -8424,7 +8424,7 @@
         <v>2507</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C308" s="2">
         <v>32</v>
@@ -8450,7 +8450,7 @@
         <v>2507</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C309" s="2">
         <v>32</v>
@@ -8476,7 +8476,7 @@
         <v>2507</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C310" s="2">
         <v>32</v>
@@ -8502,7 +8502,7 @@
         <v>2507</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C311" s="2">
         <v>32</v>
@@ -8528,7 +8528,7 @@
         <v>2509</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C312" s="2">
         <v>22</v>
@@ -8554,7 +8554,7 @@
         <v>2509</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C313" s="2">
         <v>22</v>
@@ -8580,7 +8580,7 @@
         <v>2509</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C314" s="2">
         <v>22</v>
@@ -8606,7 +8606,7 @@
         <v>2509</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C315" s="2">
         <v>22</v>
@@ -8632,7 +8632,7 @@
         <v>2509</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C316" s="2">
         <v>22</v>
@@ -8658,7 +8658,7 @@
         <v>2509</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C317" s="2">
         <v>23</v>
@@ -8684,7 +8684,7 @@
         <v>2509</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C318" s="2">
         <v>23</v>
@@ -8710,7 +8710,7 @@
         <v>2509</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C319" s="2">
         <v>23</v>
@@ -8736,7 +8736,7 @@
         <v>2509</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C320" s="2">
         <v>24</v>
@@ -8762,7 +8762,7 @@
         <v>2509</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C321" s="2">
         <v>24</v>
@@ -8788,7 +8788,7 @@
         <v>2509</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C322" s="2">
         <v>24</v>
@@ -8814,7 +8814,7 @@
         <v>2509</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C323" s="2">
         <v>25</v>
@@ -8840,7 +8840,7 @@
         <v>2509</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C324" s="2">
         <v>26</v>
@@ -8866,7 +8866,7 @@
         <v>2509</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C325" s="2">
         <v>27</v>
@@ -8892,7 +8892,7 @@
         <v>2509</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C326" s="2">
         <v>27</v>
@@ -8918,7 +8918,7 @@
         <v>2509</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C327" s="2">
         <v>27</v>
@@ -8944,7 +8944,7 @@
         <v>2509</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C328" s="2">
         <v>27</v>
@@ -8970,7 +8970,7 @@
         <v>2509</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C329" s="2">
         <v>27</v>
@@ -8996,7 +8996,7 @@
         <v>2509</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C330" s="2">
         <v>27</v>
@@ -9022,7 +9022,7 @@
         <v>2509</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C331" s="2">
         <v>27</v>
@@ -9048,7 +9048,7 @@
         <v>2509</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C332" s="2">
         <v>27</v>
@@ -9074,7 +9074,7 @@
         <v>2509</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C333" s="2">
         <v>28</v>
@@ -9100,7 +9100,7 @@
         <v>2509</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C334" s="2">
         <v>29</v>
@@ -9126,7 +9126,7 @@
         <v>2509</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C335" s="2">
         <v>29</v>
@@ -9152,7 +9152,7 @@
         <v>2509</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C336" s="2">
         <v>29</v>
@@ -9178,7 +9178,7 @@
         <v>2509</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C337" s="2">
         <v>29</v>
@@ -9204,7 +9204,7 @@
         <v>2509</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C338" s="2">
         <v>29</v>
@@ -9230,7 +9230,7 @@
         <v>2509</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C339" s="2">
         <v>30</v>
@@ -9256,7 +9256,7 @@
         <v>2509</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C340" s="2">
         <v>30</v>
@@ -9282,7 +9282,7 @@
         <v>2509</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C341" s="2">
         <v>30</v>
@@ -9308,7 +9308,7 @@
         <v>2509</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C342" s="2">
         <v>30</v>
@@ -9334,7 +9334,7 @@
         <v>2509</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C343" s="2">
         <v>31</v>
@@ -9360,7 +9360,7 @@
         <v>2509</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C344" s="2">
         <v>32</v>
@@ -9386,7 +9386,7 @@
         <v>2509</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C345" s="2">
         <v>32</v>
@@ -9412,7 +9412,7 @@
         <v>2509</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C346" s="2">
         <v>32</v>
@@ -9438,7 +9438,7 @@
         <v>2509</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C347" s="2">
         <v>32</v>
@@ -9464,7 +9464,7 @@
         <v>2509</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C348" s="2">
         <v>32</v>
@@ -9490,7 +9490,7 @@
         <v>2509</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C349" s="2">
         <v>32</v>
@@ -9516,7 +9516,7 @@
         <v>2509</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C350" s="2">
         <v>32</v>
@@ -9542,7 +9542,7 @@
         <v>2509</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C351" s="2">
         <v>32</v>
@@ -9568,7 +9568,7 @@
         <v>2509</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C352" s="2">
         <v>32</v>
@@ -9594,7 +9594,7 @@
         <v>2509</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C353" s="2">
         <v>33</v>
@@ -9620,7 +9620,7 @@
         <v>2509</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C354" s="2">
         <v>33</v>
@@ -9646,7 +9646,7 @@
         <v>2509</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C355" s="2">
         <v>33</v>
@@ -9672,7 +9672,7 @@
         <v>2509</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C356" s="2">
         <v>33</v>
@@ -9687,10 +9687,10 @@
         <v>46093</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H356" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="357">
@@ -9698,7 +9698,7 @@
         <v>2509</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C357" s="2">
         <v>33</v>
@@ -9724,7 +9724,7 @@
         <v>2509</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C358" s="2">
         <v>34</v>
@@ -11411,54 +11411,54 @@
     </row>
     <row ht="12.75" customHeight="1" r="423">
       <c r="A423" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C423" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D423" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E423" s="2">
-        <v>81484</v>
+        <v>82724</v>
       </c>
       <c r="F423" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="424">
       <c r="A424" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C424" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D424" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E424" s="2">
-        <v>81486</v>
+        <v>82725</v>
       </c>
       <c r="F424" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="425">
@@ -11475,7 +11475,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E425" s="2">
-        <v>81487</v>
+        <v>81484</v>
       </c>
       <c r="F425" s="3">
         <v>46029</v>
@@ -11495,16 +11495,16 @@
         <v>32</v>
       </c>
       <c r="C426" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D426" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E426" s="2">
-        <v>81613</v>
+        <v>81486</v>
       </c>
       <c r="F426" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>9</v>
@@ -11521,16 +11521,16 @@
         <v>32</v>
       </c>
       <c r="C427" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D427" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E427" s="2">
-        <v>81614</v>
+        <v>81487</v>
       </c>
       <c r="F427" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11553,7 +11553,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E428" s="2">
-        <v>81622</v>
+        <v>81613</v>
       </c>
       <c r="F428" s="3">
         <v>46036</v>
@@ -11579,7 +11579,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E429" s="2">
-        <v>81632</v>
+        <v>81614</v>
       </c>
       <c r="F429" s="3">
         <v>46036</v>
@@ -11605,10 +11605,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E430" s="2">
-        <v>81648</v>
+        <v>81622</v>
       </c>
       <c r="F430" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>9</v>
@@ -11631,10 +11631,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E431" s="2">
-        <v>81664</v>
+        <v>81632</v>
       </c>
       <c r="F431" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>9</v>
@@ -11651,16 +11651,16 @@
         <v>32</v>
       </c>
       <c r="C432" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D432" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E432" s="2">
-        <v>81815</v>
+        <v>81648</v>
       </c>
       <c r="F432" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11677,16 +11677,16 @@
         <v>32</v>
       </c>
       <c r="C433" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D433" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E433" s="2">
-        <v>81816</v>
+        <v>81664</v>
       </c>
       <c r="F433" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11709,7 +11709,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E434" s="2">
-        <v>81838</v>
+        <v>81815</v>
       </c>
       <c r="F434" s="3">
         <v>46045</v>
@@ -11735,7 +11735,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E435" s="2">
-        <v>81840</v>
+        <v>81816</v>
       </c>
       <c r="F435" s="3">
         <v>46045</v>
@@ -11755,16 +11755,16 @@
         <v>32</v>
       </c>
       <c r="C436" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D436" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E436" s="2">
-        <v>81959</v>
+        <v>81838</v>
       </c>
       <c r="F436" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>9</v>
@@ -11781,16 +11781,16 @@
         <v>32</v>
       </c>
       <c r="C437" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D437" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E437" s="2">
-        <v>81960</v>
+        <v>81840</v>
       </c>
       <c r="F437" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>9</v>
@@ -11807,16 +11807,16 @@
         <v>32</v>
       </c>
       <c r="C438" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D438" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E438" s="2">
-        <v>82063</v>
+        <v>81959</v>
       </c>
       <c r="F438" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11833,16 +11833,16 @@
         <v>32</v>
       </c>
       <c r="C439" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D439" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E439" s="2">
-        <v>82064</v>
+        <v>81960</v>
       </c>
       <c r="F439" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11865,10 +11865,10 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E440" s="2">
-        <v>82100</v>
+        <v>82063</v>
       </c>
       <c r="F440" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>9</v>
@@ -11885,16 +11885,16 @@
         <v>32</v>
       </c>
       <c r="C441" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D441" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E441" s="2">
-        <v>82333</v>
+        <v>82064</v>
       </c>
       <c r="F441" s="3">
-        <v>46079</v>
+        <v>46062</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11911,16 +11911,16 @@
         <v>32</v>
       </c>
       <c r="C442" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D442" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E442" s="2">
-        <v>82334</v>
+        <v>82100</v>
       </c>
       <c r="F442" s="3">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11937,16 +11937,16 @@
         <v>32</v>
       </c>
       <c r="C443" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D443" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E443" s="2">
-        <v>82258</v>
+        <v>82333</v>
       </c>
       <c r="F443" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11963,16 +11963,16 @@
         <v>32</v>
       </c>
       <c r="C444" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D444" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E444" s="2">
-        <v>82259</v>
+        <v>82334</v>
       </c>
       <c r="F444" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11995,7 +11995,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E445" s="2">
-        <v>82260</v>
+        <v>82258</v>
       </c>
       <c r="F445" s="3">
         <v>46076</v>
@@ -12021,10 +12021,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E446" s="2">
-        <v>82274</v>
+        <v>82259</v>
       </c>
       <c r="F446" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>9</v>
@@ -12041,16 +12041,16 @@
         <v>32</v>
       </c>
       <c r="C447" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D447" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E447" s="2">
-        <v>82409</v>
+        <v>82260</v>
       </c>
       <c r="F447" s="3">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>9</v>
@@ -12067,16 +12067,16 @@
         <v>32</v>
       </c>
       <c r="C448" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D448" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E448" s="2">
-        <v>82581</v>
+        <v>82274</v>
       </c>
       <c r="F448" s="3">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12093,16 +12093,16 @@
         <v>32</v>
       </c>
       <c r="C449" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D449" s="3">
-        <v>46093.4920058565</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E449" s="2">
-        <v>82582</v>
+        <v>82409</v>
       </c>
       <c r="F449" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12125,7 +12125,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E450" s="2">
-        <v>82583</v>
+        <v>82581</v>
       </c>
       <c r="F450" s="3">
         <v>46093</v>
@@ -12151,10 +12151,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E451" s="2">
-        <v>82672</v>
+        <v>82582</v>
       </c>
       <c r="F451" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>9</v>
@@ -12177,10 +12177,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E452" s="2">
-        <v>82674</v>
+        <v>82583</v>
       </c>
       <c r="F452" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12191,22 +12191,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="453">
       <c r="A453" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C453" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D453" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E453" s="2">
-        <v>81608</v>
+        <v>82672</v>
       </c>
       <c r="F453" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>9</v>
@@ -12217,22 +12217,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="454">
       <c r="A454" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C454" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D454" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E454" s="2">
-        <v>81609</v>
+        <v>82674</v>
       </c>
       <c r="F454" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>9</v>
@@ -12255,7 +12255,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E455" s="2">
-        <v>81610</v>
+        <v>81608</v>
       </c>
       <c r="F455" s="3">
         <v>46035</v>
@@ -12281,7 +12281,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E456" s="2">
-        <v>81611</v>
+        <v>81609</v>
       </c>
       <c r="F456" s="3">
         <v>46035</v>
@@ -12307,7 +12307,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E457" s="2">
-        <v>81612</v>
+        <v>81610</v>
       </c>
       <c r="F457" s="3">
         <v>46035</v>
@@ -12327,16 +12327,16 @@
         <v>33</v>
       </c>
       <c r="C458" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D458" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E458" s="2">
-        <v>81652</v>
+        <v>81611</v>
       </c>
       <c r="F458" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12353,16 +12353,16 @@
         <v>33</v>
       </c>
       <c r="C459" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D459" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E459" s="2">
-        <v>81659</v>
+        <v>81612</v>
       </c>
       <c r="F459" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12379,16 +12379,16 @@
         <v>33</v>
       </c>
       <c r="C460" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D460" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E460" s="2">
-        <v>81853</v>
+        <v>81652</v>
       </c>
       <c r="F460" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12405,16 +12405,16 @@
         <v>33</v>
       </c>
       <c r="C461" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D461" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E461" s="2">
-        <v>81869</v>
+        <v>81659</v>
       </c>
       <c r="F461" s="3">
-        <v>46049</v>
+        <v>46037</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12437,10 +12437,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E462" s="2">
-        <v>81890</v>
+        <v>81853</v>
       </c>
       <c r="F462" s="3">
-        <v>46050</v>
+        <v>46048</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12457,13 +12457,13 @@
         <v>33</v>
       </c>
       <c r="C463" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D463" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E463" s="2">
-        <v>81875</v>
+        <v>81869</v>
       </c>
       <c r="F463" s="3">
         <v>46049</v>
@@ -12483,13 +12483,13 @@
         <v>33</v>
       </c>
       <c r="C464" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D464" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E464" s="2">
-        <v>81881</v>
+        <v>81890</v>
       </c>
       <c r="F464" s="3">
         <v>46050</v>
@@ -12509,16 +12509,16 @@
         <v>33</v>
       </c>
       <c r="C465" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D465" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E465" s="2">
-        <v>82015</v>
+        <v>81875</v>
       </c>
       <c r="F465" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>9</v>
@@ -12535,16 +12535,16 @@
         <v>33</v>
       </c>
       <c r="C466" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D466" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E466" s="2">
-        <v>82017</v>
+        <v>81881</v>
       </c>
       <c r="F466" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12567,7 +12567,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E467" s="2">
-        <v>82020</v>
+        <v>82015</v>
       </c>
       <c r="F467" s="3">
         <v>46058</v>
@@ -12593,7 +12593,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E468" s="2">
-        <v>82023</v>
+        <v>82017</v>
       </c>
       <c r="F468" s="3">
         <v>46058</v>
@@ -12619,10 +12619,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E469" s="2">
-        <v>82061</v>
+        <v>82020</v>
       </c>
       <c r="F469" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>9</v>
@@ -12645,10 +12645,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E470" s="2">
-        <v>82081</v>
+        <v>82023</v>
       </c>
       <c r="F470" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>9</v>
@@ -12671,10 +12671,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E471" s="2">
-        <v>82095</v>
+        <v>82061</v>
       </c>
       <c r="F471" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>9</v>
@@ -12691,10 +12691,10 @@
         <v>33</v>
       </c>
       <c r="C472" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D472" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E472" s="2">
         <v>82081</v>
@@ -12717,13 +12717,13 @@
         <v>33</v>
       </c>
       <c r="C473" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D473" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E473" s="2">
-        <v>82107</v>
+        <v>82095</v>
       </c>
       <c r="F473" s="3">
         <v>46064</v>
@@ -12749,10 +12749,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E474" s="2">
-        <v>82112</v>
+        <v>82081</v>
       </c>
       <c r="F474" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12775,7 +12775,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E475" s="2">
-        <v>82113</v>
+        <v>82107</v>
       </c>
       <c r="F475" s="3">
         <v>46064</v>
@@ -12801,10 +12801,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E476" s="2">
-        <v>82123</v>
+        <v>82112</v>
       </c>
       <c r="F476" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>9</v>
@@ -12821,13 +12821,13 @@
         <v>33</v>
       </c>
       <c r="C477" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D477" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E477" s="2">
-        <v>82095</v>
+        <v>82113</v>
       </c>
       <c r="F477" s="3">
         <v>46064</v>
@@ -12847,16 +12847,16 @@
         <v>33</v>
       </c>
       <c r="C478" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D478" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E478" s="2">
-        <v>82106</v>
+        <v>82123</v>
       </c>
       <c r="F478" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12879,7 +12879,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E479" s="2">
-        <v>82107</v>
+        <v>82095</v>
       </c>
       <c r="F479" s="3">
         <v>46064</v>
@@ -12905,7 +12905,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E480" s="2">
-        <v>82109</v>
+        <v>82106</v>
       </c>
       <c r="F480" s="3">
         <v>46064</v>
@@ -12931,7 +12931,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E481" s="2">
-        <v>82110</v>
+        <v>82107</v>
       </c>
       <c r="F481" s="3">
         <v>46064</v>
@@ -12957,10 +12957,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E482" s="2">
-        <v>82139</v>
+        <v>82109</v>
       </c>
       <c r="F482" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12977,16 +12977,16 @@
         <v>33</v>
       </c>
       <c r="C483" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D483" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E483" s="2">
-        <v>82365</v>
+        <v>82110</v>
       </c>
       <c r="F483" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>9</v>
@@ -13003,16 +13003,16 @@
         <v>33</v>
       </c>
       <c r="C484" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D484" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E484" s="2">
-        <v>82366</v>
+        <v>82139</v>
       </c>
       <c r="F484" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G484" s="1" t="s">
         <v>9</v>
@@ -13035,7 +13035,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E485" s="2">
-        <v>82371</v>
+        <v>82365</v>
       </c>
       <c r="F485" s="3">
         <v>46080</v>
@@ -13061,10 +13061,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E486" s="2">
-        <v>82383</v>
+        <v>82366</v>
       </c>
       <c r="F486" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>9</v>
@@ -13087,10 +13087,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E487" s="2">
-        <v>82384</v>
+        <v>82371</v>
       </c>
       <c r="F487" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>9</v>
@@ -13107,16 +13107,16 @@
         <v>33</v>
       </c>
       <c r="C488" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D488" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E488" s="2">
-        <v>82693</v>
+        <v>82383</v>
       </c>
       <c r="F488" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>9</v>
@@ -13127,48 +13127,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="489">
       <c r="A489" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C489" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D489" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E489" s="2">
-        <v>81592</v>
+        <v>82384</v>
       </c>
       <c r="F489" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="G489" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H489" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="490">
       <c r="A490" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C490" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D490" s="3">
-        <v>46029.4149454282</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E490" s="2">
-        <v>81593</v>
+        <v>82693</v>
       </c>
       <c r="F490" s="3">
-        <v>46031</v>
+        <v>46098</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>9</v>
@@ -13185,22 +13185,22 @@
         <v>34</v>
       </c>
       <c r="C491" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D491" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E491" s="2">
-        <v>81697</v>
+        <v>81592</v>
       </c>
       <c r="F491" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="492">
@@ -13211,22 +13211,22 @@
         <v>34</v>
       </c>
       <c r="C492" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D492" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E492" s="2">
-        <v>81735</v>
+        <v>81593</v>
       </c>
       <c r="F492" s="3">
-        <v>46041</v>
+        <v>46031</v>
       </c>
       <c r="G492" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="493">
@@ -13237,16 +13237,16 @@
         <v>34</v>
       </c>
       <c r="C493" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D493" s="3">
-        <v>46045.4532476157</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E493" s="2">
-        <v>81823</v>
+        <v>81697</v>
       </c>
       <c r="F493" s="3">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="G493" s="1" t="s">
         <v>9</v>
@@ -13257,48 +13257,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="494">
       <c r="A494" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C494" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D494" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E494" s="2">
-        <v>81572</v>
+        <v>81735</v>
       </c>
       <c r="F494" s="3">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="G494" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H494" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="495">
       <c r="A495" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C495" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D495" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E495" s="2">
-        <v>81573</v>
+        <v>81823</v>
       </c>
       <c r="F495" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>9</v>
@@ -13321,7 +13321,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E496" s="2">
-        <v>81579</v>
+        <v>81572</v>
       </c>
       <c r="F496" s="3">
         <v>46031</v>
@@ -13347,7 +13347,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E497" s="2">
-        <v>81580</v>
+        <v>81573</v>
       </c>
       <c r="F497" s="3">
         <v>46031</v>
@@ -13373,7 +13373,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E498" s="2">
-        <v>81581</v>
+        <v>81579</v>
       </c>
       <c r="F498" s="3">
         <v>46031</v>
@@ -13399,7 +13399,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E499" s="2">
-        <v>81582</v>
+        <v>81580</v>
       </c>
       <c r="F499" s="3">
         <v>46031</v>
@@ -13425,7 +13425,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E500" s="2">
-        <v>81583</v>
+        <v>81581</v>
       </c>
       <c r="F500" s="3">
         <v>46031</v>
@@ -13445,16 +13445,16 @@
         <v>35</v>
       </c>
       <c r="C501" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D501" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E501" s="2">
-        <v>81667</v>
+        <v>81582</v>
       </c>
       <c r="F501" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G501" s="1" t="s">
         <v>9</v>
@@ -13471,16 +13471,16 @@
         <v>35</v>
       </c>
       <c r="C502" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D502" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E502" s="2">
-        <v>81668</v>
+        <v>81583</v>
       </c>
       <c r="F502" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G502" s="1" t="s">
         <v>9</v>
@@ -13503,10 +13503,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E503" s="2">
-        <v>81674</v>
+        <v>81667</v>
       </c>
       <c r="F503" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G503" s="1" t="s">
         <v>9</v>
@@ -13529,10 +13529,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E504" s="2">
-        <v>81675</v>
+        <v>81668</v>
       </c>
       <c r="F504" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>9</v>
@@ -13555,7 +13555,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E505" s="2">
-        <v>81677</v>
+        <v>81674</v>
       </c>
       <c r="F505" s="3">
         <v>46038</v>
@@ -13575,16 +13575,16 @@
         <v>35</v>
       </c>
       <c r="C506" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D506" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E506" s="2">
-        <v>81739</v>
+        <v>81675</v>
       </c>
       <c r="F506" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>9</v>
@@ -13601,16 +13601,16 @@
         <v>35</v>
       </c>
       <c r="C507" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D507" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E507" s="2">
-        <v>81741</v>
+        <v>81677</v>
       </c>
       <c r="F507" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>9</v>
@@ -13627,16 +13627,16 @@
         <v>35</v>
       </c>
       <c r="C508" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D508" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E508" s="2">
-        <v>81854</v>
+        <v>81739</v>
       </c>
       <c r="F508" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G508" s="1" t="s">
         <v>9</v>
@@ -13653,16 +13653,16 @@
         <v>35</v>
       </c>
       <c r="C509" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D509" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E509" s="2">
-        <v>81855</v>
+        <v>81741</v>
       </c>
       <c r="F509" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G509" s="1" t="s">
         <v>9</v>
@@ -13685,10 +13685,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E510" s="2">
-        <v>81858</v>
+        <v>81854</v>
       </c>
       <c r="F510" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G510" s="1" t="s">
         <v>9</v>
@@ -13711,10 +13711,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E511" s="2">
-        <v>81859</v>
+        <v>81855</v>
       </c>
       <c r="F511" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>9</v>
@@ -13737,7 +13737,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E512" s="2">
-        <v>81862</v>
+        <v>81858</v>
       </c>
       <c r="F512" s="3">
         <v>46049</v>
@@ -13763,7 +13763,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E513" s="2">
-        <v>81863</v>
+        <v>81859</v>
       </c>
       <c r="F513" s="3">
         <v>46049</v>
@@ -13783,16 +13783,16 @@
         <v>35</v>
       </c>
       <c r="C514" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D514" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E514" s="2">
-        <v>81958</v>
+        <v>81862</v>
       </c>
       <c r="F514" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G514" s="1" t="s">
         <v>9</v>
@@ -13809,16 +13809,16 @@
         <v>35</v>
       </c>
       <c r="C515" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D515" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E515" s="2">
-        <v>81965</v>
+        <v>81863</v>
       </c>
       <c r="F515" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G515" s="1" t="s">
         <v>9</v>
@@ -13835,16 +13835,16 @@
         <v>35</v>
       </c>
       <c r="C516" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D516" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E516" s="2">
-        <v>82085</v>
+        <v>81958</v>
       </c>
       <c r="F516" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G516" s="1" t="s">
         <v>9</v>
@@ -13861,16 +13861,16 @@
         <v>35</v>
       </c>
       <c r="C517" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D517" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E517" s="2">
-        <v>82086</v>
+        <v>81965</v>
       </c>
       <c r="F517" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G517" s="1" t="s">
         <v>9</v>
@@ -13893,10 +13893,10 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E518" s="2">
-        <v>82126</v>
+        <v>82085</v>
       </c>
       <c r="F518" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>9</v>
@@ -13913,16 +13913,16 @@
         <v>35</v>
       </c>
       <c r="C519" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D519" s="3">
-        <v>46064.5127051505</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E519" s="2">
-        <v>82268</v>
+        <v>82086</v>
       </c>
       <c r="F519" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G519" s="1" t="s">
         <v>9</v>
@@ -13939,13 +13939,13 @@
         <v>35</v>
       </c>
       <c r="C520" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D520" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E520" s="2">
-        <v>82142</v>
+        <v>82126</v>
       </c>
       <c r="F520" s="3">
         <v>46065</v>
@@ -13965,16 +13965,16 @@
         <v>35</v>
       </c>
       <c r="C521" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D521" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E521" s="2">
-        <v>82143</v>
+        <v>82268</v>
       </c>
       <c r="F521" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G521" s="1" t="s">
         <v>9</v>
@@ -13997,7 +13997,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E522" s="2">
-        <v>82144</v>
+        <v>82142</v>
       </c>
       <c r="F522" s="3">
         <v>46065</v>
@@ -14023,10 +14023,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E523" s="2">
-        <v>82166</v>
+        <v>82143</v>
       </c>
       <c r="F523" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>9</v>
@@ -14043,16 +14043,16 @@
         <v>35</v>
       </c>
       <c r="C524" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D524" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E524" s="2">
-        <v>82262</v>
+        <v>82144</v>
       </c>
       <c r="F524" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G524" s="1" t="s">
         <v>9</v>
@@ -14069,16 +14069,16 @@
         <v>35</v>
       </c>
       <c r="C525" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D525" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E525" s="2">
-        <v>82265</v>
+        <v>82166</v>
       </c>
       <c r="F525" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>9</v>
@@ -14101,7 +14101,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E526" s="2">
-        <v>82281</v>
+        <v>82262</v>
       </c>
       <c r="F526" s="3">
         <v>46077</v>
@@ -14127,7 +14127,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E527" s="2">
-        <v>82282</v>
+        <v>82265</v>
       </c>
       <c r="F527" s="3">
         <v>46077</v>
@@ -14147,16 +14147,16 @@
         <v>35</v>
       </c>
       <c r="C528" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D528" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E528" s="2">
-        <v>82340</v>
+        <v>82281</v>
       </c>
       <c r="F528" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G528" s="1" t="s">
         <v>9</v>
@@ -14173,16 +14173,16 @@
         <v>35</v>
       </c>
       <c r="C529" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D529" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E529" s="2">
-        <v>82399</v>
+        <v>82282</v>
       </c>
       <c r="F529" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G529" s="1" t="s">
         <v>9</v>
@@ -14199,16 +14199,16 @@
         <v>35</v>
       </c>
       <c r="C530" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D530" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E530" s="2">
-        <v>82400</v>
+        <v>82340</v>
       </c>
       <c r="F530" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>9</v>
@@ -14231,7 +14231,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E531" s="2">
-        <v>82401</v>
+        <v>82399</v>
       </c>
       <c r="F531" s="3">
         <v>46083</v>
@@ -14257,10 +14257,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E532" s="2">
-        <v>82412</v>
+        <v>82400</v>
       </c>
       <c r="F532" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G532" s="1" t="s">
         <v>9</v>
@@ -14283,10 +14283,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E533" s="2">
-        <v>82415</v>
+        <v>82401</v>
       </c>
       <c r="F533" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G533" s="1" t="s">
         <v>9</v>
@@ -14303,16 +14303,16 @@
         <v>35</v>
       </c>
       <c r="C534" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D534" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E534" s="2">
-        <v>82571</v>
+        <v>82412</v>
       </c>
       <c r="F534" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G534" s="1" t="s">
         <v>9</v>
@@ -14329,16 +14329,16 @@
         <v>35</v>
       </c>
       <c r="C535" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D535" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E535" s="2">
-        <v>82572</v>
+        <v>82415</v>
       </c>
       <c r="F535" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G535" s="1" t="s">
         <v>9</v>
@@ -14355,16 +14355,16 @@
         <v>35</v>
       </c>
       <c r="C536" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D536" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E536" s="2">
-        <v>82630</v>
+        <v>82571</v>
       </c>
       <c r="F536" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G536" s="1" t="s">
         <v>9</v>
@@ -14381,16 +14381,16 @@
         <v>35</v>
       </c>
       <c r="C537" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D537" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E537" s="2">
-        <v>82631</v>
+        <v>82572</v>
       </c>
       <c r="F537" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G537" s="1" t="s">
         <v>9</v>
@@ -14413,7 +14413,7 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E538" s="2">
-        <v>82632</v>
+        <v>82630</v>
       </c>
       <c r="F538" s="3">
         <v>46094</v>
@@ -14433,16 +14433,16 @@
         <v>35</v>
       </c>
       <c r="C539" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D539" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E539" s="2">
-        <v>82653</v>
+        <v>82631</v>
       </c>
       <c r="F539" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G539" s="1" t="s">
         <v>9</v>
@@ -14459,16 +14459,16 @@
         <v>35</v>
       </c>
       <c r="C540" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D540" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E540" s="2">
-        <v>82665</v>
+        <v>82632</v>
       </c>
       <c r="F540" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G540" s="1" t="s">
         <v>9</v>
@@ -14491,7 +14491,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E541" s="2">
-        <v>82668</v>
+        <v>82653</v>
       </c>
       <c r="F541" s="3">
         <v>46097</v>
@@ -14511,16 +14511,16 @@
         <v>35</v>
       </c>
       <c r="C542" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D542" s="3">
-        <v>46098.6661386574</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E542" s="2">
-        <v>82696</v>
+        <v>82665</v>
       </c>
       <c r="F542" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G542" s="1" t="s">
         <v>9</v>
@@ -14537,16 +14537,16 @@
         <v>35</v>
       </c>
       <c r="C543" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D543" s="3">
-        <v>46098.6661386574</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E543" s="2">
-        <v>82704</v>
+        <v>82668</v>
       </c>
       <c r="F543" s="3">
-        <v>46099</v>
+        <v>46097</v>
       </c>
       <c r="G543" s="1" t="s">
         <v>9</v>
@@ -14557,22 +14557,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="544">
       <c r="A544" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C544" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D544" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E544" s="2">
-        <v>82311</v>
+        <v>82696</v>
       </c>
       <c r="F544" s="3">
-        <v>46078</v>
+        <v>46098</v>
       </c>
       <c r="G544" s="1" t="s">
         <v>9</v>
@@ -14583,22 +14583,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="545">
       <c r="A545" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C545" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D545" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E545" s="2">
-        <v>82312</v>
+        <v>82704</v>
       </c>
       <c r="F545" s="3">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="G545" s="1" t="s">
         <v>9</v>
@@ -14621,7 +14621,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E546" s="2">
-        <v>82313</v>
+        <v>82311</v>
       </c>
       <c r="F546" s="3">
         <v>46078</v>
@@ -14647,7 +14647,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E547" s="2">
-        <v>82314</v>
+        <v>82312</v>
       </c>
       <c r="F547" s="3">
         <v>46078</v>
@@ -14673,10 +14673,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E548" s="2">
-        <v>82346</v>
+        <v>82313</v>
       </c>
       <c r="F548" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G548" s="1" t="s">
         <v>9</v>
@@ -14699,10 +14699,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E549" s="2">
-        <v>82361</v>
+        <v>82314</v>
       </c>
       <c r="F549" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G549" s="1" t="s">
         <v>9</v>
@@ -14725,10 +14725,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E550" s="2">
-        <v>82385</v>
+        <v>82346</v>
       </c>
       <c r="F550" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G550" s="1" t="s">
         <v>9</v>
@@ -14751,10 +14751,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E551" s="2">
-        <v>82391</v>
+        <v>82361</v>
       </c>
       <c r="F551" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G551" s="1" t="s">
         <v>9</v>
@@ -14777,7 +14777,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E552" s="2">
-        <v>82392</v>
+        <v>82385</v>
       </c>
       <c r="F552" s="3">
         <v>46083</v>
@@ -14797,16 +14797,16 @@
         <v>36</v>
       </c>
       <c r="C553" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D553" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E553" s="2">
-        <v>82691</v>
+        <v>82391</v>
       </c>
       <c r="F553" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G553" s="1" t="s">
         <v>9</v>
@@ -14823,16 +14823,16 @@
         <v>36</v>
       </c>
       <c r="C554" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D554" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E554" s="2">
-        <v>82692</v>
+        <v>82392</v>
       </c>
       <c r="F554" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G554" s="1" t="s">
         <v>9</v>
@@ -14855,7 +14855,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E555" s="2">
-        <v>82699</v>
+        <v>82691</v>
       </c>
       <c r="F555" s="3">
         <v>46098</v>
@@ -14881,10 +14881,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E556" s="2">
-        <v>82716</v>
+        <v>82692</v>
       </c>
       <c r="F556" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G556" s="1" t="s">
         <v>9</v>
@@ -14907,10 +14907,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E557" s="2">
-        <v>82717</v>
+        <v>82699</v>
       </c>
       <c r="F557" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G557" s="1" t="s">
         <v>9</v>
@@ -14921,22 +14921,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="558">
       <c r="A558" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C558" s="2">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D558" s="3">
-        <v>46029.4632696412</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E558" s="2">
-        <v>81495</v>
+        <v>82716</v>
       </c>
       <c r="F558" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G558" s="1" t="s">
         <v>9</v>
@@ -14947,27 +14947,79 @@
     </row>
     <row ht="12.75" customHeight="1" r="559">
       <c r="A559" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C559" s="2">
+        <v>2</v>
+      </c>
+      <c r="D559" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="E559" s="2">
+        <v>82717</v>
+      </c>
+      <c r="F559" s="3">
+        <v>46099</v>
+      </c>
+      <c r="G559" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H559" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="560">
+      <c r="A560" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C560" s="2">
+        <v>62</v>
+      </c>
+      <c r="D560" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E560" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F560" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G560" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H560" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="561">
+      <c r="A561" s="2">
         <v>9992</v>
       </c>
-      <c r="B559" s="1" t="s">
+      <c r="B561" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C559" s="2">
+      <c r="C561" s="2">
         <v>390</v>
       </c>
-      <c r="D559" s="3">
+      <c r="D561" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E559" s="2">
+      <c r="E561" s="2">
         <v>81684</v>
       </c>
-      <c r="F559" s="3">
+      <c r="F561" s="3">
         <v>46038</v>
       </c>
-      <c r="G559" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H559" s="1" t="s">
+      <c r="G561" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H561" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H561"/>
+  <dimension ref="A1:H562"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -11429,10 +11429,10 @@
         <v>46099</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="424">
@@ -11463,22 +11463,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="425">
       <c r="A425" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C425" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D425" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E425" s="2">
-        <v>81484</v>
+        <v>82727</v>
       </c>
       <c r="F425" s="3">
-        <v>46029</v>
+        <v>46100</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>9</v>
@@ -11501,7 +11501,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E426" s="2">
-        <v>81486</v>
+        <v>81484</v>
       </c>
       <c r="F426" s="3">
         <v>46029</v>
@@ -11527,7 +11527,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E427" s="2">
-        <v>81487</v>
+        <v>81486</v>
       </c>
       <c r="F427" s="3">
         <v>46029</v>
@@ -11547,16 +11547,16 @@
         <v>32</v>
       </c>
       <c r="C428" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D428" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E428" s="2">
-        <v>81613</v>
+        <v>81487</v>
       </c>
       <c r="F428" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>9</v>
@@ -11579,7 +11579,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E429" s="2">
-        <v>81614</v>
+        <v>81613</v>
       </c>
       <c r="F429" s="3">
         <v>46036</v>
@@ -11605,7 +11605,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E430" s="2">
-        <v>81622</v>
+        <v>81614</v>
       </c>
       <c r="F430" s="3">
         <v>46036</v>
@@ -11631,7 +11631,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E431" s="2">
-        <v>81632</v>
+        <v>81622</v>
       </c>
       <c r="F431" s="3">
         <v>46036</v>
@@ -11657,10 +11657,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E432" s="2">
-        <v>81648</v>
+        <v>81632</v>
       </c>
       <c r="F432" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11683,7 +11683,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E433" s="2">
-        <v>81664</v>
+        <v>81648</v>
       </c>
       <c r="F433" s="3">
         <v>46037</v>
@@ -11703,16 +11703,16 @@
         <v>32</v>
       </c>
       <c r="C434" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D434" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E434" s="2">
-        <v>81815</v>
+        <v>81664</v>
       </c>
       <c r="F434" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>9</v>
@@ -11735,7 +11735,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E435" s="2">
-        <v>81816</v>
+        <v>81815</v>
       </c>
       <c r="F435" s="3">
         <v>46045</v>
@@ -11761,7 +11761,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E436" s="2">
-        <v>81838</v>
+        <v>81816</v>
       </c>
       <c r="F436" s="3">
         <v>46045</v>
@@ -11787,7 +11787,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E437" s="2">
-        <v>81840</v>
+        <v>81838</v>
       </c>
       <c r="F437" s="3">
         <v>46045</v>
@@ -11807,16 +11807,16 @@
         <v>32</v>
       </c>
       <c r="C438" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D438" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E438" s="2">
-        <v>81959</v>
+        <v>81840</v>
       </c>
       <c r="F438" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11839,7 +11839,7 @@
         <v>46055.5991080671</v>
       </c>
       <c r="E439" s="2">
-        <v>81960</v>
+        <v>81959</v>
       </c>
       <c r="F439" s="3">
         <v>46055</v>
@@ -11859,16 +11859,16 @@
         <v>32</v>
       </c>
       <c r="C440" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D440" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E440" s="2">
-        <v>82063</v>
+        <v>81960</v>
       </c>
       <c r="F440" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>9</v>
@@ -11891,7 +11891,7 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E441" s="2">
-        <v>82064</v>
+        <v>82063</v>
       </c>
       <c r="F441" s="3">
         <v>46062</v>
@@ -11917,10 +11917,10 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E442" s="2">
-        <v>82100</v>
+        <v>82064</v>
       </c>
       <c r="F442" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11937,16 +11937,16 @@
         <v>32</v>
       </c>
       <c r="C443" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D443" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E443" s="2">
-        <v>82333</v>
+        <v>82100</v>
       </c>
       <c r="F443" s="3">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11969,7 +11969,7 @@
         <v>46072.7410579977</v>
       </c>
       <c r="E444" s="2">
-        <v>82334</v>
+        <v>82333</v>
       </c>
       <c r="F444" s="3">
         <v>46079</v>
@@ -11989,16 +11989,16 @@
         <v>32</v>
       </c>
       <c r="C445" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D445" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E445" s="2">
-        <v>82258</v>
+        <v>82334</v>
       </c>
       <c r="F445" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>9</v>
@@ -12021,7 +12021,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E446" s="2">
-        <v>82259</v>
+        <v>82258</v>
       </c>
       <c r="F446" s="3">
         <v>46076</v>
@@ -12047,7 +12047,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E447" s="2">
-        <v>82260</v>
+        <v>82259</v>
       </c>
       <c r="F447" s="3">
         <v>46076</v>
@@ -12073,10 +12073,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E448" s="2">
-        <v>82274</v>
+        <v>82260</v>
       </c>
       <c r="F448" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12093,16 +12093,16 @@
         <v>32</v>
       </c>
       <c r="C449" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D449" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E449" s="2">
-        <v>82409</v>
+        <v>82274</v>
       </c>
       <c r="F449" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12119,16 +12119,16 @@
         <v>32</v>
       </c>
       <c r="C450" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D450" s="3">
-        <v>46093.4920058565</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E450" s="2">
-        <v>82581</v>
+        <v>82409</v>
       </c>
       <c r="F450" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12151,7 +12151,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E451" s="2">
-        <v>82582</v>
+        <v>82581</v>
       </c>
       <c r="F451" s="3">
         <v>46093</v>
@@ -12177,7 +12177,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E452" s="2">
-        <v>82583</v>
+        <v>82582</v>
       </c>
       <c r="F452" s="3">
         <v>46093</v>
@@ -12203,10 +12203,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E453" s="2">
-        <v>82672</v>
+        <v>82583</v>
       </c>
       <c r="F453" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>9</v>
@@ -12229,7 +12229,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E454" s="2">
-        <v>82674</v>
+        <v>82672</v>
       </c>
       <c r="F454" s="3">
         <v>46097</v>
@@ -12243,22 +12243,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="455">
       <c r="A455" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C455" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D455" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E455" s="2">
-        <v>81608</v>
+        <v>82674</v>
       </c>
       <c r="F455" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>9</v>
@@ -12281,7 +12281,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E456" s="2">
-        <v>81609</v>
+        <v>81608</v>
       </c>
       <c r="F456" s="3">
         <v>46035</v>
@@ -12307,7 +12307,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E457" s="2">
-        <v>81610</v>
+        <v>81609</v>
       </c>
       <c r="F457" s="3">
         <v>46035</v>
@@ -12333,7 +12333,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E458" s="2">
-        <v>81611</v>
+        <v>81610</v>
       </c>
       <c r="F458" s="3">
         <v>46035</v>
@@ -12359,7 +12359,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E459" s="2">
-        <v>81612</v>
+        <v>81611</v>
       </c>
       <c r="F459" s="3">
         <v>46035</v>
@@ -12379,16 +12379,16 @@
         <v>33</v>
       </c>
       <c r="C460" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D460" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E460" s="2">
-        <v>81652</v>
+        <v>81612</v>
       </c>
       <c r="F460" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12411,7 +12411,7 @@
         <v>46036.6342081481</v>
       </c>
       <c r="E461" s="2">
-        <v>81659</v>
+        <v>81652</v>
       </c>
       <c r="F461" s="3">
         <v>46037</v>
@@ -12431,16 +12431,16 @@
         <v>33</v>
       </c>
       <c r="C462" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D462" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E462" s="2">
-        <v>81853</v>
+        <v>81659</v>
       </c>
       <c r="F462" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12463,10 +12463,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E463" s="2">
-        <v>81869</v>
+        <v>81853</v>
       </c>
       <c r="F463" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12489,10 +12489,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E464" s="2">
-        <v>81890</v>
+        <v>81869</v>
       </c>
       <c r="F464" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12509,16 +12509,16 @@
         <v>33</v>
       </c>
       <c r="C465" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D465" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E465" s="2">
-        <v>81875</v>
+        <v>81890</v>
       </c>
       <c r="F465" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>9</v>
@@ -12541,10 +12541,10 @@
         <v>46049.4871256134</v>
       </c>
       <c r="E466" s="2">
-        <v>81881</v>
+        <v>81875</v>
       </c>
       <c r="F466" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12561,16 +12561,16 @@
         <v>33</v>
       </c>
       <c r="C467" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D467" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E467" s="2">
-        <v>82015</v>
+        <v>81881</v>
       </c>
       <c r="F467" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>9</v>
@@ -12593,7 +12593,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E468" s="2">
-        <v>82017</v>
+        <v>82015</v>
       </c>
       <c r="F468" s="3">
         <v>46058</v>
@@ -12619,7 +12619,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E469" s="2">
-        <v>82020</v>
+        <v>82017</v>
       </c>
       <c r="F469" s="3">
         <v>46058</v>
@@ -12645,7 +12645,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E470" s="2">
-        <v>82023</v>
+        <v>82020</v>
       </c>
       <c r="F470" s="3">
         <v>46058</v>
@@ -12671,10 +12671,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E471" s="2">
-        <v>82061</v>
+        <v>82023</v>
       </c>
       <c r="F471" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>9</v>
@@ -12697,10 +12697,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E472" s="2">
-        <v>82081</v>
+        <v>82061</v>
       </c>
       <c r="F472" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12723,10 +12723,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E473" s="2">
-        <v>82095</v>
+        <v>82081</v>
       </c>
       <c r="F473" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12743,16 +12743,16 @@
         <v>33</v>
       </c>
       <c r="C474" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D474" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E474" s="2">
-        <v>82081</v>
+        <v>82095</v>
       </c>
       <c r="F474" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12775,10 +12775,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E475" s="2">
-        <v>82107</v>
+        <v>82081</v>
       </c>
       <c r="F475" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>9</v>
@@ -12801,7 +12801,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E476" s="2">
-        <v>82112</v>
+        <v>82107</v>
       </c>
       <c r="F476" s="3">
         <v>46064</v>
@@ -12827,7 +12827,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E477" s="2">
-        <v>82113</v>
+        <v>82112</v>
       </c>
       <c r="F477" s="3">
         <v>46064</v>
@@ -12853,10 +12853,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E478" s="2">
-        <v>82123</v>
+        <v>82113</v>
       </c>
       <c r="F478" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12873,16 +12873,16 @@
         <v>33</v>
       </c>
       <c r="C479" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D479" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E479" s="2">
-        <v>82095</v>
+        <v>82123</v>
       </c>
       <c r="F479" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12905,7 +12905,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E480" s="2">
-        <v>82106</v>
+        <v>82095</v>
       </c>
       <c r="F480" s="3">
         <v>46064</v>
@@ -12931,7 +12931,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E481" s="2">
-        <v>82107</v>
+        <v>82106</v>
       </c>
       <c r="F481" s="3">
         <v>46064</v>
@@ -12957,7 +12957,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E482" s="2">
-        <v>82109</v>
+        <v>82107</v>
       </c>
       <c r="F482" s="3">
         <v>46064</v>
@@ -12983,7 +12983,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E483" s="2">
-        <v>82110</v>
+        <v>82109</v>
       </c>
       <c r="F483" s="3">
         <v>46064</v>
@@ -13009,10 +13009,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E484" s="2">
-        <v>82139</v>
+        <v>82110</v>
       </c>
       <c r="F484" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G484" s="1" t="s">
         <v>9</v>
@@ -13029,16 +13029,16 @@
         <v>33</v>
       </c>
       <c r="C485" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D485" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E485" s="2">
-        <v>82365</v>
+        <v>82139</v>
       </c>
       <c r="F485" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>9</v>
@@ -13061,7 +13061,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E486" s="2">
-        <v>82366</v>
+        <v>82365</v>
       </c>
       <c r="F486" s="3">
         <v>46080</v>
@@ -13087,7 +13087,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E487" s="2">
-        <v>82371</v>
+        <v>82366</v>
       </c>
       <c r="F487" s="3">
         <v>46080</v>
@@ -13113,10 +13113,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E488" s="2">
-        <v>82383</v>
+        <v>82371</v>
       </c>
       <c r="F488" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>9</v>
@@ -13139,7 +13139,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E489" s="2">
-        <v>82384</v>
+        <v>82383</v>
       </c>
       <c r="F489" s="3">
         <v>46083</v>
@@ -13159,16 +13159,16 @@
         <v>33</v>
       </c>
       <c r="C490" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D490" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E490" s="2">
-        <v>82693</v>
+        <v>82384</v>
       </c>
       <c r="F490" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>9</v>
@@ -13179,28 +13179,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="491">
       <c r="A491" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C491" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D491" s="3">
-        <v>46029.4149454282</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E491" s="2">
-        <v>81592</v>
+        <v>82693</v>
       </c>
       <c r="F491" s="3">
-        <v>46031</v>
+        <v>46098</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="492">
@@ -13217,16 +13217,16 @@
         <v>46029.4149454282</v>
       </c>
       <c r="E492" s="2">
-        <v>81593</v>
+        <v>81592</v>
       </c>
       <c r="F492" s="3">
         <v>46031</v>
       </c>
       <c r="G492" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="493">
@@ -13237,16 +13237,16 @@
         <v>34</v>
       </c>
       <c r="C493" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D493" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E493" s="2">
-        <v>81697</v>
+        <v>81593</v>
       </c>
       <c r="F493" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G493" s="1" t="s">
         <v>9</v>
@@ -13269,16 +13269,16 @@
         <v>46038.6827563889</v>
       </c>
       <c r="E494" s="2">
-        <v>81735</v>
+        <v>81697</v>
       </c>
       <c r="F494" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G494" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H494" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="495">
@@ -13289,42 +13289,42 @@
         <v>34</v>
       </c>
       <c r="C495" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D495" s="3">
-        <v>46045.4532476157</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E495" s="2">
-        <v>81823</v>
+        <v>81735</v>
       </c>
       <c r="F495" s="3">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H495" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="496">
       <c r="A496" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C496" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D496" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E496" s="2">
-        <v>81572</v>
+        <v>81823</v>
       </c>
       <c r="F496" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G496" s="1" t="s">
         <v>9</v>
@@ -13347,7 +13347,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E497" s="2">
-        <v>81573</v>
+        <v>81572</v>
       </c>
       <c r="F497" s="3">
         <v>46031</v>
@@ -13373,7 +13373,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E498" s="2">
-        <v>81579</v>
+        <v>81573</v>
       </c>
       <c r="F498" s="3">
         <v>46031</v>
@@ -13399,7 +13399,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E499" s="2">
-        <v>81580</v>
+        <v>81579</v>
       </c>
       <c r="F499" s="3">
         <v>46031</v>
@@ -13425,7 +13425,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E500" s="2">
-        <v>81581</v>
+        <v>81580</v>
       </c>
       <c r="F500" s="3">
         <v>46031</v>
@@ -13451,7 +13451,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E501" s="2">
-        <v>81582</v>
+        <v>81581</v>
       </c>
       <c r="F501" s="3">
         <v>46031</v>
@@ -13477,7 +13477,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E502" s="2">
-        <v>81583</v>
+        <v>81582</v>
       </c>
       <c r="F502" s="3">
         <v>46031</v>
@@ -13497,16 +13497,16 @@
         <v>35</v>
       </c>
       <c r="C503" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D503" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E503" s="2">
-        <v>81667</v>
+        <v>81583</v>
       </c>
       <c r="F503" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G503" s="1" t="s">
         <v>9</v>
@@ -13529,7 +13529,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E504" s="2">
-        <v>81668</v>
+        <v>81667</v>
       </c>
       <c r="F504" s="3">
         <v>46037</v>
@@ -13555,10 +13555,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E505" s="2">
-        <v>81674</v>
+        <v>81668</v>
       </c>
       <c r="F505" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G505" s="1" t="s">
         <v>9</v>
@@ -13581,7 +13581,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E506" s="2">
-        <v>81675</v>
+        <v>81674</v>
       </c>
       <c r="F506" s="3">
         <v>46038</v>
@@ -13607,7 +13607,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E507" s="2">
-        <v>81677</v>
+        <v>81675</v>
       </c>
       <c r="F507" s="3">
         <v>46038</v>
@@ -13627,16 +13627,16 @@
         <v>35</v>
       </c>
       <c r="C508" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D508" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E508" s="2">
-        <v>81739</v>
+        <v>81677</v>
       </c>
       <c r="F508" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G508" s="1" t="s">
         <v>9</v>
@@ -13659,7 +13659,7 @@
         <v>46041.6133887269</v>
       </c>
       <c r="E509" s="2">
-        <v>81741</v>
+        <v>81739</v>
       </c>
       <c r="F509" s="3">
         <v>46041</v>
@@ -13679,16 +13679,16 @@
         <v>35</v>
       </c>
       <c r="C510" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D510" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E510" s="2">
-        <v>81854</v>
+        <v>81741</v>
       </c>
       <c r="F510" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G510" s="1" t="s">
         <v>9</v>
@@ -13711,7 +13711,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E511" s="2">
-        <v>81855</v>
+        <v>81854</v>
       </c>
       <c r="F511" s="3">
         <v>46048</v>
@@ -13737,10 +13737,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E512" s="2">
-        <v>81858</v>
+        <v>81855</v>
       </c>
       <c r="F512" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G512" s="1" t="s">
         <v>9</v>
@@ -13763,7 +13763,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E513" s="2">
-        <v>81859</v>
+        <v>81858</v>
       </c>
       <c r="F513" s="3">
         <v>46049</v>
@@ -13789,7 +13789,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E514" s="2">
-        <v>81862</v>
+        <v>81859</v>
       </c>
       <c r="F514" s="3">
         <v>46049</v>
@@ -13815,7 +13815,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E515" s="2">
-        <v>81863</v>
+        <v>81862</v>
       </c>
       <c r="F515" s="3">
         <v>46049</v>
@@ -13835,16 +13835,16 @@
         <v>35</v>
       </c>
       <c r="C516" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D516" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E516" s="2">
-        <v>81958</v>
+        <v>81863</v>
       </c>
       <c r="F516" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G516" s="1" t="s">
         <v>9</v>
@@ -13867,7 +13867,7 @@
         <v>46055.5924236111</v>
       </c>
       <c r="E517" s="2">
-        <v>81965</v>
+        <v>81958</v>
       </c>
       <c r="F517" s="3">
         <v>46055</v>
@@ -13887,16 +13887,16 @@
         <v>35</v>
       </c>
       <c r="C518" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D518" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E518" s="2">
-        <v>82085</v>
+        <v>81965</v>
       </c>
       <c r="F518" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>9</v>
@@ -13919,7 +13919,7 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E519" s="2">
-        <v>82086</v>
+        <v>82085</v>
       </c>
       <c r="F519" s="3">
         <v>46063</v>
@@ -13945,10 +13945,10 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E520" s="2">
-        <v>82126</v>
+        <v>82086</v>
       </c>
       <c r="F520" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G520" s="1" t="s">
         <v>9</v>
@@ -13965,16 +13965,16 @@
         <v>35</v>
       </c>
       <c r="C521" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D521" s="3">
-        <v>46064.5127051505</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E521" s="2">
-        <v>82268</v>
+        <v>82126</v>
       </c>
       <c r="F521" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G521" s="1" t="s">
         <v>9</v>
@@ -13991,16 +13991,16 @@
         <v>35</v>
       </c>
       <c r="C522" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D522" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E522" s="2">
-        <v>82142</v>
+        <v>82268</v>
       </c>
       <c r="F522" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G522" s="1" t="s">
         <v>9</v>
@@ -14023,7 +14023,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E523" s="2">
-        <v>82143</v>
+        <v>82142</v>
       </c>
       <c r="F523" s="3">
         <v>46065</v>
@@ -14049,7 +14049,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E524" s="2">
-        <v>82144</v>
+        <v>82143</v>
       </c>
       <c r="F524" s="3">
         <v>46065</v>
@@ -14075,10 +14075,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E525" s="2">
-        <v>82166</v>
+        <v>82144</v>
       </c>
       <c r="F525" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>9</v>
@@ -14095,16 +14095,16 @@
         <v>35</v>
       </c>
       <c r="C526" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D526" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E526" s="2">
-        <v>82262</v>
+        <v>82166</v>
       </c>
       <c r="F526" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G526" s="1" t="s">
         <v>9</v>
@@ -14127,7 +14127,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E527" s="2">
-        <v>82265</v>
+        <v>82262</v>
       </c>
       <c r="F527" s="3">
         <v>46077</v>
@@ -14153,7 +14153,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E528" s="2">
-        <v>82281</v>
+        <v>82265</v>
       </c>
       <c r="F528" s="3">
         <v>46077</v>
@@ -14179,7 +14179,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E529" s="2">
-        <v>82282</v>
+        <v>82281</v>
       </c>
       <c r="F529" s="3">
         <v>46077</v>
@@ -14199,16 +14199,16 @@
         <v>35</v>
       </c>
       <c r="C530" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D530" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E530" s="2">
-        <v>82340</v>
+        <v>82282</v>
       </c>
       <c r="F530" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>9</v>
@@ -14225,16 +14225,16 @@
         <v>35</v>
       </c>
       <c r="C531" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D531" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E531" s="2">
-        <v>82399</v>
+        <v>82340</v>
       </c>
       <c r="F531" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="G531" s="1" t="s">
         <v>9</v>
@@ -14257,7 +14257,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E532" s="2">
-        <v>82400</v>
+        <v>82399</v>
       </c>
       <c r="F532" s="3">
         <v>46083</v>
@@ -14283,7 +14283,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E533" s="2">
-        <v>82401</v>
+        <v>82400</v>
       </c>
       <c r="F533" s="3">
         <v>46083</v>
@@ -14309,10 +14309,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E534" s="2">
-        <v>82412</v>
+        <v>82401</v>
       </c>
       <c r="F534" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G534" s="1" t="s">
         <v>9</v>
@@ -14335,7 +14335,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E535" s="2">
-        <v>82415</v>
+        <v>82412</v>
       </c>
       <c r="F535" s="3">
         <v>46084</v>
@@ -14355,16 +14355,16 @@
         <v>35</v>
       </c>
       <c r="C536" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D536" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E536" s="2">
-        <v>82571</v>
+        <v>82415</v>
       </c>
       <c r="F536" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G536" s="1" t="s">
         <v>9</v>
@@ -14387,7 +14387,7 @@
         <v>46086.6312882639</v>
       </c>
       <c r="E537" s="2">
-        <v>82572</v>
+        <v>82571</v>
       </c>
       <c r="F537" s="3">
         <v>46093</v>
@@ -14407,16 +14407,16 @@
         <v>35</v>
       </c>
       <c r="C538" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D538" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E538" s="2">
-        <v>82630</v>
+        <v>82572</v>
       </c>
       <c r="F538" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G538" s="1" t="s">
         <v>9</v>
@@ -14439,7 +14439,7 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E539" s="2">
-        <v>82631</v>
+        <v>82630</v>
       </c>
       <c r="F539" s="3">
         <v>46094</v>
@@ -14465,7 +14465,7 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E540" s="2">
-        <v>82632</v>
+        <v>82631</v>
       </c>
       <c r="F540" s="3">
         <v>46094</v>
@@ -14485,16 +14485,16 @@
         <v>35</v>
       </c>
       <c r="C541" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D541" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E541" s="2">
-        <v>82653</v>
+        <v>82632</v>
       </c>
       <c r="F541" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G541" s="1" t="s">
         <v>9</v>
@@ -14517,7 +14517,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E542" s="2">
-        <v>82665</v>
+        <v>82653</v>
       </c>
       <c r="F542" s="3">
         <v>46097</v>
@@ -14543,7 +14543,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E543" s="2">
-        <v>82668</v>
+        <v>82665</v>
       </c>
       <c r="F543" s="3">
         <v>46097</v>
@@ -14563,16 +14563,16 @@
         <v>35</v>
       </c>
       <c r="C544" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D544" s="3">
-        <v>46098.6661386574</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E544" s="2">
-        <v>82696</v>
+        <v>82668</v>
       </c>
       <c r="F544" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G544" s="1" t="s">
         <v>9</v>
@@ -14595,10 +14595,10 @@
         <v>46098.6661386574</v>
       </c>
       <c r="E545" s="2">
-        <v>82704</v>
+        <v>82696</v>
       </c>
       <c r="F545" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G545" s="1" t="s">
         <v>9</v>
@@ -14609,22 +14609,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="546">
       <c r="A546" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C546" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D546" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E546" s="2">
-        <v>82311</v>
+        <v>82704</v>
       </c>
       <c r="F546" s="3">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="G546" s="1" t="s">
         <v>9</v>
@@ -14647,7 +14647,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E547" s="2">
-        <v>82312</v>
+        <v>82311</v>
       </c>
       <c r="F547" s="3">
         <v>46078</v>
@@ -14673,7 +14673,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E548" s="2">
-        <v>82313</v>
+        <v>82312</v>
       </c>
       <c r="F548" s="3">
         <v>46078</v>
@@ -14699,7 +14699,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E549" s="2">
-        <v>82314</v>
+        <v>82313</v>
       </c>
       <c r="F549" s="3">
         <v>46078</v>
@@ -14725,10 +14725,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E550" s="2">
-        <v>82346</v>
+        <v>82314</v>
       </c>
       <c r="F550" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G550" s="1" t="s">
         <v>9</v>
@@ -14751,7 +14751,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E551" s="2">
-        <v>82361</v>
+        <v>82346</v>
       </c>
       <c r="F551" s="3">
         <v>46080</v>
@@ -14777,10 +14777,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E552" s="2">
-        <v>82385</v>
+        <v>82361</v>
       </c>
       <c r="F552" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G552" s="1" t="s">
         <v>9</v>
@@ -14803,7 +14803,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E553" s="2">
-        <v>82391</v>
+        <v>82385</v>
       </c>
       <c r="F553" s="3">
         <v>46083</v>
@@ -14829,7 +14829,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E554" s="2">
-        <v>82392</v>
+        <v>82391</v>
       </c>
       <c r="F554" s="3">
         <v>46083</v>
@@ -14849,16 +14849,16 @@
         <v>36</v>
       </c>
       <c r="C555" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D555" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E555" s="2">
-        <v>82691</v>
+        <v>82392</v>
       </c>
       <c r="F555" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G555" s="1" t="s">
         <v>9</v>
@@ -14881,7 +14881,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E556" s="2">
-        <v>82692</v>
+        <v>82691</v>
       </c>
       <c r="F556" s="3">
         <v>46098</v>
@@ -14907,7 +14907,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E557" s="2">
-        <v>82699</v>
+        <v>82692</v>
       </c>
       <c r="F557" s="3">
         <v>46098</v>
@@ -14933,10 +14933,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E558" s="2">
-        <v>82716</v>
+        <v>82699</v>
       </c>
       <c r="F558" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G558" s="1" t="s">
         <v>9</v>
@@ -14959,36 +14959,36 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E559" s="2">
-        <v>82717</v>
+        <v>82716</v>
       </c>
       <c r="F559" s="3">
         <v>46099</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H559" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="560">
       <c r="A560" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C560" s="2">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D560" s="3">
-        <v>46029.4632696412</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E560" s="2">
-        <v>81495</v>
+        <v>82717</v>
       </c>
       <c r="F560" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G560" s="1" t="s">
         <v>9</v>
@@ -14999,27 +14999,53 @@
     </row>
     <row ht="12.75" customHeight="1" r="561">
       <c r="A561" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C561" s="2">
+        <v>62</v>
+      </c>
+      <c r="D561" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E561" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F561" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G561" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H561" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="562">
+      <c r="A562" s="2">
         <v>9992</v>
       </c>
-      <c r="B561" s="1" t="s">
+      <c r="B562" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C561" s="2">
+      <c r="C562" s="2">
         <v>390</v>
       </c>
-      <c r="D561" s="3">
+      <c r="D562" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E561" s="2">
+      <c r="E562" s="2">
         <v>81684</v>
       </c>
-      <c r="F561" s="3">
+      <c r="F562" s="3">
         <v>46038</v>
       </c>
-      <c r="G561" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H561" s="1" t="s">
+      <c r="G562" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H562" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H562"/>
+  <dimension ref="A1:H563"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -11489,22 +11489,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="426">
       <c r="A426" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C426" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D426" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E426" s="2">
-        <v>81484</v>
+        <v>82730</v>
       </c>
       <c r="F426" s="3">
-        <v>46029</v>
+        <v>46100</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>9</v>
@@ -11527,7 +11527,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E427" s="2">
-        <v>81486</v>
+        <v>81484</v>
       </c>
       <c r="F427" s="3">
         <v>46029</v>
@@ -11553,7 +11553,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E428" s="2">
-        <v>81487</v>
+        <v>81486</v>
       </c>
       <c r="F428" s="3">
         <v>46029</v>
@@ -11573,16 +11573,16 @@
         <v>32</v>
       </c>
       <c r="C429" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D429" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E429" s="2">
-        <v>81613</v>
+        <v>81487</v>
       </c>
       <c r="F429" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>9</v>
@@ -11605,7 +11605,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E430" s="2">
-        <v>81614</v>
+        <v>81613</v>
       </c>
       <c r="F430" s="3">
         <v>46036</v>
@@ -11631,7 +11631,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E431" s="2">
-        <v>81622</v>
+        <v>81614</v>
       </c>
       <c r="F431" s="3">
         <v>46036</v>
@@ -11657,7 +11657,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E432" s="2">
-        <v>81632</v>
+        <v>81622</v>
       </c>
       <c r="F432" s="3">
         <v>46036</v>
@@ -11683,10 +11683,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E433" s="2">
-        <v>81648</v>
+        <v>81632</v>
       </c>
       <c r="F433" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11709,7 +11709,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E434" s="2">
-        <v>81664</v>
+        <v>81648</v>
       </c>
       <c r="F434" s="3">
         <v>46037</v>
@@ -11729,16 +11729,16 @@
         <v>32</v>
       </c>
       <c r="C435" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D435" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E435" s="2">
-        <v>81815</v>
+        <v>81664</v>
       </c>
       <c r="F435" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>9</v>
@@ -11761,7 +11761,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E436" s="2">
-        <v>81816</v>
+        <v>81815</v>
       </c>
       <c r="F436" s="3">
         <v>46045</v>
@@ -11787,7 +11787,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E437" s="2">
-        <v>81838</v>
+        <v>81816</v>
       </c>
       <c r="F437" s="3">
         <v>46045</v>
@@ -11813,7 +11813,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E438" s="2">
-        <v>81840</v>
+        <v>81838</v>
       </c>
       <c r="F438" s="3">
         <v>46045</v>
@@ -11833,16 +11833,16 @@
         <v>32</v>
       </c>
       <c r="C439" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D439" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E439" s="2">
-        <v>81959</v>
+        <v>81840</v>
       </c>
       <c r="F439" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11865,7 +11865,7 @@
         <v>46055.5991080671</v>
       </c>
       <c r="E440" s="2">
-        <v>81960</v>
+        <v>81959</v>
       </c>
       <c r="F440" s="3">
         <v>46055</v>
@@ -11885,16 +11885,16 @@
         <v>32</v>
       </c>
       <c r="C441" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D441" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E441" s="2">
-        <v>82063</v>
+        <v>81960</v>
       </c>
       <c r="F441" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11917,7 +11917,7 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E442" s="2">
-        <v>82064</v>
+        <v>82063</v>
       </c>
       <c r="F442" s="3">
         <v>46062</v>
@@ -11943,10 +11943,10 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E443" s="2">
-        <v>82100</v>
+        <v>82064</v>
       </c>
       <c r="F443" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11963,16 +11963,16 @@
         <v>32</v>
       </c>
       <c r="C444" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D444" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E444" s="2">
-        <v>82333</v>
+        <v>82100</v>
       </c>
       <c r="F444" s="3">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11995,7 +11995,7 @@
         <v>46072.7410579977</v>
       </c>
       <c r="E445" s="2">
-        <v>82334</v>
+        <v>82333</v>
       </c>
       <c r="F445" s="3">
         <v>46079</v>
@@ -12015,16 +12015,16 @@
         <v>32</v>
       </c>
       <c r="C446" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D446" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E446" s="2">
-        <v>82258</v>
+        <v>82334</v>
       </c>
       <c r="F446" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>9</v>
@@ -12047,7 +12047,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E447" s="2">
-        <v>82259</v>
+        <v>82258</v>
       </c>
       <c r="F447" s="3">
         <v>46076</v>
@@ -12073,7 +12073,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E448" s="2">
-        <v>82260</v>
+        <v>82259</v>
       </c>
       <c r="F448" s="3">
         <v>46076</v>
@@ -12099,10 +12099,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E449" s="2">
-        <v>82274</v>
+        <v>82260</v>
       </c>
       <c r="F449" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12119,16 +12119,16 @@
         <v>32</v>
       </c>
       <c r="C450" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D450" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E450" s="2">
-        <v>82409</v>
+        <v>82274</v>
       </c>
       <c r="F450" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12145,16 +12145,16 @@
         <v>32</v>
       </c>
       <c r="C451" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D451" s="3">
-        <v>46093.4920058565</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E451" s="2">
-        <v>82581</v>
+        <v>82409</v>
       </c>
       <c r="F451" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>9</v>
@@ -12177,7 +12177,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E452" s="2">
-        <v>82582</v>
+        <v>82581</v>
       </c>
       <c r="F452" s="3">
         <v>46093</v>
@@ -12203,7 +12203,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E453" s="2">
-        <v>82583</v>
+        <v>82582</v>
       </c>
       <c r="F453" s="3">
         <v>46093</v>
@@ -12229,10 +12229,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E454" s="2">
-        <v>82672</v>
+        <v>82583</v>
       </c>
       <c r="F454" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>9</v>
@@ -12255,7 +12255,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E455" s="2">
-        <v>82674</v>
+        <v>82672</v>
       </c>
       <c r="F455" s="3">
         <v>46097</v>
@@ -12269,22 +12269,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="456">
       <c r="A456" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C456" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D456" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E456" s="2">
-        <v>81608</v>
+        <v>82674</v>
       </c>
       <c r="F456" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12307,7 +12307,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E457" s="2">
-        <v>81609</v>
+        <v>81608</v>
       </c>
       <c r="F457" s="3">
         <v>46035</v>
@@ -12333,7 +12333,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E458" s="2">
-        <v>81610</v>
+        <v>81609</v>
       </c>
       <c r="F458" s="3">
         <v>46035</v>
@@ -12359,7 +12359,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E459" s="2">
-        <v>81611</v>
+        <v>81610</v>
       </c>
       <c r="F459" s="3">
         <v>46035</v>
@@ -12385,7 +12385,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E460" s="2">
-        <v>81612</v>
+        <v>81611</v>
       </c>
       <c r="F460" s="3">
         <v>46035</v>
@@ -12405,16 +12405,16 @@
         <v>33</v>
       </c>
       <c r="C461" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D461" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E461" s="2">
-        <v>81652</v>
+        <v>81612</v>
       </c>
       <c r="F461" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12437,7 +12437,7 @@
         <v>46036.6342081481</v>
       </c>
       <c r="E462" s="2">
-        <v>81659</v>
+        <v>81652</v>
       </c>
       <c r="F462" s="3">
         <v>46037</v>
@@ -12457,16 +12457,16 @@
         <v>33</v>
       </c>
       <c r="C463" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D463" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E463" s="2">
-        <v>81853</v>
+        <v>81659</v>
       </c>
       <c r="F463" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12489,10 +12489,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E464" s="2">
-        <v>81869</v>
+        <v>81853</v>
       </c>
       <c r="F464" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12515,10 +12515,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E465" s="2">
-        <v>81890</v>
+        <v>81869</v>
       </c>
       <c r="F465" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>9</v>
@@ -12535,16 +12535,16 @@
         <v>33</v>
       </c>
       <c r="C466" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D466" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E466" s="2">
-        <v>81875</v>
+        <v>81890</v>
       </c>
       <c r="F466" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12567,10 +12567,10 @@
         <v>46049.4871256134</v>
       </c>
       <c r="E467" s="2">
-        <v>81881</v>
+        <v>81875</v>
       </c>
       <c r="F467" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>9</v>
@@ -12587,16 +12587,16 @@
         <v>33</v>
       </c>
       <c r="C468" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D468" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E468" s="2">
-        <v>82015</v>
+        <v>81881</v>
       </c>
       <c r="F468" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>9</v>
@@ -12619,7 +12619,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E469" s="2">
-        <v>82017</v>
+        <v>82015</v>
       </c>
       <c r="F469" s="3">
         <v>46058</v>
@@ -12645,7 +12645,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E470" s="2">
-        <v>82020</v>
+        <v>82017</v>
       </c>
       <c r="F470" s="3">
         <v>46058</v>
@@ -12671,7 +12671,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E471" s="2">
-        <v>82023</v>
+        <v>82020</v>
       </c>
       <c r="F471" s="3">
         <v>46058</v>
@@ -12697,10 +12697,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E472" s="2">
-        <v>82061</v>
+        <v>82023</v>
       </c>
       <c r="F472" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12723,10 +12723,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E473" s="2">
-        <v>82081</v>
+        <v>82061</v>
       </c>
       <c r="F473" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12749,10 +12749,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E474" s="2">
-        <v>82095</v>
+        <v>82081</v>
       </c>
       <c r="F474" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12769,16 +12769,16 @@
         <v>33</v>
       </c>
       <c r="C475" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D475" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E475" s="2">
-        <v>82081</v>
+        <v>82095</v>
       </c>
       <c r="F475" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>9</v>
@@ -12801,10 +12801,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E476" s="2">
-        <v>82107</v>
+        <v>82081</v>
       </c>
       <c r="F476" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>9</v>
@@ -12827,7 +12827,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E477" s="2">
-        <v>82112</v>
+        <v>82107</v>
       </c>
       <c r="F477" s="3">
         <v>46064</v>
@@ -12853,7 +12853,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E478" s="2">
-        <v>82113</v>
+        <v>82112</v>
       </c>
       <c r="F478" s="3">
         <v>46064</v>
@@ -12879,10 +12879,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E479" s="2">
-        <v>82123</v>
+        <v>82113</v>
       </c>
       <c r="F479" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12899,16 +12899,16 @@
         <v>33</v>
       </c>
       <c r="C480" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D480" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E480" s="2">
-        <v>82095</v>
+        <v>82123</v>
       </c>
       <c r="F480" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>9</v>
@@ -12931,7 +12931,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E481" s="2">
-        <v>82106</v>
+        <v>82095</v>
       </c>
       <c r="F481" s="3">
         <v>46064</v>
@@ -12957,7 +12957,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E482" s="2">
-        <v>82107</v>
+        <v>82106</v>
       </c>
       <c r="F482" s="3">
         <v>46064</v>
@@ -12983,7 +12983,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E483" s="2">
-        <v>82109</v>
+        <v>82107</v>
       </c>
       <c r="F483" s="3">
         <v>46064</v>
@@ -13009,7 +13009,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E484" s="2">
-        <v>82110</v>
+        <v>82109</v>
       </c>
       <c r="F484" s="3">
         <v>46064</v>
@@ -13035,10 +13035,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E485" s="2">
-        <v>82139</v>
+        <v>82110</v>
       </c>
       <c r="F485" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>9</v>
@@ -13055,16 +13055,16 @@
         <v>33</v>
       </c>
       <c r="C486" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D486" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E486" s="2">
-        <v>82365</v>
+        <v>82139</v>
       </c>
       <c r="F486" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>9</v>
@@ -13087,7 +13087,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E487" s="2">
-        <v>82366</v>
+        <v>82365</v>
       </c>
       <c r="F487" s="3">
         <v>46080</v>
@@ -13113,7 +13113,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E488" s="2">
-        <v>82371</v>
+        <v>82366</v>
       </c>
       <c r="F488" s="3">
         <v>46080</v>
@@ -13139,10 +13139,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E489" s="2">
-        <v>82383</v>
+        <v>82371</v>
       </c>
       <c r="F489" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>9</v>
@@ -13165,7 +13165,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E490" s="2">
-        <v>82384</v>
+        <v>82383</v>
       </c>
       <c r="F490" s="3">
         <v>46083</v>
@@ -13185,16 +13185,16 @@
         <v>33</v>
       </c>
       <c r="C491" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D491" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E491" s="2">
-        <v>82693</v>
+        <v>82384</v>
       </c>
       <c r="F491" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>9</v>
@@ -13205,28 +13205,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="492">
       <c r="A492" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C492" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D492" s="3">
-        <v>46029.4149454282</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E492" s="2">
-        <v>81592</v>
+        <v>82693</v>
       </c>
       <c r="F492" s="3">
-        <v>46031</v>
+        <v>46098</v>
       </c>
       <c r="G492" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="493">
@@ -13243,16 +13243,16 @@
         <v>46029.4149454282</v>
       </c>
       <c r="E493" s="2">
-        <v>81593</v>
+        <v>81592</v>
       </c>
       <c r="F493" s="3">
         <v>46031</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="494">
@@ -13263,16 +13263,16 @@
         <v>34</v>
       </c>
       <c r="C494" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D494" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E494" s="2">
-        <v>81697</v>
+        <v>81593</v>
       </c>
       <c r="F494" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>9</v>
@@ -13295,16 +13295,16 @@
         <v>46038.6827563889</v>
       </c>
       <c r="E495" s="2">
-        <v>81735</v>
+        <v>81697</v>
       </c>
       <c r="F495" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H495" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="496">
@@ -13315,42 +13315,42 @@
         <v>34</v>
       </c>
       <c r="C496" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D496" s="3">
-        <v>46045.4532476157</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E496" s="2">
-        <v>81823</v>
+        <v>81735</v>
       </c>
       <c r="F496" s="3">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H496" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="497">
       <c r="A497" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C497" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D497" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E497" s="2">
-        <v>81572</v>
+        <v>81823</v>
       </c>
       <c r="F497" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G497" s="1" t="s">
         <v>9</v>
@@ -13373,7 +13373,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E498" s="2">
-        <v>81573</v>
+        <v>81572</v>
       </c>
       <c r="F498" s="3">
         <v>46031</v>
@@ -13399,7 +13399,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E499" s="2">
-        <v>81579</v>
+        <v>81573</v>
       </c>
       <c r="F499" s="3">
         <v>46031</v>
@@ -13425,7 +13425,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E500" s="2">
-        <v>81580</v>
+        <v>81579</v>
       </c>
       <c r="F500" s="3">
         <v>46031</v>
@@ -13451,7 +13451,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E501" s="2">
-        <v>81581</v>
+        <v>81580</v>
       </c>
       <c r="F501" s="3">
         <v>46031</v>
@@ -13477,7 +13477,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E502" s="2">
-        <v>81582</v>
+        <v>81581</v>
       </c>
       <c r="F502" s="3">
         <v>46031</v>
@@ -13503,7 +13503,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E503" s="2">
-        <v>81583</v>
+        <v>81582</v>
       </c>
       <c r="F503" s="3">
         <v>46031</v>
@@ -13523,16 +13523,16 @@
         <v>35</v>
       </c>
       <c r="C504" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D504" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E504" s="2">
-        <v>81667</v>
+        <v>81583</v>
       </c>
       <c r="F504" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>9</v>
@@ -13555,7 +13555,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E505" s="2">
-        <v>81668</v>
+        <v>81667</v>
       </c>
       <c r="F505" s="3">
         <v>46037</v>
@@ -13581,10 +13581,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E506" s="2">
-        <v>81674</v>
+        <v>81668</v>
       </c>
       <c r="F506" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>9</v>
@@ -13607,7 +13607,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E507" s="2">
-        <v>81675</v>
+        <v>81674</v>
       </c>
       <c r="F507" s="3">
         <v>46038</v>
@@ -13633,7 +13633,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E508" s="2">
-        <v>81677</v>
+        <v>81675</v>
       </c>
       <c r="F508" s="3">
         <v>46038</v>
@@ -13653,16 +13653,16 @@
         <v>35</v>
       </c>
       <c r="C509" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D509" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E509" s="2">
-        <v>81739</v>
+        <v>81677</v>
       </c>
       <c r="F509" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G509" s="1" t="s">
         <v>9</v>
@@ -13685,7 +13685,7 @@
         <v>46041.6133887269</v>
       </c>
       <c r="E510" s="2">
-        <v>81741</v>
+        <v>81739</v>
       </c>
       <c r="F510" s="3">
         <v>46041</v>
@@ -13705,16 +13705,16 @@
         <v>35</v>
       </c>
       <c r="C511" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D511" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E511" s="2">
-        <v>81854</v>
+        <v>81741</v>
       </c>
       <c r="F511" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>9</v>
@@ -13737,7 +13737,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E512" s="2">
-        <v>81855</v>
+        <v>81854</v>
       </c>
       <c r="F512" s="3">
         <v>46048</v>
@@ -13763,10 +13763,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E513" s="2">
-        <v>81858</v>
+        <v>81855</v>
       </c>
       <c r="F513" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G513" s="1" t="s">
         <v>9</v>
@@ -13789,7 +13789,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E514" s="2">
-        <v>81859</v>
+        <v>81858</v>
       </c>
       <c r="F514" s="3">
         <v>46049</v>
@@ -13815,7 +13815,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E515" s="2">
-        <v>81862</v>
+        <v>81859</v>
       </c>
       <c r="F515" s="3">
         <v>46049</v>
@@ -13841,7 +13841,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E516" s="2">
-        <v>81863</v>
+        <v>81862</v>
       </c>
       <c r="F516" s="3">
         <v>46049</v>
@@ -13861,16 +13861,16 @@
         <v>35</v>
       </c>
       <c r="C517" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D517" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E517" s="2">
-        <v>81958</v>
+        <v>81863</v>
       </c>
       <c r="F517" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G517" s="1" t="s">
         <v>9</v>
@@ -13893,7 +13893,7 @@
         <v>46055.5924236111</v>
       </c>
       <c r="E518" s="2">
-        <v>81965</v>
+        <v>81958</v>
       </c>
       <c r="F518" s="3">
         <v>46055</v>
@@ -13913,16 +13913,16 @@
         <v>35</v>
       </c>
       <c r="C519" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D519" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E519" s="2">
-        <v>82085</v>
+        <v>81965</v>
       </c>
       <c r="F519" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G519" s="1" t="s">
         <v>9</v>
@@ -13945,7 +13945,7 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E520" s="2">
-        <v>82086</v>
+        <v>82085</v>
       </c>
       <c r="F520" s="3">
         <v>46063</v>
@@ -13971,10 +13971,10 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E521" s="2">
-        <v>82126</v>
+        <v>82086</v>
       </c>
       <c r="F521" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G521" s="1" t="s">
         <v>9</v>
@@ -13991,16 +13991,16 @@
         <v>35</v>
       </c>
       <c r="C522" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D522" s="3">
-        <v>46064.5127051505</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E522" s="2">
-        <v>82268</v>
+        <v>82126</v>
       </c>
       <c r="F522" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G522" s="1" t="s">
         <v>9</v>
@@ -14017,16 +14017,16 @@
         <v>35</v>
       </c>
       <c r="C523" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D523" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E523" s="2">
-        <v>82142</v>
+        <v>82268</v>
       </c>
       <c r="F523" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>9</v>
@@ -14049,7 +14049,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E524" s="2">
-        <v>82143</v>
+        <v>82142</v>
       </c>
       <c r="F524" s="3">
         <v>46065</v>
@@ -14075,7 +14075,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E525" s="2">
-        <v>82144</v>
+        <v>82143</v>
       </c>
       <c r="F525" s="3">
         <v>46065</v>
@@ -14101,10 +14101,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E526" s="2">
-        <v>82166</v>
+        <v>82144</v>
       </c>
       <c r="F526" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="G526" s="1" t="s">
         <v>9</v>
@@ -14121,16 +14121,16 @@
         <v>35</v>
       </c>
       <c r="C527" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D527" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E527" s="2">
-        <v>82262</v>
+        <v>82166</v>
       </c>
       <c r="F527" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G527" s="1" t="s">
         <v>9</v>
@@ -14153,7 +14153,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E528" s="2">
-        <v>82265</v>
+        <v>82262</v>
       </c>
       <c r="F528" s="3">
         <v>46077</v>
@@ -14179,7 +14179,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E529" s="2">
-        <v>82281</v>
+        <v>82265</v>
       </c>
       <c r="F529" s="3">
         <v>46077</v>
@@ -14205,7 +14205,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E530" s="2">
-        <v>82282</v>
+        <v>82281</v>
       </c>
       <c r="F530" s="3">
         <v>46077</v>
@@ -14225,16 +14225,16 @@
         <v>35</v>
       </c>
       <c r="C531" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D531" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E531" s="2">
-        <v>82340</v>
+        <v>82282</v>
       </c>
       <c r="F531" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G531" s="1" t="s">
         <v>9</v>
@@ -14251,16 +14251,16 @@
         <v>35</v>
       </c>
       <c r="C532" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D532" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E532" s="2">
-        <v>82399</v>
+        <v>82340</v>
       </c>
       <c r="F532" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="G532" s="1" t="s">
         <v>9</v>
@@ -14283,7 +14283,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E533" s="2">
-        <v>82400</v>
+        <v>82399</v>
       </c>
       <c r="F533" s="3">
         <v>46083</v>
@@ -14309,7 +14309,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E534" s="2">
-        <v>82401</v>
+        <v>82400</v>
       </c>
       <c r="F534" s="3">
         <v>46083</v>
@@ -14335,10 +14335,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E535" s="2">
-        <v>82412</v>
+        <v>82401</v>
       </c>
       <c r="F535" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G535" s="1" t="s">
         <v>9</v>
@@ -14361,7 +14361,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E536" s="2">
-        <v>82415</v>
+        <v>82412</v>
       </c>
       <c r="F536" s="3">
         <v>46084</v>
@@ -14381,16 +14381,16 @@
         <v>35</v>
       </c>
       <c r="C537" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D537" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E537" s="2">
-        <v>82571</v>
+        <v>82415</v>
       </c>
       <c r="F537" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G537" s="1" t="s">
         <v>9</v>
@@ -14413,7 +14413,7 @@
         <v>46086.6312882639</v>
       </c>
       <c r="E538" s="2">
-        <v>82572</v>
+        <v>82571</v>
       </c>
       <c r="F538" s="3">
         <v>46093</v>
@@ -14433,16 +14433,16 @@
         <v>35</v>
       </c>
       <c r="C539" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D539" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E539" s="2">
-        <v>82630</v>
+        <v>82572</v>
       </c>
       <c r="F539" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G539" s="1" t="s">
         <v>9</v>
@@ -14465,7 +14465,7 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E540" s="2">
-        <v>82631</v>
+        <v>82630</v>
       </c>
       <c r="F540" s="3">
         <v>46094</v>
@@ -14491,7 +14491,7 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E541" s="2">
-        <v>82632</v>
+        <v>82631</v>
       </c>
       <c r="F541" s="3">
         <v>46094</v>
@@ -14511,16 +14511,16 @@
         <v>35</v>
       </c>
       <c r="C542" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D542" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E542" s="2">
-        <v>82653</v>
+        <v>82632</v>
       </c>
       <c r="F542" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G542" s="1" t="s">
         <v>9</v>
@@ -14543,7 +14543,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E543" s="2">
-        <v>82665</v>
+        <v>82653</v>
       </c>
       <c r="F543" s="3">
         <v>46097</v>
@@ -14569,7 +14569,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E544" s="2">
-        <v>82668</v>
+        <v>82665</v>
       </c>
       <c r="F544" s="3">
         <v>46097</v>
@@ -14589,16 +14589,16 @@
         <v>35</v>
       </c>
       <c r="C545" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D545" s="3">
-        <v>46098.6661386574</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E545" s="2">
-        <v>82696</v>
+        <v>82668</v>
       </c>
       <c r="F545" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G545" s="1" t="s">
         <v>9</v>
@@ -14621,10 +14621,10 @@
         <v>46098.6661386574</v>
       </c>
       <c r="E546" s="2">
-        <v>82704</v>
+        <v>82696</v>
       </c>
       <c r="F546" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G546" s="1" t="s">
         <v>9</v>
@@ -14635,22 +14635,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="547">
       <c r="A547" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C547" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D547" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E547" s="2">
-        <v>82311</v>
+        <v>82704</v>
       </c>
       <c r="F547" s="3">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="G547" s="1" t="s">
         <v>9</v>
@@ -14673,7 +14673,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E548" s="2">
-        <v>82312</v>
+        <v>82311</v>
       </c>
       <c r="F548" s="3">
         <v>46078</v>
@@ -14699,7 +14699,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E549" s="2">
-        <v>82313</v>
+        <v>82312</v>
       </c>
       <c r="F549" s="3">
         <v>46078</v>
@@ -14725,7 +14725,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E550" s="2">
-        <v>82314</v>
+        <v>82313</v>
       </c>
       <c r="F550" s="3">
         <v>46078</v>
@@ -14751,10 +14751,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E551" s="2">
-        <v>82346</v>
+        <v>82314</v>
       </c>
       <c r="F551" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G551" s="1" t="s">
         <v>9</v>
@@ -14777,7 +14777,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E552" s="2">
-        <v>82361</v>
+        <v>82346</v>
       </c>
       <c r="F552" s="3">
         <v>46080</v>
@@ -14803,10 +14803,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E553" s="2">
-        <v>82385</v>
+        <v>82361</v>
       </c>
       <c r="F553" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G553" s="1" t="s">
         <v>9</v>
@@ -14829,7 +14829,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E554" s="2">
-        <v>82391</v>
+        <v>82385</v>
       </c>
       <c r="F554" s="3">
         <v>46083</v>
@@ -14855,7 +14855,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E555" s="2">
-        <v>82392</v>
+        <v>82391</v>
       </c>
       <c r="F555" s="3">
         <v>46083</v>
@@ -14875,16 +14875,16 @@
         <v>36</v>
       </c>
       <c r="C556" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D556" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E556" s="2">
-        <v>82691</v>
+        <v>82392</v>
       </c>
       <c r="F556" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G556" s="1" t="s">
         <v>9</v>
@@ -14907,7 +14907,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E557" s="2">
-        <v>82692</v>
+        <v>82691</v>
       </c>
       <c r="F557" s="3">
         <v>46098</v>
@@ -14933,7 +14933,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E558" s="2">
-        <v>82699</v>
+        <v>82692</v>
       </c>
       <c r="F558" s="3">
         <v>46098</v>
@@ -14959,16 +14959,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E559" s="2">
-        <v>82716</v>
+        <v>82699</v>
       </c>
       <c r="F559" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H559" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="560">
@@ -14985,7 +14985,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E560" s="2">
-        <v>82717</v>
+        <v>82716</v>
       </c>
       <c r="F560" s="3">
         <v>46099</v>
@@ -14999,22 +14999,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="561">
       <c r="A561" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C561" s="2">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D561" s="3">
-        <v>46029.4632696412</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E561" s="2">
-        <v>81495</v>
+        <v>82717</v>
       </c>
       <c r="F561" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G561" s="1" t="s">
         <v>9</v>
@@ -15025,27 +15025,53 @@
     </row>
     <row ht="12.75" customHeight="1" r="562">
       <c r="A562" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C562" s="2">
+        <v>62</v>
+      </c>
+      <c r="D562" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E562" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F562" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G562" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H562" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="563">
+      <c r="A563" s="2">
         <v>9992</v>
       </c>
-      <c r="B562" s="1" t="s">
+      <c r="B563" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C562" s="2">
+      <c r="C563" s="2">
         <v>390</v>
       </c>
-      <c r="D562" s="3">
+      <c r="D563" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E562" s="2">
+      <c r="E563" s="2">
         <v>81684</v>
       </c>
-      <c r="F562" s="3">
+      <c r="F563" s="3">
         <v>46038</v>
       </c>
-      <c r="G562" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H562" s="1" t="s">
+      <c r="G563" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H563" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -11455,10 +11455,10 @@
         <v>46099</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="425">

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -95,13 +95,13 @@
     <t>Não Concluídos</t>
   </si>
   <si>
-    <t>RAFAEL CURSINO DE MOURA LEVY</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
     <t>Em Aprovação</t>
+  </si>
+  <si>
+    <t>RAFAEL CURSINO DE MOURA LEVY</t>
   </si>
   <si>
     <t>SAMAUMA EVENTOS LTDA</t>
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H563"/>
+  <dimension ref="A1:H570"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -6809,22 +6809,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="246">
       <c r="A246" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C246" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D246" s="3">
-        <v>46044.6368950926</v>
+        <v>46098.5034667708</v>
       </c>
       <c r="E246" s="2">
-        <v>81802</v>
+        <v>82755</v>
       </c>
       <c r="F246" s="3">
-        <v>46044</v>
+        <v>46101</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>9</v>
@@ -6847,7 +6847,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E247" s="2">
-        <v>81803</v>
+        <v>81802</v>
       </c>
       <c r="F247" s="3">
         <v>46044</v>
@@ -6873,7 +6873,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E248" s="2">
-        <v>81804</v>
+        <v>81803</v>
       </c>
       <c r="F248" s="3">
         <v>46044</v>
@@ -6899,7 +6899,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E249" s="2">
-        <v>81806</v>
+        <v>81804</v>
       </c>
       <c r="F249" s="3">
         <v>46044</v>
@@ -6925,7 +6925,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E250" s="2">
-        <v>81807</v>
+        <v>81806</v>
       </c>
       <c r="F250" s="3">
         <v>46044</v>
@@ -6951,10 +6951,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E251" s="2">
-        <v>81812</v>
+        <v>81807</v>
       </c>
       <c r="F251" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>9</v>
@@ -6977,7 +6977,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E252" s="2">
-        <v>81813</v>
+        <v>81812</v>
       </c>
       <c r="F252" s="3">
         <v>46045</v>
@@ -7003,7 +7003,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E253" s="2">
-        <v>81814</v>
+        <v>81813</v>
       </c>
       <c r="F253" s="3">
         <v>46045</v>
@@ -7029,7 +7029,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E254" s="2">
-        <v>81818</v>
+        <v>81814</v>
       </c>
       <c r="F254" s="3">
         <v>46045</v>
@@ -7055,7 +7055,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E255" s="2">
-        <v>81822</v>
+        <v>81818</v>
       </c>
       <c r="F255" s="3">
         <v>46045</v>
@@ -7081,7 +7081,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E256" s="2">
-        <v>81833</v>
+        <v>81822</v>
       </c>
       <c r="F256" s="3">
         <v>46045</v>
@@ -7107,7 +7107,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E257" s="2">
-        <v>81841</v>
+        <v>81833</v>
       </c>
       <c r="F257" s="3">
         <v>46045</v>
@@ -7127,16 +7127,16 @@
         <v>24</v>
       </c>
       <c r="C258" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D258" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E258" s="2">
-        <v>81928</v>
+        <v>81841</v>
       </c>
       <c r="F258" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>9</v>
@@ -7159,7 +7159,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E259" s="2">
-        <v>81929</v>
+        <v>81928</v>
       </c>
       <c r="F259" s="3">
         <v>46052</v>
@@ -7185,7 +7185,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E260" s="2">
-        <v>81930</v>
+        <v>81929</v>
       </c>
       <c r="F260" s="3">
         <v>46052</v>
@@ -7211,7 +7211,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E261" s="2">
-        <v>81932</v>
+        <v>81930</v>
       </c>
       <c r="F261" s="3">
         <v>46052</v>
@@ -7237,7 +7237,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E262" s="2">
-        <v>81933</v>
+        <v>81932</v>
       </c>
       <c r="F262" s="3">
         <v>46052</v>
@@ -7263,7 +7263,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E263" s="2">
-        <v>81934</v>
+        <v>81933</v>
       </c>
       <c r="F263" s="3">
         <v>46052</v>
@@ -7289,7 +7289,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E264" s="2">
-        <v>81935</v>
+        <v>81934</v>
       </c>
       <c r="F264" s="3">
         <v>46052</v>
@@ -7315,7 +7315,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E265" s="2">
-        <v>81936</v>
+        <v>81935</v>
       </c>
       <c r="F265" s="3">
         <v>46052</v>
@@ -7335,16 +7335,16 @@
         <v>24</v>
       </c>
       <c r="C266" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D266" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E266" s="2">
-        <v>82222</v>
+        <v>81936</v>
       </c>
       <c r="F266" s="3">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>9</v>
@@ -7367,10 +7367,10 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E267" s="2">
-        <v>82226</v>
+        <v>82222</v>
       </c>
       <c r="F267" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>9</v>
@@ -7393,7 +7393,7 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E268" s="2">
-        <v>82229</v>
+        <v>82226</v>
       </c>
       <c r="F268" s="3">
         <v>46073</v>
@@ -7413,13 +7413,13 @@
         <v>24</v>
       </c>
       <c r="C269" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D269" s="3">
-        <v>46073.5838834375</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E269" s="2">
-        <v>82246</v>
+        <v>82229</v>
       </c>
       <c r="F269" s="3">
         <v>46073</v>
@@ -7439,16 +7439,16 @@
         <v>24</v>
       </c>
       <c r="C270" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D270" s="3">
-        <v>46080.6289065162</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E270" s="2">
-        <v>82387</v>
+        <v>82246</v>
       </c>
       <c r="F270" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>9</v>
@@ -7465,16 +7465,16 @@
         <v>24</v>
       </c>
       <c r="C271" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D271" s="3">
-        <v>46093.4978086806</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E271" s="2">
-        <v>82590</v>
+        <v>82387</v>
       </c>
       <c r="F271" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>9</v>
@@ -7497,16 +7497,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E272" s="2">
-        <v>82591</v>
+        <v>82590</v>
       </c>
       <c r="F272" s="3">
         <v>46093</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="273">
@@ -7523,16 +7523,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E273" s="2">
-        <v>82592</v>
+        <v>82591</v>
       </c>
       <c r="F273" s="3">
         <v>46093</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="274">
@@ -7549,7 +7549,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E274" s="2">
-        <v>82593</v>
+        <v>82592</v>
       </c>
       <c r="F274" s="3">
         <v>46093</v>
@@ -7575,7 +7575,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E275" s="2">
-        <v>82600</v>
+        <v>82593</v>
       </c>
       <c r="F275" s="3">
         <v>46093</v>
@@ -7601,7 +7601,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E276" s="2">
-        <v>82603</v>
+        <v>82600</v>
       </c>
       <c r="F276" s="3">
         <v>46093</v>
@@ -7627,7 +7627,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E277" s="2">
-        <v>82604</v>
+        <v>82603</v>
       </c>
       <c r="F277" s="3">
         <v>46093</v>
@@ -7653,7 +7653,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E278" s="2">
-        <v>82605</v>
+        <v>82604</v>
       </c>
       <c r="F278" s="3">
         <v>46093</v>
@@ -7667,22 +7667,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="279">
       <c r="A279" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C279" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D279" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E279" s="2">
-        <v>81478</v>
+        <v>82605</v>
       </c>
       <c r="F279" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>9</v>
@@ -7705,7 +7705,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E280" s="2">
-        <v>81479</v>
+        <v>81478</v>
       </c>
       <c r="F280" s="3">
         <v>46029</v>
@@ -7731,7 +7731,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E281" s="2">
-        <v>81480</v>
+        <v>81479</v>
       </c>
       <c r="F281" s="3">
         <v>46029</v>
@@ -7757,7 +7757,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E282" s="2">
-        <v>81497</v>
+        <v>81480</v>
       </c>
       <c r="F282" s="3">
         <v>46029</v>
@@ -7783,7 +7783,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E283" s="2">
-        <v>81498</v>
+        <v>81497</v>
       </c>
       <c r="F283" s="3">
         <v>46029</v>
@@ -7809,7 +7809,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E284" s="2">
-        <v>81499</v>
+        <v>81498</v>
       </c>
       <c r="F284" s="3">
         <v>46029</v>
@@ -7835,7 +7835,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E285" s="2">
-        <v>81500</v>
+        <v>81499</v>
       </c>
       <c r="F285" s="3">
         <v>46029</v>
@@ -7855,16 +7855,16 @@
         <v>24</v>
       </c>
       <c r="C286" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D286" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E286" s="2">
-        <v>81878</v>
+        <v>81500</v>
       </c>
       <c r="F286" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>9</v>
@@ -7887,7 +7887,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E287" s="2">
-        <v>81879</v>
+        <v>81878</v>
       </c>
       <c r="F287" s="3">
         <v>46049</v>
@@ -7913,10 +7913,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E288" s="2">
-        <v>81885</v>
+        <v>81879</v>
       </c>
       <c r="F288" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>9</v>
@@ -7939,7 +7939,7 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E289" s="2">
-        <v>81886</v>
+        <v>81885</v>
       </c>
       <c r="F289" s="3">
         <v>46050</v>
@@ -7959,16 +7959,16 @@
         <v>24</v>
       </c>
       <c r="C290" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D290" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E290" s="2">
-        <v>82068</v>
+        <v>81886</v>
       </c>
       <c r="F290" s="3">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>9</v>
@@ -7991,10 +7991,10 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E291" s="2">
-        <v>82072</v>
+        <v>82068</v>
       </c>
       <c r="F291" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>9</v>
@@ -8017,7 +8017,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E292" s="2">
-        <v>82076</v>
+        <v>82072</v>
       </c>
       <c r="F292" s="3">
         <v>46063</v>
@@ -8043,7 +8043,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E293" s="2">
-        <v>82078</v>
+        <v>82076</v>
       </c>
       <c r="F293" s="3">
         <v>46063</v>
@@ -8063,16 +8063,16 @@
         <v>24</v>
       </c>
       <c r="C294" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D294" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E294" s="2">
-        <v>82287</v>
+        <v>82078</v>
       </c>
       <c r="F294" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>9</v>
@@ -8095,7 +8095,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E295" s="2">
-        <v>82288</v>
+        <v>82287</v>
       </c>
       <c r="F295" s="3">
         <v>46077</v>
@@ -8121,10 +8121,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E296" s="2">
-        <v>82298</v>
+        <v>82288</v>
       </c>
       <c r="F296" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>9</v>
@@ -8147,7 +8147,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E297" s="2">
-        <v>82301</v>
+        <v>82298</v>
       </c>
       <c r="F297" s="3">
         <v>46078</v>
@@ -8173,7 +8173,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E298" s="2">
-        <v>82304</v>
+        <v>82301</v>
       </c>
       <c r="F298" s="3">
         <v>46078</v>
@@ -8199,7 +8199,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E299" s="2">
-        <v>82308</v>
+        <v>82304</v>
       </c>
       <c r="F299" s="3">
         <v>46078</v>
@@ -8219,16 +8219,16 @@
         <v>24</v>
       </c>
       <c r="C300" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D300" s="3">
-        <v>46080.628344919</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E300" s="2">
-        <v>82373</v>
+        <v>82308</v>
       </c>
       <c r="F300" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>9</v>
@@ -8245,16 +8245,16 @@
         <v>24</v>
       </c>
       <c r="C301" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D301" s="3">
-        <v>46085.6581644213</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E301" s="2">
-        <v>82445</v>
+        <v>82373</v>
       </c>
       <c r="F301" s="3">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="G301" s="1" t="s">
         <v>9</v>
@@ -8277,7 +8277,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E302" s="2">
-        <v>82447</v>
+        <v>82445</v>
       </c>
       <c r="F302" s="3">
         <v>46085</v>
@@ -8303,10 +8303,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E303" s="2">
-        <v>82453</v>
+        <v>82447</v>
       </c>
       <c r="F303" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>9</v>
@@ -8329,7 +8329,7 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E304" s="2">
-        <v>82468</v>
+        <v>82453</v>
       </c>
       <c r="F304" s="3">
         <v>46086</v>
@@ -8349,16 +8349,16 @@
         <v>24</v>
       </c>
       <c r="C305" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D305" s="3">
-        <v>46098.6669450579</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E305" s="2">
-        <v>82697</v>
+        <v>82468</v>
       </c>
       <c r="F305" s="3">
-        <v>46098</v>
+        <v>46086</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>9</v>
@@ -8381,10 +8381,10 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E306" s="2">
-        <v>82706</v>
+        <v>82697</v>
       </c>
       <c r="F306" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>9</v>
@@ -8407,7 +8407,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E307" s="2">
-        <v>82707</v>
+        <v>82706</v>
       </c>
       <c r="F307" s="3">
         <v>46099</v>
@@ -8433,7 +8433,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E308" s="2">
-        <v>82708</v>
+        <v>82707</v>
       </c>
       <c r="F308" s="3">
         <v>46099</v>
@@ -8459,7 +8459,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E309" s="2">
-        <v>82709</v>
+        <v>82708</v>
       </c>
       <c r="F309" s="3">
         <v>46099</v>
@@ -8485,7 +8485,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E310" s="2">
-        <v>82712</v>
+        <v>82709</v>
       </c>
       <c r="F310" s="3">
         <v>46099</v>
@@ -8511,7 +8511,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E311" s="2">
-        <v>82713</v>
+        <v>82712</v>
       </c>
       <c r="F311" s="3">
         <v>46099</v>
@@ -8525,22 +8525,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="312">
       <c r="A312" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C312" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D312" s="3">
-        <v>46029.6400966782</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E312" s="2">
-        <v>81506</v>
+        <v>82713</v>
       </c>
       <c r="F312" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>9</v>
@@ -8551,28 +8551,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="313">
       <c r="A313" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B313" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C313" s="2">
+        <v>33</v>
+      </c>
+      <c r="D313" s="3">
+        <v>46101.4050215162</v>
+      </c>
+      <c r="E313" s="2">
+        <v>82756</v>
+      </c>
+      <c r="F313" s="3">
+        <v>46101</v>
+      </c>
+      <c r="G313" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C313" s="2">
-        <v>22</v>
-      </c>
-      <c r="D313" s="3">
-        <v>46029.6400966782</v>
-      </c>
-      <c r="E313" s="2">
-        <v>81507</v>
-      </c>
-      <c r="F313" s="3">
-        <v>46029</v>
-      </c>
-      <c r="G313" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H313" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="314">
@@ -8580,7 +8580,7 @@
         <v>2509</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C314" s="2">
         <v>22</v>
@@ -8589,10 +8589,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E314" s="2">
-        <v>81524</v>
+        <v>81506</v>
       </c>
       <c r="F314" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>9</v>
@@ -8606,7 +8606,7 @@
         <v>2509</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C315" s="2">
         <v>22</v>
@@ -8615,10 +8615,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E315" s="2">
-        <v>81525</v>
+        <v>81507</v>
       </c>
       <c r="F315" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>9</v>
@@ -8632,7 +8632,7 @@
         <v>2509</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C316" s="2">
         <v>22</v>
@@ -8641,7 +8641,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E316" s="2">
-        <v>81526</v>
+        <v>81524</v>
       </c>
       <c r="F316" s="3">
         <v>46030</v>
@@ -8658,19 +8658,19 @@
         <v>2509</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C317" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D317" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E317" s="2">
-        <v>81640</v>
+        <v>81525</v>
       </c>
       <c r="F317" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>9</v>
@@ -8684,19 +8684,19 @@
         <v>2509</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C318" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D318" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E318" s="2">
-        <v>81642</v>
+        <v>81526</v>
       </c>
       <c r="F318" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>9</v>
@@ -8710,7 +8710,7 @@
         <v>2509</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C319" s="2">
         <v>23</v>
@@ -8719,7 +8719,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E319" s="2">
-        <v>81643</v>
+        <v>81640</v>
       </c>
       <c r="F319" s="3">
         <v>46036</v>
@@ -8736,19 +8736,19 @@
         <v>2509</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C320" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D320" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E320" s="2">
-        <v>81835</v>
+        <v>81642</v>
       </c>
       <c r="F320" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>9</v>
@@ -8762,19 +8762,19 @@
         <v>2509</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C321" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D321" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E321" s="2">
-        <v>81836</v>
+        <v>81643</v>
       </c>
       <c r="F321" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>9</v>
@@ -8788,7 +8788,7 @@
         <v>2509</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C322" s="2">
         <v>24</v>
@@ -8797,7 +8797,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E322" s="2">
-        <v>81837</v>
+        <v>81835</v>
       </c>
       <c r="F322" s="3">
         <v>46045</v>
@@ -8814,19 +8814,19 @@
         <v>2509</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C323" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D323" s="3">
-        <v>46051.6376515278</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E323" s="2">
-        <v>81931</v>
+        <v>81836</v>
       </c>
       <c r="F323" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>9</v>
@@ -8840,19 +8840,19 @@
         <v>2509</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C324" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D324" s="3">
-        <v>46056.7115158912</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E324" s="2">
-        <v>81978</v>
+        <v>81837</v>
       </c>
       <c r="F324" s="3">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>9</v>
@@ -8866,19 +8866,19 @@
         <v>2509</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C325" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D325" s="3">
-        <v>46057.6911087731</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E325" s="2">
-        <v>81994</v>
+        <v>81931</v>
       </c>
       <c r="F325" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>9</v>
@@ -8892,16 +8892,16 @@
         <v>2509</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C326" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D326" s="3">
-        <v>46057.6911087731</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E326" s="2">
-        <v>81995</v>
+        <v>81978</v>
       </c>
       <c r="F326" s="3">
         <v>46057</v>
@@ -8918,7 +8918,7 @@
         <v>2509</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C327" s="2">
         <v>27</v>
@@ -8927,7 +8927,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E327" s="2">
-        <v>81999</v>
+        <v>81994</v>
       </c>
       <c r="F327" s="3">
         <v>46057</v>
@@ -8944,7 +8944,7 @@
         <v>2509</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C328" s="2">
         <v>27</v>
@@ -8953,10 +8953,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E328" s="2">
-        <v>82008</v>
+        <v>81995</v>
       </c>
       <c r="F328" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>9</v>
@@ -8970,7 +8970,7 @@
         <v>2509</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C329" s="2">
         <v>27</v>
@@ -8979,10 +8979,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E329" s="2">
-        <v>82011</v>
+        <v>81999</v>
       </c>
       <c r="F329" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>9</v>
@@ -8996,7 +8996,7 @@
         <v>2509</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C330" s="2">
         <v>27</v>
@@ -9005,7 +9005,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E330" s="2">
-        <v>82012</v>
+        <v>82008</v>
       </c>
       <c r="F330" s="3">
         <v>46058</v>
@@ -9022,7 +9022,7 @@
         <v>2509</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C331" s="2">
         <v>27</v>
@@ -9031,7 +9031,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E331" s="2">
-        <v>82013</v>
+        <v>82011</v>
       </c>
       <c r="F331" s="3">
         <v>46058</v>
@@ -9048,7 +9048,7 @@
         <v>2509</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C332" s="2">
         <v>27</v>
@@ -9057,7 +9057,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E332" s="2">
-        <v>82014</v>
+        <v>82012</v>
       </c>
       <c r="F332" s="3">
         <v>46058</v>
@@ -9074,25 +9074,25 @@
         <v>2509</v>
       </c>
       <c r="B333" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C333" s="2">
         <v>27</v>
       </c>
-      <c r="C333" s="2">
-        <v>28</v>
-      </c>
       <c r="D333" s="3">
-        <v>46058.6604985417</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E333" s="2">
-        <v>82046</v>
+        <v>82013</v>
       </c>
       <c r="F333" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="334">
@@ -9100,19 +9100,19 @@
         <v>2509</v>
       </c>
       <c r="B334" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C334" s="2">
         <v>27</v>
       </c>
-      <c r="C334" s="2">
-        <v>29</v>
-      </c>
       <c r="D334" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E334" s="2">
-        <v>82217</v>
+        <v>82014</v>
       </c>
       <c r="F334" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>9</v>
@@ -9126,25 +9126,25 @@
         <v>2509</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C335" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D335" s="3">
-        <v>46072.738871875</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E335" s="2">
-        <v>82218</v>
+        <v>82046</v>
       </c>
       <c r="F335" s="3">
-        <v>46072</v>
+        <v>46059</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="336">
@@ -9152,7 +9152,7 @@
         <v>2509</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C336" s="2">
         <v>29</v>
@@ -9161,10 +9161,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E336" s="2">
-        <v>82234</v>
+        <v>82217</v>
       </c>
       <c r="F336" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>9</v>
@@ -9178,7 +9178,7 @@
         <v>2509</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C337" s="2">
         <v>29</v>
@@ -9187,10 +9187,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E337" s="2">
-        <v>82238</v>
+        <v>82218</v>
       </c>
       <c r="F337" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>9</v>
@@ -9204,7 +9204,7 @@
         <v>2509</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C338" s="2">
         <v>29</v>
@@ -9213,7 +9213,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E338" s="2">
-        <v>82245</v>
+        <v>82234</v>
       </c>
       <c r="F338" s="3">
         <v>46073</v>
@@ -9230,19 +9230,19 @@
         <v>2509</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C339" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D339" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E339" s="2">
-        <v>82257</v>
+        <v>82238</v>
       </c>
       <c r="F339" s="3">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>9</v>
@@ -9256,19 +9256,19 @@
         <v>2509</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C340" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D340" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E340" s="2">
-        <v>82276</v>
+        <v>82245</v>
       </c>
       <c r="F340" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>9</v>
@@ -9282,7 +9282,7 @@
         <v>2509</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C341" s="2">
         <v>30</v>
@@ -9291,10 +9291,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E341" s="2">
-        <v>82277</v>
+        <v>82257</v>
       </c>
       <c r="F341" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>9</v>
@@ -9308,7 +9308,7 @@
         <v>2509</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C342" s="2">
         <v>30</v>
@@ -9317,10 +9317,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E342" s="2">
-        <v>82293</v>
+        <v>82276</v>
       </c>
       <c r="F342" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>9</v>
@@ -9334,16 +9334,16 @@
         <v>2509</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C343" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D343" s="3">
-        <v>46077.4356327431</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E343" s="2">
-        <v>82269</v>
+        <v>82277</v>
       </c>
       <c r="F343" s="3">
         <v>46077</v>
@@ -9360,19 +9360,19 @@
         <v>2509</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C344" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D344" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E344" s="2">
-        <v>82419</v>
+        <v>82293</v>
       </c>
       <c r="F344" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>9</v>
@@ -9386,19 +9386,19 @@
         <v>2509</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C345" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D345" s="3">
-        <v>46084.7378501505</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E345" s="2">
-        <v>82420</v>
+        <v>82269</v>
       </c>
       <c r="F345" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>9</v>
@@ -9412,7 +9412,7 @@
         <v>2509</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C346" s="2">
         <v>32</v>
@@ -9421,7 +9421,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E346" s="2">
-        <v>82421</v>
+        <v>82419</v>
       </c>
       <c r="F346" s="3">
         <v>46084</v>
@@ -9438,7 +9438,7 @@
         <v>2509</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C347" s="2">
         <v>32</v>
@@ -9447,7 +9447,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E347" s="2">
-        <v>82422</v>
+        <v>82420</v>
       </c>
       <c r="F347" s="3">
         <v>46084</v>
@@ -9464,7 +9464,7 @@
         <v>2509</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C348" s="2">
         <v>32</v>
@@ -9473,7 +9473,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E348" s="2">
-        <v>82423</v>
+        <v>82421</v>
       </c>
       <c r="F348" s="3">
         <v>46084</v>
@@ -9490,7 +9490,7 @@
         <v>2509</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C349" s="2">
         <v>32</v>
@@ -9499,10 +9499,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E349" s="2">
-        <v>82433</v>
+        <v>82422</v>
       </c>
       <c r="F349" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>9</v>
@@ -9516,7 +9516,7 @@
         <v>2509</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C350" s="2">
         <v>32</v>
@@ -9525,10 +9525,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E350" s="2">
-        <v>82434</v>
+        <v>82423</v>
       </c>
       <c r="F350" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>9</v>
@@ -9542,7 +9542,7 @@
         <v>2509</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C351" s="2">
         <v>32</v>
@@ -9551,10 +9551,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E351" s="2">
-        <v>82464</v>
+        <v>82433</v>
       </c>
       <c r="F351" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G351" s="1" t="s">
         <v>9</v>
@@ -9568,7 +9568,7 @@
         <v>2509</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C352" s="2">
         <v>32</v>
@@ -9577,10 +9577,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E352" s="2">
-        <v>82472</v>
+        <v>82434</v>
       </c>
       <c r="F352" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>9</v>
@@ -9594,19 +9594,19 @@
         <v>2509</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C353" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D353" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E353" s="2">
-        <v>82578</v>
+        <v>82464</v>
       </c>
       <c r="F353" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>9</v>
@@ -9620,19 +9620,19 @@
         <v>2509</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C354" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D354" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E354" s="2">
-        <v>82579</v>
+        <v>82472</v>
       </c>
       <c r="F354" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>9</v>
@@ -9646,7 +9646,7 @@
         <v>2509</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C355" s="2">
         <v>33</v>
@@ -9655,7 +9655,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E355" s="2">
-        <v>82580</v>
+        <v>82578</v>
       </c>
       <c r="F355" s="3">
         <v>46093</v>
@@ -9672,7 +9672,7 @@
         <v>2509</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C356" s="2">
         <v>33</v>
@@ -9681,16 +9681,16 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E356" s="2">
-        <v>82599</v>
+        <v>82579</v>
       </c>
       <c r="F356" s="3">
         <v>46093</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H356" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="357">
@@ -9698,7 +9698,7 @@
         <v>2509</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C357" s="2">
         <v>33</v>
@@ -9707,7 +9707,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E357" s="2">
-        <v>82602</v>
+        <v>82580</v>
       </c>
       <c r="F357" s="3">
         <v>46093</v>
@@ -9724,45 +9724,45 @@
         <v>2509</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C358" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D358" s="3">
-        <v>46093.4957757986</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E358" s="2">
-        <v>82584</v>
+        <v>82599</v>
       </c>
       <c r="F358" s="3">
         <v>46093</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H358" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="359">
       <c r="A359" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C359" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D359" s="3">
-        <v>46027.6953206134</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E359" s="2">
-        <v>81464</v>
+        <v>82602</v>
       </c>
       <c r="F359" s="3">
-        <v>46027</v>
+        <v>46093</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>9</v>
@@ -9773,22 +9773,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="360">
       <c r="A360" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C360" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D360" s="3">
-        <v>46027.6953206134</v>
+        <v>46093.4957757986</v>
       </c>
       <c r="E360" s="2">
-        <v>81472</v>
+        <v>82584</v>
       </c>
       <c r="F360" s="3">
-        <v>46027</v>
+        <v>46093</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>9</v>
@@ -9799,106 +9799,106 @@
     </row>
     <row ht="12.75" customHeight="1" r="361">
       <c r="A361" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C361" s="2">
+        <v>35</v>
+      </c>
+      <c r="D361" s="3">
+        <v>46100.6528700694</v>
+      </c>
+      <c r="E361" s="2">
+        <v>82745</v>
+      </c>
+      <c r="F361" s="3">
+        <v>46100</v>
+      </c>
+      <c r="G361" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D361" s="3">
-        <v>46027.6953206134</v>
-      </c>
-      <c r="E361" s="2">
-        <v>81492</v>
-      </c>
-      <c r="F361" s="3">
-        <v>46029</v>
-      </c>
-      <c r="G361" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H361" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="362">
       <c r="A362" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C362" s="2">
+        <v>35</v>
+      </c>
+      <c r="D362" s="3">
+        <v>46100.6528700694</v>
+      </c>
+      <c r="E362" s="2">
+        <v>82746</v>
+      </c>
+      <c r="F362" s="3">
+        <v>46100</v>
+      </c>
+      <c r="G362" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D362" s="3">
-        <v>46027.6953206134</v>
-      </c>
-      <c r="E362" s="2">
-        <v>81493</v>
-      </c>
-      <c r="F362" s="3">
-        <v>46029</v>
-      </c>
-      <c r="G362" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H362" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="363">
       <c r="A363" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C363" s="2">
+        <v>35</v>
+      </c>
+      <c r="D363" s="3">
+        <v>46100.6528700694</v>
+      </c>
+      <c r="E363" s="2">
+        <v>82747</v>
+      </c>
+      <c r="F363" s="3">
+        <v>46100</v>
+      </c>
+      <c r="G363" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D363" s="3">
-        <v>46027.6953206134</v>
-      </c>
-      <c r="E363" s="2">
-        <v>81568</v>
-      </c>
-      <c r="F363" s="3">
-        <v>46031</v>
-      </c>
-      <c r="G363" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H363" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="364">
       <c r="A364" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C364" s="2">
+        <v>35</v>
+      </c>
+      <c r="D364" s="3">
+        <v>46100.6528700694</v>
+      </c>
+      <c r="E364" s="2">
+        <v>82748</v>
+      </c>
+      <c r="F364" s="3">
+        <v>46100</v>
+      </c>
+      <c r="G364" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D364" s="3">
-        <v>46027.6953206134</v>
-      </c>
-      <c r="E364" s="2">
-        <v>81601</v>
-      </c>
-      <c r="F364" s="3">
-        <v>46034</v>
-      </c>
-      <c r="G364" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H364" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="365">
@@ -9915,10 +9915,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E365" s="2">
-        <v>81602</v>
+        <v>81464</v>
       </c>
       <c r="F365" s="3">
-        <v>46034</v>
+        <v>46027</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>9</v>
@@ -9935,16 +9935,16 @@
         <v>30</v>
       </c>
       <c r="C366" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D366" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E366" s="2">
-        <v>81645</v>
+        <v>81472</v>
       </c>
       <c r="F366" s="3">
-        <v>46036</v>
+        <v>46027</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>9</v>
@@ -9961,16 +9961,16 @@
         <v>30</v>
       </c>
       <c r="C367" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D367" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E367" s="2">
-        <v>81646</v>
+        <v>81492</v>
       </c>
       <c r="F367" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>9</v>
@@ -9987,16 +9987,16 @@
         <v>30</v>
       </c>
       <c r="C368" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D368" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E368" s="2">
-        <v>81653</v>
+        <v>81493</v>
       </c>
       <c r="F368" s="3">
-        <v>46037</v>
+        <v>46029</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>9</v>
@@ -10013,16 +10013,16 @@
         <v>30</v>
       </c>
       <c r="C369" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D369" s="3">
-        <v>46037.4325152662</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E369" s="2">
-        <v>81662</v>
+        <v>81568</v>
       </c>
       <c r="F369" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>9</v>
@@ -10039,16 +10039,16 @@
         <v>30</v>
       </c>
       <c r="C370" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D370" s="3">
-        <v>46044.4079891435</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E370" s="2">
-        <v>81780</v>
+        <v>81601</v>
       </c>
       <c r="F370" s="3">
-        <v>46044</v>
+        <v>46034</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>9</v>
@@ -10065,16 +10065,16 @@
         <v>30</v>
       </c>
       <c r="C371" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D371" s="3">
-        <v>46044.4079891435</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E371" s="2">
-        <v>81781</v>
+        <v>81602</v>
       </c>
       <c r="F371" s="3">
-        <v>46044</v>
+        <v>46034</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>9</v>
@@ -10091,16 +10091,16 @@
         <v>30</v>
       </c>
       <c r="C372" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D372" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E372" s="2">
-        <v>81782</v>
+        <v>81645</v>
       </c>
       <c r="F372" s="3">
-        <v>46044</v>
+        <v>46036</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>9</v>
@@ -10117,16 +10117,16 @@
         <v>30</v>
       </c>
       <c r="C373" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D373" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E373" s="2">
-        <v>81784</v>
+        <v>81646</v>
       </c>
       <c r="F373" s="3">
-        <v>46044</v>
+        <v>46036</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>9</v>
@@ -10143,16 +10143,16 @@
         <v>30</v>
       </c>
       <c r="C374" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D374" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E374" s="2">
-        <v>81785</v>
+        <v>81653</v>
       </c>
       <c r="F374" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>9</v>
@@ -10169,16 +10169,16 @@
         <v>30</v>
       </c>
       <c r="C375" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D375" s="3">
-        <v>46044.4079891435</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E375" s="2">
-        <v>81801</v>
+        <v>81662</v>
       </c>
       <c r="F375" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>9</v>
@@ -10195,16 +10195,16 @@
         <v>30</v>
       </c>
       <c r="C376" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D376" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E376" s="2">
-        <v>81860</v>
+        <v>81780</v>
       </c>
       <c r="F376" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>9</v>
@@ -10221,16 +10221,16 @@
         <v>30</v>
       </c>
       <c r="C377" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D377" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E377" s="2">
-        <v>81873</v>
+        <v>81781</v>
       </c>
       <c r="F377" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>9</v>
@@ -10247,16 +10247,16 @@
         <v>30</v>
       </c>
       <c r="C378" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D378" s="3">
-        <v>46049.4883916667</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E378" s="2">
-        <v>81865</v>
+        <v>81782</v>
       </c>
       <c r="F378" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>9</v>
@@ -10273,16 +10273,16 @@
         <v>30</v>
       </c>
       <c r="C379" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D379" s="3">
-        <v>46049.4883916667</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E379" s="2">
-        <v>81870</v>
+        <v>81784</v>
       </c>
       <c r="F379" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>9</v>
@@ -10299,16 +10299,16 @@
         <v>30</v>
       </c>
       <c r="C380" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D380" s="3">
-        <v>46049.4883916667</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E380" s="2">
-        <v>81872</v>
+        <v>81785</v>
       </c>
       <c r="F380" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>9</v>
@@ -10325,16 +10325,16 @@
         <v>30</v>
       </c>
       <c r="C381" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D381" s="3">
-        <v>46049.4883916667</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E381" s="2">
-        <v>81896</v>
+        <v>81801</v>
       </c>
       <c r="F381" s="3">
-        <v>46050</v>
+        <v>46044</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>9</v>
@@ -10351,16 +10351,16 @@
         <v>30</v>
       </c>
       <c r="C382" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D382" s="3">
-        <v>46051.4046937153</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E382" s="2">
-        <v>81923</v>
+        <v>81860</v>
       </c>
       <c r="F382" s="3">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>9</v>
@@ -10377,16 +10377,16 @@
         <v>30</v>
       </c>
       <c r="C383" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D383" s="3">
-        <v>46057.6959672917</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E383" s="2">
-        <v>81998</v>
+        <v>81873</v>
       </c>
       <c r="F383" s="3">
-        <v>46057</v>
+        <v>46049</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>9</v>
@@ -10403,16 +10403,16 @@
         <v>30</v>
       </c>
       <c r="C384" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D384" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E384" s="2">
-        <v>82002</v>
+        <v>81865</v>
       </c>
       <c r="F384" s="3">
-        <v>46057</v>
+        <v>46049</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>9</v>
@@ -10429,16 +10429,16 @@
         <v>30</v>
       </c>
       <c r="C385" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D385" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E385" s="2">
-        <v>82005</v>
+        <v>81870</v>
       </c>
       <c r="F385" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>9</v>
@@ -10455,16 +10455,16 @@
         <v>30</v>
       </c>
       <c r="C386" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D386" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E386" s="2">
-        <v>82007</v>
+        <v>81872</v>
       </c>
       <c r="F386" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>9</v>
@@ -10481,16 +10481,16 @@
         <v>30</v>
       </c>
       <c r="C387" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D387" s="3">
-        <v>46063.5942651852</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E387" s="2">
-        <v>82005</v>
+        <v>81896</v>
       </c>
       <c r="F387" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>9</v>
@@ -10507,16 +10507,16 @@
         <v>30</v>
       </c>
       <c r="C388" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D388" s="3">
-        <v>46063.5942651852</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E388" s="2">
-        <v>82075</v>
+        <v>81923</v>
       </c>
       <c r="F388" s="3">
-        <v>46063</v>
+        <v>46051</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>9</v>
@@ -10533,16 +10533,16 @@
         <v>30</v>
       </c>
       <c r="C389" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D389" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E389" s="2">
-        <v>82077</v>
+        <v>81998</v>
       </c>
       <c r="F389" s="3">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>9</v>
@@ -10559,16 +10559,16 @@
         <v>30</v>
       </c>
       <c r="C390" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D390" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E390" s="2">
-        <v>82099</v>
+        <v>82002</v>
       </c>
       <c r="F390" s="3">
-        <v>46064</v>
+        <v>46057</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>9</v>
@@ -10585,16 +10585,16 @@
         <v>30</v>
       </c>
       <c r="C391" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D391" s="3">
-        <v>46072.7460071991</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E391" s="2">
-        <v>82219</v>
+        <v>82005</v>
       </c>
       <c r="F391" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>9</v>
@@ -10611,16 +10611,16 @@
         <v>30</v>
       </c>
       <c r="C392" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D392" s="3">
-        <v>46072.7460071991</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E392" s="2">
-        <v>82230</v>
+        <v>82007</v>
       </c>
       <c r="F392" s="3">
-        <v>46073</v>
+        <v>46058</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>9</v>
@@ -10637,16 +10637,16 @@
         <v>30</v>
       </c>
       <c r="C393" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D393" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E393" s="2">
-        <v>82231</v>
+        <v>82005</v>
       </c>
       <c r="F393" s="3">
-        <v>46073</v>
+        <v>46058</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>9</v>
@@ -10663,16 +10663,16 @@
         <v>30</v>
       </c>
       <c r="C394" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D394" s="3">
-        <v>46079.5787315972</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E394" s="2">
-        <v>82388</v>
+        <v>82075</v>
       </c>
       <c r="F394" s="3">
-        <v>46083</v>
+        <v>46063</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>9</v>
@@ -10689,16 +10689,16 @@
         <v>30</v>
       </c>
       <c r="C395" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D395" s="3">
-        <v>46079.5787315972</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E395" s="2">
-        <v>82389</v>
+        <v>82077</v>
       </c>
       <c r="F395" s="3">
-        <v>46083</v>
+        <v>46063</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>9</v>
@@ -10715,16 +10715,16 @@
         <v>30</v>
       </c>
       <c r="C396" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D396" s="3">
-        <v>46079.5787315972</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E396" s="2">
-        <v>82396</v>
+        <v>82099</v>
       </c>
       <c r="F396" s="3">
-        <v>46083</v>
+        <v>46064</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>9</v>
@@ -10741,16 +10741,16 @@
         <v>30</v>
       </c>
       <c r="C397" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D397" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E397" s="2">
-        <v>82397</v>
+        <v>82219</v>
       </c>
       <c r="F397" s="3">
-        <v>46083</v>
+        <v>46072</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>9</v>
@@ -10767,16 +10767,16 @@
         <v>30</v>
       </c>
       <c r="C398" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D398" s="3">
-        <v>46085.6249659838</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E398" s="2">
-        <v>82435</v>
+        <v>82230</v>
       </c>
       <c r="F398" s="3">
-        <v>46085</v>
+        <v>46073</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>9</v>
@@ -10793,16 +10793,16 @@
         <v>30</v>
       </c>
       <c r="C399" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D399" s="3">
-        <v>46091.449444456</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E399" s="2">
-        <v>82506</v>
+        <v>82231</v>
       </c>
       <c r="F399" s="3">
-        <v>46091</v>
+        <v>46073</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>9</v>
@@ -10819,16 +10819,16 @@
         <v>30</v>
       </c>
       <c r="C400" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D400" s="3">
-        <v>46091.4795702315</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E400" s="2">
-        <v>82509</v>
+        <v>82388</v>
       </c>
       <c r="F400" s="3">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>9</v>
@@ -10845,16 +10845,16 @@
         <v>30</v>
       </c>
       <c r="C401" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D401" s="3">
-        <v>46093.4969972338</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E401" s="2">
-        <v>82589</v>
+        <v>82389</v>
       </c>
       <c r="F401" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10865,22 +10865,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="402">
       <c r="A402" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C402" s="2">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D402" s="3">
-        <v>46029.3821391551</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E402" s="2">
-        <v>81477</v>
+        <v>82396</v>
       </c>
       <c r="F402" s="3">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10891,22 +10891,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="403">
       <c r="A403" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C403" s="2">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D403" s="3">
-        <v>46030.4142968056</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E403" s="2">
-        <v>81532</v>
+        <v>82397</v>
       </c>
       <c r="F403" s="3">
-        <v>46030</v>
+        <v>46083</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10917,22 +10917,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="404">
       <c r="A404" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C404" s="2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D404" s="3">
-        <v>46030.4142968056</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E404" s="2">
-        <v>81534</v>
+        <v>82435</v>
       </c>
       <c r="F404" s="3">
-        <v>46030</v>
+        <v>46085</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>9</v>
@@ -10943,22 +10943,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="405">
       <c r="A405" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C405" s="2">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D405" s="3">
-        <v>46030.4142968056</v>
+        <v>46091.449444456</v>
       </c>
       <c r="E405" s="2">
-        <v>81535</v>
+        <v>82506</v>
       </c>
       <c r="F405" s="3">
-        <v>46030</v>
+        <v>46091</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>9</v>
@@ -10969,22 +10969,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="406">
       <c r="A406" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C406" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D406" s="3">
-        <v>46030.4142968056</v>
+        <v>46091.4795702315</v>
       </c>
       <c r="E406" s="2">
-        <v>81550</v>
+        <v>82509</v>
       </c>
       <c r="F406" s="3">
-        <v>46030</v>
+        <v>46091</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>9</v>
@@ -10995,22 +10995,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="407">
       <c r="A407" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C407" s="2">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D407" s="3">
-        <v>46030.4142968056</v>
+        <v>46093.4969972338</v>
       </c>
       <c r="E407" s="2">
-        <v>81553</v>
+        <v>82589</v>
       </c>
       <c r="F407" s="3">
-        <v>46030</v>
+        <v>46093</v>
       </c>
       <c r="G407" s="1" t="s">
         <v>9</v>
@@ -11027,16 +11027,16 @@
         <v>31</v>
       </c>
       <c r="C408" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D408" s="3">
-        <v>46030.4142968056</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E408" s="2">
-        <v>81554</v>
+        <v>81477</v>
       </c>
       <c r="F408" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>9</v>
@@ -11059,7 +11059,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E409" s="2">
-        <v>81557</v>
+        <v>81532</v>
       </c>
       <c r="F409" s="3">
         <v>46030</v>
@@ -11085,10 +11085,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E410" s="2">
-        <v>81588</v>
+        <v>81534</v>
       </c>
       <c r="F410" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11105,16 +11105,16 @@
         <v>31</v>
       </c>
       <c r="C411" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D411" s="3">
-        <v>46038.593985081</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E411" s="2">
-        <v>81692</v>
+        <v>81535</v>
       </c>
       <c r="F411" s="3">
-        <v>46038</v>
+        <v>46030</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>9</v>
@@ -11131,16 +11131,16 @@
         <v>31</v>
       </c>
       <c r="C412" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D412" s="3">
-        <v>46044.46462125</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E412" s="2">
-        <v>81786</v>
+        <v>81550</v>
       </c>
       <c r="F412" s="3">
-        <v>46044</v>
+        <v>46030</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11157,16 +11157,16 @@
         <v>31</v>
       </c>
       <c r="C413" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D413" s="3">
-        <v>46044.6362443171</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E413" s="2">
-        <v>81844</v>
+        <v>81553</v>
       </c>
       <c r="F413" s="3">
-        <v>46045</v>
+        <v>46030</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>9</v>
@@ -11183,16 +11183,16 @@
         <v>31</v>
       </c>
       <c r="C414" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D414" s="3">
-        <v>46062.717040544</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E414" s="2">
-        <v>82065</v>
+        <v>81554</v>
       </c>
       <c r="F414" s="3">
-        <v>46062</v>
+        <v>46030</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>9</v>
@@ -11209,16 +11209,16 @@
         <v>31</v>
       </c>
       <c r="C415" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D415" s="3">
-        <v>46062.717040544</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E415" s="2">
-        <v>82066</v>
+        <v>81557</v>
       </c>
       <c r="F415" s="3">
-        <v>46062</v>
+        <v>46030</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>9</v>
@@ -11235,16 +11235,16 @@
         <v>31</v>
       </c>
       <c r="C416" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D416" s="3">
-        <v>46062.717040544</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E416" s="2">
-        <v>82067</v>
+        <v>81588</v>
       </c>
       <c r="F416" s="3">
-        <v>46062</v>
+        <v>46031</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>9</v>
@@ -11261,16 +11261,16 @@
         <v>31</v>
       </c>
       <c r="C417" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D417" s="3">
-        <v>46065.6300915625</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E417" s="2">
-        <v>82190</v>
+        <v>81692</v>
       </c>
       <c r="F417" s="3">
-        <v>46066</v>
+        <v>46038</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>9</v>
@@ -11287,16 +11287,16 @@
         <v>31</v>
       </c>
       <c r="C418" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D418" s="3">
-        <v>46065.6300915625</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E418" s="2">
-        <v>82197</v>
+        <v>81786</v>
       </c>
       <c r="F418" s="3">
-        <v>46066</v>
+        <v>46044</v>
       </c>
       <c r="G418" s="1" t="s">
         <v>9</v>
@@ -11313,16 +11313,16 @@
         <v>31</v>
       </c>
       <c r="C419" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D419" s="3">
-        <v>46077.5084780324</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E419" s="2">
-        <v>82270</v>
+        <v>81844</v>
       </c>
       <c r="F419" s="3">
-        <v>46077</v>
+        <v>46045</v>
       </c>
       <c r="G419" s="1" t="s">
         <v>9</v>
@@ -11339,16 +11339,16 @@
         <v>31</v>
       </c>
       <c r="C420" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D420" s="3">
-        <v>46077.721037037</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E420" s="2">
-        <v>82285</v>
+        <v>82065</v>
       </c>
       <c r="F420" s="3">
-        <v>46077</v>
+        <v>46062</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>9</v>
@@ -11365,16 +11365,16 @@
         <v>31</v>
       </c>
       <c r="C421" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D421" s="3">
-        <v>46083.6694849421</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E421" s="2">
-        <v>82417</v>
+        <v>82066</v>
       </c>
       <c r="F421" s="3">
-        <v>46084</v>
+        <v>46062</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>9</v>
@@ -11391,16 +11391,16 @@
         <v>31</v>
       </c>
       <c r="C422" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D422" s="3">
-        <v>46085.7157723032</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E422" s="2">
-        <v>82457</v>
+        <v>82067</v>
       </c>
       <c r="F422" s="3">
-        <v>46086</v>
+        <v>46062</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>9</v>
@@ -11417,16 +11417,16 @@
         <v>31</v>
       </c>
       <c r="C423" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D423" s="3">
-        <v>46099.6523956944</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E423" s="2">
-        <v>82724</v>
+        <v>82190</v>
       </c>
       <c r="F423" s="3">
-        <v>46099</v>
+        <v>46066</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>9</v>
@@ -11443,16 +11443,16 @@
         <v>31</v>
       </c>
       <c r="C424" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D424" s="3">
-        <v>46099.6523956944</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E424" s="2">
-        <v>82725</v>
+        <v>82197</v>
       </c>
       <c r="F424" s="3">
-        <v>46099</v>
+        <v>46066</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>9</v>
@@ -11469,16 +11469,16 @@
         <v>31</v>
       </c>
       <c r="C425" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D425" s="3">
-        <v>46099.6523956944</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E425" s="2">
-        <v>82727</v>
+        <v>82270</v>
       </c>
       <c r="F425" s="3">
-        <v>46100</v>
+        <v>46077</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>9</v>
@@ -11495,16 +11495,16 @@
         <v>31</v>
       </c>
       <c r="C426" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D426" s="3">
-        <v>46099.6523956944</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E426" s="2">
-        <v>82730</v>
+        <v>82285</v>
       </c>
       <c r="F426" s="3">
-        <v>46100</v>
+        <v>46077</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>9</v>
@@ -11515,22 +11515,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="427">
       <c r="A427" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C427" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D427" s="3">
-        <v>46029.381258831</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E427" s="2">
-        <v>81484</v>
+        <v>82417</v>
       </c>
       <c r="F427" s="3">
-        <v>46029</v>
+        <v>46084</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11541,22 +11541,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="428">
       <c r="A428" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C428" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D428" s="3">
-        <v>46029.381258831</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E428" s="2">
-        <v>81486</v>
+        <v>82457</v>
       </c>
       <c r="F428" s="3">
-        <v>46029</v>
+        <v>46086</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>9</v>
@@ -11567,22 +11567,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="429">
       <c r="A429" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C429" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D429" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E429" s="2">
-        <v>81487</v>
+        <v>82724</v>
       </c>
       <c r="F429" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>9</v>
@@ -11593,22 +11593,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="430">
       <c r="A430" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C430" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D430" s="3">
-        <v>46036.4048894097</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E430" s="2">
-        <v>81613</v>
+        <v>82725</v>
       </c>
       <c r="F430" s="3">
-        <v>46036</v>
+        <v>46099</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>9</v>
@@ -11619,22 +11619,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="431">
       <c r="A431" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C431" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D431" s="3">
-        <v>46036.4048894097</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E431" s="2">
-        <v>81614</v>
+        <v>82727</v>
       </c>
       <c r="F431" s="3">
-        <v>46036</v>
+        <v>46100</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>9</v>
@@ -11645,22 +11645,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="432">
       <c r="A432" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C432" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D432" s="3">
-        <v>46036.4048894097</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E432" s="2">
-        <v>81622</v>
+        <v>82730</v>
       </c>
       <c r="F432" s="3">
-        <v>46036</v>
+        <v>46100</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11677,16 +11677,16 @@
         <v>32</v>
       </c>
       <c r="C433" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D433" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E433" s="2">
-        <v>81632</v>
+        <v>81484</v>
       </c>
       <c r="F433" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11703,16 +11703,16 @@
         <v>32</v>
       </c>
       <c r="C434" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D434" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E434" s="2">
-        <v>81648</v>
+        <v>81486</v>
       </c>
       <c r="F434" s="3">
-        <v>46037</v>
+        <v>46029</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>9</v>
@@ -11729,16 +11729,16 @@
         <v>32</v>
       </c>
       <c r="C435" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D435" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E435" s="2">
-        <v>81664</v>
+        <v>81487</v>
       </c>
       <c r="F435" s="3">
-        <v>46037</v>
+        <v>46029</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>9</v>
@@ -11755,16 +11755,16 @@
         <v>32</v>
       </c>
       <c r="C436" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D436" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E436" s="2">
-        <v>81815</v>
+        <v>81613</v>
       </c>
       <c r="F436" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>9</v>
@@ -11781,16 +11781,16 @@
         <v>32</v>
       </c>
       <c r="C437" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D437" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E437" s="2">
-        <v>81816</v>
+        <v>81614</v>
       </c>
       <c r="F437" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>9</v>
@@ -11807,16 +11807,16 @@
         <v>32</v>
       </c>
       <c r="C438" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D438" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E438" s="2">
-        <v>81838</v>
+        <v>81622</v>
       </c>
       <c r="F438" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11833,16 +11833,16 @@
         <v>32</v>
       </c>
       <c r="C439" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D439" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E439" s="2">
-        <v>81840</v>
+        <v>81632</v>
       </c>
       <c r="F439" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11859,16 +11859,16 @@
         <v>32</v>
       </c>
       <c r="C440" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D440" s="3">
-        <v>46055.5991080671</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E440" s="2">
-        <v>81959</v>
+        <v>81648</v>
       </c>
       <c r="F440" s="3">
-        <v>46055</v>
+        <v>46037</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>9</v>
@@ -11885,16 +11885,16 @@
         <v>32</v>
       </c>
       <c r="C441" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D441" s="3">
-        <v>46055.5991080671</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E441" s="2">
-        <v>81960</v>
+        <v>81664</v>
       </c>
       <c r="F441" s="3">
-        <v>46055</v>
+        <v>46037</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11911,16 +11911,16 @@
         <v>32</v>
       </c>
       <c r="C442" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D442" s="3">
-        <v>46062.7151302546</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E442" s="2">
-        <v>82063</v>
+        <v>81815</v>
       </c>
       <c r="F442" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11937,16 +11937,16 @@
         <v>32</v>
       </c>
       <c r="C443" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D443" s="3">
-        <v>46062.7151302546</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E443" s="2">
-        <v>82064</v>
+        <v>81816</v>
       </c>
       <c r="F443" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11963,16 +11963,16 @@
         <v>32</v>
       </c>
       <c r="C444" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D444" s="3">
-        <v>46062.7151302546</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E444" s="2">
-        <v>82100</v>
+        <v>81838</v>
       </c>
       <c r="F444" s="3">
-        <v>46064</v>
+        <v>46045</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11989,16 +11989,16 @@
         <v>32</v>
       </c>
       <c r="C445" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D445" s="3">
-        <v>46072.7410579977</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E445" s="2">
-        <v>82333</v>
+        <v>81840</v>
       </c>
       <c r="F445" s="3">
-        <v>46079</v>
+        <v>46045</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>9</v>
@@ -12015,16 +12015,16 @@
         <v>32</v>
       </c>
       <c r="C446" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D446" s="3">
-        <v>46072.7410579977</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E446" s="2">
-        <v>82334</v>
+        <v>81959</v>
       </c>
       <c r="F446" s="3">
-        <v>46079</v>
+        <v>46055</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>9</v>
@@ -12041,16 +12041,16 @@
         <v>32</v>
       </c>
       <c r="C447" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D447" s="3">
-        <v>46076.7259125116</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E447" s="2">
-        <v>82258</v>
+        <v>81960</v>
       </c>
       <c r="F447" s="3">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>9</v>
@@ -12067,16 +12067,16 @@
         <v>32</v>
       </c>
       <c r="C448" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D448" s="3">
-        <v>46076.7259125116</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E448" s="2">
-        <v>82259</v>
+        <v>82063</v>
       </c>
       <c r="F448" s="3">
-        <v>46076</v>
+        <v>46062</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12093,16 +12093,16 @@
         <v>32</v>
       </c>
       <c r="C449" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D449" s="3">
-        <v>46076.7259125116</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E449" s="2">
-        <v>82260</v>
+        <v>82064</v>
       </c>
       <c r="F449" s="3">
-        <v>46076</v>
+        <v>46062</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12119,16 +12119,16 @@
         <v>32</v>
       </c>
       <c r="C450" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D450" s="3">
-        <v>46076.7259125116</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E450" s="2">
-        <v>82274</v>
+        <v>82100</v>
       </c>
       <c r="F450" s="3">
-        <v>46077</v>
+        <v>46064</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12145,16 +12145,16 @@
         <v>32</v>
       </c>
       <c r="C451" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D451" s="3">
-        <v>46084.5055666204</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E451" s="2">
-        <v>82409</v>
+        <v>82333</v>
       </c>
       <c r="F451" s="3">
-        <v>46084</v>
+        <v>46079</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>9</v>
@@ -12171,16 +12171,16 @@
         <v>32</v>
       </c>
       <c r="C452" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D452" s="3">
-        <v>46093.4920058565</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E452" s="2">
-        <v>82581</v>
+        <v>82334</v>
       </c>
       <c r="F452" s="3">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12197,16 +12197,16 @@
         <v>32</v>
       </c>
       <c r="C453" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D453" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E453" s="2">
-        <v>82582</v>
+        <v>82258</v>
       </c>
       <c r="F453" s="3">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>9</v>
@@ -12223,16 +12223,16 @@
         <v>32</v>
       </c>
       <c r="C454" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D454" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E454" s="2">
-        <v>82583</v>
+        <v>82259</v>
       </c>
       <c r="F454" s="3">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>9</v>
@@ -12249,16 +12249,16 @@
         <v>32</v>
       </c>
       <c r="C455" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D455" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E455" s="2">
-        <v>82672</v>
+        <v>82260</v>
       </c>
       <c r="F455" s="3">
-        <v>46097</v>
+        <v>46076</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>9</v>
@@ -12275,16 +12275,16 @@
         <v>32</v>
       </c>
       <c r="C456" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D456" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E456" s="2">
-        <v>82674</v>
+        <v>82274</v>
       </c>
       <c r="F456" s="3">
-        <v>46097</v>
+        <v>46077</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12295,22 +12295,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="457">
       <c r="A457" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C457" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D457" s="3">
-        <v>46035.4386099769</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E457" s="2">
-        <v>81608</v>
+        <v>82409</v>
       </c>
       <c r="F457" s="3">
-        <v>46035</v>
+        <v>46084</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>9</v>
@@ -12321,22 +12321,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="458">
       <c r="A458" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C458" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D458" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E458" s="2">
-        <v>81609</v>
+        <v>82581</v>
       </c>
       <c r="F458" s="3">
-        <v>46035</v>
+        <v>46093</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12347,22 +12347,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="459">
       <c r="A459" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C459" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D459" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E459" s="2">
-        <v>81610</v>
+        <v>82582</v>
       </c>
       <c r="F459" s="3">
-        <v>46035</v>
+        <v>46093</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12373,22 +12373,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="460">
       <c r="A460" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C460" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D460" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E460" s="2">
-        <v>81611</v>
+        <v>82583</v>
       </c>
       <c r="F460" s="3">
-        <v>46035</v>
+        <v>46093</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12399,22 +12399,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="461">
       <c r="A461" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C461" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D461" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E461" s="2">
-        <v>81612</v>
+        <v>82672</v>
       </c>
       <c r="F461" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12425,22 +12425,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="462">
       <c r="A462" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C462" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D462" s="3">
-        <v>46036.6342081481</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E462" s="2">
-        <v>81652</v>
+        <v>82674</v>
       </c>
       <c r="F462" s="3">
-        <v>46037</v>
+        <v>46097</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12457,16 +12457,16 @@
         <v>33</v>
       </c>
       <c r="C463" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D463" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E463" s="2">
-        <v>81659</v>
+        <v>81608</v>
       </c>
       <c r="F463" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12483,16 +12483,16 @@
         <v>33</v>
       </c>
       <c r="C464" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D464" s="3">
-        <v>46048.6509980093</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E464" s="2">
-        <v>81853</v>
+        <v>81609</v>
       </c>
       <c r="F464" s="3">
-        <v>46048</v>
+        <v>46035</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12509,16 +12509,16 @@
         <v>33</v>
       </c>
       <c r="C465" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D465" s="3">
-        <v>46048.6509980093</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E465" s="2">
-        <v>81869</v>
+        <v>81610</v>
       </c>
       <c r="F465" s="3">
-        <v>46049</v>
+        <v>46035</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>9</v>
@@ -12535,16 +12535,16 @@
         <v>33</v>
       </c>
       <c r="C466" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D466" s="3">
-        <v>46048.6509980093</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E466" s="2">
-        <v>81890</v>
+        <v>81611</v>
       </c>
       <c r="F466" s="3">
-        <v>46050</v>
+        <v>46035</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12561,16 +12561,16 @@
         <v>33</v>
       </c>
       <c r="C467" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D467" s="3">
-        <v>46049.4871256134</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E467" s="2">
-        <v>81875</v>
+        <v>81612</v>
       </c>
       <c r="F467" s="3">
-        <v>46049</v>
+        <v>46035</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>9</v>
@@ -12587,16 +12587,16 @@
         <v>33</v>
       </c>
       <c r="C468" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D468" s="3">
-        <v>46049.4871256134</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E468" s="2">
-        <v>81881</v>
+        <v>81652</v>
       </c>
       <c r="F468" s="3">
-        <v>46050</v>
+        <v>46037</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>9</v>
@@ -12613,16 +12613,16 @@
         <v>33</v>
       </c>
       <c r="C469" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D469" s="3">
-        <v>46056.7073643981</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E469" s="2">
-        <v>82015</v>
+        <v>81659</v>
       </c>
       <c r="F469" s="3">
-        <v>46058</v>
+        <v>46037</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>9</v>
@@ -12639,16 +12639,16 @@
         <v>33</v>
       </c>
       <c r="C470" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D470" s="3">
-        <v>46056.7073643981</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E470" s="2">
-        <v>82017</v>
+        <v>81853</v>
       </c>
       <c r="F470" s="3">
-        <v>46058</v>
+        <v>46048</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>9</v>
@@ -12665,16 +12665,16 @@
         <v>33</v>
       </c>
       <c r="C471" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D471" s="3">
-        <v>46056.7073643981</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E471" s="2">
-        <v>82020</v>
+        <v>81869</v>
       </c>
       <c r="F471" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>9</v>
@@ -12691,16 +12691,16 @@
         <v>33</v>
       </c>
       <c r="C472" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D472" s="3">
-        <v>46056.7073643981</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E472" s="2">
-        <v>82023</v>
+        <v>81890</v>
       </c>
       <c r="F472" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12717,16 +12717,16 @@
         <v>33</v>
       </c>
       <c r="C473" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D473" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E473" s="2">
-        <v>82061</v>
+        <v>81875</v>
       </c>
       <c r="F473" s="3">
-        <v>46062</v>
+        <v>46049</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12743,16 +12743,16 @@
         <v>33</v>
       </c>
       <c r="C474" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D474" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E474" s="2">
-        <v>82081</v>
+        <v>81881</v>
       </c>
       <c r="F474" s="3">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12775,10 +12775,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E475" s="2">
-        <v>82095</v>
+        <v>82015</v>
       </c>
       <c r="F475" s="3">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>9</v>
@@ -12795,16 +12795,16 @@
         <v>33</v>
       </c>
       <c r="C476" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D476" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E476" s="2">
-        <v>82081</v>
+        <v>82017</v>
       </c>
       <c r="F476" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>9</v>
@@ -12821,16 +12821,16 @@
         <v>33</v>
       </c>
       <c r="C477" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D477" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E477" s="2">
-        <v>82107</v>
+        <v>82020</v>
       </c>
       <c r="F477" s="3">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>9</v>
@@ -12847,16 +12847,16 @@
         <v>33</v>
       </c>
       <c r="C478" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D478" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E478" s="2">
-        <v>82112</v>
+        <v>82023</v>
       </c>
       <c r="F478" s="3">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12873,16 +12873,16 @@
         <v>33</v>
       </c>
       <c r="C479" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D479" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E479" s="2">
-        <v>82113</v>
+        <v>82061</v>
       </c>
       <c r="F479" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12899,16 +12899,16 @@
         <v>33</v>
       </c>
       <c r="C480" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D480" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E480" s="2">
-        <v>82123</v>
+        <v>82081</v>
       </c>
       <c r="F480" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>9</v>
@@ -12925,10 +12925,10 @@
         <v>33</v>
       </c>
       <c r="C481" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D481" s="3">
-        <v>46063.5787047801</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E481" s="2">
         <v>82095</v>
@@ -12951,16 +12951,16 @@
         <v>33</v>
       </c>
       <c r="C482" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D482" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E482" s="2">
-        <v>82106</v>
+        <v>82081</v>
       </c>
       <c r="F482" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12977,10 +12977,10 @@
         <v>33</v>
       </c>
       <c r="C483" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D483" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E483" s="2">
         <v>82107</v>
@@ -13003,13 +13003,13 @@
         <v>33</v>
       </c>
       <c r="C484" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D484" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E484" s="2">
-        <v>82109</v>
+        <v>82112</v>
       </c>
       <c r="F484" s="3">
         <v>46064</v>
@@ -13029,13 +13029,13 @@
         <v>33</v>
       </c>
       <c r="C485" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D485" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E485" s="2">
-        <v>82110</v>
+        <v>82113</v>
       </c>
       <c r="F485" s="3">
         <v>46064</v>
@@ -13055,13 +13055,13 @@
         <v>33</v>
       </c>
       <c r="C486" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D486" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E486" s="2">
-        <v>82139</v>
+        <v>82123</v>
       </c>
       <c r="F486" s="3">
         <v>46065</v>
@@ -13081,16 +13081,16 @@
         <v>33</v>
       </c>
       <c r="C487" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D487" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E487" s="2">
-        <v>82365</v>
+        <v>82095</v>
       </c>
       <c r="F487" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>9</v>
@@ -13107,16 +13107,16 @@
         <v>33</v>
       </c>
       <c r="C488" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D488" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E488" s="2">
-        <v>82366</v>
+        <v>82106</v>
       </c>
       <c r="F488" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>9</v>
@@ -13133,16 +13133,16 @@
         <v>33</v>
       </c>
       <c r="C489" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D489" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E489" s="2">
-        <v>82371</v>
+        <v>82107</v>
       </c>
       <c r="F489" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>9</v>
@@ -13159,16 +13159,16 @@
         <v>33</v>
       </c>
       <c r="C490" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D490" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E490" s="2">
-        <v>82383</v>
+        <v>82109</v>
       </c>
       <c r="F490" s="3">
-        <v>46083</v>
+        <v>46064</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>9</v>
@@ -13185,16 +13185,16 @@
         <v>33</v>
       </c>
       <c r="C491" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D491" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E491" s="2">
-        <v>82384</v>
+        <v>82110</v>
       </c>
       <c r="F491" s="3">
-        <v>46083</v>
+        <v>46064</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>9</v>
@@ -13211,16 +13211,16 @@
         <v>33</v>
       </c>
       <c r="C492" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D492" s="3">
-        <v>46098.4979333449</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E492" s="2">
-        <v>82693</v>
+        <v>82139</v>
       </c>
       <c r="F492" s="3">
-        <v>46098</v>
+        <v>46065</v>
       </c>
       <c r="G492" s="1" t="s">
         <v>9</v>
@@ -13231,48 +13231,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="493">
       <c r="A493" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C493" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D493" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E493" s="2">
-        <v>81592</v>
+        <v>82365</v>
       </c>
       <c r="F493" s="3">
-        <v>46031</v>
+        <v>46080</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="494">
       <c r="A494" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C494" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D494" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E494" s="2">
-        <v>81593</v>
+        <v>82366</v>
       </c>
       <c r="F494" s="3">
-        <v>46031</v>
+        <v>46080</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>9</v>
@@ -13283,22 +13283,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="495">
       <c r="A495" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C495" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D495" s="3">
-        <v>46038.6827563889</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E495" s="2">
-        <v>81697</v>
+        <v>82371</v>
       </c>
       <c r="F495" s="3">
-        <v>46038</v>
+        <v>46080</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>9</v>
@@ -13309,48 +13309,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="496">
       <c r="A496" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C496" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D496" s="3">
-        <v>46038.6827563889</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E496" s="2">
-        <v>81735</v>
+        <v>82383</v>
       </c>
       <c r="F496" s="3">
-        <v>46041</v>
+        <v>46083</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H496" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="497">
       <c r="A497" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C497" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D497" s="3">
-        <v>46045.4532476157</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E497" s="2">
-        <v>81823</v>
+        <v>82384</v>
       </c>
       <c r="F497" s="3">
-        <v>46045</v>
+        <v>46083</v>
       </c>
       <c r="G497" s="1" t="s">
         <v>9</v>
@@ -13361,22 +13361,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="498">
       <c r="A498" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C498" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D498" s="3">
-        <v>46031.4724550926</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E498" s="2">
-        <v>81572</v>
+        <v>82693</v>
       </c>
       <c r="F498" s="3">
-        <v>46031</v>
+        <v>46098</v>
       </c>
       <c r="G498" s="1" t="s">
         <v>9</v>
@@ -13387,22 +13387,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="499">
       <c r="A499" s="2">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C499" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D499" s="3">
-        <v>46031.4724550926</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E499" s="2">
-        <v>81573</v>
+        <v>82760</v>
       </c>
       <c r="F499" s="3">
-        <v>46031</v>
+        <v>46101</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>9</v>
@@ -13413,45 +13413,45 @@
     </row>
     <row ht="12.75" customHeight="1" r="500">
       <c r="A500" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C500" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D500" s="3">
-        <v>46031.4724550926</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E500" s="2">
-        <v>81579</v>
+        <v>81592</v>
       </c>
       <c r="F500" s="3">
         <v>46031</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H500" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="501">
       <c r="A501" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C501" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D501" s="3">
-        <v>46031.4724550926</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E501" s="2">
-        <v>81580</v>
+        <v>81593</v>
       </c>
       <c r="F501" s="3">
         <v>46031</v>
@@ -13465,22 +13465,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="502">
       <c r="A502" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C502" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D502" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E502" s="2">
-        <v>81581</v>
+        <v>81697</v>
       </c>
       <c r="F502" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="G502" s="1" t="s">
         <v>9</v>
@@ -13491,48 +13491,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="503">
       <c r="A503" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C503" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D503" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E503" s="2">
-        <v>81582</v>
+        <v>81735</v>
       </c>
       <c r="F503" s="3">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H503" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="504">
       <c r="A504" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C504" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D504" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E504" s="2">
-        <v>81583</v>
+        <v>81823</v>
       </c>
       <c r="F504" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>9</v>
@@ -13549,16 +13549,16 @@
         <v>35</v>
       </c>
       <c r="C505" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D505" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E505" s="2">
-        <v>81667</v>
+        <v>81572</v>
       </c>
       <c r="F505" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G505" s="1" t="s">
         <v>9</v>
@@ -13575,16 +13575,16 @@
         <v>35</v>
       </c>
       <c r="C506" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D506" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E506" s="2">
-        <v>81668</v>
+        <v>81573</v>
       </c>
       <c r="F506" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>9</v>
@@ -13601,16 +13601,16 @@
         <v>35</v>
       </c>
       <c r="C507" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D507" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E507" s="2">
-        <v>81674</v>
+        <v>81579</v>
       </c>
       <c r="F507" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>9</v>
@@ -13627,16 +13627,16 @@
         <v>35</v>
       </c>
       <c r="C508" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D508" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E508" s="2">
-        <v>81675</v>
+        <v>81580</v>
       </c>
       <c r="F508" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G508" s="1" t="s">
         <v>9</v>
@@ -13653,16 +13653,16 @@
         <v>35</v>
       </c>
       <c r="C509" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D509" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E509" s="2">
-        <v>81677</v>
+        <v>81581</v>
       </c>
       <c r="F509" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G509" s="1" t="s">
         <v>9</v>
@@ -13679,16 +13679,16 @@
         <v>35</v>
       </c>
       <c r="C510" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D510" s="3">
-        <v>46041.6133887269</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E510" s="2">
-        <v>81739</v>
+        <v>81582</v>
       </c>
       <c r="F510" s="3">
-        <v>46041</v>
+        <v>46031</v>
       </c>
       <c r="G510" s="1" t="s">
         <v>9</v>
@@ -13705,16 +13705,16 @@
         <v>35</v>
       </c>
       <c r="C511" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D511" s="3">
-        <v>46041.6133887269</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E511" s="2">
-        <v>81741</v>
+        <v>81583</v>
       </c>
       <c r="F511" s="3">
-        <v>46041</v>
+        <v>46031</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>9</v>
@@ -13731,16 +13731,16 @@
         <v>35</v>
       </c>
       <c r="C512" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D512" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E512" s="2">
-        <v>81854</v>
+        <v>81667</v>
       </c>
       <c r="F512" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G512" s="1" t="s">
         <v>9</v>
@@ -13757,16 +13757,16 @@
         <v>35</v>
       </c>
       <c r="C513" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D513" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E513" s="2">
-        <v>81855</v>
+        <v>81668</v>
       </c>
       <c r="F513" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G513" s="1" t="s">
         <v>9</v>
@@ -13783,16 +13783,16 @@
         <v>35</v>
       </c>
       <c r="C514" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D514" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E514" s="2">
-        <v>81858</v>
+        <v>81674</v>
       </c>
       <c r="F514" s="3">
-        <v>46049</v>
+        <v>46038</v>
       </c>
       <c r="G514" s="1" t="s">
         <v>9</v>
@@ -13809,16 +13809,16 @@
         <v>35</v>
       </c>
       <c r="C515" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D515" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E515" s="2">
-        <v>81859</v>
+        <v>81675</v>
       </c>
       <c r="F515" s="3">
-        <v>46049</v>
+        <v>46038</v>
       </c>
       <c r="G515" s="1" t="s">
         <v>9</v>
@@ -13835,16 +13835,16 @@
         <v>35</v>
       </c>
       <c r="C516" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D516" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E516" s="2">
-        <v>81862</v>
+        <v>81677</v>
       </c>
       <c r="F516" s="3">
-        <v>46049</v>
+        <v>46038</v>
       </c>
       <c r="G516" s="1" t="s">
         <v>9</v>
@@ -13861,16 +13861,16 @@
         <v>35</v>
       </c>
       <c r="C517" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D517" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E517" s="2">
-        <v>81863</v>
+        <v>81739</v>
       </c>
       <c r="F517" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G517" s="1" t="s">
         <v>9</v>
@@ -13887,16 +13887,16 @@
         <v>35</v>
       </c>
       <c r="C518" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D518" s="3">
-        <v>46055.5924236111</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E518" s="2">
-        <v>81958</v>
+        <v>81741</v>
       </c>
       <c r="F518" s="3">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>9</v>
@@ -13913,16 +13913,16 @@
         <v>35</v>
       </c>
       <c r="C519" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D519" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E519" s="2">
-        <v>81965</v>
+        <v>81854</v>
       </c>
       <c r="F519" s="3">
-        <v>46055</v>
+        <v>46048</v>
       </c>
       <c r="G519" s="1" t="s">
         <v>9</v>
@@ -13939,16 +13939,16 @@
         <v>35</v>
       </c>
       <c r="C520" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D520" s="3">
-        <v>46063.5923590625</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E520" s="2">
-        <v>82085</v>
+        <v>81855</v>
       </c>
       <c r="F520" s="3">
-        <v>46063</v>
+        <v>46048</v>
       </c>
       <c r="G520" s="1" t="s">
         <v>9</v>
@@ -13965,16 +13965,16 @@
         <v>35</v>
       </c>
       <c r="C521" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D521" s="3">
-        <v>46063.5923590625</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E521" s="2">
-        <v>82086</v>
+        <v>81858</v>
       </c>
       <c r="F521" s="3">
-        <v>46063</v>
+        <v>46049</v>
       </c>
       <c r="G521" s="1" t="s">
         <v>9</v>
@@ -13991,16 +13991,16 @@
         <v>35</v>
       </c>
       <c r="C522" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D522" s="3">
-        <v>46063.5923590625</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E522" s="2">
-        <v>82126</v>
+        <v>81859</v>
       </c>
       <c r="F522" s="3">
-        <v>46065</v>
+        <v>46049</v>
       </c>
       <c r="G522" s="1" t="s">
         <v>9</v>
@@ -14017,16 +14017,16 @@
         <v>35</v>
       </c>
       <c r="C523" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D523" s="3">
-        <v>46064.5127051505</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E523" s="2">
-        <v>82268</v>
+        <v>81862</v>
       </c>
       <c r="F523" s="3">
-        <v>46077</v>
+        <v>46049</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>9</v>
@@ -14043,16 +14043,16 @@
         <v>35</v>
       </c>
       <c r="C524" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D524" s="3">
-        <v>46065.6275788773</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E524" s="2">
-        <v>82142</v>
+        <v>81863</v>
       </c>
       <c r="F524" s="3">
-        <v>46065</v>
+        <v>46049</v>
       </c>
       <c r="G524" s="1" t="s">
         <v>9</v>
@@ -14069,16 +14069,16 @@
         <v>35</v>
       </c>
       <c r="C525" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D525" s="3">
-        <v>46065.6275788773</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E525" s="2">
-        <v>82143</v>
+        <v>81958</v>
       </c>
       <c r="F525" s="3">
-        <v>46065</v>
+        <v>46055</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>9</v>
@@ -14095,16 +14095,16 @@
         <v>35</v>
       </c>
       <c r="C526" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D526" s="3">
-        <v>46065.6275788773</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E526" s="2">
-        <v>82144</v>
+        <v>81965</v>
       </c>
       <c r="F526" s="3">
-        <v>46065</v>
+        <v>46055</v>
       </c>
       <c r="G526" s="1" t="s">
         <v>9</v>
@@ -14121,16 +14121,16 @@
         <v>35</v>
       </c>
       <c r="C527" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D527" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E527" s="2">
-        <v>82166</v>
+        <v>82085</v>
       </c>
       <c r="F527" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G527" s="1" t="s">
         <v>9</v>
@@ -14147,16 +14147,16 @@
         <v>35</v>
       </c>
       <c r="C528" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D528" s="3">
-        <v>46077.406463831</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E528" s="2">
-        <v>82262</v>
+        <v>82086</v>
       </c>
       <c r="F528" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G528" s="1" t="s">
         <v>9</v>
@@ -14173,16 +14173,16 @@
         <v>35</v>
       </c>
       <c r="C529" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D529" s="3">
-        <v>46077.406463831</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E529" s="2">
-        <v>82265</v>
+        <v>82126</v>
       </c>
       <c r="F529" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G529" s="1" t="s">
         <v>9</v>
@@ -14199,13 +14199,13 @@
         <v>35</v>
       </c>
       <c r="C530" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D530" s="3">
-        <v>46077.406463831</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E530" s="2">
-        <v>82281</v>
+        <v>82268</v>
       </c>
       <c r="F530" s="3">
         <v>46077</v>
@@ -14225,16 +14225,16 @@
         <v>35</v>
       </c>
       <c r="C531" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D531" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E531" s="2">
-        <v>82282</v>
+        <v>82142</v>
       </c>
       <c r="F531" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G531" s="1" t="s">
         <v>9</v>
@@ -14251,16 +14251,16 @@
         <v>35</v>
       </c>
       <c r="C532" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D532" s="3">
-        <v>46079.5782408912</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E532" s="2">
-        <v>82340</v>
+        <v>82143</v>
       </c>
       <c r="F532" s="3">
-        <v>46079</v>
+        <v>46065</v>
       </c>
       <c r="G532" s="1" t="s">
         <v>9</v>
@@ -14277,16 +14277,16 @@
         <v>35</v>
       </c>
       <c r="C533" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D533" s="3">
-        <v>46083.6671321991</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E533" s="2">
-        <v>82399</v>
+        <v>82144</v>
       </c>
       <c r="F533" s="3">
-        <v>46083</v>
+        <v>46065</v>
       </c>
       <c r="G533" s="1" t="s">
         <v>9</v>
@@ -14303,16 +14303,16 @@
         <v>35</v>
       </c>
       <c r="C534" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D534" s="3">
-        <v>46083.6671321991</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E534" s="2">
-        <v>82400</v>
+        <v>82166</v>
       </c>
       <c r="F534" s="3">
-        <v>46083</v>
+        <v>46066</v>
       </c>
       <c r="G534" s="1" t="s">
         <v>9</v>
@@ -14329,16 +14329,16 @@
         <v>35</v>
       </c>
       <c r="C535" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D535" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E535" s="2">
-        <v>82401</v>
+        <v>82262</v>
       </c>
       <c r="F535" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G535" s="1" t="s">
         <v>9</v>
@@ -14355,16 +14355,16 @@
         <v>35</v>
       </c>
       <c r="C536" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D536" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E536" s="2">
-        <v>82412</v>
+        <v>82265</v>
       </c>
       <c r="F536" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G536" s="1" t="s">
         <v>9</v>
@@ -14381,16 +14381,16 @@
         <v>35</v>
       </c>
       <c r="C537" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D537" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E537" s="2">
-        <v>82415</v>
+        <v>82281</v>
       </c>
       <c r="F537" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G537" s="1" t="s">
         <v>9</v>
@@ -14407,16 +14407,16 @@
         <v>35</v>
       </c>
       <c r="C538" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D538" s="3">
-        <v>46086.6312882639</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E538" s="2">
-        <v>82571</v>
+        <v>82282</v>
       </c>
       <c r="F538" s="3">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="G538" s="1" t="s">
         <v>9</v>
@@ -14433,16 +14433,16 @@
         <v>35</v>
       </c>
       <c r="C539" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D539" s="3">
-        <v>46086.6312882639</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E539" s="2">
-        <v>82572</v>
+        <v>82340</v>
       </c>
       <c r="F539" s="3">
-        <v>46093</v>
+        <v>46079</v>
       </c>
       <c r="G539" s="1" t="s">
         <v>9</v>
@@ -14459,16 +14459,16 @@
         <v>35</v>
       </c>
       <c r="C540" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D540" s="3">
-        <v>46094.4745190394</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E540" s="2">
-        <v>82630</v>
+        <v>82399</v>
       </c>
       <c r="F540" s="3">
-        <v>46094</v>
+        <v>46083</v>
       </c>
       <c r="G540" s="1" t="s">
         <v>9</v>
@@ -14485,16 +14485,16 @@
         <v>35</v>
       </c>
       <c r="C541" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D541" s="3">
-        <v>46094.4745190394</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E541" s="2">
-        <v>82631</v>
+        <v>82400</v>
       </c>
       <c r="F541" s="3">
-        <v>46094</v>
+        <v>46083</v>
       </c>
       <c r="G541" s="1" t="s">
         <v>9</v>
@@ -14511,16 +14511,16 @@
         <v>35</v>
       </c>
       <c r="C542" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D542" s="3">
-        <v>46094.4745190394</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E542" s="2">
-        <v>82632</v>
+        <v>82401</v>
       </c>
       <c r="F542" s="3">
-        <v>46094</v>
+        <v>46083</v>
       </c>
       <c r="G542" s="1" t="s">
         <v>9</v>
@@ -14537,16 +14537,16 @@
         <v>35</v>
       </c>
       <c r="C543" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D543" s="3">
-        <v>46097.4499278356</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E543" s="2">
-        <v>82653</v>
+        <v>82412</v>
       </c>
       <c r="F543" s="3">
-        <v>46097</v>
+        <v>46084</v>
       </c>
       <c r="G543" s="1" t="s">
         <v>9</v>
@@ -14563,16 +14563,16 @@
         <v>35</v>
       </c>
       <c r="C544" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D544" s="3">
-        <v>46097.4499278356</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E544" s="2">
-        <v>82665</v>
+        <v>82415</v>
       </c>
       <c r="F544" s="3">
-        <v>46097</v>
+        <v>46084</v>
       </c>
       <c r="G544" s="1" t="s">
         <v>9</v>
@@ -14589,16 +14589,16 @@
         <v>35</v>
       </c>
       <c r="C545" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D545" s="3">
-        <v>46097.4499278356</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E545" s="2">
-        <v>82668</v>
+        <v>82571</v>
       </c>
       <c r="F545" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G545" s="1" t="s">
         <v>9</v>
@@ -14615,16 +14615,16 @@
         <v>35</v>
       </c>
       <c r="C546" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D546" s="3">
-        <v>46098.6661386574</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E546" s="2">
-        <v>82696</v>
+        <v>82572</v>
       </c>
       <c r="F546" s="3">
-        <v>46098</v>
+        <v>46093</v>
       </c>
       <c r="G546" s="1" t="s">
         <v>9</v>
@@ -14641,16 +14641,16 @@
         <v>35</v>
       </c>
       <c r="C547" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D547" s="3">
-        <v>46098.6661386574</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E547" s="2">
-        <v>82704</v>
+        <v>82630</v>
       </c>
       <c r="F547" s="3">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="G547" s="1" t="s">
         <v>9</v>
@@ -14661,22 +14661,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="548">
       <c r="A548" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C548" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D548" s="3">
-        <v>46078.6702738773</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E548" s="2">
-        <v>82311</v>
+        <v>82631</v>
       </c>
       <c r="F548" s="3">
-        <v>46078</v>
+        <v>46094</v>
       </c>
       <c r="G548" s="1" t="s">
         <v>9</v>
@@ -14687,22 +14687,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="549">
       <c r="A549" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C549" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D549" s="3">
-        <v>46078.6702738773</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E549" s="2">
-        <v>82312</v>
+        <v>82632</v>
       </c>
       <c r="F549" s="3">
-        <v>46078</v>
+        <v>46094</v>
       </c>
       <c r="G549" s="1" t="s">
         <v>9</v>
@@ -14713,22 +14713,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="550">
       <c r="A550" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C550" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D550" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E550" s="2">
-        <v>82313</v>
+        <v>82653</v>
       </c>
       <c r="F550" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G550" s="1" t="s">
         <v>9</v>
@@ -14739,22 +14739,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="551">
       <c r="A551" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C551" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D551" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E551" s="2">
-        <v>82314</v>
+        <v>82665</v>
       </c>
       <c r="F551" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G551" s="1" t="s">
         <v>9</v>
@@ -14765,22 +14765,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="552">
       <c r="A552" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C552" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D552" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E552" s="2">
-        <v>82346</v>
+        <v>82668</v>
       </c>
       <c r="F552" s="3">
-        <v>46080</v>
+        <v>46097</v>
       </c>
       <c r="G552" s="1" t="s">
         <v>9</v>
@@ -14791,22 +14791,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="553">
       <c r="A553" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C553" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D553" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E553" s="2">
-        <v>82361</v>
+        <v>82696</v>
       </c>
       <c r="F553" s="3">
-        <v>46080</v>
+        <v>46098</v>
       </c>
       <c r="G553" s="1" t="s">
         <v>9</v>
@@ -14817,22 +14817,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="554">
       <c r="A554" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C554" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D554" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E554" s="2">
-        <v>82385</v>
+        <v>82704</v>
       </c>
       <c r="F554" s="3">
-        <v>46083</v>
+        <v>46099</v>
       </c>
       <c r="G554" s="1" t="s">
         <v>9</v>
@@ -14855,10 +14855,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E555" s="2">
-        <v>82391</v>
+        <v>82311</v>
       </c>
       <c r="F555" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G555" s="1" t="s">
         <v>9</v>
@@ -14881,10 +14881,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E556" s="2">
-        <v>82392</v>
+        <v>82312</v>
       </c>
       <c r="F556" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G556" s="1" t="s">
         <v>9</v>
@@ -14901,16 +14901,16 @@
         <v>36</v>
       </c>
       <c r="C557" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D557" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E557" s="2">
-        <v>82691</v>
+        <v>82313</v>
       </c>
       <c r="F557" s="3">
-        <v>46098</v>
+        <v>46078</v>
       </c>
       <c r="G557" s="1" t="s">
         <v>9</v>
@@ -14927,16 +14927,16 @@
         <v>36</v>
       </c>
       <c r="C558" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D558" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E558" s="2">
-        <v>82692</v>
+        <v>82314</v>
       </c>
       <c r="F558" s="3">
-        <v>46098</v>
+        <v>46078</v>
       </c>
       <c r="G558" s="1" t="s">
         <v>9</v>
@@ -14953,16 +14953,16 @@
         <v>36</v>
       </c>
       <c r="C559" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D559" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E559" s="2">
-        <v>82699</v>
+        <v>82346</v>
       </c>
       <c r="F559" s="3">
-        <v>46098</v>
+        <v>46080</v>
       </c>
       <c r="G559" s="1" t="s">
         <v>9</v>
@@ -14979,16 +14979,16 @@
         <v>36</v>
       </c>
       <c r="C560" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D560" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E560" s="2">
-        <v>82716</v>
+        <v>82361</v>
       </c>
       <c r="F560" s="3">
-        <v>46099</v>
+        <v>46080</v>
       </c>
       <c r="G560" s="1" t="s">
         <v>9</v>
@@ -15005,16 +15005,16 @@
         <v>36</v>
       </c>
       <c r="C561" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D561" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E561" s="2">
-        <v>82717</v>
+        <v>82385</v>
       </c>
       <c r="F561" s="3">
-        <v>46099</v>
+        <v>46083</v>
       </c>
       <c r="G561" s="1" t="s">
         <v>9</v>
@@ -15025,22 +15025,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="562">
       <c r="A562" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C562" s="2">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D562" s="3">
-        <v>46029.4632696412</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E562" s="2">
-        <v>81495</v>
+        <v>82391</v>
       </c>
       <c r="F562" s="3">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="G562" s="1" t="s">
         <v>9</v>
@@ -15051,27 +15051,209 @@
     </row>
     <row ht="12.75" customHeight="1" r="563">
       <c r="A563" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C563" s="2">
+        <v>1</v>
+      </c>
+      <c r="D563" s="3">
+        <v>46078.6702738773</v>
+      </c>
+      <c r="E563" s="2">
+        <v>82392</v>
+      </c>
+      <c r="F563" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G563" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H563" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="564">
+      <c r="A564" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C564" s="2">
+        <v>2</v>
+      </c>
+      <c r="D564" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="E564" s="2">
+        <v>82691</v>
+      </c>
+      <c r="F564" s="3">
+        <v>46098</v>
+      </c>
+      <c r="G564" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H564" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="565">
+      <c r="A565" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C565" s="2">
+        <v>2</v>
+      </c>
+      <c r="D565" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="E565" s="2">
+        <v>82692</v>
+      </c>
+      <c r="F565" s="3">
+        <v>46098</v>
+      </c>
+      <c r="G565" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H565" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="566">
+      <c r="A566" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C566" s="2">
+        <v>2</v>
+      </c>
+      <c r="D566" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="E566" s="2">
+        <v>82699</v>
+      </c>
+      <c r="F566" s="3">
+        <v>46098</v>
+      </c>
+      <c r="G566" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H566" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="567">
+      <c r="A567" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C567" s="2">
+        <v>2</v>
+      </c>
+      <c r="D567" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="E567" s="2">
+        <v>82716</v>
+      </c>
+      <c r="F567" s="3">
+        <v>46099</v>
+      </c>
+      <c r="G567" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H567" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="568">
+      <c r="A568" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C568" s="2">
+        <v>2</v>
+      </c>
+      <c r="D568" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="E568" s="2">
+        <v>82717</v>
+      </c>
+      <c r="F568" s="3">
+        <v>46099</v>
+      </c>
+      <c r="G568" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H568" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="569">
+      <c r="A569" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C569" s="2">
+        <v>62</v>
+      </c>
+      <c r="D569" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E569" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F569" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G569" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H569" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="570">
+      <c r="A570" s="2">
         <v>9992</v>
       </c>
-      <c r="B563" s="1" t="s">
+      <c r="B570" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C563" s="2">
+      <c r="C570" s="2">
         <v>390</v>
       </c>
-      <c r="D563" s="3">
+      <c r="D570" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E563" s="2">
+      <c r="E570" s="2">
         <v>81684</v>
       </c>
-      <c r="F563" s="3">
+      <c r="F570" s="3">
         <v>46038</v>
       </c>
-      <c r="G563" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H563" s="1" t="s">
+      <c r="G570" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H570" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -74,6 +74,12 @@
     <t>SUN MORITZ ADMINISTRADORA</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Não Concluídos</t>
+  </si>
+  <si>
     <t>MARIA BELTRÃO SALDANHA COELHO</t>
   </si>
   <si>
@@ -93,12 +99,6 @@
   </si>
   <si>
     <t>KATIA FERREIRA DE BARROS</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Não Concluídos</t>
   </si>
   <si>
     <t>RAFAEL CURSINO DE MOURA LEVY</t>
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H573"/>
+  <dimension ref="A1:H576"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -3559,54 +3559,54 @@
     </row>
     <row ht="12.75" customHeight="1" r="121">
       <c r="A121" s="2">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C121" s="2">
+        <v>86</v>
+      </c>
+      <c r="D121" s="3">
+        <v>46104.4566862384</v>
+      </c>
+      <c r="E121" s="2">
+        <v>82781</v>
+      </c>
+      <c r="F121" s="3">
+        <v>46104</v>
+      </c>
+      <c r="G121" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C121" s="2">
-        <v>82</v>
-      </c>
-      <c r="D121" s="3">
-        <v>46014.6980340162</v>
-      </c>
-      <c r="E121" s="2">
-        <v>81460</v>
-      </c>
-      <c r="F121" s="3">
-        <v>46027</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H121" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="122">
       <c r="A122" s="2">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C122" s="2">
+        <v>86</v>
+      </c>
+      <c r="D122" s="3">
+        <v>46104.4566862384</v>
+      </c>
+      <c r="E122" s="2">
+        <v>82782</v>
+      </c>
+      <c r="F122" s="3">
+        <v>46104</v>
+      </c>
+      <c r="G122" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C122" s="2">
-        <v>82</v>
-      </c>
-      <c r="D122" s="3">
-        <v>46014.6980340162</v>
-      </c>
-      <c r="E122" s="2">
-        <v>81461</v>
-      </c>
-      <c r="F122" s="3">
-        <v>46027</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H122" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="123">
@@ -3614,7 +3614,7 @@
         <v>2409</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C123" s="2">
         <v>82</v>
@@ -3623,7 +3623,7 @@
         <v>46014.6980340162</v>
       </c>
       <c r="E123" s="2">
-        <v>81463</v>
+        <v>81460</v>
       </c>
       <c r="F123" s="3">
         <v>46027</v>
@@ -3640,19 +3640,19 @@
         <v>2409</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C124" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D124" s="3">
-        <v>46030.4707423958</v>
+        <v>46014.6980340162</v>
       </c>
       <c r="E124" s="2">
-        <v>81542</v>
+        <v>81461</v>
       </c>
       <c r="F124" s="3">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>9</v>
@@ -3666,19 +3666,19 @@
         <v>2409</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C125" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D125" s="3">
-        <v>46030.4707423958</v>
+        <v>46014.6980340162</v>
       </c>
       <c r="E125" s="2">
-        <v>81548</v>
+        <v>81463</v>
       </c>
       <c r="F125" s="3">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>9</v>
@@ -3692,7 +3692,7 @@
         <v>2409</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C126" s="2">
         <v>83</v>
@@ -3701,7 +3701,7 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E126" s="2">
-        <v>81549</v>
+        <v>81542</v>
       </c>
       <c r="F126" s="3">
         <v>46030</v>
@@ -3718,7 +3718,7 @@
         <v>2409</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C127" s="2">
         <v>83</v>
@@ -3727,10 +3727,10 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E127" s="2">
-        <v>81569</v>
+        <v>81548</v>
       </c>
       <c r="F127" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>9</v>
@@ -3744,19 +3744,19 @@
         <v>2409</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C128" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D128" s="3">
-        <v>46037.6468124884</v>
+        <v>46030.4707423958</v>
       </c>
       <c r="E128" s="2">
-        <v>81669</v>
+        <v>81549</v>
       </c>
       <c r="F128" s="3">
-        <v>46037</v>
+        <v>46030</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>9</v>
@@ -3770,19 +3770,19 @@
         <v>2409</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C129" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D129" s="3">
-        <v>46037.6468124884</v>
+        <v>46030.4707423958</v>
       </c>
       <c r="E129" s="2">
-        <v>81670</v>
+        <v>81569</v>
       </c>
       <c r="F129" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>9</v>
@@ -3796,7 +3796,7 @@
         <v>2409</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C130" s="2">
         <v>84</v>
@@ -3805,10 +3805,10 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E130" s="2">
-        <v>81673</v>
+        <v>81669</v>
       </c>
       <c r="F130" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>9</v>
@@ -3822,7 +3822,7 @@
         <v>2409</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C131" s="2">
         <v>84</v>
@@ -3831,10 +3831,10 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E131" s="2">
-        <v>81682</v>
+        <v>81670</v>
       </c>
       <c r="F131" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>9</v>
@@ -3848,7 +3848,7 @@
         <v>2409</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C132" s="2">
         <v>84</v>
@@ -3857,7 +3857,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E132" s="2">
-        <v>81689</v>
+        <v>81673</v>
       </c>
       <c r="F132" s="3">
         <v>46038</v>
@@ -3874,19 +3874,19 @@
         <v>2409</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C133" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D133" s="3">
-        <v>46038.5944713773</v>
+        <v>46037.6468124884</v>
       </c>
       <c r="E133" s="2">
-        <v>81707</v>
+        <v>81682</v>
       </c>
       <c r="F133" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>9</v>
@@ -3900,19 +3900,19 @@
         <v>2409</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C134" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D134" s="3">
-        <v>46049.490160081</v>
+        <v>46037.6468124884</v>
       </c>
       <c r="E134" s="2">
-        <v>81866</v>
+        <v>81689</v>
       </c>
       <c r="F134" s="3">
-        <v>46049</v>
+        <v>46038</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>9</v>
@@ -3926,19 +3926,19 @@
         <v>2409</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C135" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D135" s="3">
-        <v>46049.490160081</v>
+        <v>46038.5944713773</v>
       </c>
       <c r="E135" s="2">
-        <v>81867</v>
+        <v>81707</v>
       </c>
       <c r="F135" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>9</v>
@@ -3952,7 +3952,7 @@
         <v>2409</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C136" s="2">
         <v>86</v>
@@ -3961,7 +3961,7 @@
         <v>46049.490160081</v>
       </c>
       <c r="E136" s="2">
-        <v>81871</v>
+        <v>81866</v>
       </c>
       <c r="F136" s="3">
         <v>46049</v>
@@ -3978,7 +3978,7 @@
         <v>2409</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C137" s="2">
         <v>86</v>
@@ -3987,10 +3987,10 @@
         <v>46049.490160081</v>
       </c>
       <c r="E137" s="2">
-        <v>81882</v>
+        <v>81867</v>
       </c>
       <c r="F137" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>9</v>
@@ -4004,19 +4004,19 @@
         <v>2409</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C138" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D138" s="3">
-        <v>46051.4127791667</v>
+        <v>46049.490160081</v>
       </c>
       <c r="E138" s="2">
-        <v>81922</v>
+        <v>81871</v>
       </c>
       <c r="F138" s="3">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>9</v>
@@ -4030,19 +4030,19 @@
         <v>2409</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C139" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D139" s="3">
-        <v>46056.7141110995</v>
+        <v>46049.490160081</v>
       </c>
       <c r="E139" s="2">
-        <v>81972</v>
+        <v>81882</v>
       </c>
       <c r="F139" s="3">
-        <v>46056</v>
+        <v>46050</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>9</v>
@@ -4056,19 +4056,19 @@
         <v>2409</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C140" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D140" s="3">
-        <v>46056.7141110995</v>
+        <v>46051.4127791667</v>
       </c>
       <c r="E140" s="2">
-        <v>81973</v>
+        <v>81922</v>
       </c>
       <c r="F140" s="3">
-        <v>46056</v>
+        <v>46051</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>9</v>
@@ -4082,7 +4082,7 @@
         <v>2409</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C141" s="2">
         <v>88</v>
@@ -4091,10 +4091,10 @@
         <v>46056.7141110995</v>
       </c>
       <c r="E141" s="2">
-        <v>81993</v>
+        <v>81972</v>
       </c>
       <c r="F141" s="3">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>9</v>
@@ -4108,19 +4108,19 @@
         <v>2409</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C142" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D142" s="3">
-        <v>46063.7282468519</v>
+        <v>46056.7141110995</v>
       </c>
       <c r="E142" s="2">
-        <v>82090</v>
+        <v>81973</v>
       </c>
       <c r="F142" s="3">
-        <v>46063</v>
+        <v>46056</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>9</v>
@@ -4134,19 +4134,19 @@
         <v>2409</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C143" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D143" s="3">
-        <v>46063.7282468519</v>
+        <v>46056.7141110995</v>
       </c>
       <c r="E143" s="2">
-        <v>82093</v>
+        <v>81993</v>
       </c>
       <c r="F143" s="3">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>9</v>
@@ -4160,7 +4160,7 @@
         <v>2409</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C144" s="2">
         <v>89</v>
@@ -4169,10 +4169,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E144" s="2">
-        <v>82094</v>
+        <v>82090</v>
       </c>
       <c r="F144" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>9</v>
@@ -4186,7 +4186,7 @@
         <v>2409</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C145" s="2">
         <v>89</v>
@@ -4195,10 +4195,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E145" s="2">
-        <v>82098</v>
+        <v>82093</v>
       </c>
       <c r="F145" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>9</v>
@@ -4212,7 +4212,7 @@
         <v>2409</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C146" s="2">
         <v>89</v>
@@ -4221,7 +4221,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E146" s="2">
-        <v>82119</v>
+        <v>82094</v>
       </c>
       <c r="F146" s="3">
         <v>46064</v>
@@ -4238,7 +4238,7 @@
         <v>2409</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C147" s="2">
         <v>89</v>
@@ -4247,7 +4247,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E147" s="2">
-        <v>82120</v>
+        <v>82098</v>
       </c>
       <c r="F147" s="3">
         <v>46064</v>
@@ -4264,7 +4264,7 @@
         <v>2409</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C148" s="2">
         <v>89</v>
@@ -4273,10 +4273,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E148" s="2">
-        <v>82131</v>
+        <v>82119</v>
       </c>
       <c r="F148" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>9</v>
@@ -4290,19 +4290,19 @@
         <v>2409</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C149" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D149" s="3">
-        <v>46078.6817048032</v>
+        <v>46063.7282468519</v>
       </c>
       <c r="E149" s="2">
-        <v>82316</v>
+        <v>82120</v>
       </c>
       <c r="F149" s="3">
-        <v>46078</v>
+        <v>46064</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>9</v>
@@ -4316,19 +4316,19 @@
         <v>2409</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C150" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D150" s="3">
-        <v>46078.6817048032</v>
+        <v>46063.7282468519</v>
       </c>
       <c r="E150" s="2">
-        <v>82325</v>
+        <v>82131</v>
       </c>
       <c r="F150" s="3">
-        <v>46079</v>
+        <v>46065</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>9</v>
@@ -4342,7 +4342,7 @@
         <v>2409</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C151" s="2">
         <v>90</v>
@@ -4351,10 +4351,10 @@
         <v>46078.6817048032</v>
       </c>
       <c r="E151" s="2">
-        <v>82327</v>
+        <v>82316</v>
       </c>
       <c r="F151" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>9</v>
@@ -4368,19 +4368,19 @@
         <v>2409</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C152" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D152" s="3">
-        <v>46086.632572419</v>
+        <v>46078.6817048032</v>
       </c>
       <c r="E152" s="2">
-        <v>82471</v>
+        <v>82325</v>
       </c>
       <c r="F152" s="3">
-        <v>46086</v>
+        <v>46079</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>9</v>
@@ -4394,19 +4394,19 @@
         <v>2409</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C153" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D153" s="3">
-        <v>46086.632572419</v>
+        <v>46078.6817048032</v>
       </c>
       <c r="E153" s="2">
-        <v>82476</v>
+        <v>82327</v>
       </c>
       <c r="F153" s="3">
-        <v>46087</v>
+        <v>46079</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>9</v>
@@ -4420,19 +4420,19 @@
         <v>2409</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C154" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D154" s="3">
-        <v>46094.4767297338</v>
+        <v>46086.632572419</v>
       </c>
       <c r="E154" s="2">
-        <v>82634</v>
+        <v>82471</v>
       </c>
       <c r="F154" s="3">
-        <v>46094</v>
+        <v>46086</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>9</v>
@@ -4446,19 +4446,19 @@
         <v>2409</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C155" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D155" s="3">
-        <v>46094.4767297338</v>
+        <v>46086.632572419</v>
       </c>
       <c r="E155" s="2">
-        <v>82635</v>
+        <v>82476</v>
       </c>
       <c r="F155" s="3">
-        <v>46094</v>
+        <v>46087</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>9</v>
@@ -4472,7 +4472,7 @@
         <v>2409</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C156" s="2">
         <v>93</v>
@@ -4481,10 +4481,10 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E156" s="2">
-        <v>82679</v>
+        <v>82634</v>
       </c>
       <c r="F156" s="3">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>9</v>
@@ -4498,7 +4498,7 @@
         <v>2409</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C157" s="2">
         <v>93</v>
@@ -4507,10 +4507,10 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E157" s="2">
-        <v>82680</v>
+        <v>82635</v>
       </c>
       <c r="F157" s="3">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>9</v>
@@ -4524,7 +4524,7 @@
         <v>2409</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C158" s="2">
         <v>93</v>
@@ -4533,7 +4533,7 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E158" s="2">
-        <v>82681</v>
+        <v>82679</v>
       </c>
       <c r="F158" s="3">
         <v>46098</v>
@@ -4550,7 +4550,7 @@
         <v>2409</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C159" s="2">
         <v>93</v>
@@ -4559,7 +4559,7 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E159" s="2">
-        <v>82698</v>
+        <v>82680</v>
       </c>
       <c r="F159" s="3">
         <v>46098</v>
@@ -4576,7 +4576,7 @@
         <v>2409</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C160" s="2">
         <v>93</v>
@@ -4585,10 +4585,10 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E160" s="2">
-        <v>82705</v>
+        <v>82681</v>
       </c>
       <c r="F160" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>9</v>
@@ -4599,22 +4599,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="161">
       <c r="A161" s="2">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C161" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D161" s="3">
-        <v>46030.4179771875</v>
+        <v>46094.4767297338</v>
       </c>
       <c r="E161" s="2">
-        <v>81536</v>
+        <v>82698</v>
       </c>
       <c r="F161" s="3">
-        <v>46030</v>
+        <v>46098</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>9</v>
@@ -4625,22 +4625,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="162">
       <c r="A162" s="2">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C162" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D162" s="3">
-        <v>46030.4179771875</v>
+        <v>46094.4767297338</v>
       </c>
       <c r="E162" s="2">
-        <v>81538</v>
+        <v>82705</v>
       </c>
       <c r="F162" s="3">
-        <v>46030</v>
+        <v>46099</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>9</v>
@@ -4654,7 +4654,7 @@
         <v>2411</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C163" s="2">
         <v>77</v>
@@ -4663,7 +4663,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E163" s="2">
-        <v>81555</v>
+        <v>81536</v>
       </c>
       <c r="F163" s="3">
         <v>46030</v>
@@ -4680,7 +4680,7 @@
         <v>2411</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C164" s="2">
         <v>77</v>
@@ -4689,7 +4689,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E164" s="2">
-        <v>81556</v>
+        <v>81538</v>
       </c>
       <c r="F164" s="3">
         <v>46030</v>
@@ -4706,7 +4706,7 @@
         <v>2411</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C165" s="2">
         <v>77</v>
@@ -4715,7 +4715,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E165" s="2">
-        <v>81558</v>
+        <v>81555</v>
       </c>
       <c r="F165" s="3">
         <v>46030</v>
@@ -4732,19 +4732,19 @@
         <v>2411</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C166" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D166" s="3">
-        <v>46036.4079311574</v>
+        <v>46030.4179771875</v>
       </c>
       <c r="E166" s="2">
-        <v>81615</v>
+        <v>81556</v>
       </c>
       <c r="F166" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>9</v>
@@ -4758,19 +4758,19 @@
         <v>2411</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C167" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D167" s="3">
-        <v>46036.4079311574</v>
+        <v>46030.4179771875</v>
       </c>
       <c r="E167" s="2">
-        <v>81621</v>
+        <v>81558</v>
       </c>
       <c r="F167" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>9</v>
@@ -4784,7 +4784,7 @@
         <v>2411</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C168" s="2">
         <v>78</v>
@@ -4793,10 +4793,10 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E168" s="2">
-        <v>81647</v>
+        <v>81615</v>
       </c>
       <c r="F168" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>9</v>
@@ -4807,22 +4807,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="169">
       <c r="A169" s="2">
-        <v>2504</v>
+        <v>2411</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C169" s="2">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D169" s="3">
-        <v>46027.6983957986</v>
+        <v>46036.4079311574</v>
       </c>
       <c r="E169" s="2">
-        <v>81465</v>
+        <v>81621</v>
       </c>
       <c r="F169" s="3">
-        <v>46027</v>
+        <v>46036</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>9</v>
@@ -4833,28 +4833,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="170">
       <c r="A170" s="2">
-        <v>2504</v>
+        <v>2411</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C170" s="2">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D170" s="3">
-        <v>46027.6983957986</v>
+        <v>46036.4079311574</v>
       </c>
       <c r="E170" s="2">
-        <v>81466</v>
+        <v>81647</v>
       </c>
       <c r="F170" s="3">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="171">
@@ -4862,7 +4862,7 @@
         <v>2504</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C171" s="2">
         <v>44</v>
@@ -4871,7 +4871,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E171" s="2">
-        <v>81471</v>
+        <v>81465</v>
       </c>
       <c r="F171" s="3">
         <v>46027</v>
@@ -4888,7 +4888,7 @@
         <v>2504</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C172" s="2">
         <v>44</v>
@@ -4897,16 +4897,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E172" s="2">
-        <v>81488</v>
+        <v>81466</v>
       </c>
       <c r="F172" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="173">
@@ -4914,7 +4914,7 @@
         <v>2504</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C173" s="2">
         <v>44</v>
@@ -4923,10 +4923,10 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E173" s="2">
-        <v>81489</v>
+        <v>81471</v>
       </c>
       <c r="F173" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>9</v>
@@ -4940,7 +4940,7 @@
         <v>2504</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C174" s="2">
         <v>44</v>
@@ -4949,7 +4949,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E174" s="2">
-        <v>81490</v>
+        <v>81488</v>
       </c>
       <c r="F174" s="3">
         <v>46029</v>
@@ -4966,7 +4966,7 @@
         <v>2504</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C175" s="2">
         <v>44</v>
@@ -4975,7 +4975,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E175" s="2">
-        <v>81491</v>
+        <v>81489</v>
       </c>
       <c r="F175" s="3">
         <v>46029</v>
@@ -4992,19 +4992,19 @@
         <v>2504</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C176" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D176" s="3">
-        <v>46038.4184531713</v>
+        <v>46027.6983957986</v>
       </c>
       <c r="E176" s="2">
-        <v>81688</v>
+        <v>81490</v>
       </c>
       <c r="F176" s="3">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>9</v>
@@ -5018,19 +5018,19 @@
         <v>2504</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C177" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D177" s="3">
-        <v>46038.6993878241</v>
+        <v>46027.6983957986</v>
       </c>
       <c r="E177" s="2">
-        <v>81700</v>
+        <v>81491</v>
       </c>
       <c r="F177" s="3">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>9</v>
@@ -5044,16 +5044,16 @@
         <v>2504</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C178" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D178" s="3">
-        <v>46038.6993878241</v>
+        <v>46038.4184531713</v>
       </c>
       <c r="E178" s="2">
-        <v>81701</v>
+        <v>81688</v>
       </c>
       <c r="F178" s="3">
         <v>46038</v>
@@ -5070,7 +5070,7 @@
         <v>2504</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C179" s="2">
         <v>46</v>
@@ -5079,7 +5079,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E179" s="2">
-        <v>81702</v>
+        <v>81700</v>
       </c>
       <c r="F179" s="3">
         <v>46038</v>
@@ -5096,7 +5096,7 @@
         <v>2504</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C180" s="2">
         <v>46</v>
@@ -5105,7 +5105,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E180" s="2">
-        <v>81703</v>
+        <v>81701</v>
       </c>
       <c r="F180" s="3">
         <v>46038</v>
@@ -5122,7 +5122,7 @@
         <v>2504</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C181" s="2">
         <v>46</v>
@@ -5131,10 +5131,10 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E181" s="2">
-        <v>81734</v>
+        <v>81702</v>
       </c>
       <c r="F181" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>9</v>
@@ -5148,19 +5148,19 @@
         <v>2504</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C182" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D182" s="3">
-        <v>46050.7176682523</v>
+        <v>46038.6993878241</v>
       </c>
       <c r="E182" s="2">
-        <v>81914</v>
+        <v>81703</v>
       </c>
       <c r="F182" s="3">
-        <v>46051</v>
+        <v>46038</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>9</v>
@@ -5174,19 +5174,19 @@
         <v>2504</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C183" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D183" s="3">
-        <v>46050.7176682523</v>
+        <v>46038.6993878241</v>
       </c>
       <c r="E183" s="2">
-        <v>81915</v>
+        <v>81734</v>
       </c>
       <c r="F183" s="3">
-        <v>46051</v>
+        <v>46041</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>9</v>
@@ -5200,7 +5200,7 @@
         <v>2504</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C184" s="2">
         <v>47</v>
@@ -5209,7 +5209,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E184" s="2">
-        <v>81921</v>
+        <v>81914</v>
       </c>
       <c r="F184" s="3">
         <v>46051</v>
@@ -5226,19 +5226,19 @@
         <v>2504</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C185" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D185" s="3">
-        <v>46052.6247194676</v>
+        <v>46050.7176682523</v>
       </c>
       <c r="E185" s="2">
-        <v>81949</v>
+        <v>81915</v>
       </c>
       <c r="F185" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>9</v>
@@ -5252,19 +5252,19 @@
         <v>2504</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C186" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D186" s="3">
-        <v>46052.6247194676</v>
+        <v>46050.7176682523</v>
       </c>
       <c r="E186" s="2">
-        <v>81950</v>
+        <v>81921</v>
       </c>
       <c r="F186" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>9</v>
@@ -5278,7 +5278,7 @@
         <v>2504</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C187" s="2">
         <v>48</v>
@@ -5287,7 +5287,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E187" s="2">
-        <v>81951</v>
+        <v>81949</v>
       </c>
       <c r="F187" s="3">
         <v>46052</v>
@@ -5304,7 +5304,7 @@
         <v>2504</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C188" s="2">
         <v>48</v>
@@ -5313,7 +5313,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E188" s="2">
-        <v>81953</v>
+        <v>81950</v>
       </c>
       <c r="F188" s="3">
         <v>46052</v>
@@ -5330,19 +5330,19 @@
         <v>2504</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C189" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D189" s="3">
-        <v>46058.6976675694</v>
+        <v>46052.6247194676</v>
       </c>
       <c r="E189" s="2">
-        <v>82028</v>
+        <v>81951</v>
       </c>
       <c r="F189" s="3">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>9</v>
@@ -5356,19 +5356,19 @@
         <v>2504</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C190" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D190" s="3">
-        <v>46058.6976675694</v>
+        <v>46052.6247194676</v>
       </c>
       <c r="E190" s="2">
-        <v>82029</v>
+        <v>81953</v>
       </c>
       <c r="F190" s="3">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>9</v>
@@ -5382,7 +5382,7 @@
         <v>2504</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C191" s="2">
         <v>49</v>
@@ -5391,10 +5391,10 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E191" s="2">
-        <v>82040</v>
+        <v>82028</v>
       </c>
       <c r="F191" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>9</v>
@@ -5408,7 +5408,7 @@
         <v>2504</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C192" s="2">
         <v>49</v>
@@ -5417,10 +5417,10 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E192" s="2">
-        <v>82041</v>
+        <v>82029</v>
       </c>
       <c r="F192" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>9</v>
@@ -5434,7 +5434,7 @@
         <v>2504</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C193" s="2">
         <v>49</v>
@@ -5443,7 +5443,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E193" s="2">
-        <v>82051</v>
+        <v>82040</v>
       </c>
       <c r="F193" s="3">
         <v>46059</v>
@@ -5460,19 +5460,19 @@
         <v>2504</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C194" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D194" s="3">
-        <v>46065.6309066782</v>
+        <v>46058.6976675694</v>
       </c>
       <c r="E194" s="2">
-        <v>82168</v>
+        <v>82041</v>
       </c>
       <c r="F194" s="3">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>9</v>
@@ -5486,25 +5486,25 @@
         <v>2504</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C195" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D195" s="3">
-        <v>46065.6309066782</v>
+        <v>46058.6976675694</v>
       </c>
       <c r="E195" s="2">
-        <v>82170</v>
+        <v>82051</v>
       </c>
       <c r="F195" s="3">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="196">
@@ -5512,7 +5512,7 @@
         <v>2504</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C196" s="2">
         <v>50</v>
@@ -5521,7 +5521,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E196" s="2">
-        <v>82171</v>
+        <v>82168</v>
       </c>
       <c r="F196" s="3">
         <v>46066</v>
@@ -5538,7 +5538,7 @@
         <v>2504</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C197" s="2">
         <v>50</v>
@@ -5547,16 +5547,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E197" s="2">
-        <v>82172</v>
+        <v>82170</v>
       </c>
       <c r="F197" s="3">
         <v>46066</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="198">
@@ -5564,7 +5564,7 @@
         <v>2504</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C198" s="2">
         <v>50</v>
@@ -5573,7 +5573,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E198" s="2">
-        <v>82175</v>
+        <v>82171</v>
       </c>
       <c r="F198" s="3">
         <v>46066</v>
@@ -5590,7 +5590,7 @@
         <v>2504</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C199" s="2">
         <v>50</v>
@@ -5599,7 +5599,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E199" s="2">
-        <v>82176</v>
+        <v>82172</v>
       </c>
       <c r="F199" s="3">
         <v>46066</v>
@@ -5616,19 +5616,19 @@
         <v>2504</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C200" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D200" s="3">
-        <v>46072.5909779051</v>
+        <v>46065.6309066782</v>
       </c>
       <c r="E200" s="2">
-        <v>82206</v>
+        <v>82175</v>
       </c>
       <c r="F200" s="3">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>9</v>
@@ -5642,19 +5642,19 @@
         <v>2504</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C201" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D201" s="3">
-        <v>46077.7262228935</v>
+        <v>46065.6309066782</v>
       </c>
       <c r="E201" s="2">
-        <v>82289</v>
+        <v>82176</v>
       </c>
       <c r="F201" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>9</v>
@@ -5668,19 +5668,19 @@
         <v>2504</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C202" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D202" s="3">
-        <v>46077.7262228935</v>
+        <v>46072.5909779051</v>
       </c>
       <c r="E202" s="2">
-        <v>82290</v>
+        <v>82206</v>
       </c>
       <c r="F202" s="3">
-        <v>46077</v>
+        <v>46072</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>9</v>
@@ -5694,19 +5694,19 @@
         <v>2504</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C203" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D203" s="3">
-        <v>46078.6799843634</v>
+        <v>46077.7262228935</v>
       </c>
       <c r="E203" s="2">
-        <v>82318</v>
+        <v>82289</v>
       </c>
       <c r="F203" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>9</v>
@@ -5720,19 +5720,19 @@
         <v>2504</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C204" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D204" s="3">
-        <v>46080.6294471412</v>
+        <v>46077.7262228935</v>
       </c>
       <c r="E204" s="2">
-        <v>82368</v>
+        <v>82290</v>
       </c>
       <c r="F204" s="3">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>9</v>
@@ -5746,19 +5746,19 @@
         <v>2504</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C205" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D205" s="3">
-        <v>46084.741264838</v>
+        <v>46078.6799843634</v>
       </c>
       <c r="E205" s="2">
-        <v>82425</v>
+        <v>82318</v>
       </c>
       <c r="F205" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>9</v>
@@ -5772,19 +5772,19 @@
         <v>2504</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C206" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D206" s="3">
-        <v>46084.741264838</v>
+        <v>46080.6294471412</v>
       </c>
       <c r="E206" s="2">
-        <v>82426</v>
+        <v>82368</v>
       </c>
       <c r="F206" s="3">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>9</v>
@@ -5798,7 +5798,7 @@
         <v>2504</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C207" s="2">
         <v>55</v>
@@ -5807,10 +5807,10 @@
         <v>46084.741264838</v>
       </c>
       <c r="E207" s="2">
-        <v>82430</v>
+        <v>82425</v>
       </c>
       <c r="F207" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>9</v>
@@ -5824,7 +5824,7 @@
         <v>2504</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C208" s="2">
         <v>55</v>
@@ -5833,10 +5833,10 @@
         <v>46084.741264838</v>
       </c>
       <c r="E208" s="2">
-        <v>82431</v>
+        <v>82426</v>
       </c>
       <c r="F208" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>9</v>
@@ -5850,19 +5850,19 @@
         <v>2504</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C209" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D209" s="3">
-        <v>46097.4509044907</v>
+        <v>46084.741264838</v>
       </c>
       <c r="E209" s="2">
-        <v>82654</v>
+        <v>82430</v>
       </c>
       <c r="F209" s="3">
-        <v>46097</v>
+        <v>46085</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>9</v>
@@ -5876,19 +5876,19 @@
         <v>2504</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C210" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D210" s="3">
-        <v>46097.4509044907</v>
+        <v>46084.741264838</v>
       </c>
       <c r="E210" s="2">
-        <v>82660</v>
+        <v>82431</v>
       </c>
       <c r="F210" s="3">
-        <v>46097</v>
+        <v>46085</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>9</v>
@@ -5902,7 +5902,7 @@
         <v>2504</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C211" s="2">
         <v>56</v>
@@ -5911,7 +5911,7 @@
         <v>46097.4509044907</v>
       </c>
       <c r="E211" s="2">
-        <v>82661</v>
+        <v>82654</v>
       </c>
       <c r="F211" s="3">
         <v>46097</v>
@@ -5928,19 +5928,19 @@
         <v>2504</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C212" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D212" s="3">
-        <v>46098.5062577778</v>
+        <v>46097.4509044907</v>
       </c>
       <c r="E212" s="2">
-        <v>82690</v>
+        <v>82660</v>
       </c>
       <c r="F212" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>9</v>
@@ -5954,19 +5954,19 @@
         <v>2504</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C213" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D213" s="3">
-        <v>46098.5062577778</v>
+        <v>46097.4509044907</v>
       </c>
       <c r="E213" s="2">
-        <v>82714</v>
+        <v>82661</v>
       </c>
       <c r="F213" s="3">
-        <v>46099</v>
+        <v>46097</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>9</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="214">
       <c r="A214" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C214" s="2">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D214" s="3">
-        <v>46041.6648751157</v>
+        <v>46098.5062577778</v>
       </c>
       <c r="E214" s="2">
-        <v>81743</v>
+        <v>82690</v>
       </c>
       <c r="F214" s="3">
-        <v>46041</v>
+        <v>46098</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>9</v>
@@ -6003,22 +6003,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="215">
       <c r="A215" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C215" s="2">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D215" s="3">
-        <v>46041.6648751157</v>
+        <v>46098.5062577778</v>
       </c>
       <c r="E215" s="2">
-        <v>81744</v>
+        <v>82714</v>
       </c>
       <c r="F215" s="3">
-        <v>46041</v>
+        <v>46099</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>9</v>
@@ -6032,7 +6032,7 @@
         <v>2505</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C216" s="2">
         <v>42</v>
@@ -6041,7 +6041,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E216" s="2">
-        <v>81745</v>
+        <v>81743</v>
       </c>
       <c r="F216" s="3">
         <v>46041</v>
@@ -6058,7 +6058,7 @@
         <v>2505</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C217" s="2">
         <v>42</v>
@@ -6067,10 +6067,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E217" s="2">
-        <v>81746</v>
+        <v>81744</v>
       </c>
       <c r="F217" s="3">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>9</v>
@@ -6084,7 +6084,7 @@
         <v>2505</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C218" s="2">
         <v>42</v>
@@ -6093,10 +6093,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E218" s="2">
-        <v>81751</v>
+        <v>81745</v>
       </c>
       <c r="F218" s="3">
-        <v>46043</v>
+        <v>46041</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>9</v>
@@ -6110,7 +6110,7 @@
         <v>2505</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C219" s="2">
         <v>42</v>
@@ -6119,10 +6119,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E219" s="2">
-        <v>81753</v>
+        <v>81746</v>
       </c>
       <c r="F219" s="3">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>9</v>
@@ -6136,7 +6136,7 @@
         <v>2505</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C220" s="2">
         <v>42</v>
@@ -6145,7 +6145,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E220" s="2">
-        <v>81754</v>
+        <v>81751</v>
       </c>
       <c r="F220" s="3">
         <v>46043</v>
@@ -6162,7 +6162,7 @@
         <v>2505</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C221" s="2">
         <v>42</v>
@@ -6171,7 +6171,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E221" s="2">
-        <v>81755</v>
+        <v>81753</v>
       </c>
       <c r="F221" s="3">
         <v>46043</v>
@@ -6188,7 +6188,7 @@
         <v>2505</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C222" s="2">
         <v>42</v>
@@ -6197,7 +6197,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E222" s="2">
-        <v>81766</v>
+        <v>81754</v>
       </c>
       <c r="F222" s="3">
         <v>46043</v>
@@ -6214,19 +6214,19 @@
         <v>2505</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C223" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D223" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E223" s="2">
-        <v>82088</v>
+        <v>81755</v>
       </c>
       <c r="F223" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>9</v>
@@ -6240,19 +6240,19 @@
         <v>2505</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C224" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D224" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E224" s="2">
-        <v>82089</v>
+        <v>81766</v>
       </c>
       <c r="F224" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>9</v>
@@ -6266,7 +6266,7 @@
         <v>2505</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C225" s="2">
         <v>43</v>
@@ -6275,10 +6275,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E225" s="2">
-        <v>82163</v>
+        <v>82088</v>
       </c>
       <c r="F225" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>9</v>
@@ -6292,7 +6292,7 @@
         <v>2505</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C226" s="2">
         <v>43</v>
@@ -6301,10 +6301,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E226" s="2">
-        <v>82179</v>
+        <v>82089</v>
       </c>
       <c r="F226" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>9</v>
@@ -6318,7 +6318,7 @@
         <v>2505</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C227" s="2">
         <v>43</v>
@@ -6327,7 +6327,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E227" s="2">
-        <v>82193</v>
+        <v>82163</v>
       </c>
       <c r="F227" s="3">
         <v>46066</v>
@@ -6344,19 +6344,19 @@
         <v>2505</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C228" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D228" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E228" s="2">
-        <v>82250</v>
+        <v>82179</v>
       </c>
       <c r="F228" s="3">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>9</v>
@@ -6370,19 +6370,19 @@
         <v>2505</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C229" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D229" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E229" s="2">
-        <v>82266</v>
+        <v>82193</v>
       </c>
       <c r="F229" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>9</v>
@@ -6396,7 +6396,7 @@
         <v>2505</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C230" s="2">
         <v>44</v>
@@ -6405,10 +6405,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E230" s="2">
-        <v>82295</v>
+        <v>82250</v>
       </c>
       <c r="F230" s="3">
-        <v>46078</v>
+        <v>46073</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>9</v>
@@ -6422,7 +6422,7 @@
         <v>2505</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C231" s="2">
         <v>44</v>
@@ -6431,10 +6431,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E231" s="2">
-        <v>82296</v>
+        <v>82266</v>
       </c>
       <c r="F231" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>9</v>
@@ -6448,7 +6448,7 @@
         <v>2505</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C232" s="2">
         <v>44</v>
@@ -6457,16 +6457,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E232" s="2">
-        <v>82332</v>
+        <v>82295</v>
       </c>
       <c r="F232" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="233">
@@ -6474,7 +6474,7 @@
         <v>2505</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C233" s="2">
         <v>44</v>
@@ -6483,10 +6483,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E233" s="2">
-        <v>82339</v>
+        <v>82296</v>
       </c>
       <c r="F233" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>9</v>
@@ -6500,25 +6500,25 @@
         <v>2505</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C234" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D234" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E234" s="2">
-        <v>82266</v>
+        <v>82332</v>
       </c>
       <c r="F234" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="235">
@@ -6526,19 +6526,19 @@
         <v>2505</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C235" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D235" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E235" s="2">
-        <v>82273</v>
+        <v>82339</v>
       </c>
       <c r="F235" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>9</v>
@@ -6552,7 +6552,7 @@
         <v>2505</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C236" s="2">
         <v>45</v>
@@ -6561,10 +6561,10 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E236" s="2">
-        <v>82294</v>
+        <v>82266</v>
       </c>
       <c r="F236" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>9</v>
@@ -6578,19 +6578,19 @@
         <v>2505</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C237" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D237" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E237" s="2">
-        <v>82411</v>
+        <v>82273</v>
       </c>
       <c r="F237" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>9</v>
@@ -6604,19 +6604,19 @@
         <v>2505</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C238" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D238" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E238" s="2">
-        <v>82432</v>
+        <v>82294</v>
       </c>
       <c r="F238" s="3">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>9</v>
@@ -6630,7 +6630,7 @@
         <v>2505</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C239" s="2">
         <v>46</v>
@@ -6639,10 +6639,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E239" s="2">
-        <v>82473</v>
+        <v>82411</v>
       </c>
       <c r="F239" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>9</v>
@@ -6656,7 +6656,7 @@
         <v>2505</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C240" s="2">
         <v>46</v>
@@ -6665,10 +6665,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E240" s="2">
-        <v>82474</v>
+        <v>82432</v>
       </c>
       <c r="F240" s="3">
-        <v>46087</v>
+        <v>46085</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>9</v>
@@ -6682,19 +6682,19 @@
         <v>2505</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C241" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D241" s="3">
-        <v>46093.5009358681</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E241" s="2">
-        <v>82594</v>
+        <v>82473</v>
       </c>
       <c r="F241" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>9</v>
@@ -6708,19 +6708,19 @@
         <v>2505</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C242" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D242" s="3">
-        <v>46093.5009358681</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E242" s="2">
-        <v>82595</v>
+        <v>82474</v>
       </c>
       <c r="F242" s="3">
-        <v>46093</v>
+        <v>46087</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>9</v>
@@ -6734,7 +6734,7 @@
         <v>2505</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C243" s="2">
         <v>47</v>
@@ -6743,10 +6743,10 @@
         <v>46093.5009358681</v>
       </c>
       <c r="E243" s="2">
-        <v>82657</v>
+        <v>82594</v>
       </c>
       <c r="F243" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>9</v>
@@ -6760,19 +6760,19 @@
         <v>2505</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C244" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D244" s="3">
-        <v>46098.5034667708</v>
+        <v>46093.5009358681</v>
       </c>
       <c r="E244" s="2">
-        <v>82686</v>
+        <v>82595</v>
       </c>
       <c r="F244" s="3">
-        <v>46098</v>
+        <v>46093</v>
       </c>
       <c r="G244" s="1" t="s">
         <v>9</v>
@@ -6786,19 +6786,19 @@
         <v>2505</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C245" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D245" s="3">
-        <v>46098.5034667708</v>
+        <v>46093.5009358681</v>
       </c>
       <c r="E245" s="2">
-        <v>82687</v>
+        <v>82657</v>
       </c>
       <c r="F245" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>9</v>
@@ -6812,7 +6812,7 @@
         <v>2505</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C246" s="2">
         <v>48</v>
@@ -6821,10 +6821,10 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E246" s="2">
-        <v>82722</v>
+        <v>82686</v>
       </c>
       <c r="F246" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>9</v>
@@ -6838,7 +6838,7 @@
         <v>2505</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C247" s="2">
         <v>48</v>
@@ -6847,10 +6847,10 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E247" s="2">
-        <v>82723</v>
+        <v>82687</v>
       </c>
       <c r="F247" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>9</v>
@@ -6864,7 +6864,7 @@
         <v>2505</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C248" s="2">
         <v>48</v>
@@ -6873,10 +6873,10 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E248" s="2">
-        <v>82755</v>
+        <v>82722</v>
       </c>
       <c r="F248" s="3">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>9</v>
@@ -6887,22 +6887,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="249">
       <c r="A249" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C249" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D249" s="3">
-        <v>46044.6368950926</v>
+        <v>46098.5034667708</v>
       </c>
       <c r="E249" s="2">
-        <v>81802</v>
+        <v>82723</v>
       </c>
       <c r="F249" s="3">
-        <v>46044</v>
+        <v>46099</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>9</v>
@@ -6913,22 +6913,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="250">
       <c r="A250" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C250" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D250" s="3">
-        <v>46044.6368950926</v>
+        <v>46098.5034667708</v>
       </c>
       <c r="E250" s="2">
-        <v>81803</v>
+        <v>82755</v>
       </c>
       <c r="F250" s="3">
-        <v>46044</v>
+        <v>46101</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>9</v>
@@ -6942,7 +6942,7 @@
         <v>2506</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C251" s="2">
         <v>27</v>
@@ -6951,7 +6951,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E251" s="2">
-        <v>81804</v>
+        <v>81802</v>
       </c>
       <c r="F251" s="3">
         <v>46044</v>
@@ -6968,7 +6968,7 @@
         <v>2506</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C252" s="2">
         <v>27</v>
@@ -6977,7 +6977,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E252" s="2">
-        <v>81806</v>
+        <v>81803</v>
       </c>
       <c r="F252" s="3">
         <v>46044</v>
@@ -6994,7 +6994,7 @@
         <v>2506</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C253" s="2">
         <v>27</v>
@@ -7003,7 +7003,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E253" s="2">
-        <v>81807</v>
+        <v>81804</v>
       </c>
       <c r="F253" s="3">
         <v>46044</v>
@@ -7020,7 +7020,7 @@
         <v>2506</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C254" s="2">
         <v>27</v>
@@ -7029,10 +7029,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E254" s="2">
-        <v>81812</v>
+        <v>81806</v>
       </c>
       <c r="F254" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>9</v>
@@ -7046,7 +7046,7 @@
         <v>2506</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C255" s="2">
         <v>27</v>
@@ -7055,10 +7055,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E255" s="2">
-        <v>81813</v>
+        <v>81807</v>
       </c>
       <c r="F255" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>9</v>
@@ -7072,7 +7072,7 @@
         <v>2506</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C256" s="2">
         <v>27</v>
@@ -7081,7 +7081,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E256" s="2">
-        <v>81814</v>
+        <v>81812</v>
       </c>
       <c r="F256" s="3">
         <v>46045</v>
@@ -7098,7 +7098,7 @@
         <v>2506</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C257" s="2">
         <v>27</v>
@@ -7107,7 +7107,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E257" s="2">
-        <v>81818</v>
+        <v>81813</v>
       </c>
       <c r="F257" s="3">
         <v>46045</v>
@@ -7124,7 +7124,7 @@
         <v>2506</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C258" s="2">
         <v>27</v>
@@ -7133,7 +7133,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E258" s="2">
-        <v>81822</v>
+        <v>81814</v>
       </c>
       <c r="F258" s="3">
         <v>46045</v>
@@ -7150,7 +7150,7 @@
         <v>2506</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C259" s="2">
         <v>27</v>
@@ -7159,7 +7159,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E259" s="2">
-        <v>81833</v>
+        <v>81818</v>
       </c>
       <c r="F259" s="3">
         <v>46045</v>
@@ -7176,7 +7176,7 @@
         <v>2506</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C260" s="2">
         <v>27</v>
@@ -7185,7 +7185,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E260" s="2">
-        <v>81841</v>
+        <v>81822</v>
       </c>
       <c r="F260" s="3">
         <v>46045</v>
@@ -7202,19 +7202,19 @@
         <v>2506</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C261" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D261" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E261" s="2">
-        <v>81928</v>
+        <v>81833</v>
       </c>
       <c r="F261" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>9</v>
@@ -7228,19 +7228,19 @@
         <v>2506</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C262" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D262" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E262" s="2">
-        <v>81929</v>
+        <v>81841</v>
       </c>
       <c r="F262" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>9</v>
@@ -7254,7 +7254,7 @@
         <v>2506</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C263" s="2">
         <v>28</v>
@@ -7263,7 +7263,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E263" s="2">
-        <v>81930</v>
+        <v>81928</v>
       </c>
       <c r="F263" s="3">
         <v>46052</v>
@@ -7280,7 +7280,7 @@
         <v>2506</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C264" s="2">
         <v>28</v>
@@ -7289,7 +7289,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E264" s="2">
-        <v>81932</v>
+        <v>81929</v>
       </c>
       <c r="F264" s="3">
         <v>46052</v>
@@ -7306,7 +7306,7 @@
         <v>2506</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C265" s="2">
         <v>28</v>
@@ -7315,7 +7315,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E265" s="2">
-        <v>81933</v>
+        <v>81930</v>
       </c>
       <c r="F265" s="3">
         <v>46052</v>
@@ -7332,7 +7332,7 @@
         <v>2506</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C266" s="2">
         <v>28</v>
@@ -7341,7 +7341,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E266" s="2">
-        <v>81934</v>
+        <v>81932</v>
       </c>
       <c r="F266" s="3">
         <v>46052</v>
@@ -7358,7 +7358,7 @@
         <v>2506</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C267" s="2">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E267" s="2">
-        <v>81935</v>
+        <v>81933</v>
       </c>
       <c r="F267" s="3">
         <v>46052</v>
@@ -7384,7 +7384,7 @@
         <v>2506</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C268" s="2">
         <v>28</v>
@@ -7393,7 +7393,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E268" s="2">
-        <v>81936</v>
+        <v>81934</v>
       </c>
       <c r="F268" s="3">
         <v>46052</v>
@@ -7410,19 +7410,19 @@
         <v>2506</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C269" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D269" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E269" s="2">
-        <v>82222</v>
+        <v>81935</v>
       </c>
       <c r="F269" s="3">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>9</v>
@@ -7436,19 +7436,19 @@
         <v>2506</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C270" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D270" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E270" s="2">
-        <v>82226</v>
+        <v>81936</v>
       </c>
       <c r="F270" s="3">
-        <v>46073</v>
+        <v>46052</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>9</v>
@@ -7462,7 +7462,7 @@
         <v>2506</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C271" s="2">
         <v>29</v>
@@ -7471,10 +7471,10 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E271" s="2">
-        <v>82229</v>
+        <v>82222</v>
       </c>
       <c r="F271" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>9</v>
@@ -7488,16 +7488,16 @@
         <v>2506</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C272" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D272" s="3">
-        <v>46073.5838834375</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E272" s="2">
-        <v>82246</v>
+        <v>82226</v>
       </c>
       <c r="F272" s="3">
         <v>46073</v>
@@ -7514,19 +7514,19 @@
         <v>2506</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C273" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D273" s="3">
-        <v>46080.6289065162</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E273" s="2">
-        <v>82387</v>
+        <v>82229</v>
       </c>
       <c r="F273" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>9</v>
@@ -7540,19 +7540,19 @@
         <v>2506</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C274" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D274" s="3">
-        <v>46093.4978086806</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E274" s="2">
-        <v>82590</v>
+        <v>82246</v>
       </c>
       <c r="F274" s="3">
-        <v>46093</v>
+        <v>46073</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>9</v>
@@ -7566,25 +7566,25 @@
         <v>2506</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C275" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D275" s="3">
-        <v>46093.4978086806</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E275" s="2">
-        <v>82591</v>
+        <v>82387</v>
       </c>
       <c r="F275" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="276">
@@ -7592,7 +7592,7 @@
         <v>2506</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C276" s="2">
         <v>32</v>
@@ -7601,7 +7601,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E276" s="2">
-        <v>82592</v>
+        <v>82590</v>
       </c>
       <c r="F276" s="3">
         <v>46093</v>
@@ -7618,7 +7618,7 @@
         <v>2506</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C277" s="2">
         <v>32</v>
@@ -7627,16 +7627,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E277" s="2">
-        <v>82593</v>
+        <v>82591</v>
       </c>
       <c r="F277" s="3">
         <v>46093</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="278">
@@ -7644,7 +7644,7 @@
         <v>2506</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C278" s="2">
         <v>32</v>
@@ -7653,7 +7653,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E278" s="2">
-        <v>82600</v>
+        <v>82592</v>
       </c>
       <c r="F278" s="3">
         <v>46093</v>
@@ -7670,7 +7670,7 @@
         <v>2506</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C279" s="2">
         <v>32</v>
@@ -7679,7 +7679,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E279" s="2">
-        <v>82603</v>
+        <v>82593</v>
       </c>
       <c r="F279" s="3">
         <v>46093</v>
@@ -7696,7 +7696,7 @@
         <v>2506</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C280" s="2">
         <v>32</v>
@@ -7705,7 +7705,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E280" s="2">
-        <v>82604</v>
+        <v>82600</v>
       </c>
       <c r="F280" s="3">
         <v>46093</v>
@@ -7722,7 +7722,7 @@
         <v>2506</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C281" s="2">
         <v>32</v>
@@ -7731,7 +7731,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E281" s="2">
-        <v>82605</v>
+        <v>82603</v>
       </c>
       <c r="F281" s="3">
         <v>46093</v>
@@ -7745,22 +7745,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="282">
       <c r="A282" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C282" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D282" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E282" s="2">
-        <v>81478</v>
+        <v>82604</v>
       </c>
       <c r="F282" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>9</v>
@@ -7771,22 +7771,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="283">
       <c r="A283" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C283" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D283" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E283" s="2">
-        <v>81479</v>
+        <v>82605</v>
       </c>
       <c r="F283" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>9</v>
@@ -7800,7 +7800,7 @@
         <v>2507</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C284" s="2">
         <v>26</v>
@@ -7809,7 +7809,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E284" s="2">
-        <v>81480</v>
+        <v>81478</v>
       </c>
       <c r="F284" s="3">
         <v>46029</v>
@@ -7826,7 +7826,7 @@
         <v>2507</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C285" s="2">
         <v>26</v>
@@ -7835,7 +7835,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E285" s="2">
-        <v>81497</v>
+        <v>81479</v>
       </c>
       <c r="F285" s="3">
         <v>46029</v>
@@ -7852,7 +7852,7 @@
         <v>2507</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C286" s="2">
         <v>26</v>
@@ -7861,7 +7861,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E286" s="2">
-        <v>81498</v>
+        <v>81480</v>
       </c>
       <c r="F286" s="3">
         <v>46029</v>
@@ -7878,7 +7878,7 @@
         <v>2507</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C287" s="2">
         <v>26</v>
@@ -7887,7 +7887,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E287" s="2">
-        <v>81499</v>
+        <v>81497</v>
       </c>
       <c r="F287" s="3">
         <v>46029</v>
@@ -7904,7 +7904,7 @@
         <v>2507</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C288" s="2">
         <v>26</v>
@@ -7913,7 +7913,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E288" s="2">
-        <v>81500</v>
+        <v>81498</v>
       </c>
       <c r="F288" s="3">
         <v>46029</v>
@@ -7930,19 +7930,19 @@
         <v>2507</v>
       </c>
       <c r="B289" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C289" s="2">
         <v>26</v>
       </c>
-      <c r="C289" s="2">
-        <v>27</v>
-      </c>
       <c r="D289" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E289" s="2">
-        <v>81878</v>
+        <v>81499</v>
       </c>
       <c r="F289" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>9</v>
@@ -7956,19 +7956,19 @@
         <v>2507</v>
       </c>
       <c r="B290" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C290" s="2">
         <v>26</v>
       </c>
-      <c r="C290" s="2">
-        <v>27</v>
-      </c>
       <c r="D290" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E290" s="2">
-        <v>81879</v>
+        <v>81500</v>
       </c>
       <c r="F290" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>9</v>
@@ -7982,7 +7982,7 @@
         <v>2507</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C291" s="2">
         <v>27</v>
@@ -7991,10 +7991,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E291" s="2">
-        <v>81885</v>
+        <v>81878</v>
       </c>
       <c r="F291" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>9</v>
@@ -8008,7 +8008,7 @@
         <v>2507</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C292" s="2">
         <v>27</v>
@@ -8017,10 +8017,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E292" s="2">
-        <v>81886</v>
+        <v>81879</v>
       </c>
       <c r="F292" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>9</v>
@@ -8034,19 +8034,19 @@
         <v>2507</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C293" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D293" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E293" s="2">
-        <v>82068</v>
+        <v>81885</v>
       </c>
       <c r="F293" s="3">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>9</v>
@@ -8060,19 +8060,19 @@
         <v>2507</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C294" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D294" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E294" s="2">
-        <v>82072</v>
+        <v>81886</v>
       </c>
       <c r="F294" s="3">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>9</v>
@@ -8086,7 +8086,7 @@
         <v>2507</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C295" s="2">
         <v>28</v>
@@ -8095,10 +8095,10 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E295" s="2">
-        <v>82076</v>
+        <v>82068</v>
       </c>
       <c r="F295" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>9</v>
@@ -8112,7 +8112,7 @@
         <v>2507</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C296" s="2">
         <v>28</v>
@@ -8121,7 +8121,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E296" s="2">
-        <v>82078</v>
+        <v>82072</v>
       </c>
       <c r="F296" s="3">
         <v>46063</v>
@@ -8138,19 +8138,19 @@
         <v>2507</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C297" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D297" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E297" s="2">
-        <v>82287</v>
+        <v>82076</v>
       </c>
       <c r="F297" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>9</v>
@@ -8164,19 +8164,19 @@
         <v>2507</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C298" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D298" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E298" s="2">
-        <v>82288</v>
+        <v>82078</v>
       </c>
       <c r="F298" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>9</v>
@@ -8190,7 +8190,7 @@
         <v>2507</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C299" s="2">
         <v>29</v>
@@ -8199,10 +8199,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E299" s="2">
-        <v>82298</v>
+        <v>82287</v>
       </c>
       <c r="F299" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>9</v>
@@ -8216,7 +8216,7 @@
         <v>2507</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C300" s="2">
         <v>29</v>
@@ -8225,10 +8225,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E300" s="2">
-        <v>82301</v>
+        <v>82288</v>
       </c>
       <c r="F300" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>9</v>
@@ -8242,7 +8242,7 @@
         <v>2507</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C301" s="2">
         <v>29</v>
@@ -8251,7 +8251,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E301" s="2">
-        <v>82304</v>
+        <v>82298</v>
       </c>
       <c r="F301" s="3">
         <v>46078</v>
@@ -8268,7 +8268,7 @@
         <v>2507</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C302" s="2">
         <v>29</v>
@@ -8277,7 +8277,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E302" s="2">
-        <v>82308</v>
+        <v>82301</v>
       </c>
       <c r="F302" s="3">
         <v>46078</v>
@@ -8294,19 +8294,19 @@
         <v>2507</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C303" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D303" s="3">
-        <v>46080.628344919</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E303" s="2">
-        <v>82373</v>
+        <v>82304</v>
       </c>
       <c r="F303" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>9</v>
@@ -8320,19 +8320,19 @@
         <v>2507</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C304" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D304" s="3">
-        <v>46085.6581644213</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E304" s="2">
-        <v>82445</v>
+        <v>82308</v>
       </c>
       <c r="F304" s="3">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>9</v>
@@ -8346,19 +8346,19 @@
         <v>2507</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C305" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D305" s="3">
-        <v>46085.6581644213</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E305" s="2">
-        <v>82447</v>
+        <v>82373</v>
       </c>
       <c r="F305" s="3">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>9</v>
@@ -8372,7 +8372,7 @@
         <v>2507</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C306" s="2">
         <v>31</v>
@@ -8381,10 +8381,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E306" s="2">
-        <v>82453</v>
+        <v>82445</v>
       </c>
       <c r="F306" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>9</v>
@@ -8398,7 +8398,7 @@
         <v>2507</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C307" s="2">
         <v>31</v>
@@ -8407,10 +8407,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E307" s="2">
-        <v>82468</v>
+        <v>82447</v>
       </c>
       <c r="F307" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>9</v>
@@ -8424,19 +8424,19 @@
         <v>2507</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C308" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D308" s="3">
-        <v>46098.6669450579</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E308" s="2">
-        <v>82697</v>
+        <v>82453</v>
       </c>
       <c r="F308" s="3">
-        <v>46098</v>
+        <v>46086</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>9</v>
@@ -8450,19 +8450,19 @@
         <v>2507</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C309" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D309" s="3">
-        <v>46098.6669450579</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E309" s="2">
-        <v>82706</v>
+        <v>82468</v>
       </c>
       <c r="F309" s="3">
-        <v>46099</v>
+        <v>46086</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>9</v>
@@ -8476,7 +8476,7 @@
         <v>2507</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C310" s="2">
         <v>32</v>
@@ -8485,10 +8485,10 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E310" s="2">
-        <v>82707</v>
+        <v>82697</v>
       </c>
       <c r="F310" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>9</v>
@@ -8502,7 +8502,7 @@
         <v>2507</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C311" s="2">
         <v>32</v>
@@ -8511,7 +8511,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E311" s="2">
-        <v>82708</v>
+        <v>82706</v>
       </c>
       <c r="F311" s="3">
         <v>46099</v>
@@ -8528,7 +8528,7 @@
         <v>2507</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C312" s="2">
         <v>32</v>
@@ -8537,7 +8537,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E312" s="2">
-        <v>82709</v>
+        <v>82707</v>
       </c>
       <c r="F312" s="3">
         <v>46099</v>
@@ -8554,7 +8554,7 @@
         <v>2507</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C313" s="2">
         <v>32</v>
@@ -8563,7 +8563,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E313" s="2">
-        <v>82712</v>
+        <v>82708</v>
       </c>
       <c r="F313" s="3">
         <v>46099</v>
@@ -8580,7 +8580,7 @@
         <v>2507</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C314" s="2">
         <v>32</v>
@@ -8589,7 +8589,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E314" s="2">
-        <v>82713</v>
+        <v>82709</v>
       </c>
       <c r="F314" s="3">
         <v>46099</v>
@@ -8606,19 +8606,19 @@
         <v>2507</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C315" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D315" s="3">
-        <v>46101.4050215162</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E315" s="2">
-        <v>82756</v>
+        <v>82712</v>
       </c>
       <c r="F315" s="3">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>9</v>
@@ -8629,22 +8629,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="316">
       <c r="A316" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C316" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D316" s="3">
-        <v>46029.6400966782</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E316" s="2">
-        <v>81506</v>
+        <v>82713</v>
       </c>
       <c r="F316" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>9</v>
@@ -8655,22 +8655,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="317">
       <c r="A317" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C317" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D317" s="3">
-        <v>46029.6400966782</v>
+        <v>46101.4050215162</v>
       </c>
       <c r="E317" s="2">
-        <v>81507</v>
+        <v>82756</v>
       </c>
       <c r="F317" s="3">
-        <v>46029</v>
+        <v>46101</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>9</v>
@@ -8681,28 +8681,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="318">
       <c r="A318" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C318" s="2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D318" s="3">
-        <v>46029.6400966782</v>
+        <v>46104.4364179167</v>
       </c>
       <c r="E318" s="2">
-        <v>81524</v>
+        <v>82777</v>
       </c>
       <c r="F318" s="3">
-        <v>46030</v>
+        <v>46104</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="319">
@@ -8719,10 +8719,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E319" s="2">
-        <v>81525</v>
+        <v>81506</v>
       </c>
       <c r="F319" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>9</v>
@@ -8745,10 +8745,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E320" s="2">
-        <v>81526</v>
+        <v>81507</v>
       </c>
       <c r="F320" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>9</v>
@@ -8765,16 +8765,16 @@
         <v>29</v>
       </c>
       <c r="C321" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D321" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E321" s="2">
-        <v>81640</v>
+        <v>81524</v>
       </c>
       <c r="F321" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>9</v>
@@ -8791,16 +8791,16 @@
         <v>29</v>
       </c>
       <c r="C322" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D322" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E322" s="2">
-        <v>81642</v>
+        <v>81525</v>
       </c>
       <c r="F322" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>9</v>
@@ -8817,16 +8817,16 @@
         <v>29</v>
       </c>
       <c r="C323" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D323" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E323" s="2">
-        <v>81643</v>
+        <v>81526</v>
       </c>
       <c r="F323" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>9</v>
@@ -8843,16 +8843,16 @@
         <v>29</v>
       </c>
       <c r="C324" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D324" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E324" s="2">
-        <v>81835</v>
+        <v>81640</v>
       </c>
       <c r="F324" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>9</v>
@@ -8869,16 +8869,16 @@
         <v>29</v>
       </c>
       <c r="C325" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D325" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E325" s="2">
-        <v>81836</v>
+        <v>81642</v>
       </c>
       <c r="F325" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>9</v>
@@ -8895,16 +8895,16 @@
         <v>29</v>
       </c>
       <c r="C326" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D326" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E326" s="2">
-        <v>81837</v>
+        <v>81643</v>
       </c>
       <c r="F326" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>9</v>
@@ -8921,16 +8921,16 @@
         <v>29</v>
       </c>
       <c r="C327" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D327" s="3">
-        <v>46051.6376515278</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E327" s="2">
-        <v>81931</v>
+        <v>81835</v>
       </c>
       <c r="F327" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>9</v>
@@ -8947,16 +8947,16 @@
         <v>29</v>
       </c>
       <c r="C328" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D328" s="3">
-        <v>46056.7115158912</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E328" s="2">
-        <v>81978</v>
+        <v>81836</v>
       </c>
       <c r="F328" s="3">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>9</v>
@@ -8973,16 +8973,16 @@
         <v>29</v>
       </c>
       <c r="C329" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D329" s="3">
-        <v>46057.6911087731</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E329" s="2">
-        <v>81994</v>
+        <v>81837</v>
       </c>
       <c r="F329" s="3">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>9</v>
@@ -8999,16 +8999,16 @@
         <v>29</v>
       </c>
       <c r="C330" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D330" s="3">
-        <v>46057.6911087731</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E330" s="2">
-        <v>81995</v>
+        <v>81931</v>
       </c>
       <c r="F330" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>9</v>
@@ -9025,13 +9025,13 @@
         <v>29</v>
       </c>
       <c r="C331" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D331" s="3">
-        <v>46057.6911087731</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E331" s="2">
-        <v>81999</v>
+        <v>81978</v>
       </c>
       <c r="F331" s="3">
         <v>46057</v>
@@ -9057,10 +9057,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E332" s="2">
-        <v>82008</v>
+        <v>81994</v>
       </c>
       <c r="F332" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>9</v>
@@ -9083,10 +9083,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E333" s="2">
-        <v>82011</v>
+        <v>81995</v>
       </c>
       <c r="F333" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>9</v>
@@ -9109,10 +9109,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E334" s="2">
-        <v>82012</v>
+        <v>81999</v>
       </c>
       <c r="F334" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>9</v>
@@ -9135,7 +9135,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E335" s="2">
-        <v>82013</v>
+        <v>82008</v>
       </c>
       <c r="F335" s="3">
         <v>46058</v>
@@ -9161,7 +9161,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E336" s="2">
-        <v>82014</v>
+        <v>82011</v>
       </c>
       <c r="F336" s="3">
         <v>46058</v>
@@ -9181,22 +9181,22 @@
         <v>29</v>
       </c>
       <c r="C337" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D337" s="3">
-        <v>46058.6604985417</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E337" s="2">
-        <v>82046</v>
+        <v>82012</v>
       </c>
       <c r="F337" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="338">
@@ -9207,16 +9207,16 @@
         <v>29</v>
       </c>
       <c r="C338" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D338" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E338" s="2">
-        <v>82217</v>
+        <v>82013</v>
       </c>
       <c r="F338" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>9</v>
@@ -9233,16 +9233,16 @@
         <v>29</v>
       </c>
       <c r="C339" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D339" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E339" s="2">
-        <v>82218</v>
+        <v>82014</v>
       </c>
       <c r="F339" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>9</v>
@@ -9259,22 +9259,22 @@
         <v>29</v>
       </c>
       <c r="C340" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D340" s="3">
-        <v>46072.738871875</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E340" s="2">
-        <v>82234</v>
+        <v>82046</v>
       </c>
       <c r="F340" s="3">
-        <v>46073</v>
+        <v>46059</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="341">
@@ -9291,10 +9291,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E341" s="2">
-        <v>82238</v>
+        <v>82217</v>
       </c>
       <c r="F341" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>9</v>
@@ -9317,10 +9317,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E342" s="2">
-        <v>82245</v>
+        <v>82218</v>
       </c>
       <c r="F342" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>9</v>
@@ -9337,16 +9337,16 @@
         <v>29</v>
       </c>
       <c r="C343" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D343" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E343" s="2">
-        <v>82257</v>
+        <v>82234</v>
       </c>
       <c r="F343" s="3">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>9</v>
@@ -9363,16 +9363,16 @@
         <v>29</v>
       </c>
       <c r="C344" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D344" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E344" s="2">
-        <v>82276</v>
+        <v>82238</v>
       </c>
       <c r="F344" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>9</v>
@@ -9389,16 +9389,16 @@
         <v>29</v>
       </c>
       <c r="C345" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D345" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E345" s="2">
-        <v>82277</v>
+        <v>82245</v>
       </c>
       <c r="F345" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>9</v>
@@ -9421,10 +9421,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E346" s="2">
-        <v>82293</v>
+        <v>82257</v>
       </c>
       <c r="F346" s="3">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>9</v>
@@ -9441,13 +9441,13 @@
         <v>29</v>
       </c>
       <c r="C347" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D347" s="3">
-        <v>46077.4356327431</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E347" s="2">
-        <v>82269</v>
+        <v>82276</v>
       </c>
       <c r="F347" s="3">
         <v>46077</v>
@@ -9467,16 +9467,16 @@
         <v>29</v>
       </c>
       <c r="C348" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D348" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E348" s="2">
-        <v>82419</v>
+        <v>82277</v>
       </c>
       <c r="F348" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>9</v>
@@ -9493,16 +9493,16 @@
         <v>29</v>
       </c>
       <c r="C349" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D349" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E349" s="2">
-        <v>82420</v>
+        <v>82293</v>
       </c>
       <c r="F349" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>9</v>
@@ -9519,16 +9519,16 @@
         <v>29</v>
       </c>
       <c r="C350" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D350" s="3">
-        <v>46084.7378501505</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E350" s="2">
-        <v>82421</v>
+        <v>82269</v>
       </c>
       <c r="F350" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>9</v>
@@ -9551,7 +9551,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E351" s="2">
-        <v>82422</v>
+        <v>82419</v>
       </c>
       <c r="F351" s="3">
         <v>46084</v>
@@ -9577,7 +9577,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E352" s="2">
-        <v>82423</v>
+        <v>82420</v>
       </c>
       <c r="F352" s="3">
         <v>46084</v>
@@ -9603,10 +9603,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E353" s="2">
-        <v>82433</v>
+        <v>82421</v>
       </c>
       <c r="F353" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>9</v>
@@ -9629,10 +9629,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E354" s="2">
-        <v>82434</v>
+        <v>82422</v>
       </c>
       <c r="F354" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>9</v>
@@ -9655,10 +9655,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E355" s="2">
-        <v>82464</v>
+        <v>82423</v>
       </c>
       <c r="F355" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>9</v>
@@ -9681,10 +9681,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E356" s="2">
-        <v>82472</v>
+        <v>82433</v>
       </c>
       <c r="F356" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>9</v>
@@ -9701,16 +9701,16 @@
         <v>29</v>
       </c>
       <c r="C357" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D357" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E357" s="2">
-        <v>82578</v>
+        <v>82434</v>
       </c>
       <c r="F357" s="3">
-        <v>46093</v>
+        <v>46085</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>9</v>
@@ -9727,16 +9727,16 @@
         <v>29</v>
       </c>
       <c r="C358" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D358" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E358" s="2">
-        <v>82579</v>
+        <v>82464</v>
       </c>
       <c r="F358" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>9</v>
@@ -9753,16 +9753,16 @@
         <v>29</v>
       </c>
       <c r="C359" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D359" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E359" s="2">
-        <v>82580</v>
+        <v>82472</v>
       </c>
       <c r="F359" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>9</v>
@@ -9785,7 +9785,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E360" s="2">
-        <v>82599</v>
+        <v>82578</v>
       </c>
       <c r="F360" s="3">
         <v>46093</v>
@@ -9811,7 +9811,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E361" s="2">
-        <v>82602</v>
+        <v>82579</v>
       </c>
       <c r="F361" s="3">
         <v>46093</v>
@@ -9831,13 +9831,13 @@
         <v>29</v>
       </c>
       <c r="C362" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D362" s="3">
-        <v>46093.4957757986</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E362" s="2">
-        <v>82584</v>
+        <v>82580</v>
       </c>
       <c r="F362" s="3">
         <v>46093</v>
@@ -9857,22 +9857,22 @@
         <v>29</v>
       </c>
       <c r="C363" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D363" s="3">
-        <v>46100.6528700694</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E363" s="2">
-        <v>82745</v>
+        <v>82599</v>
       </c>
       <c r="F363" s="3">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="364">
@@ -9883,16 +9883,16 @@
         <v>29</v>
       </c>
       <c r="C364" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D364" s="3">
-        <v>46100.6528700694</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E364" s="2">
-        <v>82746</v>
+        <v>82602</v>
       </c>
       <c r="F364" s="3">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>9</v>
@@ -9909,22 +9909,22 @@
         <v>29</v>
       </c>
       <c r="C365" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D365" s="3">
-        <v>46100.6528700694</v>
+        <v>46093.4957757986</v>
       </c>
       <c r="E365" s="2">
-        <v>82747</v>
+        <v>82584</v>
       </c>
       <c r="F365" s="3">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H365" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="366">
@@ -9941,7 +9941,7 @@
         <v>46100.6528700694</v>
       </c>
       <c r="E366" s="2">
-        <v>82748</v>
+        <v>82746</v>
       </c>
       <c r="F366" s="3">
         <v>46100</v>
@@ -9955,22 +9955,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="367">
       <c r="A367" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C367" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D367" s="3">
-        <v>46027.6953206134</v>
+        <v>46100.6528700694</v>
       </c>
       <c r="E367" s="2">
-        <v>81464</v>
+        <v>82747</v>
       </c>
       <c r="F367" s="3">
-        <v>46027</v>
+        <v>46100</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>9</v>
@@ -9981,22 +9981,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="368">
       <c r="A368" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C368" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D368" s="3">
-        <v>46027.6953206134</v>
+        <v>46100.6528700694</v>
       </c>
       <c r="E368" s="2">
-        <v>81472</v>
+        <v>82748</v>
       </c>
       <c r="F368" s="3">
-        <v>46027</v>
+        <v>46100</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>9</v>
@@ -10019,10 +10019,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E369" s="2">
-        <v>81492</v>
+        <v>81464</v>
       </c>
       <c r="F369" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>9</v>
@@ -10045,10 +10045,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E370" s="2">
-        <v>81493</v>
+        <v>81472</v>
       </c>
       <c r="F370" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>9</v>
@@ -10071,10 +10071,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E371" s="2">
-        <v>81568</v>
+        <v>81492</v>
       </c>
       <c r="F371" s="3">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>9</v>
@@ -10097,10 +10097,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E372" s="2">
-        <v>81601</v>
+        <v>81493</v>
       </c>
       <c r="F372" s="3">
-        <v>46034</v>
+        <v>46029</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>9</v>
@@ -10123,10 +10123,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E373" s="2">
-        <v>81602</v>
+        <v>81568</v>
       </c>
       <c r="F373" s="3">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>9</v>
@@ -10143,16 +10143,16 @@
         <v>30</v>
       </c>
       <c r="C374" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D374" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E374" s="2">
-        <v>81645</v>
+        <v>81601</v>
       </c>
       <c r="F374" s="3">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>9</v>
@@ -10169,16 +10169,16 @@
         <v>30</v>
       </c>
       <c r="C375" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D375" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E375" s="2">
-        <v>81646</v>
+        <v>81602</v>
       </c>
       <c r="F375" s="3">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>9</v>
@@ -10201,10 +10201,10 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E376" s="2">
-        <v>81653</v>
+        <v>81645</v>
       </c>
       <c r="F376" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>9</v>
@@ -10221,16 +10221,16 @@
         <v>30</v>
       </c>
       <c r="C377" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D377" s="3">
-        <v>46037.4325152662</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E377" s="2">
-        <v>81662</v>
+        <v>81646</v>
       </c>
       <c r="F377" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>9</v>
@@ -10247,16 +10247,16 @@
         <v>30</v>
       </c>
       <c r="C378" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D378" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E378" s="2">
-        <v>81780</v>
+        <v>81653</v>
       </c>
       <c r="F378" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>9</v>
@@ -10273,16 +10273,16 @@
         <v>30</v>
       </c>
       <c r="C379" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D379" s="3">
-        <v>46044.4079891435</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E379" s="2">
-        <v>81781</v>
+        <v>81662</v>
       </c>
       <c r="F379" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>9</v>
@@ -10305,7 +10305,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E380" s="2">
-        <v>81782</v>
+        <v>81780</v>
       </c>
       <c r="F380" s="3">
         <v>46044</v>
@@ -10331,7 +10331,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E381" s="2">
-        <v>81784</v>
+        <v>81781</v>
       </c>
       <c r="F381" s="3">
         <v>46044</v>
@@ -10357,7 +10357,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E382" s="2">
-        <v>81785</v>
+        <v>81782</v>
       </c>
       <c r="F382" s="3">
         <v>46044</v>
@@ -10383,7 +10383,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E383" s="2">
-        <v>81801</v>
+        <v>81784</v>
       </c>
       <c r="F383" s="3">
         <v>46044</v>
@@ -10403,16 +10403,16 @@
         <v>30</v>
       </c>
       <c r="C384" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D384" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E384" s="2">
-        <v>81860</v>
+        <v>81785</v>
       </c>
       <c r="F384" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>9</v>
@@ -10429,16 +10429,16 @@
         <v>30</v>
       </c>
       <c r="C385" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D385" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E385" s="2">
-        <v>81873</v>
+        <v>81801</v>
       </c>
       <c r="F385" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>9</v>
@@ -10455,13 +10455,13 @@
         <v>30</v>
       </c>
       <c r="C386" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D386" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E386" s="2">
-        <v>81865</v>
+        <v>81860</v>
       </c>
       <c r="F386" s="3">
         <v>46049</v>
@@ -10481,13 +10481,13 @@
         <v>30</v>
       </c>
       <c r="C387" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D387" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E387" s="2">
-        <v>81870</v>
+        <v>81873</v>
       </c>
       <c r="F387" s="3">
         <v>46049</v>
@@ -10513,7 +10513,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E388" s="2">
-        <v>81872</v>
+        <v>81865</v>
       </c>
       <c r="F388" s="3">
         <v>46049</v>
@@ -10539,10 +10539,10 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E389" s="2">
-        <v>81896</v>
+        <v>81870</v>
       </c>
       <c r="F389" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>9</v>
@@ -10559,16 +10559,16 @@
         <v>30</v>
       </c>
       <c r="C390" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D390" s="3">
-        <v>46051.4046937153</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E390" s="2">
-        <v>81923</v>
+        <v>81872</v>
       </c>
       <c r="F390" s="3">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>9</v>
@@ -10585,16 +10585,16 @@
         <v>30</v>
       </c>
       <c r="C391" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D391" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E391" s="2">
-        <v>81998</v>
+        <v>81896</v>
       </c>
       <c r="F391" s="3">
-        <v>46057</v>
+        <v>46050</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>9</v>
@@ -10611,16 +10611,16 @@
         <v>30</v>
       </c>
       <c r="C392" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D392" s="3">
-        <v>46057.6959672917</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E392" s="2">
-        <v>82002</v>
+        <v>81923</v>
       </c>
       <c r="F392" s="3">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>9</v>
@@ -10643,10 +10643,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E393" s="2">
-        <v>82005</v>
+        <v>81998</v>
       </c>
       <c r="F393" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>9</v>
@@ -10669,10 +10669,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E394" s="2">
-        <v>82007</v>
+        <v>82002</v>
       </c>
       <c r="F394" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>9</v>
@@ -10689,10 +10689,10 @@
         <v>30</v>
       </c>
       <c r="C395" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D395" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E395" s="2">
         <v>82005</v>
@@ -10715,16 +10715,16 @@
         <v>30</v>
       </c>
       <c r="C396" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D396" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E396" s="2">
-        <v>82075</v>
+        <v>82007</v>
       </c>
       <c r="F396" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>9</v>
@@ -10747,10 +10747,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E397" s="2">
-        <v>82077</v>
+        <v>82005</v>
       </c>
       <c r="F397" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>9</v>
@@ -10773,10 +10773,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E398" s="2">
-        <v>82099</v>
+        <v>82075</v>
       </c>
       <c r="F398" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>9</v>
@@ -10793,16 +10793,16 @@
         <v>30</v>
       </c>
       <c r="C399" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D399" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E399" s="2">
-        <v>82219</v>
+        <v>82077</v>
       </c>
       <c r="F399" s="3">
-        <v>46072</v>
+        <v>46063</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>9</v>
@@ -10819,16 +10819,16 @@
         <v>30</v>
       </c>
       <c r="C400" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D400" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E400" s="2">
-        <v>82230</v>
+        <v>82099</v>
       </c>
       <c r="F400" s="3">
-        <v>46073</v>
+        <v>46064</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>9</v>
@@ -10851,10 +10851,10 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E401" s="2">
-        <v>82231</v>
+        <v>82219</v>
       </c>
       <c r="F401" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10871,16 +10871,16 @@
         <v>30</v>
       </c>
       <c r="C402" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D402" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E402" s="2">
-        <v>82388</v>
+        <v>82230</v>
       </c>
       <c r="F402" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10897,16 +10897,16 @@
         <v>30</v>
       </c>
       <c r="C403" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D403" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E403" s="2">
-        <v>82389</v>
+        <v>82231</v>
       </c>
       <c r="F403" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10929,7 +10929,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E404" s="2">
-        <v>82396</v>
+        <v>82388</v>
       </c>
       <c r="F404" s="3">
         <v>46083</v>
@@ -10955,7 +10955,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E405" s="2">
-        <v>82397</v>
+        <v>82389</v>
       </c>
       <c r="F405" s="3">
         <v>46083</v>
@@ -10975,16 +10975,16 @@
         <v>30</v>
       </c>
       <c r="C406" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D406" s="3">
-        <v>46085.6249659838</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E406" s="2">
-        <v>82435</v>
+        <v>82396</v>
       </c>
       <c r="F406" s="3">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>9</v>
@@ -11001,16 +11001,16 @@
         <v>30</v>
       </c>
       <c r="C407" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D407" s="3">
-        <v>46091.449444456</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E407" s="2">
-        <v>82506</v>
+        <v>82397</v>
       </c>
       <c r="F407" s="3">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="G407" s="1" t="s">
         <v>9</v>
@@ -11027,16 +11027,16 @@
         <v>30</v>
       </c>
       <c r="C408" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D408" s="3">
-        <v>46091.4795702315</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E408" s="2">
-        <v>82509</v>
+        <v>82435</v>
       </c>
       <c r="F408" s="3">
-        <v>46091</v>
+        <v>46085</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>9</v>
@@ -11053,16 +11053,16 @@
         <v>30</v>
       </c>
       <c r="C409" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D409" s="3">
-        <v>46093.4969972338</v>
+        <v>46091.449444456</v>
       </c>
       <c r="E409" s="2">
-        <v>82589</v>
+        <v>82506</v>
       </c>
       <c r="F409" s="3">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>9</v>
@@ -11073,22 +11073,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="410">
       <c r="A410" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C410" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D410" s="3">
-        <v>46029.3821391551</v>
+        <v>46091.4795702315</v>
       </c>
       <c r="E410" s="2">
-        <v>81477</v>
+        <v>82509</v>
       </c>
       <c r="F410" s="3">
-        <v>46029</v>
+        <v>46091</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11099,22 +11099,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="411">
       <c r="A411" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C411" s="2">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D411" s="3">
-        <v>46030.4142968056</v>
+        <v>46093.4969972338</v>
       </c>
       <c r="E411" s="2">
-        <v>81532</v>
+        <v>82589</v>
       </c>
       <c r="F411" s="3">
-        <v>46030</v>
+        <v>46093</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>9</v>
@@ -11131,16 +11131,16 @@
         <v>31</v>
       </c>
       <c r="C412" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D412" s="3">
-        <v>46030.4142968056</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E412" s="2">
-        <v>81534</v>
+        <v>81477</v>
       </c>
       <c r="F412" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11163,7 +11163,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E413" s="2">
-        <v>81535</v>
+        <v>81532</v>
       </c>
       <c r="F413" s="3">
         <v>46030</v>
@@ -11189,7 +11189,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E414" s="2">
-        <v>81550</v>
+        <v>81534</v>
       </c>
       <c r="F414" s="3">
         <v>46030</v>
@@ -11215,7 +11215,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E415" s="2">
-        <v>81553</v>
+        <v>81535</v>
       </c>
       <c r="F415" s="3">
         <v>46030</v>
@@ -11241,7 +11241,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E416" s="2">
-        <v>81554</v>
+        <v>81550</v>
       </c>
       <c r="F416" s="3">
         <v>46030</v>
@@ -11267,7 +11267,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E417" s="2">
-        <v>81557</v>
+        <v>81553</v>
       </c>
       <c r="F417" s="3">
         <v>46030</v>
@@ -11293,10 +11293,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E418" s="2">
-        <v>81588</v>
+        <v>81554</v>
       </c>
       <c r="F418" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G418" s="1" t="s">
         <v>9</v>
@@ -11313,16 +11313,16 @@
         <v>31</v>
       </c>
       <c r="C419" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D419" s="3">
-        <v>46038.593985081</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E419" s="2">
-        <v>81692</v>
+        <v>81557</v>
       </c>
       <c r="F419" s="3">
-        <v>46038</v>
+        <v>46030</v>
       </c>
       <c r="G419" s="1" t="s">
         <v>9</v>
@@ -11339,16 +11339,16 @@
         <v>31</v>
       </c>
       <c r="C420" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D420" s="3">
-        <v>46044.46462125</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E420" s="2">
-        <v>81786</v>
+        <v>81588</v>
       </c>
       <c r="F420" s="3">
-        <v>46044</v>
+        <v>46031</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>9</v>
@@ -11365,16 +11365,16 @@
         <v>31</v>
       </c>
       <c r="C421" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D421" s="3">
-        <v>46044.6362443171</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E421" s="2">
-        <v>81844</v>
+        <v>81692</v>
       </c>
       <c r="F421" s="3">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>9</v>
@@ -11391,16 +11391,16 @@
         <v>31</v>
       </c>
       <c r="C422" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D422" s="3">
-        <v>46062.717040544</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E422" s="2">
-        <v>82065</v>
+        <v>81786</v>
       </c>
       <c r="F422" s="3">
-        <v>46062</v>
+        <v>46044</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>9</v>
@@ -11417,16 +11417,16 @@
         <v>31</v>
       </c>
       <c r="C423" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D423" s="3">
-        <v>46062.717040544</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E423" s="2">
-        <v>82066</v>
+        <v>81844</v>
       </c>
       <c r="F423" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>9</v>
@@ -11449,7 +11449,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E424" s="2">
-        <v>82067</v>
+        <v>82065</v>
       </c>
       <c r="F424" s="3">
         <v>46062</v>
@@ -11469,16 +11469,16 @@
         <v>31</v>
       </c>
       <c r="C425" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D425" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E425" s="2">
-        <v>82190</v>
+        <v>82066</v>
       </c>
       <c r="F425" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>9</v>
@@ -11495,16 +11495,16 @@
         <v>31</v>
       </c>
       <c r="C426" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D426" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E426" s="2">
-        <v>82197</v>
+        <v>82067</v>
       </c>
       <c r="F426" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>9</v>
@@ -11521,16 +11521,16 @@
         <v>31</v>
       </c>
       <c r="C427" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D427" s="3">
-        <v>46077.5084780324</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E427" s="2">
-        <v>82270</v>
+        <v>82190</v>
       </c>
       <c r="F427" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11547,16 +11547,16 @@
         <v>31</v>
       </c>
       <c r="C428" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D428" s="3">
-        <v>46077.721037037</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E428" s="2">
-        <v>82285</v>
+        <v>82197</v>
       </c>
       <c r="F428" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>9</v>
@@ -11573,16 +11573,16 @@
         <v>31</v>
       </c>
       <c r="C429" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D429" s="3">
-        <v>46083.6694849421</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E429" s="2">
-        <v>82417</v>
+        <v>82270</v>
       </c>
       <c r="F429" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>9</v>
@@ -11599,16 +11599,16 @@
         <v>31</v>
       </c>
       <c r="C430" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D430" s="3">
-        <v>46085.7157723032</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E430" s="2">
-        <v>82457</v>
+        <v>82285</v>
       </c>
       <c r="F430" s="3">
-        <v>46086</v>
+        <v>46077</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>9</v>
@@ -11625,16 +11625,16 @@
         <v>31</v>
       </c>
       <c r="C431" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D431" s="3">
-        <v>46099.6523956944</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E431" s="2">
-        <v>82724</v>
+        <v>82417</v>
       </c>
       <c r="F431" s="3">
-        <v>46099</v>
+        <v>46084</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>9</v>
@@ -11651,16 +11651,16 @@
         <v>31</v>
       </c>
       <c r="C432" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D432" s="3">
-        <v>46099.6523956944</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E432" s="2">
-        <v>82725</v>
+        <v>82457</v>
       </c>
       <c r="F432" s="3">
-        <v>46099</v>
+        <v>46086</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11683,10 +11683,10 @@
         <v>46099.6523956944</v>
       </c>
       <c r="E433" s="2">
-        <v>82727</v>
+        <v>82724</v>
       </c>
       <c r="F433" s="3">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11709,10 +11709,10 @@
         <v>46099.6523956944</v>
       </c>
       <c r="E434" s="2">
-        <v>82730</v>
+        <v>82725</v>
       </c>
       <c r="F434" s="3">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>9</v>
@@ -11723,22 +11723,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="435">
       <c r="A435" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C435" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D435" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E435" s="2">
-        <v>81484</v>
+        <v>82727</v>
       </c>
       <c r="F435" s="3">
-        <v>46029</v>
+        <v>46100</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>9</v>
@@ -11749,22 +11749,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="436">
       <c r="A436" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C436" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D436" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E436" s="2">
-        <v>81486</v>
+        <v>82730</v>
       </c>
       <c r="F436" s="3">
-        <v>46029</v>
+        <v>46100</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>9</v>
@@ -11787,7 +11787,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E437" s="2">
-        <v>81487</v>
+        <v>81484</v>
       </c>
       <c r="F437" s="3">
         <v>46029</v>
@@ -11807,16 +11807,16 @@
         <v>32</v>
       </c>
       <c r="C438" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D438" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E438" s="2">
-        <v>81613</v>
+        <v>81486</v>
       </c>
       <c r="F438" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11833,16 +11833,16 @@
         <v>32</v>
       </c>
       <c r="C439" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D439" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E439" s="2">
-        <v>81614</v>
+        <v>81487</v>
       </c>
       <c r="F439" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11865,7 +11865,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E440" s="2">
-        <v>81622</v>
+        <v>81613</v>
       </c>
       <c r="F440" s="3">
         <v>46036</v>
@@ -11891,7 +11891,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E441" s="2">
-        <v>81632</v>
+        <v>81614</v>
       </c>
       <c r="F441" s="3">
         <v>46036</v>
@@ -11917,10 +11917,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E442" s="2">
-        <v>81648</v>
+        <v>81622</v>
       </c>
       <c r="F442" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11943,10 +11943,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E443" s="2">
-        <v>81664</v>
+        <v>81632</v>
       </c>
       <c r="F443" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11963,16 +11963,16 @@
         <v>32</v>
       </c>
       <c r="C444" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D444" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E444" s="2">
-        <v>81815</v>
+        <v>81648</v>
       </c>
       <c r="F444" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11989,16 +11989,16 @@
         <v>32</v>
       </c>
       <c r="C445" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D445" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E445" s="2">
-        <v>81816</v>
+        <v>81664</v>
       </c>
       <c r="F445" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>9</v>
@@ -12021,7 +12021,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E446" s="2">
-        <v>81838</v>
+        <v>81815</v>
       </c>
       <c r="F446" s="3">
         <v>46045</v>
@@ -12047,7 +12047,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E447" s="2">
-        <v>81840</v>
+        <v>81816</v>
       </c>
       <c r="F447" s="3">
         <v>46045</v>
@@ -12067,16 +12067,16 @@
         <v>32</v>
       </c>
       <c r="C448" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D448" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E448" s="2">
-        <v>81959</v>
+        <v>81838</v>
       </c>
       <c r="F448" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12093,16 +12093,16 @@
         <v>32</v>
       </c>
       <c r="C449" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D449" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E449" s="2">
-        <v>81960</v>
+        <v>81840</v>
       </c>
       <c r="F449" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12119,16 +12119,16 @@
         <v>32</v>
       </c>
       <c r="C450" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D450" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E450" s="2">
-        <v>82063</v>
+        <v>81959</v>
       </c>
       <c r="F450" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12145,16 +12145,16 @@
         <v>32</v>
       </c>
       <c r="C451" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D451" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E451" s="2">
-        <v>82064</v>
+        <v>81960</v>
       </c>
       <c r="F451" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>9</v>
@@ -12177,10 +12177,10 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E452" s="2">
-        <v>82100</v>
+        <v>82063</v>
       </c>
       <c r="F452" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12197,16 +12197,16 @@
         <v>32</v>
       </c>
       <c r="C453" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D453" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E453" s="2">
-        <v>82333</v>
+        <v>82064</v>
       </c>
       <c r="F453" s="3">
-        <v>46079</v>
+        <v>46062</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>9</v>
@@ -12223,16 +12223,16 @@
         <v>32</v>
       </c>
       <c r="C454" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D454" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E454" s="2">
-        <v>82334</v>
+        <v>82100</v>
       </c>
       <c r="F454" s="3">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>9</v>
@@ -12249,16 +12249,16 @@
         <v>32</v>
       </c>
       <c r="C455" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D455" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E455" s="2">
-        <v>82258</v>
+        <v>82333</v>
       </c>
       <c r="F455" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>9</v>
@@ -12275,16 +12275,16 @@
         <v>32</v>
       </c>
       <c r="C456" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D456" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E456" s="2">
-        <v>82259</v>
+        <v>82334</v>
       </c>
       <c r="F456" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12307,7 +12307,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E457" s="2">
-        <v>82260</v>
+        <v>82258</v>
       </c>
       <c r="F457" s="3">
         <v>46076</v>
@@ -12333,10 +12333,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E458" s="2">
-        <v>82274</v>
+        <v>82259</v>
       </c>
       <c r="F458" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12353,16 +12353,16 @@
         <v>32</v>
       </c>
       <c r="C459" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D459" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E459" s="2">
-        <v>82409</v>
+        <v>82260</v>
       </c>
       <c r="F459" s="3">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12379,16 +12379,16 @@
         <v>32</v>
       </c>
       <c r="C460" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D460" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E460" s="2">
-        <v>82581</v>
+        <v>82274</v>
       </c>
       <c r="F460" s="3">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12405,16 +12405,16 @@
         <v>32</v>
       </c>
       <c r="C461" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D461" s="3">
-        <v>46093.4920058565</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E461" s="2">
-        <v>82582</v>
+        <v>82409</v>
       </c>
       <c r="F461" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12437,7 +12437,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E462" s="2">
-        <v>82583</v>
+        <v>82581</v>
       </c>
       <c r="F462" s="3">
         <v>46093</v>
@@ -12463,10 +12463,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E463" s="2">
-        <v>82672</v>
+        <v>82582</v>
       </c>
       <c r="F463" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12489,10 +12489,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E464" s="2">
-        <v>82674</v>
+        <v>82583</v>
       </c>
       <c r="F464" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12503,22 +12503,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="465">
       <c r="A465" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C465" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D465" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E465" s="2">
-        <v>81608</v>
+        <v>82672</v>
       </c>
       <c r="F465" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>9</v>
@@ -12529,22 +12529,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="466">
       <c r="A466" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C466" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D466" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E466" s="2">
-        <v>81609</v>
+        <v>82674</v>
       </c>
       <c r="F466" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12567,7 +12567,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E467" s="2">
-        <v>81610</v>
+        <v>81608</v>
       </c>
       <c r="F467" s="3">
         <v>46035</v>
@@ -12593,7 +12593,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E468" s="2">
-        <v>81611</v>
+        <v>81609</v>
       </c>
       <c r="F468" s="3">
         <v>46035</v>
@@ -12619,7 +12619,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E469" s="2">
-        <v>81612</v>
+        <v>81610</v>
       </c>
       <c r="F469" s="3">
         <v>46035</v>
@@ -12639,16 +12639,16 @@
         <v>33</v>
       </c>
       <c r="C470" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D470" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E470" s="2">
-        <v>81652</v>
+        <v>81611</v>
       </c>
       <c r="F470" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>9</v>
@@ -12665,16 +12665,16 @@
         <v>33</v>
       </c>
       <c r="C471" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D471" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E471" s="2">
-        <v>81659</v>
+        <v>81612</v>
       </c>
       <c r="F471" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>9</v>
@@ -12691,16 +12691,16 @@
         <v>33</v>
       </c>
       <c r="C472" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D472" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E472" s="2">
-        <v>81853</v>
+        <v>81652</v>
       </c>
       <c r="F472" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12717,16 +12717,16 @@
         <v>33</v>
       </c>
       <c r="C473" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D473" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E473" s="2">
-        <v>81869</v>
+        <v>81659</v>
       </c>
       <c r="F473" s="3">
-        <v>46049</v>
+        <v>46037</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12749,10 +12749,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E474" s="2">
-        <v>81890</v>
+        <v>81853</v>
       </c>
       <c r="F474" s="3">
-        <v>46050</v>
+        <v>46048</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12769,13 +12769,13 @@
         <v>33</v>
       </c>
       <c r="C475" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D475" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E475" s="2">
-        <v>81875</v>
+        <v>81869</v>
       </c>
       <c r="F475" s="3">
         <v>46049</v>
@@ -12795,13 +12795,13 @@
         <v>33</v>
       </c>
       <c r="C476" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D476" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E476" s="2">
-        <v>81881</v>
+        <v>81890</v>
       </c>
       <c r="F476" s="3">
         <v>46050</v>
@@ -12821,16 +12821,16 @@
         <v>33</v>
       </c>
       <c r="C477" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D477" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E477" s="2">
-        <v>82015</v>
+        <v>81875</v>
       </c>
       <c r="F477" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>9</v>
@@ -12847,16 +12847,16 @@
         <v>33</v>
       </c>
       <c r="C478" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D478" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E478" s="2">
-        <v>82017</v>
+        <v>81881</v>
       </c>
       <c r="F478" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12879,7 +12879,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E479" s="2">
-        <v>82020</v>
+        <v>82015</v>
       </c>
       <c r="F479" s="3">
         <v>46058</v>
@@ -12905,7 +12905,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E480" s="2">
-        <v>82023</v>
+        <v>82017</v>
       </c>
       <c r="F480" s="3">
         <v>46058</v>
@@ -12931,10 +12931,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E481" s="2">
-        <v>82061</v>
+        <v>82020</v>
       </c>
       <c r="F481" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>9</v>
@@ -12957,10 +12957,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E482" s="2">
-        <v>82081</v>
+        <v>82023</v>
       </c>
       <c r="F482" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12983,10 +12983,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E483" s="2">
-        <v>82095</v>
+        <v>82061</v>
       </c>
       <c r="F483" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>9</v>
@@ -13003,10 +13003,10 @@
         <v>33</v>
       </c>
       <c r="C484" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D484" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E484" s="2">
         <v>82081</v>
@@ -13029,13 +13029,13 @@
         <v>33</v>
       </c>
       <c r="C485" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D485" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E485" s="2">
-        <v>82107</v>
+        <v>82095</v>
       </c>
       <c r="F485" s="3">
         <v>46064</v>
@@ -13061,10 +13061,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E486" s="2">
-        <v>82112</v>
+        <v>82081</v>
       </c>
       <c r="F486" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>9</v>
@@ -13087,7 +13087,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E487" s="2">
-        <v>82113</v>
+        <v>82107</v>
       </c>
       <c r="F487" s="3">
         <v>46064</v>
@@ -13113,10 +13113,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E488" s="2">
-        <v>82123</v>
+        <v>82112</v>
       </c>
       <c r="F488" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>9</v>
@@ -13133,13 +13133,13 @@
         <v>33</v>
       </c>
       <c r="C489" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D489" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E489" s="2">
-        <v>82095</v>
+        <v>82113</v>
       </c>
       <c r="F489" s="3">
         <v>46064</v>
@@ -13159,16 +13159,16 @@
         <v>33</v>
       </c>
       <c r="C490" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D490" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E490" s="2">
-        <v>82106</v>
+        <v>82123</v>
       </c>
       <c r="F490" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>9</v>
@@ -13191,7 +13191,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E491" s="2">
-        <v>82107</v>
+        <v>82095</v>
       </c>
       <c r="F491" s="3">
         <v>46064</v>
@@ -13217,7 +13217,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E492" s="2">
-        <v>82109</v>
+        <v>82106</v>
       </c>
       <c r="F492" s="3">
         <v>46064</v>
@@ -13243,7 +13243,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E493" s="2">
-        <v>82110</v>
+        <v>82107</v>
       </c>
       <c r="F493" s="3">
         <v>46064</v>
@@ -13269,10 +13269,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E494" s="2">
-        <v>82139</v>
+        <v>82109</v>
       </c>
       <c r="F494" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>9</v>
@@ -13289,16 +13289,16 @@
         <v>33</v>
       </c>
       <c r="C495" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D495" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E495" s="2">
-        <v>82365</v>
+        <v>82110</v>
       </c>
       <c r="F495" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>9</v>
@@ -13315,16 +13315,16 @@
         <v>33</v>
       </c>
       <c r="C496" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D496" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E496" s="2">
-        <v>82366</v>
+        <v>82139</v>
       </c>
       <c r="F496" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G496" s="1" t="s">
         <v>9</v>
@@ -13347,7 +13347,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E497" s="2">
-        <v>82371</v>
+        <v>82365</v>
       </c>
       <c r="F497" s="3">
         <v>46080</v>
@@ -13373,10 +13373,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E498" s="2">
-        <v>82383</v>
+        <v>82366</v>
       </c>
       <c r="F498" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G498" s="1" t="s">
         <v>9</v>
@@ -13399,10 +13399,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E499" s="2">
-        <v>82384</v>
+        <v>82371</v>
       </c>
       <c r="F499" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>9</v>
@@ -13419,16 +13419,16 @@
         <v>33</v>
       </c>
       <c r="C500" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D500" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E500" s="2">
-        <v>82693</v>
+        <v>82383</v>
       </c>
       <c r="F500" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G500" s="1" t="s">
         <v>9</v>
@@ -13445,16 +13445,16 @@
         <v>33</v>
       </c>
       <c r="C501" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D501" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E501" s="2">
-        <v>82760</v>
+        <v>82384</v>
       </c>
       <c r="F501" s="3">
-        <v>46101</v>
+        <v>46083</v>
       </c>
       <c r="G501" s="1" t="s">
         <v>9</v>
@@ -13477,10 +13477,10 @@
         <v>46098.4979333449</v>
       </c>
       <c r="E502" s="2">
-        <v>82763</v>
+        <v>82693</v>
       </c>
       <c r="F502" s="3">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="G502" s="1" t="s">
         <v>9</v>
@@ -13491,48 +13491,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="503">
       <c r="A503" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C503" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D503" s="3">
-        <v>46029.4149454282</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E503" s="2">
-        <v>81592</v>
+        <v>82760</v>
       </c>
       <c r="F503" s="3">
-        <v>46031</v>
+        <v>46101</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H503" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="504">
       <c r="A504" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C504" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D504" s="3">
-        <v>46029.4149454282</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E504" s="2">
-        <v>81593</v>
+        <v>82763</v>
       </c>
       <c r="F504" s="3">
-        <v>46031</v>
+        <v>46101</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>9</v>
@@ -13549,22 +13549,22 @@
         <v>34</v>
       </c>
       <c r="C505" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D505" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E505" s="2">
-        <v>81697</v>
+        <v>81592</v>
       </c>
       <c r="F505" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H505" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="506">
@@ -13575,22 +13575,22 @@
         <v>34</v>
       </c>
       <c r="C506" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D506" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E506" s="2">
-        <v>81735</v>
+        <v>81593</v>
       </c>
       <c r="F506" s="3">
-        <v>46041</v>
+        <v>46031</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H506" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="507">
@@ -13601,16 +13601,16 @@
         <v>34</v>
       </c>
       <c r="C507" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D507" s="3">
-        <v>46045.4532476157</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E507" s="2">
-        <v>81823</v>
+        <v>81697</v>
       </c>
       <c r="F507" s="3">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>9</v>
@@ -13621,48 +13621,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="508">
       <c r="A508" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C508" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D508" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E508" s="2">
-        <v>81572</v>
+        <v>81735</v>
       </c>
       <c r="F508" s="3">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="509">
       <c r="A509" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C509" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D509" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E509" s="2">
-        <v>81573</v>
+        <v>81823</v>
       </c>
       <c r="F509" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G509" s="1" t="s">
         <v>9</v>
@@ -13685,7 +13685,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E510" s="2">
-        <v>81579</v>
+        <v>81572</v>
       </c>
       <c r="F510" s="3">
         <v>46031</v>
@@ -13711,7 +13711,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E511" s="2">
-        <v>81580</v>
+        <v>81573</v>
       </c>
       <c r="F511" s="3">
         <v>46031</v>
@@ -13737,7 +13737,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E512" s="2">
-        <v>81581</v>
+        <v>81579</v>
       </c>
       <c r="F512" s="3">
         <v>46031</v>
@@ -13763,7 +13763,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E513" s="2">
-        <v>81582</v>
+        <v>81580</v>
       </c>
       <c r="F513" s="3">
         <v>46031</v>
@@ -13789,7 +13789,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E514" s="2">
-        <v>81583</v>
+        <v>81581</v>
       </c>
       <c r="F514" s="3">
         <v>46031</v>
@@ -13809,16 +13809,16 @@
         <v>35</v>
       </c>
       <c r="C515" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D515" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E515" s="2">
-        <v>81667</v>
+        <v>81582</v>
       </c>
       <c r="F515" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G515" s="1" t="s">
         <v>9</v>
@@ -13835,16 +13835,16 @@
         <v>35</v>
       </c>
       <c r="C516" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D516" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E516" s="2">
-        <v>81668</v>
+        <v>81583</v>
       </c>
       <c r="F516" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G516" s="1" t="s">
         <v>9</v>
@@ -13867,10 +13867,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E517" s="2">
-        <v>81674</v>
+        <v>81667</v>
       </c>
       <c r="F517" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G517" s="1" t="s">
         <v>9</v>
@@ -13893,10 +13893,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E518" s="2">
-        <v>81675</v>
+        <v>81668</v>
       </c>
       <c r="F518" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>9</v>
@@ -13919,7 +13919,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E519" s="2">
-        <v>81677</v>
+        <v>81674</v>
       </c>
       <c r="F519" s="3">
         <v>46038</v>
@@ -13939,16 +13939,16 @@
         <v>35</v>
       </c>
       <c r="C520" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D520" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E520" s="2">
-        <v>81739</v>
+        <v>81675</v>
       </c>
       <c r="F520" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G520" s="1" t="s">
         <v>9</v>
@@ -13965,16 +13965,16 @@
         <v>35</v>
       </c>
       <c r="C521" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D521" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E521" s="2">
-        <v>81741</v>
+        <v>81677</v>
       </c>
       <c r="F521" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G521" s="1" t="s">
         <v>9</v>
@@ -13991,16 +13991,16 @@
         <v>35</v>
       </c>
       <c r="C522" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D522" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E522" s="2">
-        <v>81854</v>
+        <v>81739</v>
       </c>
       <c r="F522" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G522" s="1" t="s">
         <v>9</v>
@@ -14017,16 +14017,16 @@
         <v>35</v>
       </c>
       <c r="C523" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D523" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E523" s="2">
-        <v>81855</v>
+        <v>81741</v>
       </c>
       <c r="F523" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>9</v>
@@ -14049,10 +14049,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E524" s="2">
-        <v>81858</v>
+        <v>81854</v>
       </c>
       <c r="F524" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G524" s="1" t="s">
         <v>9</v>
@@ -14075,10 +14075,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E525" s="2">
-        <v>81859</v>
+        <v>81855</v>
       </c>
       <c r="F525" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>9</v>
@@ -14101,7 +14101,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E526" s="2">
-        <v>81862</v>
+        <v>81858</v>
       </c>
       <c r="F526" s="3">
         <v>46049</v>
@@ -14127,7 +14127,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E527" s="2">
-        <v>81863</v>
+        <v>81859</v>
       </c>
       <c r="F527" s="3">
         <v>46049</v>
@@ -14147,16 +14147,16 @@
         <v>35</v>
       </c>
       <c r="C528" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D528" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E528" s="2">
-        <v>81958</v>
+        <v>81862</v>
       </c>
       <c r="F528" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G528" s="1" t="s">
         <v>9</v>
@@ -14173,16 +14173,16 @@
         <v>35</v>
       </c>
       <c r="C529" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D529" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E529" s="2">
-        <v>81965</v>
+        <v>81863</v>
       </c>
       <c r="F529" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G529" s="1" t="s">
         <v>9</v>
@@ -14199,16 +14199,16 @@
         <v>35</v>
       </c>
       <c r="C530" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D530" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E530" s="2">
-        <v>82085</v>
+        <v>81958</v>
       </c>
       <c r="F530" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>9</v>
@@ -14225,16 +14225,16 @@
         <v>35</v>
       </c>
       <c r="C531" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D531" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E531" s="2">
-        <v>82086</v>
+        <v>81965</v>
       </c>
       <c r="F531" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G531" s="1" t="s">
         <v>9</v>
@@ -14257,10 +14257,10 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E532" s="2">
-        <v>82126</v>
+        <v>82085</v>
       </c>
       <c r="F532" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G532" s="1" t="s">
         <v>9</v>
@@ -14277,16 +14277,16 @@
         <v>35</v>
       </c>
       <c r="C533" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D533" s="3">
-        <v>46064.5127051505</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E533" s="2">
-        <v>82268</v>
+        <v>82086</v>
       </c>
       <c r="F533" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G533" s="1" t="s">
         <v>9</v>
@@ -14303,13 +14303,13 @@
         <v>35</v>
       </c>
       <c r="C534" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D534" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E534" s="2">
-        <v>82142</v>
+        <v>82126</v>
       </c>
       <c r="F534" s="3">
         <v>46065</v>
@@ -14329,16 +14329,16 @@
         <v>35</v>
       </c>
       <c r="C535" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D535" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E535" s="2">
-        <v>82143</v>
+        <v>82268</v>
       </c>
       <c r="F535" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G535" s="1" t="s">
         <v>9</v>
@@ -14361,7 +14361,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E536" s="2">
-        <v>82144</v>
+        <v>82142</v>
       </c>
       <c r="F536" s="3">
         <v>46065</v>
@@ -14387,10 +14387,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E537" s="2">
-        <v>82166</v>
+        <v>82143</v>
       </c>
       <c r="F537" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="G537" s="1" t="s">
         <v>9</v>
@@ -14407,16 +14407,16 @@
         <v>35</v>
       </c>
       <c r="C538" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D538" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E538" s="2">
-        <v>82262</v>
+        <v>82144</v>
       </c>
       <c r="F538" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G538" s="1" t="s">
         <v>9</v>
@@ -14433,16 +14433,16 @@
         <v>35</v>
       </c>
       <c r="C539" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D539" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E539" s="2">
-        <v>82265</v>
+        <v>82166</v>
       </c>
       <c r="F539" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G539" s="1" t="s">
         <v>9</v>
@@ -14465,7 +14465,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E540" s="2">
-        <v>82281</v>
+        <v>82262</v>
       </c>
       <c r="F540" s="3">
         <v>46077</v>
@@ -14491,7 +14491,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E541" s="2">
-        <v>82282</v>
+        <v>82265</v>
       </c>
       <c r="F541" s="3">
         <v>46077</v>
@@ -14511,16 +14511,16 @@
         <v>35</v>
       </c>
       <c r="C542" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D542" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E542" s="2">
-        <v>82340</v>
+        <v>82281</v>
       </c>
       <c r="F542" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G542" s="1" t="s">
         <v>9</v>
@@ -14537,16 +14537,16 @@
         <v>35</v>
       </c>
       <c r="C543" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D543" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E543" s="2">
-        <v>82399</v>
+        <v>82282</v>
       </c>
       <c r="F543" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G543" s="1" t="s">
         <v>9</v>
@@ -14563,16 +14563,16 @@
         <v>35</v>
       </c>
       <c r="C544" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D544" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E544" s="2">
-        <v>82400</v>
+        <v>82340</v>
       </c>
       <c r="F544" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="G544" s="1" t="s">
         <v>9</v>
@@ -14595,7 +14595,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E545" s="2">
-        <v>82401</v>
+        <v>82399</v>
       </c>
       <c r="F545" s="3">
         <v>46083</v>
@@ -14621,10 +14621,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E546" s="2">
-        <v>82412</v>
+        <v>82400</v>
       </c>
       <c r="F546" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G546" s="1" t="s">
         <v>9</v>
@@ -14647,10 +14647,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E547" s="2">
-        <v>82415</v>
+        <v>82401</v>
       </c>
       <c r="F547" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G547" s="1" t="s">
         <v>9</v>
@@ -14667,16 +14667,16 @@
         <v>35</v>
       </c>
       <c r="C548" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D548" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E548" s="2">
-        <v>82571</v>
+        <v>82412</v>
       </c>
       <c r="F548" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G548" s="1" t="s">
         <v>9</v>
@@ -14693,16 +14693,16 @@
         <v>35</v>
       </c>
       <c r="C549" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D549" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E549" s="2">
-        <v>82572</v>
+        <v>82415</v>
       </c>
       <c r="F549" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G549" s="1" t="s">
         <v>9</v>
@@ -14719,16 +14719,16 @@
         <v>35</v>
       </c>
       <c r="C550" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D550" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E550" s="2">
-        <v>82630</v>
+        <v>82571</v>
       </c>
       <c r="F550" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G550" s="1" t="s">
         <v>9</v>
@@ -14745,16 +14745,16 @@
         <v>35</v>
       </c>
       <c r="C551" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D551" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E551" s="2">
-        <v>82631</v>
+        <v>82572</v>
       </c>
       <c r="F551" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G551" s="1" t="s">
         <v>9</v>
@@ -14777,7 +14777,7 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E552" s="2">
-        <v>82632</v>
+        <v>82630</v>
       </c>
       <c r="F552" s="3">
         <v>46094</v>
@@ -14797,16 +14797,16 @@
         <v>35</v>
       </c>
       <c r="C553" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D553" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E553" s="2">
-        <v>82653</v>
+        <v>82631</v>
       </c>
       <c r="F553" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G553" s="1" t="s">
         <v>9</v>
@@ -14823,16 +14823,16 @@
         <v>35</v>
       </c>
       <c r="C554" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D554" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E554" s="2">
-        <v>82665</v>
+        <v>82632</v>
       </c>
       <c r="F554" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G554" s="1" t="s">
         <v>9</v>
@@ -14855,7 +14855,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E555" s="2">
-        <v>82668</v>
+        <v>82653</v>
       </c>
       <c r="F555" s="3">
         <v>46097</v>
@@ -14875,16 +14875,16 @@
         <v>35</v>
       </c>
       <c r="C556" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D556" s="3">
-        <v>46098.6661386574</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E556" s="2">
-        <v>82696</v>
+        <v>82665</v>
       </c>
       <c r="F556" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G556" s="1" t="s">
         <v>9</v>
@@ -14901,16 +14901,16 @@
         <v>35</v>
       </c>
       <c r="C557" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D557" s="3">
-        <v>46098.6661386574</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E557" s="2">
-        <v>82704</v>
+        <v>82668</v>
       </c>
       <c r="F557" s="3">
-        <v>46099</v>
+        <v>46097</v>
       </c>
       <c r="G557" s="1" t="s">
         <v>9</v>
@@ -14921,22 +14921,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="558">
       <c r="A558" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C558" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D558" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E558" s="2">
-        <v>82311</v>
+        <v>82696</v>
       </c>
       <c r="F558" s="3">
-        <v>46078</v>
+        <v>46098</v>
       </c>
       <c r="G558" s="1" t="s">
         <v>9</v>
@@ -14947,22 +14947,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="559">
       <c r="A559" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C559" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D559" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E559" s="2">
-        <v>82312</v>
+        <v>82704</v>
       </c>
       <c r="F559" s="3">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="G559" s="1" t="s">
         <v>9</v>
@@ -14985,7 +14985,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E560" s="2">
-        <v>82313</v>
+        <v>82311</v>
       </c>
       <c r="F560" s="3">
         <v>46078</v>
@@ -15011,7 +15011,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E561" s="2">
-        <v>82314</v>
+        <v>82312</v>
       </c>
       <c r="F561" s="3">
         <v>46078</v>
@@ -15037,10 +15037,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E562" s="2">
-        <v>82346</v>
+        <v>82313</v>
       </c>
       <c r="F562" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G562" s="1" t="s">
         <v>9</v>
@@ -15063,10 +15063,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E563" s="2">
-        <v>82361</v>
+        <v>82314</v>
       </c>
       <c r="F563" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G563" s="1" t="s">
         <v>9</v>
@@ -15089,10 +15089,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E564" s="2">
-        <v>82385</v>
+        <v>82346</v>
       </c>
       <c r="F564" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G564" s="1" t="s">
         <v>9</v>
@@ -15115,10 +15115,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E565" s="2">
-        <v>82391</v>
+        <v>82361</v>
       </c>
       <c r="F565" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G565" s="1" t="s">
         <v>9</v>
@@ -15141,7 +15141,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E566" s="2">
-        <v>82392</v>
+        <v>82385</v>
       </c>
       <c r="F566" s="3">
         <v>46083</v>
@@ -15161,16 +15161,16 @@
         <v>36</v>
       </c>
       <c r="C567" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D567" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E567" s="2">
-        <v>82691</v>
+        <v>82391</v>
       </c>
       <c r="F567" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G567" s="1" t="s">
         <v>9</v>
@@ -15187,16 +15187,16 @@
         <v>36</v>
       </c>
       <c r="C568" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D568" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E568" s="2">
-        <v>82692</v>
+        <v>82392</v>
       </c>
       <c r="F568" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G568" s="1" t="s">
         <v>9</v>
@@ -15219,7 +15219,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E569" s="2">
-        <v>82699</v>
+        <v>82691</v>
       </c>
       <c r="F569" s="3">
         <v>46098</v>
@@ -15245,10 +15245,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E570" s="2">
-        <v>82716</v>
+        <v>82692</v>
       </c>
       <c r="F570" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G570" s="1" t="s">
         <v>9</v>
@@ -15271,10 +15271,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E571" s="2">
-        <v>82717</v>
+        <v>82699</v>
       </c>
       <c r="F571" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G571" s="1" t="s">
         <v>9</v>
@@ -15285,22 +15285,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="572">
       <c r="A572" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C572" s="2">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D572" s="3">
-        <v>46029.4632696412</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E572" s="2">
-        <v>81495</v>
+        <v>82716</v>
       </c>
       <c r="F572" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G572" s="1" t="s">
         <v>9</v>
@@ -15311,27 +15311,105 @@
     </row>
     <row ht="12.75" customHeight="1" r="573">
       <c r="A573" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C573" s="2">
+        <v>2</v>
+      </c>
+      <c r="D573" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="E573" s="2">
+        <v>82717</v>
+      </c>
+      <c r="F573" s="3">
+        <v>46099</v>
+      </c>
+      <c r="G573" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H573" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="574">
+      <c r="A574" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C574" s="2">
+        <v>3</v>
+      </c>
+      <c r="D574" s="3">
+        <v>46104.452366169</v>
+      </c>
+      <c r="E574" s="2">
+        <v>82780</v>
+      </c>
+      <c r="F574" s="3">
+        <v>46104</v>
+      </c>
+      <c r="G574" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H574" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="575">
+      <c r="A575" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C575" s="2">
+        <v>62</v>
+      </c>
+      <c r="D575" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E575" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F575" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G575" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H575" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="576">
+      <c r="A576" s="2">
         <v>9992</v>
       </c>
-      <c r="B573" s="1" t="s">
+      <c r="B576" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C573" s="2">
+      <c r="C576" s="2">
         <v>390</v>
       </c>
-      <c r="D573" s="3">
+      <c r="D576" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E573" s="2">
+      <c r="E576" s="2">
         <v>81684</v>
       </c>
-      <c r="F573" s="3">
+      <c r="F576" s="3">
         <v>46038</v>
       </c>
-      <c r="G573" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H573" s="1" t="s">
+      <c r="G576" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H576" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H576"/>
+  <dimension ref="A1:H577"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -15363,22 +15363,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="575">
       <c r="A575" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C575" s="2">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="D575" s="3">
-        <v>46029.4632696412</v>
+        <v>46104.452366169</v>
       </c>
       <c r="E575" s="2">
-        <v>81495</v>
+        <v>82784</v>
       </c>
       <c r="F575" s="3">
-        <v>46029</v>
+        <v>46104</v>
       </c>
       <c r="G575" s="1" t="s">
         <v>9</v>
@@ -15389,27 +15389,53 @@
     </row>
     <row ht="12.75" customHeight="1" r="576">
       <c r="A576" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C576" s="2">
+        <v>62</v>
+      </c>
+      <c r="D576" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E576" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F576" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G576" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H576" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="577">
+      <c r="A577" s="2">
         <v>9992</v>
       </c>
-      <c r="B576" s="1" t="s">
+      <c r="B577" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C576" s="2">
+      <c r="C577" s="2">
         <v>390</v>
       </c>
-      <c r="D576" s="3">
+      <c r="D577" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E576" s="2">
+      <c r="E577" s="2">
         <v>81684</v>
       </c>
-      <c r="F576" s="3">
+      <c r="F577" s="3">
         <v>46038</v>
       </c>
-      <c r="G576" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H576" s="1" t="s">
+      <c r="G577" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H577" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -74,12 +74,6 @@
     <t>SUN MORITZ ADMINISTRADORA</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Não Concluídos</t>
-  </si>
-  <si>
     <t>MARIA BELTRÃO SALDANHA COELHO</t>
   </si>
   <si>
@@ -99,6 +93,12 @@
   </si>
   <si>
     <t>KATIA FERREIRA DE BARROS</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Não Concluídos</t>
   </si>
   <si>
     <t>RAFAEL CURSINO DE MOURA LEVY</t>
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H577"/>
+  <dimension ref="A1:H578"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -3577,10 +3577,10 @@
         <v>46104</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="122">
@@ -3603,10 +3603,10 @@
         <v>46104</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="123">
@@ -3614,7 +3614,7 @@
         <v>2409</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C123" s="2">
         <v>82</v>
@@ -3640,7 +3640,7 @@
         <v>2409</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C124" s="2">
         <v>82</v>
@@ -3666,7 +3666,7 @@
         <v>2409</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C125" s="2">
         <v>82</v>
@@ -3692,7 +3692,7 @@
         <v>2409</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C126" s="2">
         <v>83</v>
@@ -3718,7 +3718,7 @@
         <v>2409</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C127" s="2">
         <v>83</v>
@@ -3744,7 +3744,7 @@
         <v>2409</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C128" s="2">
         <v>83</v>
@@ -3770,7 +3770,7 @@
         <v>2409</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C129" s="2">
         <v>83</v>
@@ -3796,7 +3796,7 @@
         <v>2409</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C130" s="2">
         <v>84</v>
@@ -3822,7 +3822,7 @@
         <v>2409</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C131" s="2">
         <v>84</v>
@@ -3848,7 +3848,7 @@
         <v>2409</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C132" s="2">
         <v>84</v>
@@ -3874,7 +3874,7 @@
         <v>2409</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C133" s="2">
         <v>84</v>
@@ -3900,7 +3900,7 @@
         <v>2409</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C134" s="2">
         <v>84</v>
@@ -3926,7 +3926,7 @@
         <v>2409</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C135" s="2">
         <v>85</v>
@@ -3952,7 +3952,7 @@
         <v>2409</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C136" s="2">
         <v>86</v>
@@ -3978,7 +3978,7 @@
         <v>2409</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C137" s="2">
         <v>86</v>
@@ -4004,7 +4004,7 @@
         <v>2409</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C138" s="2">
         <v>86</v>
@@ -4030,7 +4030,7 @@
         <v>2409</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C139" s="2">
         <v>86</v>
@@ -4056,7 +4056,7 @@
         <v>2409</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C140" s="2">
         <v>87</v>
@@ -4082,7 +4082,7 @@
         <v>2409</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C141" s="2">
         <v>88</v>
@@ -4108,7 +4108,7 @@
         <v>2409</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C142" s="2">
         <v>88</v>
@@ -4134,7 +4134,7 @@
         <v>2409</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C143" s="2">
         <v>88</v>
@@ -4160,7 +4160,7 @@
         <v>2409</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C144" s="2">
         <v>89</v>
@@ -4186,7 +4186,7 @@
         <v>2409</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C145" s="2">
         <v>89</v>
@@ -4212,7 +4212,7 @@
         <v>2409</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C146" s="2">
         <v>89</v>
@@ -4238,7 +4238,7 @@
         <v>2409</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C147" s="2">
         <v>89</v>
@@ -4264,7 +4264,7 @@
         <v>2409</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C148" s="2">
         <v>89</v>
@@ -4290,7 +4290,7 @@
         <v>2409</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C149" s="2">
         <v>89</v>
@@ -4316,7 +4316,7 @@
         <v>2409</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C150" s="2">
         <v>89</v>
@@ -4342,7 +4342,7 @@
         <v>2409</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C151" s="2">
         <v>90</v>
@@ -4368,7 +4368,7 @@
         <v>2409</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C152" s="2">
         <v>90</v>
@@ -4394,7 +4394,7 @@
         <v>2409</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C153" s="2">
         <v>90</v>
@@ -4420,7 +4420,7 @@
         <v>2409</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C154" s="2">
         <v>92</v>
@@ -4446,7 +4446,7 @@
         <v>2409</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C155" s="2">
         <v>92</v>
@@ -4472,7 +4472,7 @@
         <v>2409</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C156" s="2">
         <v>93</v>
@@ -4498,7 +4498,7 @@
         <v>2409</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C157" s="2">
         <v>93</v>
@@ -4524,7 +4524,7 @@
         <v>2409</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C158" s="2">
         <v>93</v>
@@ -4550,7 +4550,7 @@
         <v>2409</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C159" s="2">
         <v>93</v>
@@ -4576,7 +4576,7 @@
         <v>2409</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C160" s="2">
         <v>93</v>
@@ -4602,7 +4602,7 @@
         <v>2409</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C161" s="2">
         <v>93</v>
@@ -4628,7 +4628,7 @@
         <v>2409</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C162" s="2">
         <v>93</v>
@@ -4654,7 +4654,7 @@
         <v>2411</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C163" s="2">
         <v>77</v>
@@ -4680,7 +4680,7 @@
         <v>2411</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C164" s="2">
         <v>77</v>
@@ -4706,7 +4706,7 @@
         <v>2411</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C165" s="2">
         <v>77</v>
@@ -4732,7 +4732,7 @@
         <v>2411</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C166" s="2">
         <v>77</v>
@@ -4758,7 +4758,7 @@
         <v>2411</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C167" s="2">
         <v>77</v>
@@ -4784,7 +4784,7 @@
         <v>2411</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C168" s="2">
         <v>78</v>
@@ -4810,7 +4810,7 @@
         <v>2411</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C169" s="2">
         <v>78</v>
@@ -4836,7 +4836,7 @@
         <v>2411</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C170" s="2">
         <v>78</v>
@@ -4862,7 +4862,7 @@
         <v>2504</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C171" s="2">
         <v>44</v>
@@ -4888,7 +4888,7 @@
         <v>2504</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C172" s="2">
         <v>44</v>
@@ -4914,7 +4914,7 @@
         <v>2504</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C173" s="2">
         <v>44</v>
@@ -4940,7 +4940,7 @@
         <v>2504</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C174" s="2">
         <v>44</v>
@@ -4966,7 +4966,7 @@
         <v>2504</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C175" s="2">
         <v>44</v>
@@ -4992,7 +4992,7 @@
         <v>2504</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C176" s="2">
         <v>44</v>
@@ -5018,7 +5018,7 @@
         <v>2504</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C177" s="2">
         <v>44</v>
@@ -5044,7 +5044,7 @@
         <v>2504</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C178" s="2">
         <v>45</v>
@@ -5070,7 +5070,7 @@
         <v>2504</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C179" s="2">
         <v>46</v>
@@ -5096,7 +5096,7 @@
         <v>2504</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C180" s="2">
         <v>46</v>
@@ -5122,7 +5122,7 @@
         <v>2504</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C181" s="2">
         <v>46</v>
@@ -5148,7 +5148,7 @@
         <v>2504</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C182" s="2">
         <v>46</v>
@@ -5174,7 +5174,7 @@
         <v>2504</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C183" s="2">
         <v>46</v>
@@ -5200,7 +5200,7 @@
         <v>2504</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C184" s="2">
         <v>47</v>
@@ -5226,7 +5226,7 @@
         <v>2504</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C185" s="2">
         <v>47</v>
@@ -5252,7 +5252,7 @@
         <v>2504</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C186" s="2">
         <v>47</v>
@@ -5278,7 +5278,7 @@
         <v>2504</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C187" s="2">
         <v>48</v>
@@ -5304,7 +5304,7 @@
         <v>2504</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C188" s="2">
         <v>48</v>
@@ -5330,7 +5330,7 @@
         <v>2504</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C189" s="2">
         <v>48</v>
@@ -5356,7 +5356,7 @@
         <v>2504</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C190" s="2">
         <v>48</v>
@@ -5382,7 +5382,7 @@
         <v>2504</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C191" s="2">
         <v>49</v>
@@ -5408,7 +5408,7 @@
         <v>2504</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C192" s="2">
         <v>49</v>
@@ -5434,7 +5434,7 @@
         <v>2504</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C193" s="2">
         <v>49</v>
@@ -5460,7 +5460,7 @@
         <v>2504</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C194" s="2">
         <v>49</v>
@@ -5486,7 +5486,7 @@
         <v>2504</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C195" s="2">
         <v>49</v>
@@ -5512,7 +5512,7 @@
         <v>2504</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C196" s="2">
         <v>50</v>
@@ -5538,7 +5538,7 @@
         <v>2504</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C197" s="2">
         <v>50</v>
@@ -5564,7 +5564,7 @@
         <v>2504</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C198" s="2">
         <v>50</v>
@@ -5590,7 +5590,7 @@
         <v>2504</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C199" s="2">
         <v>50</v>
@@ -5616,7 +5616,7 @@
         <v>2504</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C200" s="2">
         <v>50</v>
@@ -5642,7 +5642,7 @@
         <v>2504</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C201" s="2">
         <v>50</v>
@@ -5668,7 +5668,7 @@
         <v>2504</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C202" s="2">
         <v>51</v>
@@ -5694,7 +5694,7 @@
         <v>2504</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C203" s="2">
         <v>52</v>
@@ -5720,7 +5720,7 @@
         <v>2504</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C204" s="2">
         <v>52</v>
@@ -5746,7 +5746,7 @@
         <v>2504</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C205" s="2">
         <v>53</v>
@@ -5772,7 +5772,7 @@
         <v>2504</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C206" s="2">
         <v>54</v>
@@ -5798,7 +5798,7 @@
         <v>2504</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C207" s="2">
         <v>55</v>
@@ -5824,7 +5824,7 @@
         <v>2504</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C208" s="2">
         <v>55</v>
@@ -5850,7 +5850,7 @@
         <v>2504</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C209" s="2">
         <v>55</v>
@@ -5876,7 +5876,7 @@
         <v>2504</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C210" s="2">
         <v>55</v>
@@ -5902,7 +5902,7 @@
         <v>2504</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C211" s="2">
         <v>56</v>
@@ -5928,7 +5928,7 @@
         <v>2504</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C212" s="2">
         <v>56</v>
@@ -5954,7 +5954,7 @@
         <v>2504</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C213" s="2">
         <v>56</v>
@@ -5980,7 +5980,7 @@
         <v>2504</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C214" s="2">
         <v>57</v>
@@ -6006,7 +6006,7 @@
         <v>2504</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C215" s="2">
         <v>57</v>
@@ -6032,7 +6032,7 @@
         <v>2505</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C216" s="2">
         <v>42</v>
@@ -6058,7 +6058,7 @@
         <v>2505</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C217" s="2">
         <v>42</v>
@@ -6084,7 +6084,7 @@
         <v>2505</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C218" s="2">
         <v>42</v>
@@ -6110,7 +6110,7 @@
         <v>2505</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C219" s="2">
         <v>42</v>
@@ -6136,7 +6136,7 @@
         <v>2505</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C220" s="2">
         <v>42</v>
@@ -6162,7 +6162,7 @@
         <v>2505</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C221" s="2">
         <v>42</v>
@@ -6188,7 +6188,7 @@
         <v>2505</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C222" s="2">
         <v>42</v>
@@ -6214,7 +6214,7 @@
         <v>2505</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C223" s="2">
         <v>42</v>
@@ -6240,7 +6240,7 @@
         <v>2505</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C224" s="2">
         <v>42</v>
@@ -6266,7 +6266,7 @@
         <v>2505</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C225" s="2">
         <v>43</v>
@@ -6292,7 +6292,7 @@
         <v>2505</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C226" s="2">
         <v>43</v>
@@ -6318,7 +6318,7 @@
         <v>2505</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C227" s="2">
         <v>43</v>
@@ -6344,7 +6344,7 @@
         <v>2505</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C228" s="2">
         <v>43</v>
@@ -6370,7 +6370,7 @@
         <v>2505</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C229" s="2">
         <v>43</v>
@@ -6396,7 +6396,7 @@
         <v>2505</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C230" s="2">
         <v>44</v>
@@ -6422,7 +6422,7 @@
         <v>2505</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C231" s="2">
         <v>44</v>
@@ -6448,7 +6448,7 @@
         <v>2505</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C232" s="2">
         <v>44</v>
@@ -6474,7 +6474,7 @@
         <v>2505</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C233" s="2">
         <v>44</v>
@@ -6500,7 +6500,7 @@
         <v>2505</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C234" s="2">
         <v>44</v>
@@ -6515,10 +6515,10 @@
         <v>46079</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="235">
@@ -6526,7 +6526,7 @@
         <v>2505</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C235" s="2">
         <v>44</v>
@@ -6552,7 +6552,7 @@
         <v>2505</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C236" s="2">
         <v>45</v>
@@ -6578,7 +6578,7 @@
         <v>2505</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C237" s="2">
         <v>45</v>
@@ -6604,7 +6604,7 @@
         <v>2505</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C238" s="2">
         <v>45</v>
@@ -6630,7 +6630,7 @@
         <v>2505</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C239" s="2">
         <v>46</v>
@@ -6656,7 +6656,7 @@
         <v>2505</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C240" s="2">
         <v>46</v>
@@ -6682,7 +6682,7 @@
         <v>2505</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C241" s="2">
         <v>46</v>
@@ -6708,7 +6708,7 @@
         <v>2505</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C242" s="2">
         <v>46</v>
@@ -6734,7 +6734,7 @@
         <v>2505</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C243" s="2">
         <v>47</v>
@@ -6760,7 +6760,7 @@
         <v>2505</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C244" s="2">
         <v>47</v>
@@ -6786,7 +6786,7 @@
         <v>2505</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C245" s="2">
         <v>47</v>
@@ -6812,7 +6812,7 @@
         <v>2505</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C246" s="2">
         <v>48</v>
@@ -6838,7 +6838,7 @@
         <v>2505</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C247" s="2">
         <v>48</v>
@@ -6864,7 +6864,7 @@
         <v>2505</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C248" s="2">
         <v>48</v>
@@ -6890,7 +6890,7 @@
         <v>2505</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C249" s="2">
         <v>48</v>
@@ -6916,7 +6916,7 @@
         <v>2505</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C250" s="2">
         <v>48</v>
@@ -6942,7 +6942,7 @@
         <v>2506</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C251" s="2">
         <v>27</v>
@@ -6968,7 +6968,7 @@
         <v>2506</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C252" s="2">
         <v>27</v>
@@ -6994,7 +6994,7 @@
         <v>2506</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C253" s="2">
         <v>27</v>
@@ -7020,7 +7020,7 @@
         <v>2506</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C254" s="2">
         <v>27</v>
@@ -7046,7 +7046,7 @@
         <v>2506</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C255" s="2">
         <v>27</v>
@@ -7072,7 +7072,7 @@
         <v>2506</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C256" s="2">
         <v>27</v>
@@ -7098,7 +7098,7 @@
         <v>2506</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C257" s="2">
         <v>27</v>
@@ -7124,7 +7124,7 @@
         <v>2506</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C258" s="2">
         <v>27</v>
@@ -7150,7 +7150,7 @@
         <v>2506</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C259" s="2">
         <v>27</v>
@@ -7176,7 +7176,7 @@
         <v>2506</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C260" s="2">
         <v>27</v>
@@ -7202,7 +7202,7 @@
         <v>2506</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C261" s="2">
         <v>27</v>
@@ -7228,7 +7228,7 @@
         <v>2506</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C262" s="2">
         <v>27</v>
@@ -7254,7 +7254,7 @@
         <v>2506</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C263" s="2">
         <v>28</v>
@@ -7280,7 +7280,7 @@
         <v>2506</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C264" s="2">
         <v>28</v>
@@ -7306,7 +7306,7 @@
         <v>2506</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C265" s="2">
         <v>28</v>
@@ -7332,7 +7332,7 @@
         <v>2506</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C266" s="2">
         <v>28</v>
@@ -7358,7 +7358,7 @@
         <v>2506</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C267" s="2">
         <v>28</v>
@@ -7384,7 +7384,7 @@
         <v>2506</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C268" s="2">
         <v>28</v>
@@ -7410,7 +7410,7 @@
         <v>2506</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C269" s="2">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>2506</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C270" s="2">
         <v>28</v>
@@ -7462,7 +7462,7 @@
         <v>2506</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C271" s="2">
         <v>29</v>
@@ -7488,7 +7488,7 @@
         <v>2506</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C272" s="2">
         <v>29</v>
@@ -7514,7 +7514,7 @@
         <v>2506</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C273" s="2">
         <v>29</v>
@@ -7540,7 +7540,7 @@
         <v>2506</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C274" s="2">
         <v>30</v>
@@ -7566,7 +7566,7 @@
         <v>2506</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C275" s="2">
         <v>31</v>
@@ -7592,7 +7592,7 @@
         <v>2506</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C276" s="2">
         <v>32</v>
@@ -7618,7 +7618,7 @@
         <v>2506</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C277" s="2">
         <v>32</v>
@@ -7633,10 +7633,10 @@
         <v>46093</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="278">
@@ -7644,7 +7644,7 @@
         <v>2506</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C278" s="2">
         <v>32</v>
@@ -7670,7 +7670,7 @@
         <v>2506</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C279" s="2">
         <v>32</v>
@@ -7696,7 +7696,7 @@
         <v>2506</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C280" s="2">
         <v>32</v>
@@ -7722,7 +7722,7 @@
         <v>2506</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C281" s="2">
         <v>32</v>
@@ -7748,7 +7748,7 @@
         <v>2506</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C282" s="2">
         <v>32</v>
@@ -7774,7 +7774,7 @@
         <v>2506</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C283" s="2">
         <v>32</v>
@@ -7800,7 +7800,7 @@
         <v>2507</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C284" s="2">
         <v>26</v>
@@ -7826,7 +7826,7 @@
         <v>2507</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C285" s="2">
         <v>26</v>
@@ -7852,7 +7852,7 @@
         <v>2507</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C286" s="2">
         <v>26</v>
@@ -7878,7 +7878,7 @@
         <v>2507</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C287" s="2">
         <v>26</v>
@@ -7904,7 +7904,7 @@
         <v>2507</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C288" s="2">
         <v>26</v>
@@ -7930,7 +7930,7 @@
         <v>2507</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C289" s="2">
         <v>26</v>
@@ -7956,7 +7956,7 @@
         <v>2507</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C290" s="2">
         <v>26</v>
@@ -7982,7 +7982,7 @@
         <v>2507</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C291" s="2">
         <v>27</v>
@@ -8008,7 +8008,7 @@
         <v>2507</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C292" s="2">
         <v>27</v>
@@ -8034,7 +8034,7 @@
         <v>2507</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C293" s="2">
         <v>27</v>
@@ -8060,7 +8060,7 @@
         <v>2507</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C294" s="2">
         <v>27</v>
@@ -8086,7 +8086,7 @@
         <v>2507</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C295" s="2">
         <v>28</v>
@@ -8112,7 +8112,7 @@
         <v>2507</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C296" s="2">
         <v>28</v>
@@ -8138,7 +8138,7 @@
         <v>2507</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C297" s="2">
         <v>28</v>
@@ -8164,7 +8164,7 @@
         <v>2507</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C298" s="2">
         <v>28</v>
@@ -8190,7 +8190,7 @@
         <v>2507</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C299" s="2">
         <v>29</v>
@@ -8216,7 +8216,7 @@
         <v>2507</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C300" s="2">
         <v>29</v>
@@ -8242,7 +8242,7 @@
         <v>2507</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C301" s="2">
         <v>29</v>
@@ -8268,7 +8268,7 @@
         <v>2507</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C302" s="2">
         <v>29</v>
@@ -8294,7 +8294,7 @@
         <v>2507</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C303" s="2">
         <v>29</v>
@@ -8320,7 +8320,7 @@
         <v>2507</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C304" s="2">
         <v>29</v>
@@ -8346,7 +8346,7 @@
         <v>2507</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C305" s="2">
         <v>30</v>
@@ -8372,7 +8372,7 @@
         <v>2507</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C306" s="2">
         <v>31</v>
@@ -8398,7 +8398,7 @@
         <v>2507</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C307" s="2">
         <v>31</v>
@@ -8424,7 +8424,7 @@
         <v>2507</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C308" s="2">
         <v>31</v>
@@ -8450,7 +8450,7 @@
         <v>2507</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C309" s="2">
         <v>31</v>
@@ -8476,7 +8476,7 @@
         <v>2507</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C310" s="2">
         <v>32</v>
@@ -8502,7 +8502,7 @@
         <v>2507</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C311" s="2">
         <v>32</v>
@@ -8528,7 +8528,7 @@
         <v>2507</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C312" s="2">
         <v>32</v>
@@ -8554,7 +8554,7 @@
         <v>2507</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C313" s="2">
         <v>32</v>
@@ -8580,7 +8580,7 @@
         <v>2507</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C314" s="2">
         <v>32</v>
@@ -8606,7 +8606,7 @@
         <v>2507</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C315" s="2">
         <v>32</v>
@@ -8632,7 +8632,7 @@
         <v>2507</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C316" s="2">
         <v>32</v>
@@ -8658,7 +8658,7 @@
         <v>2507</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C317" s="2">
         <v>33</v>
@@ -8684,7 +8684,7 @@
         <v>2507</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C318" s="2">
         <v>34</v>
@@ -8699,10 +8699,10 @@
         <v>46104</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="319">
@@ -9271,10 +9271,10 @@
         <v>46059</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="341">
@@ -13561,10 +13561,10 @@
         <v>46031</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H505" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="506">
@@ -13639,10 +13639,10 @@
         <v>46041</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="509">
@@ -15355,10 +15355,10 @@
         <v>46104</v>
       </c>
       <c r="G574" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="575">
@@ -15389,22 +15389,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="576">
       <c r="A576" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C576" s="2">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="D576" s="3">
-        <v>46029.4632696412</v>
+        <v>46104.452366169</v>
       </c>
       <c r="E576" s="2">
-        <v>81495</v>
+        <v>82785</v>
       </c>
       <c r="F576" s="3">
-        <v>46029</v>
+        <v>46104</v>
       </c>
       <c r="G576" s="1" t="s">
         <v>9</v>
@@ -15415,27 +15415,53 @@
     </row>
     <row ht="12.75" customHeight="1" r="577">
       <c r="A577" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C577" s="2">
+        <v>62</v>
+      </c>
+      <c r="D577" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E577" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F577" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G577" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H577" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="578">
+      <c r="A578" s="2">
         <v>9992</v>
       </c>
-      <c r="B577" s="1" t="s">
+      <c r="B578" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C577" s="2">
+      <c r="C578" s="2">
         <v>390</v>
       </c>
-      <c r="D577" s="3">
+      <c r="D578" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E577" s="2">
+      <c r="E578" s="2">
         <v>81684</v>
       </c>
-      <c r="F577" s="3">
+      <c r="F578" s="3">
         <v>46038</v>
       </c>
-      <c r="G577" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H577" s="1" t="s">
+      <c r="G578" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H578" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H578"/>
+  <dimension ref="A1:H579"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -15343,22 +15343,22 @@
         <v>36</v>
       </c>
       <c r="C574" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D574" s="3">
-        <v>46104.452366169</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E574" s="2">
-        <v>82780</v>
+        <v>82786</v>
       </c>
       <c r="F574" s="3">
         <v>46104</v>
       </c>
       <c r="G574" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="575">
@@ -15375,7 +15375,7 @@
         <v>46104.452366169</v>
       </c>
       <c r="E575" s="2">
-        <v>82784</v>
+        <v>82780</v>
       </c>
       <c r="F575" s="3">
         <v>46104</v>
@@ -15401,7 +15401,7 @@
         <v>46104.452366169</v>
       </c>
       <c r="E576" s="2">
-        <v>82785</v>
+        <v>82784</v>
       </c>
       <c r="F576" s="3">
         <v>46104</v>
@@ -15415,22 +15415,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="577">
       <c r="A577" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C577" s="2">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="D577" s="3">
-        <v>46029.4632696412</v>
+        <v>46104.452366169</v>
       </c>
       <c r="E577" s="2">
-        <v>81495</v>
+        <v>82785</v>
       </c>
       <c r="F577" s="3">
-        <v>46029</v>
+        <v>46104</v>
       </c>
       <c r="G577" s="1" t="s">
         <v>9</v>
@@ -15441,27 +15441,53 @@
     </row>
     <row ht="12.75" customHeight="1" r="578">
       <c r="A578" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C578" s="2">
+        <v>62</v>
+      </c>
+      <c r="D578" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E578" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F578" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G578" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H578" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="579">
+      <c r="A579" s="2">
         <v>9992</v>
       </c>
-      <c r="B578" s="1" t="s">
+      <c r="B579" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C578" s="2">
+      <c r="C579" s="2">
         <v>390</v>
       </c>
-      <c r="D578" s="3">
+      <c r="D579" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E578" s="2">
+      <c r="E579" s="2">
         <v>81684</v>
       </c>
-      <c r="F578" s="3">
+      <c r="F579" s="3">
         <v>46038</v>
       </c>
-      <c r="G578" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H578" s="1" t="s">
+      <c r="G579" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H579" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -15355,10 +15355,10 @@
         <v>46104</v>
       </c>
       <c r="G574" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="575">

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H579"/>
+  <dimension ref="A1:H584"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -6029,22 +6029,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="216">
       <c r="A216" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C216" s="2">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D216" s="3">
-        <v>46041.6648751157</v>
+        <v>46105.7396245255</v>
       </c>
       <c r="E216" s="2">
-        <v>81743</v>
+        <v>82799</v>
       </c>
       <c r="F216" s="3">
-        <v>46041</v>
+        <v>46105</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>9</v>
@@ -6055,22 +6055,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="217">
       <c r="A217" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C217" s="2">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D217" s="3">
-        <v>46041.6648751157</v>
+        <v>46105.7396245255</v>
       </c>
       <c r="E217" s="2">
-        <v>81744</v>
+        <v>82807</v>
       </c>
       <c r="F217" s="3">
-        <v>46041</v>
+        <v>46106</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>9</v>
@@ -6093,7 +6093,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E218" s="2">
-        <v>81745</v>
+        <v>81743</v>
       </c>
       <c r="F218" s="3">
         <v>46041</v>
@@ -6119,10 +6119,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E219" s="2">
-        <v>81746</v>
+        <v>81744</v>
       </c>
       <c r="F219" s="3">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>9</v>
@@ -6145,10 +6145,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E220" s="2">
-        <v>81751</v>
+        <v>81745</v>
       </c>
       <c r="F220" s="3">
-        <v>46043</v>
+        <v>46041</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>9</v>
@@ -6171,10 +6171,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E221" s="2">
-        <v>81753</v>
+        <v>81746</v>
       </c>
       <c r="F221" s="3">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>9</v>
@@ -6197,7 +6197,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E222" s="2">
-        <v>81754</v>
+        <v>81751</v>
       </c>
       <c r="F222" s="3">
         <v>46043</v>
@@ -6223,7 +6223,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E223" s="2">
-        <v>81755</v>
+        <v>81753</v>
       </c>
       <c r="F223" s="3">
         <v>46043</v>
@@ -6249,7 +6249,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E224" s="2">
-        <v>81766</v>
+        <v>81754</v>
       </c>
       <c r="F224" s="3">
         <v>46043</v>
@@ -6269,16 +6269,16 @@
         <v>23</v>
       </c>
       <c r="C225" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D225" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E225" s="2">
-        <v>82088</v>
+        <v>81755</v>
       </c>
       <c r="F225" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>9</v>
@@ -6295,16 +6295,16 @@
         <v>23</v>
       </c>
       <c r="C226" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D226" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E226" s="2">
-        <v>82089</v>
+        <v>81766</v>
       </c>
       <c r="F226" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>9</v>
@@ -6327,10 +6327,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E227" s="2">
-        <v>82163</v>
+        <v>82088</v>
       </c>
       <c r="F227" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>9</v>
@@ -6353,10 +6353,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E228" s="2">
-        <v>82179</v>
+        <v>82089</v>
       </c>
       <c r="F228" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>9</v>
@@ -6379,7 +6379,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E229" s="2">
-        <v>82193</v>
+        <v>82163</v>
       </c>
       <c r="F229" s="3">
         <v>46066</v>
@@ -6399,16 +6399,16 @@
         <v>23</v>
       </c>
       <c r="C230" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D230" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E230" s="2">
-        <v>82250</v>
+        <v>82179</v>
       </c>
       <c r="F230" s="3">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>9</v>
@@ -6425,16 +6425,16 @@
         <v>23</v>
       </c>
       <c r="C231" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D231" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E231" s="2">
-        <v>82266</v>
+        <v>82193</v>
       </c>
       <c r="F231" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>9</v>
@@ -6457,10 +6457,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E232" s="2">
-        <v>82295</v>
+        <v>82250</v>
       </c>
       <c r="F232" s="3">
-        <v>46078</v>
+        <v>46073</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>9</v>
@@ -6483,10 +6483,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E233" s="2">
-        <v>82296</v>
+        <v>82266</v>
       </c>
       <c r="F233" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>9</v>
@@ -6509,16 +6509,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E234" s="2">
-        <v>82332</v>
+        <v>82295</v>
       </c>
       <c r="F234" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="235">
@@ -6535,10 +6535,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E235" s="2">
-        <v>82339</v>
+        <v>82296</v>
       </c>
       <c r="F235" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>9</v>
@@ -6555,22 +6555,22 @@
         <v>23</v>
       </c>
       <c r="C236" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D236" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E236" s="2">
-        <v>82266</v>
+        <v>82332</v>
       </c>
       <c r="F236" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="237">
@@ -6581,16 +6581,16 @@
         <v>23</v>
       </c>
       <c r="C237" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D237" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E237" s="2">
-        <v>82273</v>
+        <v>82339</v>
       </c>
       <c r="F237" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>9</v>
@@ -6613,10 +6613,10 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E238" s="2">
-        <v>82294</v>
+        <v>82266</v>
       </c>
       <c r="F238" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>9</v>
@@ -6633,16 +6633,16 @@
         <v>23</v>
       </c>
       <c r="C239" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D239" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E239" s="2">
-        <v>82411</v>
+        <v>82273</v>
       </c>
       <c r="F239" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>9</v>
@@ -6659,16 +6659,16 @@
         <v>23</v>
       </c>
       <c r="C240" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D240" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E240" s="2">
-        <v>82432</v>
+        <v>82294</v>
       </c>
       <c r="F240" s="3">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>9</v>
@@ -6691,10 +6691,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E241" s="2">
-        <v>82473</v>
+        <v>82411</v>
       </c>
       <c r="F241" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>9</v>
@@ -6717,10 +6717,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E242" s="2">
-        <v>82474</v>
+        <v>82432</v>
       </c>
       <c r="F242" s="3">
-        <v>46087</v>
+        <v>46085</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>9</v>
@@ -6737,16 +6737,16 @@
         <v>23</v>
       </c>
       <c r="C243" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D243" s="3">
-        <v>46093.5009358681</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E243" s="2">
-        <v>82594</v>
+        <v>82473</v>
       </c>
       <c r="F243" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>9</v>
@@ -6763,16 +6763,16 @@
         <v>23</v>
       </c>
       <c r="C244" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D244" s="3">
-        <v>46093.5009358681</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E244" s="2">
-        <v>82595</v>
+        <v>82474</v>
       </c>
       <c r="F244" s="3">
-        <v>46093</v>
+        <v>46087</v>
       </c>
       <c r="G244" s="1" t="s">
         <v>9</v>
@@ -6795,10 +6795,10 @@
         <v>46093.5009358681</v>
       </c>
       <c r="E245" s="2">
-        <v>82657</v>
+        <v>82594</v>
       </c>
       <c r="F245" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>9</v>
@@ -6815,16 +6815,16 @@
         <v>23</v>
       </c>
       <c r="C246" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D246" s="3">
-        <v>46098.5034667708</v>
+        <v>46093.5009358681</v>
       </c>
       <c r="E246" s="2">
-        <v>82686</v>
+        <v>82595</v>
       </c>
       <c r="F246" s="3">
-        <v>46098</v>
+        <v>46093</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>9</v>
@@ -6841,16 +6841,16 @@
         <v>23</v>
       </c>
       <c r="C247" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D247" s="3">
-        <v>46098.5034667708</v>
+        <v>46093.5009358681</v>
       </c>
       <c r="E247" s="2">
-        <v>82687</v>
+        <v>82657</v>
       </c>
       <c r="F247" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>9</v>
@@ -6873,10 +6873,10 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E248" s="2">
-        <v>82722</v>
+        <v>82686</v>
       </c>
       <c r="F248" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>9</v>
@@ -6899,10 +6899,10 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E249" s="2">
-        <v>82723</v>
+        <v>82687</v>
       </c>
       <c r="F249" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>9</v>
@@ -6925,10 +6925,10 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E250" s="2">
-        <v>82755</v>
+        <v>82722</v>
       </c>
       <c r="F250" s="3">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>9</v>
@@ -6939,22 +6939,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="251">
       <c r="A251" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C251" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D251" s="3">
-        <v>46044.6368950926</v>
+        <v>46098.5034667708</v>
       </c>
       <c r="E251" s="2">
-        <v>81802</v>
+        <v>82723</v>
       </c>
       <c r="F251" s="3">
-        <v>46044</v>
+        <v>46099</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>9</v>
@@ -6965,22 +6965,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="252">
       <c r="A252" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C252" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D252" s="3">
-        <v>46044.6368950926</v>
+        <v>46098.5034667708</v>
       </c>
       <c r="E252" s="2">
-        <v>81803</v>
+        <v>82755</v>
       </c>
       <c r="F252" s="3">
-        <v>46044</v>
+        <v>46101</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>9</v>
@@ -7003,7 +7003,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E253" s="2">
-        <v>81804</v>
+        <v>81802</v>
       </c>
       <c r="F253" s="3">
         <v>46044</v>
@@ -7029,7 +7029,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E254" s="2">
-        <v>81806</v>
+        <v>81803</v>
       </c>
       <c r="F254" s="3">
         <v>46044</v>
@@ -7055,7 +7055,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E255" s="2">
-        <v>81807</v>
+        <v>81804</v>
       </c>
       <c r="F255" s="3">
         <v>46044</v>
@@ -7081,10 +7081,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E256" s="2">
-        <v>81812</v>
+        <v>81806</v>
       </c>
       <c r="F256" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>9</v>
@@ -7107,10 +7107,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E257" s="2">
-        <v>81813</v>
+        <v>81807</v>
       </c>
       <c r="F257" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>9</v>
@@ -7133,7 +7133,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E258" s="2">
-        <v>81814</v>
+        <v>81812</v>
       </c>
       <c r="F258" s="3">
         <v>46045</v>
@@ -7159,7 +7159,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E259" s="2">
-        <v>81818</v>
+        <v>81813</v>
       </c>
       <c r="F259" s="3">
         <v>46045</v>
@@ -7185,7 +7185,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E260" s="2">
-        <v>81822</v>
+        <v>81814</v>
       </c>
       <c r="F260" s="3">
         <v>46045</v>
@@ -7211,7 +7211,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E261" s="2">
-        <v>81833</v>
+        <v>81818</v>
       </c>
       <c r="F261" s="3">
         <v>46045</v>
@@ -7237,7 +7237,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E262" s="2">
-        <v>81841</v>
+        <v>81822</v>
       </c>
       <c r="F262" s="3">
         <v>46045</v>
@@ -7257,16 +7257,16 @@
         <v>26</v>
       </c>
       <c r="C263" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D263" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E263" s="2">
-        <v>81928</v>
+        <v>81833</v>
       </c>
       <c r="F263" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>9</v>
@@ -7283,16 +7283,16 @@
         <v>26</v>
       </c>
       <c r="C264" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D264" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E264" s="2">
-        <v>81929</v>
+        <v>81841</v>
       </c>
       <c r="F264" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>9</v>
@@ -7315,7 +7315,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E265" s="2">
-        <v>81930</v>
+        <v>81928</v>
       </c>
       <c r="F265" s="3">
         <v>46052</v>
@@ -7341,7 +7341,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E266" s="2">
-        <v>81932</v>
+        <v>81929</v>
       </c>
       <c r="F266" s="3">
         <v>46052</v>
@@ -7367,7 +7367,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E267" s="2">
-        <v>81933</v>
+        <v>81930</v>
       </c>
       <c r="F267" s="3">
         <v>46052</v>
@@ -7393,7 +7393,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E268" s="2">
-        <v>81934</v>
+        <v>81932</v>
       </c>
       <c r="F268" s="3">
         <v>46052</v>
@@ -7419,7 +7419,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E269" s="2">
-        <v>81935</v>
+        <v>81933</v>
       </c>
       <c r="F269" s="3">
         <v>46052</v>
@@ -7445,7 +7445,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E270" s="2">
-        <v>81936</v>
+        <v>81934</v>
       </c>
       <c r="F270" s="3">
         <v>46052</v>
@@ -7465,16 +7465,16 @@
         <v>26</v>
       </c>
       <c r="C271" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D271" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E271" s="2">
-        <v>82222</v>
+        <v>81935</v>
       </c>
       <c r="F271" s="3">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>9</v>
@@ -7491,16 +7491,16 @@
         <v>26</v>
       </c>
       <c r="C272" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D272" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E272" s="2">
-        <v>82226</v>
+        <v>81936</v>
       </c>
       <c r="F272" s="3">
-        <v>46073</v>
+        <v>46052</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>9</v>
@@ -7523,10 +7523,10 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E273" s="2">
-        <v>82229</v>
+        <v>82222</v>
       </c>
       <c r="F273" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>9</v>
@@ -7543,13 +7543,13 @@
         <v>26</v>
       </c>
       <c r="C274" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D274" s="3">
-        <v>46073.5838834375</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E274" s="2">
-        <v>82246</v>
+        <v>82226</v>
       </c>
       <c r="F274" s="3">
         <v>46073</v>
@@ -7569,16 +7569,16 @@
         <v>26</v>
       </c>
       <c r="C275" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D275" s="3">
-        <v>46080.6289065162</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E275" s="2">
-        <v>82387</v>
+        <v>82229</v>
       </c>
       <c r="F275" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>9</v>
@@ -7595,16 +7595,16 @@
         <v>26</v>
       </c>
       <c r="C276" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D276" s="3">
-        <v>46093.4978086806</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E276" s="2">
-        <v>82590</v>
+        <v>82246</v>
       </c>
       <c r="F276" s="3">
-        <v>46093</v>
+        <v>46073</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>9</v>
@@ -7621,22 +7621,22 @@
         <v>26</v>
       </c>
       <c r="C277" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D277" s="3">
-        <v>46093.4978086806</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E277" s="2">
-        <v>82591</v>
+        <v>82387</v>
       </c>
       <c r="F277" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="278">
@@ -7653,7 +7653,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E278" s="2">
-        <v>82592</v>
+        <v>82590</v>
       </c>
       <c r="F278" s="3">
         <v>46093</v>
@@ -7679,16 +7679,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E279" s="2">
-        <v>82593</v>
+        <v>82591</v>
       </c>
       <c r="F279" s="3">
         <v>46093</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="280">
@@ -7705,7 +7705,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E280" s="2">
-        <v>82600</v>
+        <v>82592</v>
       </c>
       <c r="F280" s="3">
         <v>46093</v>
@@ -7731,7 +7731,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E281" s="2">
-        <v>82603</v>
+        <v>82593</v>
       </c>
       <c r="F281" s="3">
         <v>46093</v>
@@ -7757,7 +7757,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E282" s="2">
-        <v>82604</v>
+        <v>82600</v>
       </c>
       <c r="F282" s="3">
         <v>46093</v>
@@ -7783,7 +7783,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E283" s="2">
-        <v>82605</v>
+        <v>82603</v>
       </c>
       <c r="F283" s="3">
         <v>46093</v>
@@ -7797,22 +7797,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="284">
       <c r="A284" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C284" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D284" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E284" s="2">
-        <v>81478</v>
+        <v>82604</v>
       </c>
       <c r="F284" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>9</v>
@@ -7823,22 +7823,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="285">
       <c r="A285" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C285" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D285" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E285" s="2">
-        <v>81479</v>
+        <v>82605</v>
       </c>
       <c r="F285" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>9</v>
@@ -7861,7 +7861,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E286" s="2">
-        <v>81480</v>
+        <v>81478</v>
       </c>
       <c r="F286" s="3">
         <v>46029</v>
@@ -7887,7 +7887,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E287" s="2">
-        <v>81497</v>
+        <v>81479</v>
       </c>
       <c r="F287" s="3">
         <v>46029</v>
@@ -7913,7 +7913,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E288" s="2">
-        <v>81498</v>
+        <v>81480</v>
       </c>
       <c r="F288" s="3">
         <v>46029</v>
@@ -7939,7 +7939,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E289" s="2">
-        <v>81499</v>
+        <v>81497</v>
       </c>
       <c r="F289" s="3">
         <v>46029</v>
@@ -7965,7 +7965,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E290" s="2">
-        <v>81500</v>
+        <v>81498</v>
       </c>
       <c r="F290" s="3">
         <v>46029</v>
@@ -7985,16 +7985,16 @@
         <v>26</v>
       </c>
       <c r="C291" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D291" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E291" s="2">
-        <v>81878</v>
+        <v>81499</v>
       </c>
       <c r="F291" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>9</v>
@@ -8011,16 +8011,16 @@
         <v>26</v>
       </c>
       <c r="C292" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D292" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E292" s="2">
-        <v>81879</v>
+        <v>81500</v>
       </c>
       <c r="F292" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>9</v>
@@ -8043,10 +8043,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E293" s="2">
-        <v>81885</v>
+        <v>81878</v>
       </c>
       <c r="F293" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>9</v>
@@ -8069,10 +8069,10 @@
         <v>46049.6888218403</v>
       </c>
       <c r="E294" s="2">
-        <v>81886</v>
+        <v>81879</v>
       </c>
       <c r="F294" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>9</v>
@@ -8089,16 +8089,16 @@
         <v>26</v>
       </c>
       <c r="C295" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D295" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E295" s="2">
-        <v>82068</v>
+        <v>81885</v>
       </c>
       <c r="F295" s="3">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>9</v>
@@ -8115,16 +8115,16 @@
         <v>26</v>
       </c>
       <c r="C296" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D296" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E296" s="2">
-        <v>82072</v>
+        <v>81886</v>
       </c>
       <c r="F296" s="3">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>9</v>
@@ -8147,10 +8147,10 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E297" s="2">
-        <v>82076</v>
+        <v>82068</v>
       </c>
       <c r="F297" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>9</v>
@@ -8173,7 +8173,7 @@
         <v>46062.7199601505</v>
       </c>
       <c r="E298" s="2">
-        <v>82078</v>
+        <v>82072</v>
       </c>
       <c r="F298" s="3">
         <v>46063</v>
@@ -8193,16 +8193,16 @@
         <v>26</v>
       </c>
       <c r="C299" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D299" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E299" s="2">
-        <v>82287</v>
+        <v>82076</v>
       </c>
       <c r="F299" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>9</v>
@@ -8219,16 +8219,16 @@
         <v>26</v>
       </c>
       <c r="C300" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D300" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E300" s="2">
-        <v>82288</v>
+        <v>82078</v>
       </c>
       <c r="F300" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>9</v>
@@ -8251,10 +8251,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E301" s="2">
-        <v>82298</v>
+        <v>82287</v>
       </c>
       <c r="F301" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G301" s="1" t="s">
         <v>9</v>
@@ -8277,10 +8277,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E302" s="2">
-        <v>82301</v>
+        <v>82288</v>
       </c>
       <c r="F302" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>9</v>
@@ -8303,7 +8303,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E303" s="2">
-        <v>82304</v>
+        <v>82298</v>
       </c>
       <c r="F303" s="3">
         <v>46078</v>
@@ -8329,7 +8329,7 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E304" s="2">
-        <v>82308</v>
+        <v>82301</v>
       </c>
       <c r="F304" s="3">
         <v>46078</v>
@@ -8349,16 +8349,16 @@
         <v>26</v>
       </c>
       <c r="C305" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D305" s="3">
-        <v>46080.628344919</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E305" s="2">
-        <v>82373</v>
+        <v>82304</v>
       </c>
       <c r="F305" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>9</v>
@@ -8375,16 +8375,16 @@
         <v>26</v>
       </c>
       <c r="C306" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D306" s="3">
-        <v>46085.6581644213</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E306" s="2">
-        <v>82445</v>
+        <v>82308</v>
       </c>
       <c r="F306" s="3">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>9</v>
@@ -8401,16 +8401,16 @@
         <v>26</v>
       </c>
       <c r="C307" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D307" s="3">
-        <v>46085.6581644213</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E307" s="2">
-        <v>82447</v>
+        <v>82373</v>
       </c>
       <c r="F307" s="3">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>9</v>
@@ -8433,10 +8433,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E308" s="2">
-        <v>82453</v>
+        <v>82445</v>
       </c>
       <c r="F308" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>9</v>
@@ -8459,10 +8459,10 @@
         <v>46085.6581644213</v>
       </c>
       <c r="E309" s="2">
-        <v>82468</v>
+        <v>82447</v>
       </c>
       <c r="F309" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>9</v>
@@ -8479,16 +8479,16 @@
         <v>26</v>
       </c>
       <c r="C310" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D310" s="3">
-        <v>46098.6669450579</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E310" s="2">
-        <v>82697</v>
+        <v>82453</v>
       </c>
       <c r="F310" s="3">
-        <v>46098</v>
+        <v>46086</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>9</v>
@@ -8505,16 +8505,16 @@
         <v>26</v>
       </c>
       <c r="C311" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D311" s="3">
-        <v>46098.6669450579</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E311" s="2">
-        <v>82706</v>
+        <v>82468</v>
       </c>
       <c r="F311" s="3">
-        <v>46099</v>
+        <v>46086</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>9</v>
@@ -8537,10 +8537,10 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E312" s="2">
-        <v>82707</v>
+        <v>82697</v>
       </c>
       <c r="F312" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>9</v>
@@ -8563,7 +8563,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E313" s="2">
-        <v>82708</v>
+        <v>82706</v>
       </c>
       <c r="F313" s="3">
         <v>46099</v>
@@ -8589,7 +8589,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E314" s="2">
-        <v>82709</v>
+        <v>82707</v>
       </c>
       <c r="F314" s="3">
         <v>46099</v>
@@ -8615,7 +8615,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E315" s="2">
-        <v>82712</v>
+        <v>82708</v>
       </c>
       <c r="F315" s="3">
         <v>46099</v>
@@ -8641,7 +8641,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E316" s="2">
-        <v>82713</v>
+        <v>82709</v>
       </c>
       <c r="F316" s="3">
         <v>46099</v>
@@ -8661,16 +8661,16 @@
         <v>26</v>
       </c>
       <c r="C317" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D317" s="3">
-        <v>46101.4050215162</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E317" s="2">
-        <v>82756</v>
+        <v>82712</v>
       </c>
       <c r="F317" s="3">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>9</v>
@@ -8687,42 +8687,42 @@
         <v>26</v>
       </c>
       <c r="C318" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D318" s="3">
-        <v>46104.4364179167</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E318" s="2">
-        <v>82777</v>
+        <v>82713</v>
       </c>
       <c r="F318" s="3">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="319">
       <c r="A319" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C319" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D319" s="3">
-        <v>46029.6400966782</v>
+        <v>46101.4050215162</v>
       </c>
       <c r="E319" s="2">
-        <v>81506</v>
+        <v>82756</v>
       </c>
       <c r="F319" s="3">
-        <v>46029</v>
+        <v>46101</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>9</v>
@@ -8733,22 +8733,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="320">
       <c r="A320" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C320" s="2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D320" s="3">
-        <v>46029.6400966782</v>
+        <v>46104.4364179167</v>
       </c>
       <c r="E320" s="2">
-        <v>81507</v>
+        <v>82777</v>
       </c>
       <c r="F320" s="3">
-        <v>46029</v>
+        <v>46104</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>9</v>
@@ -8771,10 +8771,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E321" s="2">
-        <v>81524</v>
+        <v>81506</v>
       </c>
       <c r="F321" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>9</v>
@@ -8797,10 +8797,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E322" s="2">
-        <v>81525</v>
+        <v>81507</v>
       </c>
       <c r="F322" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>9</v>
@@ -8823,7 +8823,7 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E323" s="2">
-        <v>81526</v>
+        <v>81524</v>
       </c>
       <c r="F323" s="3">
         <v>46030</v>
@@ -8843,16 +8843,16 @@
         <v>29</v>
       </c>
       <c r="C324" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D324" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E324" s="2">
-        <v>81640</v>
+        <v>81525</v>
       </c>
       <c r="F324" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>9</v>
@@ -8869,16 +8869,16 @@
         <v>29</v>
       </c>
       <c r="C325" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D325" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E325" s="2">
-        <v>81642</v>
+        <v>81526</v>
       </c>
       <c r="F325" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>9</v>
@@ -8901,7 +8901,7 @@
         <v>46036.6348522801</v>
       </c>
       <c r="E326" s="2">
-        <v>81643</v>
+        <v>81640</v>
       </c>
       <c r="F326" s="3">
         <v>46036</v>
@@ -8921,16 +8921,16 @@
         <v>29</v>
       </c>
       <c r="C327" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D327" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E327" s="2">
-        <v>81835</v>
+        <v>81642</v>
       </c>
       <c r="F327" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>9</v>
@@ -8947,16 +8947,16 @@
         <v>29</v>
       </c>
       <c r="C328" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D328" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E328" s="2">
-        <v>81836</v>
+        <v>81643</v>
       </c>
       <c r="F328" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>9</v>
@@ -8979,7 +8979,7 @@
         <v>46045.4207558912</v>
       </c>
       <c r="E329" s="2">
-        <v>81837</v>
+        <v>81835</v>
       </c>
       <c r="F329" s="3">
         <v>46045</v>
@@ -8999,16 +8999,16 @@
         <v>29</v>
       </c>
       <c r="C330" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D330" s="3">
-        <v>46051.6376515278</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E330" s="2">
-        <v>81931</v>
+        <v>81836</v>
       </c>
       <c r="F330" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>9</v>
@@ -9025,16 +9025,16 @@
         <v>29</v>
       </c>
       <c r="C331" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D331" s="3">
-        <v>46056.7115158912</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E331" s="2">
-        <v>81978</v>
+        <v>81837</v>
       </c>
       <c r="F331" s="3">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>9</v>
@@ -9051,16 +9051,16 @@
         <v>29</v>
       </c>
       <c r="C332" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D332" s="3">
-        <v>46057.6911087731</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E332" s="2">
-        <v>81994</v>
+        <v>81931</v>
       </c>
       <c r="F332" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>9</v>
@@ -9077,13 +9077,13 @@
         <v>29</v>
       </c>
       <c r="C333" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D333" s="3">
-        <v>46057.6911087731</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E333" s="2">
-        <v>81995</v>
+        <v>81978</v>
       </c>
       <c r="F333" s="3">
         <v>46057</v>
@@ -9109,7 +9109,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E334" s="2">
-        <v>81999</v>
+        <v>81994</v>
       </c>
       <c r="F334" s="3">
         <v>46057</v>
@@ -9135,10 +9135,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E335" s="2">
-        <v>82008</v>
+        <v>81995</v>
       </c>
       <c r="F335" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>9</v>
@@ -9161,10 +9161,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E336" s="2">
-        <v>82011</v>
+        <v>81999</v>
       </c>
       <c r="F336" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>9</v>
@@ -9187,7 +9187,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E337" s="2">
-        <v>82012</v>
+        <v>82008</v>
       </c>
       <c r="F337" s="3">
         <v>46058</v>
@@ -9213,7 +9213,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E338" s="2">
-        <v>82013</v>
+        <v>82011</v>
       </c>
       <c r="F338" s="3">
         <v>46058</v>
@@ -9239,7 +9239,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E339" s="2">
-        <v>82014</v>
+        <v>82012</v>
       </c>
       <c r="F339" s="3">
         <v>46058</v>
@@ -9259,22 +9259,22 @@
         <v>29</v>
       </c>
       <c r="C340" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D340" s="3">
-        <v>46058.6604985417</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E340" s="2">
-        <v>82046</v>
+        <v>82013</v>
       </c>
       <c r="F340" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="341">
@@ -9285,16 +9285,16 @@
         <v>29</v>
       </c>
       <c r="C341" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D341" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E341" s="2">
-        <v>82217</v>
+        <v>82014</v>
       </c>
       <c r="F341" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>9</v>
@@ -9311,22 +9311,22 @@
         <v>29</v>
       </c>
       <c r="C342" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D342" s="3">
-        <v>46072.738871875</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E342" s="2">
-        <v>82218</v>
+        <v>82046</v>
       </c>
       <c r="F342" s="3">
-        <v>46072</v>
+        <v>46059</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="343">
@@ -9343,10 +9343,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E343" s="2">
-        <v>82234</v>
+        <v>82217</v>
       </c>
       <c r="F343" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>9</v>
@@ -9369,10 +9369,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E344" s="2">
-        <v>82238</v>
+        <v>82218</v>
       </c>
       <c r="F344" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>9</v>
@@ -9395,7 +9395,7 @@
         <v>46072.738871875</v>
       </c>
       <c r="E345" s="2">
-        <v>82245</v>
+        <v>82234</v>
       </c>
       <c r="F345" s="3">
         <v>46073</v>
@@ -9415,16 +9415,16 @@
         <v>29</v>
       </c>
       <c r="C346" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D346" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E346" s="2">
-        <v>82257</v>
+        <v>82238</v>
       </c>
       <c r="F346" s="3">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>9</v>
@@ -9441,16 +9441,16 @@
         <v>29</v>
       </c>
       <c r="C347" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D347" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E347" s="2">
-        <v>82276</v>
+        <v>82245</v>
       </c>
       <c r="F347" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>9</v>
@@ -9473,10 +9473,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E348" s="2">
-        <v>82277</v>
+        <v>82257</v>
       </c>
       <c r="F348" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>9</v>
@@ -9499,10 +9499,10 @@
         <v>46076.7244851042</v>
       </c>
       <c r="E349" s="2">
-        <v>82293</v>
+        <v>82276</v>
       </c>
       <c r="F349" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>9</v>
@@ -9519,13 +9519,13 @@
         <v>29</v>
       </c>
       <c r="C350" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D350" s="3">
-        <v>46077.4356327431</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E350" s="2">
-        <v>82269</v>
+        <v>82277</v>
       </c>
       <c r="F350" s="3">
         <v>46077</v>
@@ -9545,16 +9545,16 @@
         <v>29</v>
       </c>
       <c r="C351" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D351" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E351" s="2">
-        <v>82419</v>
+        <v>82293</v>
       </c>
       <c r="F351" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G351" s="1" t="s">
         <v>9</v>
@@ -9571,16 +9571,16 @@
         <v>29</v>
       </c>
       <c r="C352" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D352" s="3">
-        <v>46084.7378501505</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E352" s="2">
-        <v>82420</v>
+        <v>82269</v>
       </c>
       <c r="F352" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>9</v>
@@ -9603,7 +9603,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E353" s="2">
-        <v>82421</v>
+        <v>82419</v>
       </c>
       <c r="F353" s="3">
         <v>46084</v>
@@ -9629,7 +9629,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E354" s="2">
-        <v>82422</v>
+        <v>82420</v>
       </c>
       <c r="F354" s="3">
         <v>46084</v>
@@ -9655,7 +9655,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E355" s="2">
-        <v>82423</v>
+        <v>82421</v>
       </c>
       <c r="F355" s="3">
         <v>46084</v>
@@ -9681,10 +9681,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E356" s="2">
-        <v>82433</v>
+        <v>82422</v>
       </c>
       <c r="F356" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>9</v>
@@ -9707,10 +9707,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E357" s="2">
-        <v>82434</v>
+        <v>82423</v>
       </c>
       <c r="F357" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>9</v>
@@ -9733,10 +9733,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E358" s="2">
-        <v>82464</v>
+        <v>82433</v>
       </c>
       <c r="F358" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>9</v>
@@ -9759,10 +9759,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E359" s="2">
-        <v>82472</v>
+        <v>82434</v>
       </c>
       <c r="F359" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>9</v>
@@ -9779,16 +9779,16 @@
         <v>29</v>
       </c>
       <c r="C360" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D360" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E360" s="2">
-        <v>82578</v>
+        <v>82464</v>
       </c>
       <c r="F360" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>9</v>
@@ -9805,16 +9805,16 @@
         <v>29</v>
       </c>
       <c r="C361" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D361" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E361" s="2">
-        <v>82579</v>
+        <v>82472</v>
       </c>
       <c r="F361" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>9</v>
@@ -9837,7 +9837,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E362" s="2">
-        <v>82580</v>
+        <v>82578</v>
       </c>
       <c r="F362" s="3">
         <v>46093</v>
@@ -9863,7 +9863,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E363" s="2">
-        <v>82599</v>
+        <v>82579</v>
       </c>
       <c r="F363" s="3">
         <v>46093</v>
@@ -9889,7 +9889,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E364" s="2">
-        <v>82602</v>
+        <v>82580</v>
       </c>
       <c r="F364" s="3">
         <v>46093</v>
@@ -9909,13 +9909,13 @@
         <v>29</v>
       </c>
       <c r="C365" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D365" s="3">
-        <v>46093.4957757986</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E365" s="2">
-        <v>82584</v>
+        <v>82599</v>
       </c>
       <c r="F365" s="3">
         <v>46093</v>
@@ -9935,16 +9935,16 @@
         <v>29</v>
       </c>
       <c r="C366" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D366" s="3">
-        <v>46100.6528700694</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E366" s="2">
-        <v>82746</v>
+        <v>82602</v>
       </c>
       <c r="F366" s="3">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>9</v>
@@ -9961,16 +9961,16 @@
         <v>29</v>
       </c>
       <c r="C367" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D367" s="3">
-        <v>46100.6528700694</v>
+        <v>46093.4957757986</v>
       </c>
       <c r="E367" s="2">
-        <v>82747</v>
+        <v>82584</v>
       </c>
       <c r="F367" s="3">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>9</v>
@@ -9993,7 +9993,7 @@
         <v>46100.6528700694</v>
       </c>
       <c r="E368" s="2">
-        <v>82748</v>
+        <v>82746</v>
       </c>
       <c r="F368" s="3">
         <v>46100</v>
@@ -10007,22 +10007,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="369">
       <c r="A369" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C369" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D369" s="3">
-        <v>46027.6953206134</v>
+        <v>46100.6528700694</v>
       </c>
       <c r="E369" s="2">
-        <v>81464</v>
+        <v>82747</v>
       </c>
       <c r="F369" s="3">
-        <v>46027</v>
+        <v>46100</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>9</v>
@@ -10033,22 +10033,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="370">
       <c r="A370" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C370" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D370" s="3">
-        <v>46027.6953206134</v>
+        <v>46100.6528700694</v>
       </c>
       <c r="E370" s="2">
-        <v>81472</v>
+        <v>82748</v>
       </c>
       <c r="F370" s="3">
-        <v>46027</v>
+        <v>46100</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>9</v>
@@ -10071,10 +10071,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E371" s="2">
-        <v>81492</v>
+        <v>81464</v>
       </c>
       <c r="F371" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>9</v>
@@ -10097,10 +10097,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E372" s="2">
-        <v>81493</v>
+        <v>81472</v>
       </c>
       <c r="F372" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>9</v>
@@ -10123,10 +10123,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E373" s="2">
-        <v>81568</v>
+        <v>81492</v>
       </c>
       <c r="F373" s="3">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>9</v>
@@ -10149,10 +10149,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E374" s="2">
-        <v>81601</v>
+        <v>81493</v>
       </c>
       <c r="F374" s="3">
-        <v>46034</v>
+        <v>46029</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>9</v>
@@ -10175,10 +10175,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E375" s="2">
-        <v>81602</v>
+        <v>81568</v>
       </c>
       <c r="F375" s="3">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>9</v>
@@ -10195,16 +10195,16 @@
         <v>30</v>
       </c>
       <c r="C376" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D376" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E376" s="2">
-        <v>81645</v>
+        <v>81601</v>
       </c>
       <c r="F376" s="3">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>9</v>
@@ -10221,16 +10221,16 @@
         <v>30</v>
       </c>
       <c r="C377" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D377" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E377" s="2">
-        <v>81646</v>
+        <v>81602</v>
       </c>
       <c r="F377" s="3">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>9</v>
@@ -10253,10 +10253,10 @@
         <v>46036.6368094444</v>
       </c>
       <c r="E378" s="2">
-        <v>81653</v>
+        <v>81645</v>
       </c>
       <c r="F378" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>9</v>
@@ -10273,16 +10273,16 @@
         <v>30</v>
       </c>
       <c r="C379" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D379" s="3">
-        <v>46037.4325152662</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E379" s="2">
-        <v>81662</v>
+        <v>81646</v>
       </c>
       <c r="F379" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>9</v>
@@ -10299,16 +10299,16 @@
         <v>30</v>
       </c>
       <c r="C380" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D380" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E380" s="2">
-        <v>81780</v>
+        <v>81653</v>
       </c>
       <c r="F380" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>9</v>
@@ -10325,16 +10325,16 @@
         <v>30</v>
       </c>
       <c r="C381" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D381" s="3">
-        <v>46044.4079891435</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E381" s="2">
-        <v>81781</v>
+        <v>81662</v>
       </c>
       <c r="F381" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>9</v>
@@ -10357,7 +10357,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E382" s="2">
-        <v>81782</v>
+        <v>81780</v>
       </c>
       <c r="F382" s="3">
         <v>46044</v>
@@ -10383,7 +10383,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E383" s="2">
-        <v>81784</v>
+        <v>81781</v>
       </c>
       <c r="F383" s="3">
         <v>46044</v>
@@ -10409,7 +10409,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E384" s="2">
-        <v>81785</v>
+        <v>81782</v>
       </c>
       <c r="F384" s="3">
         <v>46044</v>
@@ -10435,7 +10435,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E385" s="2">
-        <v>81801</v>
+        <v>81784</v>
       </c>
       <c r="F385" s="3">
         <v>46044</v>
@@ -10455,16 +10455,16 @@
         <v>30</v>
       </c>
       <c r="C386" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D386" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E386" s="2">
-        <v>81860</v>
+        <v>81785</v>
       </c>
       <c r="F386" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>9</v>
@@ -10481,16 +10481,16 @@
         <v>30</v>
       </c>
       <c r="C387" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D387" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E387" s="2">
-        <v>81873</v>
+        <v>81801</v>
       </c>
       <c r="F387" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>9</v>
@@ -10507,13 +10507,13 @@
         <v>30</v>
       </c>
       <c r="C388" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D388" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E388" s="2">
-        <v>81865</v>
+        <v>81860</v>
       </c>
       <c r="F388" s="3">
         <v>46049</v>
@@ -10533,13 +10533,13 @@
         <v>30</v>
       </c>
       <c r="C389" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D389" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E389" s="2">
-        <v>81870</v>
+        <v>81873</v>
       </c>
       <c r="F389" s="3">
         <v>46049</v>
@@ -10565,7 +10565,7 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E390" s="2">
-        <v>81872</v>
+        <v>81865</v>
       </c>
       <c r="F390" s="3">
         <v>46049</v>
@@ -10591,10 +10591,10 @@
         <v>46049.4883916667</v>
       </c>
       <c r="E391" s="2">
-        <v>81896</v>
+        <v>81870</v>
       </c>
       <c r="F391" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>9</v>
@@ -10611,16 +10611,16 @@
         <v>30</v>
       </c>
       <c r="C392" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D392" s="3">
-        <v>46051.4046937153</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E392" s="2">
-        <v>81923</v>
+        <v>81872</v>
       </c>
       <c r="F392" s="3">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>9</v>
@@ -10637,16 +10637,16 @@
         <v>30</v>
       </c>
       <c r="C393" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D393" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E393" s="2">
-        <v>81998</v>
+        <v>81896</v>
       </c>
       <c r="F393" s="3">
-        <v>46057</v>
+        <v>46050</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>9</v>
@@ -10663,16 +10663,16 @@
         <v>30</v>
       </c>
       <c r="C394" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D394" s="3">
-        <v>46057.6959672917</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E394" s="2">
-        <v>82002</v>
+        <v>81923</v>
       </c>
       <c r="F394" s="3">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>9</v>
@@ -10695,10 +10695,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E395" s="2">
-        <v>82005</v>
+        <v>81998</v>
       </c>
       <c r="F395" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>9</v>
@@ -10721,10 +10721,10 @@
         <v>46057.6959672917</v>
       </c>
       <c r="E396" s="2">
-        <v>82007</v>
+        <v>82002</v>
       </c>
       <c r="F396" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>9</v>
@@ -10741,10 +10741,10 @@
         <v>30</v>
       </c>
       <c r="C397" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D397" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E397" s="2">
         <v>82005</v>
@@ -10767,16 +10767,16 @@
         <v>30</v>
       </c>
       <c r="C398" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D398" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E398" s="2">
-        <v>82075</v>
+        <v>82007</v>
       </c>
       <c r="F398" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>9</v>
@@ -10799,10 +10799,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E399" s="2">
-        <v>82077</v>
+        <v>82005</v>
       </c>
       <c r="F399" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>9</v>
@@ -10825,10 +10825,10 @@
         <v>46063.5942651852</v>
       </c>
       <c r="E400" s="2">
-        <v>82099</v>
+        <v>82075</v>
       </c>
       <c r="F400" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>9</v>
@@ -10845,16 +10845,16 @@
         <v>30</v>
       </c>
       <c r="C401" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D401" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E401" s="2">
-        <v>82219</v>
+        <v>82077</v>
       </c>
       <c r="F401" s="3">
-        <v>46072</v>
+        <v>46063</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10871,16 +10871,16 @@
         <v>30</v>
       </c>
       <c r="C402" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D402" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E402" s="2">
-        <v>82230</v>
+        <v>82099</v>
       </c>
       <c r="F402" s="3">
-        <v>46073</v>
+        <v>46064</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10903,10 +10903,10 @@
         <v>46072.7460071991</v>
       </c>
       <c r="E403" s="2">
-        <v>82231</v>
+        <v>82219</v>
       </c>
       <c r="F403" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10923,16 +10923,16 @@
         <v>30</v>
       </c>
       <c r="C404" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D404" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E404" s="2">
-        <v>82388</v>
+        <v>82230</v>
       </c>
       <c r="F404" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>9</v>
@@ -10949,16 +10949,16 @@
         <v>30</v>
       </c>
       <c r="C405" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D405" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E405" s="2">
-        <v>82389</v>
+        <v>82231</v>
       </c>
       <c r="F405" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>9</v>
@@ -10981,7 +10981,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E406" s="2">
-        <v>82396</v>
+        <v>82388</v>
       </c>
       <c r="F406" s="3">
         <v>46083</v>
@@ -11007,7 +11007,7 @@
         <v>46079.5787315972</v>
       </c>
       <c r="E407" s="2">
-        <v>82397</v>
+        <v>82389</v>
       </c>
       <c r="F407" s="3">
         <v>46083</v>
@@ -11027,16 +11027,16 @@
         <v>30</v>
       </c>
       <c r="C408" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D408" s="3">
-        <v>46085.6249659838</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E408" s="2">
-        <v>82435</v>
+        <v>82396</v>
       </c>
       <c r="F408" s="3">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>9</v>
@@ -11053,16 +11053,16 @@
         <v>30</v>
       </c>
       <c r="C409" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D409" s="3">
-        <v>46091.449444456</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E409" s="2">
-        <v>82506</v>
+        <v>82397</v>
       </c>
       <c r="F409" s="3">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>9</v>
@@ -11079,16 +11079,16 @@
         <v>30</v>
       </c>
       <c r="C410" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D410" s="3">
-        <v>46091.4795702315</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E410" s="2">
-        <v>82509</v>
+        <v>82435</v>
       </c>
       <c r="F410" s="3">
-        <v>46091</v>
+        <v>46085</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11105,16 +11105,16 @@
         <v>30</v>
       </c>
       <c r="C411" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D411" s="3">
-        <v>46093.4969972338</v>
+        <v>46091.449444456</v>
       </c>
       <c r="E411" s="2">
-        <v>82589</v>
+        <v>82506</v>
       </c>
       <c r="F411" s="3">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>9</v>
@@ -11125,22 +11125,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="412">
       <c r="A412" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C412" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D412" s="3">
-        <v>46029.3821391551</v>
+        <v>46091.4795702315</v>
       </c>
       <c r="E412" s="2">
-        <v>81477</v>
+        <v>82509</v>
       </c>
       <c r="F412" s="3">
-        <v>46029</v>
+        <v>46091</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11151,22 +11151,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="413">
       <c r="A413" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C413" s="2">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D413" s="3">
-        <v>46030.4142968056</v>
+        <v>46093.4969972338</v>
       </c>
       <c r="E413" s="2">
-        <v>81532</v>
+        <v>82589</v>
       </c>
       <c r="F413" s="3">
-        <v>46030</v>
+        <v>46093</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>9</v>
@@ -11177,22 +11177,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="414">
       <c r="A414" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C414" s="2">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D414" s="3">
-        <v>46030.4142968056</v>
+        <v>46105.7312393519</v>
       </c>
       <c r="E414" s="2">
-        <v>81534</v>
+        <v>82798</v>
       </c>
       <c r="F414" s="3">
-        <v>46030</v>
+        <v>46105</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>9</v>
@@ -11203,22 +11203,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="415">
       <c r="A415" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C415" s="2">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D415" s="3">
-        <v>46030.4142968056</v>
+        <v>46105.7312393519</v>
       </c>
       <c r="E415" s="2">
-        <v>81535</v>
+        <v>82805</v>
       </c>
       <c r="F415" s="3">
-        <v>46030</v>
+        <v>46106</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>9</v>
@@ -11235,16 +11235,16 @@
         <v>31</v>
       </c>
       <c r="C416" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D416" s="3">
-        <v>46030.4142968056</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E416" s="2">
-        <v>81550</v>
+        <v>81477</v>
       </c>
       <c r="F416" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>9</v>
@@ -11267,7 +11267,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E417" s="2">
-        <v>81553</v>
+        <v>81532</v>
       </c>
       <c r="F417" s="3">
         <v>46030</v>
@@ -11293,7 +11293,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E418" s="2">
-        <v>81554</v>
+        <v>81534</v>
       </c>
       <c r="F418" s="3">
         <v>46030</v>
@@ -11319,7 +11319,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E419" s="2">
-        <v>81557</v>
+        <v>81535</v>
       </c>
       <c r="F419" s="3">
         <v>46030</v>
@@ -11345,10 +11345,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E420" s="2">
-        <v>81588</v>
+        <v>81550</v>
       </c>
       <c r="F420" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>9</v>
@@ -11365,16 +11365,16 @@
         <v>31</v>
       </c>
       <c r="C421" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D421" s="3">
-        <v>46038.593985081</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E421" s="2">
-        <v>81692</v>
+        <v>81553</v>
       </c>
       <c r="F421" s="3">
-        <v>46038</v>
+        <v>46030</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>9</v>
@@ -11391,16 +11391,16 @@
         <v>31</v>
       </c>
       <c r="C422" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D422" s="3">
-        <v>46044.46462125</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E422" s="2">
-        <v>81786</v>
+        <v>81554</v>
       </c>
       <c r="F422" s="3">
-        <v>46044</v>
+        <v>46030</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>9</v>
@@ -11417,16 +11417,16 @@
         <v>31</v>
       </c>
       <c r="C423" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D423" s="3">
-        <v>46044.6362443171</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E423" s="2">
-        <v>81844</v>
+        <v>81557</v>
       </c>
       <c r="F423" s="3">
-        <v>46045</v>
+        <v>46030</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>9</v>
@@ -11443,16 +11443,16 @@
         <v>31</v>
       </c>
       <c r="C424" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D424" s="3">
-        <v>46062.717040544</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E424" s="2">
-        <v>82065</v>
+        <v>81588</v>
       </c>
       <c r="F424" s="3">
-        <v>46062</v>
+        <v>46031</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>9</v>
@@ -11469,16 +11469,16 @@
         <v>31</v>
       </c>
       <c r="C425" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D425" s="3">
-        <v>46062.717040544</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E425" s="2">
-        <v>82066</v>
+        <v>81692</v>
       </c>
       <c r="F425" s="3">
-        <v>46062</v>
+        <v>46038</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>9</v>
@@ -11495,16 +11495,16 @@
         <v>31</v>
       </c>
       <c r="C426" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D426" s="3">
-        <v>46062.717040544</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E426" s="2">
-        <v>82067</v>
+        <v>81786</v>
       </c>
       <c r="F426" s="3">
-        <v>46062</v>
+        <v>46044</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>9</v>
@@ -11521,16 +11521,16 @@
         <v>31</v>
       </c>
       <c r="C427" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D427" s="3">
-        <v>46065.6300915625</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E427" s="2">
-        <v>82190</v>
+        <v>81844</v>
       </c>
       <c r="F427" s="3">
-        <v>46066</v>
+        <v>46045</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11547,16 +11547,16 @@
         <v>31</v>
       </c>
       <c r="C428" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D428" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E428" s="2">
-        <v>82197</v>
+        <v>82065</v>
       </c>
       <c r="F428" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>9</v>
@@ -11573,16 +11573,16 @@
         <v>31</v>
       </c>
       <c r="C429" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D429" s="3">
-        <v>46077.5084780324</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E429" s="2">
-        <v>82270</v>
+        <v>82066</v>
       </c>
       <c r="F429" s="3">
-        <v>46077</v>
+        <v>46062</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>9</v>
@@ -11599,16 +11599,16 @@
         <v>31</v>
       </c>
       <c r="C430" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D430" s="3">
-        <v>46077.721037037</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E430" s="2">
-        <v>82285</v>
+        <v>82067</v>
       </c>
       <c r="F430" s="3">
-        <v>46077</v>
+        <v>46062</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>9</v>
@@ -11625,16 +11625,16 @@
         <v>31</v>
       </c>
       <c r="C431" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D431" s="3">
-        <v>46083.6694849421</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E431" s="2">
-        <v>82417</v>
+        <v>82190</v>
       </c>
       <c r="F431" s="3">
-        <v>46084</v>
+        <v>46066</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>9</v>
@@ -11651,16 +11651,16 @@
         <v>31</v>
       </c>
       <c r="C432" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D432" s="3">
-        <v>46085.7157723032</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E432" s="2">
-        <v>82457</v>
+        <v>82197</v>
       </c>
       <c r="F432" s="3">
-        <v>46086</v>
+        <v>46066</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11677,16 +11677,16 @@
         <v>31</v>
       </c>
       <c r="C433" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D433" s="3">
-        <v>46099.6523956944</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E433" s="2">
-        <v>82724</v>
+        <v>82270</v>
       </c>
       <c r="F433" s="3">
-        <v>46099</v>
+        <v>46077</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11703,16 +11703,16 @@
         <v>31</v>
       </c>
       <c r="C434" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D434" s="3">
-        <v>46099.6523956944</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E434" s="2">
-        <v>82725</v>
+        <v>82285</v>
       </c>
       <c r="F434" s="3">
-        <v>46099</v>
+        <v>46077</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>9</v>
@@ -11729,16 +11729,16 @@
         <v>31</v>
       </c>
       <c r="C435" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D435" s="3">
-        <v>46099.6523956944</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E435" s="2">
-        <v>82727</v>
+        <v>82417</v>
       </c>
       <c r="F435" s="3">
-        <v>46100</v>
+        <v>46084</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>9</v>
@@ -11755,16 +11755,16 @@
         <v>31</v>
       </c>
       <c r="C436" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D436" s="3">
-        <v>46099.6523956944</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E436" s="2">
-        <v>82730</v>
+        <v>82457</v>
       </c>
       <c r="F436" s="3">
-        <v>46100</v>
+        <v>46086</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>9</v>
@@ -11775,22 +11775,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="437">
       <c r="A437" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C437" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D437" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E437" s="2">
-        <v>81484</v>
+        <v>82724</v>
       </c>
       <c r="F437" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>9</v>
@@ -11801,22 +11801,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="438">
       <c r="A438" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C438" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D438" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E438" s="2">
-        <v>81486</v>
+        <v>82725</v>
       </c>
       <c r="F438" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11827,22 +11827,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="439">
       <c r="A439" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C439" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D439" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E439" s="2">
-        <v>81487</v>
+        <v>82727</v>
       </c>
       <c r="F439" s="3">
-        <v>46029</v>
+        <v>46100</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11853,22 +11853,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="440">
       <c r="A440" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C440" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D440" s="3">
-        <v>46036.4048894097</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E440" s="2">
-        <v>81613</v>
+        <v>82730</v>
       </c>
       <c r="F440" s="3">
-        <v>46036</v>
+        <v>46100</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>9</v>
@@ -11885,16 +11885,16 @@
         <v>32</v>
       </c>
       <c r="C441" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D441" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E441" s="2">
-        <v>81614</v>
+        <v>81484</v>
       </c>
       <c r="F441" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11911,16 +11911,16 @@
         <v>32</v>
       </c>
       <c r="C442" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D442" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E442" s="2">
-        <v>81622</v>
+        <v>81486</v>
       </c>
       <c r="F442" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11937,16 +11937,16 @@
         <v>32</v>
       </c>
       <c r="C443" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D443" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E443" s="2">
-        <v>81632</v>
+        <v>81487</v>
       </c>
       <c r="F443" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11969,10 +11969,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E444" s="2">
-        <v>81648</v>
+        <v>81613</v>
       </c>
       <c r="F444" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11995,10 +11995,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E445" s="2">
-        <v>81664</v>
+        <v>81614</v>
       </c>
       <c r="F445" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>9</v>
@@ -12015,16 +12015,16 @@
         <v>32</v>
       </c>
       <c r="C446" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D446" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E446" s="2">
-        <v>81815</v>
+        <v>81622</v>
       </c>
       <c r="F446" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>9</v>
@@ -12041,16 +12041,16 @@
         <v>32</v>
       </c>
       <c r="C447" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D447" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E447" s="2">
-        <v>81816</v>
+        <v>81632</v>
       </c>
       <c r="F447" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>9</v>
@@ -12067,16 +12067,16 @@
         <v>32</v>
       </c>
       <c r="C448" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D448" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E448" s="2">
-        <v>81838</v>
+        <v>81648</v>
       </c>
       <c r="F448" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12093,16 +12093,16 @@
         <v>32</v>
       </c>
       <c r="C449" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D449" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E449" s="2">
-        <v>81840</v>
+        <v>81664</v>
       </c>
       <c r="F449" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12119,16 +12119,16 @@
         <v>32</v>
       </c>
       <c r="C450" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D450" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E450" s="2">
-        <v>81959</v>
+        <v>81815</v>
       </c>
       <c r="F450" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12145,16 +12145,16 @@
         <v>32</v>
       </c>
       <c r="C451" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D451" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E451" s="2">
-        <v>81960</v>
+        <v>81816</v>
       </c>
       <c r="F451" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>9</v>
@@ -12171,16 +12171,16 @@
         <v>32</v>
       </c>
       <c r="C452" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D452" s="3">
-        <v>46062.7151302546</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E452" s="2">
-        <v>82063</v>
+        <v>81838</v>
       </c>
       <c r="F452" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12197,16 +12197,16 @@
         <v>32</v>
       </c>
       <c r="C453" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D453" s="3">
-        <v>46062.7151302546</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E453" s="2">
-        <v>82064</v>
+        <v>81840</v>
       </c>
       <c r="F453" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>9</v>
@@ -12223,16 +12223,16 @@
         <v>32</v>
       </c>
       <c r="C454" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D454" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E454" s="2">
-        <v>82100</v>
+        <v>81959</v>
       </c>
       <c r="F454" s="3">
-        <v>46064</v>
+        <v>46055</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>9</v>
@@ -12249,16 +12249,16 @@
         <v>32</v>
       </c>
       <c r="C455" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D455" s="3">
-        <v>46072.7410579977</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E455" s="2">
-        <v>82333</v>
+        <v>81960</v>
       </c>
       <c r="F455" s="3">
-        <v>46079</v>
+        <v>46055</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>9</v>
@@ -12275,16 +12275,16 @@
         <v>32</v>
       </c>
       <c r="C456" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D456" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E456" s="2">
-        <v>82334</v>
+        <v>82063</v>
       </c>
       <c r="F456" s="3">
-        <v>46079</v>
+        <v>46062</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12301,16 +12301,16 @@
         <v>32</v>
       </c>
       <c r="C457" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D457" s="3">
-        <v>46076.7259125116</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E457" s="2">
-        <v>82258</v>
+        <v>82064</v>
       </c>
       <c r="F457" s="3">
-        <v>46076</v>
+        <v>46062</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>9</v>
@@ -12327,16 +12327,16 @@
         <v>32</v>
       </c>
       <c r="C458" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D458" s="3">
-        <v>46076.7259125116</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E458" s="2">
-        <v>82259</v>
+        <v>82100</v>
       </c>
       <c r="F458" s="3">
-        <v>46076</v>
+        <v>46064</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12353,16 +12353,16 @@
         <v>32</v>
       </c>
       <c r="C459" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D459" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E459" s="2">
-        <v>82260</v>
+        <v>82333</v>
       </c>
       <c r="F459" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12379,16 +12379,16 @@
         <v>32</v>
       </c>
       <c r="C460" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D460" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E460" s="2">
-        <v>82274</v>
+        <v>82334</v>
       </c>
       <c r="F460" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12405,16 +12405,16 @@
         <v>32</v>
       </c>
       <c r="C461" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D461" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E461" s="2">
-        <v>82409</v>
+        <v>82258</v>
       </c>
       <c r="F461" s="3">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12431,16 +12431,16 @@
         <v>32</v>
       </c>
       <c r="C462" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D462" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E462" s="2">
-        <v>82581</v>
+        <v>82259</v>
       </c>
       <c r="F462" s="3">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12457,16 +12457,16 @@
         <v>32</v>
       </c>
       <c r="C463" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D463" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E463" s="2">
-        <v>82582</v>
+        <v>82260</v>
       </c>
       <c r="F463" s="3">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12483,16 +12483,16 @@
         <v>32</v>
       </c>
       <c r="C464" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D464" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E464" s="2">
-        <v>82583</v>
+        <v>82274</v>
       </c>
       <c r="F464" s="3">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12509,16 +12509,16 @@
         <v>32</v>
       </c>
       <c r="C465" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D465" s="3">
-        <v>46093.4920058565</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E465" s="2">
-        <v>82672</v>
+        <v>82409</v>
       </c>
       <c r="F465" s="3">
-        <v>46097</v>
+        <v>46084</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>9</v>
@@ -12541,10 +12541,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E466" s="2">
-        <v>82674</v>
+        <v>82581</v>
       </c>
       <c r="F466" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12555,22 +12555,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="467">
       <c r="A467" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C467" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D467" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E467" s="2">
-        <v>81608</v>
+        <v>82582</v>
       </c>
       <c r="F467" s="3">
-        <v>46035</v>
+        <v>46093</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>9</v>
@@ -12581,22 +12581,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="468">
       <c r="A468" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C468" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D468" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E468" s="2">
-        <v>81609</v>
+        <v>82583</v>
       </c>
       <c r="F468" s="3">
-        <v>46035</v>
+        <v>46093</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>9</v>
@@ -12607,22 +12607,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="469">
       <c r="A469" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C469" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D469" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E469" s="2">
-        <v>81610</v>
+        <v>82672</v>
       </c>
       <c r="F469" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>9</v>
@@ -12633,22 +12633,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="470">
       <c r="A470" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C470" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D470" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E470" s="2">
-        <v>81611</v>
+        <v>82674</v>
       </c>
       <c r="F470" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>9</v>
@@ -12671,7 +12671,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E471" s="2">
-        <v>81612</v>
+        <v>81608</v>
       </c>
       <c r="F471" s="3">
         <v>46035</v>
@@ -12691,16 +12691,16 @@
         <v>33</v>
       </c>
       <c r="C472" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D472" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E472" s="2">
-        <v>81652</v>
+        <v>81609</v>
       </c>
       <c r="F472" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12717,16 +12717,16 @@
         <v>33</v>
       </c>
       <c r="C473" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D473" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E473" s="2">
-        <v>81659</v>
+        <v>81610</v>
       </c>
       <c r="F473" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12743,16 +12743,16 @@
         <v>33</v>
       </c>
       <c r="C474" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D474" s="3">
-        <v>46048.6509980093</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E474" s="2">
-        <v>81853</v>
+        <v>81611</v>
       </c>
       <c r="F474" s="3">
-        <v>46048</v>
+        <v>46035</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12769,16 +12769,16 @@
         <v>33</v>
       </c>
       <c r="C475" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D475" s="3">
-        <v>46048.6509980093</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E475" s="2">
-        <v>81869</v>
+        <v>81612</v>
       </c>
       <c r="F475" s="3">
-        <v>46049</v>
+        <v>46035</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>9</v>
@@ -12795,16 +12795,16 @@
         <v>33</v>
       </c>
       <c r="C476" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D476" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E476" s="2">
-        <v>81890</v>
+        <v>81652</v>
       </c>
       <c r="F476" s="3">
-        <v>46050</v>
+        <v>46037</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>9</v>
@@ -12821,16 +12821,16 @@
         <v>33</v>
       </c>
       <c r="C477" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D477" s="3">
-        <v>46049.4871256134</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E477" s="2">
-        <v>81875</v>
+        <v>81659</v>
       </c>
       <c r="F477" s="3">
-        <v>46049</v>
+        <v>46037</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>9</v>
@@ -12847,16 +12847,16 @@
         <v>33</v>
       </c>
       <c r="C478" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D478" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E478" s="2">
-        <v>81881</v>
+        <v>81853</v>
       </c>
       <c r="F478" s="3">
-        <v>46050</v>
+        <v>46048</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12873,16 +12873,16 @@
         <v>33</v>
       </c>
       <c r="C479" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D479" s="3">
-        <v>46056.7073643981</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E479" s="2">
-        <v>82015</v>
+        <v>81869</v>
       </c>
       <c r="F479" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12899,16 +12899,16 @@
         <v>33</v>
       </c>
       <c r="C480" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D480" s="3">
-        <v>46056.7073643981</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E480" s="2">
-        <v>82017</v>
+        <v>81890</v>
       </c>
       <c r="F480" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>9</v>
@@ -12925,16 +12925,16 @@
         <v>33</v>
       </c>
       <c r="C481" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D481" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E481" s="2">
-        <v>82020</v>
+        <v>81875</v>
       </c>
       <c r="F481" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>9</v>
@@ -12951,16 +12951,16 @@
         <v>33</v>
       </c>
       <c r="C482" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D482" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E482" s="2">
-        <v>82023</v>
+        <v>81881</v>
       </c>
       <c r="F482" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12983,10 +12983,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E483" s="2">
-        <v>82061</v>
+        <v>82015</v>
       </c>
       <c r="F483" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>9</v>
@@ -13009,10 +13009,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E484" s="2">
-        <v>82081</v>
+        <v>82017</v>
       </c>
       <c r="F484" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G484" s="1" t="s">
         <v>9</v>
@@ -13035,10 +13035,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E485" s="2">
-        <v>82095</v>
+        <v>82020</v>
       </c>
       <c r="F485" s="3">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>9</v>
@@ -13055,16 +13055,16 @@
         <v>33</v>
       </c>
       <c r="C486" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D486" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E486" s="2">
-        <v>82081</v>
+        <v>82023</v>
       </c>
       <c r="F486" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>9</v>
@@ -13081,16 +13081,16 @@
         <v>33</v>
       </c>
       <c r="C487" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D487" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E487" s="2">
-        <v>82107</v>
+        <v>82061</v>
       </c>
       <c r="F487" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>9</v>
@@ -13107,16 +13107,16 @@
         <v>33</v>
       </c>
       <c r="C488" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D488" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E488" s="2">
-        <v>82112</v>
+        <v>82081</v>
       </c>
       <c r="F488" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>9</v>
@@ -13133,13 +13133,13 @@
         <v>33</v>
       </c>
       <c r="C489" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D489" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E489" s="2">
-        <v>82113</v>
+        <v>82095</v>
       </c>
       <c r="F489" s="3">
         <v>46064</v>
@@ -13165,10 +13165,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E490" s="2">
-        <v>82123</v>
+        <v>82081</v>
       </c>
       <c r="F490" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>9</v>
@@ -13185,13 +13185,13 @@
         <v>33</v>
       </c>
       <c r="C491" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D491" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E491" s="2">
-        <v>82095</v>
+        <v>82107</v>
       </c>
       <c r="F491" s="3">
         <v>46064</v>
@@ -13211,13 +13211,13 @@
         <v>33</v>
       </c>
       <c r="C492" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D492" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E492" s="2">
-        <v>82106</v>
+        <v>82112</v>
       </c>
       <c r="F492" s="3">
         <v>46064</v>
@@ -13237,13 +13237,13 @@
         <v>33</v>
       </c>
       <c r="C493" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D493" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E493" s="2">
-        <v>82107</v>
+        <v>82113</v>
       </c>
       <c r="F493" s="3">
         <v>46064</v>
@@ -13263,16 +13263,16 @@
         <v>33</v>
       </c>
       <c r="C494" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D494" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E494" s="2">
-        <v>82109</v>
+        <v>82123</v>
       </c>
       <c r="F494" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>9</v>
@@ -13295,7 +13295,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E495" s="2">
-        <v>82110</v>
+        <v>82095</v>
       </c>
       <c r="F495" s="3">
         <v>46064</v>
@@ -13321,10 +13321,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E496" s="2">
-        <v>82139</v>
+        <v>82106</v>
       </c>
       <c r="F496" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G496" s="1" t="s">
         <v>9</v>
@@ -13341,16 +13341,16 @@
         <v>33</v>
       </c>
       <c r="C497" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D497" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E497" s="2">
-        <v>82365</v>
+        <v>82107</v>
       </c>
       <c r="F497" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G497" s="1" t="s">
         <v>9</v>
@@ -13367,16 +13367,16 @@
         <v>33</v>
       </c>
       <c r="C498" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D498" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E498" s="2">
-        <v>82366</v>
+        <v>82109</v>
       </c>
       <c r="F498" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G498" s="1" t="s">
         <v>9</v>
@@ -13393,16 +13393,16 @@
         <v>33</v>
       </c>
       <c r="C499" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D499" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E499" s="2">
-        <v>82371</v>
+        <v>82110</v>
       </c>
       <c r="F499" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>9</v>
@@ -13419,16 +13419,16 @@
         <v>33</v>
       </c>
       <c r="C500" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D500" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E500" s="2">
-        <v>82383</v>
+        <v>82139</v>
       </c>
       <c r="F500" s="3">
-        <v>46083</v>
+        <v>46065</v>
       </c>
       <c r="G500" s="1" t="s">
         <v>9</v>
@@ -13451,10 +13451,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E501" s="2">
-        <v>82384</v>
+        <v>82365</v>
       </c>
       <c r="F501" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G501" s="1" t="s">
         <v>9</v>
@@ -13471,16 +13471,16 @@
         <v>33</v>
       </c>
       <c r="C502" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D502" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E502" s="2">
-        <v>82693</v>
+        <v>82366</v>
       </c>
       <c r="F502" s="3">
-        <v>46098</v>
+        <v>46080</v>
       </c>
       <c r="G502" s="1" t="s">
         <v>9</v>
@@ -13497,16 +13497,16 @@
         <v>33</v>
       </c>
       <c r="C503" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D503" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E503" s="2">
-        <v>82760</v>
+        <v>82371</v>
       </c>
       <c r="F503" s="3">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="G503" s="1" t="s">
         <v>9</v>
@@ -13523,16 +13523,16 @@
         <v>33</v>
       </c>
       <c r="C504" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D504" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E504" s="2">
-        <v>82763</v>
+        <v>82383</v>
       </c>
       <c r="F504" s="3">
-        <v>46101</v>
+        <v>46083</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>9</v>
@@ -13543,48 +13543,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="505">
       <c r="A505" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C505" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D505" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E505" s="2">
-        <v>81592</v>
+        <v>82384</v>
       </c>
       <c r="F505" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H505" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="506">
       <c r="A506" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C506" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D506" s="3">
-        <v>46029.4149454282</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E506" s="2">
-        <v>81593</v>
+        <v>82693</v>
       </c>
       <c r="F506" s="3">
-        <v>46031</v>
+        <v>46098</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>9</v>
@@ -13595,22 +13595,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="507">
       <c r="A507" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C507" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D507" s="3">
-        <v>46038.6827563889</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E507" s="2">
-        <v>81697</v>
+        <v>82760</v>
       </c>
       <c r="F507" s="3">
-        <v>46038</v>
+        <v>46101</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>9</v>
@@ -13621,28 +13621,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="508">
       <c r="A508" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C508" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D508" s="3">
-        <v>46038.6827563889</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E508" s="2">
-        <v>81735</v>
+        <v>82763</v>
       </c>
       <c r="F508" s="3">
-        <v>46041</v>
+        <v>46101</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="509">
@@ -13653,39 +13653,39 @@
         <v>34</v>
       </c>
       <c r="C509" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D509" s="3">
-        <v>46045.4532476157</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E509" s="2">
-        <v>81823</v>
+        <v>81592</v>
       </c>
       <c r="F509" s="3">
-        <v>46045</v>
+        <v>46031</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="510">
       <c r="A510" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C510" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D510" s="3">
-        <v>46031.4724550926</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E510" s="2">
-        <v>81572</v>
+        <v>81593</v>
       </c>
       <c r="F510" s="3">
         <v>46031</v>
@@ -13699,22 +13699,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="511">
       <c r="A511" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C511" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D511" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E511" s="2">
-        <v>81573</v>
+        <v>81697</v>
       </c>
       <c r="F511" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>9</v>
@@ -13725,48 +13725,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="512">
       <c r="A512" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C512" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D512" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E512" s="2">
-        <v>81579</v>
+        <v>81735</v>
       </c>
       <c r="F512" s="3">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="G512" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="513">
       <c r="A513" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C513" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D513" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E513" s="2">
-        <v>81580</v>
+        <v>81823</v>
       </c>
       <c r="F513" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G513" s="1" t="s">
         <v>9</v>
@@ -13789,7 +13789,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E514" s="2">
-        <v>81581</v>
+        <v>81572</v>
       </c>
       <c r="F514" s="3">
         <v>46031</v>
@@ -13815,7 +13815,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E515" s="2">
-        <v>81582</v>
+        <v>81573</v>
       </c>
       <c r="F515" s="3">
         <v>46031</v>
@@ -13841,7 +13841,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E516" s="2">
-        <v>81583</v>
+        <v>81579</v>
       </c>
       <c r="F516" s="3">
         <v>46031</v>
@@ -13861,16 +13861,16 @@
         <v>35</v>
       </c>
       <c r="C517" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D517" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E517" s="2">
-        <v>81667</v>
+        <v>81580</v>
       </c>
       <c r="F517" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G517" s="1" t="s">
         <v>9</v>
@@ -13887,16 +13887,16 @@
         <v>35</v>
       </c>
       <c r="C518" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D518" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E518" s="2">
-        <v>81668</v>
+        <v>81581</v>
       </c>
       <c r="F518" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>9</v>
@@ -13913,16 +13913,16 @@
         <v>35</v>
       </c>
       <c r="C519" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D519" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E519" s="2">
-        <v>81674</v>
+        <v>81582</v>
       </c>
       <c r="F519" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G519" s="1" t="s">
         <v>9</v>
@@ -13939,16 +13939,16 @@
         <v>35</v>
       </c>
       <c r="C520" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D520" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E520" s="2">
-        <v>81675</v>
+        <v>81583</v>
       </c>
       <c r="F520" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G520" s="1" t="s">
         <v>9</v>
@@ -13971,10 +13971,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E521" s="2">
-        <v>81677</v>
+        <v>81667</v>
       </c>
       <c r="F521" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G521" s="1" t="s">
         <v>9</v>
@@ -13991,16 +13991,16 @@
         <v>35</v>
       </c>
       <c r="C522" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D522" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E522" s="2">
-        <v>81739</v>
+        <v>81668</v>
       </c>
       <c r="F522" s="3">
-        <v>46041</v>
+        <v>46037</v>
       </c>
       <c r="G522" s="1" t="s">
         <v>9</v>
@@ -14017,16 +14017,16 @@
         <v>35</v>
       </c>
       <c r="C523" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D523" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E523" s="2">
-        <v>81741</v>
+        <v>81674</v>
       </c>
       <c r="F523" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>9</v>
@@ -14043,16 +14043,16 @@
         <v>35</v>
       </c>
       <c r="C524" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D524" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E524" s="2">
-        <v>81854</v>
+        <v>81675</v>
       </c>
       <c r="F524" s="3">
-        <v>46048</v>
+        <v>46038</v>
       </c>
       <c r="G524" s="1" t="s">
         <v>9</v>
@@ -14069,16 +14069,16 @@
         <v>35</v>
       </c>
       <c r="C525" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D525" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E525" s="2">
-        <v>81855</v>
+        <v>81677</v>
       </c>
       <c r="F525" s="3">
-        <v>46048</v>
+        <v>46038</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>9</v>
@@ -14095,16 +14095,16 @@
         <v>35</v>
       </c>
       <c r="C526" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D526" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E526" s="2">
-        <v>81858</v>
+        <v>81739</v>
       </c>
       <c r="F526" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G526" s="1" t="s">
         <v>9</v>
@@ -14121,16 +14121,16 @@
         <v>35</v>
       </c>
       <c r="C527" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D527" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E527" s="2">
-        <v>81859</v>
+        <v>81741</v>
       </c>
       <c r="F527" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G527" s="1" t="s">
         <v>9</v>
@@ -14153,10 +14153,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E528" s="2">
-        <v>81862</v>
+        <v>81854</v>
       </c>
       <c r="F528" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G528" s="1" t="s">
         <v>9</v>
@@ -14179,10 +14179,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E529" s="2">
-        <v>81863</v>
+        <v>81855</v>
       </c>
       <c r="F529" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G529" s="1" t="s">
         <v>9</v>
@@ -14199,16 +14199,16 @@
         <v>35</v>
       </c>
       <c r="C530" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D530" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E530" s="2">
-        <v>81958</v>
+        <v>81858</v>
       </c>
       <c r="F530" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>9</v>
@@ -14225,16 +14225,16 @@
         <v>35</v>
       </c>
       <c r="C531" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D531" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E531" s="2">
-        <v>81965</v>
+        <v>81859</v>
       </c>
       <c r="F531" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G531" s="1" t="s">
         <v>9</v>
@@ -14251,16 +14251,16 @@
         <v>35</v>
       </c>
       <c r="C532" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D532" s="3">
-        <v>46063.5923590625</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E532" s="2">
-        <v>82085</v>
+        <v>81862</v>
       </c>
       <c r="F532" s="3">
-        <v>46063</v>
+        <v>46049</v>
       </c>
       <c r="G532" s="1" t="s">
         <v>9</v>
@@ -14277,16 +14277,16 @@
         <v>35</v>
       </c>
       <c r="C533" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D533" s="3">
-        <v>46063.5923590625</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E533" s="2">
-        <v>82086</v>
+        <v>81863</v>
       </c>
       <c r="F533" s="3">
-        <v>46063</v>
+        <v>46049</v>
       </c>
       <c r="G533" s="1" t="s">
         <v>9</v>
@@ -14303,16 +14303,16 @@
         <v>35</v>
       </c>
       <c r="C534" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D534" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E534" s="2">
-        <v>82126</v>
+        <v>81958</v>
       </c>
       <c r="F534" s="3">
-        <v>46065</v>
+        <v>46055</v>
       </c>
       <c r="G534" s="1" t="s">
         <v>9</v>
@@ -14329,16 +14329,16 @@
         <v>35</v>
       </c>
       <c r="C535" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D535" s="3">
-        <v>46064.5127051505</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E535" s="2">
-        <v>82268</v>
+        <v>81965</v>
       </c>
       <c r="F535" s="3">
-        <v>46077</v>
+        <v>46055</v>
       </c>
       <c r="G535" s="1" t="s">
         <v>9</v>
@@ -14355,16 +14355,16 @@
         <v>35</v>
       </c>
       <c r="C536" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D536" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E536" s="2">
-        <v>82142</v>
+        <v>82085</v>
       </c>
       <c r="F536" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G536" s="1" t="s">
         <v>9</v>
@@ -14381,16 +14381,16 @@
         <v>35</v>
       </c>
       <c r="C537" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D537" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E537" s="2">
-        <v>82143</v>
+        <v>82086</v>
       </c>
       <c r="F537" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G537" s="1" t="s">
         <v>9</v>
@@ -14407,13 +14407,13 @@
         <v>35</v>
       </c>
       <c r="C538" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D538" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E538" s="2">
-        <v>82144</v>
+        <v>82126</v>
       </c>
       <c r="F538" s="3">
         <v>46065</v>
@@ -14433,16 +14433,16 @@
         <v>35</v>
       </c>
       <c r="C539" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D539" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E539" s="2">
-        <v>82166</v>
+        <v>82268</v>
       </c>
       <c r="F539" s="3">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="G539" s="1" t="s">
         <v>9</v>
@@ -14459,16 +14459,16 @@
         <v>35</v>
       </c>
       <c r="C540" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D540" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E540" s="2">
-        <v>82262</v>
+        <v>82142</v>
       </c>
       <c r="F540" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G540" s="1" t="s">
         <v>9</v>
@@ -14485,16 +14485,16 @@
         <v>35</v>
       </c>
       <c r="C541" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D541" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E541" s="2">
-        <v>82265</v>
+        <v>82143</v>
       </c>
       <c r="F541" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G541" s="1" t="s">
         <v>9</v>
@@ -14511,16 +14511,16 @@
         <v>35</v>
       </c>
       <c r="C542" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D542" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E542" s="2">
-        <v>82281</v>
+        <v>82144</v>
       </c>
       <c r="F542" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G542" s="1" t="s">
         <v>9</v>
@@ -14537,16 +14537,16 @@
         <v>35</v>
       </c>
       <c r="C543" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D543" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E543" s="2">
-        <v>82282</v>
+        <v>82166</v>
       </c>
       <c r="F543" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G543" s="1" t="s">
         <v>9</v>
@@ -14563,16 +14563,16 @@
         <v>35</v>
       </c>
       <c r="C544" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D544" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E544" s="2">
-        <v>82340</v>
+        <v>82262</v>
       </c>
       <c r="F544" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G544" s="1" t="s">
         <v>9</v>
@@ -14589,16 +14589,16 @@
         <v>35</v>
       </c>
       <c r="C545" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D545" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E545" s="2">
-        <v>82399</v>
+        <v>82265</v>
       </c>
       <c r="F545" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G545" s="1" t="s">
         <v>9</v>
@@ -14615,16 +14615,16 @@
         <v>35</v>
       </c>
       <c r="C546" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D546" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E546" s="2">
-        <v>82400</v>
+        <v>82281</v>
       </c>
       <c r="F546" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G546" s="1" t="s">
         <v>9</v>
@@ -14641,16 +14641,16 @@
         <v>35</v>
       </c>
       <c r="C547" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D547" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E547" s="2">
-        <v>82401</v>
+        <v>82282</v>
       </c>
       <c r="F547" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G547" s="1" t="s">
         <v>9</v>
@@ -14667,16 +14667,16 @@
         <v>35</v>
       </c>
       <c r="C548" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D548" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E548" s="2">
-        <v>82412</v>
+        <v>82340</v>
       </c>
       <c r="F548" s="3">
-        <v>46084</v>
+        <v>46079</v>
       </c>
       <c r="G548" s="1" t="s">
         <v>9</v>
@@ -14699,10 +14699,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E549" s="2">
-        <v>82415</v>
+        <v>82399</v>
       </c>
       <c r="F549" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G549" s="1" t="s">
         <v>9</v>
@@ -14719,16 +14719,16 @@
         <v>35</v>
       </c>
       <c r="C550" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D550" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E550" s="2">
-        <v>82571</v>
+        <v>82400</v>
       </c>
       <c r="F550" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G550" s="1" t="s">
         <v>9</v>
@@ -14745,16 +14745,16 @@
         <v>35</v>
       </c>
       <c r="C551" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D551" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E551" s="2">
-        <v>82572</v>
+        <v>82401</v>
       </c>
       <c r="F551" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G551" s="1" t="s">
         <v>9</v>
@@ -14771,16 +14771,16 @@
         <v>35</v>
       </c>
       <c r="C552" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D552" s="3">
-        <v>46094.4745190394</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E552" s="2">
-        <v>82630</v>
+        <v>82412</v>
       </c>
       <c r="F552" s="3">
-        <v>46094</v>
+        <v>46084</v>
       </c>
       <c r="G552" s="1" t="s">
         <v>9</v>
@@ -14797,16 +14797,16 @@
         <v>35</v>
       </c>
       <c r="C553" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D553" s="3">
-        <v>46094.4745190394</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E553" s="2">
-        <v>82631</v>
+        <v>82415</v>
       </c>
       <c r="F553" s="3">
-        <v>46094</v>
+        <v>46084</v>
       </c>
       <c r="G553" s="1" t="s">
         <v>9</v>
@@ -14823,16 +14823,16 @@
         <v>35</v>
       </c>
       <c r="C554" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D554" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E554" s="2">
-        <v>82632</v>
+        <v>82571</v>
       </c>
       <c r="F554" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G554" s="1" t="s">
         <v>9</v>
@@ -14849,16 +14849,16 @@
         <v>35</v>
       </c>
       <c r="C555" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D555" s="3">
-        <v>46097.4499278356</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E555" s="2">
-        <v>82653</v>
+        <v>82572</v>
       </c>
       <c r="F555" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G555" s="1" t="s">
         <v>9</v>
@@ -14875,16 +14875,16 @@
         <v>35</v>
       </c>
       <c r="C556" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D556" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E556" s="2">
-        <v>82665</v>
+        <v>82630</v>
       </c>
       <c r="F556" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G556" s="1" t="s">
         <v>9</v>
@@ -14901,16 +14901,16 @@
         <v>35</v>
       </c>
       <c r="C557" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D557" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E557" s="2">
-        <v>82668</v>
+        <v>82631</v>
       </c>
       <c r="F557" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G557" s="1" t="s">
         <v>9</v>
@@ -14927,16 +14927,16 @@
         <v>35</v>
       </c>
       <c r="C558" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D558" s="3">
-        <v>46098.6661386574</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E558" s="2">
-        <v>82696</v>
+        <v>82632</v>
       </c>
       <c r="F558" s="3">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="G558" s="1" t="s">
         <v>9</v>
@@ -14953,16 +14953,16 @@
         <v>35</v>
       </c>
       <c r="C559" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D559" s="3">
-        <v>46098.6661386574</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E559" s="2">
-        <v>82704</v>
+        <v>82653</v>
       </c>
       <c r="F559" s="3">
-        <v>46099</v>
+        <v>46097</v>
       </c>
       <c r="G559" s="1" t="s">
         <v>9</v>
@@ -14973,22 +14973,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="560">
       <c r="A560" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C560" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D560" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E560" s="2">
-        <v>82311</v>
+        <v>82665</v>
       </c>
       <c r="F560" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G560" s="1" t="s">
         <v>9</v>
@@ -14999,22 +14999,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="561">
       <c r="A561" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C561" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D561" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E561" s="2">
-        <v>82312</v>
+        <v>82668</v>
       </c>
       <c r="F561" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G561" s="1" t="s">
         <v>9</v>
@@ -15025,22 +15025,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="562">
       <c r="A562" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C562" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D562" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E562" s="2">
-        <v>82313</v>
+        <v>82696</v>
       </c>
       <c r="F562" s="3">
-        <v>46078</v>
+        <v>46098</v>
       </c>
       <c r="G562" s="1" t="s">
         <v>9</v>
@@ -15051,22 +15051,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="563">
       <c r="A563" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C563" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D563" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E563" s="2">
-        <v>82314</v>
+        <v>82704</v>
       </c>
       <c r="F563" s="3">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="G563" s="1" t="s">
         <v>9</v>
@@ -15089,10 +15089,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E564" s="2">
-        <v>82346</v>
+        <v>82311</v>
       </c>
       <c r="F564" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G564" s="1" t="s">
         <v>9</v>
@@ -15115,10 +15115,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E565" s="2">
-        <v>82361</v>
+        <v>82312</v>
       </c>
       <c r="F565" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G565" s="1" t="s">
         <v>9</v>
@@ -15141,10 +15141,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E566" s="2">
-        <v>82385</v>
+        <v>82313</v>
       </c>
       <c r="F566" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G566" s="1" t="s">
         <v>9</v>
@@ -15167,10 +15167,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E567" s="2">
-        <v>82391</v>
+        <v>82314</v>
       </c>
       <c r="F567" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G567" s="1" t="s">
         <v>9</v>
@@ -15193,10 +15193,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E568" s="2">
-        <v>82392</v>
+        <v>82346</v>
       </c>
       <c r="F568" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G568" s="1" t="s">
         <v>9</v>
@@ -15213,16 +15213,16 @@
         <v>36</v>
       </c>
       <c r="C569" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D569" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E569" s="2">
-        <v>82691</v>
+        <v>82361</v>
       </c>
       <c r="F569" s="3">
-        <v>46098</v>
+        <v>46080</v>
       </c>
       <c r="G569" s="1" t="s">
         <v>9</v>
@@ -15239,16 +15239,16 @@
         <v>36</v>
       </c>
       <c r="C570" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D570" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E570" s="2">
-        <v>82692</v>
+        <v>82385</v>
       </c>
       <c r="F570" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G570" s="1" t="s">
         <v>9</v>
@@ -15265,16 +15265,16 @@
         <v>36</v>
       </c>
       <c r="C571" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D571" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E571" s="2">
-        <v>82699</v>
+        <v>82391</v>
       </c>
       <c r="F571" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G571" s="1" t="s">
         <v>9</v>
@@ -15291,16 +15291,16 @@
         <v>36</v>
       </c>
       <c r="C572" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D572" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E572" s="2">
-        <v>82716</v>
+        <v>82392</v>
       </c>
       <c r="F572" s="3">
-        <v>46099</v>
+        <v>46083</v>
       </c>
       <c r="G572" s="1" t="s">
         <v>9</v>
@@ -15323,10 +15323,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E573" s="2">
-        <v>82717</v>
+        <v>82691</v>
       </c>
       <c r="F573" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G573" s="1" t="s">
         <v>9</v>
@@ -15349,10 +15349,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E574" s="2">
-        <v>82786</v>
+        <v>82692</v>
       </c>
       <c r="F574" s="3">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="G574" s="1" t="s">
         <v>9</v>
@@ -15369,16 +15369,16 @@
         <v>36</v>
       </c>
       <c r="C575" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D575" s="3">
-        <v>46104.452366169</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E575" s="2">
-        <v>82780</v>
+        <v>82699</v>
       </c>
       <c r="F575" s="3">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="G575" s="1" t="s">
         <v>9</v>
@@ -15395,16 +15395,16 @@
         <v>36</v>
       </c>
       <c r="C576" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D576" s="3">
-        <v>46104.452366169</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E576" s="2">
-        <v>82784</v>
+        <v>82716</v>
       </c>
       <c r="F576" s="3">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="G576" s="1" t="s">
         <v>9</v>
@@ -15421,16 +15421,16 @@
         <v>36</v>
       </c>
       <c r="C577" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D577" s="3">
-        <v>46104.452366169</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E577" s="2">
-        <v>82785</v>
+        <v>82717</v>
       </c>
       <c r="F577" s="3">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="G577" s="1" t="s">
         <v>9</v>
@@ -15441,22 +15441,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="578">
       <c r="A578" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C578" s="2">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D578" s="3">
-        <v>46029.4632696412</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E578" s="2">
-        <v>81495</v>
+        <v>82786</v>
       </c>
       <c r="F578" s="3">
-        <v>46029</v>
+        <v>46104</v>
       </c>
       <c r="G578" s="1" t="s">
         <v>9</v>
@@ -15467,27 +15467,157 @@
     </row>
     <row ht="12.75" customHeight="1" r="579">
       <c r="A579" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C579" s="2">
+        <v>3</v>
+      </c>
+      <c r="D579" s="3">
+        <v>46104.452366169</v>
+      </c>
+      <c r="E579" s="2">
+        <v>82780</v>
+      </c>
+      <c r="F579" s="3">
+        <v>46104</v>
+      </c>
+      <c r="G579" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H579" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="580">
+      <c r="A580" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C580" s="2">
+        <v>3</v>
+      </c>
+      <c r="D580" s="3">
+        <v>46104.452366169</v>
+      </c>
+      <c r="E580" s="2">
+        <v>82784</v>
+      </c>
+      <c r="F580" s="3">
+        <v>46104</v>
+      </c>
+      <c r="G580" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H580" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="581">
+      <c r="A581" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C581" s="2">
+        <v>3</v>
+      </c>
+      <c r="D581" s="3">
+        <v>46104.452366169</v>
+      </c>
+      <c r="E581" s="2">
+        <v>82785</v>
+      </c>
+      <c r="F581" s="3">
+        <v>46104</v>
+      </c>
+      <c r="G581" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H581" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="582">
+      <c r="A582" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C582" s="2">
+        <v>3</v>
+      </c>
+      <c r="D582" s="3">
+        <v>46104.452366169</v>
+      </c>
+      <c r="E582" s="2">
+        <v>82792</v>
+      </c>
+      <c r="F582" s="3">
+        <v>46105</v>
+      </c>
+      <c r="G582" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H582" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="583">
+      <c r="A583" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C583" s="2">
+        <v>62</v>
+      </c>
+      <c r="D583" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E583" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F583" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G583" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H583" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="584">
+      <c r="A584" s="2">
         <v>9992</v>
       </c>
-      <c r="B579" s="1" t="s">
+      <c r="B584" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C579" s="2">
+      <c r="C584" s="2">
         <v>390</v>
       </c>
-      <c r="D579" s="3">
+      <c r="D584" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E579" s="2">
+      <c r="E584" s="2">
         <v>81684</v>
       </c>
-      <c r="F579" s="3">
+      <c r="F584" s="3">
         <v>46038</v>
       </c>
-      <c r="G579" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H579" s="1" t="s">
+      <c r="G584" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H584" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H584"/>
+  <dimension ref="A1:H586"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -11229,22 +11229,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="416">
       <c r="A416" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C416" s="2">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D416" s="3">
-        <v>46029.3821391551</v>
+        <v>46105.7312393519</v>
       </c>
       <c r="E416" s="2">
-        <v>81477</v>
+        <v>82812</v>
       </c>
       <c r="F416" s="3">
-        <v>46029</v>
+        <v>46106</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>9</v>
@@ -11261,16 +11261,16 @@
         <v>31</v>
       </c>
       <c r="C417" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D417" s="3">
-        <v>46030.4142968056</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E417" s="2">
-        <v>81532</v>
+        <v>81477</v>
       </c>
       <c r="F417" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>9</v>
@@ -11293,7 +11293,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E418" s="2">
-        <v>81534</v>
+        <v>81532</v>
       </c>
       <c r="F418" s="3">
         <v>46030</v>
@@ -11319,7 +11319,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E419" s="2">
-        <v>81535</v>
+        <v>81534</v>
       </c>
       <c r="F419" s="3">
         <v>46030</v>
@@ -11345,7 +11345,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E420" s="2">
-        <v>81550</v>
+        <v>81535</v>
       </c>
       <c r="F420" s="3">
         <v>46030</v>
@@ -11371,7 +11371,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E421" s="2">
-        <v>81553</v>
+        <v>81550</v>
       </c>
       <c r="F421" s="3">
         <v>46030</v>
@@ -11397,7 +11397,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E422" s="2">
-        <v>81554</v>
+        <v>81553</v>
       </c>
       <c r="F422" s="3">
         <v>46030</v>
@@ -11423,7 +11423,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E423" s="2">
-        <v>81557</v>
+        <v>81554</v>
       </c>
       <c r="F423" s="3">
         <v>46030</v>
@@ -11449,10 +11449,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E424" s="2">
-        <v>81588</v>
+        <v>81557</v>
       </c>
       <c r="F424" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>9</v>
@@ -11469,16 +11469,16 @@
         <v>31</v>
       </c>
       <c r="C425" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D425" s="3">
-        <v>46038.593985081</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E425" s="2">
-        <v>81692</v>
+        <v>81588</v>
       </c>
       <c r="F425" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>9</v>
@@ -11495,16 +11495,16 @@
         <v>31</v>
       </c>
       <c r="C426" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D426" s="3">
-        <v>46044.46462125</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E426" s="2">
-        <v>81786</v>
+        <v>81692</v>
       </c>
       <c r="F426" s="3">
-        <v>46044</v>
+        <v>46038</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>9</v>
@@ -11521,16 +11521,16 @@
         <v>31</v>
       </c>
       <c r="C427" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D427" s="3">
-        <v>46044.6362443171</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E427" s="2">
-        <v>81844</v>
+        <v>81786</v>
       </c>
       <c r="F427" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11547,16 +11547,16 @@
         <v>31</v>
       </c>
       <c r="C428" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D428" s="3">
-        <v>46062.717040544</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E428" s="2">
-        <v>82065</v>
+        <v>81844</v>
       </c>
       <c r="F428" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>9</v>
@@ -11579,7 +11579,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E429" s="2">
-        <v>82066</v>
+        <v>82065</v>
       </c>
       <c r="F429" s="3">
         <v>46062</v>
@@ -11605,7 +11605,7 @@
         <v>46062.717040544</v>
       </c>
       <c r="E430" s="2">
-        <v>82067</v>
+        <v>82066</v>
       </c>
       <c r="F430" s="3">
         <v>46062</v>
@@ -11625,16 +11625,16 @@
         <v>31</v>
       </c>
       <c r="C431" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D431" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E431" s="2">
-        <v>82190</v>
+        <v>82067</v>
       </c>
       <c r="F431" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>9</v>
@@ -11657,7 +11657,7 @@
         <v>46065.6300915625</v>
       </c>
       <c r="E432" s="2">
-        <v>82197</v>
+        <v>82190</v>
       </c>
       <c r="F432" s="3">
         <v>46066</v>
@@ -11677,16 +11677,16 @@
         <v>31</v>
       </c>
       <c r="C433" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D433" s="3">
-        <v>46077.5084780324</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E433" s="2">
-        <v>82270</v>
+        <v>82197</v>
       </c>
       <c r="F433" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11703,13 +11703,13 @@
         <v>31</v>
       </c>
       <c r="C434" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D434" s="3">
-        <v>46077.721037037</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E434" s="2">
-        <v>82285</v>
+        <v>82270</v>
       </c>
       <c r="F434" s="3">
         <v>46077</v>
@@ -11729,16 +11729,16 @@
         <v>31</v>
       </c>
       <c r="C435" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D435" s="3">
-        <v>46083.6694849421</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E435" s="2">
-        <v>82417</v>
+        <v>82285</v>
       </c>
       <c r="F435" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>9</v>
@@ -11755,16 +11755,16 @@
         <v>31</v>
       </c>
       <c r="C436" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D436" s="3">
-        <v>46085.7157723032</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E436" s="2">
-        <v>82457</v>
+        <v>82417</v>
       </c>
       <c r="F436" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>9</v>
@@ -11781,16 +11781,16 @@
         <v>31</v>
       </c>
       <c r="C437" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D437" s="3">
-        <v>46099.6523956944</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E437" s="2">
-        <v>82724</v>
+        <v>82457</v>
       </c>
       <c r="F437" s="3">
-        <v>46099</v>
+        <v>46086</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>9</v>
@@ -11813,7 +11813,7 @@
         <v>46099.6523956944</v>
       </c>
       <c r="E438" s="2">
-        <v>82725</v>
+        <v>82724</v>
       </c>
       <c r="F438" s="3">
         <v>46099</v>
@@ -11839,10 +11839,10 @@
         <v>46099.6523956944</v>
       </c>
       <c r="E439" s="2">
-        <v>82727</v>
+        <v>82725</v>
       </c>
       <c r="F439" s="3">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11865,7 +11865,7 @@
         <v>46099.6523956944</v>
       </c>
       <c r="E440" s="2">
-        <v>82730</v>
+        <v>82727</v>
       </c>
       <c r="F440" s="3">
         <v>46100</v>
@@ -11879,22 +11879,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="441">
       <c r="A441" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C441" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D441" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E441" s="2">
-        <v>81484</v>
+        <v>82730</v>
       </c>
       <c r="F441" s="3">
-        <v>46029</v>
+        <v>46100</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11917,7 +11917,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E442" s="2">
-        <v>81486</v>
+        <v>81484</v>
       </c>
       <c r="F442" s="3">
         <v>46029</v>
@@ -11943,7 +11943,7 @@
         <v>46029.381258831</v>
       </c>
       <c r="E443" s="2">
-        <v>81487</v>
+        <v>81486</v>
       </c>
       <c r="F443" s="3">
         <v>46029</v>
@@ -11963,16 +11963,16 @@
         <v>32</v>
       </c>
       <c r="C444" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D444" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E444" s="2">
-        <v>81613</v>
+        <v>81487</v>
       </c>
       <c r="F444" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11995,7 +11995,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E445" s="2">
-        <v>81614</v>
+        <v>81613</v>
       </c>
       <c r="F445" s="3">
         <v>46036</v>
@@ -12021,7 +12021,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E446" s="2">
-        <v>81622</v>
+        <v>81614</v>
       </c>
       <c r="F446" s="3">
         <v>46036</v>
@@ -12047,7 +12047,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E447" s="2">
-        <v>81632</v>
+        <v>81622</v>
       </c>
       <c r="F447" s="3">
         <v>46036</v>
@@ -12073,10 +12073,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E448" s="2">
-        <v>81648</v>
+        <v>81632</v>
       </c>
       <c r="F448" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12099,7 +12099,7 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E449" s="2">
-        <v>81664</v>
+        <v>81648</v>
       </c>
       <c r="F449" s="3">
         <v>46037</v>
@@ -12119,16 +12119,16 @@
         <v>32</v>
       </c>
       <c r="C450" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D450" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E450" s="2">
-        <v>81815</v>
+        <v>81664</v>
       </c>
       <c r="F450" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12151,7 +12151,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E451" s="2">
-        <v>81816</v>
+        <v>81815</v>
       </c>
       <c r="F451" s="3">
         <v>46045</v>
@@ -12177,7 +12177,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E452" s="2">
-        <v>81838</v>
+        <v>81816</v>
       </c>
       <c r="F452" s="3">
         <v>46045</v>
@@ -12203,7 +12203,7 @@
         <v>46045.4188638426</v>
       </c>
       <c r="E453" s="2">
-        <v>81840</v>
+        <v>81838</v>
       </c>
       <c r="F453" s="3">
         <v>46045</v>
@@ -12223,16 +12223,16 @@
         <v>32</v>
       </c>
       <c r="C454" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D454" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E454" s="2">
-        <v>81959</v>
+        <v>81840</v>
       </c>
       <c r="F454" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>9</v>
@@ -12255,7 +12255,7 @@
         <v>46055.5991080671</v>
       </c>
       <c r="E455" s="2">
-        <v>81960</v>
+        <v>81959</v>
       </c>
       <c r="F455" s="3">
         <v>46055</v>
@@ -12275,16 +12275,16 @@
         <v>32</v>
       </c>
       <c r="C456" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D456" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E456" s="2">
-        <v>82063</v>
+        <v>81960</v>
       </c>
       <c r="F456" s="3">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12307,7 +12307,7 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E457" s="2">
-        <v>82064</v>
+        <v>82063</v>
       </c>
       <c r="F457" s="3">
         <v>46062</v>
@@ -12333,10 +12333,10 @@
         <v>46062.7151302546</v>
       </c>
       <c r="E458" s="2">
-        <v>82100</v>
+        <v>82064</v>
       </c>
       <c r="F458" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12353,16 +12353,16 @@
         <v>32</v>
       </c>
       <c r="C459" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D459" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E459" s="2">
-        <v>82333</v>
+        <v>82100</v>
       </c>
       <c r="F459" s="3">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12385,7 +12385,7 @@
         <v>46072.7410579977</v>
       </c>
       <c r="E460" s="2">
-        <v>82334</v>
+        <v>82333</v>
       </c>
       <c r="F460" s="3">
         <v>46079</v>
@@ -12405,16 +12405,16 @@
         <v>32</v>
       </c>
       <c r="C461" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D461" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E461" s="2">
-        <v>82258</v>
+        <v>82334</v>
       </c>
       <c r="F461" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12437,7 +12437,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E462" s="2">
-        <v>82259</v>
+        <v>82258</v>
       </c>
       <c r="F462" s="3">
         <v>46076</v>
@@ -12463,7 +12463,7 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E463" s="2">
-        <v>82260</v>
+        <v>82259</v>
       </c>
       <c r="F463" s="3">
         <v>46076</v>
@@ -12489,10 +12489,10 @@
         <v>46076.7259125116</v>
       </c>
       <c r="E464" s="2">
-        <v>82274</v>
+        <v>82260</v>
       </c>
       <c r="F464" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12509,16 +12509,16 @@
         <v>32</v>
       </c>
       <c r="C465" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D465" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E465" s="2">
-        <v>82409</v>
+        <v>82274</v>
       </c>
       <c r="F465" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>9</v>
@@ -12535,16 +12535,16 @@
         <v>32</v>
       </c>
       <c r="C466" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D466" s="3">
-        <v>46093.4920058565</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E466" s="2">
-        <v>82581</v>
+        <v>82409</v>
       </c>
       <c r="F466" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12567,7 +12567,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E467" s="2">
-        <v>82582</v>
+        <v>82581</v>
       </c>
       <c r="F467" s="3">
         <v>46093</v>
@@ -12593,7 +12593,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E468" s="2">
-        <v>82583</v>
+        <v>82582</v>
       </c>
       <c r="F468" s="3">
         <v>46093</v>
@@ -12619,10 +12619,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E469" s="2">
-        <v>82672</v>
+        <v>82583</v>
       </c>
       <c r="F469" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>9</v>
@@ -12645,7 +12645,7 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E470" s="2">
-        <v>82674</v>
+        <v>82672</v>
       </c>
       <c r="F470" s="3">
         <v>46097</v>
@@ -12659,22 +12659,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="471">
       <c r="A471" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C471" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D471" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E471" s="2">
-        <v>81608</v>
+        <v>82674</v>
       </c>
       <c r="F471" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>9</v>
@@ -12697,7 +12697,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E472" s="2">
-        <v>81609</v>
+        <v>81608</v>
       </c>
       <c r="F472" s="3">
         <v>46035</v>
@@ -12723,7 +12723,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E473" s="2">
-        <v>81610</v>
+        <v>81609</v>
       </c>
       <c r="F473" s="3">
         <v>46035</v>
@@ -12749,7 +12749,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E474" s="2">
-        <v>81611</v>
+        <v>81610</v>
       </c>
       <c r="F474" s="3">
         <v>46035</v>
@@ -12775,7 +12775,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E475" s="2">
-        <v>81612</v>
+        <v>81611</v>
       </c>
       <c r="F475" s="3">
         <v>46035</v>
@@ -12795,16 +12795,16 @@
         <v>33</v>
       </c>
       <c r="C476" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D476" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E476" s="2">
-        <v>81652</v>
+        <v>81612</v>
       </c>
       <c r="F476" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>9</v>
@@ -12827,7 +12827,7 @@
         <v>46036.6342081481</v>
       </c>
       <c r="E477" s="2">
-        <v>81659</v>
+        <v>81652</v>
       </c>
       <c r="F477" s="3">
         <v>46037</v>
@@ -12847,16 +12847,16 @@
         <v>33</v>
       </c>
       <c r="C478" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D478" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E478" s="2">
-        <v>81853</v>
+        <v>81659</v>
       </c>
       <c r="F478" s="3">
-        <v>46048</v>
+        <v>46037</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12879,10 +12879,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E479" s="2">
-        <v>81869</v>
+        <v>81853</v>
       </c>
       <c r="F479" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12905,10 +12905,10 @@
         <v>46048.6509980093</v>
       </c>
       <c r="E480" s="2">
-        <v>81890</v>
+        <v>81869</v>
       </c>
       <c r="F480" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>9</v>
@@ -12925,16 +12925,16 @@
         <v>33</v>
       </c>
       <c r="C481" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D481" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E481" s="2">
-        <v>81875</v>
+        <v>81890</v>
       </c>
       <c r="F481" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>9</v>
@@ -12957,10 +12957,10 @@
         <v>46049.4871256134</v>
       </c>
       <c r="E482" s="2">
-        <v>81881</v>
+        <v>81875</v>
       </c>
       <c r="F482" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12977,16 +12977,16 @@
         <v>33</v>
       </c>
       <c r="C483" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D483" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E483" s="2">
-        <v>82015</v>
+        <v>81881</v>
       </c>
       <c r="F483" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>9</v>
@@ -13009,7 +13009,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E484" s="2">
-        <v>82017</v>
+        <v>82015</v>
       </c>
       <c r="F484" s="3">
         <v>46058</v>
@@ -13035,7 +13035,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E485" s="2">
-        <v>82020</v>
+        <v>82017</v>
       </c>
       <c r="F485" s="3">
         <v>46058</v>
@@ -13061,7 +13061,7 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E486" s="2">
-        <v>82023</v>
+        <v>82020</v>
       </c>
       <c r="F486" s="3">
         <v>46058</v>
@@ -13087,10 +13087,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E487" s="2">
-        <v>82061</v>
+        <v>82023</v>
       </c>
       <c r="F487" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>9</v>
@@ -13113,10 +13113,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E488" s="2">
-        <v>82081</v>
+        <v>82061</v>
       </c>
       <c r="F488" s="3">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>9</v>
@@ -13139,10 +13139,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E489" s="2">
-        <v>82095</v>
+        <v>82081</v>
       </c>
       <c r="F489" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>9</v>
@@ -13159,16 +13159,16 @@
         <v>33</v>
       </c>
       <c r="C490" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D490" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E490" s="2">
-        <v>82081</v>
+        <v>82095</v>
       </c>
       <c r="F490" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>9</v>
@@ -13191,10 +13191,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E491" s="2">
-        <v>82107</v>
+        <v>82081</v>
       </c>
       <c r="F491" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>9</v>
@@ -13217,7 +13217,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E492" s="2">
-        <v>82112</v>
+        <v>82107</v>
       </c>
       <c r="F492" s="3">
         <v>46064</v>
@@ -13243,7 +13243,7 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E493" s="2">
-        <v>82113</v>
+        <v>82112</v>
       </c>
       <c r="F493" s="3">
         <v>46064</v>
@@ -13269,10 +13269,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E494" s="2">
-        <v>82123</v>
+        <v>82113</v>
       </c>
       <c r="F494" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>9</v>
@@ -13289,16 +13289,16 @@
         <v>33</v>
       </c>
       <c r="C495" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D495" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E495" s="2">
-        <v>82095</v>
+        <v>82123</v>
       </c>
       <c r="F495" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>9</v>
@@ -13321,7 +13321,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E496" s="2">
-        <v>82106</v>
+        <v>82095</v>
       </c>
       <c r="F496" s="3">
         <v>46064</v>
@@ -13347,7 +13347,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E497" s="2">
-        <v>82107</v>
+        <v>82106</v>
       </c>
       <c r="F497" s="3">
         <v>46064</v>
@@ -13373,7 +13373,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E498" s="2">
-        <v>82109</v>
+        <v>82107</v>
       </c>
       <c r="F498" s="3">
         <v>46064</v>
@@ -13399,7 +13399,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E499" s="2">
-        <v>82110</v>
+        <v>82109</v>
       </c>
       <c r="F499" s="3">
         <v>46064</v>
@@ -13425,10 +13425,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E500" s="2">
-        <v>82139</v>
+        <v>82110</v>
       </c>
       <c r="F500" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G500" s="1" t="s">
         <v>9</v>
@@ -13445,16 +13445,16 @@
         <v>33</v>
       </c>
       <c r="C501" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D501" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E501" s="2">
-        <v>82365</v>
+        <v>82139</v>
       </c>
       <c r="F501" s="3">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="G501" s="1" t="s">
         <v>9</v>
@@ -13477,7 +13477,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E502" s="2">
-        <v>82366</v>
+        <v>82365</v>
       </c>
       <c r="F502" s="3">
         <v>46080</v>
@@ -13503,7 +13503,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E503" s="2">
-        <v>82371</v>
+        <v>82366</v>
       </c>
       <c r="F503" s="3">
         <v>46080</v>
@@ -13529,10 +13529,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E504" s="2">
-        <v>82383</v>
+        <v>82371</v>
       </c>
       <c r="F504" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>9</v>
@@ -13555,7 +13555,7 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E505" s="2">
-        <v>82384</v>
+        <v>82383</v>
       </c>
       <c r="F505" s="3">
         <v>46083</v>
@@ -13575,16 +13575,16 @@
         <v>33</v>
       </c>
       <c r="C506" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D506" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E506" s="2">
-        <v>82693</v>
+        <v>82384</v>
       </c>
       <c r="F506" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>9</v>
@@ -13607,10 +13607,10 @@
         <v>46098.4979333449</v>
       </c>
       <c r="E507" s="2">
-        <v>82760</v>
+        <v>82693</v>
       </c>
       <c r="F507" s="3">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>9</v>
@@ -13633,7 +13633,7 @@
         <v>46098.4979333449</v>
       </c>
       <c r="E508" s="2">
-        <v>82763</v>
+        <v>82760</v>
       </c>
       <c r="F508" s="3">
         <v>46101</v>
@@ -13647,28 +13647,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="509">
       <c r="A509" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C509" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D509" s="3">
-        <v>46029.4149454282</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E509" s="2">
-        <v>81592</v>
+        <v>82763</v>
       </c>
       <c r="F509" s="3">
-        <v>46031</v>
+        <v>46101</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="510">
@@ -13685,16 +13685,16 @@
         <v>46029.4149454282</v>
       </c>
       <c r="E510" s="2">
-        <v>81593</v>
+        <v>81592</v>
       </c>
       <c r="F510" s="3">
         <v>46031</v>
       </c>
       <c r="G510" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H510" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="511">
@@ -13705,16 +13705,16 @@
         <v>34</v>
       </c>
       <c r="C511" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D511" s="3">
-        <v>46038.6827563889</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E511" s="2">
-        <v>81697</v>
+        <v>81593</v>
       </c>
       <c r="F511" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>9</v>
@@ -13737,16 +13737,16 @@
         <v>46038.6827563889</v>
       </c>
       <c r="E512" s="2">
-        <v>81735</v>
+        <v>81697</v>
       </c>
       <c r="F512" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G512" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="513">
@@ -13757,42 +13757,42 @@
         <v>34</v>
       </c>
       <c r="C513" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D513" s="3">
-        <v>46045.4532476157</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E513" s="2">
-        <v>81823</v>
+        <v>81735</v>
       </c>
       <c r="F513" s="3">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="514">
       <c r="A514" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C514" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D514" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E514" s="2">
-        <v>81572</v>
+        <v>81823</v>
       </c>
       <c r="F514" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G514" s="1" t="s">
         <v>9</v>
@@ -13815,7 +13815,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E515" s="2">
-        <v>81573</v>
+        <v>81572</v>
       </c>
       <c r="F515" s="3">
         <v>46031</v>
@@ -13841,7 +13841,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E516" s="2">
-        <v>81579</v>
+        <v>81573</v>
       </c>
       <c r="F516" s="3">
         <v>46031</v>
@@ -13867,7 +13867,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E517" s="2">
-        <v>81580</v>
+        <v>81579</v>
       </c>
       <c r="F517" s="3">
         <v>46031</v>
@@ -13893,7 +13893,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E518" s="2">
-        <v>81581</v>
+        <v>81580</v>
       </c>
       <c r="F518" s="3">
         <v>46031</v>
@@ -13919,7 +13919,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E519" s="2">
-        <v>81582</v>
+        <v>81581</v>
       </c>
       <c r="F519" s="3">
         <v>46031</v>
@@ -13945,7 +13945,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E520" s="2">
-        <v>81583</v>
+        <v>81582</v>
       </c>
       <c r="F520" s="3">
         <v>46031</v>
@@ -13965,16 +13965,16 @@
         <v>35</v>
       </c>
       <c r="C521" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D521" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E521" s="2">
-        <v>81667</v>
+        <v>81583</v>
       </c>
       <c r="F521" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G521" s="1" t="s">
         <v>9</v>
@@ -13997,7 +13997,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E522" s="2">
-        <v>81668</v>
+        <v>81667</v>
       </c>
       <c r="F522" s="3">
         <v>46037</v>
@@ -14023,10 +14023,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E523" s="2">
-        <v>81674</v>
+        <v>81668</v>
       </c>
       <c r="F523" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>9</v>
@@ -14049,7 +14049,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E524" s="2">
-        <v>81675</v>
+        <v>81674</v>
       </c>
       <c r="F524" s="3">
         <v>46038</v>
@@ -14075,7 +14075,7 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E525" s="2">
-        <v>81677</v>
+        <v>81675</v>
       </c>
       <c r="F525" s="3">
         <v>46038</v>
@@ -14095,16 +14095,16 @@
         <v>35</v>
       </c>
       <c r="C526" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D526" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E526" s="2">
-        <v>81739</v>
+        <v>81677</v>
       </c>
       <c r="F526" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G526" s="1" t="s">
         <v>9</v>
@@ -14127,7 +14127,7 @@
         <v>46041.6133887269</v>
       </c>
       <c r="E527" s="2">
-        <v>81741</v>
+        <v>81739</v>
       </c>
       <c r="F527" s="3">
         <v>46041</v>
@@ -14147,16 +14147,16 @@
         <v>35</v>
       </c>
       <c r="C528" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D528" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E528" s="2">
-        <v>81854</v>
+        <v>81741</v>
       </c>
       <c r="F528" s="3">
-        <v>46048</v>
+        <v>46041</v>
       </c>
       <c r="G528" s="1" t="s">
         <v>9</v>
@@ -14179,7 +14179,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E529" s="2">
-        <v>81855</v>
+        <v>81854</v>
       </c>
       <c r="F529" s="3">
         <v>46048</v>
@@ -14205,10 +14205,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E530" s="2">
-        <v>81858</v>
+        <v>81855</v>
       </c>
       <c r="F530" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>9</v>
@@ -14231,7 +14231,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E531" s="2">
-        <v>81859</v>
+        <v>81858</v>
       </c>
       <c r="F531" s="3">
         <v>46049</v>
@@ -14257,7 +14257,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E532" s="2">
-        <v>81862</v>
+        <v>81859</v>
       </c>
       <c r="F532" s="3">
         <v>46049</v>
@@ -14283,7 +14283,7 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E533" s="2">
-        <v>81863</v>
+        <v>81862</v>
       </c>
       <c r="F533" s="3">
         <v>46049</v>
@@ -14303,16 +14303,16 @@
         <v>35</v>
       </c>
       <c r="C534" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D534" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E534" s="2">
-        <v>81958</v>
+        <v>81863</v>
       </c>
       <c r="F534" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G534" s="1" t="s">
         <v>9</v>
@@ -14335,7 +14335,7 @@
         <v>46055.5924236111</v>
       </c>
       <c r="E535" s="2">
-        <v>81965</v>
+        <v>81958</v>
       </c>
       <c r="F535" s="3">
         <v>46055</v>
@@ -14355,16 +14355,16 @@
         <v>35</v>
       </c>
       <c r="C536" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D536" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E536" s="2">
-        <v>82085</v>
+        <v>81965</v>
       </c>
       <c r="F536" s="3">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="G536" s="1" t="s">
         <v>9</v>
@@ -14387,7 +14387,7 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E537" s="2">
-        <v>82086</v>
+        <v>82085</v>
       </c>
       <c r="F537" s="3">
         <v>46063</v>
@@ -14413,10 +14413,10 @@
         <v>46063.5923590625</v>
       </c>
       <c r="E538" s="2">
-        <v>82126</v>
+        <v>82086</v>
       </c>
       <c r="F538" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G538" s="1" t="s">
         <v>9</v>
@@ -14433,16 +14433,16 @@
         <v>35</v>
       </c>
       <c r="C539" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D539" s="3">
-        <v>46064.5127051505</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E539" s="2">
-        <v>82268</v>
+        <v>82126</v>
       </c>
       <c r="F539" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G539" s="1" t="s">
         <v>9</v>
@@ -14459,16 +14459,16 @@
         <v>35</v>
       </c>
       <c r="C540" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D540" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E540" s="2">
-        <v>82142</v>
+        <v>82268</v>
       </c>
       <c r="F540" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G540" s="1" t="s">
         <v>9</v>
@@ -14491,7 +14491,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E541" s="2">
-        <v>82143</v>
+        <v>82142</v>
       </c>
       <c r="F541" s="3">
         <v>46065</v>
@@ -14517,7 +14517,7 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E542" s="2">
-        <v>82144</v>
+        <v>82143</v>
       </c>
       <c r="F542" s="3">
         <v>46065</v>
@@ -14543,10 +14543,10 @@
         <v>46065.6275788773</v>
       </c>
       <c r="E543" s="2">
-        <v>82166</v>
+        <v>82144</v>
       </c>
       <c r="F543" s="3">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="G543" s="1" t="s">
         <v>9</v>
@@ -14563,16 +14563,16 @@
         <v>35</v>
       </c>
       <c r="C544" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D544" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E544" s="2">
-        <v>82262</v>
+        <v>82166</v>
       </c>
       <c r="F544" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G544" s="1" t="s">
         <v>9</v>
@@ -14595,7 +14595,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E545" s="2">
-        <v>82265</v>
+        <v>82262</v>
       </c>
       <c r="F545" s="3">
         <v>46077</v>
@@ -14621,7 +14621,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E546" s="2">
-        <v>82281</v>
+        <v>82265</v>
       </c>
       <c r="F546" s="3">
         <v>46077</v>
@@ -14647,7 +14647,7 @@
         <v>46077.406463831</v>
       </c>
       <c r="E547" s="2">
-        <v>82282</v>
+        <v>82281</v>
       </c>
       <c r="F547" s="3">
         <v>46077</v>
@@ -14667,16 +14667,16 @@
         <v>35</v>
       </c>
       <c r="C548" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D548" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E548" s="2">
-        <v>82340</v>
+        <v>82282</v>
       </c>
       <c r="F548" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G548" s="1" t="s">
         <v>9</v>
@@ -14693,16 +14693,16 @@
         <v>35</v>
       </c>
       <c r="C549" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D549" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E549" s="2">
-        <v>82399</v>
+        <v>82340</v>
       </c>
       <c r="F549" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="G549" s="1" t="s">
         <v>9</v>
@@ -14725,7 +14725,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E550" s="2">
-        <v>82400</v>
+        <v>82399</v>
       </c>
       <c r="F550" s="3">
         <v>46083</v>
@@ -14751,7 +14751,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E551" s="2">
-        <v>82401</v>
+        <v>82400</v>
       </c>
       <c r="F551" s="3">
         <v>46083</v>
@@ -14777,10 +14777,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E552" s="2">
-        <v>82412</v>
+        <v>82401</v>
       </c>
       <c r="F552" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G552" s="1" t="s">
         <v>9</v>
@@ -14803,7 +14803,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E553" s="2">
-        <v>82415</v>
+        <v>82412</v>
       </c>
       <c r="F553" s="3">
         <v>46084</v>
@@ -14823,16 +14823,16 @@
         <v>35</v>
       </c>
       <c r="C554" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D554" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E554" s="2">
-        <v>82571</v>
+        <v>82415</v>
       </c>
       <c r="F554" s="3">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="G554" s="1" t="s">
         <v>9</v>
@@ -14855,7 +14855,7 @@
         <v>46086.6312882639</v>
       </c>
       <c r="E555" s="2">
-        <v>82572</v>
+        <v>82571</v>
       </c>
       <c r="F555" s="3">
         <v>46093</v>
@@ -14875,16 +14875,16 @@
         <v>35</v>
       </c>
       <c r="C556" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D556" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E556" s="2">
-        <v>82630</v>
+        <v>82572</v>
       </c>
       <c r="F556" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G556" s="1" t="s">
         <v>9</v>
@@ -14907,7 +14907,7 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E557" s="2">
-        <v>82631</v>
+        <v>82630</v>
       </c>
       <c r="F557" s="3">
         <v>46094</v>
@@ -14933,7 +14933,7 @@
         <v>46094.4745190394</v>
       </c>
       <c r="E558" s="2">
-        <v>82632</v>
+        <v>82631</v>
       </c>
       <c r="F558" s="3">
         <v>46094</v>
@@ -14953,16 +14953,16 @@
         <v>35</v>
       </c>
       <c r="C559" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D559" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E559" s="2">
-        <v>82653</v>
+        <v>82632</v>
       </c>
       <c r="F559" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G559" s="1" t="s">
         <v>9</v>
@@ -14985,7 +14985,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E560" s="2">
-        <v>82665</v>
+        <v>82653</v>
       </c>
       <c r="F560" s="3">
         <v>46097</v>
@@ -15011,7 +15011,7 @@
         <v>46097.4499278356</v>
       </c>
       <c r="E561" s="2">
-        <v>82668</v>
+        <v>82665</v>
       </c>
       <c r="F561" s="3">
         <v>46097</v>
@@ -15031,16 +15031,16 @@
         <v>35</v>
       </c>
       <c r="C562" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D562" s="3">
-        <v>46098.6661386574</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E562" s="2">
-        <v>82696</v>
+        <v>82668</v>
       </c>
       <c r="F562" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G562" s="1" t="s">
         <v>9</v>
@@ -15063,10 +15063,10 @@
         <v>46098.6661386574</v>
       </c>
       <c r="E563" s="2">
-        <v>82704</v>
+        <v>82696</v>
       </c>
       <c r="F563" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G563" s="1" t="s">
         <v>9</v>
@@ -15077,22 +15077,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="564">
       <c r="A564" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C564" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D564" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E564" s="2">
-        <v>82311</v>
+        <v>82704</v>
       </c>
       <c r="F564" s="3">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="G564" s="1" t="s">
         <v>9</v>
@@ -15115,7 +15115,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E565" s="2">
-        <v>82312</v>
+        <v>82311</v>
       </c>
       <c r="F565" s="3">
         <v>46078</v>
@@ -15141,7 +15141,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E566" s="2">
-        <v>82313</v>
+        <v>82312</v>
       </c>
       <c r="F566" s="3">
         <v>46078</v>
@@ -15167,7 +15167,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E567" s="2">
-        <v>82314</v>
+        <v>82313</v>
       </c>
       <c r="F567" s="3">
         <v>46078</v>
@@ -15193,10 +15193,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E568" s="2">
-        <v>82346</v>
+        <v>82314</v>
       </c>
       <c r="F568" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G568" s="1" t="s">
         <v>9</v>
@@ -15219,7 +15219,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E569" s="2">
-        <v>82361</v>
+        <v>82346</v>
       </c>
       <c r="F569" s="3">
         <v>46080</v>
@@ -15245,10 +15245,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E570" s="2">
-        <v>82385</v>
+        <v>82361</v>
       </c>
       <c r="F570" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G570" s="1" t="s">
         <v>9</v>
@@ -15271,7 +15271,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E571" s="2">
-        <v>82391</v>
+        <v>82385</v>
       </c>
       <c r="F571" s="3">
         <v>46083</v>
@@ -15297,7 +15297,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E572" s="2">
-        <v>82392</v>
+        <v>82391</v>
       </c>
       <c r="F572" s="3">
         <v>46083</v>
@@ -15317,16 +15317,16 @@
         <v>36</v>
       </c>
       <c r="C573" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D573" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E573" s="2">
-        <v>82691</v>
+        <v>82392</v>
       </c>
       <c r="F573" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G573" s="1" t="s">
         <v>9</v>
@@ -15349,7 +15349,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E574" s="2">
-        <v>82692</v>
+        <v>82691</v>
       </c>
       <c r="F574" s="3">
         <v>46098</v>
@@ -15375,7 +15375,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E575" s="2">
-        <v>82699</v>
+        <v>82692</v>
       </c>
       <c r="F575" s="3">
         <v>46098</v>
@@ -15401,10 +15401,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E576" s="2">
-        <v>82716</v>
+        <v>82699</v>
       </c>
       <c r="F576" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G576" s="1" t="s">
         <v>9</v>
@@ -15427,7 +15427,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E577" s="2">
-        <v>82717</v>
+        <v>82716</v>
       </c>
       <c r="F577" s="3">
         <v>46099</v>
@@ -15453,10 +15453,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E578" s="2">
-        <v>82786</v>
+        <v>82717</v>
       </c>
       <c r="F578" s="3">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="G578" s="1" t="s">
         <v>9</v>
@@ -15473,13 +15473,13 @@
         <v>36</v>
       </c>
       <c r="C579" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D579" s="3">
-        <v>46104.452366169</v>
+        <v>46097.4682502893</v>
       </c>
       <c r="E579" s="2">
-        <v>82780</v>
+        <v>82786</v>
       </c>
       <c r="F579" s="3">
         <v>46104</v>
@@ -15505,7 +15505,7 @@
         <v>46104.452366169</v>
       </c>
       <c r="E580" s="2">
-        <v>82784</v>
+        <v>82780</v>
       </c>
       <c r="F580" s="3">
         <v>46104</v>
@@ -15531,7 +15531,7 @@
         <v>46104.452366169</v>
       </c>
       <c r="E581" s="2">
-        <v>82785</v>
+        <v>82784</v>
       </c>
       <c r="F581" s="3">
         <v>46104</v>
@@ -15557,10 +15557,10 @@
         <v>46104.452366169</v>
       </c>
       <c r="E582" s="2">
-        <v>82792</v>
+        <v>82785</v>
       </c>
       <c r="F582" s="3">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="G582" s="1" t="s">
         <v>9</v>
@@ -15571,22 +15571,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="583">
       <c r="A583" s="2">
-        <v>9991</v>
+        <v>2601</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C583" s="2">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="D583" s="3">
-        <v>46029.4632696412</v>
+        <v>46104.452366169</v>
       </c>
       <c r="E583" s="2">
-        <v>81495</v>
+        <v>82792</v>
       </c>
       <c r="F583" s="3">
-        <v>46029</v>
+        <v>46105</v>
       </c>
       <c r="G583" s="1" t="s">
         <v>9</v>
@@ -15597,27 +15597,79 @@
     </row>
     <row ht="12.75" customHeight="1" r="584">
       <c r="A584" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C584" s="2">
+        <v>3</v>
+      </c>
+      <c r="D584" s="3">
+        <v>46104.452366169</v>
+      </c>
+      <c r="E584" s="2">
+        <v>82810</v>
+      </c>
+      <c r="F584" s="3">
+        <v>46106</v>
+      </c>
+      <c r="G584" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H584" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="585">
+      <c r="A585" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C585" s="2">
+        <v>62</v>
+      </c>
+      <c r="D585" s="3">
+        <v>46029.4632696412</v>
+      </c>
+      <c r="E585" s="2">
+        <v>81495</v>
+      </c>
+      <c r="F585" s="3">
+        <v>46029</v>
+      </c>
+      <c r="G585" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H585" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="586">
+      <c r="A586" s="2">
         <v>9992</v>
       </c>
-      <c r="B584" s="1" t="s">
+      <c r="B586" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C584" s="2">
+      <c r="C586" s="2">
         <v>390</v>
       </c>
-      <c r="D584" s="3">
+      <c r="D586" s="3">
         <v>46038.4486541204</v>
       </c>
-      <c r="E584" s="2">
+      <c r="E586" s="2">
         <v>81684</v>
       </c>
-      <c r="F584" s="3">
+      <c r="F586" s="3">
         <v>46038</v>
       </c>
-      <c r="G584" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H584" s="1" t="s">
+      <c r="G586" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H586" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Relat_OF.xlsx
+++ b/Relat_OF.xlsx
@@ -423,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H586"/>
+  <dimension ref="A1:H590"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.7142857142857" customWidth="1" style="1"/>
@@ -2961,22 +2961,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="98">
       <c r="A98" s="2">
-        <v>2404</v>
+        <v>2317</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C98" s="2">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="D98" s="3">
-        <v>46098.4966723148</v>
+        <v>46106.4928109606</v>
       </c>
       <c r="E98" s="2">
-        <v>82685</v>
+        <v>82814</v>
       </c>
       <c r="F98" s="3">
-        <v>46098</v>
+        <v>46106</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>9</v>
@@ -2987,22 +2987,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="99">
       <c r="A99" s="2">
-        <v>2407</v>
+        <v>2404</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C99" s="2">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="D99" s="3">
-        <v>46035.4418341204</v>
+        <v>46098.4966723148</v>
       </c>
       <c r="E99" s="2">
-        <v>81606</v>
+        <v>82685</v>
       </c>
       <c r="F99" s="3">
-        <v>46035</v>
+        <v>46098</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>9</v>
@@ -3025,7 +3025,7 @@
         <v>46035.4418341204</v>
       </c>
       <c r="E100" s="2">
-        <v>81607</v>
+        <v>81606</v>
       </c>
       <c r="F100" s="3">
         <v>46035</v>
@@ -3045,16 +3045,16 @@
         <v>19</v>
       </c>
       <c r="C101" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D101" s="3">
-        <v>46048.4246969907</v>
+        <v>46035.4418341204</v>
       </c>
       <c r="E101" s="2">
-        <v>81847</v>
+        <v>81607</v>
       </c>
       <c r="F101" s="3">
-        <v>46048</v>
+        <v>46035</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>9</v>
@@ -3077,7 +3077,7 @@
         <v>46048.4246969907</v>
       </c>
       <c r="E102" s="2">
-        <v>81848</v>
+        <v>81847</v>
       </c>
       <c r="F102" s="3">
         <v>46048</v>
@@ -3103,7 +3103,7 @@
         <v>46048.4246969907</v>
       </c>
       <c r="E103" s="2">
-        <v>81849</v>
+        <v>81848</v>
       </c>
       <c r="F103" s="3">
         <v>46048</v>
@@ -3129,7 +3129,7 @@
         <v>46048.4246969907</v>
       </c>
       <c r="E104" s="2">
-        <v>81850</v>
+        <v>81849</v>
       </c>
       <c r="F104" s="3">
         <v>46048</v>
@@ -3149,16 +3149,16 @@
         <v>19</v>
       </c>
       <c r="C105" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D105" s="3">
-        <v>46055.6013222338</v>
+        <v>46048.4246969907</v>
       </c>
       <c r="E105" s="2">
-        <v>81962</v>
+        <v>81850</v>
       </c>
       <c r="F105" s="3">
-        <v>46055</v>
+        <v>46048</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>9</v>
@@ -3181,7 +3181,7 @@
         <v>46055.6013222338</v>
       </c>
       <c r="E106" s="2">
-        <v>81963</v>
+        <v>81962</v>
       </c>
       <c r="F106" s="3">
         <v>46055</v>
@@ -3201,16 +3201,16 @@
         <v>19</v>
       </c>
       <c r="C107" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D107" s="3">
-        <v>46072.5914714352</v>
+        <v>46055.6013222338</v>
       </c>
       <c r="E107" s="2">
-        <v>82207</v>
+        <v>81963</v>
       </c>
       <c r="F107" s="3">
-        <v>46072</v>
+        <v>46055</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>9</v>
@@ -3233,7 +3233,7 @@
         <v>46072.5914714352</v>
       </c>
       <c r="E108" s="2">
-        <v>82209</v>
+        <v>82207</v>
       </c>
       <c r="F108" s="3">
         <v>46072</v>
@@ -3259,7 +3259,7 @@
         <v>46072.5914714352</v>
       </c>
       <c r="E109" s="2">
-        <v>82210</v>
+        <v>82209</v>
       </c>
       <c r="F109" s="3">
         <v>46072</v>
@@ -3285,7 +3285,7 @@
         <v>46072.5914714352</v>
       </c>
       <c r="E110" s="2">
-        <v>82213</v>
+        <v>82210</v>
       </c>
       <c r="F110" s="3">
         <v>46072</v>
@@ -3311,10 +3311,10 @@
         <v>46072.5914714352</v>
       </c>
       <c r="E111" s="2">
-        <v>82227</v>
+        <v>82213</v>
       </c>
       <c r="F111" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>9</v>
@@ -3337,7 +3337,7 @@
         <v>46072.5914714352</v>
       </c>
       <c r="E112" s="2">
-        <v>82228</v>
+        <v>82227</v>
       </c>
       <c r="F112" s="3">
         <v>46073</v>
@@ -3357,13 +3357,13 @@
         <v>19</v>
       </c>
       <c r="C113" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D113" s="3">
-        <v>46073.7174898611</v>
+        <v>46072.5914714352</v>
       </c>
       <c r="E113" s="2">
-        <v>82252</v>
+        <v>82228</v>
       </c>
       <c r="F113" s="3">
         <v>46073</v>
@@ -3389,10 +3389,10 @@
         <v>46073.7174898611</v>
       </c>
       <c r="E114" s="2">
-        <v>82256</v>
+        <v>82252</v>
       </c>
       <c r="F114" s="3">
-        <v>46076</v>
+        <v>46073</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>9</v>
@@ -3409,16 +3409,16 @@
         <v>19</v>
       </c>
       <c r="C115" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D115" s="3">
-        <v>46080.46293125</v>
+        <v>46073.7174898611</v>
       </c>
       <c r="E115" s="2">
-        <v>82359</v>
+        <v>82256</v>
       </c>
       <c r="F115" s="3">
-        <v>46080</v>
+        <v>46076</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>9</v>
@@ -3441,7 +3441,7 @@
         <v>46080.46293125</v>
       </c>
       <c r="E116" s="2">
-        <v>82360</v>
+        <v>82359</v>
       </c>
       <c r="F116" s="3">
         <v>46080</v>
@@ -3467,7 +3467,7 @@
         <v>46080.46293125</v>
       </c>
       <c r="E117" s="2">
-        <v>82376</v>
+        <v>82360</v>
       </c>
       <c r="F117" s="3">
         <v>46080</v>
@@ -3487,16 +3487,16 @@
         <v>19</v>
       </c>
       <c r="C118" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D118" s="3">
-        <v>46087.643003044</v>
+        <v>46080.46293125</v>
       </c>
       <c r="E118" s="2">
-        <v>82489</v>
+        <v>82376</v>
       </c>
       <c r="F118" s="3">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>9</v>
@@ -3519,10 +3519,10 @@
         <v>46087.643003044</v>
       </c>
       <c r="E119" s="2">
-        <v>82496</v>
+        <v>82489</v>
       </c>
       <c r="F119" s="3">
-        <v>46090</v>
+        <v>46087</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>9</v>
@@ -3545,7 +3545,7 @@
         <v>46087.643003044</v>
       </c>
       <c r="E120" s="2">
-        <v>82497</v>
+        <v>82496</v>
       </c>
       <c r="F120" s="3">
         <v>46090</v>
@@ -3565,16 +3565,16 @@
         <v>19</v>
       </c>
       <c r="C121" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D121" s="3">
-        <v>46104.4566862384</v>
+        <v>46087.643003044</v>
       </c>
       <c r="E121" s="2">
-        <v>82781</v>
+        <v>82497</v>
       </c>
       <c r="F121" s="3">
-        <v>46104</v>
+        <v>46090</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>9</v>
@@ -3597,7 +3597,7 @@
         <v>46104.4566862384</v>
       </c>
       <c r="E122" s="2">
-        <v>82782</v>
+        <v>82781</v>
       </c>
       <c r="F122" s="3">
         <v>46104</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="123">
       <c r="A123" s="2">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C123" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D123" s="3">
-        <v>46014.6980340162</v>
+        <v>46104.4566862384</v>
       </c>
       <c r="E123" s="2">
-        <v>81460</v>
+        <v>82782</v>
       </c>
       <c r="F123" s="3">
-        <v>46027</v>
+        <v>46104</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>9</v>
@@ -3649,7 +3649,7 @@
         <v>46014.6980340162</v>
       </c>
       <c r="E124" s="2">
-        <v>81461</v>
+        <v>81460</v>
       </c>
       <c r="F124" s="3">
         <v>46027</v>
@@ -3675,7 +3675,7 @@
         <v>46014.6980340162</v>
       </c>
       <c r="E125" s="2">
-        <v>81463</v>
+        <v>81461</v>
       </c>
       <c r="F125" s="3">
         <v>46027</v>
@@ -3695,16 +3695,16 @@
         <v>20</v>
       </c>
       <c r="C126" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D126" s="3">
-        <v>46030.4707423958</v>
+        <v>46014.6980340162</v>
       </c>
       <c r="E126" s="2">
-        <v>81542</v>
+        <v>81463</v>
       </c>
       <c r="F126" s="3">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>9</v>
@@ -3727,7 +3727,7 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E127" s="2">
-        <v>81548</v>
+        <v>81542</v>
       </c>
       <c r="F127" s="3">
         <v>46030</v>
@@ -3753,7 +3753,7 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E128" s="2">
-        <v>81549</v>
+        <v>81548</v>
       </c>
       <c r="F128" s="3">
         <v>46030</v>
@@ -3779,10 +3779,10 @@
         <v>46030.4707423958</v>
       </c>
       <c r="E129" s="2">
-        <v>81569</v>
+        <v>81549</v>
       </c>
       <c r="F129" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>9</v>
@@ -3799,16 +3799,16 @@
         <v>20</v>
       </c>
       <c r="C130" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D130" s="3">
-        <v>46037.6468124884</v>
+        <v>46030.4707423958</v>
       </c>
       <c r="E130" s="2">
-        <v>81669</v>
+        <v>81569</v>
       </c>
       <c r="F130" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>9</v>
@@ -3831,7 +3831,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E131" s="2">
-        <v>81670</v>
+        <v>81669</v>
       </c>
       <c r="F131" s="3">
         <v>46037</v>
@@ -3857,10 +3857,10 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E132" s="2">
-        <v>81673</v>
+        <v>81670</v>
       </c>
       <c r="F132" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>9</v>
@@ -3883,7 +3883,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E133" s="2">
-        <v>81682</v>
+        <v>81673</v>
       </c>
       <c r="F133" s="3">
         <v>46038</v>
@@ -3909,7 +3909,7 @@
         <v>46037.6468124884</v>
       </c>
       <c r="E134" s="2">
-        <v>81689</v>
+        <v>81682</v>
       </c>
       <c r="F134" s="3">
         <v>46038</v>
@@ -3929,16 +3929,16 @@
         <v>20</v>
       </c>
       <c r="C135" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D135" s="3">
-        <v>46038.5944713773</v>
+        <v>46037.6468124884</v>
       </c>
       <c r="E135" s="2">
-        <v>81707</v>
+        <v>81689</v>
       </c>
       <c r="F135" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>9</v>
@@ -3955,16 +3955,16 @@
         <v>20</v>
       </c>
       <c r="C136" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D136" s="3">
-        <v>46049.490160081</v>
+        <v>46038.5944713773</v>
       </c>
       <c r="E136" s="2">
-        <v>81866</v>
+        <v>81707</v>
       </c>
       <c r="F136" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>9</v>
@@ -3987,7 +3987,7 @@
         <v>46049.490160081</v>
       </c>
       <c r="E137" s="2">
-        <v>81867</v>
+        <v>81866</v>
       </c>
       <c r="F137" s="3">
         <v>46049</v>
@@ -4013,7 +4013,7 @@
         <v>46049.490160081</v>
       </c>
       <c r="E138" s="2">
-        <v>81871</v>
+        <v>81867</v>
       </c>
       <c r="F138" s="3">
         <v>46049</v>
@@ -4039,10 +4039,10 @@
         <v>46049.490160081</v>
       </c>
       <c r="E139" s="2">
-        <v>81882</v>
+        <v>81871</v>
       </c>
       <c r="F139" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>9</v>
@@ -4059,16 +4059,16 @@
         <v>20</v>
       </c>
       <c r="C140" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D140" s="3">
-        <v>46051.4127791667</v>
+        <v>46049.490160081</v>
       </c>
       <c r="E140" s="2">
-        <v>81922</v>
+        <v>81882</v>
       </c>
       <c r="F140" s="3">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>9</v>
@@ -4085,16 +4085,16 @@
         <v>20</v>
       </c>
       <c r="C141" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D141" s="3">
-        <v>46056.7141110995</v>
+        <v>46051.4127791667</v>
       </c>
       <c r="E141" s="2">
-        <v>81972</v>
+        <v>81922</v>
       </c>
       <c r="F141" s="3">
-        <v>46056</v>
+        <v>46051</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>9</v>
@@ -4117,7 +4117,7 @@
         <v>46056.7141110995</v>
       </c>
       <c r="E142" s="2">
-        <v>81973</v>
+        <v>81972</v>
       </c>
       <c r="F142" s="3">
         <v>46056</v>
@@ -4143,10 +4143,10 @@
         <v>46056.7141110995</v>
       </c>
       <c r="E143" s="2">
-        <v>81993</v>
+        <v>81973</v>
       </c>
       <c r="F143" s="3">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>9</v>
@@ -4163,16 +4163,16 @@
         <v>20</v>
       </c>
       <c r="C144" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D144" s="3">
-        <v>46063.7282468519</v>
+        <v>46056.7141110995</v>
       </c>
       <c r="E144" s="2">
-        <v>82090</v>
+        <v>81993</v>
       </c>
       <c r="F144" s="3">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>9</v>
@@ -4195,7 +4195,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E145" s="2">
-        <v>82093</v>
+        <v>82090</v>
       </c>
       <c r="F145" s="3">
         <v>46063</v>
@@ -4221,10 +4221,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E146" s="2">
-        <v>82094</v>
+        <v>82093</v>
       </c>
       <c r="F146" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>9</v>
@@ -4247,7 +4247,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E147" s="2">
-        <v>82098</v>
+        <v>82094</v>
       </c>
       <c r="F147" s="3">
         <v>46064</v>
@@ -4273,7 +4273,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E148" s="2">
-        <v>82119</v>
+        <v>82098</v>
       </c>
       <c r="F148" s="3">
         <v>46064</v>
@@ -4299,7 +4299,7 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E149" s="2">
-        <v>82120</v>
+        <v>82119</v>
       </c>
       <c r="F149" s="3">
         <v>46064</v>
@@ -4325,10 +4325,10 @@
         <v>46063.7282468519</v>
       </c>
       <c r="E150" s="2">
-        <v>82131</v>
+        <v>82120</v>
       </c>
       <c r="F150" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>9</v>
@@ -4345,16 +4345,16 @@
         <v>20</v>
       </c>
       <c r="C151" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D151" s="3">
-        <v>46078.6817048032</v>
+        <v>46063.7282468519</v>
       </c>
       <c r="E151" s="2">
-        <v>82316</v>
+        <v>82131</v>
       </c>
       <c r="F151" s="3">
-        <v>46078</v>
+        <v>46065</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>9</v>
@@ -4377,10 +4377,10 @@
         <v>46078.6817048032</v>
       </c>
       <c r="E152" s="2">
-        <v>82325</v>
+        <v>82316</v>
       </c>
       <c r="F152" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>9</v>
@@ -4403,7 +4403,7 @@
         <v>46078.6817048032</v>
       </c>
       <c r="E153" s="2">
-        <v>82327</v>
+        <v>82325</v>
       </c>
       <c r="F153" s="3">
         <v>46079</v>
@@ -4423,16 +4423,16 @@
         <v>20</v>
       </c>
       <c r="C154" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D154" s="3">
-        <v>46086.632572419</v>
+        <v>46078.6817048032</v>
       </c>
       <c r="E154" s="2">
-        <v>82471</v>
+        <v>82327</v>
       </c>
       <c r="F154" s="3">
-        <v>46086</v>
+        <v>46079</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>9</v>
@@ -4455,10 +4455,10 @@
         <v>46086.632572419</v>
       </c>
       <c r="E155" s="2">
-        <v>82476</v>
+        <v>82471</v>
       </c>
       <c r="F155" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>9</v>
@@ -4475,16 +4475,16 @@
         <v>20</v>
       </c>
       <c r="C156" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D156" s="3">
-        <v>46094.4767297338</v>
+        <v>46086.632572419</v>
       </c>
       <c r="E156" s="2">
-        <v>82634</v>
+        <v>82476</v>
       </c>
       <c r="F156" s="3">
-        <v>46094</v>
+        <v>46087</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>9</v>
@@ -4507,7 +4507,7 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E157" s="2">
-        <v>82635</v>
+        <v>82634</v>
       </c>
       <c r="F157" s="3">
         <v>46094</v>
@@ -4533,10 +4533,10 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E158" s="2">
-        <v>82679</v>
+        <v>82635</v>
       </c>
       <c r="F158" s="3">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>9</v>
@@ -4559,7 +4559,7 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E159" s="2">
-        <v>82680</v>
+        <v>82679</v>
       </c>
       <c r="F159" s="3">
         <v>46098</v>
@@ -4585,7 +4585,7 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E160" s="2">
-        <v>82681</v>
+        <v>82680</v>
       </c>
       <c r="F160" s="3">
         <v>46098</v>
@@ -4611,7 +4611,7 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E161" s="2">
-        <v>82698</v>
+        <v>82681</v>
       </c>
       <c r="F161" s="3">
         <v>46098</v>
@@ -4637,10 +4637,10 @@
         <v>46094.4767297338</v>
       </c>
       <c r="E162" s="2">
-        <v>82705</v>
+        <v>82698</v>
       </c>
       <c r="F162" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>9</v>
@@ -4651,22 +4651,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="163">
       <c r="A163" s="2">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C163" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D163" s="3">
-        <v>46030.4179771875</v>
+        <v>46094.4767297338</v>
       </c>
       <c r="E163" s="2">
-        <v>81536</v>
+        <v>82705</v>
       </c>
       <c r="F163" s="3">
-        <v>46030</v>
+        <v>46099</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>9</v>
@@ -4689,7 +4689,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E164" s="2">
-        <v>81538</v>
+        <v>81536</v>
       </c>
       <c r="F164" s="3">
         <v>46030</v>
@@ -4715,7 +4715,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E165" s="2">
-        <v>81555</v>
+        <v>81538</v>
       </c>
       <c r="F165" s="3">
         <v>46030</v>
@@ -4741,7 +4741,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E166" s="2">
-        <v>81556</v>
+        <v>81555</v>
       </c>
       <c r="F166" s="3">
         <v>46030</v>
@@ -4767,7 +4767,7 @@
         <v>46030.4179771875</v>
       </c>
       <c r="E167" s="2">
-        <v>81558</v>
+        <v>81556</v>
       </c>
       <c r="F167" s="3">
         <v>46030</v>
@@ -4787,16 +4787,16 @@
         <v>21</v>
       </c>
       <c r="C168" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D168" s="3">
-        <v>46036.4079311574</v>
+        <v>46030.4179771875</v>
       </c>
       <c r="E168" s="2">
-        <v>81615</v>
+        <v>81558</v>
       </c>
       <c r="F168" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>9</v>
@@ -4819,7 +4819,7 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E169" s="2">
-        <v>81621</v>
+        <v>81615</v>
       </c>
       <c r="F169" s="3">
         <v>46036</v>
@@ -4845,10 +4845,10 @@
         <v>46036.4079311574</v>
       </c>
       <c r="E170" s="2">
-        <v>81647</v>
+        <v>81621</v>
       </c>
       <c r="F170" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>9</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="171">
       <c r="A171" s="2">
-        <v>2504</v>
+        <v>2411</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C171" s="2">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="D171" s="3">
-        <v>46027.6983957986</v>
+        <v>46036.4079311574</v>
       </c>
       <c r="E171" s="2">
-        <v>81465</v>
+        <v>81647</v>
       </c>
       <c r="F171" s="3">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>9</v>
@@ -4897,16 +4897,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E172" s="2">
-        <v>81466</v>
+        <v>81465</v>
       </c>
       <c r="F172" s="3">
         <v>46027</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="173">
@@ -4923,16 +4923,16 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E173" s="2">
-        <v>81471</v>
+        <v>81466</v>
       </c>
       <c r="F173" s="3">
         <v>46027</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="174">
@@ -4949,10 +4949,10 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E174" s="2">
-        <v>81488</v>
+        <v>81471</v>
       </c>
       <c r="F174" s="3">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>9</v>
@@ -4975,7 +4975,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E175" s="2">
-        <v>81489</v>
+        <v>81488</v>
       </c>
       <c r="F175" s="3">
         <v>46029</v>
@@ -5001,7 +5001,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E176" s="2">
-        <v>81490</v>
+        <v>81489</v>
       </c>
       <c r="F176" s="3">
         <v>46029</v>
@@ -5027,7 +5027,7 @@
         <v>46027.6983957986</v>
       </c>
       <c r="E177" s="2">
-        <v>81491</v>
+        <v>81490</v>
       </c>
       <c r="F177" s="3">
         <v>46029</v>
@@ -5047,16 +5047,16 @@
         <v>22</v>
       </c>
       <c r="C178" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D178" s="3">
-        <v>46038.4184531713</v>
+        <v>46027.6983957986</v>
       </c>
       <c r="E178" s="2">
-        <v>81688</v>
+        <v>81491</v>
       </c>
       <c r="F178" s="3">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>9</v>
@@ -5073,13 +5073,13 @@
         <v>22</v>
       </c>
       <c r="C179" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D179" s="3">
-        <v>46038.6993878241</v>
+        <v>46038.4184531713</v>
       </c>
       <c r="E179" s="2">
-        <v>81700</v>
+        <v>81688</v>
       </c>
       <c r="F179" s="3">
         <v>46038</v>
@@ -5105,7 +5105,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E180" s="2">
-        <v>81701</v>
+        <v>81700</v>
       </c>
       <c r="F180" s="3">
         <v>46038</v>
@@ -5131,7 +5131,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E181" s="2">
-        <v>81702</v>
+        <v>81701</v>
       </c>
       <c r="F181" s="3">
         <v>46038</v>
@@ -5157,7 +5157,7 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E182" s="2">
-        <v>81703</v>
+        <v>81702</v>
       </c>
       <c r="F182" s="3">
         <v>46038</v>
@@ -5183,10 +5183,10 @@
         <v>46038.6993878241</v>
       </c>
       <c r="E183" s="2">
-        <v>81734</v>
+        <v>81703</v>
       </c>
       <c r="F183" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>9</v>
@@ -5203,16 +5203,16 @@
         <v>22</v>
       </c>
       <c r="C184" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D184" s="3">
-        <v>46050.7176682523</v>
+        <v>46038.6993878241</v>
       </c>
       <c r="E184" s="2">
-        <v>81914</v>
+        <v>81734</v>
       </c>
       <c r="F184" s="3">
-        <v>46051</v>
+        <v>46041</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>9</v>
@@ -5235,7 +5235,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E185" s="2">
-        <v>81915</v>
+        <v>81914</v>
       </c>
       <c r="F185" s="3">
         <v>46051</v>
@@ -5261,7 +5261,7 @@
         <v>46050.7176682523</v>
       </c>
       <c r="E186" s="2">
-        <v>81921</v>
+        <v>81915</v>
       </c>
       <c r="F186" s="3">
         <v>46051</v>
@@ -5281,16 +5281,16 @@
         <v>22</v>
       </c>
       <c r="C187" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D187" s="3">
-        <v>46052.6247194676</v>
+        <v>46050.7176682523</v>
       </c>
       <c r="E187" s="2">
-        <v>81949</v>
+        <v>81921</v>
       </c>
       <c r="F187" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>9</v>
@@ -5313,7 +5313,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E188" s="2">
-        <v>81950</v>
+        <v>81949</v>
       </c>
       <c r="F188" s="3">
         <v>46052</v>
@@ -5339,7 +5339,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E189" s="2">
-        <v>81951</v>
+        <v>81950</v>
       </c>
       <c r="F189" s="3">
         <v>46052</v>
@@ -5365,7 +5365,7 @@
         <v>46052.6247194676</v>
       </c>
       <c r="E190" s="2">
-        <v>81953</v>
+        <v>81951</v>
       </c>
       <c r="F190" s="3">
         <v>46052</v>
@@ -5385,16 +5385,16 @@
         <v>22</v>
       </c>
       <c r="C191" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D191" s="3">
-        <v>46058.6976675694</v>
+        <v>46052.6247194676</v>
       </c>
       <c r="E191" s="2">
-        <v>82028</v>
+        <v>81953</v>
       </c>
       <c r="F191" s="3">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>9</v>
@@ -5417,7 +5417,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E192" s="2">
-        <v>82029</v>
+        <v>82028</v>
       </c>
       <c r="F192" s="3">
         <v>46058</v>
@@ -5443,10 +5443,10 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E193" s="2">
-        <v>82040</v>
+        <v>82029</v>
       </c>
       <c r="F193" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>9</v>
@@ -5469,7 +5469,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E194" s="2">
-        <v>82041</v>
+        <v>82040</v>
       </c>
       <c r="F194" s="3">
         <v>46059</v>
@@ -5495,7 +5495,7 @@
         <v>46058.6976675694</v>
       </c>
       <c r="E195" s="2">
-        <v>82051</v>
+        <v>82041</v>
       </c>
       <c r="F195" s="3">
         <v>46059</v>
@@ -5515,16 +5515,16 @@
         <v>22</v>
       </c>
       <c r="C196" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D196" s="3">
-        <v>46065.6309066782</v>
+        <v>46058.6976675694</v>
       </c>
       <c r="E196" s="2">
-        <v>82168</v>
+        <v>82051</v>
       </c>
       <c r="F196" s="3">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>9</v>
@@ -5547,16 +5547,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E197" s="2">
-        <v>82170</v>
+        <v>82168</v>
       </c>
       <c r="F197" s="3">
         <v>46066</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="198">
@@ -5573,16 +5573,16 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E198" s="2">
-        <v>82171</v>
+        <v>82170</v>
       </c>
       <c r="F198" s="3">
         <v>46066</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="199">
@@ -5599,7 +5599,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E199" s="2">
-        <v>82172</v>
+        <v>82171</v>
       </c>
       <c r="F199" s="3">
         <v>46066</v>
@@ -5625,7 +5625,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E200" s="2">
-        <v>82175</v>
+        <v>82172</v>
       </c>
       <c r="F200" s="3">
         <v>46066</v>
@@ -5651,7 +5651,7 @@
         <v>46065.6309066782</v>
       </c>
       <c r="E201" s="2">
-        <v>82176</v>
+        <v>82175</v>
       </c>
       <c r="F201" s="3">
         <v>46066</v>
@@ -5671,16 +5671,16 @@
         <v>22</v>
       </c>
       <c r="C202" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D202" s="3">
-        <v>46072.5909779051</v>
+        <v>46065.6309066782</v>
       </c>
       <c r="E202" s="2">
-        <v>82206</v>
+        <v>82176</v>
       </c>
       <c r="F202" s="3">
-        <v>46072</v>
+        <v>46066</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>9</v>
@@ -5697,16 +5697,16 @@
         <v>22</v>
       </c>
       <c r="C203" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D203" s="3">
-        <v>46077.7262228935</v>
+        <v>46072.5909779051</v>
       </c>
       <c r="E203" s="2">
-        <v>82289</v>
+        <v>82206</v>
       </c>
       <c r="F203" s="3">
-        <v>46077</v>
+        <v>46072</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>9</v>
@@ -5729,7 +5729,7 @@
         <v>46077.7262228935</v>
       </c>
       <c r="E204" s="2">
-        <v>82290</v>
+        <v>82289</v>
       </c>
       <c r="F204" s="3">
         <v>46077</v>
@@ -5749,16 +5749,16 @@
         <v>22</v>
       </c>
       <c r="C205" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D205" s="3">
-        <v>46078.6799843634</v>
+        <v>46077.7262228935</v>
       </c>
       <c r="E205" s="2">
-        <v>82318</v>
+        <v>82290</v>
       </c>
       <c r="F205" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>9</v>
@@ -5775,16 +5775,16 @@
         <v>22</v>
       </c>
       <c r="C206" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D206" s="3">
-        <v>46080.6294471412</v>
+        <v>46078.6799843634</v>
       </c>
       <c r="E206" s="2">
-        <v>82368</v>
+        <v>82318</v>
       </c>
       <c r="F206" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>9</v>
@@ -5801,16 +5801,16 @@
         <v>22</v>
       </c>
       <c r="C207" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D207" s="3">
-        <v>46084.741264838</v>
+        <v>46080.6294471412</v>
       </c>
       <c r="E207" s="2">
-        <v>82425</v>
+        <v>82368</v>
       </c>
       <c r="F207" s="3">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>9</v>
@@ -5833,7 +5833,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="E208" s="2">
-        <v>82426</v>
+        <v>82425</v>
       </c>
       <c r="F208" s="3">
         <v>46084</v>
@@ -5859,10 +5859,10 @@
         <v>46084.741264838</v>
       </c>
       <c r="E209" s="2">
-        <v>82430</v>
+        <v>82426</v>
       </c>
       <c r="F209" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>9</v>
@@ -5885,7 +5885,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="E210" s="2">
-        <v>82431</v>
+        <v>82430</v>
       </c>
       <c r="F210" s="3">
         <v>46085</v>
@@ -5905,16 +5905,16 @@
         <v>22</v>
       </c>
       <c r="C211" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D211" s="3">
-        <v>46097.4509044907</v>
+        <v>46084.741264838</v>
       </c>
       <c r="E211" s="2">
-        <v>82654</v>
+        <v>82431</v>
       </c>
       <c r="F211" s="3">
-        <v>46097</v>
+        <v>46085</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>9</v>
@@ -5937,7 +5937,7 @@
         <v>46097.4509044907</v>
       </c>
       <c r="E212" s="2">
-        <v>82660</v>
+        <v>82654</v>
       </c>
       <c r="F212" s="3">
         <v>46097</v>
@@ -5963,7 +5963,7 @@
         <v>46097.4509044907</v>
       </c>
       <c r="E213" s="2">
-        <v>82661</v>
+        <v>82660</v>
       </c>
       <c r="F213" s="3">
         <v>46097</v>
@@ -5983,16 +5983,16 @@
         <v>22</v>
       </c>
       <c r="C214" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D214" s="3">
-        <v>46098.5062577778</v>
+        <v>46097.4509044907</v>
       </c>
       <c r="E214" s="2">
-        <v>82690</v>
+        <v>82661</v>
       </c>
       <c r="F214" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>9</v>
@@ -6015,10 +6015,10 @@
         <v>46098.5062577778</v>
       </c>
       <c r="E215" s="2">
-        <v>82714</v>
+        <v>82690</v>
       </c>
       <c r="F215" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>9</v>
@@ -6035,16 +6035,16 @@
         <v>22</v>
       </c>
       <c r="C216" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D216" s="3">
-        <v>46105.7396245255</v>
+        <v>46098.5062577778</v>
       </c>
       <c r="E216" s="2">
-        <v>82799</v>
+        <v>82714</v>
       </c>
       <c r="F216" s="3">
-        <v>46105</v>
+        <v>46099</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>9</v>
@@ -6067,10 +6067,10 @@
         <v>46105.7396245255</v>
       </c>
       <c r="E217" s="2">
-        <v>82807</v>
+        <v>82799</v>
       </c>
       <c r="F217" s="3">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>9</v>
@@ -6081,22 +6081,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="218">
       <c r="A218" s="2">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C218" s="2">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D218" s="3">
-        <v>46041.6648751157</v>
+        <v>46105.7396245255</v>
       </c>
       <c r="E218" s="2">
-        <v>81743</v>
+        <v>82807</v>
       </c>
       <c r="F218" s="3">
-        <v>46041</v>
+        <v>46106</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>9</v>
@@ -6119,7 +6119,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E219" s="2">
-        <v>81744</v>
+        <v>81743</v>
       </c>
       <c r="F219" s="3">
         <v>46041</v>
@@ -6145,7 +6145,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E220" s="2">
-        <v>81745</v>
+        <v>81744</v>
       </c>
       <c r="F220" s="3">
         <v>46041</v>
@@ -6171,10 +6171,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E221" s="2">
-        <v>81746</v>
+        <v>81745</v>
       </c>
       <c r="F221" s="3">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>9</v>
@@ -6197,10 +6197,10 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E222" s="2">
-        <v>81751</v>
+        <v>81746</v>
       </c>
       <c r="F222" s="3">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>9</v>
@@ -6223,7 +6223,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E223" s="2">
-        <v>81753</v>
+        <v>81751</v>
       </c>
       <c r="F223" s="3">
         <v>46043</v>
@@ -6249,7 +6249,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E224" s="2">
-        <v>81754</v>
+        <v>81753</v>
       </c>
       <c r="F224" s="3">
         <v>46043</v>
@@ -6275,7 +6275,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E225" s="2">
-        <v>81755</v>
+        <v>81754</v>
       </c>
       <c r="F225" s="3">
         <v>46043</v>
@@ -6301,7 +6301,7 @@
         <v>46041.6648751157</v>
       </c>
       <c r="E226" s="2">
-        <v>81766</v>
+        <v>81755</v>
       </c>
       <c r="F226" s="3">
         <v>46043</v>
@@ -6321,16 +6321,16 @@
         <v>23</v>
       </c>
       <c r="C227" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D227" s="3">
-        <v>46063.7255115046</v>
+        <v>46041.6648751157</v>
       </c>
       <c r="E227" s="2">
-        <v>82088</v>
+        <v>81766</v>
       </c>
       <c r="F227" s="3">
-        <v>46063</v>
+        <v>46043</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>9</v>
@@ -6353,7 +6353,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E228" s="2">
-        <v>82089</v>
+        <v>82088</v>
       </c>
       <c r="F228" s="3">
         <v>46063</v>
@@ -6379,10 +6379,10 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E229" s="2">
-        <v>82163</v>
+        <v>82089</v>
       </c>
       <c r="F229" s="3">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>9</v>
@@ -6405,7 +6405,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E230" s="2">
-        <v>82179</v>
+        <v>82163</v>
       </c>
       <c r="F230" s="3">
         <v>46066</v>
@@ -6431,7 +6431,7 @@
         <v>46063.7255115046</v>
       </c>
       <c r="E231" s="2">
-        <v>82193</v>
+        <v>82179</v>
       </c>
       <c r="F231" s="3">
         <v>46066</v>
@@ -6451,16 +6451,16 @@
         <v>23</v>
       </c>
       <c r="C232" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D232" s="3">
-        <v>46073.714168287</v>
+        <v>46063.7255115046</v>
       </c>
       <c r="E232" s="2">
-        <v>82250</v>
+        <v>82193</v>
       </c>
       <c r="F232" s="3">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>9</v>
@@ -6483,10 +6483,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E233" s="2">
-        <v>82266</v>
+        <v>82250</v>
       </c>
       <c r="F233" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>9</v>
@@ -6509,10 +6509,10 @@
         <v>46073.714168287</v>
       </c>
       <c r="E234" s="2">
-        <v>82295</v>
+        <v>82266</v>
       </c>
       <c r="F234" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>9</v>
@@ -6535,7 +6535,7 @@
         <v>46073.714168287</v>
       </c>
       <c r="E235" s="2">
-        <v>82296</v>
+        <v>82295</v>
       </c>
       <c r="F235" s="3">
         <v>46078</v>
@@ -6561,16 +6561,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E236" s="2">
-        <v>82332</v>
+        <v>82296</v>
       </c>
       <c r="F236" s="3">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="237">
@@ -6587,16 +6587,16 @@
         <v>46073.714168287</v>
       </c>
       <c r="E237" s="2">
-        <v>82339</v>
+        <v>82332</v>
       </c>
       <c r="F237" s="3">
         <v>46079</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="238">
@@ -6607,16 +6607,16 @@
         <v>23</v>
       </c>
       <c r="C238" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D238" s="3">
-        <v>46077.4087697222</v>
+        <v>46073.714168287</v>
       </c>
       <c r="E238" s="2">
-        <v>82266</v>
+        <v>82339</v>
       </c>
       <c r="F238" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>9</v>
@@ -6639,7 +6639,7 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E239" s="2">
-        <v>82273</v>
+        <v>82266</v>
       </c>
       <c r="F239" s="3">
         <v>46077</v>
@@ -6665,10 +6665,10 @@
         <v>46077.4087697222</v>
       </c>
       <c r="E240" s="2">
-        <v>82294</v>
+        <v>82273</v>
       </c>
       <c r="F240" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>9</v>
@@ -6685,16 +6685,16 @@
         <v>23</v>
       </c>
       <c r="C241" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D241" s="3">
-        <v>46084.5060569213</v>
+        <v>46077.4087697222</v>
       </c>
       <c r="E241" s="2">
-        <v>82411</v>
+        <v>82294</v>
       </c>
       <c r="F241" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>9</v>
@@ -6717,10 +6717,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E242" s="2">
-        <v>82432</v>
+        <v>82411</v>
       </c>
       <c r="F242" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>9</v>
@@ -6743,10 +6743,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E243" s="2">
-        <v>82473</v>
+        <v>82432</v>
       </c>
       <c r="F243" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>9</v>
@@ -6769,10 +6769,10 @@
         <v>46084.5060569213</v>
       </c>
       <c r="E244" s="2">
-        <v>82474</v>
+        <v>82473</v>
       </c>
       <c r="F244" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G244" s="1" t="s">
         <v>9</v>
@@ -6789,16 +6789,16 @@
         <v>23</v>
       </c>
       <c r="C245" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D245" s="3">
-        <v>46093.5009358681</v>
+        <v>46084.5060569213</v>
       </c>
       <c r="E245" s="2">
-        <v>82594</v>
+        <v>82474</v>
       </c>
       <c r="F245" s="3">
-        <v>46093</v>
+        <v>46087</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>9</v>
@@ -6821,7 +6821,7 @@
         <v>46093.5009358681</v>
       </c>
       <c r="E246" s="2">
-        <v>82595</v>
+        <v>82594</v>
       </c>
       <c r="F246" s="3">
         <v>46093</v>
@@ -6847,10 +6847,10 @@
         <v>46093.5009358681</v>
       </c>
       <c r="E247" s="2">
-        <v>82657</v>
+        <v>82595</v>
       </c>
       <c r="F247" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>9</v>
@@ -6867,16 +6867,16 @@
         <v>23</v>
       </c>
       <c r="C248" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D248" s="3">
-        <v>46098.5034667708</v>
+        <v>46093.5009358681</v>
       </c>
       <c r="E248" s="2">
-        <v>82686</v>
+        <v>82657</v>
       </c>
       <c r="F248" s="3">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>9</v>
@@ -6899,7 +6899,7 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E249" s="2">
-        <v>82687</v>
+        <v>82686</v>
       </c>
       <c r="F249" s="3">
         <v>46098</v>
@@ -6925,10 +6925,10 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E250" s="2">
-        <v>82722</v>
+        <v>82687</v>
       </c>
       <c r="F250" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>9</v>
@@ -6951,7 +6951,7 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E251" s="2">
-        <v>82723</v>
+        <v>82722</v>
       </c>
       <c r="F251" s="3">
         <v>46099</v>
@@ -6977,10 +6977,10 @@
         <v>46098.5034667708</v>
       </c>
       <c r="E252" s="2">
-        <v>82755</v>
+        <v>82723</v>
       </c>
       <c r="F252" s="3">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>9</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="253">
       <c r="A253" s="2">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C253" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D253" s="3">
-        <v>46044.6368950926</v>
+        <v>46098.5034667708</v>
       </c>
       <c r="E253" s="2">
-        <v>81802</v>
+        <v>82755</v>
       </c>
       <c r="F253" s="3">
-        <v>46044</v>
+        <v>46101</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>9</v>
@@ -7029,7 +7029,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E254" s="2">
-        <v>81803</v>
+        <v>81802</v>
       </c>
       <c r="F254" s="3">
         <v>46044</v>
@@ -7055,7 +7055,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E255" s="2">
-        <v>81804</v>
+        <v>81803</v>
       </c>
       <c r="F255" s="3">
         <v>46044</v>
@@ -7081,7 +7081,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E256" s="2">
-        <v>81806</v>
+        <v>81804</v>
       </c>
       <c r="F256" s="3">
         <v>46044</v>
@@ -7107,7 +7107,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E257" s="2">
-        <v>81807</v>
+        <v>81806</v>
       </c>
       <c r="F257" s="3">
         <v>46044</v>
@@ -7133,10 +7133,10 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E258" s="2">
-        <v>81812</v>
+        <v>81807</v>
       </c>
       <c r="F258" s="3">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>9</v>
@@ -7159,7 +7159,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E259" s="2">
-        <v>81813</v>
+        <v>81812</v>
       </c>
       <c r="F259" s="3">
         <v>46045</v>
@@ -7185,7 +7185,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E260" s="2">
-        <v>81814</v>
+        <v>81813</v>
       </c>
       <c r="F260" s="3">
         <v>46045</v>
@@ -7211,7 +7211,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E261" s="2">
-        <v>81818</v>
+        <v>81814</v>
       </c>
       <c r="F261" s="3">
         <v>46045</v>
@@ -7237,7 +7237,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E262" s="2">
-        <v>81822</v>
+        <v>81818</v>
       </c>
       <c r="F262" s="3">
         <v>46045</v>
@@ -7263,7 +7263,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E263" s="2">
-        <v>81833</v>
+        <v>81822</v>
       </c>
       <c r="F263" s="3">
         <v>46045</v>
@@ -7289,7 +7289,7 @@
         <v>46044.6368950926</v>
       </c>
       <c r="E264" s="2">
-        <v>81841</v>
+        <v>81833</v>
       </c>
       <c r="F264" s="3">
         <v>46045</v>
@@ -7309,16 +7309,16 @@
         <v>26</v>
       </c>
       <c r="C265" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D265" s="3">
-        <v>46052.4025905208</v>
+        <v>46044.6368950926</v>
       </c>
       <c r="E265" s="2">
-        <v>81928</v>
+        <v>81841</v>
       </c>
       <c r="F265" s="3">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>9</v>
@@ -7341,7 +7341,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E266" s="2">
-        <v>81929</v>
+        <v>81928</v>
       </c>
       <c r="F266" s="3">
         <v>46052</v>
@@ -7367,7 +7367,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E267" s="2">
-        <v>81930</v>
+        <v>81929</v>
       </c>
       <c r="F267" s="3">
         <v>46052</v>
@@ -7393,7 +7393,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E268" s="2">
-        <v>81932</v>
+        <v>81930</v>
       </c>
       <c r="F268" s="3">
         <v>46052</v>
@@ -7419,7 +7419,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E269" s="2">
-        <v>81933</v>
+        <v>81932</v>
       </c>
       <c r="F269" s="3">
         <v>46052</v>
@@ -7445,7 +7445,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E270" s="2">
-        <v>81934</v>
+        <v>81933</v>
       </c>
       <c r="F270" s="3">
         <v>46052</v>
@@ -7471,7 +7471,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E271" s="2">
-        <v>81935</v>
+        <v>81934</v>
       </c>
       <c r="F271" s="3">
         <v>46052</v>
@@ -7497,7 +7497,7 @@
         <v>46052.4025905208</v>
       </c>
       <c r="E272" s="2">
-        <v>81936</v>
+        <v>81935</v>
       </c>
       <c r="F272" s="3">
         <v>46052</v>
@@ -7517,16 +7517,16 @@
         <v>26</v>
       </c>
       <c r="C273" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D273" s="3">
-        <v>46072.7468210069</v>
+        <v>46052.4025905208</v>
       </c>
       <c r="E273" s="2">
-        <v>82222</v>
+        <v>81936</v>
       </c>
       <c r="F273" s="3">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>9</v>
@@ -7549,10 +7549,10 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E274" s="2">
-        <v>82226</v>
+        <v>82222</v>
       </c>
       <c r="F274" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>9</v>
@@ -7575,7 +7575,7 @@
         <v>46072.7468210069</v>
       </c>
       <c r="E275" s="2">
-        <v>82229</v>
+        <v>82226</v>
       </c>
       <c r="F275" s="3">
         <v>46073</v>
@@ -7595,13 +7595,13 @@
         <v>26</v>
       </c>
       <c r="C276" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D276" s="3">
-        <v>46073.5838834375</v>
+        <v>46072.7468210069</v>
       </c>
       <c r="E276" s="2">
-        <v>82246</v>
+        <v>82229</v>
       </c>
       <c r="F276" s="3">
         <v>46073</v>
@@ -7621,16 +7621,16 @@
         <v>26</v>
       </c>
       <c r="C277" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D277" s="3">
-        <v>46080.6289065162</v>
+        <v>46073.5838834375</v>
       </c>
       <c r="E277" s="2">
-        <v>82387</v>
+        <v>82246</v>
       </c>
       <c r="F277" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>9</v>
@@ -7647,16 +7647,16 @@
         <v>26</v>
       </c>
       <c r="C278" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D278" s="3">
-        <v>46093.4978086806</v>
+        <v>46080.6289065162</v>
       </c>
       <c r="E278" s="2">
-        <v>82590</v>
+        <v>82387</v>
       </c>
       <c r="F278" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>9</v>
@@ -7679,16 +7679,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E279" s="2">
-        <v>82591</v>
+        <v>82590</v>
       </c>
       <c r="F279" s="3">
         <v>46093</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="280">
@@ -7705,16 +7705,16 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E280" s="2">
-        <v>82592</v>
+        <v>82591</v>
       </c>
       <c r="F280" s="3">
         <v>46093</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="281">
@@ -7731,7 +7731,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E281" s="2">
-        <v>82593</v>
+        <v>82592</v>
       </c>
       <c r="F281" s="3">
         <v>46093</v>
@@ -7757,7 +7757,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E282" s="2">
-        <v>82600</v>
+        <v>82593</v>
       </c>
       <c r="F282" s="3">
         <v>46093</v>
@@ -7783,7 +7783,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E283" s="2">
-        <v>82603</v>
+        <v>82600</v>
       </c>
       <c r="F283" s="3">
         <v>46093</v>
@@ -7809,7 +7809,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E284" s="2">
-        <v>82604</v>
+        <v>82603</v>
       </c>
       <c r="F284" s="3">
         <v>46093</v>
@@ -7835,7 +7835,7 @@
         <v>46093.4978086806</v>
       </c>
       <c r="E285" s="2">
-        <v>82605</v>
+        <v>82604</v>
       </c>
       <c r="F285" s="3">
         <v>46093</v>
@@ -7849,22 +7849,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="286">
       <c r="A286" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C286" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D286" s="3">
-        <v>46029.4161474769</v>
+        <v>46093.4978086806</v>
       </c>
       <c r="E286" s="2">
-        <v>81478</v>
+        <v>82605</v>
       </c>
       <c r="F286" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>9</v>
@@ -7875,80 +7875,80 @@
     </row>
     <row ht="12.75" customHeight="1" r="287">
       <c r="A287" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C287" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D287" s="3">
-        <v>46029.4161474769</v>
+        <v>46106.7275206944</v>
       </c>
       <c r="E287" s="2">
-        <v>81479</v>
+        <v>82819</v>
       </c>
       <c r="F287" s="3">
-        <v>46029</v>
+        <v>46106</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="288">
       <c r="A288" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C288" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D288" s="3">
-        <v>46029.4161474769</v>
+        <v>46106.7275206944</v>
       </c>
       <c r="E288" s="2">
-        <v>81480</v>
+        <v>82820</v>
       </c>
       <c r="F288" s="3">
-        <v>46029</v>
+        <v>46106</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="289">
       <c r="A289" s="2">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C289" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D289" s="3">
-        <v>46029.4161474769</v>
+        <v>46106.7275206944</v>
       </c>
       <c r="E289" s="2">
-        <v>81497</v>
+        <v>82821</v>
       </c>
       <c r="F289" s="3">
-        <v>46029</v>
+        <v>46106</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="290">
@@ -7965,7 +7965,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E290" s="2">
-        <v>81498</v>
+        <v>81478</v>
       </c>
       <c r="F290" s="3">
         <v>46029</v>
@@ -7991,7 +7991,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E291" s="2">
-        <v>81499</v>
+        <v>81479</v>
       </c>
       <c r="F291" s="3">
         <v>46029</v>
@@ -8017,7 +8017,7 @@
         <v>46029.4161474769</v>
       </c>
       <c r="E292" s="2">
-        <v>81500</v>
+        <v>81480</v>
       </c>
       <c r="F292" s="3">
         <v>46029</v>
@@ -8037,16 +8037,16 @@
         <v>26</v>
       </c>
       <c r="C293" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D293" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E293" s="2">
-        <v>81878</v>
+        <v>81497</v>
       </c>
       <c r="F293" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>9</v>
@@ -8063,16 +8063,16 @@
         <v>26</v>
       </c>
       <c r="C294" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D294" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E294" s="2">
-        <v>81879</v>
+        <v>81498</v>
       </c>
       <c r="F294" s="3">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>9</v>
@@ -8089,16 +8089,16 @@
         <v>26</v>
       </c>
       <c r="C295" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D295" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E295" s="2">
-        <v>81885</v>
+        <v>81499</v>
       </c>
       <c r="F295" s="3">
-        <v>46050</v>
+        <v>46029</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>9</v>
@@ -8115,16 +8115,16 @@
         <v>26</v>
       </c>
       <c r="C296" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D296" s="3">
-        <v>46049.6888218403</v>
+        <v>46029.4161474769</v>
       </c>
       <c r="E296" s="2">
-        <v>81886</v>
+        <v>81500</v>
       </c>
       <c r="F296" s="3">
-        <v>46050</v>
+        <v>46029</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>9</v>
@@ -8141,16 +8141,16 @@
         <v>26</v>
       </c>
       <c r="C297" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D297" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E297" s="2">
-        <v>82068</v>
+        <v>81878</v>
       </c>
       <c r="F297" s="3">
-        <v>46062</v>
+        <v>46049</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>9</v>
@@ -8167,16 +8167,16 @@
         <v>26</v>
       </c>
       <c r="C298" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D298" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E298" s="2">
-        <v>82072</v>
+        <v>81879</v>
       </c>
       <c r="F298" s="3">
-        <v>46063</v>
+        <v>46049</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>9</v>
@@ -8193,16 +8193,16 @@
         <v>26</v>
       </c>
       <c r="C299" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D299" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E299" s="2">
-        <v>82076</v>
+        <v>81885</v>
       </c>
       <c r="F299" s="3">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>9</v>
@@ -8219,16 +8219,16 @@
         <v>26</v>
       </c>
       <c r="C300" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D300" s="3">
-        <v>46062.7199601505</v>
+        <v>46049.6888218403</v>
       </c>
       <c r="E300" s="2">
-        <v>82078</v>
+        <v>81886</v>
       </c>
       <c r="F300" s="3">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>9</v>
@@ -8245,16 +8245,16 @@
         <v>26</v>
       </c>
       <c r="C301" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D301" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E301" s="2">
-        <v>82287</v>
+        <v>82068</v>
       </c>
       <c r="F301" s="3">
-        <v>46077</v>
+        <v>46062</v>
       </c>
       <c r="G301" s="1" t="s">
         <v>9</v>
@@ -8271,16 +8271,16 @@
         <v>26</v>
       </c>
       <c r="C302" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D302" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E302" s="2">
-        <v>82288</v>
+        <v>82072</v>
       </c>
       <c r="F302" s="3">
-        <v>46077</v>
+        <v>46063</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>9</v>
@@ -8297,16 +8297,16 @@
         <v>26</v>
       </c>
       <c r="C303" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D303" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E303" s="2">
-        <v>82298</v>
+        <v>82076</v>
       </c>
       <c r="F303" s="3">
-        <v>46078</v>
+        <v>46063</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>9</v>
@@ -8323,16 +8323,16 @@
         <v>26</v>
       </c>
       <c r="C304" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D304" s="3">
-        <v>46077.7216803356</v>
+        <v>46062.7199601505</v>
       </c>
       <c r="E304" s="2">
-        <v>82301</v>
+        <v>82078</v>
       </c>
       <c r="F304" s="3">
-        <v>46078</v>
+        <v>46063</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>9</v>
@@ -8355,10 +8355,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E305" s="2">
-        <v>82304</v>
+        <v>82287</v>
       </c>
       <c r="F305" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>9</v>
@@ -8381,10 +8381,10 @@
         <v>46077.7216803356</v>
       </c>
       <c r="E306" s="2">
-        <v>82308</v>
+        <v>82288</v>
       </c>
       <c r="F306" s="3">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>9</v>
@@ -8401,16 +8401,16 @@
         <v>26</v>
       </c>
       <c r="C307" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D307" s="3">
-        <v>46080.628344919</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E307" s="2">
-        <v>82373</v>
+        <v>82298</v>
       </c>
       <c r="F307" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>9</v>
@@ -8427,16 +8427,16 @@
         <v>26</v>
       </c>
       <c r="C308" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D308" s="3">
-        <v>46085.6581644213</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E308" s="2">
-        <v>82445</v>
+        <v>82301</v>
       </c>
       <c r="F308" s="3">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>9</v>
@@ -8453,16 +8453,16 @@
         <v>26</v>
       </c>
       <c r="C309" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D309" s="3">
-        <v>46085.6581644213</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E309" s="2">
-        <v>82447</v>
+        <v>82304</v>
       </c>
       <c r="F309" s="3">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>9</v>
@@ -8479,16 +8479,16 @@
         <v>26</v>
       </c>
       <c r="C310" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D310" s="3">
-        <v>46085.6581644213</v>
+        <v>46077.7216803356</v>
       </c>
       <c r="E310" s="2">
-        <v>82453</v>
+        <v>82308</v>
       </c>
       <c r="F310" s="3">
-        <v>46086</v>
+        <v>46078</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>9</v>
@@ -8505,16 +8505,16 @@
         <v>26</v>
       </c>
       <c r="C311" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D311" s="3">
-        <v>46085.6581644213</v>
+        <v>46080.628344919</v>
       </c>
       <c r="E311" s="2">
-        <v>82468</v>
+        <v>82373</v>
       </c>
       <c r="F311" s="3">
-        <v>46086</v>
+        <v>46080</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>9</v>
@@ -8531,16 +8531,16 @@
         <v>26</v>
       </c>
       <c r="C312" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D312" s="3">
-        <v>46098.6669450579</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E312" s="2">
-        <v>82697</v>
+        <v>82445</v>
       </c>
       <c r="F312" s="3">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>9</v>
@@ -8557,16 +8557,16 @@
         <v>26</v>
       </c>
       <c r="C313" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D313" s="3">
-        <v>46098.6669450579</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E313" s="2">
-        <v>82706</v>
+        <v>82447</v>
       </c>
       <c r="F313" s="3">
-        <v>46099</v>
+        <v>46085</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>9</v>
@@ -8583,16 +8583,16 @@
         <v>26</v>
       </c>
       <c r="C314" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D314" s="3">
-        <v>46098.6669450579</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E314" s="2">
-        <v>82707</v>
+        <v>82453</v>
       </c>
       <c r="F314" s="3">
-        <v>46099</v>
+        <v>46086</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>9</v>
@@ -8609,16 +8609,16 @@
         <v>26</v>
       </c>
       <c r="C315" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D315" s="3">
-        <v>46098.6669450579</v>
+        <v>46085.6581644213</v>
       </c>
       <c r="E315" s="2">
-        <v>82708</v>
+        <v>82468</v>
       </c>
       <c r="F315" s="3">
-        <v>46099</v>
+        <v>46086</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>9</v>
@@ -8641,10 +8641,10 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E316" s="2">
-        <v>82709</v>
+        <v>82697</v>
       </c>
       <c r="F316" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>9</v>
@@ -8667,7 +8667,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E317" s="2">
-        <v>82712</v>
+        <v>82706</v>
       </c>
       <c r="F317" s="3">
         <v>46099</v>
@@ -8693,7 +8693,7 @@
         <v>46098.6669450579</v>
       </c>
       <c r="E318" s="2">
-        <v>82713</v>
+        <v>82707</v>
       </c>
       <c r="F318" s="3">
         <v>46099</v>
@@ -8713,16 +8713,16 @@
         <v>26</v>
       </c>
       <c r="C319" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D319" s="3">
-        <v>46101.4050215162</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E319" s="2">
-        <v>82756</v>
+        <v>82708</v>
       </c>
       <c r="F319" s="3">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>9</v>
@@ -8739,16 +8739,16 @@
         <v>26</v>
       </c>
       <c r="C320" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D320" s="3">
-        <v>46104.4364179167</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E320" s="2">
-        <v>82777</v>
+        <v>82709</v>
       </c>
       <c r="F320" s="3">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>9</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="321">
       <c r="A321" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C321" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D321" s="3">
-        <v>46029.6400966782</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E321" s="2">
-        <v>81506</v>
+        <v>82712</v>
       </c>
       <c r="F321" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>9</v>
@@ -8785,22 +8785,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="322">
       <c r="A322" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C322" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D322" s="3">
-        <v>46029.6400966782</v>
+        <v>46098.6669450579</v>
       </c>
       <c r="E322" s="2">
-        <v>81507</v>
+        <v>82713</v>
       </c>
       <c r="F322" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>9</v>
@@ -8811,22 +8811,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="323">
       <c r="A323" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C323" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D323" s="3">
-        <v>46029.6400966782</v>
+        <v>46101.4050215162</v>
       </c>
       <c r="E323" s="2">
-        <v>81524</v>
+        <v>82756</v>
       </c>
       <c r="F323" s="3">
-        <v>46030</v>
+        <v>46101</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>9</v>
@@ -8837,22 +8837,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="324">
       <c r="A324" s="2">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C324" s="2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D324" s="3">
-        <v>46029.6400966782</v>
+        <v>46104.4364179167</v>
       </c>
       <c r="E324" s="2">
-        <v>81525</v>
+        <v>82777</v>
       </c>
       <c r="F324" s="3">
-        <v>46030</v>
+        <v>46104</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>9</v>
@@ -8875,10 +8875,10 @@
         <v>46029.6400966782</v>
       </c>
       <c r="E325" s="2">
-        <v>81526</v>
+        <v>81506</v>
       </c>
       <c r="F325" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>9</v>
@@ -8895,16 +8895,16 @@
         <v>29</v>
       </c>
       <c r="C326" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D326" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E326" s="2">
-        <v>81640</v>
+        <v>81507</v>
       </c>
       <c r="F326" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>9</v>
@@ -8921,16 +8921,16 @@
         <v>29</v>
       </c>
       <c r="C327" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D327" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E327" s="2">
-        <v>81642</v>
+        <v>81524</v>
       </c>
       <c r="F327" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>9</v>
@@ -8947,16 +8947,16 @@
         <v>29</v>
       </c>
       <c r="C328" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D328" s="3">
-        <v>46036.6348522801</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E328" s="2">
-        <v>81643</v>
+        <v>81525</v>
       </c>
       <c r="F328" s="3">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>9</v>
@@ -8973,16 +8973,16 @@
         <v>29</v>
       </c>
       <c r="C329" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D329" s="3">
-        <v>46045.4207558912</v>
+        <v>46029.6400966782</v>
       </c>
       <c r="E329" s="2">
-        <v>81835</v>
+        <v>81526</v>
       </c>
       <c r="F329" s="3">
-        <v>46045</v>
+        <v>46030</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>9</v>
@@ -8999,16 +8999,16 @@
         <v>29</v>
       </c>
       <c r="C330" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D330" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E330" s="2">
-        <v>81836</v>
+        <v>81640</v>
       </c>
       <c r="F330" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>9</v>
@@ -9025,16 +9025,16 @@
         <v>29</v>
       </c>
       <c r="C331" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D331" s="3">
-        <v>46045.4207558912</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E331" s="2">
-        <v>81837</v>
+        <v>81642</v>
       </c>
       <c r="F331" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>9</v>
@@ -9051,16 +9051,16 @@
         <v>29</v>
       </c>
       <c r="C332" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D332" s="3">
-        <v>46051.6376515278</v>
+        <v>46036.6348522801</v>
       </c>
       <c r="E332" s="2">
-        <v>81931</v>
+        <v>81643</v>
       </c>
       <c r="F332" s="3">
-        <v>46052</v>
+        <v>46036</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>9</v>
@@ -9077,16 +9077,16 @@
         <v>29</v>
       </c>
       <c r="C333" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D333" s="3">
-        <v>46056.7115158912</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E333" s="2">
-        <v>81978</v>
+        <v>81835</v>
       </c>
       <c r="F333" s="3">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>9</v>
@@ -9103,16 +9103,16 @@
         <v>29</v>
       </c>
       <c r="C334" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D334" s="3">
-        <v>46057.6911087731</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E334" s="2">
-        <v>81994</v>
+        <v>81836</v>
       </c>
       <c r="F334" s="3">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>9</v>
@@ -9129,16 +9129,16 @@
         <v>29</v>
       </c>
       <c r="C335" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D335" s="3">
-        <v>46057.6911087731</v>
+        <v>46045.4207558912</v>
       </c>
       <c r="E335" s="2">
-        <v>81995</v>
+        <v>81837</v>
       </c>
       <c r="F335" s="3">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>9</v>
@@ -9155,16 +9155,16 @@
         <v>29</v>
       </c>
       <c r="C336" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D336" s="3">
-        <v>46057.6911087731</v>
+        <v>46051.6376515278</v>
       </c>
       <c r="E336" s="2">
-        <v>81999</v>
+        <v>81931</v>
       </c>
       <c r="F336" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>9</v>
@@ -9181,16 +9181,16 @@
         <v>29</v>
       </c>
       <c r="C337" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D337" s="3">
-        <v>46057.6911087731</v>
+        <v>46056.7115158912</v>
       </c>
       <c r="E337" s="2">
-        <v>82008</v>
+        <v>81978</v>
       </c>
       <c r="F337" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>9</v>
@@ -9213,10 +9213,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E338" s="2">
-        <v>82011</v>
+        <v>81994</v>
       </c>
       <c r="F338" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>9</v>
@@ -9239,10 +9239,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E339" s="2">
-        <v>82012</v>
+        <v>81995</v>
       </c>
       <c r="F339" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>9</v>
@@ -9265,10 +9265,10 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E340" s="2">
-        <v>82013</v>
+        <v>81999</v>
       </c>
       <c r="F340" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>9</v>
@@ -9291,7 +9291,7 @@
         <v>46057.6911087731</v>
       </c>
       <c r="E341" s="2">
-        <v>82014</v>
+        <v>82008</v>
       </c>
       <c r="F341" s="3">
         <v>46058</v>
@@ -9311,22 +9311,22 @@
         <v>29</v>
       </c>
       <c r="C342" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D342" s="3">
-        <v>46058.6604985417</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E342" s="2">
-        <v>82046</v>
+        <v>82011</v>
       </c>
       <c r="F342" s="3">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="343">
@@ -9337,16 +9337,16 @@
         <v>29</v>
       </c>
       <c r="C343" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D343" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E343" s="2">
-        <v>82217</v>
+        <v>82012</v>
       </c>
       <c r="F343" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>9</v>
@@ -9363,16 +9363,16 @@
         <v>29</v>
       </c>
       <c r="C344" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D344" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E344" s="2">
-        <v>82218</v>
+        <v>82013</v>
       </c>
       <c r="F344" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>9</v>
@@ -9389,16 +9389,16 @@
         <v>29</v>
       </c>
       <c r="C345" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D345" s="3">
-        <v>46072.738871875</v>
+        <v>46057.6911087731</v>
       </c>
       <c r="E345" s="2">
-        <v>82234</v>
+        <v>82014</v>
       </c>
       <c r="F345" s="3">
-        <v>46073</v>
+        <v>46058</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>9</v>
@@ -9415,22 +9415,22 @@
         <v>29</v>
       </c>
       <c r="C346" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D346" s="3">
-        <v>46072.738871875</v>
+        <v>46058.6604985417</v>
       </c>
       <c r="E346" s="2">
-        <v>82238</v>
+        <v>82046</v>
       </c>
       <c r="F346" s="3">
-        <v>46073</v>
+        <v>46059</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="347">
@@ -9447,10 +9447,10 @@
         <v>46072.738871875</v>
       </c>
       <c r="E347" s="2">
-        <v>82245</v>
+        <v>82217</v>
       </c>
       <c r="F347" s="3">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>9</v>
@@ -9467,16 +9467,16 @@
         <v>29</v>
       </c>
       <c r="C348" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D348" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E348" s="2">
-        <v>82257</v>
+        <v>82218</v>
       </c>
       <c r="F348" s="3">
-        <v>46076</v>
+        <v>46072</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>9</v>
@@ -9493,16 +9493,16 @@
         <v>29</v>
       </c>
       <c r="C349" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D349" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E349" s="2">
-        <v>82276</v>
+        <v>82234</v>
       </c>
       <c r="F349" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>9</v>
@@ -9519,16 +9519,16 @@
         <v>29</v>
       </c>
       <c r="C350" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D350" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E350" s="2">
-        <v>82277</v>
+        <v>82238</v>
       </c>
       <c r="F350" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>9</v>
@@ -9545,16 +9545,16 @@
         <v>29</v>
       </c>
       <c r="C351" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D351" s="3">
-        <v>46076.7244851042</v>
+        <v>46072.738871875</v>
       </c>
       <c r="E351" s="2">
-        <v>82293</v>
+        <v>82245</v>
       </c>
       <c r="F351" s="3">
-        <v>46078</v>
+        <v>46073</v>
       </c>
       <c r="G351" s="1" t="s">
         <v>9</v>
@@ -9571,16 +9571,16 @@
         <v>29</v>
       </c>
       <c r="C352" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D352" s="3">
-        <v>46077.4356327431</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E352" s="2">
-        <v>82269</v>
+        <v>82257</v>
       </c>
       <c r="F352" s="3">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>9</v>
@@ -9597,16 +9597,16 @@
         <v>29</v>
       </c>
       <c r="C353" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D353" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E353" s="2">
-        <v>82419</v>
+        <v>82276</v>
       </c>
       <c r="F353" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>9</v>
@@ -9623,16 +9623,16 @@
         <v>29</v>
       </c>
       <c r="C354" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D354" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E354" s="2">
-        <v>82420</v>
+        <v>82277</v>
       </c>
       <c r="F354" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>9</v>
@@ -9649,16 +9649,16 @@
         <v>29</v>
       </c>
       <c r="C355" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D355" s="3">
-        <v>46084.7378501505</v>
+        <v>46076.7244851042</v>
       </c>
       <c r="E355" s="2">
-        <v>82421</v>
+        <v>82293</v>
       </c>
       <c r="F355" s="3">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>9</v>
@@ -9675,16 +9675,16 @@
         <v>29</v>
       </c>
       <c r="C356" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D356" s="3">
-        <v>46084.7378501505</v>
+        <v>46077.4356327431</v>
       </c>
       <c r="E356" s="2">
-        <v>82422</v>
+        <v>82269</v>
       </c>
       <c r="F356" s="3">
-        <v>46084</v>
+        <v>46077</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>9</v>
@@ -9707,7 +9707,7 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E357" s="2">
-        <v>82423</v>
+        <v>82419</v>
       </c>
       <c r="F357" s="3">
         <v>46084</v>
@@ -9733,10 +9733,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E358" s="2">
-        <v>82433</v>
+        <v>82420</v>
       </c>
       <c r="F358" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>9</v>
@@ -9759,10 +9759,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E359" s="2">
-        <v>82434</v>
+        <v>82421</v>
       </c>
       <c r="F359" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>9</v>
@@ -9785,10 +9785,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E360" s="2">
-        <v>82464</v>
+        <v>82422</v>
       </c>
       <c r="F360" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>9</v>
@@ -9811,10 +9811,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="E361" s="2">
-        <v>82472</v>
+        <v>82423</v>
       </c>
       <c r="F361" s="3">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>9</v>
@@ -9831,16 +9831,16 @@
         <v>29</v>
       </c>
       <c r="C362" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D362" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E362" s="2">
-        <v>82578</v>
+        <v>82433</v>
       </c>
       <c r="F362" s="3">
-        <v>46093</v>
+        <v>46085</v>
       </c>
       <c r="G362" s="1" t="s">
         <v>9</v>
@@ -9857,16 +9857,16 @@
         <v>29</v>
       </c>
       <c r="C363" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D363" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E363" s="2">
-        <v>82579</v>
+        <v>82434</v>
       </c>
       <c r="F363" s="3">
-        <v>46093</v>
+        <v>46085</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>9</v>
@@ -9883,16 +9883,16 @@
         <v>29</v>
       </c>
       <c r="C364" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D364" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E364" s="2">
-        <v>82580</v>
+        <v>82464</v>
       </c>
       <c r="F364" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>9</v>
@@ -9909,16 +9909,16 @@
         <v>29</v>
       </c>
       <c r="C365" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D365" s="3">
-        <v>46093.4897546412</v>
+        <v>46084.7378501505</v>
       </c>
       <c r="E365" s="2">
-        <v>82599</v>
+        <v>82472</v>
       </c>
       <c r="F365" s="3">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>9</v>
@@ -9941,7 +9941,7 @@
         <v>46093.4897546412</v>
       </c>
       <c r="E366" s="2">
-        <v>82602</v>
+        <v>82578</v>
       </c>
       <c r="F366" s="3">
         <v>46093</v>
@@ -9961,13 +9961,13 @@
         <v>29</v>
       </c>
       <c r="C367" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D367" s="3">
-        <v>46093.4957757986</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E367" s="2">
-        <v>82584</v>
+        <v>82579</v>
       </c>
       <c r="F367" s="3">
         <v>46093</v>
@@ -9987,16 +9987,16 @@
         <v>29</v>
       </c>
       <c r="C368" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D368" s="3">
-        <v>46100.6528700694</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E368" s="2">
-        <v>82746</v>
+        <v>82580</v>
       </c>
       <c r="F368" s="3">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>9</v>
@@ -10013,16 +10013,16 @@
         <v>29</v>
       </c>
       <c r="C369" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D369" s="3">
-        <v>46100.6528700694</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E369" s="2">
-        <v>82747</v>
+        <v>82599</v>
       </c>
       <c r="F369" s="3">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>9</v>
@@ -10039,16 +10039,16 @@
         <v>29</v>
       </c>
       <c r="C370" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D370" s="3">
-        <v>46100.6528700694</v>
+        <v>46093.4897546412</v>
       </c>
       <c r="E370" s="2">
-        <v>82748</v>
+        <v>82602</v>
       </c>
       <c r="F370" s="3">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>9</v>
@@ -10059,22 +10059,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="371">
       <c r="A371" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C371" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D371" s="3">
-        <v>46027.6953206134</v>
+        <v>46093.4957757986</v>
       </c>
       <c r="E371" s="2">
-        <v>81464</v>
+        <v>82584</v>
       </c>
       <c r="F371" s="3">
-        <v>46027</v>
+        <v>46093</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>9</v>
@@ -10085,22 +10085,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="372">
       <c r="A372" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C372" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D372" s="3">
-        <v>46027.6953206134</v>
+        <v>46100.6528700694</v>
       </c>
       <c r="E372" s="2">
-        <v>81472</v>
+        <v>82746</v>
       </c>
       <c r="F372" s="3">
-        <v>46027</v>
+        <v>46100</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>9</v>
@@ -10111,22 +10111,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="373">
       <c r="A373" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C373" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D373" s="3">
-        <v>46027.6953206134</v>
+        <v>46100.6528700694</v>
       </c>
       <c r="E373" s="2">
-        <v>81492</v>
+        <v>82747</v>
       </c>
       <c r="F373" s="3">
-        <v>46029</v>
+        <v>46100</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>9</v>
@@ -10137,22 +10137,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="374">
       <c r="A374" s="2">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C374" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D374" s="3">
-        <v>46027.6953206134</v>
+        <v>46100.6528700694</v>
       </c>
       <c r="E374" s="2">
-        <v>81493</v>
+        <v>82748</v>
       </c>
       <c r="F374" s="3">
-        <v>46029</v>
+        <v>46100</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>9</v>
@@ -10175,10 +10175,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E375" s="2">
-        <v>81568</v>
+        <v>81464</v>
       </c>
       <c r="F375" s="3">
-        <v>46031</v>
+        <v>46027</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>9</v>
@@ -10201,10 +10201,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E376" s="2">
-        <v>81601</v>
+        <v>81472</v>
       </c>
       <c r="F376" s="3">
-        <v>46034</v>
+        <v>46027</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>9</v>
@@ -10227,10 +10227,10 @@
         <v>46027.6953206134</v>
       </c>
       <c r="E377" s="2">
-        <v>81602</v>
+        <v>81492</v>
       </c>
       <c r="F377" s="3">
-        <v>46034</v>
+        <v>46029</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>9</v>
@@ -10247,16 +10247,16 @@
         <v>30</v>
       </c>
       <c r="C378" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D378" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E378" s="2">
-        <v>81645</v>
+        <v>81493</v>
       </c>
       <c r="F378" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>9</v>
@@ -10273,16 +10273,16 @@
         <v>30</v>
       </c>
       <c r="C379" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D379" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E379" s="2">
-        <v>81646</v>
+        <v>81568</v>
       </c>
       <c r="F379" s="3">
-        <v>46036</v>
+        <v>46031</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>9</v>
@@ -10299,16 +10299,16 @@
         <v>30</v>
       </c>
       <c r="C380" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D380" s="3">
-        <v>46036.6368094444</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E380" s="2">
-        <v>81653</v>
+        <v>81601</v>
       </c>
       <c r="F380" s="3">
-        <v>46037</v>
+        <v>46034</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>9</v>
@@ -10325,16 +10325,16 @@
         <v>30</v>
       </c>
       <c r="C381" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D381" s="3">
-        <v>46037.4325152662</v>
+        <v>46027.6953206134</v>
       </c>
       <c r="E381" s="2">
-        <v>81662</v>
+        <v>81602</v>
       </c>
       <c r="F381" s="3">
-        <v>46037</v>
+        <v>46034</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>9</v>
@@ -10351,16 +10351,16 @@
         <v>30</v>
       </c>
       <c r="C382" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D382" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E382" s="2">
-        <v>81780</v>
+        <v>81645</v>
       </c>
       <c r="F382" s="3">
-        <v>46044</v>
+        <v>46036</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>9</v>
@@ -10377,16 +10377,16 @@
         <v>30</v>
       </c>
       <c r="C383" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D383" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E383" s="2">
-        <v>81781</v>
+        <v>81646</v>
       </c>
       <c r="F383" s="3">
-        <v>46044</v>
+        <v>46036</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>9</v>
@@ -10403,16 +10403,16 @@
         <v>30</v>
       </c>
       <c r="C384" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D384" s="3">
-        <v>46044.4079891435</v>
+        <v>46036.6368094444</v>
       </c>
       <c r="E384" s="2">
-        <v>81782</v>
+        <v>81653</v>
       </c>
       <c r="F384" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>9</v>
@@ -10429,16 +10429,16 @@
         <v>30</v>
       </c>
       <c r="C385" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D385" s="3">
-        <v>46044.4079891435</v>
+        <v>46037.4325152662</v>
       </c>
       <c r="E385" s="2">
-        <v>81784</v>
+        <v>81662</v>
       </c>
       <c r="F385" s="3">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>9</v>
@@ -10461,7 +10461,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E386" s="2">
-        <v>81785</v>
+        <v>81780</v>
       </c>
       <c r="F386" s="3">
         <v>46044</v>
@@ -10487,7 +10487,7 @@
         <v>46044.4079891435</v>
       </c>
       <c r="E387" s="2">
-        <v>81801</v>
+        <v>81781</v>
       </c>
       <c r="F387" s="3">
         <v>46044</v>
@@ -10507,16 +10507,16 @@
         <v>30</v>
       </c>
       <c r="C388" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D388" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E388" s="2">
-        <v>81860</v>
+        <v>81782</v>
       </c>
       <c r="F388" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>9</v>
@@ -10533,16 +10533,16 @@
         <v>30</v>
       </c>
       <c r="C389" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D389" s="3">
-        <v>46048.7319778588</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E389" s="2">
-        <v>81873</v>
+        <v>81784</v>
       </c>
       <c r="F389" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>9</v>
@@ -10559,16 +10559,16 @@
         <v>30</v>
       </c>
       <c r="C390" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D390" s="3">
-        <v>46049.4883916667</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E390" s="2">
-        <v>81865</v>
+        <v>81785</v>
       </c>
       <c r="F390" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>9</v>
@@ -10585,16 +10585,16 @@
         <v>30</v>
       </c>
       <c r="C391" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D391" s="3">
-        <v>46049.4883916667</v>
+        <v>46044.4079891435</v>
       </c>
       <c r="E391" s="2">
-        <v>81870</v>
+        <v>81801</v>
       </c>
       <c r="F391" s="3">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>9</v>
@@ -10611,13 +10611,13 @@
         <v>30</v>
       </c>
       <c r="C392" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D392" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E392" s="2">
-        <v>81872</v>
+        <v>81860</v>
       </c>
       <c r="F392" s="3">
         <v>46049</v>
@@ -10637,16 +10637,16 @@
         <v>30</v>
       </c>
       <c r="C393" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D393" s="3">
-        <v>46049.4883916667</v>
+        <v>46048.7319778588</v>
       </c>
       <c r="E393" s="2">
-        <v>81896</v>
+        <v>81873</v>
       </c>
       <c r="F393" s="3">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>9</v>
@@ -10663,16 +10663,16 @@
         <v>30</v>
       </c>
       <c r="C394" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D394" s="3">
-        <v>46051.4046937153</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E394" s="2">
-        <v>81923</v>
+        <v>81865</v>
       </c>
       <c r="F394" s="3">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>9</v>
@@ -10689,16 +10689,16 @@
         <v>30</v>
       </c>
       <c r="C395" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D395" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E395" s="2">
-        <v>81998</v>
+        <v>81870</v>
       </c>
       <c r="F395" s="3">
-        <v>46057</v>
+        <v>46049</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>9</v>
@@ -10715,16 +10715,16 @@
         <v>30</v>
       </c>
       <c r="C396" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D396" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E396" s="2">
-        <v>82002</v>
+        <v>81872</v>
       </c>
       <c r="F396" s="3">
-        <v>46057</v>
+        <v>46049</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>9</v>
@@ -10741,16 +10741,16 @@
         <v>30</v>
       </c>
       <c r="C397" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D397" s="3">
-        <v>46057.6959672917</v>
+        <v>46049.4883916667</v>
       </c>
       <c r="E397" s="2">
-        <v>82005</v>
+        <v>81896</v>
       </c>
       <c r="F397" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>9</v>
@@ -10767,16 +10767,16 @@
         <v>30</v>
       </c>
       <c r="C398" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D398" s="3">
-        <v>46057.6959672917</v>
+        <v>46051.4046937153</v>
       </c>
       <c r="E398" s="2">
-        <v>82007</v>
+        <v>81923</v>
       </c>
       <c r="F398" s="3">
-        <v>46058</v>
+        <v>46051</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>9</v>
@@ -10793,16 +10793,16 @@
         <v>30</v>
       </c>
       <c r="C399" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D399" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E399" s="2">
-        <v>82005</v>
+        <v>81998</v>
       </c>
       <c r="F399" s="3">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>9</v>
@@ -10819,16 +10819,16 @@
         <v>30</v>
       </c>
       <c r="C400" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D400" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E400" s="2">
-        <v>82075</v>
+        <v>82002</v>
       </c>
       <c r="F400" s="3">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>9</v>
@@ -10845,16 +10845,16 @@
         <v>30</v>
       </c>
       <c r="C401" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D401" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E401" s="2">
-        <v>82077</v>
+        <v>82005</v>
       </c>
       <c r="F401" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>9</v>
@@ -10871,16 +10871,16 @@
         <v>30</v>
       </c>
       <c r="C402" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D402" s="3">
-        <v>46063.5942651852</v>
+        <v>46057.6959672917</v>
       </c>
       <c r="E402" s="2">
-        <v>82099</v>
+        <v>82007</v>
       </c>
       <c r="F402" s="3">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>9</v>
@@ -10897,16 +10897,16 @@
         <v>30</v>
       </c>
       <c r="C403" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D403" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E403" s="2">
-        <v>82219</v>
+        <v>82005</v>
       </c>
       <c r="F403" s="3">
-        <v>46072</v>
+        <v>46058</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>9</v>
@@ -10923,16 +10923,16 @@
         <v>30</v>
       </c>
       <c r="C404" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D404" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E404" s="2">
-        <v>82230</v>
+        <v>82075</v>
       </c>
       <c r="F404" s="3">
-        <v>46073</v>
+        <v>46063</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>9</v>
@@ -10949,16 +10949,16 @@
         <v>30</v>
       </c>
       <c r="C405" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D405" s="3">
-        <v>46072.7460071991</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E405" s="2">
-        <v>82231</v>
+        <v>82077</v>
       </c>
       <c r="F405" s="3">
-        <v>46073</v>
+        <v>46063</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>9</v>
@@ -10975,16 +10975,16 @@
         <v>30</v>
       </c>
       <c r="C406" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D406" s="3">
-        <v>46079.5787315972</v>
+        <v>46063.5942651852</v>
       </c>
       <c r="E406" s="2">
-        <v>82388</v>
+        <v>82099</v>
       </c>
       <c r="F406" s="3">
-        <v>46083</v>
+        <v>46064</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>9</v>
@@ -11001,16 +11001,16 @@
         <v>30</v>
       </c>
       <c r="C407" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D407" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E407" s="2">
-        <v>82389</v>
+        <v>82219</v>
       </c>
       <c r="F407" s="3">
-        <v>46083</v>
+        <v>46072</v>
       </c>
       <c r="G407" s="1" t="s">
         <v>9</v>
@@ -11027,16 +11027,16 @@
         <v>30</v>
       </c>
       <c r="C408" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D408" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E408" s="2">
-        <v>82396</v>
+        <v>82230</v>
       </c>
       <c r="F408" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>9</v>
@@ -11053,16 +11053,16 @@
         <v>30</v>
       </c>
       <c r="C409" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D409" s="3">
-        <v>46079.5787315972</v>
+        <v>46072.7460071991</v>
       </c>
       <c r="E409" s="2">
-        <v>82397</v>
+        <v>82231</v>
       </c>
       <c r="F409" s="3">
-        <v>46083</v>
+        <v>46073</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>9</v>
@@ -11079,16 +11079,16 @@
         <v>30</v>
       </c>
       <c r="C410" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D410" s="3">
-        <v>46085.6249659838</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E410" s="2">
-        <v>82435</v>
+        <v>82388</v>
       </c>
       <c r="F410" s="3">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>9</v>
@@ -11105,16 +11105,16 @@
         <v>30</v>
       </c>
       <c r="C411" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D411" s="3">
-        <v>46091.449444456</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E411" s="2">
-        <v>82506</v>
+        <v>82389</v>
       </c>
       <c r="F411" s="3">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>9</v>
@@ -11131,16 +11131,16 @@
         <v>30</v>
       </c>
       <c r="C412" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D412" s="3">
-        <v>46091.4795702315</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E412" s="2">
-        <v>82509</v>
+        <v>82396</v>
       </c>
       <c r="F412" s="3">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>9</v>
@@ -11157,16 +11157,16 @@
         <v>30</v>
       </c>
       <c r="C413" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D413" s="3">
-        <v>46093.4969972338</v>
+        <v>46079.5787315972</v>
       </c>
       <c r="E413" s="2">
-        <v>82589</v>
+        <v>82397</v>
       </c>
       <c r="F413" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>9</v>
@@ -11183,16 +11183,16 @@
         <v>30</v>
       </c>
       <c r="C414" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D414" s="3">
-        <v>46105.7312393519</v>
+        <v>46085.6249659838</v>
       </c>
       <c r="E414" s="2">
-        <v>82798</v>
+        <v>82435</v>
       </c>
       <c r="F414" s="3">
-        <v>46105</v>
+        <v>46085</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>9</v>
@@ -11209,16 +11209,16 @@
         <v>30</v>
       </c>
       <c r="C415" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D415" s="3">
-        <v>46105.7312393519</v>
+        <v>46091.449444456</v>
       </c>
       <c r="E415" s="2">
-        <v>82805</v>
+        <v>82506</v>
       </c>
       <c r="F415" s="3">
-        <v>46106</v>
+        <v>46091</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>9</v>
@@ -11235,16 +11235,16 @@
         <v>30</v>
       </c>
       <c r="C416" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D416" s="3">
-        <v>46105.7312393519</v>
+        <v>46091.4795702315</v>
       </c>
       <c r="E416" s="2">
-        <v>82812</v>
+        <v>82509</v>
       </c>
       <c r="F416" s="3">
-        <v>46106</v>
+        <v>46091</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>9</v>
@@ -11255,22 +11255,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="417">
       <c r="A417" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C417" s="2">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D417" s="3">
-        <v>46029.3821391551</v>
+        <v>46093.4969972338</v>
       </c>
       <c r="E417" s="2">
-        <v>81477</v>
+        <v>82589</v>
       </c>
       <c r="F417" s="3">
-        <v>46029</v>
+        <v>46093</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>9</v>
@@ -11281,22 +11281,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="418">
       <c r="A418" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C418" s="2">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D418" s="3">
-        <v>46030.4142968056</v>
+        <v>46105.7312393519</v>
       </c>
       <c r="E418" s="2">
-        <v>81532</v>
+        <v>82798</v>
       </c>
       <c r="F418" s="3">
-        <v>46030</v>
+        <v>46105</v>
       </c>
       <c r="G418" s="1" t="s">
         <v>9</v>
@@ -11307,22 +11307,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="419">
       <c r="A419" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C419" s="2">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D419" s="3">
-        <v>46030.4142968056</v>
+        <v>46105.7312393519</v>
       </c>
       <c r="E419" s="2">
-        <v>81534</v>
+        <v>82805</v>
       </c>
       <c r="F419" s="3">
-        <v>46030</v>
+        <v>46106</v>
       </c>
       <c r="G419" s="1" t="s">
         <v>9</v>
@@ -11333,22 +11333,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="420">
       <c r="A420" s="2">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C420" s="2">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D420" s="3">
-        <v>46030.4142968056</v>
+        <v>46105.7312393519</v>
       </c>
       <c r="E420" s="2">
-        <v>81535</v>
+        <v>82812</v>
       </c>
       <c r="F420" s="3">
-        <v>46030</v>
+        <v>46106</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>9</v>
@@ -11365,16 +11365,16 @@
         <v>31</v>
       </c>
       <c r="C421" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D421" s="3">
-        <v>46030.4142968056</v>
+        <v>46029.3821391551</v>
       </c>
       <c r="E421" s="2">
-        <v>81550</v>
+        <v>81477</v>
       </c>
       <c r="F421" s="3">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>9</v>
@@ -11397,7 +11397,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E422" s="2">
-        <v>81553</v>
+        <v>81532</v>
       </c>
       <c r="F422" s="3">
         <v>46030</v>
@@ -11423,7 +11423,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E423" s="2">
-        <v>81554</v>
+        <v>81534</v>
       </c>
       <c r="F423" s="3">
         <v>46030</v>
@@ -11449,7 +11449,7 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E424" s="2">
-        <v>81557</v>
+        <v>81535</v>
       </c>
       <c r="F424" s="3">
         <v>46030</v>
@@ -11475,10 +11475,10 @@
         <v>46030.4142968056</v>
       </c>
       <c r="E425" s="2">
-        <v>81588</v>
+        <v>81550</v>
       </c>
       <c r="F425" s="3">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>9</v>
@@ -11495,16 +11495,16 @@
         <v>31</v>
       </c>
       <c r="C426" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D426" s="3">
-        <v>46038.593985081</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E426" s="2">
-        <v>81692</v>
+        <v>81553</v>
       </c>
       <c r="F426" s="3">
-        <v>46038</v>
+        <v>46030</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>9</v>
@@ -11521,16 +11521,16 @@
         <v>31</v>
       </c>
       <c r="C427" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D427" s="3">
-        <v>46044.46462125</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E427" s="2">
-        <v>81786</v>
+        <v>81554</v>
       </c>
       <c r="F427" s="3">
-        <v>46044</v>
+        <v>46030</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>9</v>
@@ -11547,16 +11547,16 @@
         <v>31</v>
       </c>
       <c r="C428" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D428" s="3">
-        <v>46044.6362443171</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E428" s="2">
-        <v>81844</v>
+        <v>81557</v>
       </c>
       <c r="F428" s="3">
-        <v>46045</v>
+        <v>46030</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>9</v>
@@ -11573,16 +11573,16 @@
         <v>31</v>
       </c>
       <c r="C429" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D429" s="3">
-        <v>46062.717040544</v>
+        <v>46030.4142968056</v>
       </c>
       <c r="E429" s="2">
-        <v>82065</v>
+        <v>81588</v>
       </c>
       <c r="F429" s="3">
-        <v>46062</v>
+        <v>46031</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>9</v>
@@ -11599,16 +11599,16 @@
         <v>31</v>
       </c>
       <c r="C430" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D430" s="3">
-        <v>46062.717040544</v>
+        <v>46038.593985081</v>
       </c>
       <c r="E430" s="2">
-        <v>82066</v>
+        <v>81692</v>
       </c>
       <c r="F430" s="3">
-        <v>46062</v>
+        <v>46038</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>9</v>
@@ -11625,16 +11625,16 @@
         <v>31</v>
       </c>
       <c r="C431" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D431" s="3">
-        <v>46062.717040544</v>
+        <v>46044.46462125</v>
       </c>
       <c r="E431" s="2">
-        <v>82067</v>
+        <v>81786</v>
       </c>
       <c r="F431" s="3">
-        <v>46062</v>
+        <v>46044</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>9</v>
@@ -11651,16 +11651,16 @@
         <v>31</v>
       </c>
       <c r="C432" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D432" s="3">
-        <v>46065.6300915625</v>
+        <v>46044.6362443171</v>
       </c>
       <c r="E432" s="2">
-        <v>82190</v>
+        <v>81844</v>
       </c>
       <c r="F432" s="3">
-        <v>46066</v>
+        <v>46045</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>9</v>
@@ -11677,16 +11677,16 @@
         <v>31</v>
       </c>
       <c r="C433" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D433" s="3">
-        <v>46065.6300915625</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E433" s="2">
-        <v>82197</v>
+        <v>82065</v>
       </c>
       <c r="F433" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>9</v>
@@ -11703,16 +11703,16 @@
         <v>31</v>
       </c>
       <c r="C434" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D434" s="3">
-        <v>46077.5084780324</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E434" s="2">
-        <v>82270</v>
+        <v>82066</v>
       </c>
       <c r="F434" s="3">
-        <v>46077</v>
+        <v>46062</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>9</v>
@@ -11729,16 +11729,16 @@
         <v>31</v>
       </c>
       <c r="C435" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D435" s="3">
-        <v>46077.721037037</v>
+        <v>46062.717040544</v>
       </c>
       <c r="E435" s="2">
-        <v>82285</v>
+        <v>82067</v>
       </c>
       <c r="F435" s="3">
-        <v>46077</v>
+        <v>46062</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>9</v>
@@ -11755,16 +11755,16 @@
         <v>31</v>
       </c>
       <c r="C436" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D436" s="3">
-        <v>46083.6694849421</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E436" s="2">
-        <v>82417</v>
+        <v>82190</v>
       </c>
       <c r="F436" s="3">
-        <v>46084</v>
+        <v>46066</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>9</v>
@@ -11781,16 +11781,16 @@
         <v>31</v>
       </c>
       <c r="C437" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D437" s="3">
-        <v>46085.7157723032</v>
+        <v>46065.6300915625</v>
       </c>
       <c r="E437" s="2">
-        <v>82457</v>
+        <v>82197</v>
       </c>
       <c r="F437" s="3">
-        <v>46086</v>
+        <v>46066</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>9</v>
@@ -11807,16 +11807,16 @@
         <v>31</v>
       </c>
       <c r="C438" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D438" s="3">
-        <v>46099.6523956944</v>
+        <v>46077.5084780324</v>
       </c>
       <c r="E438" s="2">
-        <v>82724</v>
+        <v>82270</v>
       </c>
       <c r="F438" s="3">
-        <v>46099</v>
+        <v>46077</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>9</v>
@@ -11833,16 +11833,16 @@
         <v>31</v>
       </c>
       <c r="C439" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D439" s="3">
-        <v>46099.6523956944</v>
+        <v>46077.721037037</v>
       </c>
       <c r="E439" s="2">
-        <v>82725</v>
+        <v>82285</v>
       </c>
       <c r="F439" s="3">
-        <v>46099</v>
+        <v>46077</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>9</v>
@@ -11859,16 +11859,16 @@
         <v>31</v>
       </c>
       <c r="C440" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D440" s="3">
-        <v>46099.6523956944</v>
+        <v>46083.6694849421</v>
       </c>
       <c r="E440" s="2">
-        <v>82727</v>
+        <v>82417</v>
       </c>
       <c r="F440" s="3">
-        <v>46100</v>
+        <v>46084</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>9</v>
@@ -11885,16 +11885,16 @@
         <v>31</v>
       </c>
       <c r="C441" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D441" s="3">
-        <v>46099.6523956944</v>
+        <v>46085.7157723032</v>
       </c>
       <c r="E441" s="2">
-        <v>82730</v>
+        <v>82457</v>
       </c>
       <c r="F441" s="3">
-        <v>46100</v>
+        <v>46086</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>9</v>
@@ -11905,22 +11905,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="442">
       <c r="A442" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C442" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D442" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E442" s="2">
-        <v>81484</v>
+        <v>82724</v>
       </c>
       <c r="F442" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>9</v>
@@ -11931,22 +11931,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="443">
       <c r="A443" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C443" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D443" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E443" s="2">
-        <v>81486</v>
+        <v>82725</v>
       </c>
       <c r="F443" s="3">
-        <v>46029</v>
+        <v>46099</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>9</v>
@@ -11957,22 +11957,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="444">
       <c r="A444" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C444" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D444" s="3">
-        <v>46029.381258831</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E444" s="2">
-        <v>81487</v>
+        <v>82727</v>
       </c>
       <c r="F444" s="3">
-        <v>46029</v>
+        <v>46100</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>9</v>
@@ -11983,22 +11983,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="445">
       <c r="A445" s="2">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C445" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D445" s="3">
-        <v>46036.4048894097</v>
+        <v>46099.6523956944</v>
       </c>
       <c r="E445" s="2">
-        <v>81613</v>
+        <v>82730</v>
       </c>
       <c r="F445" s="3">
-        <v>46036</v>
+        <v>46100</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>9</v>
@@ -12015,16 +12015,16 @@
         <v>32</v>
       </c>
       <c r="C446" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D446" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E446" s="2">
-        <v>81614</v>
+        <v>81484</v>
       </c>
       <c r="F446" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>9</v>
@@ -12041,16 +12041,16 @@
         <v>32</v>
       </c>
       <c r="C447" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D447" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E447" s="2">
-        <v>81622</v>
+        <v>81486</v>
       </c>
       <c r="F447" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>9</v>
@@ -12067,16 +12067,16 @@
         <v>32</v>
       </c>
       <c r="C448" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D448" s="3">
-        <v>46036.4048894097</v>
+        <v>46029.381258831</v>
       </c>
       <c r="E448" s="2">
-        <v>81632</v>
+        <v>81487</v>
       </c>
       <c r="F448" s="3">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>9</v>
@@ -12099,10 +12099,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E449" s="2">
-        <v>81648</v>
+        <v>81613</v>
       </c>
       <c r="F449" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>9</v>
@@ -12125,10 +12125,10 @@
         <v>46036.4048894097</v>
       </c>
       <c r="E450" s="2">
-        <v>81664</v>
+        <v>81614</v>
       </c>
       <c r="F450" s="3">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>9</v>
@@ -12145,16 +12145,16 @@
         <v>32</v>
       </c>
       <c r="C451" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D451" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E451" s="2">
-        <v>81815</v>
+        <v>81622</v>
       </c>
       <c r="F451" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>9</v>
@@ -12171,16 +12171,16 @@
         <v>32</v>
       </c>
       <c r="C452" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D452" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E452" s="2">
-        <v>81816</v>
+        <v>81632</v>
       </c>
       <c r="F452" s="3">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>9</v>
@@ -12197,16 +12197,16 @@
         <v>32</v>
       </c>
       <c r="C453" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D453" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E453" s="2">
-        <v>81838</v>
+        <v>81648</v>
       </c>
       <c r="F453" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>9</v>
@@ -12223,16 +12223,16 @@
         <v>32</v>
       </c>
       <c r="C454" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D454" s="3">
-        <v>46045.4188638426</v>
+        <v>46036.4048894097</v>
       </c>
       <c r="E454" s="2">
-        <v>81840</v>
+        <v>81664</v>
       </c>
       <c r="F454" s="3">
-        <v>46045</v>
+        <v>46037</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>9</v>
@@ -12249,16 +12249,16 @@
         <v>32</v>
       </c>
       <c r="C455" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D455" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E455" s="2">
-        <v>81959</v>
+        <v>81815</v>
       </c>
       <c r="F455" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>9</v>
@@ -12275,16 +12275,16 @@
         <v>32</v>
       </c>
       <c r="C456" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D456" s="3">
-        <v>46055.5991080671</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E456" s="2">
-        <v>81960</v>
+        <v>81816</v>
       </c>
       <c r="F456" s="3">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>9</v>
@@ -12301,16 +12301,16 @@
         <v>32</v>
       </c>
       <c r="C457" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D457" s="3">
-        <v>46062.7151302546</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E457" s="2">
-        <v>82063</v>
+        <v>81838</v>
       </c>
       <c r="F457" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>9</v>
@@ -12327,16 +12327,16 @@
         <v>32</v>
       </c>
       <c r="C458" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D458" s="3">
-        <v>46062.7151302546</v>
+        <v>46045.4188638426</v>
       </c>
       <c r="E458" s="2">
-        <v>82064</v>
+        <v>81840</v>
       </c>
       <c r="F458" s="3">
-        <v>46062</v>
+        <v>46045</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>9</v>
@@ -12353,16 +12353,16 @@
         <v>32</v>
       </c>
       <c r="C459" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D459" s="3">
-        <v>46062.7151302546</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E459" s="2">
-        <v>82100</v>
+        <v>81959</v>
       </c>
       <c r="F459" s="3">
-        <v>46064</v>
+        <v>46055</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>9</v>
@@ -12379,16 +12379,16 @@
         <v>32</v>
       </c>
       <c r="C460" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D460" s="3">
-        <v>46072.7410579977</v>
+        <v>46055.5991080671</v>
       </c>
       <c r="E460" s="2">
-        <v>82333</v>
+        <v>81960</v>
       </c>
       <c r="F460" s="3">
-        <v>46079</v>
+        <v>46055</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>9</v>
@@ -12405,16 +12405,16 @@
         <v>32</v>
       </c>
       <c r="C461" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D461" s="3">
-        <v>46072.7410579977</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E461" s="2">
-        <v>82334</v>
+        <v>82063</v>
       </c>
       <c r="F461" s="3">
-        <v>46079</v>
+        <v>46062</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>9</v>
@@ -12431,16 +12431,16 @@
         <v>32</v>
       </c>
       <c r="C462" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D462" s="3">
-        <v>46076.7259125116</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E462" s="2">
-        <v>82258</v>
+        <v>82064</v>
       </c>
       <c r="F462" s="3">
-        <v>46076</v>
+        <v>46062</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>9</v>
@@ -12457,16 +12457,16 @@
         <v>32</v>
       </c>
       <c r="C463" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D463" s="3">
-        <v>46076.7259125116</v>
+        <v>46062.7151302546</v>
       </c>
       <c r="E463" s="2">
-        <v>82259</v>
+        <v>82100</v>
       </c>
       <c r="F463" s="3">
-        <v>46076</v>
+        <v>46064</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>9</v>
@@ -12483,16 +12483,16 @@
         <v>32</v>
       </c>
       <c r="C464" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D464" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E464" s="2">
-        <v>82260</v>
+        <v>82333</v>
       </c>
       <c r="F464" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>9</v>
@@ -12509,16 +12509,16 @@
         <v>32</v>
       </c>
       <c r="C465" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D465" s="3">
-        <v>46076.7259125116</v>
+        <v>46072.7410579977</v>
       </c>
       <c r="E465" s="2">
-        <v>82274</v>
+        <v>82334</v>
       </c>
       <c r="F465" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>9</v>
@@ -12535,16 +12535,16 @@
         <v>32</v>
       </c>
       <c r="C466" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D466" s="3">
-        <v>46084.5055666204</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E466" s="2">
-        <v>82409</v>
+        <v>82258</v>
       </c>
       <c r="F466" s="3">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>9</v>
@@ -12561,16 +12561,16 @@
         <v>32</v>
       </c>
       <c r="C467" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D467" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E467" s="2">
-        <v>82581</v>
+        <v>82259</v>
       </c>
       <c r="F467" s="3">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>9</v>
@@ -12587,16 +12587,16 @@
         <v>32</v>
       </c>
       <c r="C468" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D468" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E468" s="2">
-        <v>82582</v>
+        <v>82260</v>
       </c>
       <c r="F468" s="3">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>9</v>
@@ -12613,16 +12613,16 @@
         <v>32</v>
       </c>
       <c r="C469" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D469" s="3">
-        <v>46093.4920058565</v>
+        <v>46076.7259125116</v>
       </c>
       <c r="E469" s="2">
-        <v>82583</v>
+        <v>82274</v>
       </c>
       <c r="F469" s="3">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>9</v>
@@ -12639,16 +12639,16 @@
         <v>32</v>
       </c>
       <c r="C470" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D470" s="3">
-        <v>46093.4920058565</v>
+        <v>46084.5055666204</v>
       </c>
       <c r="E470" s="2">
-        <v>82672</v>
+        <v>82409</v>
       </c>
       <c r="F470" s="3">
-        <v>46097</v>
+        <v>46084</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>9</v>
@@ -12671,10 +12671,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="E471" s="2">
-        <v>82674</v>
+        <v>82581</v>
       </c>
       <c r="F471" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>9</v>
@@ -12685,22 +12685,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="472">
       <c r="A472" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C472" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D472" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E472" s="2">
-        <v>81608</v>
+        <v>82582</v>
       </c>
       <c r="F472" s="3">
-        <v>46035</v>
+        <v>46093</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>9</v>
@@ -12711,22 +12711,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="473">
       <c r="A473" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C473" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D473" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E473" s="2">
-        <v>81609</v>
+        <v>82583</v>
       </c>
       <c r="F473" s="3">
-        <v>46035</v>
+        <v>46093</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>9</v>
@@ -12737,22 +12737,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="474">
       <c r="A474" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C474" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D474" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E474" s="2">
-        <v>81610</v>
+        <v>82672</v>
       </c>
       <c r="F474" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>9</v>
@@ -12763,22 +12763,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="475">
       <c r="A475" s="2">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C475" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D475" s="3">
-        <v>46035.4386099769</v>
+        <v>46093.4920058565</v>
       </c>
       <c r="E475" s="2">
-        <v>81611</v>
+        <v>82674</v>
       </c>
       <c r="F475" s="3">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>9</v>
@@ -12801,7 +12801,7 @@
         <v>46035.4386099769</v>
       </c>
       <c r="E476" s="2">
-        <v>81612</v>
+        <v>81608</v>
       </c>
       <c r="F476" s="3">
         <v>46035</v>
@@ -12821,16 +12821,16 @@
         <v>33</v>
       </c>
       <c r="C477" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D477" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E477" s="2">
-        <v>81652</v>
+        <v>81609</v>
       </c>
       <c r="F477" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>9</v>
@@ -12847,16 +12847,16 @@
         <v>33</v>
       </c>
       <c r="C478" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D478" s="3">
-        <v>46036.6342081481</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E478" s="2">
-        <v>81659</v>
+        <v>81610</v>
       </c>
       <c r="F478" s="3">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>9</v>
@@ -12873,16 +12873,16 @@
         <v>33</v>
       </c>
       <c r="C479" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D479" s="3">
-        <v>46048.6509980093</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E479" s="2">
-        <v>81853</v>
+        <v>81611</v>
       </c>
       <c r="F479" s="3">
-        <v>46048</v>
+        <v>46035</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>9</v>
@@ -12899,16 +12899,16 @@
         <v>33</v>
       </c>
       <c r="C480" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D480" s="3">
-        <v>46048.6509980093</v>
+        <v>46035.4386099769</v>
       </c>
       <c r="E480" s="2">
-        <v>81869</v>
+        <v>81612</v>
       </c>
       <c r="F480" s="3">
-        <v>46049</v>
+        <v>46035</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>9</v>
@@ -12925,16 +12925,16 @@
         <v>33</v>
       </c>
       <c r="C481" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D481" s="3">
-        <v>46048.6509980093</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E481" s="2">
-        <v>81890</v>
+        <v>81652</v>
       </c>
       <c r="F481" s="3">
-        <v>46050</v>
+        <v>46037</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>9</v>
@@ -12951,16 +12951,16 @@
         <v>33</v>
       </c>
       <c r="C482" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D482" s="3">
-        <v>46049.4871256134</v>
+        <v>46036.6342081481</v>
       </c>
       <c r="E482" s="2">
-        <v>81875</v>
+        <v>81659</v>
       </c>
       <c r="F482" s="3">
-        <v>46049</v>
+        <v>46037</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>9</v>
@@ -12977,16 +12977,16 @@
         <v>33</v>
       </c>
       <c r="C483" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D483" s="3">
-        <v>46049.4871256134</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E483" s="2">
-        <v>81881</v>
+        <v>81853</v>
       </c>
       <c r="F483" s="3">
-        <v>46050</v>
+        <v>46048</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>9</v>
@@ -13003,16 +13003,16 @@
         <v>33</v>
       </c>
       <c r="C484" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D484" s="3">
-        <v>46056.7073643981</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E484" s="2">
-        <v>82015</v>
+        <v>81869</v>
       </c>
       <c r="F484" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G484" s="1" t="s">
         <v>9</v>
@@ -13029,16 +13029,16 @@
         <v>33</v>
       </c>
       <c r="C485" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D485" s="3">
-        <v>46056.7073643981</v>
+        <v>46048.6509980093</v>
       </c>
       <c r="E485" s="2">
-        <v>82017</v>
+        <v>81890</v>
       </c>
       <c r="F485" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>9</v>
@@ -13055,16 +13055,16 @@
         <v>33</v>
       </c>
       <c r="C486" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D486" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E486" s="2">
-        <v>82020</v>
+        <v>81875</v>
       </c>
       <c r="F486" s="3">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>9</v>
@@ -13081,16 +13081,16 @@
         <v>33</v>
       </c>
       <c r="C487" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D487" s="3">
-        <v>46056.7073643981</v>
+        <v>46049.4871256134</v>
       </c>
       <c r="E487" s="2">
-        <v>82023</v>
+        <v>81881</v>
       </c>
       <c r="F487" s="3">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>9</v>
@@ -13113,10 +13113,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E488" s="2">
-        <v>82061</v>
+        <v>82015</v>
       </c>
       <c r="F488" s="3">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>9</v>
@@ -13139,10 +13139,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E489" s="2">
-        <v>82081</v>
+        <v>82017</v>
       </c>
       <c r="F489" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>9</v>
@@ -13165,10 +13165,10 @@
         <v>46056.7073643981</v>
       </c>
       <c r="E490" s="2">
-        <v>82095</v>
+        <v>82020</v>
       </c>
       <c r="F490" s="3">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>9</v>
@@ -13185,16 +13185,16 @@
         <v>33</v>
       </c>
       <c r="C491" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D491" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E491" s="2">
-        <v>82081</v>
+        <v>82023</v>
       </c>
       <c r="F491" s="3">
-        <v>46063</v>
+        <v>46058</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>9</v>
@@ -13211,16 +13211,16 @@
         <v>33</v>
       </c>
       <c r="C492" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D492" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E492" s="2">
-        <v>82107</v>
+        <v>82061</v>
       </c>
       <c r="F492" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="G492" s="1" t="s">
         <v>9</v>
@@ -13237,16 +13237,16 @@
         <v>33</v>
       </c>
       <c r="C493" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D493" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E493" s="2">
-        <v>82112</v>
+        <v>82081</v>
       </c>
       <c r="F493" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="G493" s="1" t="s">
         <v>9</v>
@@ -13263,13 +13263,13 @@
         <v>33</v>
       </c>
       <c r="C494" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D494" s="3">
-        <v>46062.7129743866</v>
+        <v>46056.7073643981</v>
       </c>
       <c r="E494" s="2">
-        <v>82113</v>
+        <v>82095</v>
       </c>
       <c r="F494" s="3">
         <v>46064</v>
@@ -13295,10 +13295,10 @@
         <v>46062.7129743866</v>
       </c>
       <c r="E495" s="2">
-        <v>82123</v>
+        <v>82081</v>
       </c>
       <c r="F495" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>9</v>
@@ -13315,13 +13315,13 @@
         <v>33</v>
       </c>
       <c r="C496" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D496" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E496" s="2">
-        <v>82095</v>
+        <v>82107</v>
       </c>
       <c r="F496" s="3">
         <v>46064</v>
@@ -13341,13 +13341,13 @@
         <v>33</v>
       </c>
       <c r="C497" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D497" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E497" s="2">
-        <v>82106</v>
+        <v>82112</v>
       </c>
       <c r="F497" s="3">
         <v>46064</v>
@@ -13367,13 +13367,13 @@
         <v>33</v>
       </c>
       <c r="C498" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D498" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E498" s="2">
-        <v>82107</v>
+        <v>82113</v>
       </c>
       <c r="F498" s="3">
         <v>46064</v>
@@ -13393,16 +13393,16 @@
         <v>33</v>
       </c>
       <c r="C499" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D499" s="3">
-        <v>46063.5787047801</v>
+        <v>46062.7129743866</v>
       </c>
       <c r="E499" s="2">
-        <v>82109</v>
+        <v>82123</v>
       </c>
       <c r="F499" s="3">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>9</v>
@@ -13425,7 +13425,7 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E500" s="2">
-        <v>82110</v>
+        <v>82095</v>
       </c>
       <c r="F500" s="3">
         <v>46064</v>
@@ -13451,10 +13451,10 @@
         <v>46063.5787047801</v>
       </c>
       <c r="E501" s="2">
-        <v>82139</v>
+        <v>82106</v>
       </c>
       <c r="F501" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="G501" s="1" t="s">
         <v>9</v>
@@ -13471,16 +13471,16 @@
         <v>33</v>
       </c>
       <c r="C502" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D502" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E502" s="2">
-        <v>82365</v>
+        <v>82107</v>
       </c>
       <c r="F502" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G502" s="1" t="s">
         <v>9</v>
@@ -13497,16 +13497,16 @@
         <v>33</v>
       </c>
       <c r="C503" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D503" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E503" s="2">
-        <v>82366</v>
+        <v>82109</v>
       </c>
       <c r="F503" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G503" s="1" t="s">
         <v>9</v>
@@ -13523,16 +13523,16 @@
         <v>33</v>
       </c>
       <c r="C504" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D504" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E504" s="2">
-        <v>82371</v>
+        <v>82110</v>
       </c>
       <c r="F504" s="3">
-        <v>46080</v>
+        <v>46064</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>9</v>
@@ -13549,16 +13549,16 @@
         <v>33</v>
       </c>
       <c r="C505" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D505" s="3">
-        <v>46080.4604712616</v>
+        <v>46063.5787047801</v>
       </c>
       <c r="E505" s="2">
-        <v>82383</v>
+        <v>82139</v>
       </c>
       <c r="F505" s="3">
-        <v>46083</v>
+        <v>46065</v>
       </c>
       <c r="G505" s="1" t="s">
         <v>9</v>
@@ -13581,10 +13581,10 @@
         <v>46080.4604712616</v>
       </c>
       <c r="E506" s="2">
-        <v>82384</v>
+        <v>82365</v>
       </c>
       <c r="F506" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>9</v>
@@ -13601,16 +13601,16 @@
         <v>33</v>
       </c>
       <c r="C507" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D507" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E507" s="2">
-        <v>82693</v>
+        <v>82366</v>
       </c>
       <c r="F507" s="3">
-        <v>46098</v>
+        <v>46080</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>9</v>
@@ -13627,16 +13627,16 @@
         <v>33</v>
       </c>
       <c r="C508" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D508" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E508" s="2">
-        <v>82760</v>
+        <v>82371</v>
       </c>
       <c r="F508" s="3">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="G508" s="1" t="s">
         <v>9</v>
@@ -13653,16 +13653,16 @@
         <v>33</v>
       </c>
       <c r="C509" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D509" s="3">
-        <v>46098.4979333449</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E509" s="2">
-        <v>82763</v>
+        <v>82383</v>
       </c>
       <c r="F509" s="3">
-        <v>46101</v>
+        <v>46083</v>
       </c>
       <c r="G509" s="1" t="s">
         <v>9</v>
@@ -13673,48 +13673,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="510">
       <c r="A510" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C510" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D510" s="3">
-        <v>46029.4149454282</v>
+        <v>46080.4604712616</v>
       </c>
       <c r="E510" s="2">
-        <v>81592</v>
+        <v>82384</v>
       </c>
       <c r="F510" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="G510" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H510" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="511">
       <c r="A511" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C511" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D511" s="3">
-        <v>46029.4149454282</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E511" s="2">
-        <v>81593</v>
+        <v>82693</v>
       </c>
       <c r="F511" s="3">
-        <v>46031</v>
+        <v>46098</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>9</v>
@@ -13725,22 +13725,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="512">
       <c r="A512" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C512" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D512" s="3">
-        <v>46038.6827563889</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E512" s="2">
-        <v>81697</v>
+        <v>82760</v>
       </c>
       <c r="F512" s="3">
-        <v>46038</v>
+        <v>46101</v>
       </c>
       <c r="G512" s="1" t="s">
         <v>9</v>
@@ -13751,28 +13751,28 @@
     </row>
     <row ht="12.75" customHeight="1" r="513">
       <c r="A513" s="2">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C513" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D513" s="3">
-        <v>46038.6827563889</v>
+        <v>46098.4979333449</v>
       </c>
       <c r="E513" s="2">
-        <v>81735</v>
+        <v>82763</v>
       </c>
       <c r="F513" s="3">
-        <v>46041</v>
+        <v>46101</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="514">
@@ -13783,39 +13783,39 @@
         <v>34</v>
       </c>
       <c r="C514" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D514" s="3">
-        <v>46045.4532476157</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E514" s="2">
-        <v>81823</v>
+        <v>81592</v>
       </c>
       <c r="F514" s="3">
-        <v>46045</v>
+        <v>46031</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="515">
       <c r="A515" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C515" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D515" s="3">
-        <v>46031.4724550926</v>
+        <v>46029.4149454282</v>
       </c>
       <c r="E515" s="2">
-        <v>81572</v>
+        <v>81593</v>
       </c>
       <c r="F515" s="3">
         <v>46031</v>
@@ -13829,22 +13829,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="516">
       <c r="A516" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C516" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D516" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E516" s="2">
-        <v>81573</v>
+        <v>81697</v>
       </c>
       <c r="F516" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="G516" s="1" t="s">
         <v>9</v>
@@ -13855,48 +13855,48 @@
     </row>
     <row ht="12.75" customHeight="1" r="517">
       <c r="A517" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C517" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D517" s="3">
-        <v>46031.4724550926</v>
+        <v>46038.6827563889</v>
       </c>
       <c r="E517" s="2">
-        <v>81579</v>
+        <v>81735</v>
       </c>
       <c r="F517" s="3">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="518">
       <c r="A518" s="2">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C518" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D518" s="3">
-        <v>46031.4724550926</v>
+        <v>46045.4532476157</v>
       </c>
       <c r="E518" s="2">
-        <v>81580</v>
+        <v>81823</v>
       </c>
       <c r="F518" s="3">
-        <v>46031</v>
+        <v>46045</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>9</v>
@@ -13919,7 +13919,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E519" s="2">
-        <v>81581</v>
+        <v>81572</v>
       </c>
       <c r="F519" s="3">
         <v>46031</v>
@@ -13945,7 +13945,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E520" s="2">
-        <v>81582</v>
+        <v>81573</v>
       </c>
       <c r="F520" s="3">
         <v>46031</v>
@@ -13971,7 +13971,7 @@
         <v>46031.4724550926</v>
       </c>
       <c r="E521" s="2">
-        <v>81583</v>
+        <v>81579</v>
       </c>
       <c r="F521" s="3">
         <v>46031</v>
@@ -13991,16 +13991,16 @@
         <v>35</v>
       </c>
       <c r="C522" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D522" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E522" s="2">
-        <v>81667</v>
+        <v>81580</v>
       </c>
       <c r="F522" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G522" s="1" t="s">
         <v>9</v>
@@ -14017,16 +14017,16 @@
         <v>35</v>
       </c>
       <c r="C523" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D523" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E523" s="2">
-        <v>81668</v>
+        <v>81581</v>
       </c>
       <c r="F523" s="3">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>9</v>
@@ -14043,16 +14043,16 @@
         <v>35</v>
       </c>
       <c r="C524" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D524" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E524" s="2">
-        <v>81674</v>
+        <v>81582</v>
       </c>
       <c r="F524" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G524" s="1" t="s">
         <v>9</v>
@@ -14069,16 +14069,16 @@
         <v>35</v>
       </c>
       <c r="C525" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D525" s="3">
-        <v>46037.6443999306</v>
+        <v>46031.4724550926</v>
       </c>
       <c r="E525" s="2">
-        <v>81675</v>
+        <v>81583</v>
       </c>
       <c r="F525" s="3">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>9</v>
@@ -14101,10 +14101,10 @@
         <v>46037.6443999306</v>
       </c>
       <c r="E526" s="2">
-        <v>81677</v>
+        <v>81667</v>
       </c>
       <c r="F526" s="3">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="G526" s="1" t="s">
         <v>9</v>
@@ -14121,16 +14121,16 @@
         <v>35</v>
       </c>
       <c r="C527" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D527" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E527" s="2">
-        <v>81739</v>
+        <v>81668</v>
       </c>
       <c r="F527" s="3">
-        <v>46041</v>
+        <v>46037</v>
       </c>
       <c r="G527" s="1" t="s">
         <v>9</v>
@@ -14147,16 +14147,16 @@
         <v>35</v>
       </c>
       <c r="C528" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D528" s="3">
-        <v>46041.6133887269</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E528" s="2">
-        <v>81741</v>
+        <v>81674</v>
       </c>
       <c r="F528" s="3">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="G528" s="1" t="s">
         <v>9</v>
@@ -14173,16 +14173,16 @@
         <v>35</v>
       </c>
       <c r="C529" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D529" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E529" s="2">
-        <v>81854</v>
+        <v>81675</v>
       </c>
       <c r="F529" s="3">
-        <v>46048</v>
+        <v>46038</v>
       </c>
       <c r="G529" s="1" t="s">
         <v>9</v>
@@ -14199,16 +14199,16 @@
         <v>35</v>
       </c>
       <c r="C530" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D530" s="3">
-        <v>46048.7298086806</v>
+        <v>46037.6443999306</v>
       </c>
       <c r="E530" s="2">
-        <v>81855</v>
+        <v>81677</v>
       </c>
       <c r="F530" s="3">
-        <v>46048</v>
+        <v>46038</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>9</v>
@@ -14225,16 +14225,16 @@
         <v>35</v>
       </c>
       <c r="C531" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D531" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E531" s="2">
-        <v>81858</v>
+        <v>81739</v>
       </c>
       <c r="F531" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G531" s="1" t="s">
         <v>9</v>
@@ -14251,16 +14251,16 @@
         <v>35</v>
       </c>
       <c r="C532" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D532" s="3">
-        <v>46048.7298086806</v>
+        <v>46041.6133887269</v>
       </c>
       <c r="E532" s="2">
-        <v>81859</v>
+        <v>81741</v>
       </c>
       <c r="F532" s="3">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G532" s="1" t="s">
         <v>9</v>
@@ -14283,10 +14283,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E533" s="2">
-        <v>81862</v>
+        <v>81854</v>
       </c>
       <c r="F533" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G533" s="1" t="s">
         <v>9</v>
@@ -14309,10 +14309,10 @@
         <v>46048.7298086806</v>
       </c>
       <c r="E534" s="2">
-        <v>81863</v>
+        <v>81855</v>
       </c>
       <c r="F534" s="3">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="G534" s="1" t="s">
         <v>9</v>
@@ -14329,16 +14329,16 @@
         <v>35</v>
       </c>
       <c r="C535" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D535" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E535" s="2">
-        <v>81958</v>
+        <v>81858</v>
       </c>
       <c r="F535" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G535" s="1" t="s">
         <v>9</v>
@@ -14355,16 +14355,16 @@
         <v>35</v>
       </c>
       <c r="C536" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D536" s="3">
-        <v>46055.5924236111</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E536" s="2">
-        <v>81965</v>
+        <v>81859</v>
       </c>
       <c r="F536" s="3">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="G536" s="1" t="s">
         <v>9</v>
@@ -14381,16 +14381,16 @@
         <v>35</v>
       </c>
       <c r="C537" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D537" s="3">
-        <v>46063.5923590625</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E537" s="2">
-        <v>82085</v>
+        <v>81862</v>
       </c>
       <c r="F537" s="3">
-        <v>46063</v>
+        <v>46049</v>
       </c>
       <c r="G537" s="1" t="s">
         <v>9</v>
@@ -14407,16 +14407,16 @@
         <v>35</v>
       </c>
       <c r="C538" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D538" s="3">
-        <v>46063.5923590625</v>
+        <v>46048.7298086806</v>
       </c>
       <c r="E538" s="2">
-        <v>82086</v>
+        <v>81863</v>
       </c>
       <c r="F538" s="3">
-        <v>46063</v>
+        <v>46049</v>
       </c>
       <c r="G538" s="1" t="s">
         <v>9</v>
@@ -14433,16 +14433,16 @@
         <v>35</v>
       </c>
       <c r="C539" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D539" s="3">
-        <v>46063.5923590625</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E539" s="2">
-        <v>82126</v>
+        <v>81958</v>
       </c>
       <c r="F539" s="3">
-        <v>46065</v>
+        <v>46055</v>
       </c>
       <c r="G539" s="1" t="s">
         <v>9</v>
@@ -14459,16 +14459,16 @@
         <v>35</v>
       </c>
       <c r="C540" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D540" s="3">
-        <v>46064.5127051505</v>
+        <v>46055.5924236111</v>
       </c>
       <c r="E540" s="2">
-        <v>82268</v>
+        <v>81965</v>
       </c>
       <c r="F540" s="3">
-        <v>46077</v>
+        <v>46055</v>
       </c>
       <c r="G540" s="1" t="s">
         <v>9</v>
@@ -14485,16 +14485,16 @@
         <v>35</v>
       </c>
       <c r="C541" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D541" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E541" s="2">
-        <v>82142</v>
+        <v>82085</v>
       </c>
       <c r="F541" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G541" s="1" t="s">
         <v>9</v>
@@ -14511,16 +14511,16 @@
         <v>35</v>
       </c>
       <c r="C542" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D542" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E542" s="2">
-        <v>82143</v>
+        <v>82086</v>
       </c>
       <c r="F542" s="3">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="G542" s="1" t="s">
         <v>9</v>
@@ -14537,13 +14537,13 @@
         <v>35</v>
       </c>
       <c r="C543" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D543" s="3">
-        <v>46065.6275788773</v>
+        <v>46063.5923590625</v>
       </c>
       <c r="E543" s="2">
-        <v>82144</v>
+        <v>82126</v>
       </c>
       <c r="F543" s="3">
         <v>46065</v>
@@ -14563,16 +14563,16 @@
         <v>35</v>
       </c>
       <c r="C544" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D544" s="3">
-        <v>46065.6275788773</v>
+        <v>46064.5127051505</v>
       </c>
       <c r="E544" s="2">
-        <v>82166</v>
+        <v>82268</v>
       </c>
       <c r="F544" s="3">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="G544" s="1" t="s">
         <v>9</v>
@@ -14589,16 +14589,16 @@
         <v>35</v>
       </c>
       <c r="C545" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D545" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E545" s="2">
-        <v>82262</v>
+        <v>82142</v>
       </c>
       <c r="F545" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G545" s="1" t="s">
         <v>9</v>
@@ -14615,16 +14615,16 @@
         <v>35</v>
       </c>
       <c r="C546" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D546" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E546" s="2">
-        <v>82265</v>
+        <v>82143</v>
       </c>
       <c r="F546" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G546" s="1" t="s">
         <v>9</v>
@@ -14641,16 +14641,16 @@
         <v>35</v>
       </c>
       <c r="C547" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D547" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E547" s="2">
-        <v>82281</v>
+        <v>82144</v>
       </c>
       <c r="F547" s="3">
-        <v>46077</v>
+        <v>46065</v>
       </c>
       <c r="G547" s="1" t="s">
         <v>9</v>
@@ -14667,16 +14667,16 @@
         <v>35</v>
       </c>
       <c r="C548" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D548" s="3">
-        <v>46077.406463831</v>
+        <v>46065.6275788773</v>
       </c>
       <c r="E548" s="2">
-        <v>82282</v>
+        <v>82166</v>
       </c>
       <c r="F548" s="3">
-        <v>46077</v>
+        <v>46066</v>
       </c>
       <c r="G548" s="1" t="s">
         <v>9</v>
@@ -14693,16 +14693,16 @@
         <v>35</v>
       </c>
       <c r="C549" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D549" s="3">
-        <v>46079.5782408912</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E549" s="2">
-        <v>82340</v>
+        <v>82262</v>
       </c>
       <c r="F549" s="3">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="G549" s="1" t="s">
         <v>9</v>
@@ -14719,16 +14719,16 @@
         <v>35</v>
       </c>
       <c r="C550" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D550" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E550" s="2">
-        <v>82399</v>
+        <v>82265</v>
       </c>
       <c r="F550" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G550" s="1" t="s">
         <v>9</v>
@@ -14745,16 +14745,16 @@
         <v>35</v>
       </c>
       <c r="C551" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D551" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E551" s="2">
-        <v>82400</v>
+        <v>82281</v>
       </c>
       <c r="F551" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G551" s="1" t="s">
         <v>9</v>
@@ -14771,16 +14771,16 @@
         <v>35</v>
       </c>
       <c r="C552" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D552" s="3">
-        <v>46083.6671321991</v>
+        <v>46077.406463831</v>
       </c>
       <c r="E552" s="2">
-        <v>82401</v>
+        <v>82282</v>
       </c>
       <c r="F552" s="3">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="G552" s="1" t="s">
         <v>9</v>
@@ -14797,16 +14797,16 @@
         <v>35</v>
       </c>
       <c r="C553" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D553" s="3">
-        <v>46083.6671321991</v>
+        <v>46079.5782408912</v>
       </c>
       <c r="E553" s="2">
-        <v>82412</v>
+        <v>82340</v>
       </c>
       <c r="F553" s="3">
-        <v>46084</v>
+        <v>46079</v>
       </c>
       <c r="G553" s="1" t="s">
         <v>9</v>
@@ -14829,10 +14829,10 @@
         <v>46083.6671321991</v>
       </c>
       <c r="E554" s="2">
-        <v>82415</v>
+        <v>82399</v>
       </c>
       <c r="F554" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="G554" s="1" t="s">
         <v>9</v>
@@ -14849,16 +14849,16 @@
         <v>35</v>
       </c>
       <c r="C555" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D555" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E555" s="2">
-        <v>82571</v>
+        <v>82400</v>
       </c>
       <c r="F555" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G555" s="1" t="s">
         <v>9</v>
@@ -14875,16 +14875,16 @@
         <v>35</v>
       </c>
       <c r="C556" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D556" s="3">
-        <v>46086.6312882639</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E556" s="2">
-        <v>82572</v>
+        <v>82401</v>
       </c>
       <c r="F556" s="3">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="G556" s="1" t="s">
         <v>9</v>
@@ -14901,16 +14901,16 @@
         <v>35</v>
       </c>
       <c r="C557" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D557" s="3">
-        <v>46094.4745190394</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E557" s="2">
-        <v>82630</v>
+        <v>82412</v>
       </c>
       <c r="F557" s="3">
-        <v>46094</v>
+        <v>46084</v>
       </c>
       <c r="G557" s="1" t="s">
         <v>9</v>
@@ -14927,16 +14927,16 @@
         <v>35</v>
       </c>
       <c r="C558" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D558" s="3">
-        <v>46094.4745190394</v>
+        <v>46083.6671321991</v>
       </c>
       <c r="E558" s="2">
-        <v>82631</v>
+        <v>82415</v>
       </c>
       <c r="F558" s="3">
-        <v>46094</v>
+        <v>46084</v>
       </c>
       <c r="G558" s="1" t="s">
         <v>9</v>
@@ -14953,16 +14953,16 @@
         <v>35</v>
       </c>
       <c r="C559" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D559" s="3">
-        <v>46094.4745190394</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E559" s="2">
-        <v>82632</v>
+        <v>82571</v>
       </c>
       <c r="F559" s="3">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="G559" s="1" t="s">
         <v>9</v>
@@ -14979,16 +14979,16 @@
         <v>35</v>
       </c>
       <c r="C560" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D560" s="3">
-        <v>46097.4499278356</v>
+        <v>46086.6312882639</v>
       </c>
       <c r="E560" s="2">
-        <v>82653</v>
+        <v>82572</v>
       </c>
       <c r="F560" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="G560" s="1" t="s">
         <v>9</v>
@@ -15005,16 +15005,16 @@
         <v>35</v>
       </c>
       <c r="C561" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D561" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E561" s="2">
-        <v>82665</v>
+        <v>82630</v>
       </c>
       <c r="F561" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G561" s="1" t="s">
         <v>9</v>
@@ -15031,16 +15031,16 @@
         <v>35</v>
       </c>
       <c r="C562" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D562" s="3">
-        <v>46097.4499278356</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E562" s="2">
-        <v>82668</v>
+        <v>82631</v>
       </c>
       <c r="F562" s="3">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="G562" s="1" t="s">
         <v>9</v>
@@ -15057,16 +15057,16 @@
         <v>35</v>
       </c>
       <c r="C563" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D563" s="3">
-        <v>46098.6661386574</v>
+        <v>46094.4745190394</v>
       </c>
       <c r="E563" s="2">
-        <v>82696</v>
+        <v>82632</v>
       </c>
       <c r="F563" s="3">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="G563" s="1" t="s">
         <v>9</v>
@@ -15083,16 +15083,16 @@
         <v>35</v>
       </c>
       <c r="C564" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D564" s="3">
-        <v>46098.6661386574</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E564" s="2">
-        <v>82704</v>
+        <v>82653</v>
       </c>
       <c r="F564" s="3">
-        <v>46099</v>
+        <v>46097</v>
       </c>
       <c r="G564" s="1" t="s">
         <v>9</v>
@@ -15103,22 +15103,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="565">
       <c r="A565" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C565" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D565" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E565" s="2">
-        <v>82311</v>
+        <v>82665</v>
       </c>
       <c r="F565" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G565" s="1" t="s">
         <v>9</v>
@@ -15129,22 +15129,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="566">
       <c r="A566" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C566" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D566" s="3">
-        <v>46078.6702738773</v>
+        <v>46097.4499278356</v>
       </c>
       <c r="E566" s="2">
-        <v>82312</v>
+        <v>82668</v>
       </c>
       <c r="F566" s="3">
-        <v>46078</v>
+        <v>46097</v>
       </c>
       <c r="G566" s="1" t="s">
         <v>9</v>
@@ -15155,22 +15155,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="567">
       <c r="A567" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C567" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D567" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E567" s="2">
-        <v>82313</v>
+        <v>82696</v>
       </c>
       <c r="F567" s="3">
-        <v>46078</v>
+        <v>46098</v>
       </c>
       <c r="G567" s="1" t="s">
         <v>9</v>
@@ -15181,22 +15181,22 @@
     </row>
     <row ht="12.75" customHeight="1" r="568">
       <c r="A568" s="2">
-        <v>2601</v>
+        <v>2516</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C568" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D568" s="3">
-        <v>46078.6702738773</v>
+        <v>46098.6661386574</v>
       </c>
       <c r="E568" s="2">
-        <v>82314</v>
+        <v>82704</v>
       </c>
       <c r="F568" s="3">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="G568" s="1" t="s">
         <v>9</v>
@@ -15219,10 +15219,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E569" s="2">
-        <v>82346</v>
+        <v>82311</v>
       </c>
       <c r="F569" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G569" s="1" t="s">
         <v>9</v>
@@ -15245,10 +15245,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E570" s="2">
-        <v>82361</v>
+        <v>82312</v>
       </c>
       <c r="F570" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="G570" s="1" t="s">
         <v>9</v>
@@ -15271,10 +15271,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E571" s="2">
-        <v>82385</v>
+        <v>82313</v>
       </c>
       <c r="F571" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G571" s="1" t="s">
         <v>9</v>
@@ -15297,10 +15297,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E572" s="2">
-        <v>82391</v>
+        <v>82314</v>
       </c>
       <c r="F572" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="G572" s="1" t="s">
         <v>9</v>
@@ -15323,10 +15323,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="E573" s="2">
-        <v>82392</v>
+        <v>82346</v>
       </c>
       <c r="F573" s="3">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="G573" s="1" t="s">
         <v>9</v>
@@ -15343,16 +15343,16 @@
         <v>36</v>
       </c>
       <c r="C574" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D574" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E574" s="2">
-        <v>82691</v>
+        <v>82361</v>
       </c>
       <c r="F574" s="3">
-        <v>46098</v>
+        <v>46080</v>
       </c>
       <c r="G574" s="1" t="s">
         <v>9</v>
@@ -15369,16 +15369,16 @@
         <v>36</v>
       </c>
       <c r="C575" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D575" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E575" s="2">
-        <v>82692</v>
+        <v>82385</v>
       </c>
       <c r="F575" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G575" s="1" t="s">
         <v>9</v>
@@ -15395,16 +15395,16 @@
         <v>36</v>
       </c>
       <c r="C576" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D576" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E576" s="2">
-        <v>82699</v>
+        <v>82391</v>
       </c>
       <c r="F576" s="3">
-        <v>46098</v>
+        <v>46083</v>
       </c>
       <c r="G576" s="1" t="s">
         <v>9</v>
@@ -15421,16 +15421,16 @@
         <v>36</v>
       </c>
       <c r="C577" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D577" s="3">
-        <v>46097.4682502893</v>
+        <v>46078.6702738773</v>
       </c>
       <c r="E577" s="2">
-        <v>82716</v>
+        <v>82392</v>
       </c>
       <c r="F577" s="3">
-        <v>46099</v>
+        <v>46083</v>
       </c>
       <c r="G577" s="1" t="s">
         <v>9</v>
@@ -15453,10 +15453,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E578" s="2">
-        <v>82717</v>
+        <v>82691</v>
       </c>
       <c r="F578" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G578" s="1" t="s">
         <v>9</v>
@@ -15479,10 +15479,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="E579" s="2">
-        <v>82786</v>
+        <v>82692</v>
       </c>
       <c r="F579" s="3">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="G579" s="1" t="s">
         <v>9</v>
@@ -15499,16 +15499,16 @@
         <v>36</v>
  